--- a/file/table/DAPC_ProyectoCAD.xlsx
+++ b/file/table/DAPC_ProyectoCAD.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{626358DA-A121-4446-8439-4ACFBE7BFFC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6738C9D-B331-441B-AFD2-349C202BAAEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1.Técnicas" sheetId="2" r:id="rId1"/>
     <sheet name="2.Arquitectónica" sheetId="4" r:id="rId2"/>
     <sheet name="3.Eléctrica" sheetId="5" r:id="rId3"/>
-    <sheet name="3.Bodegaje" sheetId="6" r:id="rId4"/>
+    <sheet name="3.Planos" sheetId="6" r:id="rId4"/>
     <sheet name="Files" sheetId="1" r:id="rId5"/>
     <sheet name="Metadata" sheetId="3" r:id="rId6"/>
   </sheets>
@@ -72,7 +72,7 @@
     <author>Test</author>
   </authors>
   <commentList>
-    <comment ref="E6" authorId="0" shapeId="0" xr:uid="{0CB28302-451A-4555-A660-A2220D7B31D2}">
+    <comment ref="E6" authorId="0" shapeId="0" xr:uid="{3B399783-EF46-4E16-BEE3-FB6A7B4FB7D8}">
       <text>
         <r>
           <rPr>
@@ -81,7 +81,8 @@
             <rFont val="Segoe UI Light"/>
             <family val="2"/>
           </rPr>
-          <t>Un. corresponde a Unidad.</t>
+          <t>Un. corresponde a Unidad.
+n/a: no aplica.</t>
         </r>
       </text>
     </comment>
@@ -109,7 +110,7 @@
     <author>Test</author>
   </authors>
   <commentList>
-    <comment ref="E6" authorId="0" shapeId="0" xr:uid="{C543050A-FDED-428A-9308-BA8924B01043}">
+    <comment ref="E6" authorId="0" shapeId="0" xr:uid="{B52C7FAF-2ACF-4F89-851C-376A59298D24}">
       <text>
         <r>
           <rPr>
@@ -118,7 +119,8 @@
             <rFont val="Segoe UI Light"/>
             <family val="2"/>
           </rPr>
-          <t>Un. corresponde a Unidad.</t>
+          <t>Un. corresponde a Unidad.
+n/a: no aplica.</t>
         </r>
       </text>
     </comment>
@@ -155,7 +157,8 @@
             <rFont val="Segoe UI Light"/>
             <family val="2"/>
           </rPr>
-          <t>Un. corresponde a Unidad.</t>
+          <t>Un. corresponde a Unidad.
+n/a: no aplica.</t>
         </r>
       </text>
     </comment>
@@ -178,7 +181,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="278">
   <si>
     <t>1. Especificaciones técnicas generales</t>
   </si>
@@ -881,9 +884,6 @@
     <t>Largo de bodega - Proyecto</t>
   </si>
   <si>
-    <t>Cuadro de cantidades (resumen a incluir en planos)</t>
-  </si>
-  <si>
     <t>Placa de contra piso - Área</t>
   </si>
   <si>
@@ -1131,6 +1131,87 @@
   </si>
   <si>
     <t>En un proyecto, las especificaciones eléctricas son un conjunto de directrices técnicas que describen detalladamente las características y requisitos de los componentes y equipos eléctricos que se utilizarán. Estas especificaciones aseguran que la instalación eléctrica sea segura, confiable y cumpla con los estándares y normativas aplicables.</t>
+  </si>
+  <si>
+    <t>Separación entre estantes</t>
+  </si>
+  <si>
+    <t>Estantería</t>
+  </si>
+  <si>
+    <t>Altura máxima de montacargas</t>
+  </si>
+  <si>
+    <t>Número de niveles en estantes</t>
+  </si>
+  <si>
+    <t>Nivel</t>
+  </si>
+  <si>
+    <t>Ancho de estante</t>
+  </si>
+  <si>
+    <t>Alto de entrepiso en estante</t>
+  </si>
+  <si>
+    <t>Separación o ancho del corredor por donde se desplaza el montacargas industrial.</t>
+  </si>
+  <si>
+    <t>Ancho total del estante. En zonas internas se pueden colocar en hileras de dos, en costados de bodega solo una hilera.</t>
+  </si>
+  <si>
+    <t>Altura del entrepiso incluyendo el espesor de la base.</t>
+  </si>
+  <si>
+    <t>Altura máxima que puede elevar el montacargas, requerido para definir la altura superior de la estantería.</t>
+  </si>
+  <si>
+    <t>Elevación de piso del último estante</t>
+  </si>
+  <si>
+    <t>Indique la referencia y cantidad de elementos a almacenar en la bodega. Para la distribución en estantes, los transformadores grandes se almacenan en la parte inferior, los medianos en los estantes intermedios y los livianos en la parte superior.</t>
+  </si>
+  <si>
+    <t>Calcular</t>
+  </si>
+  <si>
+    <t>Corresponde al número de pisos que tendrá la estantería incluído el piso a nivel de placa.</t>
+  </si>
+  <si>
+    <t>Esta elevación no debe ser superior a la altura vertical de desplazamiento del montacarga.</t>
+  </si>
+  <si>
+    <t>Verificación de montacarga</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Verificación de desplazamiento para carga y descarga del montacargas.</t>
+  </si>
+  <si>
+    <t>Longitud total de estantería en planta</t>
+  </si>
+  <si>
+    <t>Distribuir dentro de la bodeda y medir.</t>
+  </si>
+  <si>
+    <t>Longitud total de estantería en todos los niveles</t>
+  </si>
+  <si>
+    <t>Valor longitudinal por número de niveles.</t>
+  </si>
+  <si>
+    <t>Transformador 1 - Ref: #####</t>
+  </si>
+  <si>
+    <t>Transformador 2 - Ref: #####</t>
+  </si>
+  <si>
+    <t>Transformador 3 - Ref: #####</t>
+  </si>
+  <si>
+    <t>Cuadro de cantidades (resumen a incluir en planos, no es necesario realizar costos unitarios)</t>
   </si>
 </sst>
 </file>
@@ -2133,7 +2214,7 @@
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B4" s="86" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C4" s="86"/>
       <c r="D4" s="86"/>
@@ -2460,7 +2541,7 @@
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B4" s="86" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C4" s="86"/>
       <c r="D4" s="86"/>
@@ -2587,7 +2668,7 @@
         <v>45</v>
       </c>
       <c r="C12" s="40" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D12" s="41">
         <v>12</v>
@@ -2770,7 +2851,7 @@
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B23" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C23" s="37"/>
       <c r="D23" s="38"/>
@@ -3295,7 +3376,7 @@
         <v>140</v>
       </c>
       <c r="C55" s="40" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D55" s="41">
         <v>6</v>
@@ -3312,7 +3393,7 @@
         <v>141</v>
       </c>
       <c r="C56" s="40" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D56" s="41">
         <v>4.5</v>
@@ -3343,10 +3424,10 @@
     </row>
     <row r="58" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B58" s="35" t="s">
+        <v>201</v>
+      </c>
+      <c r="C58" s="40" t="s">
         <v>202</v>
-      </c>
-      <c r="C58" s="40" t="s">
-        <v>203</v>
       </c>
       <c r="D58" s="41">
         <v>2.2999999999999998</v>
@@ -3363,7 +3444,7 @@
         <v>144</v>
       </c>
       <c r="C59" s="40" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D59" s="41">
         <v>3</v>
@@ -3377,10 +3458,10 @@
     </row>
     <row r="60" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
       <c r="B60" s="35" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C60" s="40" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D60" s="41">
         <v>2</v>
@@ -3414,7 +3495,7 @@
     </row>
     <row r="63" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
       <c r="B63" s="35" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C63" s="40" t="s">
         <v>117</v>
@@ -3431,10 +3512,10 @@
     </row>
     <row r="64" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
       <c r="B64" s="35" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="C64" s="40" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D64" s="54">
         <f>D18</f>
@@ -3740,7 +3821,7 @@
     </row>
     <row r="90" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B90" s="2" t="s">
-        <v>183</v>
+        <v>277</v>
       </c>
     </row>
     <row r="91" spans="2:5" x14ac:dyDescent="0.45">
@@ -3759,10 +3840,10 @@
     </row>
     <row r="92" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B92" s="35" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C92" s="29" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D92" s="73">
         <f>D64</f>
@@ -3774,25 +3855,25 @@
     </row>
     <row r="93" spans="2:5" ht="33" x14ac:dyDescent="0.45">
       <c r="B93" s="35" t="s">
+        <v>188</v>
+      </c>
+      <c r="C93" s="29" t="s">
         <v>189</v>
-      </c>
-      <c r="C93" s="29" t="s">
-        <v>190</v>
       </c>
       <c r="D93" s="73">
         <f>D92*D63</f>
         <v>57400</v>
       </c>
       <c r="E93" s="11" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="94" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B94" s="35" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C94" s="29" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D94" s="73">
         <f>D49</f>
@@ -3804,10 +3885,10 @@
     </row>
     <row r="95" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B95" s="35" t="s">
+        <v>192</v>
+      </c>
+      <c r="C95" s="29" t="s">
         <v>193</v>
-      </c>
-      <c r="C95" s="29" t="s">
-        <v>194</v>
       </c>
       <c r="D95" s="73">
         <f>D69</f>
@@ -3819,10 +3900,10 @@
     </row>
     <row r="96" spans="2:5" ht="33" x14ac:dyDescent="0.45">
       <c r="B96" s="35" t="s">
+        <v>194</v>
+      </c>
+      <c r="C96" s="29" t="s">
         <v>195</v>
-      </c>
-      <c r="C96" s="29" t="s">
-        <v>196</v>
       </c>
       <c r="D96" s="73">
         <f>D95*D12</f>
@@ -3834,10 +3915,10 @@
     </row>
     <row r="97" spans="2:5" ht="49.5" x14ac:dyDescent="0.45">
       <c r="B97" s="35" t="s">
+        <v>196</v>
+      </c>
+      <c r="C97" s="29" t="s">
         <v>197</v>
-      </c>
-      <c r="C97" s="29" t="s">
-        <v>198</v>
       </c>
       <c r="D97" s="73">
         <f>((D67*D9)+(D68*D8))*INT(D12/D48)</f>
@@ -3849,13 +3930,13 @@
     </row>
     <row r="98" spans="2:5" ht="33" x14ac:dyDescent="0.45">
       <c r="B98" s="50" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C98" s="31" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D98" s="76" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E98" s="11" t="s">
         <v>60</v>
@@ -3863,10 +3944,10 @@
     </row>
     <row r="99" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B99" s="50" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C99" s="31" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D99" s="76">
         <v>2</v>
@@ -3880,10 +3961,10 @@
         <v>52</v>
       </c>
       <c r="C100" s="31" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D100" s="76" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E100" s="11" t="s">
         <v>129</v>
@@ -3894,10 +3975,10 @@
         <v>53</v>
       </c>
       <c r="C101" s="31" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D101" s="76" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="E101" s="11" t="s">
         <v>129</v>
@@ -3994,7 +4075,7 @@
     </row>
     <row r="4" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B4" s="86" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C4" s="86"/>
       <c r="D4" s="86"/>
@@ -4048,10 +4129,10 @@
     </row>
     <row r="8" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
       <c r="B8" s="35" t="s">
+        <v>214</v>
+      </c>
+      <c r="C8" s="40" t="s">
         <v>215</v>
-      </c>
-      <c r="C8" s="40" t="s">
-        <v>216</v>
       </c>
       <c r="D8" s="34">
         <v>1</v>
@@ -4074,7 +4155,7 @@
     </row>
     <row r="10" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="B10" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C10" s="37"/>
       <c r="D10" s="38"/>
@@ -4085,10 +4166,10 @@
     </row>
     <row r="11" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
       <c r="B11" s="35" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C11" s="40" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D11" s="34">
         <v>1</v>
@@ -4102,10 +4183,10 @@
     </row>
     <row r="12" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="B12" s="35" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="C12" s="40" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D12" s="34">
         <v>1</v>
@@ -4119,10 +4200,10 @@
     </row>
     <row r="13" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="B13" s="35" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="C13" s="40" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="D13" s="34">
         <v>1</v>
@@ -4136,10 +4217,10 @@
     </row>
     <row r="14" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
       <c r="B14" s="35" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C14" s="40" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D14" s="34">
         <v>1</v>
@@ -4153,10 +4234,10 @@
     </row>
     <row r="15" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
       <c r="B15" s="50" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C15" s="40" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D15" s="34">
         <v>1</v>
@@ -4170,10 +4251,10 @@
     </row>
     <row r="16" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="B16" s="50" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C16" s="40" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D16" s="34">
         <v>1</v>
@@ -4187,10 +4268,10 @@
     </row>
     <row r="17" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="B17" s="35" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C17" s="40" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D17" s="34">
         <v>1</v>
@@ -4204,10 +4285,10 @@
     </row>
     <row r="18" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="B18" s="35" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C18" s="40" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D18" s="34">
         <v>1</v>
@@ -4221,10 +4302,10 @@
     </row>
     <row r="19" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="B19" s="50" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C19" s="40" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D19" s="34">
         <v>1</v>
@@ -4238,10 +4319,10 @@
     </row>
     <row r="20" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="B20" s="50" t="s">
+        <v>219</v>
+      </c>
+      <c r="C20" s="40" t="s">
         <v>220</v>
-      </c>
-      <c r="C20" s="40" t="s">
-        <v>221</v>
       </c>
       <c r="D20" s="34">
         <v>1</v>
@@ -4255,10 +4336,10 @@
     </row>
     <row r="21" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="B21" s="50" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C21" s="40" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D21" s="52">
         <v>1</v>
@@ -4272,10 +4353,10 @@
     </row>
     <row r="22" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="B22" s="50" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C22" s="40" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D22" s="52">
         <v>1</v>
@@ -4298,7 +4379,7 @@
     </row>
     <row r="24" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="B24" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C24" s="37"/>
       <c r="D24" s="38"/>
@@ -4309,10 +4390,10 @@
     </row>
     <row r="25" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
       <c r="B25" s="35" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C25" s="40" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D25" s="54">
         <f>'2.Arquitectónica'!D31-'2.Arquitectónica'!D37-'2.Arquitectónica'!D43</f>
@@ -4327,10 +4408,10 @@
     </row>
     <row r="26" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="B26" s="35" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C26" s="40" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D26" s="41">
         <v>992</v>
@@ -4344,10 +4425,10 @@
     </row>
     <row r="27" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="B27" s="35" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C27" s="40" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D27" s="41">
         <v>1950</v>
@@ -4361,10 +4442,10 @@
     </row>
     <row r="28" spans="2:8" ht="51" x14ac:dyDescent="0.45">
       <c r="B28" s="35" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C28" s="40" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D28" s="34">
         <f>INT(D25/(D26/1000*D27/1000))</f>
@@ -4416,12 +4497,12 @@
     </row>
     <row r="3" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="B3" s="20" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B4" s="86" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C4" s="86"/>
       <c r="D4" s="86"/>
@@ -4464,7 +4545,7 @@
     </row>
     <row r="7" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="B7" s="6" t="s">
-        <v>71</v>
+        <v>252</v>
       </c>
       <c r="C7" s="37"/>
       <c r="D7" s="38"/>
@@ -4473,101 +4554,166 @@
       <c r="G7" s="37"/>
       <c r="H7" s="39"/>
     </row>
-    <row r="8" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="B8" s="35" t="s">
-        <v>215</v>
+        <v>251</v>
       </c>
       <c r="C8" s="40" t="s">
-        <v>216</v>
-      </c>
-      <c r="D8" s="34">
-        <v>1</v>
+        <v>258</v>
+      </c>
+      <c r="D8" s="41">
+        <v>3</v>
       </c>
       <c r="E8" s="34" t="s">
-        <v>129</v>
+        <v>59</v>
       </c>
       <c r="F8" s="34"/>
       <c r="G8" s="29"/>
       <c r="H8" s="36"/>
     </row>
-    <row r="9" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="B9" s="35"/>
-      <c r="C9" s="40"/>
-      <c r="D9" s="34"/>
-      <c r="E9" s="34"/>
+    <row r="9" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
+      <c r="B9" s="35" t="s">
+        <v>256</v>
+      </c>
+      <c r="C9" s="40" t="s">
+        <v>259</v>
+      </c>
+      <c r="D9" s="41">
+        <v>2.5</v>
+      </c>
+      <c r="E9" s="34" t="s">
+        <v>59</v>
+      </c>
       <c r="F9" s="34"/>
       <c r="G9" s="29"/>
       <c r="H9" s="36"/>
     </row>
-    <row r="10" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="B10" s="6" t="s">
-        <v>247</v>
-      </c>
-      <c r="C10" s="37"/>
-      <c r="D10" s="38"/>
-      <c r="E10" s="38"/>
-      <c r="F10" s="38"/>
-      <c r="G10" s="37"/>
-      <c r="H10" s="39"/>
+    <row r="10" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
+      <c r="B10" s="35" t="s">
+        <v>254</v>
+      </c>
+      <c r="C10" s="40" t="s">
+        <v>265</v>
+      </c>
+      <c r="D10" s="41">
+        <v>4</v>
+      </c>
+      <c r="E10" s="34" t="s">
+        <v>255</v>
+      </c>
+      <c r="F10" s="34"/>
+      <c r="G10" s="29"/>
+      <c r="H10" s="36"/>
     </row>
     <row r="11" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="B11" s="35"/>
-      <c r="C11" s="40"/>
-      <c r="D11" s="34"/>
-      <c r="E11" s="34"/>
+      <c r="B11" s="35" t="s">
+        <v>257</v>
+      </c>
+      <c r="C11" s="40" t="s">
+        <v>260</v>
+      </c>
+      <c r="D11" s="41">
+        <v>2</v>
+      </c>
+      <c r="E11" s="34" t="s">
+        <v>59</v>
+      </c>
       <c r="F11" s="34"/>
       <c r="G11" s="29"/>
       <c r="H11" s="36"/>
     </row>
-    <row r="12" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="B12" s="35"/>
-      <c r="C12" s="40"/>
-      <c r="D12" s="34"/>
-      <c r="E12" s="34"/>
+    <row r="12" spans="2:8" ht="33" x14ac:dyDescent="0.45">
+      <c r="B12" s="35" t="s">
+        <v>262</v>
+      </c>
+      <c r="C12" s="40" t="s">
+        <v>266</v>
+      </c>
+      <c r="D12" s="34">
+        <f>D10*D11</f>
+        <v>8</v>
+      </c>
+      <c r="E12" s="34" t="s">
+        <v>59</v>
+      </c>
       <c r="F12" s="34"/>
       <c r="G12" s="29"/>
       <c r="H12" s="36"/>
     </row>
-    <row r="13" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="B13" s="35"/>
-      <c r="C13" s="40"/>
-      <c r="D13" s="34"/>
-      <c r="E13" s="34"/>
+    <row r="13" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
+      <c r="B13" s="35" t="s">
+        <v>253</v>
+      </c>
+      <c r="C13" s="40" t="s">
+        <v>261</v>
+      </c>
+      <c r="D13" s="41">
+        <v>8</v>
+      </c>
+      <c r="E13" s="34" t="s">
+        <v>59</v>
+      </c>
       <c r="F13" s="34"/>
       <c r="G13" s="29"/>
       <c r="H13" s="36"/>
     </row>
     <row r="14" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="B14" s="35"/>
-      <c r="C14" s="40"/>
-      <c r="D14" s="34"/>
-      <c r="E14" s="34"/>
+      <c r="B14" s="35" t="s">
+        <v>267</v>
+      </c>
+      <c r="C14" s="40" t="s">
+        <v>269</v>
+      </c>
+      <c r="D14" s="34" t="str">
+        <f>IF(D12&lt;=D13, "Cumple","No cumple")</f>
+        <v>Cumple</v>
+      </c>
+      <c r="E14" s="34" t="s">
+        <v>268</v>
+      </c>
       <c r="F14" s="34"/>
       <c r="G14" s="29"/>
       <c r="H14" s="36"/>
     </row>
-    <row r="15" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="B15" s="50"/>
-      <c r="C15" s="40"/>
-      <c r="D15" s="34"/>
-      <c r="E15" s="34"/>
-      <c r="F15" s="52"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="53"/>
-    </row>
-    <row r="16" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="B16" s="50"/>
-      <c r="C16" s="40"/>
-      <c r="D16" s="34"/>
-      <c r="E16" s="34"/>
-      <c r="F16" s="52"/>
-      <c r="G16" s="31"/>
-      <c r="H16" s="53"/>
+    <row r="15" spans="2:8" ht="33" x14ac:dyDescent="0.45">
+      <c r="B15" s="35" t="s">
+        <v>270</v>
+      </c>
+      <c r="C15" s="40" t="s">
+        <v>271</v>
+      </c>
+      <c r="D15" s="41">
+        <v>60</v>
+      </c>
+      <c r="E15" s="34" t="s">
+        <v>59</v>
+      </c>
+      <c r="F15" s="34"/>
+      <c r="G15" s="29"/>
+      <c r="H15" s="36"/>
+    </row>
+    <row r="16" spans="2:8" ht="33" x14ac:dyDescent="0.45">
+      <c r="B16" s="35" t="s">
+        <v>272</v>
+      </c>
+      <c r="C16" s="40" t="s">
+        <v>273</v>
+      </c>
+      <c r="D16" s="34">
+        <f>D15*D10</f>
+        <v>240</v>
+      </c>
+      <c r="E16" s="34" t="s">
+        <v>59</v>
+      </c>
+      <c r="F16" s="34"/>
+      <c r="G16" s="29"/>
+      <c r="H16" s="36"/>
     </row>
     <row r="17" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="B17" s="35"/>
       <c r="C17" s="40"/>
-      <c r="D17" s="34"/>
+      <c r="D17" s="41"/>
       <c r="E17" s="34"/>
       <c r="F17" s="34"/>
       <c r="G17" s="29"/>
@@ -4583,40 +4729,66 @@
       <c r="H18" s="36"/>
     </row>
     <row r="19" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="B19" s="50"/>
-      <c r="C19" s="40"/>
-      <c r="D19" s="34"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="52"/>
-      <c r="G19" s="31"/>
-      <c r="H19" s="53"/>
-    </row>
-    <row r="20" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="B20" s="50"/>
-      <c r="C20" s="40"/>
-      <c r="D20" s="34"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="52"/>
-      <c r="G20" s="31"/>
-      <c r="H20" s="53"/>
-    </row>
-    <row r="21" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="B21" s="50"/>
-      <c r="C21" s="40"/>
-      <c r="D21" s="52"/>
-      <c r="E21" s="34"/>
-      <c r="F21" s="52"/>
-      <c r="G21" s="31"/>
-      <c r="H21" s="53"/>
-    </row>
-    <row r="22" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="B22" s="50"/>
-      <c r="C22" s="40"/>
-      <c r="D22" s="52"/>
-      <c r="E22" s="34"/>
-      <c r="F22" s="52"/>
-      <c r="G22" s="31"/>
-      <c r="H22" s="53"/>
+      <c r="B19" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="C19" s="37"/>
+      <c r="D19" s="38"/>
+      <c r="E19" s="38"/>
+      <c r="F19" s="38"/>
+      <c r="G19" s="37"/>
+      <c r="H19" s="39"/>
+    </row>
+    <row r="20" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
+      <c r="B20" s="35" t="s">
+        <v>274</v>
+      </c>
+      <c r="C20" s="40" t="s">
+        <v>263</v>
+      </c>
+      <c r="D20" s="41" t="s">
+        <v>264</v>
+      </c>
+      <c r="E20" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="F20" s="34"/>
+      <c r="G20" s="29"/>
+      <c r="H20" s="36"/>
+    </row>
+    <row r="21" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
+      <c r="B21" s="35" t="s">
+        <v>275</v>
+      </c>
+      <c r="C21" s="40" t="s">
+        <v>263</v>
+      </c>
+      <c r="D21" s="41" t="s">
+        <v>264</v>
+      </c>
+      <c r="E21" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="F21" s="34"/>
+      <c r="G21" s="29"/>
+      <c r="H21" s="36"/>
+    </row>
+    <row r="22" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
+      <c r="B22" s="35" t="s">
+        <v>276</v>
+      </c>
+      <c r="C22" s="40" t="s">
+        <v>263</v>
+      </c>
+      <c r="D22" s="41" t="s">
+        <v>264</v>
+      </c>
+      <c r="E22" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="F22" s="34"/>
+      <c r="G22" s="29"/>
+      <c r="H22" s="36"/>
     </row>
     <row r="23" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="B23" s="46"/>

--- a/file/table/DAPC_ProyectoCAD.xlsx
+++ b/file/table/DAPC_ProyectoCAD.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6738C9D-B331-441B-AFD2-349C202BAAEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9291498-1444-4BDC-9263-5F7567A87E7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1.Técnicas" sheetId="2" r:id="rId1"/>
@@ -181,7 +181,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="414" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="265">
   <si>
     <t>1. Especificaciones técnicas generales</t>
   </si>
@@ -1103,26 +1103,6 @@
     </r>
   </si>
   <si>
-    <t>La distribución de una bodega en un proyecto implica planificar la disposición de las áreas y elementos para optimizar el flujo de materiales, maximizar el espacio y garantizar la eficiencia operativa. Se deben considerar factores como el tipo de productos, la rotación, el tamaño del almacén y los equipos de manipulación.</t>
-  </si>
-  <si>
-    <r>
-      <t>Distribución interna</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (al menos se deben incluir 3 referencias distintas de transformadores eléctricos industriales)</t>
-    </r>
-  </si>
-  <si>
-    <t>4. Bodegaje</t>
-  </si>
-  <si>
     <t>En un proyecto, las especificaciones técnicas son documentos que detallan las normas, requisitos, procedimientos y condiciones técnicas que deben cumplirse en la ejecución de un proyecto. Estos documentos guían la implementación del proyecto, asegurando que se cumplan los estándares de calidad y se alcancen los resultados deseados. 
 El proyecto se desarrolla en grupo, el número de estudiantes se indica al inicio del curso. Cada grupo tendrá un código numérico consecutivo asignado por el instructor. Los estudiantes deberán definir el nombre de su grupo de proyecto y crear un logotipo en AutoCAD. El código, logotipo y nombre del grupo deberán incluirse en todos los planos generados.</t>
   </si>
@@ -1133,85 +1113,55 @@
     <t>En un proyecto, las especificaciones eléctricas son un conjunto de directrices técnicas que describen detalladamente las características y requisitos de los componentes y equipos eléctricos que se utilizarán. Estas especificaciones aseguran que la instalación eléctrica sea segura, confiable y cumpla con los estándares y normativas aplicables.</t>
   </si>
   <si>
-    <t>Separación entre estantes</t>
-  </si>
-  <si>
-    <t>Estantería</t>
-  </si>
-  <si>
-    <t>Altura máxima de montacargas</t>
-  </si>
-  <si>
-    <t>Número de niveles en estantes</t>
-  </si>
-  <si>
-    <t>Nivel</t>
-  </si>
-  <si>
-    <t>Ancho de estante</t>
-  </si>
-  <si>
-    <t>Alto de entrepiso en estante</t>
-  </si>
-  <si>
-    <t>Separación o ancho del corredor por donde se desplaza el montacargas industrial.</t>
-  </si>
-  <si>
-    <t>Ancho total del estante. En zonas internas se pueden colocar en hileras de dos, en costados de bodega solo una hilera.</t>
-  </si>
-  <si>
-    <t>Altura del entrepiso incluyendo el espesor de la base.</t>
-  </si>
-  <si>
-    <t>Altura máxima que puede elevar el montacargas, requerido para definir la altura superior de la estantería.</t>
-  </si>
-  <si>
-    <t>Elevación de piso del último estante</t>
-  </si>
-  <si>
-    <t>Indique la referencia y cantidad de elementos a almacenar en la bodega. Para la distribución en estantes, los transformadores grandes se almacenan en la parte inferior, los medianos en los estantes intermedios y los livianos en la parte superior.</t>
-  </si>
-  <si>
-    <t>Calcular</t>
-  </si>
-  <si>
-    <t>Corresponde al número de pisos que tendrá la estantería incluído el piso a nivel de placa.</t>
-  </si>
-  <si>
-    <t>Esta elevación no debe ser superior a la altura vertical de desplazamiento del montacarga.</t>
-  </si>
-  <si>
-    <t>Verificación de montacarga</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>Verificación de desplazamiento para carga y descarga del montacargas.</t>
-  </si>
-  <si>
-    <t>Longitud total de estantería en planta</t>
-  </si>
-  <si>
-    <t>Distribuir dentro de la bodeda y medir.</t>
-  </si>
-  <si>
-    <t>Longitud total de estantería en todos los niveles</t>
-  </si>
-  <si>
-    <t>Valor longitudinal por número de niveles.</t>
-  </si>
-  <si>
-    <t>Transformador 1 - Ref: #####</t>
-  </si>
-  <si>
-    <t>Transformador 2 - Ref: #####</t>
-  </si>
-  <si>
-    <t>Transformador 3 - Ref: #####</t>
-  </si>
-  <si>
     <t>Cuadro de cantidades (resumen a incluir en planos, no es necesario realizar costos unitarios)</t>
+  </si>
+  <si>
+    <t>5. Planos</t>
+  </si>
+  <si>
+    <t>Plano de planta general</t>
+  </si>
+  <si>
+    <t>Planta con visibilidad interna de la distribución de los espacios internos. Detalles de zonas de oficinas y baños. Incluir cuadro de áreas.</t>
+  </si>
+  <si>
+    <t>Plano de cubiertas y fachadas</t>
+  </si>
+  <si>
+    <t>Plano de corte longitudinal</t>
+  </si>
+  <si>
+    <t>Plano de corte transversal</t>
+  </si>
+  <si>
+    <t>En el contexto de un proyecto, los planos de diseño son representaciones gráficas que detallan la forma, dimensiones y características de la obra a construir o implementar. Son documentos esenciales que guían a los constructores y otros profesionales durante la ejecución del proyecto, asegurando que se materialice según lo planificado. Para los planos requeridos, utilice uno o varios layouts</t>
+  </si>
+  <si>
+    <t>Plano de red eléctrica interna 110v</t>
+  </si>
+  <si>
+    <t>Plano de red eléctrica interna 220v</t>
+  </si>
+  <si>
+    <t>Plano de red de datos usando cableado</t>
+  </si>
+  <si>
+    <t>Plano de red foto-voltáica</t>
+  </si>
+  <si>
+    <t>Plano de red vigilancia</t>
+  </si>
+  <si>
+    <t>Cámaras de vigilancia</t>
+  </si>
+  <si>
+    <t>Cubiertas y fachadas. En la cubierta incluir la distribución de los paneles solares, líneas de vída y ventiladores extractores de calor. Incluir cuadro de áreas.</t>
+  </si>
+  <si>
+    <t>Plano en el sentido del largo de la bodega incluyendo detalle de oficinas, baños y escalera..</t>
+  </si>
+  <si>
+    <t>Plano en el sentido del ancho de la bodega incluyendo detalle de oficinas, baños y escalera.</t>
   </si>
 </sst>
 </file>
@@ -1621,7 +1571,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="94">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1905,6 +1855,9 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2214,7 +2167,7 @@
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B4" s="86" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="C4" s="86"/>
       <c r="D4" s="86"/>
@@ -2541,7 +2494,7 @@
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B4" s="86" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="C4" s="86"/>
       <c r="D4" s="86"/>
@@ -3821,7 +3774,7 @@
     </row>
     <row r="90" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B90" s="2" t="s">
-        <v>277</v>
+        <v>248</v>
       </c>
     </row>
     <row r="91" spans="2:5" x14ac:dyDescent="0.45">
@@ -4051,7 +4004,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDC0663E-105D-42EA-893B-DB8B7FE41FC2}">
-  <dimension ref="B2:H29"/>
+  <dimension ref="B2:H30"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.59765625" customWidth="1"/>
@@ -4075,7 +4028,7 @@
     </row>
     <row r="4" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B4" s="86" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C4" s="86"/>
       <c r="D4" s="86"/>
@@ -4319,7 +4272,7 @@
     </row>
     <row r="20" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="B20" s="50" t="s">
-        <v>219</v>
+        <v>261</v>
       </c>
       <c r="C20" s="40" t="s">
         <v>220</v>
@@ -4336,12 +4289,12 @@
     </row>
     <row r="21" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="B21" s="50" t="s">
-        <v>232</v>
+        <v>219</v>
       </c>
       <c r="C21" s="40" t="s">
         <v>220</v>
       </c>
-      <c r="D21" s="52">
+      <c r="D21" s="34">
         <v>1</v>
       </c>
       <c r="E21" s="34" t="s">
@@ -4353,7 +4306,7 @@
     </row>
     <row r="22" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="B22" s="50" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C22" s="40" t="s">
         <v>220</v>
@@ -4369,55 +4322,55 @@
       <c r="H22" s="53"/>
     </row>
     <row r="23" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="B23" s="50"/>
-      <c r="C23" s="51"/>
-      <c r="D23" s="52"/>
-      <c r="E23" s="52"/>
+      <c r="B23" s="50" t="s">
+        <v>233</v>
+      </c>
+      <c r="C23" s="40" t="s">
+        <v>220</v>
+      </c>
+      <c r="D23" s="52">
+        <v>1</v>
+      </c>
+      <c r="E23" s="34" t="s">
+        <v>129</v>
+      </c>
       <c r="F23" s="52"/>
       <c r="G23" s="31"/>
       <c r="H23" s="53"/>
     </row>
     <row r="24" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="B24" s="6" t="s">
+      <c r="B24" s="50"/>
+      <c r="C24" s="51"/>
+      <c r="D24" s="52"/>
+      <c r="E24" s="52"/>
+      <c r="F24" s="52"/>
+      <c r="G24" s="31"/>
+      <c r="H24" s="53"/>
+    </row>
+    <row r="25" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="B25" s="6" t="s">
         <v>244</v>
       </c>
-      <c r="C24" s="37"/>
-      <c r="D24" s="38"/>
-      <c r="E24" s="38"/>
-      <c r="F24" s="38"/>
-      <c r="G24" s="37"/>
-      <c r="H24" s="39"/>
-    </row>
-    <row r="25" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
-      <c r="B25" s="35" t="s">
+      <c r="C25" s="37"/>
+      <c r="D25" s="38"/>
+      <c r="E25" s="38"/>
+      <c r="F25" s="38"/>
+      <c r="G25" s="37"/>
+      <c r="H25" s="39"/>
+    </row>
+    <row r="26" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
+      <c r="B26" s="35" t="s">
         <v>222</v>
       </c>
-      <c r="C25" s="40" t="s">
+      <c r="C26" s="40" t="s">
         <v>227</v>
       </c>
-      <c r="D25" s="54">
+      <c r="D26" s="54">
         <f>'2.Arquitectónica'!D31-'2.Arquitectónica'!D37-'2.Arquitectónica'!D43</f>
         <v>1135.04</v>
       </c>
-      <c r="E25" s="34" t="s">
+      <c r="E26" s="34" t="s">
         <v>60</v>
-      </c>
-      <c r="F25" s="34"/>
-      <c r="G25" s="29"/>
-      <c r="H25" s="36"/>
-    </row>
-    <row r="26" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="B26" s="35" t="s">
-        <v>226</v>
-      </c>
-      <c r="C26" s="40" t="s">
-        <v>229</v>
-      </c>
-      <c r="D26" s="41">
-        <v>992</v>
-      </c>
-      <c r="E26" s="34" t="s">
-        <v>70</v>
       </c>
       <c r="F26" s="34"/>
       <c r="G26" s="29"/>
@@ -4425,13 +4378,13 @@
     </row>
     <row r="27" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="B27" s="35" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C27" s="40" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D27" s="41">
-        <v>1950</v>
+        <v>992</v>
       </c>
       <c r="E27" s="34" t="s">
         <v>70</v>
@@ -4440,32 +4393,49 @@
       <c r="G27" s="29"/>
       <c r="H27" s="36"/>
     </row>
-    <row r="28" spans="2:8" ht="51" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="B28" s="35" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C28" s="40" t="s">
-        <v>231</v>
-      </c>
-      <c r="D28" s="34">
-        <f>INT(D25/(D26/1000*D27/1000))</f>
-        <v>586</v>
+        <v>230</v>
+      </c>
+      <c r="D28" s="41">
+        <v>1950</v>
       </c>
       <c r="E28" s="34" t="s">
-        <v>129</v>
+        <v>70</v>
       </c>
       <c r="F28" s="34"/>
       <c r="G28" s="29"/>
       <c r="H28" s="36"/>
     </row>
-    <row r="29" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="B29" s="46"/>
-      <c r="C29" s="47"/>
-      <c r="D29" s="48"/>
-      <c r="E29" s="48"/>
-      <c r="F29" s="48"/>
-      <c r="G29" s="30"/>
-      <c r="H29" s="49"/>
+    <row r="29" spans="2:8" ht="51" x14ac:dyDescent="0.45">
+      <c r="B29" s="35" t="s">
+        <v>228</v>
+      </c>
+      <c r="C29" s="40" t="s">
+        <v>231</v>
+      </c>
+      <c r="D29" s="34">
+        <f>INT(D26/(D27/1000*D28/1000))</f>
+        <v>586</v>
+      </c>
+      <c r="E29" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="F29" s="34"/>
+      <c r="G29" s="29"/>
+      <c r="H29" s="36"/>
+    </row>
+    <row r="30" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="B30" s="46"/>
+      <c r="C30" s="47"/>
+      <c r="D30" s="48"/>
+      <c r="E30" s="48"/>
+      <c r="F30" s="48"/>
+      <c r="G30" s="30"/>
+      <c r="H30" s="49"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4478,11 +4448,11 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36B29233-B656-46A0-B3DE-6C1E8F28F7E1}">
-  <dimension ref="B2:H23"/>
+  <dimension ref="B2:H16"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.59765625" customWidth="1"/>
-    <col min="2" max="2" width="29.1328125" customWidth="1"/>
+    <col min="2" max="2" width="36.3984375" customWidth="1"/>
     <col min="3" max="3" width="51.73046875" customWidth="1"/>
     <col min="4" max="4" width="11.265625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.59765625" customWidth="1"/>
@@ -4497,12 +4467,12 @@
     </row>
     <row r="3" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="B3" s="20" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="4" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.45">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B4" s="86" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="C4" s="86"/>
       <c r="D4" s="86"/>
@@ -4543,29 +4513,35 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="B7" s="6" t="s">
+    <row r="7" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
+      <c r="B7" s="35" t="s">
+        <v>250</v>
+      </c>
+      <c r="C7" s="40" t="s">
+        <v>251</v>
+      </c>
+      <c r="D7" s="41">
+        <v>1</v>
+      </c>
+      <c r="E7" s="34" t="s">
+        <v>129</v>
+      </c>
+      <c r="F7" s="34"/>
+      <c r="G7" s="29"/>
+      <c r="H7" s="36"/>
+    </row>
+    <row r="8" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
+      <c r="B8" s="35" t="s">
         <v>252</v>
       </c>
-      <c r="C7" s="37"/>
-      <c r="D7" s="38"/>
-      <c r="E7" s="38"/>
-      <c r="F7" s="38"/>
-      <c r="G7" s="37"/>
-      <c r="H7" s="39"/>
-    </row>
-    <row r="8" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="B8" s="35" t="s">
-        <v>251</v>
-      </c>
       <c r="C8" s="40" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="D8" s="41">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E8" s="34" t="s">
-        <v>59</v>
+        <v>129</v>
       </c>
       <c r="F8" s="34"/>
       <c r="G8" s="29"/>
@@ -4573,16 +4549,16 @@
     </row>
     <row r="9" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
       <c r="B9" s="35" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C9" s="40" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="D9" s="41">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>59</v>
+        <v>129</v>
       </c>
       <c r="F9" s="34"/>
       <c r="G9" s="29"/>
@@ -4593,13 +4569,13 @@
         <v>254</v>
       </c>
       <c r="C10" s="40" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D10" s="41">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="E10" s="34" t="s">
-        <v>255</v>
+        <v>129</v>
       </c>
       <c r="F10" s="34"/>
       <c r="G10" s="29"/>
@@ -4607,34 +4583,33 @@
     </row>
     <row r="11" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="B11" s="35" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C11" s="40" t="s">
-        <v>260</v>
+        <v>239</v>
       </c>
       <c r="D11" s="41">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11" s="34" t="s">
-        <v>59</v>
+        <v>129</v>
       </c>
       <c r="F11" s="34"/>
       <c r="G11" s="29"/>
       <c r="H11" s="36"/>
     </row>
-    <row r="12" spans="2:8" ht="33" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="B12" s="35" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="C12" s="40" t="s">
-        <v>266</v>
-      </c>
-      <c r="D12" s="34">
-        <f>D10*D11</f>
-        <v>8</v>
+        <v>239</v>
+      </c>
+      <c r="D12" s="41">
+        <v>1</v>
       </c>
       <c r="E12" s="34" t="s">
-        <v>59</v>
+        <v>129</v>
       </c>
       <c r="F12" s="34"/>
       <c r="G12" s="29"/>
@@ -4642,162 +4617,63 @@
     </row>
     <row r="13" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
       <c r="B13" s="35" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="C13" s="40" t="s">
-        <v>261</v>
+        <v>243</v>
       </c>
       <c r="D13" s="41">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="E13" s="34" t="s">
-        <v>59</v>
+        <v>129</v>
       </c>
       <c r="F13" s="34"/>
       <c r="G13" s="29"/>
       <c r="H13" s="36"/>
     </row>
-    <row r="14" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
       <c r="B14" s="35" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="C14" s="40" t="s">
-        <v>269</v>
-      </c>
-      <c r="D14" s="34" t="str">
-        <f>IF(D12&lt;=D13, "Cumple","No cumple")</f>
-        <v>Cumple</v>
+        <v>240</v>
+      </c>
+      <c r="D14" s="41">
+        <v>1</v>
       </c>
       <c r="E14" s="34" t="s">
-        <v>268</v>
+        <v>129</v>
       </c>
       <c r="F14" s="34"/>
       <c r="G14" s="29"/>
       <c r="H14" s="36"/>
     </row>
-    <row r="15" spans="2:8" ht="33" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="B15" s="35" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="C15" s="40" t="s">
-        <v>271</v>
+        <v>241</v>
       </c>
       <c r="D15" s="41">
-        <v>60</v>
+        <v>1</v>
       </c>
       <c r="E15" s="34" t="s">
-        <v>59</v>
+        <v>129</v>
       </c>
       <c r="F15" s="34"/>
       <c r="G15" s="29"/>
       <c r="H15" s="36"/>
     </row>
-    <row r="16" spans="2:8" ht="33" x14ac:dyDescent="0.45">
-      <c r="B16" s="35" t="s">
-        <v>272</v>
-      </c>
-      <c r="C16" s="40" t="s">
-        <v>273</v>
-      </c>
-      <c r="D16" s="34">
-        <f>D15*D10</f>
-        <v>240</v>
-      </c>
-      <c r="E16" s="34" t="s">
-        <v>59</v>
-      </c>
-      <c r="F16" s="34"/>
-      <c r="G16" s="29"/>
-      <c r="H16" s="36"/>
-    </row>
-    <row r="17" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="B17" s="35"/>
-      <c r="C17" s="40"/>
-      <c r="D17" s="41"/>
-      <c r="E17" s="34"/>
-      <c r="F17" s="34"/>
-      <c r="G17" s="29"/>
-      <c r="H17" s="36"/>
-    </row>
-    <row r="18" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="B18" s="35"/>
-      <c r="C18" s="40"/>
-      <c r="D18" s="34"/>
-      <c r="E18" s="34"/>
-      <c r="F18" s="34"/>
-      <c r="G18" s="29"/>
-      <c r="H18" s="36"/>
-    </row>
-    <row r="19" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="B19" s="6" t="s">
-        <v>246</v>
-      </c>
-      <c r="C19" s="37"/>
-      <c r="D19" s="38"/>
-      <c r="E19" s="38"/>
-      <c r="F19" s="38"/>
-      <c r="G19" s="37"/>
-      <c r="H19" s="39"/>
-    </row>
-    <row r="20" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
-      <c r="B20" s="35" t="s">
-        <v>274</v>
-      </c>
-      <c r="C20" s="40" t="s">
-        <v>263</v>
-      </c>
-      <c r="D20" s="41" t="s">
-        <v>264</v>
-      </c>
-      <c r="E20" s="34" t="s">
-        <v>129</v>
-      </c>
-      <c r="F20" s="34"/>
-      <c r="G20" s="29"/>
-      <c r="H20" s="36"/>
-    </row>
-    <row r="21" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
-      <c r="B21" s="35" t="s">
-        <v>275</v>
-      </c>
-      <c r="C21" s="40" t="s">
-        <v>263</v>
-      </c>
-      <c r="D21" s="41" t="s">
-        <v>264</v>
-      </c>
-      <c r="E21" s="34" t="s">
-        <v>129</v>
-      </c>
-      <c r="F21" s="34"/>
-      <c r="G21" s="29"/>
-      <c r="H21" s="36"/>
-    </row>
-    <row r="22" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
-      <c r="B22" s="35" t="s">
-        <v>276</v>
-      </c>
-      <c r="C22" s="40" t="s">
-        <v>263</v>
-      </c>
-      <c r="D22" s="41" t="s">
-        <v>264</v>
-      </c>
-      <c r="E22" s="34" t="s">
-        <v>129</v>
-      </c>
-      <c r="F22" s="34"/>
-      <c r="G22" s="29"/>
-      <c r="H22" s="36"/>
-    </row>
-    <row r="23" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="B23" s="46"/>
-      <c r="C23" s="47"/>
-      <c r="D23" s="48"/>
-      <c r="E23" s="48"/>
-      <c r="F23" s="48"/>
-      <c r="G23" s="30"/>
-      <c r="H23" s="49"/>
+    <row r="16" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="B16" s="46"/>
+      <c r="C16" s="47"/>
+      <c r="D16" s="94"/>
+      <c r="E16" s="48"/>
+      <c r="F16" s="48"/>
+      <c r="G16" s="30"/>
+      <c r="H16" s="49"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/file/table/DAPC_ProyectoCAD.xlsx
+++ b/file/table/DAPC_ProyectoCAD.xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9291498-1444-4BDC-9263-5F7567A87E7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5587D53-E66E-4033-B768-26DA77B8FEB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="1.Técnicas" sheetId="2" r:id="rId1"/>
-    <sheet name="2.Arquitectónica" sheetId="4" r:id="rId2"/>
-    <sheet name="3.Eléctrica" sheetId="5" r:id="rId3"/>
-    <sheet name="3.Planos" sheetId="6" r:id="rId4"/>
-    <sheet name="Files" sheetId="1" r:id="rId5"/>
-    <sheet name="Metadata" sheetId="3" r:id="rId6"/>
+    <sheet name="0.Inicio" sheetId="7" r:id="rId1"/>
+    <sheet name="1.Técnica" sheetId="2" r:id="rId2"/>
+    <sheet name="2.Arquitectónica" sheetId="4" r:id="rId3"/>
+    <sheet name="3.Eléctrica" sheetId="5" r:id="rId4"/>
+    <sheet name="3.Planos" sheetId="6" r:id="rId5"/>
+    <sheet name="Files" sheetId="1" r:id="rId6"/>
+    <sheet name="Metadata" sheetId="3" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="SumUDig">'1.Técnicas'!$E$32</definedName>
+    <definedName name="SumUDig">'0.Inicio'!$E$30</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -49,7 +50,7 @@
     <author>Test</author>
   </authors>
   <commentList>
-    <comment ref="E21" authorId="0" shapeId="0" xr:uid="{8FA6F4B0-21C7-4A5C-ABA3-36A7AA5DFC59}">
+    <comment ref="E19" authorId="0" shapeId="0" xr:uid="{8786F758-EC5E-4426-92D1-B2FAF1BCAE4E}">
       <text>
         <r>
           <rPr>
@@ -67,6 +68,44 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Test</author>
+  </authors>
+  <commentList>
+    <comment ref="E7" authorId="0" shapeId="0" xr:uid="{1CC115FE-8EE3-41FE-9390-20E34CE223E1}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI Light"/>
+            <family val="2"/>
+          </rPr>
+          <t>Un. corresponde a Unidad.
+n/a: no aplica.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F7" authorId="0" shapeId="0" xr:uid="{3370069B-EA07-43C8-B4DF-40CDA6C2AF87}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI Light"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Actividad de referencia en curso DAPC.
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Test</author>
@@ -100,11 +139,25 @@
         </r>
       </text>
     </comment>
+    <comment ref="F91" authorId="0" shapeId="0" xr:uid="{58FB072B-AFAB-4EFA-BE22-BCCEF0C50642}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI Light"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Actividad de referencia en curso DAPC.
+</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
-<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Test</author>
@@ -142,7 +195,7 @@
 </comments>
 </file>
 
-<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Test</author>
@@ -180,8 +233,30 @@
 </comments>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="403" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="280">
   <si>
     <t>1. Especificaciones técnicas generales</t>
   </si>
@@ -348,6 +423,9 @@
   </si>
   <si>
     <t>/file/</t>
+  </si>
+  <si>
+    <t>El proyecto se desarrolla en grupo, el número de estudiantes se indica al inicio del curso. Cada grupo tendrá un código numérico consecutivo asignado por el instructor. Los estudiantes deberán definir el nombre de su grupo de proyecto y crear un logotipo en AutoCAD. El código, logotipo y nombre del grupo deberán incluirse en todos los planos generados.</t>
   </si>
   <si>
     <r>
@@ -1103,10 +1181,6 @@
     </r>
   </si>
   <si>
-    <t>En un proyecto, las especificaciones técnicas son documentos que detallan las normas, requisitos, procedimientos y condiciones técnicas que deben cumplirse en la ejecución de un proyecto. Estos documentos guían la implementación del proyecto, asegurando que se cumplan los estándares de calidad y se alcancen los resultados deseados. 
-El proyecto se desarrolla en grupo, el número de estudiantes se indica al inicio del curso. Cada grupo tendrá un código numérico consecutivo asignado por el instructor. Los estudiantes deberán definir el nombre de su grupo de proyecto y crear un logotipo en AutoCAD. El código, logotipo y nombre del grupo deberán incluirse en todos los planos generados.</t>
-  </si>
-  <si>
     <t>En arquitectura, las especificaciones de un proyecto son documentos técnicos detallados que describen las características, materiales, estándares y métodos de construcción necesarios para ejecutar un proyecto. Estas especificaciones complementan los planos y proporcionan información precisa sobre cómo se deben realizar los trabajos, garantizando la calidad y cumplimiento de los requisitos.</t>
   </si>
   <si>
@@ -1162,6 +1236,52 @@
   </si>
   <si>
     <t>Plano en el sentido del ancho de la bodega incluyendo detalle de oficinas, baños y escalera.</t>
+  </si>
+  <si>
+    <t>Resumen de calificaciones del proyecto</t>
+  </si>
+  <si>
+    <t>Técnica</t>
+  </si>
+  <si>
+    <t>Arquitectónica</t>
+  </si>
+  <si>
+    <t>Eléctrica</t>
+  </si>
+  <si>
+    <t>Planos</t>
+  </si>
+  <si>
+    <t>Archivos</t>
+  </si>
+  <si>
+    <t>Otros</t>
+  </si>
+  <si>
+    <t>Promedio de calificación:</t>
+  </si>
+  <si>
+    <t>Grupos, integrantes y resúmen de calificaciones</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En un proyecto, las especificaciones técnicas son documentos que detallan las normas, requisitos, procedimientos y condiciones técnicas que deben cumplirse en la ejecución de un proyecto. Estos documentos guían la implementación del proyecto, asegurando que se cumplan los estándares de calidad y se alcancen los resultados deseados. 
+</t>
+  </si>
+  <si>
+    <t>Nombre de grupo y logotipo</t>
+  </si>
+  <si>
+    <t>Promedio:</t>
+  </si>
+  <si>
+    <t>Nombre y logotipo creado por el grupo.</t>
+  </si>
+  <si>
+    <t>Estructura de directorios</t>
+  </si>
+  <si>
+    <t>Utilizar la estructura definida para el curso DAPC.</t>
   </si>
 </sst>
 </file>
@@ -1266,7 +1386,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="25">
     <border>
       <left/>
       <right/>
@@ -1565,13 +1685,52 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="95">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1754,9 +1913,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -1788,15 +1944,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1858,6 +2005,61 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2140,8 +2342,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0659C4DD-D653-4634-8C4F-29057F021A54}">
-  <dimension ref="B1:E32"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82EDA320-F942-4FCE-8343-60C075021E69}">
+  <dimension ref="B1:E40"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="2.59765625" style="2" customWidth="1"/>
@@ -2162,221 +2364,235 @@
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B3" s="20" t="s">
-        <v>0</v>
+        <v>273</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B4" s="86" t="s">
-        <v>245</v>
-      </c>
-      <c r="C4" s="86"/>
-      <c r="D4" s="86"/>
-      <c r="E4" s="86"/>
+      <c r="B4" s="82" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="82"/>
+      <c r="D4" s="82"/>
+      <c r="E4" s="82"/>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B5" s="86"/>
-      <c r="C5" s="86"/>
-      <c r="D5" s="86"/>
-      <c r="E5" s="86"/>
+      <c r="B5" s="82"/>
+      <c r="C5" s="82"/>
+      <c r="D5" s="82"/>
+      <c r="E5" s="82"/>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B6" s="86"/>
-      <c r="C6" s="86"/>
-      <c r="D6" s="86"/>
-      <c r="E6" s="86"/>
+      <c r="B6" s="82"/>
+      <c r="C6" s="82"/>
+      <c r="D6" s="82"/>
+      <c r="E6" s="82"/>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B7" s="86"/>
-      <c r="C7" s="86"/>
-      <c r="D7" s="86"/>
-      <c r="E7" s="86"/>
+      <c r="B7" s="82"/>
+      <c r="C7" s="82"/>
+      <c r="D7" s="82"/>
+      <c r="E7" s="82"/>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B8" s="86"/>
-      <c r="C8" s="86"/>
-      <c r="D8" s="86"/>
+      <c r="B8" s="84" t="s">
+        <v>1</v>
+      </c>
+      <c r="C8" s="85"/>
+      <c r="D8" s="85"/>
       <c r="E8" s="86"/>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B9" s="86"/>
-      <c r="C9" s="86"/>
-      <c r="D9" s="86"/>
-      <c r="E9" s="86"/>
+      <c r="B9" s="76" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" s="77"/>
+      <c r="D9" s="77"/>
+      <c r="E9" s="78"/>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B10" s="88" t="s">
+      <c r="B10" s="73" t="s">
+        <v>2</v>
+      </c>
+      <c r="C10" s="74"/>
+      <c r="D10" s="74"/>
+      <c r="E10" s="75"/>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B11" s="76" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="77"/>
+      <c r="D11" s="77"/>
+      <c r="E11" s="78"/>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B12" s="79"/>
+      <c r="C12" s="80"/>
+      <c r="D12" s="80"/>
+      <c r="E12" s="81"/>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B13" s="73" t="s">
+        <v>21</v>
+      </c>
+      <c r="C13" s="74"/>
+      <c r="D13" s="74"/>
+      <c r="E13" s="75"/>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B14" s="76" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14" s="77"/>
+      <c r="D14" s="77"/>
+      <c r="E14" s="78"/>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B15" s="79"/>
+      <c r="C15" s="80"/>
+      <c r="D15" s="80"/>
+      <c r="E15" s="81"/>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B16" s="23" t="s">
+        <v>22</v>
+      </c>
+      <c r="C16" s="23"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="23"/>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B18" s="83" t="s">
+        <v>14</v>
+      </c>
+      <c r="C18" s="83"/>
+      <c r="D18" s="83"/>
+      <c r="E18" s="83"/>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B19" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B20" s="15">
         <v>1</v>
       </c>
-      <c r="C10" s="89"/>
-      <c r="D10" s="89"/>
-      <c r="E10" s="90"/>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B11" s="80" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="81"/>
-      <c r="D11" s="81"/>
-      <c r="E11" s="82"/>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B12" s="77" t="s">
+      <c r="C20" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="E20" s="11">
+        <f t="shared" ref="E20:E29" si="0">IFERROR(RIGHT(D20,1)*1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B21" s="15">
         <v>2</v>
       </c>
-      <c r="C12" s="78"/>
-      <c r="D12" s="78"/>
-      <c r="E12" s="79"/>
-    </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B13" s="80" t="s">
-        <v>13</v>
-      </c>
-      <c r="C13" s="81"/>
-      <c r="D13" s="81"/>
-      <c r="E13" s="82"/>
-    </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B14" s="83"/>
-      <c r="C14" s="84"/>
-      <c r="D14" s="84"/>
-      <c r="E14" s="85"/>
-    </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B15" s="77" t="s">
-        <v>21</v>
-      </c>
-      <c r="C15" s="78"/>
-      <c r="D15" s="78"/>
-      <c r="E15" s="79"/>
-    </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B16" s="80" t="s">
-        <v>19</v>
-      </c>
-      <c r="C16" s="81"/>
-      <c r="D16" s="81"/>
-      <c r="E16" s="82"/>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B17" s="83"/>
-      <c r="C17" s="84"/>
-      <c r="D17" s="84"/>
-      <c r="E17" s="85"/>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B18" s="23" t="s">
-        <v>22</v>
-      </c>
-      <c r="C18" s="23"/>
-      <c r="D18" s="23"/>
-      <c r="E18" s="23"/>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B19" s="18"/>
-      <c r="C19" s="18"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="18"/>
-    </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B20" s="87" t="s">
-        <v>14</v>
-      </c>
-      <c r="C20" s="87"/>
-      <c r="D20" s="87"/>
-      <c r="E20" s="87"/>
-    </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B21" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>29</v>
-      </c>
-      <c r="E21" s="10" t="s">
+      <c r="C21" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="27" t="s">
+        <v>5</v>
+      </c>
+      <c r="E21" s="11">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B22" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C22" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D22" s="27" t="s">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E22" s="11">
-        <f t="shared" ref="E22:E31" si="0">IFERROR(RIGHT(D22,1)*1,0)</f>
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B23" s="15">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C23" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D23" s="27" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E23" s="11">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B24" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C24" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D24" s="27" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E24" s="11">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B25" s="15">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C25" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D25" s="27" t="s">
-        <v>7</v>
-      </c>
+      <c r="D25" s="27"/>
       <c r="E25" s="11">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B26" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C26" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D26" s="27" t="s">
-        <v>9</v>
-      </c>
+      <c r="D26" s="27"/>
       <c r="E26" s="11">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B27" s="15">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C27" s="25" t="s">
         <v>8</v>
@@ -2389,7 +2605,7 @@
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B28" s="15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C28" s="25" t="s">
         <v>8</v>
@@ -2401,73 +2617,354 @@
       </c>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B29" s="15">
+      <c r="B29" s="16">
+        <v>10</v>
+      </c>
+      <c r="C29" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="C29" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D29" s="27"/>
-      <c r="E29" s="11">
+      <c r="D29" s="28"/>
+      <c r="E29" s="9">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B30" s="15">
-        <v>9</v>
-      </c>
-      <c r="C30" s="25" t="s">
-        <v>8</v>
-      </c>
-      <c r="D30" s="27"/>
-      <c r="E30" s="11">
-        <f t="shared" si="0"/>
+      <c r="D30" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E30" s="12">
+        <f>SUM(E20:E29)</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B32" s="83" t="s">
+        <v>265</v>
+      </c>
+      <c r="C32" s="83"/>
+      <c r="D32" s="83"/>
+      <c r="E32" s="83"/>
+    </row>
+    <row r="33" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B33" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="D33" s="10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B34" s="99">
+        <v>1</v>
+      </c>
+      <c r="C34" s="100" t="s">
+        <v>266</v>
+      </c>
+      <c r="D34" s="103"/>
+    </row>
+    <row r="35" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B35" s="99">
+        <v>2</v>
+      </c>
+      <c r="C35" s="100" t="s">
+        <v>267</v>
+      </c>
+      <c r="D35" s="103"/>
+    </row>
+    <row r="36" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B36" s="99">
+        <v>3</v>
+      </c>
+      <c r="C36" s="100" t="s">
+        <v>268</v>
+      </c>
+      <c r="D36" s="103"/>
+    </row>
+    <row r="37" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B37" s="99">
+        <v>4</v>
+      </c>
+      <c r="C37" s="100" t="s">
+        <v>269</v>
+      </c>
+      <c r="D37" s="103"/>
+    </row>
+    <row r="38" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B38" s="99">
+        <v>5</v>
+      </c>
+      <c r="C38" s="100" t="s">
+        <v>270</v>
+      </c>
+      <c r="D38" s="103"/>
+    </row>
+    <row r="39" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B39" s="101">
+        <v>6</v>
+      </c>
+      <c r="C39" s="102" t="s">
+        <v>271</v>
+      </c>
+      <c r="D39" s="104"/>
+    </row>
+    <row r="40" spans="2:4" x14ac:dyDescent="0.45">
+      <c r="B40" s="105" t="s">
+        <v>272</v>
+      </c>
+      <c r="C40" s="106"/>
+      <c r="D40" s="98">
+        <f>SUM(E34:E39)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B31" s="16">
-        <v>10</v>
-      </c>
-      <c r="C31" s="26" t="s">
-        <v>8</v>
-      </c>
-      <c r="D31" s="28"/>
-      <c r="E31" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="D32" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="E32" s="12">
-        <f>SUM(E22:E31)</f>
-        <v>27</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="8">
-    <mergeCell ref="B15:E15"/>
-    <mergeCell ref="B16:E17"/>
-    <mergeCell ref="B4:E9"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="B13:E14"/>
-    <mergeCell ref="B12:E12"/>
-    <mergeCell ref="B11:E11"/>
+  <mergeCells count="11">
+    <mergeCell ref="B14:E15"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="B32:E32"/>
+    <mergeCell ref="B40:C40"/>
+    <mergeCell ref="B4:E6"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="B9:E9"/>
     <mergeCell ref="B10:E10"/>
+    <mergeCell ref="B11:E12"/>
+    <mergeCell ref="B13:E13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="D22:D31" numberStoredAsText="1"/>
-  </ignoredErrors>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0659C4DD-D653-4634-8C4F-29057F021A54}">
+  <dimension ref="B1:H18"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="2.59765625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="30.06640625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="50.59765625" style="2" customWidth="1"/>
+    <col min="4" max="4" width="15.59765625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="9.06640625" style="2"/>
+    <col min="6" max="6" width="12.265625" style="2" customWidth="1"/>
+    <col min="7" max="7" width="9.06640625" style="2"/>
+    <col min="8" max="8" width="12.3984375" style="2" customWidth="1"/>
+    <col min="9" max="16384" width="9.06640625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="E1" s="24"/>
+    </row>
+    <row r="2" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B2" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B3" s="20" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B4" s="82" t="s">
+        <v>274</v>
+      </c>
+      <c r="C4" s="82"/>
+      <c r="D4" s="82"/>
+      <c r="E4" s="82"/>
+    </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B5" s="82"/>
+      <c r="C5" s="82"/>
+      <c r="D5" s="82"/>
+      <c r="E5" s="82"/>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B6" s="82"/>
+      <c r="C6" s="82"/>
+      <c r="D6" s="82"/>
+      <c r="E6" s="82"/>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B7" s="42" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" s="43" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" s="44" t="s">
+        <v>55</v>
+      </c>
+      <c r="E7" s="44" t="s">
+        <v>56</v>
+      </c>
+      <c r="F7" s="44" t="s">
+        <v>45</v>
+      </c>
+      <c r="G7" s="43" t="s">
+        <v>27</v>
+      </c>
+      <c r="H7" s="45" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B8" s="35" t="s">
+        <v>275</v>
+      </c>
+      <c r="C8" s="40" t="s">
+        <v>277</v>
+      </c>
+      <c r="D8" s="41">
+        <v>1</v>
+      </c>
+      <c r="E8" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="F8" s="34"/>
+      <c r="G8" s="29"/>
+      <c r="H8" s="36"/>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B9" s="35" t="s">
+        <v>278</v>
+      </c>
+      <c r="C9" s="40" t="s">
+        <v>279</v>
+      </c>
+      <c r="D9" s="41">
+        <v>1</v>
+      </c>
+      <c r="E9" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="F9" s="34"/>
+      <c r="G9" s="29"/>
+      <c r="H9" s="36"/>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B10" s="35"/>
+      <c r="C10" s="40"/>
+      <c r="D10" s="41">
+        <v>1</v>
+      </c>
+      <c r="E10" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="F10" s="34"/>
+      <c r="G10" s="29"/>
+      <c r="H10" s="36"/>
+    </row>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B11" s="35"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="41">
+        <v>1</v>
+      </c>
+      <c r="E11" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="F11" s="34"/>
+      <c r="G11" s="29"/>
+      <c r="H11" s="36"/>
+    </row>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B12" s="35"/>
+      <c r="C12" s="40"/>
+      <c r="D12" s="41">
+        <v>1</v>
+      </c>
+      <c r="E12" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="F12" s="34"/>
+      <c r="G12" s="29"/>
+      <c r="H12" s="36"/>
+    </row>
+    <row r="13" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B13" s="35"/>
+      <c r="C13" s="40"/>
+      <c r="D13" s="41">
+        <v>1</v>
+      </c>
+      <c r="E13" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="F13" s="34"/>
+      <c r="G13" s="29"/>
+      <c r="H13" s="36"/>
+    </row>
+    <row r="14" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B14" s="35"/>
+      <c r="C14" s="40"/>
+      <c r="D14" s="41">
+        <v>1</v>
+      </c>
+      <c r="E14" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="F14" s="34"/>
+      <c r="G14" s="29"/>
+      <c r="H14" s="36"/>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B15" s="35"/>
+      <c r="C15" s="40"/>
+      <c r="D15" s="41">
+        <v>1</v>
+      </c>
+      <c r="E15" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="F15" s="34"/>
+      <c r="G15" s="29"/>
+      <c r="H15" s="36"/>
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B16" s="35"/>
+      <c r="C16" s="40"/>
+      <c r="D16" s="41">
+        <v>1</v>
+      </c>
+      <c r="E16" s="34" t="s">
+        <v>130</v>
+      </c>
+      <c r="F16" s="34"/>
+      <c r="G16" s="29"/>
+      <c r="H16" s="36"/>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B17" s="46"/>
+      <c r="C17" s="47"/>
+      <c r="D17" s="90"/>
+      <c r="E17" s="48"/>
+      <c r="F17" s="48"/>
+      <c r="G17" s="30"/>
+      <c r="H17" s="49"/>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="G18" s="107" t="s">
+        <v>276</v>
+      </c>
+      <c r="H18" s="2" t="e">
+        <f>AVERAGE(H8:H17)</f>
+        <v>#DIV/0!</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B4:E6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1EE59D4-4937-4491-BD3F-7DBC007EDF85}">
   <dimension ref="B2:H114"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
@@ -2477,7 +2974,7 @@
     <col min="3" max="3" width="41" style="2" customWidth="1"/>
     <col min="4" max="6" width="9.19921875" style="55" customWidth="1"/>
     <col min="7" max="7" width="28.53125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="14.86328125" style="2" customWidth="1"/>
+    <col min="8" max="8" width="14.86328125" style="55" customWidth="1"/>
     <col min="9" max="9" width="2.59765625" style="2" customWidth="1"/>
     <col min="10" max="16384" width="9.06640625" style="2"/>
   </cols>
@@ -2489,309 +2986,311 @@
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B3" s="20" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B4" s="86" t="s">
+      <c r="B4" s="82" t="s">
         <v>246</v>
       </c>
-      <c r="C4" s="86"/>
-      <c r="D4" s="86"/>
-      <c r="E4" s="86"/>
-      <c r="F4" s="86"/>
-      <c r="G4" s="86"/>
-      <c r="H4" s="86"/>
+      <c r="C4" s="82"/>
+      <c r="D4" s="82"/>
+      <c r="E4" s="82"/>
+      <c r="F4" s="82"/>
+      <c r="G4" s="82"/>
+      <c r="H4" s="82"/>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B5" s="91"/>
-      <c r="C5" s="91"/>
-      <c r="D5" s="91"/>
-      <c r="E5" s="91"/>
-      <c r="F5" s="91"/>
-      <c r="G5" s="91"/>
-      <c r="H5" s="91"/>
+      <c r="B5" s="87"/>
+      <c r="C5" s="87"/>
+      <c r="D5" s="87"/>
+      <c r="E5" s="87"/>
+      <c r="F5" s="87"/>
+      <c r="G5" s="87"/>
+      <c r="H5" s="87"/>
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B6" s="42" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C6" s="43" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D6" s="44" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E6" s="44" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F6" s="44" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G6" s="43" t="s">
         <v>27</v>
       </c>
-      <c r="H6" s="45" t="s">
+      <c r="H6" s="92" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B7" s="6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C7" s="37"/>
       <c r="D7" s="38"/>
       <c r="E7" s="38"/>
       <c r="F7" s="38"/>
       <c r="G7" s="37"/>
-      <c r="H7" s="39"/>
+      <c r="H7" s="93"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B8" s="35" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C8" s="40" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D8" s="41">
         <v>8</v>
       </c>
       <c r="E8" s="34" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F8" s="34"/>
       <c r="G8" s="29"/>
-      <c r="H8" s="36"/>
+      <c r="H8" s="94"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B9" s="35" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C9" s="40" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="D9" s="41">
         <v>10</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F9" s="34"/>
       <c r="G9" s="29"/>
-      <c r="H9" s="36"/>
+      <c r="H9" s="94"/>
     </row>
     <row r="10" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
       <c r="B10" s="35" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C10" s="40" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D10" s="34">
         <f>D8+SumUDig</f>
         <v>35</v>
       </c>
       <c r="E10" s="34" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F10" s="34"/>
       <c r="G10" s="29"/>
-      <c r="H10" s="36"/>
+      <c r="H10" s="94">
+        <v>5</v>
+      </c>
     </row>
     <row r="11" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
       <c r="B11" s="35" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C11" s="40" t="s">
-        <v>180</v>
-      </c>
-      <c r="D11" s="34">
-        <f>D9+SumUDig</f>
+        <v>181</v>
+      </c>
+      <c r="D11" s="34" cm="1">
+        <f t="array" ref="D11">D9+SumUDig</f>
         <v>37</v>
       </c>
       <c r="E11" s="34" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F11" s="34"/>
       <c r="G11" s="29"/>
-      <c r="H11" s="36"/>
+      <c r="H11" s="94"/>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B12" s="35" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C12" s="40" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D12" s="41">
         <v>12</v>
       </c>
       <c r="E12" s="34" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F12" s="34"/>
       <c r="G12" s="29"/>
-      <c r="H12" s="36"/>
+      <c r="H12" s="94"/>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B13" s="35" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C13" s="40" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D13" s="41">
         <v>6</v>
       </c>
       <c r="E13" s="34" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F13" s="34"/>
       <c r="G13" s="29"/>
-      <c r="H13" s="36"/>
+      <c r="H13" s="94"/>
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B14" s="35" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C14" s="40" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D14" s="41">
         <v>12</v>
       </c>
       <c r="E14" s="34" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F14" s="34"/>
       <c r="G14" s="29"/>
-      <c r="H14" s="36"/>
+      <c r="H14" s="94"/>
     </row>
     <row r="15" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
       <c r="B15" s="35" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C15" s="40" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D15" s="34">
         <f>D10</f>
         <v>35</v>
       </c>
       <c r="E15" s="34" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F15" s="34"/>
       <c r="G15" s="29"/>
-      <c r="H15" s="36"/>
+      <c r="H15" s="94"/>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B16" s="35" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C16" s="40" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D16" s="34">
         <f>D11+D14+D13</f>
         <v>55</v>
       </c>
       <c r="E16" s="34" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F16" s="34"/>
       <c r="G16" s="29"/>
-      <c r="H16" s="36"/>
+      <c r="H16" s="94"/>
     </row>
     <row r="17" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
       <c r="B17" s="35" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C17" s="40" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="D17" s="34">
         <f>D16*D15</f>
         <v>1925</v>
       </c>
       <c r="E17" s="34" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F17" s="34"/>
       <c r="G17" s="29"/>
-      <c r="H17" s="36"/>
+      <c r="H17" s="94"/>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B18" s="50" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C18" s="51" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D18" s="52">
         <f>D32+D30</f>
         <v>1435</v>
       </c>
       <c r="E18" s="34" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F18" s="52"/>
       <c r="G18" s="31"/>
-      <c r="H18" s="53"/>
+      <c r="H18" s="95"/>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B19" s="50" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C19" s="51" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D19" s="52">
         <f>D32+D30+D46</f>
         <v>1495</v>
       </c>
       <c r="E19" s="34" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F19" s="52"/>
       <c r="G19" s="31"/>
-      <c r="H19" s="53"/>
+      <c r="H19" s="95"/>
     </row>
     <row r="20" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
       <c r="B20" s="50" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C20" s="51" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D20" s="52">
         <f>D18/D17</f>
         <v>0.74545454545454548</v>
       </c>
       <c r="E20" s="52" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F20" s="52"/>
       <c r="G20" s="31"/>
-      <c r="H20" s="53"/>
+      <c r="H20" s="95"/>
     </row>
     <row r="21" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
       <c r="B21" s="50" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C21" s="51" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D21" s="52">
         <f>D19/D17</f>
         <v>0.77662337662337666</v>
       </c>
       <c r="E21" s="52" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F21" s="52"/>
       <c r="G21" s="31"/>
-      <c r="H21" s="53"/>
+      <c r="H21" s="95"/>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B22" s="46"/>
@@ -2800,263 +3299,265 @@
       <c r="E22" s="48"/>
       <c r="F22" s="48"/>
       <c r="G22" s="30"/>
-      <c r="H22" s="49"/>
+      <c r="H22" s="96"/>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B23" s="6" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="C23" s="37"/>
       <c r="D23" s="38"/>
       <c r="E23" s="38"/>
       <c r="F23" s="38"/>
       <c r="G23" s="37"/>
-      <c r="H23" s="39"/>
+      <c r="H23" s="93"/>
     </row>
     <row r="24" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
       <c r="B24" s="35" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C24" s="40" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D24" s="41">
         <v>2</v>
       </c>
       <c r="E24" s="34" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F24" s="34"/>
       <c r="G24" s="29"/>
-      <c r="H24" s="36"/>
+      <c r="H24" s="94">
+        <v>5</v>
+      </c>
     </row>
     <row r="25" spans="2:8" ht="76.5" x14ac:dyDescent="0.45">
       <c r="B25" s="35" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C25" s="40" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D25" s="57">
         <v>5</v>
       </c>
       <c r="E25" s="34" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F25" s="34"/>
       <c r="G25" s="29"/>
-      <c r="H25" s="36"/>
+      <c r="H25" s="94"/>
     </row>
     <row r="26" spans="2:8" ht="51" x14ac:dyDescent="0.45">
       <c r="B26" s="35" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C26" s="40" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D26" s="34">
         <f>ROUND(ATAN(D25/100)*180/PI(),0)</f>
         <v>3</v>
       </c>
       <c r="E26" s="34" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F26" s="34"/>
       <c r="G26" s="29"/>
-      <c r="H26" s="36"/>
+      <c r="H26" s="94"/>
     </row>
     <row r="27" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
       <c r="B27" s="50" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C27" s="51" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D27" s="58">
         <v>0.6</v>
       </c>
       <c r="E27" s="52" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F27" s="52"/>
       <c r="G27" s="31"/>
-      <c r="H27" s="53"/>
+      <c r="H27" s="95"/>
     </row>
     <row r="28" spans="2:8" ht="33" x14ac:dyDescent="0.45">
       <c r="B28" s="35" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C28" s="40" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="D28" s="41">
         <v>0.2</v>
       </c>
       <c r="E28" s="34" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F28" s="34"/>
       <c r="G28" s="29"/>
-      <c r="H28" s="36"/>
+      <c r="H28" s="94"/>
     </row>
     <row r="29" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
       <c r="B29" s="35" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C29" s="40" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D29" s="41">
         <v>2</v>
       </c>
       <c r="E29" s="34" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F29" s="34"/>
       <c r="G29" s="29"/>
-      <c r="H29" s="36"/>
+      <c r="H29" s="94"/>
     </row>
     <row r="30" spans="2:8" ht="33" x14ac:dyDescent="0.45">
       <c r="B30" s="50" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C30" s="51" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D30" s="52">
         <f>(D27-D28)*(D11+D24+D24)*D29</f>
         <v>32.799999999999997</v>
       </c>
       <c r="E30" s="34" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F30" s="52"/>
       <c r="G30" s="31"/>
-      <c r="H30" s="53"/>
+      <c r="H30" s="95"/>
     </row>
     <row r="31" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
       <c r="B31" s="35" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C31" s="40" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D31" s="34">
         <f>(D10*D11)-D30</f>
         <v>1262.2</v>
       </c>
       <c r="E31" s="34" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F31" s="34"/>
       <c r="G31" s="29"/>
-      <c r="H31" s="36"/>
+      <c r="H31" s="94"/>
     </row>
     <row r="32" spans="2:8" ht="51" x14ac:dyDescent="0.45">
       <c r="B32" s="35" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C32" s="40" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D32" s="34">
         <f>((D10*D11)+D10*(D24+D24))-D30</f>
         <v>1402.2</v>
       </c>
       <c r="E32" s="34" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F32" s="34"/>
       <c r="G32" s="29"/>
-      <c r="H32" s="36"/>
+      <c r="H32" s="94"/>
     </row>
     <row r="33" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
       <c r="B33" s="35" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C33" s="40" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D33" s="41">
         <v>10</v>
       </c>
       <c r="E33" s="34" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F33" s="34"/>
       <c r="G33" s="29"/>
-      <c r="H33" s="36"/>
+      <c r="H33" s="94"/>
     </row>
     <row r="34" spans="2:8" ht="51" x14ac:dyDescent="0.45">
       <c r="B34" s="35" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C34" s="40" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D34" s="34">
         <f>EVEN(D31/(D33*D33))</f>
         <v>14</v>
       </c>
       <c r="E34" s="34" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F34" s="34"/>
       <c r="G34" s="29"/>
-      <c r="H34" s="36"/>
+      <c r="H34" s="94"/>
     </row>
     <row r="35" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
       <c r="B35" s="35" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C35" s="40" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D35" s="41">
         <v>1200</v>
       </c>
       <c r="E35" s="34" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F35" s="34"/>
       <c r="G35" s="29"/>
-      <c r="H35" s="36"/>
+      <c r="H35" s="94"/>
     </row>
     <row r="36" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
       <c r="B36" s="35" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C36" s="40" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D36" s="34">
         <f>D35*D35/(1000*1000)</f>
         <v>1.44</v>
       </c>
       <c r="E36" s="34" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F36" s="34"/>
       <c r="G36" s="29"/>
-      <c r="H36" s="36"/>
+      <c r="H36" s="94"/>
     </row>
     <row r="37" spans="2:8" ht="33" x14ac:dyDescent="0.45">
       <c r="B37" s="35" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C37" s="40" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D37" s="34">
         <f>D34*D36</f>
         <v>20.16</v>
       </c>
       <c r="E37" s="34" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F37" s="34"/>
       <c r="G37" s="29"/>
-      <c r="H37" s="36"/>
+      <c r="H37" s="94"/>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B38" s="46"/>
@@ -3065,88 +3566,90 @@
       <c r="E38" s="48"/>
       <c r="F38" s="48"/>
       <c r="G38" s="30"/>
-      <c r="H38" s="49"/>
+      <c r="H38" s="96"/>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B39" s="56" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C39" s="37"/>
       <c r="D39" s="38"/>
       <c r="E39" s="38"/>
       <c r="F39" s="38"/>
       <c r="G39" s="37"/>
-      <c r="H39" s="39"/>
+      <c r="H39" s="93"/>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B40" s="35" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C40" s="40" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D40" s="41">
         <v>1</v>
       </c>
       <c r="E40" s="34" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F40" s="34"/>
       <c r="G40" s="29"/>
-      <c r="H40" s="36"/>
+      <c r="H40" s="94">
+        <v>5</v>
+      </c>
     </row>
     <row r="41" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
       <c r="B41" s="35" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C41" s="40" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D41" s="41">
         <v>15</v>
       </c>
       <c r="E41" s="34" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F41" s="34"/>
       <c r="G41" s="29"/>
-      <c r="H41" s="36"/>
+      <c r="H41" s="94"/>
     </row>
     <row r="42" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
       <c r="B42" s="35" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C42" s="40" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D42" s="34">
         <f>D11+(INT(D11/D41)*D10)</f>
         <v>107</v>
       </c>
       <c r="E42" s="34" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F42" s="34"/>
       <c r="G42" s="29"/>
-      <c r="H42" s="36"/>
+      <c r="H42" s="94"/>
     </row>
     <row r="43" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
       <c r="B43" s="35" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C43" s="40" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D43" s="34">
         <f>D42*D40</f>
         <v>107</v>
       </c>
       <c r="E43" s="34" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F43" s="34"/>
       <c r="G43" s="29"/>
-      <c r="H43" s="36"/>
+      <c r="H43" s="94"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B44" s="46"/>
@@ -3155,276 +3658,278 @@
       <c r="E44" s="48"/>
       <c r="F44" s="48"/>
       <c r="G44" s="30"/>
-      <c r="H44" s="49"/>
+      <c r="H44" s="96"/>
     </row>
     <row r="45" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B45" s="56" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C45" s="37"/>
       <c r="D45" s="38"/>
       <c r="E45" s="38"/>
       <c r="F45" s="38"/>
       <c r="G45" s="37"/>
-      <c r="H45" s="39"/>
+      <c r="H45" s="93"/>
     </row>
     <row r="46" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
       <c r="B46" s="35" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C46" s="40" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="D46" s="41">
         <v>60</v>
       </c>
       <c r="E46" s="34" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F46" s="34"/>
       <c r="G46" s="29"/>
-      <c r="H46" s="36"/>
+      <c r="H46" s="94">
+        <v>5</v>
+      </c>
     </row>
     <row r="47" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
       <c r="B47" s="35" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C47" s="40" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D47" s="41">
         <v>24</v>
       </c>
       <c r="E47" s="34" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F47" s="34"/>
       <c r="G47" s="29"/>
-      <c r="H47" s="36"/>
+      <c r="H47" s="94"/>
     </row>
     <row r="48" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
       <c r="B48" s="35" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C48" s="40" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D48" s="41">
         <v>3.9900000000000007</v>
       </c>
       <c r="E48" s="34" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F48" s="34"/>
       <c r="G48" s="29"/>
-      <c r="H48" s="36"/>
+      <c r="H48" s="94"/>
     </row>
     <row r="49" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
       <c r="B49" s="35" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C49" s="40" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D49" s="34">
         <f>D46-D54</f>
         <v>52.943999999999996</v>
       </c>
       <c r="E49" s="34" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F49" s="34"/>
       <c r="G49" s="29"/>
-      <c r="H49" s="36"/>
+      <c r="H49" s="94"/>
     </row>
     <row r="50" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
       <c r="B50" s="35" t="s">
+        <v>64</v>
+      </c>
+      <c r="C50" s="40" t="s">
         <v>63</v>
-      </c>
-      <c r="C50" s="40" t="s">
-        <v>62</v>
       </c>
       <c r="D50" s="41">
         <v>28</v>
       </c>
       <c r="E50" s="34" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F50" s="34"/>
       <c r="G50" s="29"/>
-      <c r="H50" s="36"/>
+      <c r="H50" s="94"/>
     </row>
     <row r="51" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
       <c r="B51" s="35" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C51" s="40" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D51" s="41">
         <v>19</v>
       </c>
       <c r="E51" s="34" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F51" s="34"/>
       <c r="G51" s="29"/>
-      <c r="H51" s="36"/>
+      <c r="H51" s="94"/>
     </row>
     <row r="52" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
       <c r="B52" s="35" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C52" s="40" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D52" s="34">
         <f>D48/(D51/100)</f>
         <v>21.000000000000004</v>
       </c>
       <c r="E52" s="34" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F52" s="34"/>
       <c r="G52" s="29"/>
-      <c r="H52" s="36"/>
+      <c r="H52" s="94"/>
     </row>
     <row r="53" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B53" s="35" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C53" s="40" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D53" s="41">
         <v>1.2</v>
       </c>
       <c r="E53" s="34" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F53" s="34"/>
       <c r="G53" s="29"/>
-      <c r="H53" s="36"/>
+      <c r="H53" s="94"/>
     </row>
     <row r="54" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
       <c r="B54" s="35" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C54" s="40" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="D54" s="54">
         <f>D53*D52*(D50/100)</f>
         <v>7.0560000000000018</v>
       </c>
       <c r="E54" s="34" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F54" s="34"/>
       <c r="G54" s="29"/>
-      <c r="H54" s="36"/>
+      <c r="H54" s="94"/>
     </row>
     <row r="55" spans="2:8" ht="89.25" x14ac:dyDescent="0.45">
       <c r="B55" s="35" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C55" s="40" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D55" s="41">
         <v>6</v>
       </c>
       <c r="E55" s="34" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F55" s="34"/>
       <c r="G55" s="29"/>
-      <c r="H55" s="36"/>
+      <c r="H55" s="94"/>
     </row>
     <row r="56" spans="2:8" ht="102" x14ac:dyDescent="0.45">
       <c r="B56" s="35" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C56" s="40" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D56" s="41">
         <v>4.5</v>
       </c>
       <c r="E56" s="34" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F56" s="34"/>
       <c r="G56" s="29"/>
-      <c r="H56" s="36"/>
+      <c r="H56" s="94"/>
     </row>
     <row r="57" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B57" s="35" t="s">
+        <v>144</v>
+      </c>
+      <c r="C57" s="40" t="s">
         <v>143</v>
-      </c>
-      <c r="C57" s="40" t="s">
-        <v>142</v>
       </c>
       <c r="D57" s="41">
         <v>1.2</v>
       </c>
       <c r="E57" s="34" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F57" s="34"/>
       <c r="G57" s="29"/>
-      <c r="H57" s="36"/>
+      <c r="H57" s="94"/>
     </row>
     <row r="58" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B58" s="35" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C58" s="40" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="D58" s="41">
         <v>2.2999999999999998</v>
       </c>
       <c r="E58" s="34" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F58" s="34"/>
       <c r="G58" s="29"/>
-      <c r="H58" s="36"/>
+      <c r="H58" s="94"/>
     </row>
     <row r="59" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
       <c r="B59" s="35" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C59" s="40" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="D59" s="41">
         <v>3</v>
       </c>
       <c r="E59" s="34" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F59" s="34"/>
       <c r="G59" s="29"/>
-      <c r="H59" s="36"/>
+      <c r="H59" s="94"/>
     </row>
     <row r="60" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
       <c r="B60" s="35" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C60" s="40" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="D60" s="41">
         <v>2</v>
       </c>
       <c r="E60" s="34" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F60" s="34"/>
       <c r="G60" s="29"/>
-      <c r="H60" s="36"/>
+      <c r="H60" s="94"/>
     </row>
     <row r="61" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B61" s="46"/>
@@ -3433,565 +3938,621 @@
       <c r="E61" s="48"/>
       <c r="F61" s="48"/>
       <c r="G61" s="30"/>
-      <c r="H61" s="49"/>
+      <c r="H61" s="96"/>
     </row>
     <row r="62" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B62" s="59" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C62" s="60"/>
       <c r="D62" s="61"/>
       <c r="E62" s="61"/>
       <c r="F62" s="61"/>
       <c r="G62" s="60"/>
-      <c r="H62" s="62"/>
+      <c r="H62" s="97"/>
     </row>
     <row r="63" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
       <c r="B63" s="35" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C63" s="40" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D63" s="41">
         <v>40</v>
       </c>
       <c r="E63" s="34" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F63" s="34"/>
       <c r="G63" s="29"/>
-      <c r="H63" s="36"/>
+      <c r="H63" s="94">
+        <v>5</v>
+      </c>
     </row>
     <row r="64" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
       <c r="B64" s="35" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C64" s="40" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D64" s="54">
         <f>D18</f>
         <v>1435</v>
       </c>
       <c r="E64" s="34" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F64" s="34"/>
       <c r="G64" s="29"/>
-      <c r="H64" s="36"/>
+      <c r="H64" s="94"/>
     </row>
     <row r="65" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
       <c r="B65" s="35" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C65" s="40" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D65" s="41">
         <v>20</v>
       </c>
       <c r="E65" s="34" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F65" s="34"/>
       <c r="G65" s="29"/>
-      <c r="H65" s="36"/>
+      <c r="H65" s="94"/>
     </row>
     <row r="66" spans="2:8" ht="33" x14ac:dyDescent="0.45">
       <c r="B66" s="35" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C66" s="40" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D66" s="41">
         <v>6</v>
       </c>
       <c r="E66" s="34" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F66" s="34"/>
       <c r="G66" s="29"/>
-      <c r="H66" s="36"/>
+      <c r="H66" s="94"/>
     </row>
     <row r="67" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
       <c r="B67" s="35" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C67" s="40" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D67" s="54">
         <f>ROUND(D10/D66,0)</f>
         <v>6</v>
       </c>
       <c r="E67" s="34" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F67" s="34"/>
       <c r="G67" s="29"/>
-      <c r="H67" s="36"/>
+      <c r="H67" s="94"/>
     </row>
     <row r="68" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
       <c r="B68" s="35" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C68" s="40" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D68" s="54">
         <f>ROUND(D11/D66,0)</f>
         <v>6</v>
       </c>
       <c r="E68" s="34" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F68" s="34"/>
       <c r="G68" s="29"/>
-      <c r="H68" s="36"/>
+      <c r="H68" s="94"/>
     </row>
     <row r="69" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B69" s="35" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C69" s="40" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D69" s="54">
         <f>D68*D67</f>
         <v>36</v>
       </c>
       <c r="E69" s="34" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F69" s="34"/>
       <c r="G69" s="29"/>
-      <c r="H69" s="36"/>
+      <c r="H69" s="94"/>
     </row>
     <row r="70" spans="2:8" ht="51" x14ac:dyDescent="0.45">
       <c r="B70" s="35" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C70" s="40" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D70" s="41">
         <v>0.3</v>
       </c>
       <c r="E70" s="34" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F70" s="34"/>
       <c r="G70" s="29"/>
-      <c r="H70" s="36"/>
+      <c r="H70" s="94"/>
     </row>
     <row r="71" spans="2:8" ht="51" x14ac:dyDescent="0.45">
       <c r="B71" s="35" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C71" s="40" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D71" s="41">
         <v>0.4</v>
       </c>
       <c r="E71" s="34" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F71" s="34"/>
       <c r="G71" s="29"/>
-      <c r="H71" s="36"/>
+      <c r="H71" s="94"/>
     </row>
     <row r="72" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
       <c r="B72" s="35" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C72" s="40" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D72" s="41">
         <v>0.3</v>
       </c>
       <c r="E72" s="34" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F72" s="34"/>
       <c r="G72" s="29"/>
-      <c r="H72" s="36"/>
+      <c r="H72" s="94"/>
     </row>
     <row r="73" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
       <c r="B73" s="35" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C73" s="40" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D73" s="41">
         <v>0.4</v>
       </c>
       <c r="E73" s="34" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F73" s="34"/>
       <c r="G73" s="29"/>
-      <c r="H73" s="36"/>
+      <c r="H73" s="94"/>
     </row>
     <row r="74" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
       <c r="B74" s="35" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C74" s="40" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="D74" s="54">
         <f>(D10-D70)/D67</f>
         <v>5.7833333333333341</v>
       </c>
       <c r="E74" s="34" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F74" s="34"/>
       <c r="G74" s="29"/>
-      <c r="H74" s="36"/>
+      <c r="H74" s="94"/>
     </row>
     <row r="75" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
       <c r="B75" s="35" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C75" s="40" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D75" s="54">
         <f>(D11-D71)/D68</f>
         <v>6.1000000000000005</v>
       </c>
       <c r="E75" s="34" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="F75" s="34"/>
       <c r="G75" s="29"/>
-      <c r="H75" s="36"/>
+      <c r="H75" s="94"/>
     </row>
     <row r="76" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B76" s="63"/>
-      <c r="C76" s="64"/>
-      <c r="D76" s="65"/>
-      <c r="E76" s="65"/>
-      <c r="F76" s="65"/>
+      <c r="B76" s="62"/>
+      <c r="C76" s="63"/>
+      <c r="D76" s="64"/>
+      <c r="E76" s="64"/>
+      <c r="F76" s="64"/>
       <c r="G76" s="4"/>
-      <c r="H76" s="5"/>
+      <c r="H76" s="9"/>
     </row>
     <row r="77" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B77" s="66" t="s">
-        <v>122</v>
+      <c r="B77" s="65" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="79" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B79" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="80" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B80" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C80" s="14" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="81" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B81" s="67" t="s">
         <v>169</v>
+      </c>
+    </row>
+    <row r="81" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B81" s="66" t="s">
+        <v>170</v>
       </c>
       <c r="C81" s="13">
         <f>D17</f>
         <v>1925</v>
       </c>
     </row>
-    <row r="82" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B82" s="67" t="s">
-        <v>172</v>
+    <row r="82" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B82" s="66" t="s">
+        <v>173</v>
       </c>
       <c r="C82" s="13">
         <f>D18</f>
         <v>1435</v>
       </c>
     </row>
-    <row r="83" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B83" s="67" t="s">
-        <v>171</v>
+    <row r="83" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B83" s="66" t="s">
+        <v>172</v>
       </c>
       <c r="C83" s="13">
         <f>D46</f>
         <v>60</v>
       </c>
     </row>
-    <row r="84" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B84" s="67" t="s">
-        <v>51</v>
+    <row r="84" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B84" s="66" t="s">
+        <v>52</v>
       </c>
       <c r="C84" s="13">
         <f>D54</f>
         <v>7.0560000000000018</v>
       </c>
     </row>
-    <row r="85" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B85" s="67" t="s">
-        <v>50</v>
+    <row r="85" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B85" s="66" t="s">
+        <v>51</v>
       </c>
       <c r="C85" s="13">
         <f>D49</f>
         <v>52.943999999999996</v>
       </c>
     </row>
-    <row r="86" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B86" s="68" t="s">
-        <v>170</v>
-      </c>
-      <c r="C86" s="69">
+    <row r="86" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B86" s="67" t="s">
+        <v>171</v>
+      </c>
+      <c r="C86" s="68">
         <f>D19</f>
         <v>1495</v>
       </c>
     </row>
-    <row r="87" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B87" s="70" t="s">
-        <v>77</v>
-      </c>
-      <c r="C87" s="71">
+    <row r="87" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B87" s="69" t="s">
+        <v>78</v>
+      </c>
+      <c r="C87" s="70">
         <f>D20</f>
         <v>0.74545454545454548</v>
       </c>
     </row>
-    <row r="88" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B88" s="63" t="s">
-        <v>113</v>
+    <row r="88" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B88" s="62" t="s">
+        <v>114</v>
       </c>
       <c r="C88" s="5">
         <f>D21</f>
         <v>0.77662337662337666</v>
       </c>
     </row>
-    <row r="90" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="90" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B90" s="2" t="s">
         <v>248</v>
       </c>
     </row>
-    <row r="91" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="91" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B91" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C91" s="37" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D91" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="E91" s="10" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="92" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="E91" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="F91" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="G91" s="37" t="s">
+        <v>27</v>
+      </c>
+      <c r="H91" s="93" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="92" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B92" s="35" t="s">
+        <v>188</v>
+      </c>
+      <c r="C92" s="29" t="s">
         <v>187</v>
       </c>
-      <c r="C92" s="29" t="s">
-        <v>186</v>
-      </c>
-      <c r="D92" s="73">
+      <c r="D92" s="72">
         <f>D64</f>
         <v>1435</v>
       </c>
-      <c r="E92" s="11" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="93" spans="2:5" ht="33" x14ac:dyDescent="0.45">
+      <c r="E92" s="72" t="s">
+        <v>61</v>
+      </c>
+      <c r="F92" s="34"/>
+      <c r="G92" s="29"/>
+      <c r="H92" s="94"/>
+    </row>
+    <row r="93" spans="2:8" ht="33" x14ac:dyDescent="0.45">
       <c r="B93" s="35" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C93" s="29" t="s">
-        <v>189</v>
-      </c>
-      <c r="D93" s="73">
+        <v>190</v>
+      </c>
+      <c r="D93" s="72">
         <f>D92*D63</f>
         <v>57400</v>
       </c>
-      <c r="E93" s="11" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="94" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="E93" s="72" t="s">
+        <v>191</v>
+      </c>
+      <c r="F93" s="34"/>
+      <c r="G93" s="29"/>
+      <c r="H93" s="94"/>
+    </row>
+    <row r="94" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B94" s="35" t="s">
+        <v>200</v>
+      </c>
+      <c r="C94" s="29" t="s">
         <v>199</v>
       </c>
-      <c r="C94" s="29" t="s">
-        <v>198</v>
-      </c>
-      <c r="D94" s="73">
+      <c r="D94" s="72">
         <f>D49</f>
         <v>52.943999999999996</v>
       </c>
-      <c r="E94" s="11" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="95" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="E94" s="72" t="s">
+        <v>61</v>
+      </c>
+      <c r="F94" s="72"/>
+      <c r="G94" s="3"/>
+      <c r="H94" s="11"/>
+    </row>
+    <row r="95" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B95" s="35" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C95" s="29" t="s">
-        <v>193</v>
-      </c>
-      <c r="D95" s="73">
+        <v>194</v>
+      </c>
+      <c r="D95" s="72">
         <f>D69</f>
         <v>36</v>
       </c>
-      <c r="E95" s="11" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="96" spans="2:5" ht="33" x14ac:dyDescent="0.45">
+      <c r="E95" s="72" t="s">
+        <v>130</v>
+      </c>
+      <c r="F95" s="72"/>
+      <c r="G95" s="3"/>
+      <c r="H95" s="11"/>
+    </row>
+    <row r="96" spans="2:8" ht="33" x14ac:dyDescent="0.45">
       <c r="B96" s="35" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C96" s="29" t="s">
-        <v>195</v>
-      </c>
-      <c r="D96" s="73">
+        <v>196</v>
+      </c>
+      <c r="D96" s="72">
         <f>D95*D12</f>
         <v>432</v>
       </c>
-      <c r="E96" s="11" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="97" spans="2:5" ht="49.5" x14ac:dyDescent="0.45">
+      <c r="E96" s="72" t="s">
+        <v>60</v>
+      </c>
+      <c r="F96" s="72"/>
+      <c r="G96" s="3"/>
+      <c r="H96" s="11"/>
+    </row>
+    <row r="97" spans="2:8" ht="49.5" x14ac:dyDescent="0.45">
       <c r="B97" s="35" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C97" s="29" t="s">
-        <v>197</v>
-      </c>
-      <c r="D97" s="73">
+        <v>198</v>
+      </c>
+      <c r="D97" s="72">
         <f>((D67*D9)+(D68*D8))*INT(D12/D48)</f>
         <v>324</v>
       </c>
-      <c r="E97" s="11" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="98" spans="2:5" ht="33" x14ac:dyDescent="0.45">
-      <c r="B98" s="50" t="s">
-        <v>207</v>
-      </c>
-      <c r="C98" s="31" t="s">
+      <c r="E97" s="72" t="s">
+        <v>60</v>
+      </c>
+      <c r="F97" s="72"/>
+      <c r="G97" s="3"/>
+      <c r="H97" s="11"/>
+    </row>
+    <row r="98" spans="2:8" ht="33" x14ac:dyDescent="0.45">
+      <c r="B98" s="35" t="s">
+        <v>208</v>
+      </c>
+      <c r="C98" s="29" t="s">
+        <v>211</v>
+      </c>
+      <c r="D98" s="91" t="s">
         <v>210</v>
       </c>
-      <c r="D98" s="76" t="s">
+      <c r="E98" s="72" t="s">
+        <v>61</v>
+      </c>
+      <c r="F98" s="72"/>
+      <c r="G98" s="3"/>
+      <c r="H98" s="11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="99" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B99" s="35" t="s">
         <v>209</v>
       </c>
-      <c r="E98" s="11" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="99" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B99" s="50" t="s">
-        <v>208</v>
-      </c>
-      <c r="C99" s="31" t="s">
-        <v>211</v>
-      </c>
-      <c r="D99" s="76">
+      <c r="C99" s="29" t="s">
+        <v>212</v>
+      </c>
+      <c r="D99" s="91">
         <v>2</v>
       </c>
-      <c r="E99" s="11" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="100" spans="2:5" ht="49.5" x14ac:dyDescent="0.45">
-      <c r="B100" s="50" t="s">
-        <v>52</v>
-      </c>
-      <c r="C100" s="31" t="s">
-        <v>212</v>
-      </c>
-      <c r="D100" s="76" t="s">
-        <v>209</v>
-      </c>
-      <c r="E100" s="11" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="101" spans="2:5" ht="33" x14ac:dyDescent="0.45">
-      <c r="B101" s="50" t="s">
+      <c r="E99" s="72" t="s">
+        <v>130</v>
+      </c>
+      <c r="F99" s="72"/>
+      <c r="G99" s="3"/>
+      <c r="H99" s="11"/>
+    </row>
+    <row r="100" spans="2:8" ht="49.5" x14ac:dyDescent="0.45">
+      <c r="B100" s="35" t="s">
         <v>53</v>
       </c>
-      <c r="C101" s="31" t="s">
+      <c r="C100" s="29" t="s">
         <v>213</v>
       </c>
-      <c r="D101" s="76" t="s">
-        <v>209</v>
-      </c>
-      <c r="E101" s="11" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="102" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B102" s="50"/>
-      <c r="C102" s="31"/>
-      <c r="D102" s="74"/>
-      <c r="E102" s="75"/>
-    </row>
-    <row r="103" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="D100" s="91" t="s">
+        <v>210</v>
+      </c>
+      <c r="E100" s="72" t="s">
+        <v>130</v>
+      </c>
+      <c r="F100" s="72"/>
+      <c r="G100" s="3"/>
+      <c r="H100" s="11"/>
+    </row>
+    <row r="101" spans="2:8" ht="33" x14ac:dyDescent="0.45">
+      <c r="B101" s="35" t="s">
+        <v>54</v>
+      </c>
+      <c r="C101" s="29" t="s">
+        <v>214</v>
+      </c>
+      <c r="D101" s="91" t="s">
+        <v>210</v>
+      </c>
+      <c r="E101" s="72" t="s">
+        <v>130</v>
+      </c>
+      <c r="F101" s="72"/>
+      <c r="G101" s="3"/>
+      <c r="H101" s="11"/>
+    </row>
+    <row r="102" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B102" s="35"/>
+      <c r="C102" s="29"/>
+      <c r="D102" s="72"/>
+      <c r="E102" s="72"/>
+      <c r="F102" s="72"/>
+      <c r="G102" s="3"/>
+      <c r="H102" s="11"/>
+    </row>
+    <row r="103" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B103" s="46"/>
       <c r="C103" s="30"/>
-      <c r="D103" s="65"/>
-      <c r="E103" s="9"/>
-    </row>
-    <row r="104" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B104" s="72"/>
-      <c r="C104" s="72"/>
-    </row>
-    <row r="105" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B105" s="72"/>
-      <c r="C105" s="72"/>
-    </row>
-    <row r="106" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B106" s="72"/>
-      <c r="C106" s="72"/>
-    </row>
-    <row r="107" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B107" s="72"/>
-      <c r="C107" s="72"/>
-    </row>
-    <row r="108" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B108" s="72"/>
-      <c r="C108" s="72"/>
-    </row>
-    <row r="109" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B109" s="72"/>
-      <c r="C109" s="72"/>
-    </row>
-    <row r="110" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B110" s="72"/>
-      <c r="C110" s="72"/>
-    </row>
-    <row r="111" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B111" s="72"/>
-      <c r="C111" s="72"/>
-    </row>
-    <row r="112" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B112" s="72"/>
-      <c r="C112" s="72"/>
+      <c r="D103" s="64"/>
+      <c r="E103" s="64"/>
+      <c r="F103" s="64"/>
+      <c r="G103" s="4"/>
+      <c r="H103" s="9"/>
+    </row>
+    <row r="104" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B104" s="71"/>
+      <c r="C104" s="71"/>
+    </row>
+    <row r="105" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B105" s="71"/>
+      <c r="C105" s="71"/>
+      <c r="G105" s="107" t="s">
+        <v>276</v>
+      </c>
+      <c r="H105" s="55">
+        <f>AVERAGE(H6:H104)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="106" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B106" s="71"/>
+      <c r="C106" s="71"/>
+    </row>
+    <row r="107" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B107" s="71"/>
+      <c r="C107" s="71"/>
+    </row>
+    <row r="108" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B108" s="71"/>
+      <c r="C108" s="71"/>
+    </row>
+    <row r="109" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B109" s="71"/>
+      <c r="C109" s="71"/>
+    </row>
+    <row r="110" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B110" s="71"/>
+      <c r="C110" s="71"/>
+    </row>
+    <row r="111" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B111" s="71"/>
+      <c r="C111" s="71"/>
+    </row>
+    <row r="112" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B112" s="71"/>
+      <c r="C112" s="71"/>
     </row>
     <row r="113" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B113" s="72"/>
-      <c r="C113" s="72"/>
+      <c r="B113" s="71"/>
+      <c r="C113" s="71"/>
     </row>
     <row r="114" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B114" s="72"/>
-      <c r="C114" s="72"/>
+      <c r="B114" s="71"/>
+      <c r="C114" s="71"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4002,7 +4563,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDC0663E-105D-42EA-893B-DB8B7FE41FC2}">
   <dimension ref="B2:H30"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -4023,44 +4584,44 @@
     </row>
     <row r="3" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="B3" s="20" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B4" s="86" t="s">
+      <c r="B4" s="82" t="s">
         <v>247</v>
       </c>
-      <c r="C4" s="86"/>
-      <c r="D4" s="86"/>
-      <c r="E4" s="86"/>
-      <c r="F4" s="86"/>
-      <c r="G4" s="86"/>
-      <c r="H4" s="86"/>
+      <c r="C4" s="82"/>
+      <c r="D4" s="82"/>
+      <c r="E4" s="82"/>
+      <c r="F4" s="82"/>
+      <c r="G4" s="82"/>
+      <c r="H4" s="82"/>
     </row>
     <row r="5" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B5" s="91"/>
-      <c r="C5" s="91"/>
-      <c r="D5" s="91"/>
-      <c r="E5" s="91"/>
-      <c r="F5" s="91"/>
-      <c r="G5" s="91"/>
-      <c r="H5" s="91"/>
+      <c r="B5" s="87"/>
+      <c r="C5" s="87"/>
+      <c r="D5" s="87"/>
+      <c r="E5" s="87"/>
+      <c r="F5" s="87"/>
+      <c r="G5" s="87"/>
+      <c r="H5" s="87"/>
     </row>
     <row r="6" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="B6" s="42" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C6" s="43" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D6" s="44" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E6" s="44" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F6" s="44" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G6" s="43" t="s">
         <v>27</v>
@@ -4071,7 +4632,7 @@
     </row>
     <row r="7" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="B7" s="6" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C7" s="37"/>
       <c r="D7" s="38"/>
@@ -4082,16 +4643,16 @@
     </row>
     <row r="8" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
       <c r="B8" s="35" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="C8" s="40" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="D8" s="34">
         <v>1</v>
       </c>
       <c r="E8" s="34" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F8" s="34"/>
       <c r="G8" s="29"/>
@@ -4108,7 +4669,7 @@
     </row>
     <row r="10" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="B10" s="6" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C10" s="37"/>
       <c r="D10" s="38"/>
@@ -4119,16 +4680,16 @@
     </row>
     <row r="11" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
       <c r="B11" s="35" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="C11" s="40" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="D11" s="34">
         <v>1</v>
       </c>
       <c r="E11" s="34" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F11" s="34"/>
       <c r="G11" s="29"/>
@@ -4136,16 +4697,16 @@
     </row>
     <row r="12" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="B12" s="35" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C12" s="40" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D12" s="34">
         <v>1</v>
       </c>
       <c r="E12" s="34" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F12" s="34"/>
       <c r="G12" s="29"/>
@@ -4153,16 +4714,16 @@
     </row>
     <row r="13" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="B13" s="35" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C13" s="40" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D13" s="34">
         <v>1</v>
       </c>
       <c r="E13" s="34" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F13" s="34"/>
       <c r="G13" s="29"/>
@@ -4170,16 +4731,16 @@
     </row>
     <row r="14" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
       <c r="B14" s="35" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="C14" s="40" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D14" s="34">
         <v>1</v>
       </c>
       <c r="E14" s="34" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F14" s="34"/>
       <c r="G14" s="29"/>
@@ -4187,16 +4748,16 @@
     </row>
     <row r="15" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
       <c r="B15" s="50" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="C15" s="40" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D15" s="34">
         <v>1</v>
       </c>
       <c r="E15" s="34" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F15" s="52"/>
       <c r="G15" s="31"/>
@@ -4204,16 +4765,16 @@
     </row>
     <row r="16" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="B16" s="50" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="C16" s="40" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D16" s="34">
         <v>1</v>
       </c>
       <c r="E16" s="34" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F16" s="52"/>
       <c r="G16" s="31"/>
@@ -4221,16 +4782,16 @@
     </row>
     <row r="17" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="B17" s="35" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="C17" s="40" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D17" s="34">
         <v>1</v>
       </c>
       <c r="E17" s="34" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F17" s="34"/>
       <c r="G17" s="29"/>
@@ -4238,16 +4799,16 @@
     </row>
     <row r="18" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="B18" s="35" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C18" s="40" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D18" s="34">
         <v>1</v>
       </c>
       <c r="E18" s="34" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F18" s="34"/>
       <c r="G18" s="29"/>
@@ -4255,16 +4816,16 @@
     </row>
     <row r="19" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="B19" s="50" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C19" s="40" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D19" s="34">
         <v>1</v>
       </c>
       <c r="E19" s="34" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F19" s="52"/>
       <c r="G19" s="31"/>
@@ -4275,13 +4836,13 @@
         <v>261</v>
       </c>
       <c r="C20" s="40" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D20" s="34">
         <v>1</v>
       </c>
       <c r="E20" s="34" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F20" s="52"/>
       <c r="G20" s="31"/>
@@ -4289,16 +4850,16 @@
     </row>
     <row r="21" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="B21" s="50" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C21" s="40" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D21" s="34">
         <v>1</v>
       </c>
       <c r="E21" s="34" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F21" s="52"/>
       <c r="G21" s="31"/>
@@ -4306,16 +4867,16 @@
     </row>
     <row r="22" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="B22" s="50" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="C22" s="40" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D22" s="52">
         <v>1</v>
       </c>
       <c r="E22" s="34" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F22" s="52"/>
       <c r="G22" s="31"/>
@@ -4323,16 +4884,16 @@
     </row>
     <row r="23" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="B23" s="50" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="C23" s="40" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D23" s="52">
         <v>1</v>
       </c>
       <c r="E23" s="34" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F23" s="52"/>
       <c r="G23" s="31"/>
@@ -4349,7 +4910,7 @@
     </row>
     <row r="25" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="B25" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="C25" s="37"/>
       <c r="D25" s="38"/>
@@ -4360,17 +4921,17 @@
     </row>
     <row r="26" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
       <c r="B26" s="35" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="C26" s="40" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="D26" s="54">
         <f>'2.Arquitectónica'!D31-'2.Arquitectónica'!D37-'2.Arquitectónica'!D43</f>
         <v>1135.04</v>
       </c>
       <c r="E26" s="34" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F26" s="34"/>
       <c r="G26" s="29"/>
@@ -4378,16 +4939,16 @@
     </row>
     <row r="27" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="B27" s="35" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="C27" s="40" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D27" s="41">
         <v>992</v>
       </c>
       <c r="E27" s="34" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F27" s="34"/>
       <c r="G27" s="29"/>
@@ -4395,16 +4956,16 @@
     </row>
     <row r="28" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="B28" s="35" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="C28" s="40" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="D28" s="41">
         <v>1950</v>
       </c>
       <c r="E28" s="34" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F28" s="34"/>
       <c r="G28" s="29"/>
@@ -4412,17 +4973,17 @@
     </row>
     <row r="29" spans="2:8" ht="51" x14ac:dyDescent="0.45">
       <c r="B29" s="35" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="C29" s="40" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="D29" s="34">
         <f>INT(D26/(D27/1000*D28/1000))</f>
         <v>586</v>
       </c>
       <c r="E29" s="34" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F29" s="34"/>
       <c r="G29" s="29"/>
@@ -4446,7 +5007,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36B29233-B656-46A0-B3DE-6C1E8F28F7E1}">
   <dimension ref="B2:H16"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -4471,40 +5032,40 @@
       </c>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B4" s="86" t="s">
+      <c r="B4" s="82" t="s">
         <v>255</v>
       </c>
-      <c r="C4" s="86"/>
-      <c r="D4" s="86"/>
-      <c r="E4" s="86"/>
-      <c r="F4" s="86"/>
-      <c r="G4" s="86"/>
-      <c r="H4" s="86"/>
+      <c r="C4" s="82"/>
+      <c r="D4" s="82"/>
+      <c r="E4" s="82"/>
+      <c r="F4" s="82"/>
+      <c r="G4" s="82"/>
+      <c r="H4" s="82"/>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B5" s="91"/>
-      <c r="C5" s="91"/>
-      <c r="D5" s="91"/>
-      <c r="E5" s="91"/>
-      <c r="F5" s="91"/>
-      <c r="G5" s="91"/>
-      <c r="H5" s="91"/>
+      <c r="B5" s="87"/>
+      <c r="C5" s="87"/>
+      <c r="D5" s="87"/>
+      <c r="E5" s="87"/>
+      <c r="F5" s="87"/>
+      <c r="G5" s="87"/>
+      <c r="H5" s="87"/>
     </row>
     <row r="6" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="B6" s="42" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C6" s="43" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D6" s="44" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E6" s="44" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="F6" s="44" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G6" s="43" t="s">
         <v>27</v>
@@ -4524,7 +5085,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="34" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F7" s="34"/>
       <c r="G7" s="29"/>
@@ -4541,7 +5102,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="34" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F8" s="34"/>
       <c r="G8" s="29"/>
@@ -4558,7 +5119,7 @@
         <v>1</v>
       </c>
       <c r="E9" s="34" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F9" s="34"/>
       <c r="G9" s="29"/>
@@ -4575,7 +5136,7 @@
         <v>1</v>
       </c>
       <c r="E10" s="34" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F10" s="34"/>
       <c r="G10" s="29"/>
@@ -4586,13 +5147,13 @@
         <v>256</v>
       </c>
       <c r="C11" s="40" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D11" s="41">
         <v>1</v>
       </c>
       <c r="E11" s="34" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F11" s="34"/>
       <c r="G11" s="29"/>
@@ -4603,13 +5164,13 @@
         <v>257</v>
       </c>
       <c r="C12" s="40" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="D12" s="41">
         <v>1</v>
       </c>
       <c r="E12" s="34" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F12" s="34"/>
       <c r="G12" s="29"/>
@@ -4620,13 +5181,13 @@
         <v>258</v>
       </c>
       <c r="C13" s="40" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="D13" s="41">
         <v>1</v>
       </c>
       <c r="E13" s="34" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F13" s="34"/>
       <c r="G13" s="29"/>
@@ -4637,13 +5198,13 @@
         <v>259</v>
       </c>
       <c r="C14" s="40" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D14" s="41">
         <v>1</v>
       </c>
       <c r="E14" s="34" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F14" s="34"/>
       <c r="G14" s="29"/>
@@ -4654,13 +5215,13 @@
         <v>260</v>
       </c>
       <c r="C15" s="40" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="D15" s="41">
         <v>1</v>
       </c>
       <c r="E15" s="34" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F15" s="34"/>
       <c r="G15" s="29"/>
@@ -4669,7 +5230,7 @@
     <row r="16" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="B16" s="46"/>
       <c r="C16" s="47"/>
-      <c r="D16" s="94"/>
+      <c r="D16" s="90"/>
       <c r="E16" s="48"/>
       <c r="F16" s="48"/>
       <c r="G16" s="30"/>
@@ -4684,7 +5245,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:F26"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
@@ -4698,22 +5259,22 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B2" s="87" t="s">
+      <c r="B2" s="83" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="87"/>
-      <c r="D2" s="87"/>
-      <c r="E2" s="87"/>
-      <c r="F2" s="87"/>
+      <c r="C2" s="83"/>
+      <c r="D2" s="83"/>
+      <c r="E2" s="83"/>
+      <c r="F2" s="83"/>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B3" s="87" t="s">
+      <c r="B3" s="83" t="s">
         <v>16</v>
       </c>
-      <c r="C3" s="87"/>
-      <c r="D3" s="87"/>
-      <c r="E3" s="87"/>
-      <c r="F3" s="87"/>
+      <c r="C3" s="83"/>
+      <c r="D3" s="83"/>
+      <c r="E3" s="83"/>
+      <c r="F3" s="83"/>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B5" s="17" t="s">
@@ -4763,7 +5324,7 @@
         <v>2</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>15</v>
@@ -4781,8 +5342,8 @@
       <c r="D9" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E9" s="92"/>
-      <c r="F9" s="93"/>
+      <c r="E9" s="88"/>
+      <c r="F9" s="89"/>
     </row>
     <row r="10" spans="2:6" ht="54.75" x14ac:dyDescent="0.45">
       <c r="B10" s="15">
@@ -4794,8 +5355,8 @@
       <c r="D10" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E10" s="92"/>
-      <c r="F10" s="93"/>
+      <c r="E10" s="88"/>
+      <c r="F10" s="89"/>
     </row>
     <row r="11" spans="2:6" ht="29.25" x14ac:dyDescent="0.45">
       <c r="B11" s="15">
@@ -4807,8 +5368,8 @@
       <c r="D11" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="E11" s="92"/>
-      <c r="F11" s="93"/>
+      <c r="E11" s="88"/>
+      <c r="F11" s="89"/>
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B12" s="15">
@@ -4957,7 +5518,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCD4CBC5-BEDD-4E97-A57A-4EDFE72E7B14}">
   <dimension ref="B1:B4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.6"/>

--- a/file/table/DAPC_ProyectoCAD.xlsx
+++ b/file/table/DAPC_ProyectoCAD.xlsx
@@ -8,20 +8,25 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5587D53-E66E-4033-B768-26DA77B8FEB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1CABA3C-473F-4262-9284-D51AFEBC2BA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0.Inicio" sheetId="7" r:id="rId1"/>
-    <sheet name="1.Técnica" sheetId="2" r:id="rId2"/>
-    <sheet name="2.Arquitectónica" sheetId="4" r:id="rId3"/>
-    <sheet name="3.Eléctrica" sheetId="5" r:id="rId4"/>
-    <sheet name="3.Planos" sheetId="6" r:id="rId5"/>
-    <sheet name="Files" sheetId="1" r:id="rId6"/>
-    <sheet name="Metadata" sheetId="3" r:id="rId7"/>
+    <sheet name="1.Tecnica" sheetId="2" r:id="rId2"/>
+    <sheet name="2.ArquitectonicaEstructural" sheetId="4" r:id="rId3"/>
+    <sheet name="3.Electrica" sheetId="5" r:id="rId4"/>
+    <sheet name="4.Bodegaje" sheetId="9" r:id="rId5"/>
+    <sheet name="5.Planos" sheetId="6" r:id="rId6"/>
+    <sheet name="5.Archivos" sheetId="1" r:id="rId7"/>
+    <sheet name="Metadata" sheetId="3" r:id="rId8"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId9"/>
+  </externalReferences>
   <definedNames>
+    <definedName name="SumUDig" localSheetId="4">'[1]1.Técnicas'!$E$32</definedName>
     <definedName name="SumUDig">'0.Inicio'!$E$30</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -73,7 +78,7 @@
     <author>Test</author>
   </authors>
   <commentList>
-    <comment ref="E7" authorId="0" shapeId="0" xr:uid="{1CC115FE-8EE3-41FE-9390-20E34CE223E1}">
+    <comment ref="E6" authorId="0" shapeId="0" xr:uid="{1CC115FE-8EE3-41FE-9390-20E34CE223E1}">
       <text>
         <r>
           <rPr>
@@ -87,7 +92,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F7" authorId="0" shapeId="0" xr:uid="{3370069B-EA07-43C8-B4DF-40CDA6C2AF87}">
+    <comment ref="F6" authorId="0" shapeId="0" xr:uid="{3370069B-EA07-43C8-B4DF-40CDA6C2AF87}">
       <text>
         <r>
           <rPr>
@@ -201,6 +206,44 @@
     <author>Test</author>
   </authors>
   <commentList>
+    <comment ref="E6" authorId="0" shapeId="0" xr:uid="{4AAB5D75-8B66-4956-854F-BDEB1CBEB32D}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI Light"/>
+            <family val="2"/>
+          </rPr>
+          <t>Un. corresponde a Unidad.
+n/a: no aplica.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F6" authorId="0" shapeId="0" xr:uid="{1437ED91-2183-47E5-9523-7741C32FA50D}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI Light"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Actividad de referencia en curso DAPC.
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Test</author>
+  </authors>
+  <commentList>
     <comment ref="E6" authorId="0" shapeId="0" xr:uid="{8681E41C-04C6-435F-A500-461FDAE9051E}">
       <text>
         <r>
@@ -256,7 +299,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="280">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="336">
   <si>
     <t>1. Especificaciones técnicas generales</t>
   </si>
@@ -304,9 +347,6 @@
   </si>
   <si>
     <t>/file/cad/DAPC.dwt</t>
-  </si>
-  <si>
-    <t>Archivos digitales del proyecto</t>
   </si>
   <si>
     <t>Archivo</t>
@@ -408,41 +448,12 @@
     </r>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Estructura de directorios </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>(Utilizar la estructura definida para el curso DAPC)</t>
-    </r>
-  </si>
-  <si>
     <t>/file/</t>
   </si>
   <si>
     <t>El proyecto se desarrolla en grupo, el número de estudiantes se indica al inicio del curso. Cada grupo tendrá un código numérico consecutivo asignado por el instructor. Los estudiantes deberán definir el nombre de su grupo de proyecto y crear un logotipo en AutoCAD. El código, logotipo y nombre del grupo deberán incluirse en todos los planos generados.</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">Plantilla o layout AutoCAD
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>Incluye unidades de dibujo lineales en metros, angulares en grados, precisión a dos decimales, capas o layers, estilos de acotado fijos y anotativos para las diferentes escalas de impresión a usar utilizando el prefijo DAPC., formatos para impresión A0 / A4 con logotipo, código y nombre del grupo. Se deben utilizar los nombres de capas establecidos en la norma internacional estándar ISO-13567, aplicando las especificaciones del United States National CAD Stardard - v5 del National Institute of Building Sciences para los grupos A-Architectural, C-Civil, E-Electrical, S-Structural, V-Survey / Mapping y W-Distributed Energy.</t>
-    </r>
-  </si>
-  <si>
     <t>Especificación</t>
   </si>
   <si>
@@ -528,9 +539,6 @@
   </si>
   <si>
     <t>mm</t>
-  </si>
-  <si>
-    <t>Especificaciones generales</t>
   </si>
   <si>
     <t>Líneas de vida</t>
@@ -1055,12 +1063,6 @@
     <t>Total de ventanas localizadas en fachada principal, posterior y en oficinas.</t>
   </si>
   <si>
-    <t>Acometida</t>
-  </si>
-  <si>
-    <t>Utilizando las especificaciones del Reglamento Técnico de Instalaciones Eléctricas - RETIE del Ministerio de Minas y Energía de Colombia, dibuje la acometida eléctrica. Dibujar en planta y en cortes.</t>
-  </si>
-  <si>
     <t>Tomacorrientes</t>
   </si>
   <si>
@@ -1080,20 +1082,6 @@
   </si>
   <si>
     <t>Área disponible en cubierta</t>
-  </si>
-  <si>
-    <r>
-      <t>Redes</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (en este curso, no es necesario crear los planos de instalaciones hidráulicas, sanitarias y contra incendios)</t>
-    </r>
   </si>
   <si>
     <r>
@@ -1161,9 +1149,6 @@
     <t>Esquema solo en planta. Localización de cámaras de seguridad.</t>
   </si>
   <si>
-    <t>Esquema solo en planta. Conexión desde poste o subterránea desde lindero de entrada al predio en uno de los laterales.</t>
-  </si>
-  <si>
     <t>Esquema solo en planta. Red de datos en zona de oficinas y puntos generales de localización de equipos de cómputo, repetidores wi-fi y cámaras.</t>
   </si>
   <si>
@@ -1181,18 +1166,113 @@
     </r>
   </si>
   <si>
+    <t>La distribución de una bodega en un proyecto implica planificar la disposición de las áreas y elementos para optimizar el flujo de materiales, maximizar el espacio y garantizar la eficiencia operativa. Se deben considerar factores como el tipo de productos, la rotación, el tamaño del almacén y los equipos de manipulación.</t>
+  </si>
+  <si>
+    <r>
+      <t>Distribución interna</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (al menos se deben incluir 3 referencias distintas de transformadores eléctricos industriales)</t>
+    </r>
+  </si>
+  <si>
+    <t>4. Bodegaje</t>
+  </si>
+  <si>
     <t>En arquitectura, las especificaciones de un proyecto son documentos técnicos detallados que describen las características, materiales, estándares y métodos de construcción necesarios para ejecutar un proyecto. Estas especificaciones complementan los planos y proporcionan información precisa sobre cómo se deben realizar los trabajos, garantizando la calidad y cumplimiento de los requisitos.</t>
   </si>
   <si>
     <t>En un proyecto, las especificaciones eléctricas son un conjunto de directrices técnicas que describen detalladamente las características y requisitos de los componentes y equipos eléctricos que se utilizarán. Estas especificaciones aseguran que la instalación eléctrica sea segura, confiable y cumpla con los estándares y normativas aplicables.</t>
   </si>
   <si>
+    <t>Separación entre estantes</t>
+  </si>
+  <si>
+    <t>Estantería</t>
+  </si>
+  <si>
+    <t>Altura máxima de montacargas</t>
+  </si>
+  <si>
+    <t>Número de niveles en estantes</t>
+  </si>
+  <si>
+    <t>Nivel</t>
+  </si>
+  <si>
+    <t>Ancho de estante</t>
+  </si>
+  <si>
+    <t>Alto de entrepiso en estante</t>
+  </si>
+  <si>
+    <t>Separación o ancho del corredor por donde se desplaza el montacargas industrial.</t>
+  </si>
+  <si>
+    <t>Ancho total del estante. En zonas internas se pueden colocar en hileras de dos, en costados de bodega solo una hilera.</t>
+  </si>
+  <si>
+    <t>Altura del entrepiso incluyendo el espesor de la base.</t>
+  </si>
+  <si>
+    <t>Altura máxima que puede elevar el montacargas, requerido para definir la altura superior de la estantería.</t>
+  </si>
+  <si>
+    <t>Elevación de piso del último estante</t>
+  </si>
+  <si>
+    <t>Indique la referencia y cantidad de elementos a almacenar en la bodega. Para la distribución en estantes, los transformadores grandes se almacenan en la parte inferior, los medianos en los estantes intermedios y los livianos en la parte superior.</t>
+  </si>
+  <si>
+    <t>Calcular</t>
+  </si>
+  <si>
+    <t>Corresponde al número de pisos que tendrá la estantería incluído el piso a nivel de placa.</t>
+  </si>
+  <si>
+    <t>Esta elevación no debe ser superior a la altura vertical de desplazamiento del montacarga.</t>
+  </si>
+  <si>
+    <t>Verificación de montacarga</t>
+  </si>
+  <si>
+    <t>n/a</t>
+  </si>
+  <si>
+    <t>Verificación de desplazamiento para carga y descarga del montacargas.</t>
+  </si>
+  <si>
+    <t>Longitud total de estantería en planta</t>
+  </si>
+  <si>
+    <t>Distribuir dentro de la bodeda y medir.</t>
+  </si>
+  <si>
+    <t>Longitud total de estantería en todos los niveles</t>
+  </si>
+  <si>
+    <t>Valor longitudinal por número de niveles.</t>
+  </si>
+  <si>
+    <t>Transformador 1 - Ref: #####</t>
+  </si>
+  <si>
+    <t>Transformador 2 - Ref: #####</t>
+  </si>
+  <si>
+    <t>Transformador 3 - Ref: #####</t>
+  </si>
+  <si>
     <t>Cuadro de cantidades (resumen a incluir en planos, no es necesario realizar costos unitarios)</t>
   </si>
   <si>
-    <t>5. Planos</t>
-  </si>
-  <si>
     <t>Plano de planta general</t>
   </si>
   <si>
@@ -1244,9 +1324,6 @@
     <t>Técnica</t>
   </si>
   <si>
-    <t>Arquitectónica</t>
-  </si>
-  <si>
     <t>Eléctrica</t>
   </si>
   <si>
@@ -1254,12 +1331,6 @@
   </si>
   <si>
     <t>Archivos</t>
-  </si>
-  <si>
-    <t>Otros</t>
-  </si>
-  <si>
-    <t>Promedio de calificación:</t>
   </si>
   <si>
     <t>Grupos, integrantes y resúmen de calificaciones</t>
@@ -1275,20 +1346,169 @@
     <t>Promedio:</t>
   </si>
   <si>
-    <t>Nombre y logotipo creado por el grupo.</t>
-  </si>
-  <si>
     <t>Estructura de directorios</t>
   </si>
   <si>
     <t>Utilizar la estructura definida para el curso DAPC.</t>
+  </si>
+  <si>
+    <t>Repositorio digital de proyecto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Repositorio de datos creado, compartido y accesible. Crear en OneDrive de Campus. </t>
+  </si>
+  <si>
+    <t>Plantilla o layout - Unidades de dibujo</t>
+  </si>
+  <si>
+    <t>Plantilla o layout - Archivo</t>
+  </si>
+  <si>
+    <t>Guardar como /file/cad/DAPC.dwt</t>
+  </si>
+  <si>
+    <t>Lineales en metros, angulares en grados, precisión a dos decimales.</t>
+  </si>
+  <si>
+    <t>Se deben utilizar los nombres de capas establecidos en la norma internacional estándar ISO-13567, aplicando las especificaciones del United States National CAD Stardard - v5 del National Institute of Building Sciences para los grupos A-Architectural, C-Civil, E-Electrical, S-Structural, V-Survey / Mapping y W-Distributed Energy.</t>
+  </si>
+  <si>
+    <t>Crear estilos propios fijos y anotativos para las diferentes escalas de impresión a usar, utilizar el prefijo DAPC.</t>
+  </si>
+  <si>
+    <t>A0 / A4, horizontal y vertical. Formatos adicionales pueden ser incluídos en la plantilla.</t>
+  </si>
+  <si>
+    <t>Bloques - arquitectónicos</t>
+  </si>
+  <si>
+    <t>Bloques - eléctricos</t>
+  </si>
+  <si>
+    <t>Bloques - otros</t>
+  </si>
+  <si>
+    <t>Plantilla o layout - Capas o layers</t>
+  </si>
+  <si>
+    <t>Plantilla o layout - Acotado</t>
+  </si>
+  <si>
+    <t>Plantilla o layout - Formatos para impresión</t>
+  </si>
+  <si>
+    <t>Utilizar los bloques ejemplo del ADC de AutoCAD, o utilizar una librería de bloque externos, citando la fuente de descarga. /file/cad/Bloque_Arquitectonico.dwg</t>
+  </si>
+  <si>
+    <t>Para el dibujo de los planos eléctricos, utilizar los bloques creados a partir de las especificaciones establecidas en el Reglamento Técnico de Instalaciones Eléctricas - RETIE del Ministerio de Minas y Energía de Colombia. /file/cad/Bloque_Electrico.dwg</t>
+  </si>
+  <si>
+    <t>Utilizar una librería de bloque externos citando la fuente de descarga. Por ejemplo: cámaras de vigilancia, luces de emergencia, panel solar. /file/cad/Bloque_Otros.dwg</t>
+  </si>
+  <si>
+    <t>Archivo DWG de proyecto</t>
+  </si>
+  <si>
+    <t>Mantener este valor para el proyecto.</t>
+  </si>
+  <si>
+    <t>Los estudiantes deberán definir el nombre de su grupo de proyecto y crear un logotipo en AutoCAD (guardar como /file/cad/logotipo.dwg). El código, logotipo y nombre del grupo deberán incluirse en todos los planos generados.</t>
+  </si>
+  <si>
+    <r>
+      <t>Otros estudiante</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Segoe UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (auto-calificación)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Otros instructor</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Segoe UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (participación en clase, dedicación, calidad del proyecto)</t>
+    </r>
+  </si>
+  <si>
+    <t>Utilizando las especificaciones del Reglamento Técnico de Instalaciones Eléctricas - RETIE del Ministerio de Minas y Energía de Colombia, dibuje la acometida eléctrica. Dibujar en planta y en cortes. Esquema solo en planta. Conexión desde poste o subterránea desde lindero de entrada al predio en uno de los laterales.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Especificaciones generales y redes </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>(en este curso, no es necesario crear los planos de instalaciones hidráulicas, sanitarias y contra incendios)</t>
+    </r>
+  </si>
+  <si>
+    <t>Archivo único de dibujo del proyecto. Guardar copias de las diferentes versiones de avance creadas colocando el sufijo correspondiente al aaaammdd.</t>
+  </si>
+  <si>
+    <t>/file/cad/DAPC.dwg</t>
+  </si>
+  <si>
+    <t>Plano digital del proyecto</t>
+  </si>
+  <si>
+    <t>Generados a partir de layouts e integrados en un único archivo de Acrobat .pdf.</t>
+  </si>
+  <si>
+    <t>/file/report/DAPC_Planos.pdf</t>
+  </si>
+  <si>
+    <t>Crear un logotipo en AutoCAD.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plantilla o layout AutoCAD
+</t>
+  </si>
+  <si>
+    <t>Incluye unidades de dibujo lineales en metros, angulares en grados, precisión a dos decimales, capas o layers, estilos de acotado fijos y anotativos para las diferentes escalas de impresión a usar utilizando el prefijo DAPC., formatos para impresión A0 / A4 con logotipo, código y nombre del grupo. Se deben utilizar los nombres de capas establecidos en la norma internacional estándar ISO-13567, aplicando las especificaciones del United States National CAD Stardard - v5 del National Institute of Building Sciences para los grupos A-Architectural, C-Civil, E-Electrical, S-Structural, V-Survey / Mapping y W-Distributed Energy.</t>
+  </si>
+  <si>
+    <t>Fichas técnicas</t>
+  </si>
+  <si>
+    <t>Fichas técnicas de elementos utilizandos para el dibujo.</t>
+  </si>
+  <si>
+    <t>/file/ref/*.pdf</t>
+  </si>
+  <si>
+    <t>5. Archivos digitales del proyecto</t>
+  </si>
+  <si>
+    <t>4. Planos</t>
+  </si>
+  <si>
+    <t>Bodegaje</t>
+  </si>
+  <si>
+    <t>Arquitectónica y estructural</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1371,6 +1591,13 @@
       <name val="Segoe UI Light"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1386,7 +1613,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="25">
+  <borders count="31">
     <border>
       <left/>
       <right/>
@@ -1686,16 +1913,14 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left/>
+      <right style="thin">
         <color theme="0" tint="-4.9989318521683403E-2"/>
-      </left>
-      <right style="thin">
+      </right>
+      <top style="thin">
         <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -1712,12 +1937,84 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right style="thin">
         <color theme="0" tint="-4.9989318521683403E-2"/>
       </right>
       <top style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </top>
+      <bottom style="thin">
         <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
       </top>
       <bottom style="thin">
         <color indexed="64"/>
@@ -1730,7 +2027,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="108">
+  <cellXfs count="118">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1820,33 +2117,18 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1862,9 +2144,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1874,9 +2153,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1885,9 +2161,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -1997,11 +2270,8 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -2027,39 +2297,91 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2078,6 +2400,38 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="1.Técnicas"/>
+      <sheetName val="2.Arquitectónica"/>
+      <sheetName val="3.Eléctrica"/>
+      <sheetName val="4.Bodegaje"/>
+      <sheetName val="Files"/>
+      <sheetName val="Metadata"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="32">
+          <cell r="E32">
+            <v>27</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1" refreshError="1"/>
+      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="3" refreshError="1"/>
+      <sheetData sheetId="4" refreshError="1"/>
+      <sheetData sheetId="5" refreshError="1"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2343,13 +2697,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82EDA320-F942-4FCE-8343-60C075021E69}">
-  <dimension ref="B1:E40"/>
+  <dimension ref="B1:H46"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="2.59765625" style="2" customWidth="1"/>
     <col min="3" max="3" width="50.59765625" style="2" customWidth="1"/>
     <col min="4" max="4" width="15.59765625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="9.06640625" style="2"/>
+    <col min="5" max="5" width="11.53125" style="2" customWidth="1"/>
     <col min="6" max="6" width="2.59765625" style="2" customWidth="1"/>
     <col min="7" max="16384" width="9.06640625" style="2"/>
   </cols>
@@ -2359,137 +2713,137 @@
     </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B2" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B3" s="20" t="s">
-        <v>273</v>
+        <v>290</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B4" s="82" t="s">
-        <v>41</v>
-      </c>
-      <c r="C4" s="82"/>
-      <c r="D4" s="82"/>
-      <c r="E4" s="82"/>
+      <c r="B4" s="74" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="74"/>
+      <c r="D4" s="74"/>
+      <c r="E4" s="74"/>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B5" s="82"/>
-      <c r="C5" s="82"/>
-      <c r="D5" s="82"/>
-      <c r="E5" s="82"/>
+      <c r="B5" s="74"/>
+      <c r="C5" s="74"/>
+      <c r="D5" s="74"/>
+      <c r="E5" s="74"/>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B6" s="82"/>
-      <c r="C6" s="82"/>
-      <c r="D6" s="82"/>
-      <c r="E6" s="82"/>
+      <c r="B6" s="74"/>
+      <c r="C6" s="74"/>
+      <c r="D6" s="74"/>
+      <c r="E6" s="74"/>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B7" s="82"/>
-      <c r="C7" s="82"/>
-      <c r="D7" s="82"/>
-      <c r="E7" s="82"/>
+      <c r="B7" s="74"/>
+      <c r="C7" s="74"/>
+      <c r="D7" s="74"/>
+      <c r="E7" s="74"/>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B8" s="84" t="s">
+      <c r="B8" s="76" t="s">
         <v>1</v>
       </c>
-      <c r="C8" s="85"/>
-      <c r="D8" s="85"/>
-      <c r="E8" s="86"/>
+      <c r="C8" s="77"/>
+      <c r="D8" s="77"/>
+      <c r="E8" s="78"/>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B9" s="76" t="s">
+      <c r="B9" s="68" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="77"/>
-      <c r="D9" s="77"/>
-      <c r="E9" s="78"/>
+      <c r="C9" s="69"/>
+      <c r="D9" s="69"/>
+      <c r="E9" s="70"/>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B10" s="73" t="s">
+      <c r="B10" s="65" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="74"/>
-      <c r="D10" s="74"/>
-      <c r="E10" s="75"/>
+      <c r="C10" s="66"/>
+      <c r="D10" s="66"/>
+      <c r="E10" s="67"/>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B11" s="76" t="s">
+      <c r="B11" s="68" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="77"/>
-      <c r="D11" s="77"/>
-      <c r="E11" s="78"/>
+      <c r="C11" s="69"/>
+      <c r="D11" s="69"/>
+      <c r="E11" s="70"/>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B12" s="79"/>
-      <c r="C12" s="80"/>
-      <c r="D12" s="80"/>
-      <c r="E12" s="81"/>
+      <c r="B12" s="71"/>
+      <c r="C12" s="72"/>
+      <c r="D12" s="72"/>
+      <c r="E12" s="73"/>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B13" s="73" t="s">
-        <v>21</v>
-      </c>
-      <c r="C13" s="74"/>
-      <c r="D13" s="74"/>
-      <c r="E13" s="75"/>
+      <c r="B13" s="65" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="66"/>
+      <c r="D13" s="66"/>
+      <c r="E13" s="67"/>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B14" s="76" t="s">
-        <v>19</v>
-      </c>
-      <c r="C14" s="77"/>
-      <c r="D14" s="77"/>
-      <c r="E14" s="78"/>
+      <c r="B14" s="68" t="s">
+        <v>18</v>
+      </c>
+      <c r="C14" s="69"/>
+      <c r="D14" s="69"/>
+      <c r="E14" s="70"/>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B15" s="79"/>
-      <c r="C15" s="80"/>
-      <c r="D15" s="80"/>
-      <c r="E15" s="81"/>
+      <c r="B15" s="71"/>
+      <c r="C15" s="72"/>
+      <c r="D15" s="72"/>
+      <c r="E15" s="73"/>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.45">
       <c r="B16" s="23" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C16" s="23"/>
       <c r="D16" s="23"/>
       <c r="E16" s="23"/>
     </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B17" s="18"/>
       <c r="C17" s="18"/>
       <c r="D17" s="18"/>
       <c r="E17" s="18"/>
     </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B18" s="83" t="s">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B18" s="75" t="s">
         <v>14</v>
       </c>
-      <c r="C18" s="83"/>
-      <c r="D18" s="83"/>
-      <c r="E18" s="83"/>
-    </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="C18" s="75"/>
+      <c r="D18" s="75"/>
+      <c r="E18" s="75"/>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B19" s="17" t="s">
         <v>10</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E19" s="10" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B20" s="15">
         <v>1</v>
       </c>
@@ -2504,7 +2858,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B21" s="15">
         <v>2</v>
       </c>
@@ -2519,7 +2873,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B22" s="15">
         <v>3</v>
       </c>
@@ -2534,7 +2888,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B23" s="15">
         <v>4</v>
       </c>
@@ -2549,7 +2903,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B24" s="15">
         <v>5</v>
       </c>
@@ -2564,7 +2918,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B25" s="15">
         <v>6</v>
       </c>
@@ -2577,7 +2931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B26" s="15">
         <v>7</v>
       </c>
@@ -2590,7 +2944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B27" s="15">
         <v>8</v>
       </c>
@@ -2603,7 +2957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B28" s="15">
         <v>9</v>
       </c>
@@ -2616,7 +2970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B29" s="16">
         <v>10</v>
       </c>
@@ -2629,7 +2983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.45">
       <c r="D30" s="19" t="s">
         <v>11</v>
       </c>
@@ -2638,96 +2992,231 @@
         <v>27</v>
       </c>
     </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B32" s="83" t="s">
-        <v>265</v>
-      </c>
-      <c r="C32" s="83"/>
-      <c r="D32" s="83"/>
-      <c r="E32" s="83"/>
-    </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B33" s="17" t="s">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B31" s="91"/>
+      <c r="C31" s="91"/>
+      <c r="D31" s="91"/>
+      <c r="E31" s="91"/>
+      <c r="F31" s="91"/>
+      <c r="G31" s="91"/>
+      <c r="H31" s="91"/>
+    </row>
+    <row r="32" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B32" s="92" t="s">
+        <v>285</v>
+      </c>
+      <c r="C32" s="92"/>
+      <c r="D32" s="92"/>
+      <c r="E32" s="92"/>
+      <c r="F32" s="91"/>
+      <c r="G32" s="91"/>
+      <c r="H32" s="91"/>
+    </row>
+    <row r="33" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B33" s="93" t="s">
         <v>10</v>
       </c>
-      <c r="C33" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="D33" s="10" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B34" s="99">
+      <c r="C33" s="106" t="s">
+        <v>40</v>
+      </c>
+      <c r="D33" s="107"/>
+      <c r="E33" s="94" t="s">
+        <v>27</v>
+      </c>
+      <c r="F33" s="91"/>
+      <c r="G33" s="91"/>
+      <c r="H33" s="91"/>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B34" s="95">
         <v>1</v>
       </c>
-      <c r="C34" s="100" t="s">
-        <v>266</v>
-      </c>
-      <c r="D34" s="103"/>
-    </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B35" s="99">
+      <c r="C34" s="109" t="s">
+        <v>286</v>
+      </c>
+      <c r="D34" s="110"/>
+      <c r="E34" s="96">
+        <f>'1.Tecnica'!H19</f>
+        <v>5</v>
+      </c>
+      <c r="F34" s="91"/>
+      <c r="G34" s="91"/>
+      <c r="H34" s="91"/>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B35" s="95">
         <v>2</v>
       </c>
-      <c r="C35" s="100" t="s">
-        <v>267</v>
-      </c>
-      <c r="D35" s="103"/>
-    </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B36" s="99">
+      <c r="C35" s="111" t="s">
+        <v>335</v>
+      </c>
+      <c r="D35" s="112"/>
+      <c r="E35" s="96">
+        <f>'2.ArquitectonicaEstructural'!H104</f>
+        <v>5</v>
+      </c>
+      <c r="F35" s="91"/>
+      <c r="G35" s="91"/>
+      <c r="H35" s="91"/>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B36" s="95">
         <v>3</v>
       </c>
-      <c r="C36" s="100" t="s">
-        <v>268</v>
-      </c>
-      <c r="D36" s="103"/>
-    </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B37" s="99">
+      <c r="C36" s="111" t="s">
+        <v>287</v>
+      </c>
+      <c r="D36" s="112"/>
+      <c r="E36" s="96">
+        <f>'3.Electrica'!H28</f>
+        <v>5</v>
+      </c>
+      <c r="F36" s="91"/>
+      <c r="G36" s="91"/>
+      <c r="H36" s="91"/>
+    </row>
+    <row r="37" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B37" s="95">
         <v>4</v>
       </c>
-      <c r="C37" s="100" t="s">
-        <v>269</v>
-      </c>
-      <c r="D37" s="103"/>
-    </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B38" s="99">
+      <c r="C37" s="116" t="s">
+        <v>334</v>
+      </c>
+      <c r="D37" s="117"/>
+      <c r="E37" s="96">
+        <f>'4.Bodegaje'!H24</f>
         <v>5</v>
       </c>
-      <c r="C38" s="100" t="s">
-        <v>270</v>
-      </c>
-      <c r="D38" s="103"/>
-    </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B39" s="101">
+      <c r="F37" s="91"/>
+      <c r="G37" s="91"/>
+      <c r="H37" s="91"/>
+    </row>
+    <row r="38" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B38" s="95">
+        <v>4</v>
+      </c>
+      <c r="C38" s="111" t="s">
+        <v>288</v>
+      </c>
+      <c r="D38" s="112"/>
+      <c r="E38" s="96">
+        <f>'5.Planos'!H17</f>
+        <v>5</v>
+      </c>
+      <c r="F38" s="91"/>
+      <c r="G38" s="91"/>
+      <c r="H38" s="91"/>
+    </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B39" s="95">
+        <v>5</v>
+      </c>
+      <c r="C39" s="111" t="s">
+        <v>289</v>
+      </c>
+      <c r="D39" s="112"/>
+      <c r="E39" s="96">
+        <f>'5.Archivos'!G17</f>
+        <v>5</v>
+      </c>
+      <c r="F39" s="91"/>
+      <c r="G39" s="91"/>
+      <c r="H39" s="91"/>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B40" s="95">
         <v>6</v>
       </c>
-      <c r="C39" s="102" t="s">
-        <v>271</v>
-      </c>
-      <c r="D39" s="104"/>
-    </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.45">
-      <c r="B40" s="105" t="s">
-        <v>272</v>
-      </c>
-      <c r="C40" s="106"/>
-      <c r="D40" s="98">
-        <f>SUM(E34:E39)</f>
-        <v>0</v>
-      </c>
+      <c r="C40" s="111" t="s">
+        <v>317</v>
+      </c>
+      <c r="D40" s="112"/>
+      <c r="E40" s="105">
+        <v>5</v>
+      </c>
+      <c r="F40" s="91"/>
+      <c r="G40" s="91"/>
+      <c r="H40" s="91"/>
+    </row>
+    <row r="41" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B41" s="97">
+        <v>7</v>
+      </c>
+      <c r="C41" s="113" t="s">
+        <v>318</v>
+      </c>
+      <c r="D41" s="114"/>
+      <c r="E41" s="104">
+        <v>5</v>
+      </c>
+      <c r="F41" s="91"/>
+      <c r="G41" s="91"/>
+      <c r="H41" s="91"/>
+    </row>
+    <row r="42" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B42" s="91"/>
+      <c r="C42" s="91"/>
+      <c r="D42" s="89" t="s">
+        <v>293</v>
+      </c>
+      <c r="E42" s="108">
+        <f>AVERAGE(E34:E41)</f>
+        <v>5</v>
+      </c>
+      <c r="F42" s="91"/>
+      <c r="G42" s="91"/>
+      <c r="H42" s="91"/>
+    </row>
+    <row r="43" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B43" s="91"/>
+      <c r="C43" s="91"/>
+      <c r="D43" s="91"/>
+      <c r="E43" s="91"/>
+      <c r="F43" s="91"/>
+      <c r="G43" s="91"/>
+      <c r="H43" s="91"/>
+    </row>
+    <row r="44" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B44" s="91"/>
+      <c r="C44" s="91"/>
+      <c r="D44" s="91"/>
+      <c r="E44" s="91"/>
+      <c r="F44" s="91"/>
+      <c r="G44" s="91"/>
+      <c r="H44" s="91"/>
+    </row>
+    <row r="45" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B45" s="91"/>
+      <c r="C45" s="91"/>
+      <c r="D45" s="91"/>
+      <c r="E45" s="91"/>
+      <c r="F45" s="91"/>
+      <c r="G45" s="91"/>
+      <c r="H45" s="91"/>
+    </row>
+    <row r="46" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B46" s="91"/>
+      <c r="C46" s="91"/>
+      <c r="D46" s="91"/>
+      <c r="E46" s="91"/>
+      <c r="F46" s="91"/>
+      <c r="G46" s="91"/>
+      <c r="H46" s="91"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="18">
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="C41:D41"/>
     <mergeCell ref="B14:E15"/>
     <mergeCell ref="B18:E18"/>
     <mergeCell ref="B32:E32"/>
-    <mergeCell ref="B40:C40"/>
     <mergeCell ref="B4:E6"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="C38:D38"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="B8:E8"/>
     <mergeCell ref="B9:E9"/>
@@ -2742,7 +3231,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0659C4DD-D653-4634-8C4F-29057F021A54}">
-  <dimension ref="B1:H18"/>
+  <dimension ref="B1:H19"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.59765625" style="2" customWidth="1"/>
@@ -2751,8 +3240,8 @@
     <col min="4" max="4" width="15.59765625" style="2" customWidth="1"/>
     <col min="5" max="5" width="9.06640625" style="2"/>
     <col min="6" max="6" width="12.265625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="9.06640625" style="2"/>
-    <col min="8" max="8" width="12.3984375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="20.265625" style="98" customWidth="1"/>
+    <col min="8" max="8" width="12.3984375" style="47" customWidth="1"/>
     <col min="9" max="16384" width="9.06640625" style="2"/>
   </cols>
   <sheetData>
@@ -2761,7 +3250,7 @@
     </row>
     <row r="2" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B2" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.45">
@@ -2770,194 +3259,252 @@
       </c>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B4" s="82" t="s">
-        <v>274</v>
-      </c>
-      <c r="C4" s="82"/>
-      <c r="D4" s="82"/>
-      <c r="E4" s="82"/>
+      <c r="B4" s="74" t="s">
+        <v>291</v>
+      </c>
+      <c r="C4" s="74"/>
+      <c r="D4" s="74"/>
+      <c r="E4" s="74"/>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B5" s="82"/>
-      <c r="C5" s="82"/>
-      <c r="D5" s="82"/>
-      <c r="E5" s="82"/>
+      <c r="B5" s="74"/>
+      <c r="C5" s="74"/>
+      <c r="D5" s="74"/>
+      <c r="E5" s="74"/>
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B6" s="82"/>
-      <c r="C6" s="82"/>
-      <c r="D6" s="82"/>
-      <c r="E6" s="82"/>
-    </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B7" s="42" t="s">
-        <v>43</v>
-      </c>
-      <c r="C7" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="D7" s="44" t="s">
-        <v>55</v>
-      </c>
-      <c r="E7" s="44" t="s">
-        <v>56</v>
-      </c>
-      <c r="F7" s="44" t="s">
-        <v>45</v>
-      </c>
-      <c r="G7" s="43" t="s">
+      <c r="B6" s="37" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" s="39" t="s">
+        <v>52</v>
+      </c>
+      <c r="E6" s="39" t="s">
+        <v>53</v>
+      </c>
+      <c r="F6" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="G6" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" s="83" t="s">
         <v>27</v>
       </c>
-      <c r="H7" s="45" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B8" s="35" t="s">
-        <v>275</v>
-      </c>
-      <c r="C8" s="40" t="s">
-        <v>277</v>
-      </c>
-      <c r="D8" s="41">
+    </row>
+    <row r="7" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
+      <c r="B7" s="32" t="s">
+        <v>292</v>
+      </c>
+      <c r="C7" s="35" t="s">
+        <v>316</v>
+      </c>
+      <c r="D7" s="36">
         <v>1</v>
       </c>
-      <c r="E8" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="F8" s="34"/>
-      <c r="G8" s="29"/>
-      <c r="H8" s="36"/>
+      <c r="E7" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="F7" s="31"/>
+      <c r="G7" s="35"/>
+      <c r="H7" s="85">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
+      <c r="B8" s="32" t="s">
+        <v>296</v>
+      </c>
+      <c r="C8" s="35" t="s">
+        <v>297</v>
+      </c>
+      <c r="D8" s="36">
+        <v>1</v>
+      </c>
+      <c r="E8" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="F8" s="31"/>
+      <c r="G8" s="35"/>
+      <c r="H8" s="85"/>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B9" s="35" t="s">
-        <v>278</v>
-      </c>
-      <c r="C9" s="40" t="s">
-        <v>279</v>
-      </c>
-      <c r="D9" s="41">
+      <c r="B9" s="32" t="s">
+        <v>294</v>
+      </c>
+      <c r="C9" s="35" t="s">
+        <v>295</v>
+      </c>
+      <c r="D9" s="36">
         <v>1</v>
       </c>
-      <c r="E9" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="F9" s="34"/>
-      <c r="G9" s="29"/>
-      <c r="H9" s="36"/>
+      <c r="E9" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="F9" s="31"/>
+      <c r="G9" s="35"/>
+      <c r="H9" s="85"/>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B10" s="35"/>
-      <c r="C10" s="40"/>
-      <c r="D10" s="41">
+      <c r="B10" s="32" t="s">
+        <v>299</v>
+      </c>
+      <c r="C10" s="35" t="s">
+        <v>300</v>
+      </c>
+      <c r="D10" s="36">
         <v>1</v>
       </c>
-      <c r="E10" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="F10" s="34"/>
-      <c r="G10" s="29"/>
-      <c r="H10" s="36"/>
-    </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B11" s="35"/>
-      <c r="C11" s="40"/>
-      <c r="D11" s="41">
+      <c r="E10" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="F10" s="31"/>
+      <c r="G10" s="35"/>
+      <c r="H10" s="85"/>
+    </row>
+    <row r="11" spans="2:8" ht="33" x14ac:dyDescent="0.45">
+      <c r="B11" s="32" t="s">
+        <v>298</v>
+      </c>
+      <c r="C11" s="35" t="s">
+        <v>301</v>
+      </c>
+      <c r="D11" s="36">
         <v>1</v>
       </c>
-      <c r="E11" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="F11" s="34"/>
-      <c r="G11" s="29"/>
-      <c r="H11" s="36"/>
-    </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B12" s="35"/>
-      <c r="C12" s="40"/>
-      <c r="D12" s="41">
+      <c r="E11" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="F11" s="31"/>
+      <c r="G11" s="35"/>
+      <c r="H11" s="85"/>
+    </row>
+    <row r="12" spans="2:8" ht="63.75" x14ac:dyDescent="0.45">
+      <c r="B12" s="32" t="s">
+        <v>308</v>
+      </c>
+      <c r="C12" s="35" t="s">
+        <v>302</v>
+      </c>
+      <c r="D12" s="36">
         <v>1</v>
       </c>
-      <c r="E12" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="F12" s="34"/>
-      <c r="G12" s="29"/>
-      <c r="H12" s="36"/>
-    </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B13" s="35"/>
-      <c r="C13" s="40"/>
-      <c r="D13" s="41">
+      <c r="E12" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="F12" s="31"/>
+      <c r="G12" s="35"/>
+      <c r="H12" s="85"/>
+    </row>
+    <row r="13" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
+      <c r="B13" s="32" t="s">
+        <v>309</v>
+      </c>
+      <c r="C13" s="35" t="s">
+        <v>303</v>
+      </c>
+      <c r="D13" s="36">
         <v>1</v>
       </c>
-      <c r="E13" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="F13" s="34"/>
-      <c r="G13" s="29"/>
-      <c r="H13" s="36"/>
-    </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B14" s="35"/>
-      <c r="C14" s="40"/>
-      <c r="D14" s="41">
+      <c r="E13" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="F13" s="31"/>
+      <c r="G13" s="35"/>
+      <c r="H13" s="85"/>
+    </row>
+    <row r="14" spans="2:8" ht="33" x14ac:dyDescent="0.45">
+      <c r="B14" s="32" t="s">
+        <v>310</v>
+      </c>
+      <c r="C14" s="35" t="s">
+        <v>304</v>
+      </c>
+      <c r="D14" s="36">
         <v>1</v>
       </c>
-      <c r="E14" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="F14" s="34"/>
-      <c r="G14" s="29"/>
-      <c r="H14" s="36"/>
-    </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B15" s="35"/>
-      <c r="C15" s="40"/>
-      <c r="D15" s="41">
+      <c r="E14" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="F14" s="31"/>
+      <c r="G14" s="35"/>
+      <c r="H14" s="85"/>
+    </row>
+    <row r="15" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
+      <c r="B15" s="32" t="s">
+        <v>305</v>
+      </c>
+      <c r="C15" s="35" t="s">
+        <v>311</v>
+      </c>
+      <c r="D15" s="36">
         <v>1</v>
       </c>
-      <c r="E15" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="F15" s="34"/>
-      <c r="G15" s="29"/>
-      <c r="H15" s="36"/>
-    </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B16" s="35"/>
-      <c r="C16" s="40"/>
-      <c r="D16" s="41">
+      <c r="E15" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="F15" s="31"/>
+      <c r="G15" s="35"/>
+      <c r="H15" s="85"/>
+    </row>
+    <row r="16" spans="2:8" ht="52.15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B16" s="32" t="s">
+        <v>306</v>
+      </c>
+      <c r="C16" s="35" t="s">
+        <v>312</v>
+      </c>
+      <c r="D16" s="36">
         <v>1</v>
       </c>
-      <c r="E16" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="F16" s="34"/>
-      <c r="G16" s="29"/>
-      <c r="H16" s="36"/>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B17" s="46"/>
-      <c r="C17" s="47"/>
-      <c r="D17" s="90"/>
-      <c r="E17" s="48"/>
-      <c r="F17" s="48"/>
-      <c r="G17" s="30"/>
-      <c r="H17" s="49"/>
+      <c r="E16" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="F16" s="31"/>
+      <c r="G16" s="35"/>
+      <c r="H16" s="85"/>
+    </row>
+    <row r="17" spans="2:8" ht="35.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B17" s="43" t="s">
+        <v>307</v>
+      </c>
+      <c r="C17" s="44" t="s">
+        <v>313</v>
+      </c>
+      <c r="D17" s="36">
+        <v>1</v>
+      </c>
+      <c r="E17" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="F17" s="45"/>
+      <c r="G17" s="44"/>
+      <c r="H17" s="86"/>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="G18" s="107" t="s">
-        <v>276</v>
-      </c>
-      <c r="H18" s="2" t="e">
-        <f>AVERAGE(H8:H17)</f>
-        <v>#DIV/0!</v>
+      <c r="B18" s="40"/>
+      <c r="C18" s="41"/>
+      <c r="D18" s="81"/>
+      <c r="E18" s="42"/>
+      <c r="F18" s="42"/>
+      <c r="G18" s="41"/>
+      <c r="H18" s="87"/>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="G19" s="90" t="s">
+        <v>293</v>
+      </c>
+      <c r="H19" s="47">
+        <f>AVERAGE(H7:H18)</f>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="B4:E6"/>
+    <mergeCell ref="B4:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -2972,1244 +3519,1254 @@
     <col min="1" max="1" width="2.59765625" style="2" customWidth="1"/>
     <col min="2" max="2" width="27.06640625" style="2" customWidth="1"/>
     <col min="3" max="3" width="41" style="2" customWidth="1"/>
-    <col min="4" max="6" width="9.19921875" style="55" customWidth="1"/>
-    <col min="7" max="7" width="28.53125" style="2" customWidth="1"/>
-    <col min="8" max="8" width="14.86328125" style="55" customWidth="1"/>
+    <col min="4" max="6" width="9.19921875" style="47" customWidth="1"/>
+    <col min="7" max="7" width="28.53125" style="98" customWidth="1"/>
+    <col min="8" max="8" width="14.86328125" style="47" customWidth="1"/>
     <col min="9" max="9" width="2.59765625" style="2" customWidth="1"/>
     <col min="10" max="16384" width="9.06640625" style="2"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B2" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B3" s="20" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
     </row>
     <row r="4" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B4" s="82" t="s">
-        <v>246</v>
-      </c>
-      <c r="C4" s="82"/>
-      <c r="D4" s="82"/>
-      <c r="E4" s="82"/>
-      <c r="F4" s="82"/>
-      <c r="G4" s="82"/>
-      <c r="H4" s="82"/>
+      <c r="B4" s="74" t="s">
+        <v>241</v>
+      </c>
+      <c r="C4" s="74"/>
+      <c r="D4" s="74"/>
+      <c r="E4" s="74"/>
+      <c r="F4" s="74"/>
+      <c r="G4" s="74"/>
+      <c r="H4" s="74"/>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B5" s="87"/>
-      <c r="C5" s="87"/>
-      <c r="D5" s="87"/>
-      <c r="E5" s="87"/>
-      <c r="F5" s="87"/>
-      <c r="G5" s="87"/>
-      <c r="H5" s="87"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B6" s="42" t="s">
-        <v>43</v>
-      </c>
-      <c r="C6" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="D6" s="44" t="s">
-        <v>55</v>
-      </c>
-      <c r="E6" s="44" t="s">
-        <v>56</v>
-      </c>
-      <c r="F6" s="44" t="s">
-        <v>45</v>
-      </c>
-      <c r="G6" s="43" t="s">
+      <c r="B6" s="37" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" s="39" t="s">
+        <v>52</v>
+      </c>
+      <c r="E6" s="39" t="s">
+        <v>53</v>
+      </c>
+      <c r="F6" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="G6" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" s="83" t="s">
         <v>27</v>
-      </c>
-      <c r="H6" s="92" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B7" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="C7" s="37"/>
-      <c r="D7" s="38"/>
-      <c r="E7" s="38"/>
-      <c r="F7" s="38"/>
-      <c r="G7" s="37"/>
-      <c r="H7" s="93"/>
+        <v>108</v>
+      </c>
+      <c r="C7" s="33"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="34"/>
+      <c r="G7" s="99"/>
+      <c r="H7" s="84"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B8" s="35" t="s">
+      <c r="B8" s="32" t="s">
+        <v>172</v>
+      </c>
+      <c r="C8" s="35" t="s">
+        <v>174</v>
+      </c>
+      <c r="D8" s="36">
+        <v>8</v>
+      </c>
+      <c r="E8" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="F8" s="31"/>
+      <c r="G8" s="35" t="s">
+        <v>315</v>
+      </c>
+      <c r="H8" s="85">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B9" s="32" t="s">
+        <v>173</v>
+      </c>
+      <c r="C9" s="35" t="s">
+        <v>175</v>
+      </c>
+      <c r="D9" s="36">
+        <v>10</v>
+      </c>
+      <c r="E9" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="F9" s="31"/>
+      <c r="G9" s="35" t="s">
+        <v>315</v>
+      </c>
+      <c r="H9" s="85"/>
+    </row>
+    <row r="10" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
+      <c r="B10" s="32" t="s">
+        <v>178</v>
+      </c>
+      <c r="C10" s="35" t="s">
         <v>176</v>
       </c>
-      <c r="C8" s="40" t="s">
-        <v>178</v>
-      </c>
-      <c r="D8" s="41">
-        <v>8</v>
-      </c>
-      <c r="E8" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="F8" s="34"/>
-      <c r="G8" s="29"/>
-      <c r="H8" s="94"/>
-    </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B9" s="35" t="s">
-        <v>177</v>
-      </c>
-      <c r="C9" s="40" t="s">
-        <v>179</v>
-      </c>
-      <c r="D9" s="41">
-        <v>10</v>
-      </c>
-      <c r="E9" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="F9" s="34"/>
-      <c r="G9" s="29"/>
-      <c r="H9" s="94"/>
-    </row>
-    <row r="10" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
-      <c r="B10" s="35" t="s">
-        <v>182</v>
-      </c>
-      <c r="C10" s="40" t="s">
-        <v>180</v>
-      </c>
-      <c r="D10" s="34">
+      <c r="D10" s="31">
         <f>D8+SumUDig</f>
         <v>35</v>
       </c>
-      <c r="E10" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="F10" s="34"/>
-      <c r="G10" s="29"/>
-      <c r="H10" s="94">
-        <v>5</v>
-      </c>
+      <c r="E10" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="F10" s="31"/>
+      <c r="G10" s="35"/>
+      <c r="H10" s="85"/>
     </row>
     <row r="11" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
-      <c r="B11" s="35" t="s">
-        <v>183</v>
-      </c>
-      <c r="C11" s="40" t="s">
-        <v>181</v>
-      </c>
-      <c r="D11" s="34" cm="1">
+      <c r="B11" s="32" t="s">
+        <v>179</v>
+      </c>
+      <c r="C11" s="35" t="s">
+        <v>177</v>
+      </c>
+      <c r="D11" s="31" cm="1">
         <f t="array" ref="D11">D9+SumUDig</f>
         <v>37</v>
       </c>
-      <c r="E11" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="F11" s="34"/>
-      <c r="G11" s="29"/>
-      <c r="H11" s="94"/>
+      <c r="E11" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="F11" s="31"/>
+      <c r="G11" s="35"/>
+      <c r="H11" s="85"/>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B12" s="35" t="s">
-        <v>46</v>
-      </c>
-      <c r="C12" s="40" t="s">
-        <v>192</v>
-      </c>
-      <c r="D12" s="41">
+      <c r="B12" s="32" t="s">
+        <v>43</v>
+      </c>
+      <c r="C12" s="35" t="s">
+        <v>188</v>
+      </c>
+      <c r="D12" s="36">
         <v>12</v>
       </c>
-      <c r="E12" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="F12" s="34"/>
-      <c r="G12" s="29"/>
-      <c r="H12" s="94"/>
+      <c r="E12" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="F12" s="31"/>
+      <c r="G12" s="35" t="s">
+        <v>315</v>
+      </c>
+      <c r="H12" s="85"/>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B13" s="35" t="s">
-        <v>67</v>
-      </c>
-      <c r="C13" s="40" t="s">
-        <v>77</v>
-      </c>
-      <c r="D13" s="41">
+      <c r="B13" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="C13" s="35" t="s">
+        <v>73</v>
+      </c>
+      <c r="D13" s="36">
         <v>6</v>
       </c>
-      <c r="E13" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="F13" s="34"/>
-      <c r="G13" s="29"/>
-      <c r="H13" s="94"/>
+      <c r="E13" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="F13" s="31"/>
+      <c r="G13" s="35" t="s">
+        <v>315</v>
+      </c>
+      <c r="H13" s="85"/>
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B14" s="35" t="s">
-        <v>47</v>
-      </c>
-      <c r="C14" s="40" t="s">
-        <v>76</v>
-      </c>
-      <c r="D14" s="41">
+      <c r="B14" s="32" t="s">
+        <v>44</v>
+      </c>
+      <c r="C14" s="35" t="s">
+        <v>72</v>
+      </c>
+      <c r="D14" s="36">
         <v>12</v>
       </c>
-      <c r="E14" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="F14" s="34"/>
-      <c r="G14" s="29"/>
-      <c r="H14" s="94"/>
+      <c r="E14" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="F14" s="31"/>
+      <c r="G14" s="35" t="s">
+        <v>315</v>
+      </c>
+      <c r="H14" s="85"/>
     </row>
     <row r="15" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
-      <c r="B15" s="35" t="s">
-        <v>59</v>
-      </c>
-      <c r="C15" s="40" t="s">
-        <v>68</v>
-      </c>
-      <c r="D15" s="34">
+      <c r="B15" s="32" t="s">
+        <v>56</v>
+      </c>
+      <c r="C15" s="35" t="s">
+        <v>65</v>
+      </c>
+      <c r="D15" s="31">
         <f>D10</f>
         <v>35</v>
       </c>
-      <c r="E15" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="F15" s="34"/>
-      <c r="G15" s="29"/>
-      <c r="H15" s="94"/>
+      <c r="E15" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="F15" s="31"/>
+      <c r="G15" s="35"/>
+      <c r="H15" s="85"/>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B16" s="35" t="s">
-        <v>58</v>
-      </c>
-      <c r="C16" s="40" t="s">
-        <v>66</v>
-      </c>
-      <c r="D16" s="34">
+      <c r="B16" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="C16" s="35" t="s">
+        <v>63</v>
+      </c>
+      <c r="D16" s="31">
         <f>D11+D14+D13</f>
         <v>55</v>
       </c>
-      <c r="E16" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="F16" s="34"/>
-      <c r="G16" s="29"/>
-      <c r="H16" s="94"/>
+      <c r="E16" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="F16" s="31"/>
+      <c r="G16" s="35"/>
+      <c r="H16" s="85"/>
     </row>
     <row r="17" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
-      <c r="B17" s="35" t="s">
-        <v>57</v>
-      </c>
-      <c r="C17" s="40" t="s">
-        <v>146</v>
-      </c>
-      <c r="D17" s="34">
+      <c r="B17" s="32" t="s">
+        <v>54</v>
+      </c>
+      <c r="C17" s="35" t="s">
+        <v>142</v>
+      </c>
+      <c r="D17" s="31">
         <f>D16*D15</f>
         <v>1925</v>
       </c>
-      <c r="E17" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="F17" s="34"/>
-      <c r="G17" s="29"/>
-      <c r="H17" s="94"/>
+      <c r="E17" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="F17" s="31"/>
+      <c r="G17" s="35"/>
+      <c r="H17" s="85"/>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B18" s="50" t="s">
-        <v>115</v>
-      </c>
-      <c r="C18" s="51" t="s">
-        <v>116</v>
-      </c>
-      <c r="D18" s="52">
+      <c r="B18" s="43" t="s">
+        <v>111</v>
+      </c>
+      <c r="C18" s="44" t="s">
+        <v>112</v>
+      </c>
+      <c r="D18" s="45">
         <f>D32+D30</f>
         <v>1435</v>
       </c>
-      <c r="E18" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="F18" s="52"/>
-      <c r="G18" s="31"/>
-      <c r="H18" s="95"/>
+      <c r="E18" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="F18" s="45"/>
+      <c r="G18" s="44"/>
+      <c r="H18" s="86"/>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B19" s="50" t="s">
-        <v>113</v>
-      </c>
-      <c r="C19" s="51" t="s">
-        <v>147</v>
-      </c>
-      <c r="D19" s="52">
+      <c r="B19" s="43" t="s">
+        <v>109</v>
+      </c>
+      <c r="C19" s="44" t="s">
+        <v>143</v>
+      </c>
+      <c r="D19" s="45">
         <f>D32+D30+D46</f>
         <v>1495</v>
       </c>
-      <c r="E19" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="F19" s="52"/>
-      <c r="G19" s="31"/>
-      <c r="H19" s="95"/>
+      <c r="E19" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="F19" s="45"/>
+      <c r="G19" s="44"/>
+      <c r="H19" s="86"/>
     </row>
     <row r="20" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
-      <c r="B20" s="50" t="s">
-        <v>78</v>
-      </c>
-      <c r="C20" s="51" t="s">
-        <v>148</v>
-      </c>
-      <c r="D20" s="52">
+      <c r="B20" s="43" t="s">
+        <v>74</v>
+      </c>
+      <c r="C20" s="44" t="s">
+        <v>144</v>
+      </c>
+      <c r="D20" s="45">
         <f>D18/D17</f>
         <v>0.74545454545454548</v>
       </c>
-      <c r="E20" s="52" t="s">
-        <v>79</v>
-      </c>
-      <c r="F20" s="52"/>
-      <c r="G20" s="31"/>
-      <c r="H20" s="95"/>
+      <c r="E20" s="45" t="s">
+        <v>75</v>
+      </c>
+      <c r="F20" s="45"/>
+      <c r="G20" s="44"/>
+      <c r="H20" s="86"/>
     </row>
     <row r="21" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
-      <c r="B21" s="50" t="s">
-        <v>114</v>
-      </c>
-      <c r="C21" s="51" t="s">
-        <v>149</v>
-      </c>
-      <c r="D21" s="52">
+      <c r="B21" s="43" t="s">
+        <v>110</v>
+      </c>
+      <c r="C21" s="44" t="s">
+        <v>145</v>
+      </c>
+      <c r="D21" s="45">
         <f>D19/D17</f>
         <v>0.77662337662337666</v>
       </c>
-      <c r="E21" s="52" t="s">
-        <v>79</v>
-      </c>
-      <c r="F21" s="52"/>
-      <c r="G21" s="31"/>
-      <c r="H21" s="95"/>
+      <c r="E21" s="45" t="s">
+        <v>75</v>
+      </c>
+      <c r="F21" s="45"/>
+      <c r="G21" s="44"/>
+      <c r="H21" s="86"/>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B22" s="46"/>
-      <c r="C22" s="47"/>
-      <c r="D22" s="48"/>
-      <c r="E22" s="48"/>
-      <c r="F22" s="48"/>
-      <c r="G22" s="30"/>
-      <c r="H22" s="96"/>
+      <c r="B22" s="40"/>
+      <c r="C22" s="41"/>
+      <c r="D22" s="42"/>
+      <c r="E22" s="42"/>
+      <c r="F22" s="42"/>
+      <c r="G22" s="41"/>
+      <c r="H22" s="87"/>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B23" s="6" t="s">
-        <v>225</v>
-      </c>
-      <c r="C23" s="37"/>
-      <c r="D23" s="38"/>
-      <c r="E23" s="38"/>
-      <c r="F23" s="38"/>
-      <c r="G23" s="37"/>
-      <c r="H23" s="93"/>
+        <v>218</v>
+      </c>
+      <c r="C23" s="33"/>
+      <c r="D23" s="34"/>
+      <c r="E23" s="34"/>
+      <c r="F23" s="34"/>
+      <c r="G23" s="99"/>
+      <c r="H23" s="84"/>
     </row>
     <row r="24" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
-      <c r="B24" s="35" t="s">
-        <v>83</v>
-      </c>
-      <c r="C24" s="40" t="s">
-        <v>150</v>
-      </c>
-      <c r="D24" s="41">
+      <c r="B24" s="32" t="s">
+        <v>79</v>
+      </c>
+      <c r="C24" s="35" t="s">
+        <v>146</v>
+      </c>
+      <c r="D24" s="36">
         <v>2</v>
       </c>
-      <c r="E24" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="F24" s="34"/>
-      <c r="G24" s="29"/>
-      <c r="H24" s="94">
+      <c r="E24" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="F24" s="31"/>
+      <c r="G24" s="35"/>
+      <c r="H24" s="85">
         <v>5</v>
       </c>
     </row>
     <row r="25" spans="2:8" ht="76.5" x14ac:dyDescent="0.45">
-      <c r="B25" s="35" t="s">
-        <v>84</v>
-      </c>
-      <c r="C25" s="40" t="s">
-        <v>94</v>
-      </c>
-      <c r="D25" s="57">
+      <c r="B25" s="32" t="s">
+        <v>80</v>
+      </c>
+      <c r="C25" s="35" t="s">
+        <v>90</v>
+      </c>
+      <c r="D25" s="49">
         <v>5</v>
       </c>
-      <c r="E25" s="34" t="s">
-        <v>80</v>
-      </c>
-      <c r="F25" s="34"/>
-      <c r="G25" s="29"/>
-      <c r="H25" s="94"/>
+      <c r="E25" s="31" t="s">
+        <v>76</v>
+      </c>
+      <c r="F25" s="31"/>
+      <c r="G25" s="35"/>
+      <c r="H25" s="85"/>
     </row>
     <row r="26" spans="2:8" ht="51" x14ac:dyDescent="0.45">
-      <c r="B26" s="35" t="s">
-        <v>85</v>
-      </c>
-      <c r="C26" s="40" t="s">
-        <v>82</v>
-      </c>
-      <c r="D26" s="34">
+      <c r="B26" s="32" t="s">
+        <v>81</v>
+      </c>
+      <c r="C26" s="35" t="s">
+        <v>78</v>
+      </c>
+      <c r="D26" s="31">
         <f>ROUND(ATAN(D25/100)*180/PI(),0)</f>
         <v>3</v>
       </c>
-      <c r="E26" s="34" t="s">
-        <v>81</v>
-      </c>
-      <c r="F26" s="34"/>
-      <c r="G26" s="29"/>
-      <c r="H26" s="94"/>
+      <c r="E26" s="31" t="s">
+        <v>77</v>
+      </c>
+      <c r="F26" s="31"/>
+      <c r="G26" s="35"/>
+      <c r="H26" s="85"/>
     </row>
     <row r="27" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
-      <c r="B27" s="50" t="s">
-        <v>87</v>
-      </c>
-      <c r="C27" s="51" t="s">
-        <v>152</v>
-      </c>
-      <c r="D27" s="58">
+      <c r="B27" s="43" t="s">
+        <v>83</v>
+      </c>
+      <c r="C27" s="44" t="s">
+        <v>148</v>
+      </c>
+      <c r="D27" s="50">
         <v>0.6</v>
       </c>
-      <c r="E27" s="52" t="s">
-        <v>60</v>
-      </c>
-      <c r="F27" s="52"/>
-      <c r="G27" s="31"/>
-      <c r="H27" s="95"/>
+      <c r="E27" s="45" t="s">
+        <v>57</v>
+      </c>
+      <c r="F27" s="45"/>
+      <c r="G27" s="44"/>
+      <c r="H27" s="86"/>
     </row>
     <row r="28" spans="2:8" ht="33" x14ac:dyDescent="0.45">
-      <c r="B28" s="35" t="s">
-        <v>86</v>
-      </c>
-      <c r="C28" s="40" t="s">
+      <c r="B28" s="32" t="s">
+        <v>82</v>
+      </c>
+      <c r="C28" s="35" t="s">
+        <v>147</v>
+      </c>
+      <c r="D28" s="36">
+        <v>0.2</v>
+      </c>
+      <c r="E28" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="F28" s="31"/>
+      <c r="G28" s="35"/>
+      <c r="H28" s="85"/>
+    </row>
+    <row r="29" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
+      <c r="B29" s="32" t="s">
+        <v>149</v>
+      </c>
+      <c r="C29" s="35" t="s">
         <v>151</v>
       </c>
-      <c r="D28" s="41">
-        <v>0.2</v>
-      </c>
-      <c r="E28" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="F28" s="34"/>
-      <c r="G28" s="29"/>
-      <c r="H28" s="94"/>
-    </row>
-    <row r="29" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
-      <c r="B29" s="35" t="s">
-        <v>153</v>
-      </c>
-      <c r="C29" s="40" t="s">
-        <v>155</v>
-      </c>
-      <c r="D29" s="41">
+      <c r="D29" s="36">
         <v>2</v>
       </c>
-      <c r="E29" s="34" t="s">
-        <v>79</v>
-      </c>
-      <c r="F29" s="34"/>
-      <c r="G29" s="29"/>
-      <c r="H29" s="94"/>
+      <c r="E29" s="31" t="s">
+        <v>75</v>
+      </c>
+      <c r="F29" s="31"/>
+      <c r="G29" s="35"/>
+      <c r="H29" s="85"/>
     </row>
     <row r="30" spans="2:8" ht="33" x14ac:dyDescent="0.45">
-      <c r="B30" s="50" t="s">
-        <v>88</v>
-      </c>
-      <c r="C30" s="51" t="s">
-        <v>154</v>
-      </c>
-      <c r="D30" s="52">
+      <c r="B30" s="43" t="s">
+        <v>84</v>
+      </c>
+      <c r="C30" s="44" t="s">
+        <v>150</v>
+      </c>
+      <c r="D30" s="45">
         <f>(D27-D28)*(D11+D24+D24)*D29</f>
         <v>32.799999999999997</v>
       </c>
-      <c r="E30" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="F30" s="52"/>
-      <c r="G30" s="31"/>
-      <c r="H30" s="95"/>
+      <c r="E30" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="F30" s="45"/>
+      <c r="G30" s="44"/>
+      <c r="H30" s="86"/>
     </row>
     <row r="31" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
-      <c r="B31" s="35" t="s">
-        <v>156</v>
-      </c>
-      <c r="C31" s="40" t="s">
-        <v>158</v>
-      </c>
-      <c r="D31" s="34">
+      <c r="B31" s="32" t="s">
+        <v>152</v>
+      </c>
+      <c r="C31" s="35" t="s">
+        <v>154</v>
+      </c>
+      <c r="D31" s="31">
         <f>(D10*D11)-D30</f>
         <v>1262.2</v>
       </c>
-      <c r="E31" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="F31" s="34"/>
-      <c r="G31" s="29"/>
-      <c r="H31" s="94"/>
+      <c r="E31" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="F31" s="31"/>
+      <c r="G31" s="35"/>
+      <c r="H31" s="85"/>
     </row>
     <row r="32" spans="2:8" ht="51" x14ac:dyDescent="0.45">
-      <c r="B32" s="35" t="s">
-        <v>157</v>
-      </c>
-      <c r="C32" s="40" t="s">
-        <v>159</v>
-      </c>
-      <c r="D32" s="34">
+      <c r="B32" s="32" t="s">
+        <v>153</v>
+      </c>
+      <c r="C32" s="35" t="s">
+        <v>155</v>
+      </c>
+      <c r="D32" s="31">
         <f>((D10*D11)+D10*(D24+D24))-D30</f>
         <v>1402.2</v>
       </c>
-      <c r="E32" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="F32" s="34"/>
-      <c r="G32" s="29"/>
-      <c r="H32" s="94"/>
+      <c r="E32" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="F32" s="31"/>
+      <c r="G32" s="35"/>
+      <c r="H32" s="85"/>
     </row>
     <row r="33" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
-      <c r="B33" s="35" t="s">
-        <v>89</v>
-      </c>
-      <c r="C33" s="40" t="s">
-        <v>139</v>
-      </c>
-      <c r="D33" s="41">
+      <c r="B33" s="32" t="s">
+        <v>85</v>
+      </c>
+      <c r="C33" s="35" t="s">
+        <v>135</v>
+      </c>
+      <c r="D33" s="36">
         <v>10</v>
       </c>
-      <c r="E33" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="F33" s="34"/>
-      <c r="G33" s="29"/>
-      <c r="H33" s="94"/>
+      <c r="E33" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="F33" s="31"/>
+      <c r="G33" s="35"/>
+      <c r="H33" s="85"/>
     </row>
     <row r="34" spans="2:8" ht="51" x14ac:dyDescent="0.45">
-      <c r="B34" s="35" t="s">
-        <v>90</v>
-      </c>
-      <c r="C34" s="40" t="s">
-        <v>160</v>
-      </c>
-      <c r="D34" s="34">
+      <c r="B34" s="32" t="s">
+        <v>86</v>
+      </c>
+      <c r="C34" s="35" t="s">
+        <v>156</v>
+      </c>
+      <c r="D34" s="31">
         <f>EVEN(D31/(D33*D33))</f>
         <v>14</v>
       </c>
-      <c r="E34" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="F34" s="34"/>
-      <c r="G34" s="29"/>
-      <c r="H34" s="94"/>
+      <c r="E34" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="F34" s="31"/>
+      <c r="G34" s="35"/>
+      <c r="H34" s="85"/>
     </row>
     <row r="35" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
-      <c r="B35" s="35" t="s">
-        <v>91</v>
-      </c>
-      <c r="C35" s="40" t="s">
-        <v>70</v>
-      </c>
-      <c r="D35" s="41">
+      <c r="B35" s="32" t="s">
+        <v>87</v>
+      </c>
+      <c r="C35" s="35" t="s">
+        <v>67</v>
+      </c>
+      <c r="D35" s="36">
         <v>1200</v>
       </c>
-      <c r="E35" s="34" t="s">
-        <v>71</v>
-      </c>
-      <c r="F35" s="34"/>
-      <c r="G35" s="29"/>
-      <c r="H35" s="94"/>
+      <c r="E35" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="F35" s="31"/>
+      <c r="G35" s="35"/>
+      <c r="H35" s="85"/>
     </row>
     <row r="36" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
-      <c r="B36" s="35" t="s">
-        <v>92</v>
-      </c>
-      <c r="C36" s="40" t="s">
-        <v>69</v>
-      </c>
-      <c r="D36" s="34">
+      <c r="B36" s="32" t="s">
+        <v>88</v>
+      </c>
+      <c r="C36" s="35" t="s">
+        <v>66</v>
+      </c>
+      <c r="D36" s="31">
         <f>D35*D35/(1000*1000)</f>
         <v>1.44</v>
       </c>
-      <c r="E36" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="F36" s="34"/>
-      <c r="G36" s="29"/>
-      <c r="H36" s="94"/>
+      <c r="E36" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="F36" s="31"/>
+      <c r="G36" s="35"/>
+      <c r="H36" s="85"/>
     </row>
     <row r="37" spans="2:8" ht="33" x14ac:dyDescent="0.45">
-      <c r="B37" s="35" t="s">
-        <v>93</v>
-      </c>
-      <c r="C37" s="40" t="s">
-        <v>161</v>
-      </c>
-      <c r="D37" s="34">
+      <c r="B37" s="32" t="s">
+        <v>89</v>
+      </c>
+      <c r="C37" s="35" t="s">
+        <v>157</v>
+      </c>
+      <c r="D37" s="31">
         <f>D34*D36</f>
         <v>20.16</v>
       </c>
-      <c r="E37" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="F37" s="34"/>
-      <c r="G37" s="29"/>
-      <c r="H37" s="94"/>
+      <c r="E37" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="F37" s="31"/>
+      <c r="G37" s="35"/>
+      <c r="H37" s="85"/>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B38" s="46"/>
-      <c r="C38" s="47"/>
-      <c r="D38" s="48"/>
-      <c r="E38" s="48"/>
-      <c r="F38" s="48"/>
-      <c r="G38" s="30"/>
-      <c r="H38" s="96"/>
+      <c r="B38" s="40"/>
+      <c r="C38" s="41"/>
+      <c r="D38" s="42"/>
+      <c r="E38" s="42"/>
+      <c r="F38" s="42"/>
+      <c r="G38" s="41"/>
+      <c r="H38" s="87"/>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B39" s="56" t="s">
-        <v>73</v>
-      </c>
-      <c r="C39" s="37"/>
-      <c r="D39" s="38"/>
-      <c r="E39" s="38"/>
-      <c r="F39" s="38"/>
-      <c r="G39" s="37"/>
-      <c r="H39" s="93"/>
+      <c r="B39" s="48" t="s">
+        <v>69</v>
+      </c>
+      <c r="C39" s="33"/>
+      <c r="D39" s="34"/>
+      <c r="E39" s="34"/>
+      <c r="F39" s="34"/>
+      <c r="G39" s="99"/>
+      <c r="H39" s="84"/>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B40" s="35" t="s">
+      <c r="B40" s="32" t="s">
+        <v>91</v>
+      </c>
+      <c r="C40" s="35" t="s">
         <v>95</v>
       </c>
-      <c r="C40" s="40" t="s">
-        <v>99</v>
-      </c>
-      <c r="D40" s="41">
+      <c r="D40" s="36">
         <v>1</v>
       </c>
-      <c r="E40" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="F40" s="34"/>
-      <c r="G40" s="29"/>
-      <c r="H40" s="94">
+      <c r="E40" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="F40" s="31"/>
+      <c r="G40" s="35"/>
+      <c r="H40" s="85">
         <v>5</v>
       </c>
     </row>
     <row r="41" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
-      <c r="B41" s="35" t="s">
+      <c r="B41" s="32" t="s">
+        <v>92</v>
+      </c>
+      <c r="C41" s="35" t="s">
         <v>96</v>
       </c>
-      <c r="C41" s="40" t="s">
-        <v>100</v>
-      </c>
-      <c r="D41" s="41">
+      <c r="D41" s="36">
         <v>15</v>
       </c>
-      <c r="E41" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="F41" s="34"/>
-      <c r="G41" s="29"/>
-      <c r="H41" s="94"/>
+      <c r="E41" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="F41" s="31"/>
+      <c r="G41" s="35"/>
+      <c r="H41" s="85"/>
     </row>
     <row r="42" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
-      <c r="B42" s="35" t="s">
+      <c r="B42" s="32" t="s">
+        <v>93</v>
+      </c>
+      <c r="C42" s="35" t="s">
         <v>97</v>
       </c>
-      <c r="C42" s="40" t="s">
-        <v>101</v>
-      </c>
-      <c r="D42" s="34">
+      <c r="D42" s="31">
         <f>D11+(INT(D11/D41)*D10)</f>
         <v>107</v>
       </c>
-      <c r="E42" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="F42" s="34"/>
-      <c r="G42" s="29"/>
-      <c r="H42" s="94"/>
+      <c r="E42" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="F42" s="31"/>
+      <c r="G42" s="35"/>
+      <c r="H42" s="85"/>
     </row>
     <row r="43" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
-      <c r="B43" s="35" t="s">
+      <c r="B43" s="32" t="s">
+        <v>94</v>
+      </c>
+      <c r="C43" s="35" t="s">
         <v>98</v>
       </c>
-      <c r="C43" s="40" t="s">
-        <v>102</v>
-      </c>
-      <c r="D43" s="34">
+      <c r="D43" s="31">
         <f>D42*D40</f>
         <v>107</v>
       </c>
-      <c r="E43" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="F43" s="34"/>
-      <c r="G43" s="29"/>
-      <c r="H43" s="94"/>
+      <c r="E43" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="F43" s="31"/>
+      <c r="G43" s="35"/>
+      <c r="H43" s="85"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B44" s="46"/>
-      <c r="C44" s="47"/>
-      <c r="D44" s="48"/>
-      <c r="E44" s="48"/>
-      <c r="F44" s="48"/>
-      <c r="G44" s="30"/>
-      <c r="H44" s="96"/>
+      <c r="B44" s="40"/>
+      <c r="C44" s="41"/>
+      <c r="D44" s="42"/>
+      <c r="E44" s="42"/>
+      <c r="F44" s="42"/>
+      <c r="G44" s="41"/>
+      <c r="H44" s="87"/>
     </row>
     <row r="45" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B45" s="56" t="s">
-        <v>74</v>
-      </c>
-      <c r="C45" s="37"/>
-      <c r="D45" s="38"/>
-      <c r="E45" s="38"/>
-      <c r="F45" s="38"/>
-      <c r="G45" s="37"/>
-      <c r="H45" s="93"/>
+      <c r="B45" s="48" t="s">
+        <v>70</v>
+      </c>
+      <c r="C45" s="33"/>
+      <c r="D45" s="34"/>
+      <c r="E45" s="34"/>
+      <c r="F45" s="34"/>
+      <c r="G45" s="99"/>
+      <c r="H45" s="84"/>
     </row>
     <row r="46" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
-      <c r="B46" s="35" t="s">
-        <v>48</v>
-      </c>
-      <c r="C46" s="40" t="s">
-        <v>162</v>
-      </c>
-      <c r="D46" s="41">
+      <c r="B46" s="32" t="s">
+        <v>45</v>
+      </c>
+      <c r="C46" s="35" t="s">
+        <v>158</v>
+      </c>
+      <c r="D46" s="36">
         <v>60</v>
       </c>
-      <c r="E46" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="F46" s="34"/>
-      <c r="G46" s="29"/>
-      <c r="H46" s="94">
+      <c r="E46" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="F46" s="31"/>
+      <c r="G46" s="35"/>
+      <c r="H46" s="85">
         <v>5</v>
       </c>
     </row>
     <row r="47" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
-      <c r="B47" s="35" t="s">
-        <v>49</v>
-      </c>
-      <c r="C47" s="40" t="s">
-        <v>50</v>
-      </c>
-      <c r="D47" s="41">
+      <c r="B47" s="32" t="s">
+        <v>46</v>
+      </c>
+      <c r="C47" s="35" t="s">
+        <v>47</v>
+      </c>
+      <c r="D47" s="36">
         <v>24</v>
       </c>
-      <c r="E47" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="F47" s="34"/>
-      <c r="G47" s="29"/>
-      <c r="H47" s="94"/>
+      <c r="E47" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="F47" s="31"/>
+      <c r="G47" s="35"/>
+      <c r="H47" s="85"/>
     </row>
     <row r="48" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
-      <c r="B48" s="35" t="s">
-        <v>103</v>
-      </c>
-      <c r="C48" s="40" t="s">
-        <v>140</v>
-      </c>
-      <c r="D48" s="41">
+      <c r="B48" s="32" t="s">
+        <v>99</v>
+      </c>
+      <c r="C48" s="35" t="s">
+        <v>136</v>
+      </c>
+      <c r="D48" s="36">
         <v>3.9900000000000007</v>
       </c>
-      <c r="E48" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="F48" s="34"/>
-      <c r="G48" s="29"/>
-      <c r="H48" s="94"/>
+      <c r="E48" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="F48" s="31"/>
+      <c r="G48" s="35"/>
+      <c r="H48" s="85"/>
     </row>
     <row r="49" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
-      <c r="B49" s="35" t="s">
-        <v>104</v>
-      </c>
-      <c r="C49" s="40" t="s">
-        <v>163</v>
-      </c>
-      <c r="D49" s="34">
+      <c r="B49" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="C49" s="35" t="s">
+        <v>159</v>
+      </c>
+      <c r="D49" s="31">
         <f>D46-D54</f>
         <v>52.943999999999996</v>
       </c>
-      <c r="E49" s="34" t="s">
+      <c r="E49" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="F49" s="31"/>
+      <c r="G49" s="35"/>
+      <c r="H49" s="85"/>
+    </row>
+    <row r="50" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
+      <c r="B50" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="F49" s="34"/>
-      <c r="G49" s="29"/>
-      <c r="H49" s="94"/>
-    </row>
-    <row r="50" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
-      <c r="B50" s="35" t="s">
-        <v>64</v>
-      </c>
-      <c r="C50" s="40" t="s">
-        <v>63</v>
-      </c>
-      <c r="D50" s="41">
+      <c r="C50" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="D50" s="36">
         <v>28</v>
       </c>
-      <c r="E50" s="34" t="s">
+      <c r="E50" s="31" t="s">
+        <v>59</v>
+      </c>
+      <c r="F50" s="31"/>
+      <c r="G50" s="35"/>
+      <c r="H50" s="85"/>
+    </row>
+    <row r="51" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
+      <c r="B51" s="32" t="s">
+        <v>103</v>
+      </c>
+      <c r="C51" s="35" t="s">
         <v>62</v>
       </c>
-      <c r="F50" s="34"/>
-      <c r="G50" s="29"/>
-      <c r="H50" s="94"/>
-    </row>
-    <row r="51" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
-      <c r="B51" s="35" t="s">
-        <v>107</v>
-      </c>
-      <c r="C51" s="40" t="s">
-        <v>65</v>
-      </c>
-      <c r="D51" s="41">
+      <c r="D51" s="36">
         <v>19</v>
       </c>
-      <c r="E51" s="34" t="s">
-        <v>62</v>
-      </c>
-      <c r="F51" s="34"/>
-      <c r="G51" s="29"/>
-      <c r="H51" s="94"/>
+      <c r="E51" s="31" t="s">
+        <v>59</v>
+      </c>
+      <c r="F51" s="31"/>
+      <c r="G51" s="35"/>
+      <c r="H51" s="85"/>
     </row>
     <row r="52" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
-      <c r="B52" s="35" t="s">
-        <v>105</v>
-      </c>
-      <c r="C52" s="40" t="s">
-        <v>106</v>
-      </c>
-      <c r="D52" s="34">
+      <c r="B52" s="32" t="s">
+        <v>101</v>
+      </c>
+      <c r="C52" s="35" t="s">
+        <v>102</v>
+      </c>
+      <c r="D52" s="31">
         <f>D48/(D51/100)</f>
         <v>21.000000000000004</v>
       </c>
-      <c r="E52" s="34" t="s">
-        <v>56</v>
-      </c>
-      <c r="F52" s="34"/>
-      <c r="G52" s="29"/>
-      <c r="H52" s="94"/>
+      <c r="E52" s="31" t="s">
+        <v>53</v>
+      </c>
+      <c r="F52" s="31"/>
+      <c r="G52" s="35"/>
+      <c r="H52" s="85"/>
     </row>
     <row r="53" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B53" s="35" t="s">
-        <v>108</v>
-      </c>
-      <c r="C53" s="40" t="s">
-        <v>109</v>
-      </c>
-      <c r="D53" s="41">
+      <c r="B53" s="32" t="s">
+        <v>104</v>
+      </c>
+      <c r="C53" s="35" t="s">
+        <v>105</v>
+      </c>
+      <c r="D53" s="36">
         <v>1.2</v>
       </c>
-      <c r="E53" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="F53" s="34"/>
-      <c r="G53" s="29"/>
-      <c r="H53" s="94"/>
+      <c r="E53" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="F53" s="31"/>
+      <c r="G53" s="35"/>
+      <c r="H53" s="85"/>
     </row>
     <row r="54" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
-      <c r="B54" s="35" t="s">
-        <v>110</v>
-      </c>
-      <c r="C54" s="40" t="s">
-        <v>111</v>
-      </c>
-      <c r="D54" s="54">
+      <c r="B54" s="32" t="s">
+        <v>106</v>
+      </c>
+      <c r="C54" s="35" t="s">
+        <v>107</v>
+      </c>
+      <c r="D54" s="46">
         <f>D53*D52*(D50/100)</f>
         <v>7.0560000000000018</v>
       </c>
-      <c r="E54" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="F54" s="34"/>
-      <c r="G54" s="29"/>
-      <c r="H54" s="94"/>
+      <c r="E54" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="F54" s="31"/>
+      <c r="G54" s="35"/>
+      <c r="H54" s="85"/>
     </row>
     <row r="55" spans="2:8" ht="89.25" x14ac:dyDescent="0.45">
-      <c r="B55" s="35" t="s">
+      <c r="B55" s="32" t="s">
+        <v>137</v>
+      </c>
+      <c r="C55" s="35" t="s">
+        <v>200</v>
+      </c>
+      <c r="D55" s="36">
+        <v>6</v>
+      </c>
+      <c r="E55" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="F55" s="31"/>
+      <c r="G55" s="35"/>
+      <c r="H55" s="85"/>
+    </row>
+    <row r="56" spans="2:8" ht="102" x14ac:dyDescent="0.45">
+      <c r="B56" s="32" t="s">
+        <v>138</v>
+      </c>
+      <c r="C56" s="35" t="s">
+        <v>201</v>
+      </c>
+      <c r="D56" s="36">
+        <v>4.5</v>
+      </c>
+      <c r="E56" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="F56" s="31"/>
+      <c r="G56" s="35"/>
+      <c r="H56" s="85"/>
+    </row>
+    <row r="57" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B57" s="32" t="s">
+        <v>140</v>
+      </c>
+      <c r="C57" s="35" t="s">
+        <v>139</v>
+      </c>
+      <c r="D57" s="36">
+        <v>1.2</v>
+      </c>
+      <c r="E57" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="F57" s="31"/>
+      <c r="G57" s="35"/>
+      <c r="H57" s="85"/>
+    </row>
+    <row r="58" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B58" s="32" t="s">
+        <v>198</v>
+      </c>
+      <c r="C58" s="35" t="s">
+        <v>199</v>
+      </c>
+      <c r="D58" s="36">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="E58" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="F58" s="31"/>
+      <c r="G58" s="35"/>
+      <c r="H58" s="85"/>
+    </row>
+    <row r="59" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
+      <c r="B59" s="32" t="s">
         <v>141</v>
       </c>
-      <c r="C55" s="40" t="s">
-        <v>204</v>
-      </c>
-      <c r="D55" s="41">
-        <v>6</v>
-      </c>
-      <c r="E55" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="F55" s="34"/>
-      <c r="G55" s="29"/>
-      <c r="H55" s="94"/>
-    </row>
-    <row r="56" spans="2:8" ht="102" x14ac:dyDescent="0.45">
-      <c r="B56" s="35" t="s">
-        <v>142</v>
-      </c>
-      <c r="C56" s="40" t="s">
-        <v>205</v>
-      </c>
-      <c r="D56" s="41">
-        <v>4.5</v>
-      </c>
-      <c r="E56" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="F56" s="34"/>
-      <c r="G56" s="29"/>
-      <c r="H56" s="94"/>
-    </row>
-    <row r="57" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B57" s="35" t="s">
-        <v>144</v>
-      </c>
-      <c r="C57" s="40" t="s">
-        <v>143</v>
-      </c>
-      <c r="D57" s="41">
-        <v>1.2</v>
-      </c>
-      <c r="E57" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="F57" s="34"/>
-      <c r="G57" s="29"/>
-      <c r="H57" s="94"/>
-    </row>
-    <row r="58" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B58" s="35" t="s">
+      <c r="C59" s="35" t="s">
         <v>202</v>
       </c>
-      <c r="C58" s="40" t="s">
+      <c r="D59" s="36">
+        <v>3</v>
+      </c>
+      <c r="E59" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="F59" s="31"/>
+      <c r="G59" s="35"/>
+      <c r="H59" s="85"/>
+    </row>
+    <row r="60" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
+      <c r="B60" s="32" t="s">
+        <v>197</v>
+      </c>
+      <c r="C60" s="35" t="s">
         <v>203</v>
       </c>
-      <c r="D58" s="41">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="E58" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="F58" s="34"/>
-      <c r="G58" s="29"/>
-      <c r="H58" s="94"/>
-    </row>
-    <row r="59" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
-      <c r="B59" s="35" t="s">
-        <v>145</v>
-      </c>
-      <c r="C59" s="40" t="s">
-        <v>206</v>
-      </c>
-      <c r="D59" s="41">
-        <v>3</v>
-      </c>
-      <c r="E59" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="F59" s="34"/>
-      <c r="G59" s="29"/>
-      <c r="H59" s="94"/>
-    </row>
-    <row r="60" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
-      <c r="B60" s="35" t="s">
-        <v>201</v>
-      </c>
-      <c r="C60" s="40" t="s">
-        <v>207</v>
-      </c>
-      <c r="D60" s="41">
+      <c r="D60" s="36">
         <v>2</v>
       </c>
-      <c r="E60" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="F60" s="34"/>
-      <c r="G60" s="29"/>
-      <c r="H60" s="94"/>
+      <c r="E60" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="F60" s="31"/>
+      <c r="G60" s="35"/>
+      <c r="H60" s="85"/>
     </row>
     <row r="61" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B61" s="46"/>
-      <c r="C61" s="47"/>
-      <c r="D61" s="48"/>
-      <c r="E61" s="48"/>
-      <c r="F61" s="48"/>
-      <c r="G61" s="30"/>
-      <c r="H61" s="96"/>
+      <c r="B61" s="40"/>
+      <c r="C61" s="41"/>
+      <c r="D61" s="42"/>
+      <c r="E61" s="42"/>
+      <c r="F61" s="42"/>
+      <c r="G61" s="41"/>
+      <c r="H61" s="87"/>
     </row>
     <row r="62" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B62" s="59" t="s">
-        <v>75</v>
-      </c>
-      <c r="C62" s="60"/>
-      <c r="D62" s="61"/>
-      <c r="E62" s="61"/>
-      <c r="F62" s="61"/>
-      <c r="G62" s="60"/>
-      <c r="H62" s="97"/>
+      <c r="B62" s="51" t="s">
+        <v>71</v>
+      </c>
+      <c r="C62" s="52"/>
+      <c r="D62" s="53"/>
+      <c r="E62" s="53"/>
+      <c r="F62" s="53"/>
+      <c r="G62" s="100"/>
+      <c r="H62" s="88"/>
     </row>
     <row r="63" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
-      <c r="B63" s="35" t="s">
-        <v>185</v>
-      </c>
-      <c r="C63" s="40" t="s">
-        <v>118</v>
-      </c>
-      <c r="D63" s="41">
+      <c r="B63" s="32" t="s">
+        <v>181</v>
+      </c>
+      <c r="C63" s="35" t="s">
+        <v>114</v>
+      </c>
+      <c r="D63" s="36">
         <v>40</v>
       </c>
-      <c r="E63" s="34" t="s">
-        <v>62</v>
-      </c>
-      <c r="F63" s="34"/>
-      <c r="G63" s="29"/>
-      <c r="H63" s="94">
+      <c r="E63" s="31" t="s">
+        <v>59</v>
+      </c>
+      <c r="F63" s="31"/>
+      <c r="G63" s="35"/>
+      <c r="H63" s="85">
         <v>5</v>
       </c>
     </row>
     <row r="64" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
-      <c r="B64" s="35" t="s">
-        <v>184</v>
-      </c>
-      <c r="C64" s="40" t="s">
-        <v>186</v>
-      </c>
-      <c r="D64" s="54">
+      <c r="B64" s="32" t="s">
+        <v>180</v>
+      </c>
+      <c r="C64" s="35" t="s">
+        <v>182</v>
+      </c>
+      <c r="D64" s="46">
         <f>D18</f>
         <v>1435</v>
       </c>
-      <c r="E64" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="F64" s="34"/>
-      <c r="G64" s="29"/>
-      <c r="H64" s="94"/>
+      <c r="E64" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="F64" s="31"/>
+      <c r="G64" s="35"/>
+      <c r="H64" s="85"/>
     </row>
     <row r="65" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
-      <c r="B65" s="35" t="s">
+      <c r="B65" s="32" t="s">
+        <v>113</v>
+      </c>
+      <c r="C65" s="35" t="s">
+        <v>115</v>
+      </c>
+      <c r="D65" s="36">
+        <v>20</v>
+      </c>
+      <c r="E65" s="31" t="s">
+        <v>59</v>
+      </c>
+      <c r="F65" s="31"/>
+      <c r="G65" s="35"/>
+      <c r="H65" s="85"/>
+    </row>
+    <row r="66" spans="2:8" ht="33" x14ac:dyDescent="0.45">
+      <c r="B66" s="32" t="s">
+        <v>124</v>
+      </c>
+      <c r="C66" s="35" t="s">
         <v>117</v>
       </c>
-      <c r="C65" s="40" t="s">
-        <v>119</v>
-      </c>
-      <c r="D65" s="41">
-        <v>20</v>
-      </c>
-      <c r="E65" s="34" t="s">
-        <v>62</v>
-      </c>
-      <c r="F65" s="34"/>
-      <c r="G65" s="29"/>
-      <c r="H65" s="94"/>
-    </row>
-    <row r="66" spans="2:8" ht="33" x14ac:dyDescent="0.45">
-      <c r="B66" s="35" t="s">
-        <v>128</v>
-      </c>
-      <c r="C66" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="D66" s="41">
+      <c r="D66" s="36">
         <v>6</v>
       </c>
-      <c r="E66" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="F66" s="34"/>
-      <c r="G66" s="29"/>
-      <c r="H66" s="94"/>
+      <c r="E66" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="F66" s="31"/>
+      <c r="G66" s="35"/>
+      <c r="H66" s="85"/>
     </row>
     <row r="67" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
-      <c r="B67" s="35" t="s">
-        <v>129</v>
-      </c>
-      <c r="C67" s="40" t="s">
-        <v>164</v>
-      </c>
-      <c r="D67" s="54">
+      <c r="B67" s="32" t="s">
+        <v>125</v>
+      </c>
+      <c r="C67" s="35" t="s">
+        <v>160</v>
+      </c>
+      <c r="D67" s="46">
         <f>ROUND(D10/D66,0)</f>
         <v>6</v>
       </c>
-      <c r="E67" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="F67" s="34"/>
-      <c r="G67" s="29"/>
-      <c r="H67" s="94"/>
+      <c r="E67" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="F67" s="31"/>
+      <c r="G67" s="35"/>
+      <c r="H67" s="85"/>
     </row>
     <row r="68" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
-      <c r="B68" s="35" t="s">
-        <v>132</v>
-      </c>
-      <c r="C68" s="40" t="s">
-        <v>165</v>
-      </c>
-      <c r="D68" s="54">
+      <c r="B68" s="32" t="s">
+        <v>128</v>
+      </c>
+      <c r="C68" s="35" t="s">
+        <v>161</v>
+      </c>
+      <c r="D68" s="46">
         <f>ROUND(D11/D66,0)</f>
         <v>6</v>
       </c>
-      <c r="E68" s="34" t="s">
+      <c r="E68" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="F68" s="31"/>
+      <c r="G68" s="35"/>
+      <c r="H68" s="85"/>
+    </row>
+    <row r="69" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="B69" s="32" t="s">
+        <v>129</v>
+      </c>
+      <c r="C69" s="35" t="s">
         <v>130</v>
       </c>
-      <c r="F68" s="34"/>
-      <c r="G68" s="29"/>
-      <c r="H68" s="94"/>
-    </row>
-    <row r="69" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B69" s="35" t="s">
-        <v>133</v>
-      </c>
-      <c r="C69" s="40" t="s">
-        <v>134</v>
-      </c>
-      <c r="D69" s="54">
+      <c r="D69" s="46">
         <f>D68*D67</f>
         <v>36</v>
       </c>
-      <c r="E69" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="F69" s="34"/>
-      <c r="G69" s="29"/>
-      <c r="H69" s="94"/>
+      <c r="E69" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="F69" s="31"/>
+      <c r="G69" s="35"/>
+      <c r="H69" s="85"/>
     </row>
     <row r="70" spans="2:8" ht="51" x14ac:dyDescent="0.45">
-      <c r="B70" s="35" t="s">
+      <c r="B70" s="32" t="s">
+        <v>116</v>
+      </c>
+      <c r="C70" s="35" t="s">
+        <v>162</v>
+      </c>
+      <c r="D70" s="36">
+        <v>0.3</v>
+      </c>
+      <c r="E70" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="F70" s="31"/>
+      <c r="G70" s="35"/>
+      <c r="H70" s="85"/>
+    </row>
+    <row r="71" spans="2:8" ht="51" x14ac:dyDescent="0.45">
+      <c r="B71" s="32" t="s">
+        <v>118</v>
+      </c>
+      <c r="C71" s="35" t="s">
+        <v>163</v>
+      </c>
+      <c r="D71" s="36">
+        <v>0.4</v>
+      </c>
+      <c r="E71" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="F71" s="31"/>
+      <c r="G71" s="35"/>
+      <c r="H71" s="85"/>
+    </row>
+    <row r="72" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
+      <c r="B72" s="32" t="s">
         <v>120</v>
       </c>
-      <c r="C70" s="40" t="s">
-        <v>166</v>
-      </c>
-      <c r="D70" s="41">
+      <c r="C72" s="35" t="s">
+        <v>122</v>
+      </c>
+      <c r="D72" s="36">
         <v>0.3</v>
       </c>
-      <c r="E70" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="F70" s="34"/>
-      <c r="G70" s="29"/>
-      <c r="H70" s="94"/>
-    </row>
-    <row r="71" spans="2:8" ht="51" x14ac:dyDescent="0.45">
-      <c r="B71" s="35" t="s">
-        <v>122</v>
-      </c>
-      <c r="C71" s="40" t="s">
-        <v>167</v>
-      </c>
-      <c r="D71" s="41">
+      <c r="E72" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="F72" s="31"/>
+      <c r="G72" s="35"/>
+      <c r="H72" s="85"/>
+    </row>
+    <row r="73" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
+      <c r="B73" s="32" t="s">
+        <v>121</v>
+      </c>
+      <c r="C73" s="35" t="s">
+        <v>123</v>
+      </c>
+      <c r="D73" s="36">
         <v>0.4</v>
       </c>
-      <c r="E71" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="F71" s="34"/>
-      <c r="G71" s="29"/>
-      <c r="H71" s="94"/>
-    </row>
-    <row r="72" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
-      <c r="B72" s="35" t="s">
-        <v>124</v>
-      </c>
-      <c r="C72" s="40" t="s">
-        <v>126</v>
-      </c>
-      <c r="D72" s="41">
-        <v>0.3</v>
-      </c>
-      <c r="E72" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="F72" s="34"/>
-      <c r="G72" s="29"/>
-      <c r="H72" s="94"/>
-    </row>
-    <row r="73" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
-      <c r="B73" s="35" t="s">
-        <v>125</v>
-      </c>
-      <c r="C73" s="40" t="s">
-        <v>127</v>
-      </c>
-      <c r="D73" s="41">
-        <v>0.4</v>
-      </c>
-      <c r="E73" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="F73" s="34"/>
-      <c r="G73" s="29"/>
-      <c r="H73" s="94"/>
+      <c r="E73" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="F73" s="31"/>
+      <c r="G73" s="35"/>
+      <c r="H73" s="85"/>
     </row>
     <row r="74" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
-      <c r="B74" s="35" t="s">
-        <v>135</v>
-      </c>
-      <c r="C74" s="40" t="s">
-        <v>137</v>
-      </c>
-      <c r="D74" s="54">
+      <c r="B74" s="32" t="s">
+        <v>131</v>
+      </c>
+      <c r="C74" s="35" t="s">
+        <v>133</v>
+      </c>
+      <c r="D74" s="46">
         <f>(D10-D70)/D67</f>
         <v>5.7833333333333341</v>
       </c>
-      <c r="E74" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="F74" s="34"/>
-      <c r="G74" s="29"/>
-      <c r="H74" s="94"/>
+      <c r="E74" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="F74" s="31"/>
+      <c r="G74" s="35"/>
+      <c r="H74" s="85"/>
     </row>
     <row r="75" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
-      <c r="B75" s="35" t="s">
-        <v>136</v>
-      </c>
-      <c r="C75" s="40" t="s">
-        <v>138</v>
-      </c>
-      <c r="D75" s="54">
+      <c r="B75" s="32" t="s">
+        <v>132</v>
+      </c>
+      <c r="C75" s="35" t="s">
+        <v>134</v>
+      </c>
+      <c r="D75" s="46">
         <f>(D11-D71)/D68</f>
         <v>6.1000000000000005</v>
       </c>
-      <c r="E75" s="34" t="s">
-        <v>60</v>
-      </c>
-      <c r="F75" s="34"/>
-      <c r="G75" s="29"/>
-      <c r="H75" s="94"/>
+      <c r="E75" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="F75" s="31"/>
+      <c r="G75" s="35"/>
+      <c r="H75" s="85"/>
     </row>
     <row r="76" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B76" s="62"/>
-      <c r="C76" s="63"/>
-      <c r="D76" s="64"/>
-      <c r="E76" s="64"/>
-      <c r="F76" s="64"/>
-      <c r="G76" s="4"/>
+      <c r="B76" s="54"/>
+      <c r="C76" s="55"/>
+      <c r="D76" s="56"/>
+      <c r="E76" s="56"/>
+      <c r="F76" s="56"/>
+      <c r="G76" s="55"/>
       <c r="H76" s="9"/>
     </row>
     <row r="77" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B77" s="65" t="s">
-        <v>123</v>
+      <c r="B77" s="57" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="79" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B79" s="2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="80" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B80" s="6" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="C80" s="14" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
     </row>
     <row r="81" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B81" s="66" t="s">
-        <v>170</v>
+      <c r="B81" s="58" t="s">
+        <v>166</v>
       </c>
       <c r="C81" s="13">
         <f>D17</f>
@@ -4217,8 +4774,8 @@
       </c>
     </row>
     <row r="82" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B82" s="66" t="s">
-        <v>173</v>
+      <c r="B82" s="58" t="s">
+        <v>169</v>
       </c>
       <c r="C82" s="13">
         <f>D18</f>
@@ -4226,8 +4783,8 @@
       </c>
     </row>
     <row r="83" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B83" s="66" t="s">
-        <v>172</v>
+      <c r="B83" s="58" t="s">
+        <v>168</v>
       </c>
       <c r="C83" s="13">
         <f>D46</f>
@@ -4235,8 +4792,8 @@
       </c>
     </row>
     <row r="84" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B84" s="66" t="s">
-        <v>52</v>
+      <c r="B84" s="58" t="s">
+        <v>49</v>
       </c>
       <c r="C84" s="13">
         <f>D54</f>
@@ -4244,8 +4801,8 @@
       </c>
     </row>
     <row r="85" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B85" s="66" t="s">
-        <v>51</v>
+      <c r="B85" s="58" t="s">
+        <v>48</v>
       </c>
       <c r="C85" s="13">
         <f>D49</f>
@@ -4253,26 +4810,26 @@
       </c>
     </row>
     <row r="86" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B86" s="67" t="s">
-        <v>171</v>
-      </c>
-      <c r="C86" s="68">
+      <c r="B86" s="59" t="s">
+        <v>167</v>
+      </c>
+      <c r="C86" s="60">
         <f>D19</f>
         <v>1495</v>
       </c>
     </row>
     <row r="87" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B87" s="69" t="s">
-        <v>78</v>
-      </c>
-      <c r="C87" s="70">
+      <c r="B87" s="61" t="s">
+        <v>74</v>
+      </c>
+      <c r="C87" s="62">
         <f>D20</f>
         <v>0.74545454545454548</v>
       </c>
     </row>
     <row r="88" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B88" s="62" t="s">
-        <v>114</v>
+      <c r="B88" s="54" t="s">
+        <v>110</v>
       </c>
       <c r="C88" s="5">
         <f>D21</f>
@@ -4281,278 +4838,278 @@
     </row>
     <row r="90" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B90" s="2" t="s">
-        <v>248</v>
+        <v>269</v>
       </c>
     </row>
     <row r="91" spans="2:8" x14ac:dyDescent="0.45">
       <c r="B91" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="C91" s="37" t="s">
-        <v>44</v>
+        <v>164</v>
+      </c>
+      <c r="C91" s="33" t="s">
+        <v>41</v>
       </c>
       <c r="D91" s="8" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E91" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="F91" s="38" t="s">
-        <v>45</v>
-      </c>
-      <c r="G91" s="37" t="s">
+        <v>53</v>
+      </c>
+      <c r="F91" s="34" t="s">
+        <v>42</v>
+      </c>
+      <c r="G91" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="H91" s="84" t="s">
         <v>27</v>
       </c>
-      <c r="H91" s="93" t="s">
-        <v>28</v>
-      </c>
     </row>
     <row r="92" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B92" s="35" t="s">
-        <v>188</v>
+      <c r="B92" s="32" t="s">
+        <v>184</v>
       </c>
       <c r="C92" s="29" t="s">
-        <v>187</v>
-      </c>
-      <c r="D92" s="72">
+        <v>183</v>
+      </c>
+      <c r="D92" s="64">
         <f>D64</f>
         <v>1435</v>
       </c>
-      <c r="E92" s="72" t="s">
-        <v>61</v>
-      </c>
-      <c r="F92" s="34"/>
-      <c r="G92" s="29"/>
-      <c r="H92" s="94"/>
+      <c r="E92" s="64" t="s">
+        <v>58</v>
+      </c>
+      <c r="F92" s="31"/>
+      <c r="G92" s="35"/>
+      <c r="H92" s="85"/>
     </row>
     <row r="93" spans="2:8" ht="33" x14ac:dyDescent="0.45">
-      <c r="B93" s="35" t="s">
-        <v>189</v>
+      <c r="B93" s="32" t="s">
+        <v>185</v>
       </c>
       <c r="C93" s="29" t="s">
-        <v>190</v>
-      </c>
-      <c r="D93" s="72">
+        <v>186</v>
+      </c>
+      <c r="D93" s="64">
         <f>D92*D63</f>
         <v>57400</v>
       </c>
-      <c r="E93" s="72" t="s">
-        <v>191</v>
-      </c>
-      <c r="F93" s="34"/>
-      <c r="G93" s="29"/>
-      <c r="H93" s="94"/>
+      <c r="E93" s="64" t="s">
+        <v>187</v>
+      </c>
+      <c r="F93" s="31"/>
+      <c r="G93" s="35"/>
+      <c r="H93" s="85"/>
     </row>
     <row r="94" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B94" s="35" t="s">
-        <v>200</v>
+      <c r="B94" s="32" t="s">
+        <v>196</v>
       </c>
       <c r="C94" s="29" t="s">
-        <v>199</v>
-      </c>
-      <c r="D94" s="72">
+        <v>195</v>
+      </c>
+      <c r="D94" s="64">
         <f>D49</f>
         <v>52.943999999999996</v>
       </c>
-      <c r="E94" s="72" t="s">
-        <v>61</v>
-      </c>
-      <c r="F94" s="72"/>
-      <c r="G94" s="3"/>
+      <c r="E94" s="64" t="s">
+        <v>58</v>
+      </c>
+      <c r="F94" s="64"/>
+      <c r="G94" s="101"/>
       <c r="H94" s="11"/>
     </row>
     <row r="95" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B95" s="35" t="s">
-        <v>193</v>
+      <c r="B95" s="32" t="s">
+        <v>189</v>
       </c>
       <c r="C95" s="29" t="s">
-        <v>194</v>
-      </c>
-      <c r="D95" s="72">
+        <v>190</v>
+      </c>
+      <c r="D95" s="64">
         <f>D69</f>
         <v>36</v>
       </c>
-      <c r="E95" s="72" t="s">
-        <v>130</v>
-      </c>
-      <c r="F95" s="72"/>
-      <c r="G95" s="3"/>
+      <c r="E95" s="64" t="s">
+        <v>126</v>
+      </c>
+      <c r="F95" s="64"/>
+      <c r="G95" s="101"/>
       <c r="H95" s="11"/>
     </row>
     <row r="96" spans="2:8" ht="33" x14ac:dyDescent="0.45">
-      <c r="B96" s="35" t="s">
-        <v>195</v>
+      <c r="B96" s="32" t="s">
+        <v>191</v>
       </c>
       <c r="C96" s="29" t="s">
-        <v>196</v>
-      </c>
-      <c r="D96" s="72">
+        <v>192</v>
+      </c>
+      <c r="D96" s="64">
         <f>D95*D12</f>
         <v>432</v>
       </c>
-      <c r="E96" s="72" t="s">
-        <v>60</v>
-      </c>
-      <c r="F96" s="72"/>
-      <c r="G96" s="3"/>
+      <c r="E96" s="64" t="s">
+        <v>57</v>
+      </c>
+      <c r="F96" s="64"/>
+      <c r="G96" s="101"/>
       <c r="H96" s="11"/>
     </row>
     <row r="97" spans="2:8" ht="49.5" x14ac:dyDescent="0.45">
-      <c r="B97" s="35" t="s">
-        <v>197</v>
+      <c r="B97" s="32" t="s">
+        <v>193</v>
       </c>
       <c r="C97" s="29" t="s">
-        <v>198</v>
-      </c>
-      <c r="D97" s="72">
+        <v>194</v>
+      </c>
+      <c r="D97" s="64">
         <f>((D67*D9)+(D68*D8))*INT(D12/D48)</f>
         <v>324</v>
       </c>
-      <c r="E97" s="72" t="s">
-        <v>60</v>
-      </c>
-      <c r="F97" s="72"/>
-      <c r="G97" s="3"/>
+      <c r="E97" s="64" t="s">
+        <v>57</v>
+      </c>
+      <c r="F97" s="64"/>
+      <c r="G97" s="101"/>
       <c r="H97" s="11"/>
     </row>
     <row r="98" spans="2:8" ht="33" x14ac:dyDescent="0.45">
-      <c r="B98" s="35" t="s">
-        <v>208</v>
+      <c r="B98" s="32" t="s">
+        <v>204</v>
       </c>
       <c r="C98" s="29" t="s">
-        <v>211</v>
-      </c>
-      <c r="D98" s="91" t="s">
-        <v>210</v>
-      </c>
-      <c r="E98" s="72" t="s">
-        <v>61</v>
-      </c>
-      <c r="F98" s="72"/>
-      <c r="G98" s="3"/>
+        <v>207</v>
+      </c>
+      <c r="D98" s="82" t="s">
+        <v>206</v>
+      </c>
+      <c r="E98" s="64" t="s">
+        <v>58</v>
+      </c>
+      <c r="F98" s="64"/>
+      <c r="G98" s="101"/>
       <c r="H98" s="11">
         <v>5</v>
       </c>
     </row>
     <row r="99" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B99" s="35" t="s">
+      <c r="B99" s="32" t="s">
+        <v>205</v>
+      </c>
+      <c r="C99" s="29" t="s">
+        <v>208</v>
+      </c>
+      <c r="D99" s="82">
+        <v>2</v>
+      </c>
+      <c r="E99" s="64" t="s">
+        <v>126</v>
+      </c>
+      <c r="F99" s="64"/>
+      <c r="G99" s="101"/>
+      <c r="H99" s="11"/>
+    </row>
+    <row r="100" spans="2:8" ht="49.5" x14ac:dyDescent="0.45">
+      <c r="B100" s="32" t="s">
+        <v>50</v>
+      </c>
+      <c r="C100" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="C99" s="29" t="s">
-        <v>212</v>
-      </c>
-      <c r="D99" s="91">
-        <v>2</v>
-      </c>
-      <c r="E99" s="72" t="s">
-        <v>130</v>
-      </c>
-      <c r="F99" s="72"/>
-      <c r="G99" s="3"/>
-      <c r="H99" s="11"/>
-    </row>
-    <row r="100" spans="2:8" ht="49.5" x14ac:dyDescent="0.45">
-      <c r="B100" s="35" t="s">
-        <v>53</v>
-      </c>
-      <c r="C100" s="29" t="s">
-        <v>213</v>
-      </c>
-      <c r="D100" s="91" t="s">
+      <c r="D100" s="82" t="s">
+        <v>206</v>
+      </c>
+      <c r="E100" s="64" t="s">
+        <v>126</v>
+      </c>
+      <c r="F100" s="64"/>
+      <c r="G100" s="101"/>
+      <c r="H100" s="11"/>
+    </row>
+    <row r="101" spans="2:8" ht="33" x14ac:dyDescent="0.45">
+      <c r="B101" s="32" t="s">
+        <v>51</v>
+      </c>
+      <c r="C101" s="29" t="s">
         <v>210</v>
       </c>
-      <c r="E100" s="72" t="s">
-        <v>130</v>
-      </c>
-      <c r="F100" s="72"/>
-      <c r="G100" s="3"/>
-      <c r="H100" s="11"/>
-    </row>
-    <row r="101" spans="2:8" ht="33" x14ac:dyDescent="0.45">
-      <c r="B101" s="35" t="s">
-        <v>54</v>
-      </c>
-      <c r="C101" s="29" t="s">
-        <v>214</v>
-      </c>
-      <c r="D101" s="91" t="s">
-        <v>210</v>
-      </c>
-      <c r="E101" s="72" t="s">
-        <v>130</v>
-      </c>
-      <c r="F101" s="72"/>
-      <c r="G101" s="3"/>
+      <c r="D101" s="82" t="s">
+        <v>206</v>
+      </c>
+      <c r="E101" s="64" t="s">
+        <v>126</v>
+      </c>
+      <c r="F101" s="64"/>
+      <c r="G101" s="101"/>
       <c r="H101" s="11"/>
     </row>
     <row r="102" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B102" s="35"/>
+      <c r="B102" s="32"/>
       <c r="C102" s="29"/>
-      <c r="D102" s="72"/>
-      <c r="E102" s="72"/>
-      <c r="F102" s="72"/>
-      <c r="G102" s="3"/>
+      <c r="D102" s="64"/>
+      <c r="E102" s="64"/>
+      <c r="F102" s="64"/>
+      <c r="G102" s="101"/>
       <c r="H102" s="11"/>
     </row>
     <row r="103" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B103" s="46"/>
+      <c r="B103" s="40"/>
       <c r="C103" s="30"/>
-      <c r="D103" s="64"/>
-      <c r="E103" s="64"/>
-      <c r="F103" s="64"/>
-      <c r="G103" s="4"/>
+      <c r="D103" s="56"/>
+      <c r="E103" s="56"/>
+      <c r="F103" s="56"/>
+      <c r="G103" s="55"/>
       <c r="H103" s="9"/>
     </row>
     <row r="104" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B104" s="71"/>
-      <c r="C104" s="71"/>
+      <c r="B104" s="63"/>
+      <c r="C104" s="63"/>
+      <c r="G104" s="90" t="s">
+        <v>293</v>
+      </c>
+      <c r="H104" s="47">
+        <f>AVERAGE(H7:H103)</f>
+        <v>5</v>
+      </c>
     </row>
     <row r="105" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B105" s="71"/>
-      <c r="C105" s="71"/>
-      <c r="G105" s="107" t="s">
-        <v>276</v>
-      </c>
-      <c r="H105" s="55">
-        <f>AVERAGE(H6:H104)</f>
-        <v>5</v>
-      </c>
+      <c r="B105" s="63"/>
+      <c r="C105" s="63"/>
     </row>
     <row r="106" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B106" s="71"/>
-      <c r="C106" s="71"/>
+      <c r="B106" s="63"/>
+      <c r="C106" s="63"/>
     </row>
     <row r="107" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B107" s="71"/>
-      <c r="C107" s="71"/>
+      <c r="B107" s="63"/>
+      <c r="C107" s="63"/>
     </row>
     <row r="108" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B108" s="71"/>
-      <c r="C108" s="71"/>
+      <c r="B108" s="63"/>
+      <c r="C108" s="63"/>
     </row>
     <row r="109" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B109" s="71"/>
-      <c r="C109" s="71"/>
+      <c r="B109" s="63"/>
+      <c r="C109" s="63"/>
     </row>
     <row r="110" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B110" s="71"/>
-      <c r="C110" s="71"/>
+      <c r="B110" s="63"/>
+      <c r="C110" s="63"/>
     </row>
     <row r="111" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B111" s="71"/>
-      <c r="C111" s="71"/>
+      <c r="B111" s="63"/>
+      <c r="C111" s="63"/>
     </row>
     <row r="112" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B112" s="71"/>
-      <c r="C112" s="71"/>
+      <c r="B112" s="63"/>
+      <c r="C112" s="63"/>
     </row>
     <row r="113" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B113" s="71"/>
-      <c r="C113" s="71"/>
+      <c r="B113" s="63"/>
+      <c r="C113" s="63"/>
     </row>
     <row r="114" spans="2:3" x14ac:dyDescent="0.45">
-      <c r="B114" s="71"/>
-      <c r="C114" s="71"/>
+      <c r="B114" s="63"/>
+      <c r="C114" s="63"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4565,7 +5122,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDC0663E-105D-42EA-893B-DB8B7FE41FC2}">
-  <dimension ref="B2:H30"/>
+  <dimension ref="B2:H28"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.59765625" customWidth="1"/>
@@ -4573,430 +5130,406 @@
     <col min="3" max="3" width="51.73046875" customWidth="1"/>
     <col min="4" max="4" width="11.265625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.59765625" customWidth="1"/>
-    <col min="7" max="7" width="35.1328125" customWidth="1"/>
-    <col min="8" max="8" width="13.46484375" customWidth="1"/>
+    <col min="7" max="7" width="35.1328125" style="102" customWidth="1"/>
+    <col min="8" max="8" width="13.46484375" style="80" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="B2" s="2" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="B3" s="20" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B4" s="82" t="s">
-        <v>247</v>
-      </c>
-      <c r="C4" s="82"/>
-      <c r="D4" s="82"/>
-      <c r="E4" s="82"/>
-      <c r="F4" s="82"/>
-      <c r="G4" s="82"/>
-      <c r="H4" s="82"/>
+      <c r="B4" s="74" t="s">
+        <v>242</v>
+      </c>
+      <c r="C4" s="74"/>
+      <c r="D4" s="74"/>
+      <c r="E4" s="74"/>
+      <c r="F4" s="74"/>
+      <c r="G4" s="74"/>
+      <c r="H4" s="74"/>
     </row>
     <row r="5" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B5" s="87"/>
-      <c r="C5" s="87"/>
-      <c r="D5" s="87"/>
-      <c r="E5" s="87"/>
-      <c r="F5" s="87"/>
-      <c r="G5" s="87"/>
-      <c r="H5" s="87"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
     </row>
     <row r="6" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="B6" s="42" t="s">
-        <v>43</v>
-      </c>
-      <c r="C6" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="D6" s="44" t="s">
-        <v>55</v>
-      </c>
-      <c r="E6" s="44" t="s">
-        <v>56</v>
-      </c>
-      <c r="F6" s="44" t="s">
-        <v>45</v>
-      </c>
-      <c r="G6" s="43" t="s">
+      <c r="B6" s="37" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" s="39" t="s">
+        <v>52</v>
+      </c>
+      <c r="E6" s="39" t="s">
+        <v>53</v>
+      </c>
+      <c r="F6" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="G6" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" s="83" t="s">
         <v>27</v>
-      </c>
-      <c r="H6" s="45" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="7" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
       <c r="B7" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="C7" s="37"/>
-      <c r="D7" s="38"/>
-      <c r="E7" s="38"/>
-      <c r="F7" s="38"/>
-      <c r="G7" s="37"/>
-      <c r="H7" s="39"/>
-    </row>
-    <row r="8" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
-      <c r="B8" s="35" t="s">
+        <v>320</v>
+      </c>
+      <c r="C7" s="33"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="34"/>
+      <c r="G7" s="99"/>
+      <c r="H7" s="84"/>
+    </row>
+    <row r="8" spans="2:8" ht="51" x14ac:dyDescent="0.45">
+      <c r="B8" s="32" t="s">
+        <v>228</v>
+      </c>
+      <c r="C8" s="35" t="s">
+        <v>319</v>
+      </c>
+      <c r="D8" s="31">
+        <v>1</v>
+      </c>
+      <c r="E8" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="F8" s="31"/>
+      <c r="G8" s="35"/>
+      <c r="H8" s="85">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="B9" s="32" t="s">
+        <v>230</v>
+      </c>
+      <c r="C9" s="35" t="s">
+        <v>233</v>
+      </c>
+      <c r="D9" s="31">
+        <v>1</v>
+      </c>
+      <c r="E9" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="F9" s="31"/>
+      <c r="G9" s="35"/>
+      <c r="H9" s="85"/>
+    </row>
+    <row r="10" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="B10" s="32" t="s">
+        <v>229</v>
+      </c>
+      <c r="C10" s="35" t="s">
+        <v>233</v>
+      </c>
+      <c r="D10" s="31">
+        <v>1</v>
+      </c>
+      <c r="E10" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="F10" s="31"/>
+      <c r="G10" s="35"/>
+      <c r="H10" s="85"/>
+    </row>
+    <row r="11" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
+      <c r="B11" s="32" t="s">
+        <v>231</v>
+      </c>
+      <c r="C11" s="35" t="s">
+        <v>236</v>
+      </c>
+      <c r="D11" s="31">
+        <v>1</v>
+      </c>
+      <c r="E11" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="F11" s="31"/>
+      <c r="G11" s="35"/>
+      <c r="H11" s="85"/>
+    </row>
+    <row r="12" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
+      <c r="B12" s="43" t="s">
+        <v>216</v>
+      </c>
+      <c r="C12" s="35" t="s">
+        <v>234</v>
+      </c>
+      <c r="D12" s="31">
+        <v>1</v>
+      </c>
+      <c r="E12" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="F12" s="45"/>
+      <c r="G12" s="44"/>
+      <c r="H12" s="86"/>
+    </row>
+    <row r="13" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="B13" s="43" t="s">
+        <v>232</v>
+      </c>
+      <c r="C13" s="35" t="s">
+        <v>235</v>
+      </c>
+      <c r="D13" s="31">
+        <v>1</v>
+      </c>
+      <c r="E13" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="F13" s="45"/>
+      <c r="G13" s="44"/>
+      <c r="H13" s="86"/>
+    </row>
+    <row r="14" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="B14" s="32" t="s">
+        <v>211</v>
+      </c>
+      <c r="C14" s="35" t="s">
         <v>215</v>
       </c>
-      <c r="C8" s="40" t="s">
-        <v>216</v>
-      </c>
-      <c r="D8" s="34">
+      <c r="D14" s="31">
         <v>1</v>
       </c>
-      <c r="E8" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="F8" s="34"/>
-      <c r="G8" s="29"/>
-      <c r="H8" s="36"/>
-    </row>
-    <row r="9" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="B9" s="35"/>
-      <c r="C9" s="40"/>
-      <c r="D9" s="34"/>
-      <c r="E9" s="34"/>
-      <c r="F9" s="34"/>
-      <c r="G9" s="29"/>
-      <c r="H9" s="36"/>
-    </row>
-    <row r="10" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="B10" s="6" t="s">
+      <c r="E14" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="F14" s="31"/>
+      <c r="G14" s="35"/>
+      <c r="H14" s="85"/>
+    </row>
+    <row r="15" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="B15" s="32" t="s">
+        <v>212</v>
+      </c>
+      <c r="C15" s="35" t="s">
+        <v>215</v>
+      </c>
+      <c r="D15" s="31">
+        <v>1</v>
+      </c>
+      <c r="E15" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="F15" s="31"/>
+      <c r="G15" s="35"/>
+      <c r="H15" s="85"/>
+    </row>
+    <row r="16" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="B16" s="43" t="s">
+        <v>213</v>
+      </c>
+      <c r="C16" s="35" t="s">
+        <v>215</v>
+      </c>
+      <c r="D16" s="31">
+        <v>1</v>
+      </c>
+      <c r="E16" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="F16" s="45"/>
+      <c r="G16" s="44"/>
+      <c r="H16" s="86"/>
+    </row>
+    <row r="17" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="B17" s="43" t="s">
+        <v>281</v>
+      </c>
+      <c r="C17" s="35" t="s">
+        <v>215</v>
+      </c>
+      <c r="D17" s="31">
+        <v>1</v>
+      </c>
+      <c r="E17" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="F17" s="45"/>
+      <c r="G17" s="44"/>
+      <c r="H17" s="86"/>
+    </row>
+    <row r="18" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="B18" s="43" t="s">
+        <v>214</v>
+      </c>
+      <c r="C18" s="35" t="s">
+        <v>215</v>
+      </c>
+      <c r="D18" s="31">
+        <v>1</v>
+      </c>
+      <c r="E18" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="F18" s="45"/>
+      <c r="G18" s="44"/>
+      <c r="H18" s="86"/>
+    </row>
+    <row r="19" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="B19" s="43" t="s">
+        <v>226</v>
+      </c>
+      <c r="C19" s="35" t="s">
+        <v>215</v>
+      </c>
+      <c r="D19" s="45">
+        <v>1</v>
+      </c>
+      <c r="E19" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="F19" s="45"/>
+      <c r="G19" s="44"/>
+      <c r="H19" s="86"/>
+    </row>
+    <row r="20" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="B20" s="43" t="s">
+        <v>227</v>
+      </c>
+      <c r="C20" s="35" t="s">
+        <v>215</v>
+      </c>
+      <c r="D20" s="45">
+        <v>1</v>
+      </c>
+      <c r="E20" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="F20" s="45"/>
+      <c r="G20" s="44"/>
+      <c r="H20" s="86"/>
+    </row>
+    <row r="21" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="B21" s="43"/>
+      <c r="C21" s="44"/>
+      <c r="D21" s="45"/>
+      <c r="E21" s="45"/>
+      <c r="F21" s="45"/>
+      <c r="G21" s="44"/>
+      <c r="H21" s="86"/>
+    </row>
+    <row r="22" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="B22" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="C22" s="33"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="34"/>
+      <c r="G22" s="99"/>
+      <c r="H22" s="84"/>
+    </row>
+    <row r="23" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
+      <c r="B23" s="32" t="s">
+        <v>217</v>
+      </c>
+      <c r="C23" s="35" t="s">
+        <v>221</v>
+      </c>
+      <c r="D23" s="46">
+        <f>'2.ArquitectonicaEstructural'!D31-'2.ArquitectonicaEstructural'!D37-'2.ArquitectonicaEstructural'!D43</f>
+        <v>1135.04</v>
+      </c>
+      <c r="E23" s="31" t="s">
+        <v>58</v>
+      </c>
+      <c r="F23" s="31"/>
+      <c r="G23" s="35"/>
+      <c r="H23" s="85">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="24" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="B24" s="32" t="s">
+        <v>220</v>
+      </c>
+      <c r="C24" s="35" t="s">
+        <v>223</v>
+      </c>
+      <c r="D24" s="36">
+        <v>992</v>
+      </c>
+      <c r="E24" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="F24" s="31"/>
+      <c r="G24" s="35"/>
+      <c r="H24" s="85"/>
+    </row>
+    <row r="25" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="B25" s="32" t="s">
+        <v>219</v>
+      </c>
+      <c r="C25" s="35" t="s">
         <v>224</v>
       </c>
-      <c r="C10" s="37"/>
-      <c r="D10" s="38"/>
-      <c r="E10" s="38"/>
-      <c r="F10" s="38"/>
-      <c r="G10" s="37"/>
-      <c r="H10" s="39"/>
-    </row>
-    <row r="11" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
-      <c r="B11" s="35" t="s">
-        <v>235</v>
-      </c>
-      <c r="C11" s="40" t="s">
-        <v>243</v>
-      </c>
-      <c r="D11" s="34">
-        <v>1</v>
-      </c>
-      <c r="E11" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="F11" s="34"/>
-      <c r="G11" s="29"/>
-      <c r="H11" s="36"/>
-    </row>
-    <row r="12" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="B12" s="35" t="s">
-        <v>237</v>
-      </c>
-      <c r="C12" s="40" t="s">
-        <v>240</v>
-      </c>
-      <c r="D12" s="34">
-        <v>1</v>
-      </c>
-      <c r="E12" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="F12" s="34"/>
-      <c r="G12" s="29"/>
-      <c r="H12" s="36"/>
-    </row>
-    <row r="13" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="B13" s="35" t="s">
-        <v>236</v>
-      </c>
-      <c r="C13" s="40" t="s">
-        <v>240</v>
-      </c>
-      <c r="D13" s="34">
-        <v>1</v>
-      </c>
-      <c r="E13" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="F13" s="34"/>
-      <c r="G13" s="29"/>
-      <c r="H13" s="36"/>
-    </row>
-    <row r="14" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
-      <c r="B14" s="35" t="s">
-        <v>238</v>
-      </c>
-      <c r="C14" s="40" t="s">
-        <v>244</v>
-      </c>
-      <c r="D14" s="34">
-        <v>1</v>
-      </c>
-      <c r="E14" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="F14" s="34"/>
-      <c r="G14" s="29"/>
-      <c r="H14" s="36"/>
-    </row>
-    <row r="15" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
-      <c r="B15" s="50" t="s">
+      <c r="D25" s="36">
+        <v>1950</v>
+      </c>
+      <c r="E25" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="F25" s="31"/>
+      <c r="G25" s="35"/>
+      <c r="H25" s="85"/>
+    </row>
+    <row r="26" spans="2:8" ht="51" x14ac:dyDescent="0.45">
+      <c r="B26" s="32" t="s">
         <v>222</v>
       </c>
-      <c r="C15" s="40" t="s">
-        <v>241</v>
-      </c>
-      <c r="D15" s="34">
-        <v>1</v>
-      </c>
-      <c r="E15" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="F15" s="52"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="53"/>
-    </row>
-    <row r="16" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="B16" s="50" t="s">
-        <v>239</v>
-      </c>
-      <c r="C16" s="40" t="s">
-        <v>242</v>
-      </c>
-      <c r="D16" s="34">
-        <v>1</v>
-      </c>
-      <c r="E16" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="F16" s="52"/>
-      <c r="G16" s="31"/>
-      <c r="H16" s="53"/>
-    </row>
-    <row r="17" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="B17" s="35" t="s">
-        <v>217</v>
-      </c>
-      <c r="C17" s="40" t="s">
-        <v>221</v>
-      </c>
-      <c r="D17" s="34">
-        <v>1</v>
-      </c>
-      <c r="E17" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="F17" s="34"/>
-      <c r="G17" s="29"/>
-      <c r="H17" s="36"/>
-    </row>
-    <row r="18" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="B18" s="35" t="s">
-        <v>218</v>
-      </c>
-      <c r="C18" s="40" t="s">
-        <v>221</v>
-      </c>
-      <c r="D18" s="34">
-        <v>1</v>
-      </c>
-      <c r="E18" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="F18" s="34"/>
-      <c r="G18" s="29"/>
-      <c r="H18" s="36"/>
-    </row>
-    <row r="19" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="B19" s="50" t="s">
-        <v>219</v>
-      </c>
-      <c r="C19" s="40" t="s">
-        <v>221</v>
-      </c>
-      <c r="D19" s="34">
-        <v>1</v>
-      </c>
-      <c r="E19" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="F19" s="52"/>
-      <c r="G19" s="31"/>
-      <c r="H19" s="53"/>
-    </row>
-    <row r="20" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="B20" s="50" t="s">
-        <v>261</v>
-      </c>
-      <c r="C20" s="40" t="s">
-        <v>221</v>
-      </c>
-      <c r="D20" s="34">
-        <v>1</v>
-      </c>
-      <c r="E20" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="F20" s="52"/>
-      <c r="G20" s="31"/>
-      <c r="H20" s="53"/>
-    </row>
-    <row r="21" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="B21" s="50" t="s">
-        <v>220</v>
-      </c>
-      <c r="C21" s="40" t="s">
-        <v>221</v>
-      </c>
-      <c r="D21" s="34">
-        <v>1</v>
-      </c>
-      <c r="E21" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="F21" s="52"/>
-      <c r="G21" s="31"/>
-      <c r="H21" s="53"/>
-    </row>
-    <row r="22" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="B22" s="50" t="s">
-        <v>233</v>
-      </c>
-      <c r="C22" s="40" t="s">
-        <v>221</v>
-      </c>
-      <c r="D22" s="52">
-        <v>1</v>
-      </c>
-      <c r="E22" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="F22" s="52"/>
-      <c r="G22" s="31"/>
-      <c r="H22" s="53"/>
-    </row>
-    <row r="23" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="B23" s="50" t="s">
-        <v>234</v>
-      </c>
-      <c r="C23" s="40" t="s">
-        <v>221</v>
-      </c>
-      <c r="D23" s="52">
-        <v>1</v>
-      </c>
-      <c r="E23" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="F23" s="52"/>
-      <c r="G23" s="31"/>
-      <c r="H23" s="53"/>
-    </row>
-    <row r="24" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="B24" s="50"/>
-      <c r="C24" s="51"/>
-      <c r="D24" s="52"/>
-      <c r="E24" s="52"/>
-      <c r="F24" s="52"/>
-      <c r="G24" s="31"/>
-      <c r="H24" s="53"/>
-    </row>
-    <row r="25" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="B25" s="6" t="s">
-        <v>245</v>
-      </c>
-      <c r="C25" s="37"/>
-      <c r="D25" s="38"/>
-      <c r="E25" s="38"/>
-      <c r="F25" s="38"/>
-      <c r="G25" s="37"/>
-      <c r="H25" s="39"/>
-    </row>
-    <row r="26" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
-      <c r="B26" s="35" t="s">
-        <v>223</v>
-      </c>
-      <c r="C26" s="40" t="s">
-        <v>228</v>
-      </c>
-      <c r="D26" s="54">
-        <f>'2.Arquitectónica'!D31-'2.Arquitectónica'!D37-'2.Arquitectónica'!D43</f>
-        <v>1135.04</v>
-      </c>
-      <c r="E26" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="F26" s="34"/>
-      <c r="G26" s="29"/>
-      <c r="H26" s="36"/>
+      <c r="C26" s="35" t="s">
+        <v>225</v>
+      </c>
+      <c r="D26" s="31">
+        <f>INT(D23/(D24/1000*D25/1000))</f>
+        <v>586</v>
+      </c>
+      <c r="E26" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="F26" s="31"/>
+      <c r="G26" s="35"/>
+      <c r="H26" s="85"/>
     </row>
     <row r="27" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="B27" s="35" t="s">
-        <v>227</v>
-      </c>
-      <c r="C27" s="40" t="s">
-        <v>230</v>
-      </c>
-      <c r="D27" s="41">
-        <v>992</v>
-      </c>
-      <c r="E27" s="34" t="s">
-        <v>71</v>
-      </c>
-      <c r="F27" s="34"/>
-      <c r="G27" s="29"/>
-      <c r="H27" s="36"/>
-    </row>
-    <row r="28" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="B28" s="35" t="s">
-        <v>226</v>
-      </c>
-      <c r="C28" s="40" t="s">
-        <v>231</v>
-      </c>
-      <c r="D28" s="41">
-        <v>1950</v>
-      </c>
-      <c r="E28" s="34" t="s">
-        <v>71</v>
-      </c>
-      <c r="F28" s="34"/>
-      <c r="G28" s="29"/>
-      <c r="H28" s="36"/>
-    </row>
-    <row r="29" spans="2:8" ht="51" x14ac:dyDescent="0.45">
-      <c r="B29" s="35" t="s">
-        <v>229</v>
-      </c>
-      <c r="C29" s="40" t="s">
-        <v>232</v>
-      </c>
-      <c r="D29" s="34">
-        <f>INT(D26/(D27/1000*D28/1000))</f>
-        <v>586</v>
-      </c>
-      <c r="E29" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="F29" s="34"/>
-      <c r="G29" s="29"/>
-      <c r="H29" s="36"/>
-    </row>
-    <row r="30" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="B30" s="46"/>
-      <c r="C30" s="47"/>
-      <c r="D30" s="48"/>
-      <c r="E30" s="48"/>
-      <c r="F30" s="48"/>
-      <c r="G30" s="30"/>
-      <c r="H30" s="49"/>
+      <c r="B27" s="40"/>
+      <c r="C27" s="41"/>
+      <c r="D27" s="42"/>
+      <c r="E27" s="42"/>
+      <c r="F27" s="42"/>
+      <c r="G27" s="41"/>
+      <c r="H27" s="87"/>
+    </row>
+    <row r="28" spans="2:8" ht="16.5" x14ac:dyDescent="0.6">
+      <c r="G28" s="90" t="s">
+        <v>293</v>
+      </c>
+      <c r="H28" s="103">
+        <f>AVERAGE(H7:H27)</f>
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5008,233 +5541,342 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36B29233-B656-46A0-B3DE-6C1E8F28F7E1}">
-  <dimension ref="B2:H16"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61FBD0B4-938E-4D04-BE03-979DB3A57126}">
+  <dimension ref="B2:H24"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.6"/>
   <cols>
-    <col min="1" max="1" width="2.59765625" customWidth="1"/>
-    <col min="2" max="2" width="36.3984375" customWidth="1"/>
-    <col min="3" max="3" width="51.73046875" customWidth="1"/>
-    <col min="4" max="4" width="11.265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.59765625" customWidth="1"/>
-    <col min="7" max="7" width="35.1328125" customWidth="1"/>
-    <col min="8" max="8" width="13.46484375" customWidth="1"/>
+    <col min="1" max="1" width="2.59765625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="29.1328125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="51.73046875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.06640625" style="1"/>
+    <col min="6" max="6" width="11.59765625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.1328125" style="22" customWidth="1"/>
+    <col min="8" max="8" width="13.46484375" style="103" customWidth="1"/>
+    <col min="9" max="16384" width="9.06640625" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.6">
       <c r="B2" s="2" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="3" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.6">
       <c r="B3" s="20" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.6">
+      <c r="B4" s="74" t="s">
+        <v>238</v>
+      </c>
+      <c r="C4" s="74"/>
+      <c r="D4" s="74"/>
+      <c r="E4" s="74"/>
+      <c r="F4" s="74"/>
+      <c r="G4" s="74"/>
+      <c r="H4" s="74"/>
+    </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.6">
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.6">
+      <c r="B6" s="37" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" s="39" t="s">
+        <v>52</v>
+      </c>
+      <c r="E6" s="39" t="s">
+        <v>53</v>
+      </c>
+      <c r="F6" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="G6" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" s="83" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.6">
+      <c r="B7" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="C7" s="33"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="34"/>
+      <c r="G7" s="99"/>
+      <c r="H7" s="84"/>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.6">
+      <c r="B8" s="32" t="s">
+        <v>243</v>
+      </c>
+      <c r="C8" s="35" t="s">
+        <v>250</v>
+      </c>
+      <c r="D8" s="36">
+        <v>3</v>
+      </c>
+      <c r="E8" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="F8" s="31"/>
+      <c r="G8" s="35"/>
+      <c r="H8" s="85">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" ht="25.5" x14ac:dyDescent="0.6">
+      <c r="B9" s="32" t="s">
+        <v>248</v>
+      </c>
+      <c r="C9" s="35" t="s">
+        <v>251</v>
+      </c>
+      <c r="D9" s="36">
+        <v>2.5</v>
+      </c>
+      <c r="E9" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="F9" s="31"/>
+      <c r="G9" s="35"/>
+      <c r="H9" s="85"/>
+    </row>
+    <row r="10" spans="2:8" ht="25.5" x14ac:dyDescent="0.6">
+      <c r="B10" s="32" t="s">
+        <v>246</v>
+      </c>
+      <c r="C10" s="35" t="s">
+        <v>257</v>
+      </c>
+      <c r="D10" s="36">
+        <v>4</v>
+      </c>
+      <c r="E10" s="31" t="s">
+        <v>247</v>
+      </c>
+      <c r="F10" s="31"/>
+      <c r="G10" s="35"/>
+      <c r="H10" s="85"/>
+    </row>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.6">
+      <c r="B11" s="32" t="s">
         <v>249</v>
       </c>
-    </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B4" s="82" t="s">
+      <c r="C11" s="35" t="s">
+        <v>252</v>
+      </c>
+      <c r="D11" s="36">
+        <v>2</v>
+      </c>
+      <c r="E11" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="F11" s="31"/>
+      <c r="G11" s="35"/>
+      <c r="H11" s="85"/>
+    </row>
+    <row r="12" spans="2:8" ht="33" x14ac:dyDescent="0.6">
+      <c r="B12" s="32" t="s">
+        <v>254</v>
+      </c>
+      <c r="C12" s="35" t="s">
+        <v>258</v>
+      </c>
+      <c r="D12" s="31">
+        <f>D10*D11</f>
+        <v>8</v>
+      </c>
+      <c r="E12" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="F12" s="31"/>
+      <c r="G12" s="35"/>
+      <c r="H12" s="85"/>
+    </row>
+    <row r="13" spans="2:8" ht="25.5" x14ac:dyDescent="0.6">
+      <c r="B13" s="32" t="s">
+        <v>245</v>
+      </c>
+      <c r="C13" s="35" t="s">
+        <v>253</v>
+      </c>
+      <c r="D13" s="36">
+        <v>8</v>
+      </c>
+      <c r="E13" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="F13" s="31"/>
+      <c r="G13" s="35"/>
+      <c r="H13" s="85"/>
+    </row>
+    <row r="14" spans="2:8" x14ac:dyDescent="0.6">
+      <c r="B14" s="32" t="s">
+        <v>259</v>
+      </c>
+      <c r="C14" s="35" t="s">
+        <v>261</v>
+      </c>
+      <c r="D14" s="31" t="str">
+        <f>IF(D12&lt;=D13, "Cumple","No cumple")</f>
+        <v>Cumple</v>
+      </c>
+      <c r="E14" s="31" t="s">
+        <v>260</v>
+      </c>
+      <c r="F14" s="31"/>
+      <c r="G14" s="35"/>
+      <c r="H14" s="85"/>
+    </row>
+    <row r="15" spans="2:8" ht="33" x14ac:dyDescent="0.6">
+      <c r="B15" s="32" t="s">
+        <v>262</v>
+      </c>
+      <c r="C15" s="35" t="s">
+        <v>263</v>
+      </c>
+      <c r="D15" s="36">
+        <v>60</v>
+      </c>
+      <c r="E15" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="F15" s="31"/>
+      <c r="G15" s="35"/>
+      <c r="H15" s="85"/>
+    </row>
+    <row r="16" spans="2:8" ht="33" x14ac:dyDescent="0.6">
+      <c r="B16" s="32" t="s">
+        <v>264</v>
+      </c>
+      <c r="C16" s="35" t="s">
+        <v>265</v>
+      </c>
+      <c r="D16" s="31">
+        <f>D15*D10</f>
+        <v>240</v>
+      </c>
+      <c r="E16" s="31" t="s">
+        <v>57</v>
+      </c>
+      <c r="F16" s="31"/>
+      <c r="G16" s="35"/>
+      <c r="H16" s="85"/>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.6">
+      <c r="B17" s="32"/>
+      <c r="C17" s="35"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="31"/>
+      <c r="F17" s="31"/>
+      <c r="G17" s="35"/>
+      <c r="H17" s="85"/>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.6">
+      <c r="B18" s="32"/>
+      <c r="C18" s="35"/>
+      <c r="D18" s="31"/>
+      <c r="E18" s="31"/>
+      <c r="F18" s="31"/>
+      <c r="G18" s="35"/>
+      <c r="H18" s="85"/>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.6">
+      <c r="B19" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="C19" s="33"/>
+      <c r="D19" s="34"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="34"/>
+      <c r="G19" s="99"/>
+      <c r="H19" s="84"/>
+    </row>
+    <row r="20" spans="2:8" ht="38.25" x14ac:dyDescent="0.6">
+      <c r="B20" s="32" t="s">
+        <v>266</v>
+      </c>
+      <c r="C20" s="35" t="s">
         <v>255</v>
       </c>
-      <c r="C4" s="82"/>
-      <c r="D4" s="82"/>
-      <c r="E4" s="82"/>
-      <c r="F4" s="82"/>
-      <c r="G4" s="82"/>
-      <c r="H4" s="82"/>
-    </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B5" s="87"/>
-      <c r="C5" s="87"/>
-      <c r="D5" s="87"/>
-      <c r="E5" s="87"/>
-      <c r="F5" s="87"/>
-      <c r="G5" s="87"/>
-      <c r="H5" s="87"/>
-    </row>
-    <row r="6" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="B6" s="42" t="s">
-        <v>43</v>
-      </c>
-      <c r="C6" s="43" t="s">
-        <v>44</v>
-      </c>
-      <c r="D6" s="44" t="s">
-        <v>55</v>
-      </c>
-      <c r="E6" s="44" t="s">
-        <v>56</v>
-      </c>
-      <c r="F6" s="44" t="s">
-        <v>45</v>
-      </c>
-      <c r="G6" s="43" t="s">
-        <v>27</v>
-      </c>
-      <c r="H6" s="45" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
-      <c r="B7" s="35" t="s">
-        <v>250</v>
-      </c>
-      <c r="C7" s="40" t="s">
-        <v>251</v>
-      </c>
-      <c r="D7" s="41">
-        <v>1</v>
-      </c>
-      <c r="E7" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="F7" s="34"/>
-      <c r="G7" s="29"/>
-      <c r="H7" s="36"/>
-    </row>
-    <row r="8" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
-      <c r="B8" s="35" t="s">
-        <v>252</v>
-      </c>
-      <c r="C8" s="40" t="s">
-        <v>262</v>
-      </c>
-      <c r="D8" s="41">
-        <v>1</v>
-      </c>
-      <c r="E8" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="F8" s="34"/>
-      <c r="G8" s="29"/>
-      <c r="H8" s="36"/>
-    </row>
-    <row r="9" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
-      <c r="B9" s="35" t="s">
-        <v>253</v>
-      </c>
-      <c r="C9" s="40" t="s">
-        <v>263</v>
-      </c>
-      <c r="D9" s="41">
-        <v>1</v>
-      </c>
-      <c r="E9" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="F9" s="34"/>
-      <c r="G9" s="29"/>
-      <c r="H9" s="36"/>
-    </row>
-    <row r="10" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
-      <c r="B10" s="35" t="s">
-        <v>254</v>
-      </c>
-      <c r="C10" s="40" t="s">
-        <v>264</v>
-      </c>
-      <c r="D10" s="41">
-        <v>1</v>
-      </c>
-      <c r="E10" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="F10" s="34"/>
-      <c r="G10" s="29"/>
-      <c r="H10" s="36"/>
-    </row>
-    <row r="11" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="B11" s="35" t="s">
+      <c r="D20" s="36" t="s">
         <v>256</v>
       </c>
-      <c r="C11" s="40" t="s">
-        <v>240</v>
-      </c>
-      <c r="D11" s="41">
-        <v>1</v>
-      </c>
-      <c r="E11" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="F11" s="34"/>
-      <c r="G11" s="29"/>
-      <c r="H11" s="36"/>
-    </row>
-    <row r="12" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="B12" s="35" t="s">
-        <v>257</v>
-      </c>
-      <c r="C12" s="40" t="s">
-        <v>240</v>
-      </c>
-      <c r="D12" s="41">
-        <v>1</v>
-      </c>
-      <c r="E12" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="F12" s="34"/>
-      <c r="G12" s="29"/>
-      <c r="H12" s="36"/>
-    </row>
-    <row r="13" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
-      <c r="B13" s="35" t="s">
-        <v>258</v>
-      </c>
-      <c r="C13" s="40" t="s">
-        <v>244</v>
-      </c>
-      <c r="D13" s="41">
-        <v>1</v>
-      </c>
-      <c r="E13" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="F13" s="34"/>
-      <c r="G13" s="29"/>
-      <c r="H13" s="36"/>
-    </row>
-    <row r="14" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
-      <c r="B14" s="35" t="s">
-        <v>259</v>
-      </c>
-      <c r="C14" s="40" t="s">
-        <v>241</v>
-      </c>
-      <c r="D14" s="41">
-        <v>1</v>
-      </c>
-      <c r="E14" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="F14" s="34"/>
-      <c r="G14" s="29"/>
-      <c r="H14" s="36"/>
-    </row>
-    <row r="15" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="B15" s="35" t="s">
-        <v>260</v>
-      </c>
-      <c r="C15" s="40" t="s">
-        <v>242</v>
-      </c>
-      <c r="D15" s="41">
-        <v>1</v>
-      </c>
-      <c r="E15" s="34" t="s">
-        <v>130</v>
-      </c>
-      <c r="F15" s="34"/>
-      <c r="G15" s="29"/>
-      <c r="H15" s="36"/>
-    </row>
-    <row r="16" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
-      <c r="B16" s="46"/>
-      <c r="C16" s="47"/>
-      <c r="D16" s="90"/>
-      <c r="E16" s="48"/>
-      <c r="F16" s="48"/>
-      <c r="G16" s="30"/>
-      <c r="H16" s="49"/>
+      <c r="E20" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="F20" s="31"/>
+      <c r="G20" s="35"/>
+      <c r="H20" s="85">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="2:8" ht="38.25" x14ac:dyDescent="0.6">
+      <c r="B21" s="32" t="s">
+        <v>267</v>
+      </c>
+      <c r="C21" s="35" t="s">
+        <v>255</v>
+      </c>
+      <c r="D21" s="36" t="s">
+        <v>256</v>
+      </c>
+      <c r="E21" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="F21" s="31"/>
+      <c r="G21" s="35"/>
+      <c r="H21" s="85"/>
+    </row>
+    <row r="22" spans="2:8" ht="38.25" x14ac:dyDescent="0.6">
+      <c r="B22" s="32" t="s">
+        <v>268</v>
+      </c>
+      <c r="C22" s="35" t="s">
+        <v>255</v>
+      </c>
+      <c r="D22" s="36" t="s">
+        <v>256</v>
+      </c>
+      <c r="E22" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="F22" s="31"/>
+      <c r="G22" s="35"/>
+      <c r="H22" s="85"/>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.6">
+      <c r="B23" s="40"/>
+      <c r="C23" s="41"/>
+      <c r="D23" s="42"/>
+      <c r="E23" s="42"/>
+      <c r="F23" s="42"/>
+      <c r="G23" s="41"/>
+      <c r="H23" s="87"/>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.6">
+      <c r="G24" s="90" t="s">
+        <v>293</v>
+      </c>
+      <c r="H24" s="103">
+        <f>AVERAGE(H7:H23)</f>
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5246,279 +5888,488 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36B29233-B656-46A0-B3DE-6C1E8F28F7E1}">
+  <dimension ref="B2:H17"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.6"/>
+  <cols>
+    <col min="1" max="1" width="2.59765625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="36.3984375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="51.73046875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.265625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.06640625" style="1"/>
+    <col min="6" max="6" width="11.59765625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.1328125" style="22" customWidth="1"/>
+    <col min="8" max="8" width="13.46484375" style="103" customWidth="1"/>
+    <col min="9" max="16384" width="9.06640625" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:8" x14ac:dyDescent="0.6">
+      <c r="B2" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.6">
+      <c r="B3" s="20" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" x14ac:dyDescent="0.6">
+      <c r="B4" s="74" t="s">
+        <v>275</v>
+      </c>
+      <c r="C4" s="74"/>
+      <c r="D4" s="74"/>
+      <c r="E4" s="74"/>
+      <c r="F4" s="74"/>
+      <c r="G4" s="74"/>
+      <c r="H4" s="74"/>
+    </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.6">
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.6">
+      <c r="B6" s="37" t="s">
+        <v>40</v>
+      </c>
+      <c r="C6" s="38" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" s="39" t="s">
+        <v>52</v>
+      </c>
+      <c r="E6" s="39" t="s">
+        <v>53</v>
+      </c>
+      <c r="F6" s="39" t="s">
+        <v>42</v>
+      </c>
+      <c r="G6" s="38" t="s">
+        <v>26</v>
+      </c>
+      <c r="H6" s="83" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" ht="25.5" x14ac:dyDescent="0.6">
+      <c r="B7" s="32" t="s">
+        <v>270</v>
+      </c>
+      <c r="C7" s="35" t="s">
+        <v>271</v>
+      </c>
+      <c r="D7" s="36">
+        <v>1</v>
+      </c>
+      <c r="E7" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="F7" s="31"/>
+      <c r="G7" s="35"/>
+      <c r="H7" s="85">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" ht="25.5" x14ac:dyDescent="0.6">
+      <c r="B8" s="32" t="s">
+        <v>272</v>
+      </c>
+      <c r="C8" s="35" t="s">
+        <v>282</v>
+      </c>
+      <c r="D8" s="36">
+        <v>1</v>
+      </c>
+      <c r="E8" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="F8" s="31"/>
+      <c r="G8" s="35"/>
+      <c r="H8" s="85"/>
+    </row>
+    <row r="9" spans="2:8" ht="25.5" x14ac:dyDescent="0.6">
+      <c r="B9" s="32" t="s">
+        <v>273</v>
+      </c>
+      <c r="C9" s="35" t="s">
+        <v>283</v>
+      </c>
+      <c r="D9" s="36">
+        <v>1</v>
+      </c>
+      <c r="E9" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="F9" s="31"/>
+      <c r="G9" s="35"/>
+      <c r="H9" s="85"/>
+    </row>
+    <row r="10" spans="2:8" ht="25.5" x14ac:dyDescent="0.6">
+      <c r="B10" s="32" t="s">
+        <v>274</v>
+      </c>
+      <c r="C10" s="35" t="s">
+        <v>284</v>
+      </c>
+      <c r="D10" s="36">
+        <v>1</v>
+      </c>
+      <c r="E10" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="F10" s="31"/>
+      <c r="G10" s="35"/>
+      <c r="H10" s="85"/>
+    </row>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.6">
+      <c r="B11" s="32" t="s">
+        <v>276</v>
+      </c>
+      <c r="C11" s="35" t="s">
+        <v>233</v>
+      </c>
+      <c r="D11" s="36">
+        <v>1</v>
+      </c>
+      <c r="E11" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="F11" s="31"/>
+      <c r="G11" s="35"/>
+      <c r="H11" s="85"/>
+    </row>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.6">
+      <c r="B12" s="32" t="s">
+        <v>277</v>
+      </c>
+      <c r="C12" s="35" t="s">
+        <v>233</v>
+      </c>
+      <c r="D12" s="36">
+        <v>1</v>
+      </c>
+      <c r="E12" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="F12" s="31"/>
+      <c r="G12" s="35"/>
+      <c r="H12" s="85"/>
+    </row>
+    <row r="13" spans="2:8" ht="25.5" x14ac:dyDescent="0.6">
+      <c r="B13" s="32" t="s">
+        <v>278</v>
+      </c>
+      <c r="C13" s="35" t="s">
+        <v>236</v>
+      </c>
+      <c r="D13" s="36">
+        <v>1</v>
+      </c>
+      <c r="E13" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="F13" s="31"/>
+      <c r="G13" s="35"/>
+      <c r="H13" s="85"/>
+    </row>
+    <row r="14" spans="2:8" ht="25.5" x14ac:dyDescent="0.6">
+      <c r="B14" s="32" t="s">
+        <v>279</v>
+      </c>
+      <c r="C14" s="35" t="s">
+        <v>234</v>
+      </c>
+      <c r="D14" s="36">
+        <v>1</v>
+      </c>
+      <c r="E14" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="F14" s="31"/>
+      <c r="G14" s="35"/>
+      <c r="H14" s="85"/>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.6">
+      <c r="B15" s="32" t="s">
+        <v>280</v>
+      </c>
+      <c r="C15" s="35" t="s">
+        <v>235</v>
+      </c>
+      <c r="D15" s="36">
+        <v>1</v>
+      </c>
+      <c r="E15" s="31" t="s">
+        <v>126</v>
+      </c>
+      <c r="F15" s="31"/>
+      <c r="G15" s="35"/>
+      <c r="H15" s="85"/>
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.6">
+      <c r="B16" s="40"/>
+      <c r="C16" s="41"/>
+      <c r="D16" s="81"/>
+      <c r="E16" s="42"/>
+      <c r="F16" s="42"/>
+      <c r="G16" s="41"/>
+      <c r="H16" s="87"/>
+    </row>
+    <row r="17" spans="7:8" x14ac:dyDescent="0.6">
+      <c r="G17" s="90" t="s">
+        <v>293</v>
+      </c>
+      <c r="H17" s="103">
+        <f>AVERAGE(H7:H16)</f>
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B4:H5"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:F26"/>
+  <dimension ref="B2:G17"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="2.59765625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="46.6640625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="33.46484375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="30.3984375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="11.59765625" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.06640625" style="2"/>
+    <col min="3" max="4" width="46.6640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="33.46484375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="30.3984375" style="98" customWidth="1"/>
+    <col min="7" max="7" width="11.59765625" style="47" customWidth="1"/>
+    <col min="8" max="16384" width="9.06640625" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B2" s="83" t="s">
-        <v>23</v>
-      </c>
-      <c r="C2" s="83"/>
-      <c r="D2" s="83"/>
-      <c r="E2" s="83"/>
-      <c r="F2" s="83"/>
-    </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B3" s="83" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" s="83"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="83"/>
-    </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B2" s="75" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" s="75"/>
+      <c r="D2" s="75"/>
+      <c r="E2" s="75"/>
+      <c r="F2" s="75"/>
+      <c r="G2" s="75"/>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B3" s="115" t="s">
+        <v>332</v>
+      </c>
+      <c r="C3" s="115"/>
+      <c r="D3" s="115"/>
+      <c r="E3" s="115"/>
+      <c r="F3" s="115"/>
+      <c r="G3" s="115"/>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B5" s="17" t="s">
         <v>10</v>
       </c>
       <c r="C5" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="7" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="7" t="s">
+      <c r="F5" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="F5" s="14" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="2:6" ht="29.25" x14ac:dyDescent="0.45">
+    </row>
+    <row r="6" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B6" s="15">
         <v>0</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>39</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="13"/>
-    </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.45">
+        <v>294</v>
+      </c>
+      <c r="D6" s="35" t="s">
+        <v>295</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" s="101"/>
+      <c r="G6" s="11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B7" s="15">
         <v>1</v>
       </c>
       <c r="C7" s="29" t="s">
-        <v>20</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="13"/>
-    </row>
-    <row r="8" spans="2:6" ht="131.25" x14ac:dyDescent="0.45">
+        <v>19</v>
+      </c>
+      <c r="D7" s="35" t="s">
+        <v>326</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F7" s="101"/>
+      <c r="G7" s="11"/>
+    </row>
+    <row r="8" spans="2:7" ht="114.75" x14ac:dyDescent="0.45">
       <c r="B8" s="15">
         <v>2</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>42</v>
-      </c>
-      <c r="D8" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="D8" s="35" t="s">
+        <v>328</v>
+      </c>
+      <c r="E8" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="13"/>
-    </row>
-    <row r="9" spans="2:6" ht="42" x14ac:dyDescent="0.45">
+      <c r="F8" s="101"/>
+      <c r="G8" s="11"/>
+    </row>
+    <row r="9" spans="2:7" ht="42" x14ac:dyDescent="0.45">
       <c r="B9" s="15">
         <v>3</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E9" s="88"/>
-      <c r="F9" s="89"/>
-    </row>
-    <row r="10" spans="2:6" ht="54.75" x14ac:dyDescent="0.45">
+        <v>35</v>
+      </c>
+      <c r="D9" s="35"/>
+      <c r="E9" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F9" s="101"/>
+      <c r="G9" s="11"/>
+    </row>
+    <row r="10" spans="2:7" ht="54.75" x14ac:dyDescent="0.45">
       <c r="B10" s="15">
         <v>4</v>
       </c>
       <c r="C10" s="29" t="s">
-        <v>37</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E10" s="88"/>
-      <c r="F10" s="89"/>
-    </row>
-    <row r="11" spans="2:6" ht="29.25" x14ac:dyDescent="0.45">
+        <v>36</v>
+      </c>
+      <c r="D10" s="35"/>
+      <c r="E10" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F10" s="101"/>
+      <c r="G10" s="11"/>
+    </row>
+    <row r="11" spans="2:7" ht="29.25" x14ac:dyDescent="0.45">
       <c r="B11" s="15">
         <v>5</v>
       </c>
       <c r="C11" s="29" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="E11" s="88"/>
-      <c r="F11" s="89"/>
-    </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.45">
+        <v>37</v>
+      </c>
+      <c r="D11" s="35"/>
+      <c r="E11" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F11" s="101"/>
+      <c r="G11" s="11"/>
+    </row>
+    <row r="12" spans="2:7" ht="38.25" x14ac:dyDescent="0.45">
       <c r="B12" s="15">
         <v>6</v>
       </c>
-      <c r="C12" s="29"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="13"/>
-    </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="C12" s="29" t="s">
+        <v>314</v>
+      </c>
+      <c r="D12" s="35" t="s">
+        <v>321</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="F12" s="101"/>
+      <c r="G12" s="11"/>
+    </row>
+    <row r="13" spans="2:7" ht="25.5" x14ac:dyDescent="0.45">
       <c r="B13" s="15">
         <v>7</v>
       </c>
-      <c r="C13" s="29"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-      <c r="F13" s="13"/>
-    </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="C13" s="29" t="s">
+        <v>323</v>
+      </c>
+      <c r="D13" s="35" t="s">
+        <v>324</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="F13" s="101"/>
+      <c r="G13" s="11"/>
+    </row>
+    <row r="14" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B14" s="15">
         <v>8</v>
       </c>
-      <c r="C14" s="29"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="13"/>
-    </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.45">
+      <c r="C14" s="29" t="s">
+        <v>329</v>
+      </c>
+      <c r="D14" s="35" t="s">
+        <v>330</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="F14" s="101"/>
+      <c r="G14" s="11"/>
+    </row>
+    <row r="15" spans="2:7" x14ac:dyDescent="0.45">
       <c r="B15" s="15">
         <v>9</v>
       </c>
       <c r="C15" s="29"/>
-      <c r="D15" s="3"/>
+      <c r="D15" s="35"/>
       <c r="E15" s="3"/>
-      <c r="F15" s="13"/>
-    </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B16" s="15">
+      <c r="F15" s="101"/>
+      <c r="G15" s="11"/>
+    </row>
+    <row r="16" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="B16" s="16">
         <v>10</v>
       </c>
-      <c r="C16" s="29"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="13"/>
-    </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B17" s="15">
-        <v>11</v>
-      </c>
-      <c r="C17" s="29"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="13"/>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B18" s="15">
-        <v>12</v>
-      </c>
-      <c r="C18" s="29"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="13"/>
-    </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B19" s="15">
-        <v>13</v>
-      </c>
-      <c r="C19" s="29"/>
-      <c r="D19" s="3"/>
-      <c r="E19" s="3"/>
-      <c r="F19" s="13"/>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B20" s="15">
-        <v>14</v>
-      </c>
-      <c r="C20" s="29"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="13"/>
-    </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B21" s="15">
-        <v>15</v>
-      </c>
-      <c r="C21" s="29"/>
-      <c r="D21" s="3"/>
-      <c r="E21" s="3"/>
-      <c r="F21" s="13"/>
-    </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B22" s="15">
-        <v>16</v>
-      </c>
-      <c r="C22" s="29"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="13"/>
-    </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B23" s="15">
-        <v>17</v>
-      </c>
-      <c r="C23" s="29"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="3"/>
-      <c r="F23" s="13"/>
-    </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B24" s="15">
-        <v>18</v>
-      </c>
-      <c r="C24" s="29"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="13"/>
-    </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B25" s="15">
-        <v>19</v>
-      </c>
-      <c r="C25" s="31"/>
-      <c r="D25" s="32"/>
-      <c r="E25" s="32"/>
-      <c r="F25" s="33"/>
-    </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B26" s="16">
-        <v>20</v>
-      </c>
-      <c r="C26" s="30"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4"/>
-      <c r="F26" s="5"/>
+      <c r="C16" s="30"/>
+      <c r="D16" s="41"/>
+      <c r="E16" s="4"/>
+      <c r="F16" s="55"/>
+      <c r="G16" s="9"/>
+    </row>
+    <row r="17" spans="6:7" x14ac:dyDescent="0.45">
+      <c r="F17" s="90" t="s">
+        <v>293</v>
+      </c>
+      <c r="G17" s="47">
+        <f>AVERAGE(G6:G16)</f>
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B2:F2"/>
-    <mergeCell ref="E10:F10"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="E9:F9"/>
+  <mergeCells count="2">
+    <mergeCell ref="B3:G3"/>
+    <mergeCell ref="B2:G2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCD4CBC5-BEDD-4E97-A57A-4EDFE72E7B14}">
   <dimension ref="B1:B4"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.6"/>
@@ -5530,22 +6381,22 @@
   <sheetData>
     <row r="1" spans="2:2" x14ac:dyDescent="0.6">
       <c r="B1" s="24" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="2:2" x14ac:dyDescent="0.6">
       <c r="B2" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="2:2" x14ac:dyDescent="0.6">
       <c r="B3" s="21" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.6">
       <c r="B4" s="22" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/file/table/DAPC_ProyectoCAD.xlsx
+++ b/file/table/DAPC_ProyectoCAD.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29121"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1CABA3C-473F-4262-9284-D51AFEBC2BA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B88C970-5BA9-4668-8AB7-16D363BCB90D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0.Inicio" sheetId="7" r:id="rId1"/>
@@ -2219,13 +2219,99 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -2252,10 +2338,25 @@
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2267,120 +2368,19 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
@@ -2698,116 +2698,116 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82EDA320-F942-4FCE-8343-60C075021E69}">
   <dimension ref="B1:H46"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="2.59765625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="50.59765625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="15.59765625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="11.53125" style="2" customWidth="1"/>
-    <col min="6" max="6" width="2.59765625" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.06640625" style="2"/>
+    <col min="1" max="2" width="2.5546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="50.5546875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="15.5546875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="11.5546875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="2.5546875" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="9.109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:5" x14ac:dyDescent="0.3">
       <c r="E1" s="24"/>
     </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B3" s="20" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B4" s="74" t="s">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B4" s="105" t="s">
         <v>39</v>
       </c>
-      <c r="C4" s="74"/>
-      <c r="D4" s="74"/>
-      <c r="E4" s="74"/>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B5" s="74"/>
-      <c r="C5" s="74"/>
-      <c r="D5" s="74"/>
-      <c r="E5" s="74"/>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B6" s="74"/>
-      <c r="C6" s="74"/>
-      <c r="D6" s="74"/>
-      <c r="E6" s="74"/>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B7" s="74"/>
-      <c r="C7" s="74"/>
-      <c r="D7" s="74"/>
-      <c r="E7" s="74"/>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B8" s="76" t="s">
+      <c r="C4" s="105"/>
+      <c r="D4" s="105"/>
+      <c r="E4" s="105"/>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B5" s="105"/>
+      <c r="C5" s="105"/>
+      <c r="D5" s="105"/>
+      <c r="E5" s="105"/>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B6" s="105"/>
+      <c r="C6" s="105"/>
+      <c r="D6" s="105"/>
+      <c r="E6" s="105"/>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B7" s="105"/>
+      <c r="C7" s="105"/>
+      <c r="D7" s="105"/>
+      <c r="E7" s="105"/>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="110" t="s">
         <v>1</v>
       </c>
-      <c r="C8" s="77"/>
-      <c r="D8" s="77"/>
-      <c r="E8" s="78"/>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B9" s="68" t="s">
+      <c r="C8" s="111"/>
+      <c r="D8" s="111"/>
+      <c r="E8" s="112"/>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B9" s="97" t="s">
         <v>12</v>
       </c>
-      <c r="C9" s="69"/>
-      <c r="D9" s="69"/>
-      <c r="E9" s="70"/>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B10" s="65" t="s">
+      <c r="C9" s="98"/>
+      <c r="D9" s="98"/>
+      <c r="E9" s="99"/>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="113" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="66"/>
-      <c r="D10" s="66"/>
-      <c r="E10" s="67"/>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B11" s="68" t="s">
+      <c r="C10" s="114"/>
+      <c r="D10" s="114"/>
+      <c r="E10" s="115"/>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B11" s="97" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="69"/>
-      <c r="D11" s="69"/>
-      <c r="E11" s="70"/>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B12" s="71"/>
-      <c r="C12" s="72"/>
-      <c r="D12" s="72"/>
-      <c r="E12" s="73"/>
-    </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B13" s="65" t="s">
+      <c r="C11" s="98"/>
+      <c r="D11" s="98"/>
+      <c r="E11" s="99"/>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B12" s="100"/>
+      <c r="C12" s="101"/>
+      <c r="D12" s="101"/>
+      <c r="E12" s="102"/>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="113" t="s">
         <v>20</v>
       </c>
-      <c r="C13" s="66"/>
-      <c r="D13" s="66"/>
-      <c r="E13" s="67"/>
-    </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B14" s="68" t="s">
+      <c r="C13" s="114"/>
+      <c r="D13" s="114"/>
+      <c r="E13" s="115"/>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B14" s="97" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="69"/>
-      <c r="D14" s="69"/>
-      <c r="E14" s="70"/>
-    </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.45">
-      <c r="B15" s="71"/>
-      <c r="C15" s="72"/>
-      <c r="D15" s="72"/>
-      <c r="E15" s="73"/>
-    </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="C14" s="98"/>
+      <c r="D14" s="98"/>
+      <c r="E14" s="99"/>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B15" s="100"/>
+      <c r="C15" s="101"/>
+      <c r="D15" s="101"/>
+      <c r="E15" s="102"/>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B16" s="23" t="s">
         <v>21</v>
       </c>
@@ -2815,21 +2815,21 @@
       <c r="D16" s="23"/>
       <c r="E16" s="23"/>
     </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B17" s="18"/>
       <c r="C17" s="18"/>
       <c r="D17" s="18"/>
       <c r="E17" s="18"/>
     </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B18" s="75" t="s">
+    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B18" s="103" t="s">
         <v>14</v>
       </c>
-      <c r="C18" s="75"/>
-      <c r="D18" s="75"/>
-      <c r="E18" s="75"/>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="C18" s="103"/>
+      <c r="D18" s="103"/>
+      <c r="E18" s="103"/>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B19" s="17" t="s">
         <v>10</v>
       </c>
@@ -2843,7 +2843,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B20" s="15">
         <v>1</v>
       </c>
@@ -2858,7 +2858,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B21" s="15">
         <v>2</v>
       </c>
@@ -2873,7 +2873,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B22" s="15">
         <v>3</v>
       </c>
@@ -2888,7 +2888,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B23" s="15">
         <v>4</v>
       </c>
@@ -2903,7 +2903,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B24" s="15">
         <v>5</v>
       </c>
@@ -2918,7 +2918,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B25" s="15">
         <v>6</v>
       </c>
@@ -2931,7 +2931,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B26" s="15">
         <v>7</v>
       </c>
@@ -2944,7 +2944,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B27" s="15">
         <v>8</v>
       </c>
@@ -2957,7 +2957,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B28" s="15">
         <v>9</v>
       </c>
@@ -2970,7 +2970,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B29" s="16">
         <v>10</v>
       </c>
@@ -2983,7 +2983,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
       <c r="D30" s="19" t="s">
         <v>11</v>
       </c>
@@ -2992,237 +2992,237 @@
         <v>27</v>
       </c>
     </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B31" s="91"/>
-      <c r="C31" s="91"/>
-      <c r="D31" s="91"/>
-      <c r="E31" s="91"/>
-      <c r="F31" s="91"/>
-      <c r="G31" s="91"/>
-      <c r="H31" s="91"/>
-    </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B32" s="92" t="s">
+    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B31" s="76"/>
+      <c r="C31" s="76"/>
+      <c r="D31" s="76"/>
+      <c r="E31" s="76"/>
+      <c r="F31" s="76"/>
+      <c r="G31" s="76"/>
+      <c r="H31" s="76"/>
+    </row>
+    <row r="32" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B32" s="104" t="s">
         <v>285</v>
       </c>
-      <c r="C32" s="92"/>
-      <c r="D32" s="92"/>
-      <c r="E32" s="92"/>
-      <c r="F32" s="91"/>
-      <c r="G32" s="91"/>
-      <c r="H32" s="91"/>
-    </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B33" s="93" t="s">
+      <c r="C32" s="104"/>
+      <c r="D32" s="104"/>
+      <c r="E32" s="104"/>
+      <c r="F32" s="76"/>
+      <c r="G32" s="76"/>
+      <c r="H32" s="76"/>
+    </row>
+    <row r="33" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B33" s="77" t="s">
         <v>10</v>
       </c>
       <c r="C33" s="106" t="s">
         <v>40</v>
       </c>
       <c r="D33" s="107"/>
-      <c r="E33" s="94" t="s">
+      <c r="E33" s="78" t="s">
         <v>27</v>
       </c>
-      <c r="F33" s="91"/>
-      <c r="G33" s="91"/>
-      <c r="H33" s="91"/>
-    </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B34" s="95">
+      <c r="F33" s="76"/>
+      <c r="G33" s="76"/>
+      <c r="H33" s="76"/>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B34" s="79">
         <v>1</v>
       </c>
-      <c r="C34" s="109" t="s">
+      <c r="C34" s="108" t="s">
         <v>286</v>
       </c>
-      <c r="D34" s="110"/>
-      <c r="E34" s="96">
+      <c r="D34" s="109"/>
+      <c r="E34" s="80">
         <f>'1.Tecnica'!H19</f>
         <v>5</v>
       </c>
-      <c r="F34" s="91"/>
-      <c r="G34" s="91"/>
-      <c r="H34" s="91"/>
-    </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B35" s="95">
+      <c r="F34" s="76"/>
+      <c r="G34" s="76"/>
+      <c r="H34" s="76"/>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B35" s="79">
         <v>2</v>
       </c>
-      <c r="C35" s="111" t="s">
+      <c r="C35" s="93" t="s">
         <v>335</v>
       </c>
-      <c r="D35" s="112"/>
-      <c r="E35" s="96">
+      <c r="D35" s="94"/>
+      <c r="E35" s="80">
         <f>'2.ArquitectonicaEstructural'!H104</f>
         <v>5</v>
       </c>
-      <c r="F35" s="91"/>
-      <c r="G35" s="91"/>
-      <c r="H35" s="91"/>
-    </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B36" s="95">
+      <c r="F35" s="76"/>
+      <c r="G35" s="76"/>
+      <c r="H35" s="76"/>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B36" s="79">
         <v>3</v>
       </c>
-      <c r="C36" s="111" t="s">
+      <c r="C36" s="93" t="s">
         <v>287</v>
       </c>
-      <c r="D36" s="112"/>
-      <c r="E36" s="96">
+      <c r="D36" s="94"/>
+      <c r="E36" s="80">
         <f>'3.Electrica'!H28</f>
         <v>5</v>
       </c>
-      <c r="F36" s="91"/>
-      <c r="G36" s="91"/>
-      <c r="H36" s="91"/>
-    </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B37" s="95">
+      <c r="F36" s="76"/>
+      <c r="G36" s="76"/>
+      <c r="H36" s="76"/>
+    </row>
+    <row r="37" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B37" s="79">
         <v>4</v>
       </c>
-      <c r="C37" s="116" t="s">
+      <c r="C37" s="91" t="s">
         <v>334</v>
       </c>
-      <c r="D37" s="117"/>
-      <c r="E37" s="96">
+      <c r="D37" s="92"/>
+      <c r="E37" s="80">
         <f>'4.Bodegaje'!H24</f>
         <v>5</v>
       </c>
-      <c r="F37" s="91"/>
-      <c r="G37" s="91"/>
-      <c r="H37" s="91"/>
-    </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B38" s="95">
+      <c r="F37" s="76"/>
+      <c r="G37" s="76"/>
+      <c r="H37" s="76"/>
+    </row>
+    <row r="38" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B38" s="79">
         <v>4</v>
       </c>
-      <c r="C38" s="111" t="s">
+      <c r="C38" s="93" t="s">
         <v>288</v>
       </c>
-      <c r="D38" s="112"/>
-      <c r="E38" s="96">
+      <c r="D38" s="94"/>
+      <c r="E38" s="80">
         <f>'5.Planos'!H17</f>
         <v>5</v>
       </c>
-      <c r="F38" s="91"/>
-      <c r="G38" s="91"/>
-      <c r="H38" s="91"/>
-    </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B39" s="95">
+      <c r="F38" s="76"/>
+      <c r="G38" s="76"/>
+      <c r="H38" s="76"/>
+    </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B39" s="79">
         <v>5</v>
       </c>
-      <c r="C39" s="111" t="s">
+      <c r="C39" s="93" t="s">
         <v>289</v>
       </c>
-      <c r="D39" s="112"/>
-      <c r="E39" s="96">
+      <c r="D39" s="94"/>
+      <c r="E39" s="80">
         <f>'5.Archivos'!G17</f>
         <v>5</v>
       </c>
-      <c r="F39" s="91"/>
-      <c r="G39" s="91"/>
-      <c r="H39" s="91"/>
-    </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B40" s="95">
+      <c r="F39" s="76"/>
+      <c r="G39" s="76"/>
+      <c r="H39" s="76"/>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B40" s="79">
         <v>6</v>
       </c>
-      <c r="C40" s="111" t="s">
+      <c r="C40" s="93" t="s">
         <v>317</v>
       </c>
-      <c r="D40" s="112"/>
-      <c r="E40" s="105">
+      <c r="D40" s="94"/>
+      <c r="E40" s="89">
         <v>5</v>
       </c>
-      <c r="F40" s="91"/>
-      <c r="G40" s="91"/>
-      <c r="H40" s="91"/>
-    </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B41" s="97">
+      <c r="F40" s="76"/>
+      <c r="G40" s="76"/>
+      <c r="H40" s="76"/>
+    </row>
+    <row r="41" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B41" s="81">
         <v>7</v>
       </c>
-      <c r="C41" s="113" t="s">
+      <c r="C41" s="95" t="s">
         <v>318</v>
       </c>
-      <c r="D41" s="114"/>
-      <c r="E41" s="104">
+      <c r="D41" s="96"/>
+      <c r="E41" s="88">
         <v>5</v>
       </c>
-      <c r="F41" s="91"/>
-      <c r="G41" s="91"/>
-      <c r="H41" s="91"/>
-    </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B42" s="91"/>
-      <c r="C42" s="91"/>
-      <c r="D42" s="89" t="s">
+      <c r="F41" s="76"/>
+      <c r="G41" s="76"/>
+      <c r="H41" s="76"/>
+    </row>
+    <row r="42" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B42" s="76"/>
+      <c r="C42" s="76"/>
+      <c r="D42" s="74" t="s">
         <v>293</v>
       </c>
-      <c r="E42" s="108">
+      <c r="E42" s="90">
         <f>AVERAGE(E34:E41)</f>
         <v>5</v>
       </c>
-      <c r="F42" s="91"/>
-      <c r="G42" s="91"/>
-      <c r="H42" s="91"/>
-    </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B43" s="91"/>
-      <c r="C43" s="91"/>
-      <c r="D43" s="91"/>
-      <c r="E43" s="91"/>
-      <c r="F43" s="91"/>
-      <c r="G43" s="91"/>
-      <c r="H43" s="91"/>
-    </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B44" s="91"/>
-      <c r="C44" s="91"/>
-      <c r="D44" s="91"/>
-      <c r="E44" s="91"/>
-      <c r="F44" s="91"/>
-      <c r="G44" s="91"/>
-      <c r="H44" s="91"/>
-    </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B45" s="91"/>
-      <c r="C45" s="91"/>
-      <c r="D45" s="91"/>
-      <c r="E45" s="91"/>
-      <c r="F45" s="91"/>
-      <c r="G45" s="91"/>
-      <c r="H45" s="91"/>
-    </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B46" s="91"/>
-      <c r="C46" s="91"/>
-      <c r="D46" s="91"/>
-      <c r="E46" s="91"/>
-      <c r="F46" s="91"/>
-      <c r="G46" s="91"/>
-      <c r="H46" s="91"/>
+      <c r="F42" s="76"/>
+      <c r="G42" s="76"/>
+      <c r="H42" s="76"/>
+    </row>
+    <row r="43" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B43" s="76"/>
+      <c r="C43" s="76"/>
+      <c r="D43" s="76"/>
+      <c r="E43" s="76"/>
+      <c r="F43" s="76"/>
+      <c r="G43" s="76"/>
+      <c r="H43" s="76"/>
+    </row>
+    <row r="44" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B44" s="76"/>
+      <c r="C44" s="76"/>
+      <c r="D44" s="76"/>
+      <c r="E44" s="76"/>
+      <c r="F44" s="76"/>
+      <c r="G44" s="76"/>
+      <c r="H44" s="76"/>
+    </row>
+    <row r="45" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B45" s="76"/>
+      <c r="C45" s="76"/>
+      <c r="D45" s="76"/>
+      <c r="E45" s="76"/>
+      <c r="F45" s="76"/>
+      <c r="G45" s="76"/>
+      <c r="H45" s="76"/>
+    </row>
+    <row r="46" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B46" s="76"/>
+      <c r="C46" s="76"/>
+      <c r="D46" s="76"/>
+      <c r="E46" s="76"/>
+      <c r="F46" s="76"/>
+      <c r="G46" s="76"/>
+      <c r="H46" s="76"/>
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="B4:E6"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="B10:E10"/>
+    <mergeCell ref="B11:E12"/>
+    <mergeCell ref="B13:E13"/>
     <mergeCell ref="C39:D39"/>
     <mergeCell ref="C40:D40"/>
     <mergeCell ref="C41:D41"/>
     <mergeCell ref="B14:E15"/>
     <mergeCell ref="B18:E18"/>
     <mergeCell ref="B32:E32"/>
-    <mergeCell ref="B4:E6"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C36:D36"/>
     <mergeCell ref="C38:D38"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="B11:E12"/>
-    <mergeCell ref="B13:E13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -3232,47 +3232,47 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0659C4DD-D653-4634-8C4F-29057F021A54}">
   <dimension ref="B1:H19"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.59765625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="30.06640625" style="2" customWidth="1"/>
-    <col min="3" max="3" width="50.59765625" style="2" customWidth="1"/>
-    <col min="4" max="4" width="15.59765625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="9.06640625" style="2"/>
-    <col min="6" max="6" width="12.265625" style="2" customWidth="1"/>
-    <col min="7" max="7" width="20.265625" style="98" customWidth="1"/>
-    <col min="8" max="8" width="12.3984375" style="47" customWidth="1"/>
-    <col min="9" max="16384" width="9.06640625" style="2"/>
+    <col min="1" max="1" width="2.5546875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="30.109375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="50.5546875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="15.5546875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="9.109375" style="2"/>
+    <col min="6" max="6" width="12.21875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="20.21875" style="82" customWidth="1"/>
+    <col min="8" max="8" width="12.44140625" style="47" customWidth="1"/>
+    <col min="9" max="16384" width="9.109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="1" spans="2:8" x14ac:dyDescent="0.3">
       <c r="E1" s="24"/>
     </row>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B3" s="20" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B4" s="74" t="s">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B4" s="105" t="s">
         <v>291</v>
       </c>
-      <c r="C4" s="74"/>
-      <c r="D4" s="74"/>
-      <c r="E4" s="74"/>
-    </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B5" s="74"/>
-      <c r="C5" s="74"/>
-      <c r="D5" s="74"/>
-      <c r="E5" s="74"/>
-    </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="C4" s="105"/>
+      <c r="D4" s="105"/>
+      <c r="E4" s="105"/>
+    </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B5" s="105"/>
+      <c r="C5" s="105"/>
+      <c r="D5" s="105"/>
+      <c r="E5" s="105"/>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B6" s="37" t="s">
         <v>40</v>
       </c>
@@ -3291,11 +3291,11 @@
       <c r="G6" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="H6" s="83" t="s">
+      <c r="H6" s="68" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="B7" s="32" t="s">
         <v>292</v>
       </c>
@@ -3310,11 +3310,11 @@
       </c>
       <c r="F7" s="31"/>
       <c r="G7" s="35"/>
-      <c r="H7" s="85">
+      <c r="H7" s="70">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B8" s="32" t="s">
         <v>296</v>
       </c>
@@ -3329,9 +3329,9 @@
       </c>
       <c r="F8" s="31"/>
       <c r="G8" s="35"/>
-      <c r="H8" s="85"/>
-    </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="H8" s="70"/>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B9" s="32" t="s">
         <v>294</v>
       </c>
@@ -3346,9 +3346,9 @@
       </c>
       <c r="F9" s="31"/>
       <c r="G9" s="35"/>
-      <c r="H9" s="85"/>
-    </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="H9" s="70"/>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B10" s="32" t="s">
         <v>299</v>
       </c>
@@ -3363,9 +3363,9 @@
       </c>
       <c r="F10" s="31"/>
       <c r="G10" s="35"/>
-      <c r="H10" s="85"/>
-    </row>
-    <row r="11" spans="2:8" ht="33" x14ac:dyDescent="0.45">
+      <c r="H10" s="70"/>
+    </row>
+    <row r="11" spans="2:8" ht="33.6" x14ac:dyDescent="0.3">
       <c r="B11" s="32" t="s">
         <v>298</v>
       </c>
@@ -3380,9 +3380,9 @@
       </c>
       <c r="F11" s="31"/>
       <c r="G11" s="35"/>
-      <c r="H11" s="85"/>
-    </row>
-    <row r="12" spans="2:8" ht="63.75" x14ac:dyDescent="0.45">
+      <c r="H11" s="70"/>
+    </row>
+    <row r="12" spans="2:8" ht="57" x14ac:dyDescent="0.3">
       <c r="B12" s="32" t="s">
         <v>308</v>
       </c>
@@ -3397,9 +3397,9 @@
       </c>
       <c r="F12" s="31"/>
       <c r="G12" s="35"/>
-      <c r="H12" s="85"/>
-    </row>
-    <row r="13" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
+      <c r="H12" s="70"/>
+    </row>
+    <row r="13" spans="2:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B13" s="32" t="s">
         <v>309</v>
       </c>
@@ -3414,9 +3414,9 @@
       </c>
       <c r="F13" s="31"/>
       <c r="G13" s="35"/>
-      <c r="H13" s="85"/>
-    </row>
-    <row r="14" spans="2:8" ht="33" x14ac:dyDescent="0.45">
+      <c r="H13" s="70"/>
+    </row>
+    <row r="14" spans="2:8" ht="33.6" x14ac:dyDescent="0.3">
       <c r="B14" s="32" t="s">
         <v>310</v>
       </c>
@@ -3431,9 +3431,9 @@
       </c>
       <c r="F14" s="31"/>
       <c r="G14" s="35"/>
-      <c r="H14" s="85"/>
-    </row>
-    <row r="15" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
+      <c r="H14" s="70"/>
+    </row>
+    <row r="15" spans="2:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="B15" s="32" t="s">
         <v>305</v>
       </c>
@@ -3448,9 +3448,9 @@
       </c>
       <c r="F15" s="31"/>
       <c r="G15" s="35"/>
-      <c r="H15" s="85"/>
-    </row>
-    <row r="16" spans="2:8" ht="52.15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="H15" s="70"/>
+    </row>
+    <row r="16" spans="2:8" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="32" t="s">
         <v>306</v>
       </c>
@@ -3465,9 +3465,9 @@
       </c>
       <c r="F16" s="31"/>
       <c r="G16" s="35"/>
-      <c r="H16" s="85"/>
-    </row>
-    <row r="17" spans="2:8" ht="35.65" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="H16" s="70"/>
+    </row>
+    <row r="17" spans="2:8" ht="35.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="43" t="s">
         <v>307</v>
       </c>
@@ -3482,19 +3482,19 @@
       </c>
       <c r="F17" s="45"/>
       <c r="G17" s="44"/>
-      <c r="H17" s="86"/>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="H17" s="71"/>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B18" s="40"/>
       <c r="C18" s="41"/>
-      <c r="D18" s="81"/>
+      <c r="D18" s="66"/>
       <c r="E18" s="42"/>
       <c r="F18" s="42"/>
       <c r="G18" s="41"/>
-      <c r="H18" s="87"/>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="G19" s="90" t="s">
+      <c r="H18" s="72"/>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="G19" s="75" t="s">
         <v>293</v>
       </c>
       <c r="H19" s="47">
@@ -3514,49 +3514,49 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1EE59D4-4937-4491-BD3F-7DBC007EDF85}">
   <dimension ref="B2:H114"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.59765625" style="2" customWidth="1"/>
-    <col min="2" max="2" width="27.06640625" style="2" customWidth="1"/>
+    <col min="1" max="1" width="2.5546875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="27.109375" style="2" customWidth="1"/>
     <col min="3" max="3" width="41" style="2" customWidth="1"/>
-    <col min="4" max="6" width="9.19921875" style="47" customWidth="1"/>
-    <col min="7" max="7" width="28.53125" style="98" customWidth="1"/>
-    <col min="8" max="8" width="14.86328125" style="47" customWidth="1"/>
-    <col min="9" max="9" width="2.59765625" style="2" customWidth="1"/>
-    <col min="10" max="16384" width="9.06640625" style="2"/>
+    <col min="4" max="6" width="9.21875" style="47" customWidth="1"/>
+    <col min="7" max="7" width="28.5546875" style="82" customWidth="1"/>
+    <col min="8" max="8" width="14.88671875" style="47" customWidth="1"/>
+    <col min="9" max="9" width="2.5546875" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="9.109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B3" s="20" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B4" s="74" t="s">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B4" s="105" t="s">
         <v>241</v>
       </c>
-      <c r="C4" s="74"/>
-      <c r="D4" s="74"/>
-      <c r="E4" s="74"/>
-      <c r="F4" s="74"/>
-      <c r="G4" s="74"/>
-      <c r="H4" s="74"/>
-    </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.45">
-      <c r="B5" s="79"/>
-      <c r="C5" s="79"/>
-      <c r="D5" s="79"/>
-      <c r="E5" s="79"/>
-      <c r="F5" s="79"/>
-      <c r="G5" s="79"/>
-      <c r="H5" s="79"/>
-    </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="C4" s="105"/>
+      <c r="D4" s="105"/>
+      <c r="E4" s="105"/>
+      <c r="F4" s="105"/>
+      <c r="G4" s="105"/>
+      <c r="H4" s="105"/>
+    </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B5" s="116"/>
+      <c r="C5" s="116"/>
+      <c r="D5" s="116"/>
+      <c r="E5" s="116"/>
+      <c r="F5" s="116"/>
+      <c r="G5" s="116"/>
+      <c r="H5" s="116"/>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B6" s="37" t="s">
         <v>40</v>
       </c>
@@ -3575,11 +3575,11 @@
       <c r="G6" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="H6" s="83" t="s">
+      <c r="H6" s="68" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B7" s="6" t="s">
         <v>108</v>
       </c>
@@ -3587,10 +3587,10 @@
       <c r="D7" s="34"/>
       <c r="E7" s="34"/>
       <c r="F7" s="34"/>
-      <c r="G7" s="99"/>
-      <c r="H7" s="84"/>
-    </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="G7" s="83"/>
+      <c r="H7" s="69"/>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B8" s="32" t="s">
         <v>172</v>
       </c>
@@ -3607,11 +3607,11 @@
       <c r="G8" s="35" t="s">
         <v>315</v>
       </c>
-      <c r="H8" s="85">
+      <c r="H8" s="70">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B9" s="32" t="s">
         <v>173</v>
       </c>
@@ -3628,9 +3628,9 @@
       <c r="G9" s="35" t="s">
         <v>315</v>
       </c>
-      <c r="H9" s="85"/>
-    </row>
-    <row r="10" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
+      <c r="H9" s="70"/>
+    </row>
+    <row r="10" spans="2:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="B10" s="32" t="s">
         <v>178</v>
       </c>
@@ -3646,9 +3646,9 @@
       </c>
       <c r="F10" s="31"/>
       <c r="G10" s="35"/>
-      <c r="H10" s="85"/>
-    </row>
-    <row r="11" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
+      <c r="H10" s="70"/>
+    </row>
+    <row r="11" spans="2:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B11" s="32" t="s">
         <v>179</v>
       </c>
@@ -3664,9 +3664,9 @@
       </c>
       <c r="F11" s="31"/>
       <c r="G11" s="35"/>
-      <c r="H11" s="85"/>
-    </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="H11" s="70"/>
+    </row>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B12" s="32" t="s">
         <v>43</v>
       </c>
@@ -3683,9 +3683,9 @@
       <c r="G12" s="35" t="s">
         <v>315</v>
       </c>
-      <c r="H12" s="85"/>
-    </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="H12" s="70"/>
+    </row>
+    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B13" s="32" t="s">
         <v>64</v>
       </c>
@@ -3702,9 +3702,9 @@
       <c r="G13" s="35" t="s">
         <v>315</v>
       </c>
-      <c r="H13" s="85"/>
-    </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="H13" s="70"/>
+    </row>
+    <row r="14" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B14" s="32" t="s">
         <v>44</v>
       </c>
@@ -3721,9 +3721,9 @@
       <c r="G14" s="35" t="s">
         <v>315</v>
       </c>
-      <c r="H14" s="85"/>
-    </row>
-    <row r="15" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
+      <c r="H14" s="70"/>
+    </row>
+    <row r="15" spans="2:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="B15" s="32" t="s">
         <v>56</v>
       </c>
@@ -3739,9 +3739,9 @@
       </c>
       <c r="F15" s="31"/>
       <c r="G15" s="35"/>
-      <c r="H15" s="85"/>
-    </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="H15" s="70"/>
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B16" s="32" t="s">
         <v>55</v>
       </c>
@@ -3757,9 +3757,9 @@
       </c>
       <c r="F16" s="31"/>
       <c r="G16" s="35"/>
-      <c r="H16" s="85"/>
-    </row>
-    <row r="17" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
+      <c r="H16" s="70"/>
+    </row>
+    <row r="17" spans="2:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B17" s="32" t="s">
         <v>54</v>
       </c>
@@ -3775,9 +3775,9 @@
       </c>
       <c r="F17" s="31"/>
       <c r="G17" s="35"/>
-      <c r="H17" s="85"/>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="H17" s="70"/>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B18" s="43" t="s">
         <v>111</v>
       </c>
@@ -3793,9 +3793,9 @@
       </c>
       <c r="F18" s="45"/>
       <c r="G18" s="44"/>
-      <c r="H18" s="86"/>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="H18" s="71"/>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B19" s="43" t="s">
         <v>109</v>
       </c>
@@ -3811,9 +3811,9 @@
       </c>
       <c r="F19" s="45"/>
       <c r="G19" s="44"/>
-      <c r="H19" s="86"/>
-    </row>
-    <row r="20" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
+      <c r="H19" s="71"/>
+    </row>
+    <row r="20" spans="2:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="B20" s="43" t="s">
         <v>74</v>
       </c>
@@ -3829,9 +3829,9 @@
       </c>
       <c r="F20" s="45"/>
       <c r="G20" s="44"/>
-      <c r="H20" s="86"/>
-    </row>
-    <row r="21" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
+      <c r="H20" s="71"/>
+    </row>
+    <row r="21" spans="2:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B21" s="43" t="s">
         <v>110</v>
       </c>
@@ -3847,18 +3847,18 @@
       </c>
       <c r="F21" s="45"/>
       <c r="G21" s="44"/>
-      <c r="H21" s="86"/>
-    </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="H21" s="71"/>
+    </row>
+    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B22" s="40"/>
       <c r="C22" s="41"/>
       <c r="D22" s="42"/>
       <c r="E22" s="42"/>
       <c r="F22" s="42"/>
       <c r="G22" s="41"/>
-      <c r="H22" s="87"/>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="H22" s="72"/>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B23" s="6" t="s">
         <v>218</v>
       </c>
@@ -3866,10 +3866,10 @@
       <c r="D23" s="34"/>
       <c r="E23" s="34"/>
       <c r="F23" s="34"/>
-      <c r="G23" s="99"/>
-      <c r="H23" s="84"/>
-    </row>
-    <row r="24" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
+      <c r="G23" s="83"/>
+      <c r="H23" s="69"/>
+    </row>
+    <row r="24" spans="2:8" ht="45.6" x14ac:dyDescent="0.3">
       <c r="B24" s="32" t="s">
         <v>79</v>
       </c>
@@ -3884,11 +3884,11 @@
       </c>
       <c r="F24" s="31"/>
       <c r="G24" s="35"/>
-      <c r="H24" s="85">
+      <c r="H24" s="70">
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="2:8" ht="76.5" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:8" ht="68.400000000000006" x14ac:dyDescent="0.3">
       <c r="B25" s="32" t="s">
         <v>80</v>
       </c>
@@ -3903,9 +3903,9 @@
       </c>
       <c r="F25" s="31"/>
       <c r="G25" s="35"/>
-      <c r="H25" s="85"/>
-    </row>
-    <row r="26" spans="2:8" ht="51" x14ac:dyDescent="0.45">
+      <c r="H25" s="70"/>
+    </row>
+    <row r="26" spans="2:8" ht="45.6" x14ac:dyDescent="0.3">
       <c r="B26" s="32" t="s">
         <v>81</v>
       </c>
@@ -3921,9 +3921,9 @@
       </c>
       <c r="F26" s="31"/>
       <c r="G26" s="35"/>
-      <c r="H26" s="85"/>
-    </row>
-    <row r="27" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
+      <c r="H26" s="70"/>
+    </row>
+    <row r="27" spans="2:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="B27" s="43" t="s">
         <v>83</v>
       </c>
@@ -3938,9 +3938,9 @@
       </c>
       <c r="F27" s="45"/>
       <c r="G27" s="44"/>
-      <c r="H27" s="86"/>
-    </row>
-    <row r="28" spans="2:8" ht="33" x14ac:dyDescent="0.45">
+      <c r="H27" s="71"/>
+    </row>
+    <row r="28" spans="2:8" ht="33.6" x14ac:dyDescent="0.3">
       <c r="B28" s="32" t="s">
         <v>82</v>
       </c>
@@ -3955,9 +3955,9 @@
       </c>
       <c r="F28" s="31"/>
       <c r="G28" s="35"/>
-      <c r="H28" s="85"/>
-    </row>
-    <row r="29" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
+      <c r="H28" s="70"/>
+    </row>
+    <row r="29" spans="2:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B29" s="32" t="s">
         <v>149</v>
       </c>
@@ -3972,9 +3972,9 @@
       </c>
       <c r="F29" s="31"/>
       <c r="G29" s="35"/>
-      <c r="H29" s="85"/>
-    </row>
-    <row r="30" spans="2:8" ht="33" x14ac:dyDescent="0.45">
+      <c r="H29" s="70"/>
+    </row>
+    <row r="30" spans="2:8" ht="33.6" x14ac:dyDescent="0.3">
       <c r="B30" s="43" t="s">
         <v>84</v>
       </c>
@@ -3990,9 +3990,9 @@
       </c>
       <c r="F30" s="45"/>
       <c r="G30" s="44"/>
-      <c r="H30" s="86"/>
-    </row>
-    <row r="31" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
+      <c r="H30" s="71"/>
+    </row>
+    <row r="31" spans="2:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="B31" s="32" t="s">
         <v>152</v>
       </c>
@@ -4008,9 +4008,9 @@
       </c>
       <c r="F31" s="31"/>
       <c r="G31" s="35"/>
-      <c r="H31" s="85"/>
-    </row>
-    <row r="32" spans="2:8" ht="51" x14ac:dyDescent="0.45">
+      <c r="H31" s="70"/>
+    </row>
+    <row r="32" spans="2:8" ht="45.6" x14ac:dyDescent="0.3">
       <c r="B32" s="32" t="s">
         <v>153</v>
       </c>
@@ -4026,9 +4026,9 @@
       </c>
       <c r="F32" s="31"/>
       <c r="G32" s="35"/>
-      <c r="H32" s="85"/>
-    </row>
-    <row r="33" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
+      <c r="H32" s="70"/>
+    </row>
+    <row r="33" spans="2:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B33" s="32" t="s">
         <v>85</v>
       </c>
@@ -4043,9 +4043,9 @@
       </c>
       <c r="F33" s="31"/>
       <c r="G33" s="35"/>
-      <c r="H33" s="85"/>
-    </row>
-    <row r="34" spans="2:8" ht="51" x14ac:dyDescent="0.45">
+      <c r="H33" s="70"/>
+    </row>
+    <row r="34" spans="2:8" ht="45.6" x14ac:dyDescent="0.3">
       <c r="B34" s="32" t="s">
         <v>86</v>
       </c>
@@ -4061,9 +4061,9 @@
       </c>
       <c r="F34" s="31"/>
       <c r="G34" s="35"/>
-      <c r="H34" s="85"/>
-    </row>
-    <row r="35" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
+      <c r="H34" s="70"/>
+    </row>
+    <row r="35" spans="2:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B35" s="32" t="s">
         <v>87</v>
       </c>
@@ -4078,9 +4078,9 @@
       </c>
       <c r="F35" s="31"/>
       <c r="G35" s="35"/>
-      <c r="H35" s="85"/>
-    </row>
-    <row r="36" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
+      <c r="H35" s="70"/>
+    </row>
+    <row r="36" spans="2:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="B36" s="32" t="s">
         <v>88</v>
       </c>
@@ -4096,9 +4096,9 @@
       </c>
       <c r="F36" s="31"/>
       <c r="G36" s="35"/>
-      <c r="H36" s="85"/>
-    </row>
-    <row r="37" spans="2:8" ht="33" x14ac:dyDescent="0.45">
+      <c r="H36" s="70"/>
+    </row>
+    <row r="37" spans="2:8" ht="33.6" x14ac:dyDescent="0.3">
       <c r="B37" s="32" t="s">
         <v>89</v>
       </c>
@@ -4114,18 +4114,18 @@
       </c>
       <c r="F37" s="31"/>
       <c r="G37" s="35"/>
-      <c r="H37" s="85"/>
-    </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="H37" s="70"/>
+    </row>
+    <row r="38" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B38" s="40"/>
       <c r="C38" s="41"/>
       <c r="D38" s="42"/>
       <c r="E38" s="42"/>
       <c r="F38" s="42"/>
       <c r="G38" s="41"/>
-      <c r="H38" s="87"/>
-    </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="H38" s="72"/>
+    </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B39" s="48" t="s">
         <v>69</v>
       </c>
@@ -4133,10 +4133,10 @@
       <c r="D39" s="34"/>
       <c r="E39" s="34"/>
       <c r="F39" s="34"/>
-      <c r="G39" s="99"/>
-      <c r="H39" s="84"/>
-    </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="G39" s="83"/>
+      <c r="H39" s="69"/>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B40" s="32" t="s">
         <v>91</v>
       </c>
@@ -4151,11 +4151,11 @@
       </c>
       <c r="F40" s="31"/>
       <c r="G40" s="35"/>
-      <c r="H40" s="85">
+      <c r="H40" s="70">
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
+    <row r="41" spans="2:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B41" s="32" t="s">
         <v>92</v>
       </c>
@@ -4170,9 +4170,9 @@
       </c>
       <c r="F41" s="31"/>
       <c r="G41" s="35"/>
-      <c r="H41" s="85"/>
-    </row>
-    <row r="42" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
+      <c r="H41" s="70"/>
+    </row>
+    <row r="42" spans="2:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B42" s="32" t="s">
         <v>93</v>
       </c>
@@ -4188,9 +4188,9 @@
       </c>
       <c r="F42" s="31"/>
       <c r="G42" s="35"/>
-      <c r="H42" s="85"/>
-    </row>
-    <row r="43" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
+      <c r="H42" s="70"/>
+    </row>
+    <row r="43" spans="2:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B43" s="32" t="s">
         <v>94</v>
       </c>
@@ -4206,18 +4206,18 @@
       </c>
       <c r="F43" s="31"/>
       <c r="G43" s="35"/>
-      <c r="H43" s="85"/>
-    </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="H43" s="70"/>
+    </row>
+    <row r="44" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B44" s="40"/>
       <c r="C44" s="41"/>
       <c r="D44" s="42"/>
       <c r="E44" s="42"/>
       <c r="F44" s="42"/>
       <c r="G44" s="41"/>
-      <c r="H44" s="87"/>
-    </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="H44" s="72"/>
+    </row>
+    <row r="45" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B45" s="48" t="s">
         <v>70</v>
       </c>
@@ -4225,10 +4225,10 @@
       <c r="D45" s="34"/>
       <c r="E45" s="34"/>
       <c r="F45" s="34"/>
-      <c r="G45" s="99"/>
-      <c r="H45" s="84"/>
-    </row>
-    <row r="46" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
+      <c r="G45" s="83"/>
+      <c r="H45" s="69"/>
+    </row>
+    <row r="46" spans="2:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="B46" s="32" t="s">
         <v>45</v>
       </c>
@@ -4243,11 +4243,11 @@
       </c>
       <c r="F46" s="31"/>
       <c r="G46" s="35"/>
-      <c r="H46" s="85">
+      <c r="H46" s="70">
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
+    <row r="47" spans="2:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="B47" s="32" t="s">
         <v>46</v>
       </c>
@@ -4262,9 +4262,9 @@
       </c>
       <c r="F47" s="31"/>
       <c r="G47" s="35"/>
-      <c r="H47" s="85"/>
-    </row>
-    <row r="48" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
+      <c r="H47" s="70"/>
+    </row>
+    <row r="48" spans="2:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="B48" s="32" t="s">
         <v>99</v>
       </c>
@@ -4279,9 +4279,9 @@
       </c>
       <c r="F48" s="31"/>
       <c r="G48" s="35"/>
-      <c r="H48" s="85"/>
-    </row>
-    <row r="49" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
+      <c r="H48" s="70"/>
+    </row>
+    <row r="49" spans="2:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B49" s="32" t="s">
         <v>100</v>
       </c>
@@ -4297,9 +4297,9 @@
       </c>
       <c r="F49" s="31"/>
       <c r="G49" s="35"/>
-      <c r="H49" s="85"/>
-    </row>
-    <row r="50" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
+      <c r="H49" s="70"/>
+    </row>
+    <row r="50" spans="2:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B50" s="32" t="s">
         <v>61</v>
       </c>
@@ -4314,9 +4314,9 @@
       </c>
       <c r="F50" s="31"/>
       <c r="G50" s="35"/>
-      <c r="H50" s="85"/>
-    </row>
-    <row r="51" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
+      <c r="H50" s="70"/>
+    </row>
+    <row r="51" spans="2:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B51" s="32" t="s">
         <v>103</v>
       </c>
@@ -4331,9 +4331,9 @@
       </c>
       <c r="F51" s="31"/>
       <c r="G51" s="35"/>
-      <c r="H51" s="85"/>
-    </row>
-    <row r="52" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
+      <c r="H51" s="70"/>
+    </row>
+    <row r="52" spans="2:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B52" s="32" t="s">
         <v>101</v>
       </c>
@@ -4349,9 +4349,9 @@
       </c>
       <c r="F52" s="31"/>
       <c r="G52" s="35"/>
-      <c r="H52" s="85"/>
-    </row>
-    <row r="53" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="H52" s="70"/>
+    </row>
+    <row r="53" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B53" s="32" t="s">
         <v>104</v>
       </c>
@@ -4366,9 +4366,9 @@
       </c>
       <c r="F53" s="31"/>
       <c r="G53" s="35"/>
-      <c r="H53" s="85"/>
-    </row>
-    <row r="54" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
+      <c r="H53" s="70"/>
+    </row>
+    <row r="54" spans="2:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B54" s="32" t="s">
         <v>106</v>
       </c>
@@ -4384,9 +4384,9 @@
       </c>
       <c r="F54" s="31"/>
       <c r="G54" s="35"/>
-      <c r="H54" s="85"/>
-    </row>
-    <row r="55" spans="2:8" ht="89.25" x14ac:dyDescent="0.45">
+      <c r="H54" s="70"/>
+    </row>
+    <row r="55" spans="2:8" ht="79.8" x14ac:dyDescent="0.3">
       <c r="B55" s="32" t="s">
         <v>137</v>
       </c>
@@ -4401,9 +4401,9 @@
       </c>
       <c r="F55" s="31"/>
       <c r="G55" s="35"/>
-      <c r="H55" s="85"/>
-    </row>
-    <row r="56" spans="2:8" ht="102" x14ac:dyDescent="0.45">
+      <c r="H55" s="70"/>
+    </row>
+    <row r="56" spans="2:8" ht="91.2" x14ac:dyDescent="0.3">
       <c r="B56" s="32" t="s">
         <v>138</v>
       </c>
@@ -4418,9 +4418,9 @@
       </c>
       <c r="F56" s="31"/>
       <c r="G56" s="35"/>
-      <c r="H56" s="85"/>
-    </row>
-    <row r="57" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="H56" s="70"/>
+    </row>
+    <row r="57" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B57" s="32" t="s">
         <v>140</v>
       </c>
@@ -4435,9 +4435,9 @@
       </c>
       <c r="F57" s="31"/>
       <c r="G57" s="35"/>
-      <c r="H57" s="85"/>
-    </row>
-    <row r="58" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="H57" s="70"/>
+    </row>
+    <row r="58" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B58" s="32" t="s">
         <v>198</v>
       </c>
@@ -4452,9 +4452,9 @@
       </c>
       <c r="F58" s="31"/>
       <c r="G58" s="35"/>
-      <c r="H58" s="85"/>
-    </row>
-    <row r="59" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
+      <c r="H58" s="70"/>
+    </row>
+    <row r="59" spans="2:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="B59" s="32" t="s">
         <v>141</v>
       </c>
@@ -4469,9 +4469,9 @@
       </c>
       <c r="F59" s="31"/>
       <c r="G59" s="35"/>
-      <c r="H59" s="85"/>
-    </row>
-    <row r="60" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
+      <c r="H59" s="70"/>
+    </row>
+    <row r="60" spans="2:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="B60" s="32" t="s">
         <v>197</v>
       </c>
@@ -4486,18 +4486,18 @@
       </c>
       <c r="F60" s="31"/>
       <c r="G60" s="35"/>
-      <c r="H60" s="85"/>
-    </row>
-    <row r="61" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="H60" s="70"/>
+    </row>
+    <row r="61" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B61" s="40"/>
       <c r="C61" s="41"/>
       <c r="D61" s="42"/>
       <c r="E61" s="42"/>
       <c r="F61" s="42"/>
       <c r="G61" s="41"/>
-      <c r="H61" s="87"/>
-    </row>
-    <row r="62" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="H61" s="72"/>
+    </row>
+    <row r="62" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B62" s="51" t="s">
         <v>71</v>
       </c>
@@ -4505,10 +4505,10 @@
       <c r="D62" s="53"/>
       <c r="E62" s="53"/>
       <c r="F62" s="53"/>
-      <c r="G62" s="100"/>
-      <c r="H62" s="88"/>
-    </row>
-    <row r="63" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
+      <c r="G62" s="84"/>
+      <c r="H62" s="73"/>
+    </row>
+    <row r="63" spans="2:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="B63" s="32" t="s">
         <v>181</v>
       </c>
@@ -4523,11 +4523,11 @@
       </c>
       <c r="F63" s="31"/>
       <c r="G63" s="35"/>
-      <c r="H63" s="85">
+      <c r="H63" s="70">
         <v>5</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
+    <row r="64" spans="2:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B64" s="32" t="s">
         <v>180</v>
       </c>
@@ -4543,9 +4543,9 @@
       </c>
       <c r="F64" s="31"/>
       <c r="G64" s="35"/>
-      <c r="H64" s="85"/>
-    </row>
-    <row r="65" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
+      <c r="H64" s="70"/>
+    </row>
+    <row r="65" spans="2:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B65" s="32" t="s">
         <v>113</v>
       </c>
@@ -4560,9 +4560,9 @@
       </c>
       <c r="F65" s="31"/>
       <c r="G65" s="35"/>
-      <c r="H65" s="85"/>
-    </row>
-    <row r="66" spans="2:8" ht="33" x14ac:dyDescent="0.45">
+      <c r="H65" s="70"/>
+    </row>
+    <row r="66" spans="2:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="B66" s="32" t="s">
         <v>124</v>
       </c>
@@ -4577,9 +4577,9 @@
       </c>
       <c r="F66" s="31"/>
       <c r="G66" s="35"/>
-      <c r="H66" s="85"/>
-    </row>
-    <row r="67" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
+      <c r="H66" s="70"/>
+    </row>
+    <row r="67" spans="2:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="B67" s="32" t="s">
         <v>125</v>
       </c>
@@ -4595,9 +4595,9 @@
       </c>
       <c r="F67" s="31"/>
       <c r="G67" s="35"/>
-      <c r="H67" s="85"/>
-    </row>
-    <row r="68" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
+      <c r="H67" s="70"/>
+    </row>
+    <row r="68" spans="2:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="B68" s="32" t="s">
         <v>128</v>
       </c>
@@ -4613,9 +4613,9 @@
       </c>
       <c r="F68" s="31"/>
       <c r="G68" s="35"/>
-      <c r="H68" s="85"/>
-    </row>
-    <row r="69" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="H68" s="70"/>
+    </row>
+    <row r="69" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B69" s="32" t="s">
         <v>129</v>
       </c>
@@ -4631,9 +4631,9 @@
       </c>
       <c r="F69" s="31"/>
       <c r="G69" s="35"/>
-      <c r="H69" s="85"/>
-    </row>
-    <row r="70" spans="2:8" ht="51" x14ac:dyDescent="0.45">
+      <c r="H69" s="70"/>
+    </row>
+    <row r="70" spans="2:8" ht="45.6" x14ac:dyDescent="0.3">
       <c r="B70" s="32" t="s">
         <v>116</v>
       </c>
@@ -4648,9 +4648,9 @@
       </c>
       <c r="F70" s="31"/>
       <c r="G70" s="35"/>
-      <c r="H70" s="85"/>
-    </row>
-    <row r="71" spans="2:8" ht="51" x14ac:dyDescent="0.45">
+      <c r="H70" s="70"/>
+    </row>
+    <row r="71" spans="2:8" ht="45.6" x14ac:dyDescent="0.3">
       <c r="B71" s="32" t="s">
         <v>118</v>
       </c>
@@ -4665,9 +4665,9 @@
       </c>
       <c r="F71" s="31"/>
       <c r="G71" s="35"/>
-      <c r="H71" s="85"/>
-    </row>
-    <row r="72" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
+      <c r="H71" s="70"/>
+    </row>
+    <row r="72" spans="2:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="B72" s="32" t="s">
         <v>120</v>
       </c>
@@ -4682,9 +4682,9 @@
       </c>
       <c r="F72" s="31"/>
       <c r="G72" s="35"/>
-      <c r="H72" s="85"/>
-    </row>
-    <row r="73" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
+      <c r="H72" s="70"/>
+    </row>
+    <row r="73" spans="2:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="B73" s="32" t="s">
         <v>121</v>
       </c>
@@ -4699,9 +4699,9 @@
       </c>
       <c r="F73" s="31"/>
       <c r="G73" s="35"/>
-      <c r="H73" s="85"/>
-    </row>
-    <row r="74" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
+      <c r="H73" s="70"/>
+    </row>
+    <row r="74" spans="2:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="B74" s="32" t="s">
         <v>131</v>
       </c>
@@ -4717,9 +4717,9 @@
       </c>
       <c r="F74" s="31"/>
       <c r="G74" s="35"/>
-      <c r="H74" s="85"/>
-    </row>
-    <row r="75" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
+      <c r="H74" s="70"/>
+    </row>
+    <row r="75" spans="2:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="B75" s="32" t="s">
         <v>132</v>
       </c>
@@ -4735,9 +4735,9 @@
       </c>
       <c r="F75" s="31"/>
       <c r="G75" s="35"/>
-      <c r="H75" s="85"/>
-    </row>
-    <row r="76" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="H75" s="70"/>
+    </row>
+    <row r="76" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B76" s="54"/>
       <c r="C76" s="55"/>
       <c r="D76" s="56"/>
@@ -4746,17 +4746,17 @@
       <c r="G76" s="55"/>
       <c r="H76" s="9"/>
     </row>
-    <row r="77" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="77" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B77" s="57" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="79" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="79" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B79" s="2" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="80" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="80" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B80" s="6" t="s">
         <v>164</v>
       </c>
@@ -4764,7 +4764,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="81" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="81" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B81" s="58" t="s">
         <v>166</v>
       </c>
@@ -4773,7 +4773,7 @@
         <v>1925</v>
       </c>
     </row>
-    <row r="82" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="82" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B82" s="58" t="s">
         <v>169</v>
       </c>
@@ -4782,7 +4782,7 @@
         <v>1435</v>
       </c>
     </row>
-    <row r="83" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="83" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B83" s="58" t="s">
         <v>168</v>
       </c>
@@ -4791,7 +4791,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="84" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="84" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B84" s="58" t="s">
         <v>49</v>
       </c>
@@ -4800,7 +4800,7 @@
         <v>7.0560000000000018</v>
       </c>
     </row>
-    <row r="85" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="85" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B85" s="58" t="s">
         <v>48</v>
       </c>
@@ -4809,7 +4809,7 @@
         <v>52.943999999999996</v>
       </c>
     </row>
-    <row r="86" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="86" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B86" s="59" t="s">
         <v>167</v>
       </c>
@@ -4818,7 +4818,7 @@
         <v>1495</v>
       </c>
     </row>
-    <row r="87" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="87" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B87" s="61" t="s">
         <v>74</v>
       </c>
@@ -4827,7 +4827,7 @@
         <v>0.74545454545454548</v>
       </c>
     </row>
-    <row r="88" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="88" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B88" s="54" t="s">
         <v>110</v>
       </c>
@@ -4836,12 +4836,12 @@
         <v>0.77662337662337666</v>
       </c>
     </row>
-    <row r="90" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="90" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B90" s="2" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="91" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="91" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B91" s="6" t="s">
         <v>164</v>
       </c>
@@ -4860,11 +4860,11 @@
       <c r="G91" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="H91" s="84" t="s">
+      <c r="H91" s="69" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="92" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="92" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B92" s="32" t="s">
         <v>184</v>
       </c>
@@ -4880,9 +4880,9 @@
       </c>
       <c r="F92" s="31"/>
       <c r="G92" s="35"/>
-      <c r="H92" s="85"/>
-    </row>
-    <row r="93" spans="2:8" ht="33" x14ac:dyDescent="0.45">
+      <c r="H92" s="70"/>
+    </row>
+    <row r="93" spans="2:8" ht="33.6" x14ac:dyDescent="0.3">
       <c r="B93" s="32" t="s">
         <v>185</v>
       </c>
@@ -4898,9 +4898,9 @@
       </c>
       <c r="F93" s="31"/>
       <c r="G93" s="35"/>
-      <c r="H93" s="85"/>
-    </row>
-    <row r="94" spans="2:8" x14ac:dyDescent="0.45">
+      <c r="H93" s="70"/>
+    </row>
+    <row r="94" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B94" s="32" t="s">
         <v>196</v>
       </c>
@@ -4915,10 +4915,10 @@
         <v>58</v>
       </c>
       <c r="F94" s="64"/>
-      <c r="G94" s="101"/>
+      <c r="G94" s="85"/>
       <c r="H94" s="11"/>
     </row>
-    <row r="95" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="95" spans="2:8" ht="33.6" x14ac:dyDescent="0.3">
       <c r="B95" s="32" t="s">
         <v>189</v>
       </c>
@@ -4933,10 +4933,10 @@
         <v>126</v>
       </c>
       <c r="F95" s="64"/>
-      <c r="G95" s="101"/>
+      <c r="G95" s="85"/>
       <c r="H95" s="11"/>
     </row>
-    <row r="96" spans="2:8" ht="33" x14ac:dyDescent="0.45">
+    <row r="96" spans="2:8" ht="33.6" x14ac:dyDescent="0.3">
       <c r="B96" s="32" t="s">
         <v>191</v>
       </c>
@@ -4951,10 +4951,10 @@
         <v>57</v>
       </c>
       <c r="F96" s="64"/>
-      <c r="G96" s="101"/>
+      <c r="G96" s="85"/>
       <c r="H96" s="11"/>
     </row>
-    <row r="97" spans="2:8" ht="49.5" x14ac:dyDescent="0.45">
+    <row r="97" spans="2:8" ht="50.4" x14ac:dyDescent="0.3">
       <c r="B97" s="32" t="s">
         <v>193</v>
       </c>
@@ -4969,89 +4969,89 @@
         <v>57</v>
       </c>
       <c r="F97" s="64"/>
-      <c r="G97" s="101"/>
+      <c r="G97" s="85"/>
       <c r="H97" s="11"/>
     </row>
-    <row r="98" spans="2:8" ht="33" x14ac:dyDescent="0.45">
+    <row r="98" spans="2:8" ht="33.6" x14ac:dyDescent="0.3">
       <c r="B98" s="32" t="s">
         <v>204</v>
       </c>
       <c r="C98" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="D98" s="82" t="s">
+      <c r="D98" s="67" t="s">
         <v>206</v>
       </c>
       <c r="E98" s="64" t="s">
         <v>58</v>
       </c>
       <c r="F98" s="64"/>
-      <c r="G98" s="101"/>
+      <c r="G98" s="85"/>
       <c r="H98" s="11">
         <v>5</v>
       </c>
     </row>
-    <row r="99" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="99" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B99" s="32" t="s">
         <v>205</v>
       </c>
       <c r="C99" s="29" t="s">
         <v>208</v>
       </c>
-      <c r="D99" s="82">
+      <c r="D99" s="67">
         <v>2</v>
       </c>
       <c r="E99" s="64" t="s">
         <v>126</v>
       </c>
       <c r="F99" s="64"/>
-      <c r="G99" s="101"/>
+      <c r="G99" s="85"/>
       <c r="H99" s="11"/>
     </row>
-    <row r="100" spans="2:8" ht="49.5" x14ac:dyDescent="0.45">
+    <row r="100" spans="2:8" ht="67.2" x14ac:dyDescent="0.3">
       <c r="B100" s="32" t="s">
         <v>50</v>
       </c>
       <c r="C100" s="29" t="s">
         <v>209</v>
       </c>
-      <c r="D100" s="82" t="s">
+      <c r="D100" s="67" t="s">
         <v>206</v>
       </c>
       <c r="E100" s="64" t="s">
         <v>126</v>
       </c>
       <c r="F100" s="64"/>
-      <c r="G100" s="101"/>
+      <c r="G100" s="85"/>
       <c r="H100" s="11"/>
     </row>
-    <row r="101" spans="2:8" ht="33" x14ac:dyDescent="0.45">
+    <row r="101" spans="2:8" ht="33.6" x14ac:dyDescent="0.3">
       <c r="B101" s="32" t="s">
         <v>51</v>
       </c>
       <c r="C101" s="29" t="s">
         <v>210</v>
       </c>
-      <c r="D101" s="82" t="s">
+      <c r="D101" s="67" t="s">
         <v>206</v>
       </c>
       <c r="E101" s="64" t="s">
         <v>126</v>
       </c>
       <c r="F101" s="64"/>
-      <c r="G101" s="101"/>
+      <c r="G101" s="85"/>
       <c r="H101" s="11"/>
     </row>
-    <row r="102" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="102" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B102" s="32"/>
       <c r="C102" s="29"/>
       <c r="D102" s="64"/>
       <c r="E102" s="64"/>
       <c r="F102" s="64"/>
-      <c r="G102" s="101"/>
+      <c r="G102" s="85"/>
       <c r="H102" s="11"/>
     </row>
-    <row r="103" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="103" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B103" s="40"/>
       <c r="C103" s="30"/>
       <c r="D103" s="56"/>
@@ -5060,10 +5060,10 @@
       <c r="G103" s="55"/>
       <c r="H103" s="9"/>
     </row>
-    <row r="104" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="104" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B104" s="63"/>
       <c r="C104" s="63"/>
-      <c r="G104" s="90" t="s">
+      <c r="G104" s="75" t="s">
         <v>293</v>
       </c>
       <c r="H104" s="47">
@@ -5071,43 +5071,43 @@
         <v>5</v>
       </c>
     </row>
-    <row r="105" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="105" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B105" s="63"/>
       <c r="C105" s="63"/>
     </row>
-    <row r="106" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="106" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B106" s="63"/>
       <c r="C106" s="63"/>
     </row>
-    <row r="107" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="107" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B107" s="63"/>
       <c r="C107" s="63"/>
     </row>
-    <row r="108" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="108" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B108" s="63"/>
       <c r="C108" s="63"/>
     </row>
-    <row r="109" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="109" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B109" s="63"/>
       <c r="C109" s="63"/>
     </row>
-    <row r="110" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="110" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B110" s="63"/>
       <c r="C110" s="63"/>
     </row>
-    <row r="111" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="111" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B111" s="63"/>
       <c r="C111" s="63"/>
     </row>
-    <row r="112" spans="2:8" x14ac:dyDescent="0.45">
+    <row r="112" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B112" s="63"/>
       <c r="C112" s="63"/>
     </row>
-    <row r="113" spans="2:3" x14ac:dyDescent="0.45">
+    <row r="113" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B113" s="63"/>
       <c r="C113" s="63"/>
     </row>
-    <row r="114" spans="2:3" x14ac:dyDescent="0.45">
+    <row r="114" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B114" s="63"/>
       <c r="C114" s="63"/>
     </row>
@@ -5123,48 +5123,48 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDC0663E-105D-42EA-893B-DB8B7FE41FC2}">
   <dimension ref="B2:H28"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.59765625" customWidth="1"/>
-    <col min="2" max="2" width="29.1328125" customWidth="1"/>
-    <col min="3" max="3" width="51.73046875" customWidth="1"/>
-    <col min="4" max="4" width="11.265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.59765625" customWidth="1"/>
-    <col min="7" max="7" width="35.1328125" style="102" customWidth="1"/>
-    <col min="8" max="8" width="13.46484375" style="80" customWidth="1"/>
+    <col min="1" max="1" width="2.5546875" customWidth="1"/>
+    <col min="2" max="2" width="29.109375" customWidth="1"/>
+    <col min="3" max="3" width="51.77734375" customWidth="1"/>
+    <col min="4" max="4" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.5546875" customWidth="1"/>
+    <col min="7" max="7" width="35.109375" style="86" customWidth="1"/>
+    <col min="8" max="8" width="13.44140625" style="65" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="2" spans="2:8" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="3" spans="2:8" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B3" s="20" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B4" s="74" t="s">
+    <row r="4" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="105" t="s">
         <v>242</v>
       </c>
-      <c r="C4" s="74"/>
-      <c r="D4" s="74"/>
-      <c r="E4" s="74"/>
-      <c r="F4" s="74"/>
-      <c r="G4" s="74"/>
-      <c r="H4" s="74"/>
-    </row>
-    <row r="5" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B5" s="79"/>
-      <c r="C5" s="79"/>
-      <c r="D5" s="79"/>
-      <c r="E5" s="79"/>
-      <c r="F5" s="79"/>
-      <c r="G5" s="79"/>
-      <c r="H5" s="79"/>
-    </row>
-    <row r="6" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="C4" s="105"/>
+      <c r="D4" s="105"/>
+      <c r="E4" s="105"/>
+      <c r="F4" s="105"/>
+      <c r="G4" s="105"/>
+      <c r="H4" s="105"/>
+    </row>
+    <row r="5" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="116"/>
+      <c r="C5" s="116"/>
+      <c r="D5" s="116"/>
+      <c r="E5" s="116"/>
+      <c r="F5" s="116"/>
+      <c r="G5" s="116"/>
+      <c r="H5" s="116"/>
+    </row>
+    <row r="6" spans="2:8" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B6" s="37" t="s">
         <v>40</v>
       </c>
@@ -5183,11 +5183,11 @@
       <c r="G6" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="H6" s="83" t="s">
+      <c r="H6" s="68" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:8" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B7" s="6" t="s">
         <v>320</v>
       </c>
@@ -5195,10 +5195,10 @@
       <c r="D7" s="34"/>
       <c r="E7" s="34"/>
       <c r="F7" s="34"/>
-      <c r="G7" s="99"/>
-      <c r="H7" s="84"/>
-    </row>
-    <row r="8" spans="2:8" ht="51" x14ac:dyDescent="0.45">
+      <c r="G7" s="83"/>
+      <c r="H7" s="69"/>
+    </row>
+    <row r="8" spans="2:8" ht="45.6" x14ac:dyDescent="0.3">
       <c r="B8" s="32" t="s">
         <v>228</v>
       </c>
@@ -5213,11 +5213,11 @@
       </c>
       <c r="F8" s="31"/>
       <c r="G8" s="35"/>
-      <c r="H8" s="85">
+      <c r="H8" s="70">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:8" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B9" s="32" t="s">
         <v>230</v>
       </c>
@@ -5232,9 +5232,9 @@
       </c>
       <c r="F9" s="31"/>
       <c r="G9" s="35"/>
-      <c r="H9" s="85"/>
-    </row>
-    <row r="10" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="H9" s="70"/>
+    </row>
+    <row r="10" spans="2:8" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B10" s="32" t="s">
         <v>229</v>
       </c>
@@ -5249,9 +5249,9 @@
       </c>
       <c r="F10" s="31"/>
       <c r="G10" s="35"/>
-      <c r="H10" s="85"/>
-    </row>
-    <row r="11" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
+      <c r="H10" s="70"/>
+    </row>
+    <row r="11" spans="2:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B11" s="32" t="s">
         <v>231</v>
       </c>
@@ -5266,9 +5266,9 @@
       </c>
       <c r="F11" s="31"/>
       <c r="G11" s="35"/>
-      <c r="H11" s="85"/>
-    </row>
-    <row r="12" spans="2:8" ht="25.5" x14ac:dyDescent="0.45">
+      <c r="H11" s="70"/>
+    </row>
+    <row r="12" spans="2:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B12" s="43" t="s">
         <v>216</v>
       </c>
@@ -5283,9 +5283,9 @@
       </c>
       <c r="F12" s="45"/>
       <c r="G12" s="44"/>
-      <c r="H12" s="86"/>
-    </row>
-    <row r="13" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="H12" s="71"/>
+    </row>
+    <row r="13" spans="2:8" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B13" s="43" t="s">
         <v>232</v>
       </c>
@@ -5300,9 +5300,9 @@
       </c>
       <c r="F13" s="45"/>
       <c r="G13" s="44"/>
-      <c r="H13" s="86"/>
-    </row>
-    <row r="14" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="H13" s="71"/>
+    </row>
+    <row r="14" spans="2:8" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B14" s="32" t="s">
         <v>211</v>
       </c>
@@ -5317,9 +5317,9 @@
       </c>
       <c r="F14" s="31"/>
       <c r="G14" s="35"/>
-      <c r="H14" s="85"/>
-    </row>
-    <row r="15" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="H14" s="70"/>
+    </row>
+    <row r="15" spans="2:8" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B15" s="32" t="s">
         <v>212</v>
       </c>
@@ -5334,9 +5334,9 @@
       </c>
       <c r="F15" s="31"/>
       <c r="G15" s="35"/>
-      <c r="H15" s="85"/>
-    </row>
-    <row r="16" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="H15" s="70"/>
+    </row>
+    <row r="16" spans="2:8" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B16" s="43" t="s">
         <v>213</v>
       </c>
@@ -5351,9 +5351,9 @@
       </c>
       <c r="F16" s="45"/>
       <c r="G16" s="44"/>
-      <c r="H16" s="86"/>
-    </row>
-    <row r="17" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="H16" s="71"/>
+    </row>
+    <row r="17" spans="2:8" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B17" s="43" t="s">
         <v>281</v>
       </c>
@@ -5368,9 +5368,9 @@
       </c>
       <c r="F17" s="45"/>
       <c r="G17" s="44"/>
-      <c r="H17" s="86"/>
-    </row>
-    <row r="18" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="H17" s="71"/>
+    </row>
+    <row r="18" spans="2:8" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B18" s="43" t="s">
         <v>214</v>
       </c>
@@ -5385,9 +5385,9 @@
       </c>
       <c r="F18" s="45"/>
       <c r="G18" s="44"/>
-      <c r="H18" s="86"/>
-    </row>
-    <row r="19" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="H18" s="71"/>
+    </row>
+    <row r="19" spans="2:8" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B19" s="43" t="s">
         <v>226</v>
       </c>
@@ -5402,9 +5402,9 @@
       </c>
       <c r="F19" s="45"/>
       <c r="G19" s="44"/>
-      <c r="H19" s="86"/>
-    </row>
-    <row r="20" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="H19" s="71"/>
+    </row>
+    <row r="20" spans="2:8" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B20" s="43" t="s">
         <v>227</v>
       </c>
@@ -5419,18 +5419,18 @@
       </c>
       <c r="F20" s="45"/>
       <c r="G20" s="44"/>
-      <c r="H20" s="86"/>
-    </row>
-    <row r="21" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="H20" s="71"/>
+    </row>
+    <row r="21" spans="2:8" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B21" s="43"/>
       <c r="C21" s="44"/>
       <c r="D21" s="45"/>
       <c r="E21" s="45"/>
       <c r="F21" s="45"/>
       <c r="G21" s="44"/>
-      <c r="H21" s="86"/>
-    </row>
-    <row r="22" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="H21" s="71"/>
+    </row>
+    <row r="22" spans="2:8" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B22" s="6" t="s">
         <v>237</v>
       </c>
@@ -5438,10 +5438,10 @@
       <c r="D22" s="34"/>
       <c r="E22" s="34"/>
       <c r="F22" s="34"/>
-      <c r="G22" s="99"/>
-      <c r="H22" s="84"/>
-    </row>
-    <row r="23" spans="2:8" ht="38.25" x14ac:dyDescent="0.45">
+      <c r="G22" s="83"/>
+      <c r="H22" s="69"/>
+    </row>
+    <row r="23" spans="2:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="B23" s="32" t="s">
         <v>217</v>
       </c>
@@ -5457,11 +5457,11 @@
       </c>
       <c r="F23" s="31"/>
       <c r="G23" s="35"/>
-      <c r="H23" s="85">
+      <c r="H23" s="70">
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:8" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B24" s="32" t="s">
         <v>220</v>
       </c>
@@ -5476,9 +5476,9 @@
       </c>
       <c r="F24" s="31"/>
       <c r="G24" s="35"/>
-      <c r="H24" s="85"/>
-    </row>
-    <row r="25" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="H24" s="70"/>
+    </row>
+    <row r="25" spans="2:8" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B25" s="32" t="s">
         <v>219</v>
       </c>
@@ -5493,9 +5493,9 @@
       </c>
       <c r="F25" s="31"/>
       <c r="G25" s="35"/>
-      <c r="H25" s="85"/>
-    </row>
-    <row r="26" spans="2:8" ht="51" x14ac:dyDescent="0.45">
+      <c r="H25" s="70"/>
+    </row>
+    <row r="26" spans="2:8" ht="45.6" x14ac:dyDescent="0.3">
       <c r="B26" s="32" t="s">
         <v>222</v>
       </c>
@@ -5511,22 +5511,22 @@
       </c>
       <c r="F26" s="31"/>
       <c r="G26" s="35"/>
-      <c r="H26" s="85"/>
-    </row>
-    <row r="27" spans="2:8" ht="16.5" x14ac:dyDescent="0.45">
+      <c r="H26" s="70"/>
+    </row>
+    <row r="27" spans="2:8" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B27" s="40"/>
       <c r="C27" s="41"/>
       <c r="D27" s="42"/>
       <c r="E27" s="42"/>
       <c r="F27" s="42"/>
       <c r="G27" s="41"/>
-      <c r="H27" s="87"/>
-    </row>
-    <row r="28" spans="2:8" ht="16.5" x14ac:dyDescent="0.6">
-      <c r="G28" s="90" t="s">
+      <c r="H27" s="72"/>
+    </row>
+    <row r="28" spans="2:8" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="G28" s="75" t="s">
         <v>293</v>
       </c>
-      <c r="H28" s="103">
+      <c r="H28" s="87">
         <f>AVERAGE(H7:H27)</f>
         <v>5</v>
       </c>
@@ -5543,50 +5543,50 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61FBD0B4-938E-4D04-BE03-979DB3A57126}">
   <dimension ref="B2:H24"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="16.8" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.59765625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="29.1328125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="51.73046875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.06640625" style="1"/>
-    <col min="6" max="6" width="11.59765625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="35.1328125" style="22" customWidth="1"/>
-    <col min="8" max="8" width="13.46484375" style="103" customWidth="1"/>
-    <col min="9" max="16384" width="9.06640625" style="1"/>
+    <col min="1" max="1" width="2.5546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="29.109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="51.77734375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.109375" style="1"/>
+    <col min="6" max="6" width="11.5546875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.109375" style="22" customWidth="1"/>
+    <col min="8" max="8" width="13.44140625" style="87" customWidth="1"/>
+    <col min="9" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.6">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.6">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B3" s="20" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.6">
-      <c r="B4" s="74" t="s">
+    <row r="4" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B4" s="105" t="s">
         <v>238</v>
       </c>
-      <c r="C4" s="74"/>
-      <c r="D4" s="74"/>
-      <c r="E4" s="74"/>
-      <c r="F4" s="74"/>
-      <c r="G4" s="74"/>
-      <c r="H4" s="74"/>
-    </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.6">
-      <c r="B5" s="79"/>
-      <c r="C5" s="79"/>
-      <c r="D5" s="79"/>
-      <c r="E5" s="79"/>
-      <c r="F5" s="79"/>
-      <c r="G5" s="79"/>
-      <c r="H5" s="79"/>
-    </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.6">
+      <c r="C4" s="105"/>
+      <c r="D4" s="105"/>
+      <c r="E4" s="105"/>
+      <c r="F4" s="105"/>
+      <c r="G4" s="105"/>
+      <c r="H4" s="105"/>
+    </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B5" s="116"/>
+      <c r="C5" s="116"/>
+      <c r="D5" s="116"/>
+      <c r="E5" s="116"/>
+      <c r="F5" s="116"/>
+      <c r="G5" s="116"/>
+      <c r="H5" s="116"/>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B6" s="37" t="s">
         <v>40</v>
       </c>
@@ -5605,11 +5605,11 @@
       <c r="G6" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="H6" s="83" t="s">
+      <c r="H6" s="68" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.6">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B7" s="6" t="s">
         <v>244</v>
       </c>
@@ -5617,10 +5617,10 @@
       <c r="D7" s="34"/>
       <c r="E7" s="34"/>
       <c r="F7" s="34"/>
-      <c r="G7" s="99"/>
-      <c r="H7" s="84"/>
-    </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.6">
+      <c r="G7" s="83"/>
+      <c r="H7" s="69"/>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B8" s="32" t="s">
         <v>243</v>
       </c>
@@ -5635,11 +5635,11 @@
       </c>
       <c r="F8" s="31"/>
       <c r="G8" s="35"/>
-      <c r="H8" s="85">
+      <c r="H8" s="70">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="25.5" x14ac:dyDescent="0.6">
+    <row r="9" spans="2:8" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B9" s="32" t="s">
         <v>248</v>
       </c>
@@ -5654,9 +5654,9 @@
       </c>
       <c r="F9" s="31"/>
       <c r="G9" s="35"/>
-      <c r="H9" s="85"/>
-    </row>
-    <row r="10" spans="2:8" ht="25.5" x14ac:dyDescent="0.6">
+      <c r="H9" s="70"/>
+    </row>
+    <row r="10" spans="2:8" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B10" s="32" t="s">
         <v>246</v>
       </c>
@@ -5671,9 +5671,9 @@
       </c>
       <c r="F10" s="31"/>
       <c r="G10" s="35"/>
-      <c r="H10" s="85"/>
-    </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.6">
+      <c r="H10" s="70"/>
+    </row>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B11" s="32" t="s">
         <v>249</v>
       </c>
@@ -5688,9 +5688,9 @@
       </c>
       <c r="F11" s="31"/>
       <c r="G11" s="35"/>
-      <c r="H11" s="85"/>
-    </row>
-    <row r="12" spans="2:8" ht="33" x14ac:dyDescent="0.6">
+      <c r="H11" s="70"/>
+    </row>
+    <row r="12" spans="2:8" ht="33.6" x14ac:dyDescent="0.4">
       <c r="B12" s="32" t="s">
         <v>254</v>
       </c>
@@ -5706,9 +5706,9 @@
       </c>
       <c r="F12" s="31"/>
       <c r="G12" s="35"/>
-      <c r="H12" s="85"/>
-    </row>
-    <row r="13" spans="2:8" ht="25.5" x14ac:dyDescent="0.6">
+      <c r="H12" s="70"/>
+    </row>
+    <row r="13" spans="2:8" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B13" s="32" t="s">
         <v>245</v>
       </c>
@@ -5723,9 +5723,9 @@
       </c>
       <c r="F13" s="31"/>
       <c r="G13" s="35"/>
-      <c r="H13" s="85"/>
-    </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.6">
+      <c r="H13" s="70"/>
+    </row>
+    <row r="14" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B14" s="32" t="s">
         <v>259</v>
       </c>
@@ -5741,9 +5741,9 @@
       </c>
       <c r="F14" s="31"/>
       <c r="G14" s="35"/>
-      <c r="H14" s="85"/>
-    </row>
-    <row r="15" spans="2:8" ht="33" x14ac:dyDescent="0.6">
+      <c r="H14" s="70"/>
+    </row>
+    <row r="15" spans="2:8" ht="33.6" x14ac:dyDescent="0.4">
       <c r="B15" s="32" t="s">
         <v>262</v>
       </c>
@@ -5758,9 +5758,9 @@
       </c>
       <c r="F15" s="31"/>
       <c r="G15" s="35"/>
-      <c r="H15" s="85"/>
-    </row>
-    <row r="16" spans="2:8" ht="33" x14ac:dyDescent="0.6">
+      <c r="H15" s="70"/>
+    </row>
+    <row r="16" spans="2:8" ht="33.6" x14ac:dyDescent="0.4">
       <c r="B16" s="32" t="s">
         <v>264</v>
       </c>
@@ -5776,27 +5776,27 @@
       </c>
       <c r="F16" s="31"/>
       <c r="G16" s="35"/>
-      <c r="H16" s="85"/>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.6">
+      <c r="H16" s="70"/>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B17" s="32"/>
       <c r="C17" s="35"/>
       <c r="D17" s="36"/>
       <c r="E17" s="31"/>
       <c r="F17" s="31"/>
       <c r="G17" s="35"/>
-      <c r="H17" s="85"/>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.6">
+      <c r="H17" s="70"/>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B18" s="32"/>
       <c r="C18" s="35"/>
       <c r="D18" s="31"/>
       <c r="E18" s="31"/>
       <c r="F18" s="31"/>
       <c r="G18" s="35"/>
-      <c r="H18" s="85"/>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.6">
+      <c r="H18" s="70"/>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B19" s="6" t="s">
         <v>239</v>
       </c>
@@ -5804,10 +5804,10 @@
       <c r="D19" s="34"/>
       <c r="E19" s="34"/>
       <c r="F19" s="34"/>
-      <c r="G19" s="99"/>
-      <c r="H19" s="84"/>
-    </row>
-    <row r="20" spans="2:8" ht="38.25" x14ac:dyDescent="0.6">
+      <c r="G19" s="83"/>
+      <c r="H19" s="69"/>
+    </row>
+    <row r="20" spans="2:8" ht="45.6" x14ac:dyDescent="0.4">
       <c r="B20" s="32" t="s">
         <v>266</v>
       </c>
@@ -5822,11 +5822,11 @@
       </c>
       <c r="F20" s="31"/>
       <c r="G20" s="35"/>
-      <c r="H20" s="85">
+      <c r="H20" s="70">
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="38.25" x14ac:dyDescent="0.6">
+    <row r="21" spans="2:8" ht="45.6" x14ac:dyDescent="0.4">
       <c r="B21" s="32" t="s">
         <v>267</v>
       </c>
@@ -5841,9 +5841,9 @@
       </c>
       <c r="F21" s="31"/>
       <c r="G21" s="35"/>
-      <c r="H21" s="85"/>
-    </row>
-    <row r="22" spans="2:8" ht="38.25" x14ac:dyDescent="0.6">
+      <c r="H21" s="70"/>
+    </row>
+    <row r="22" spans="2:8" ht="45.6" x14ac:dyDescent="0.4">
       <c r="B22" s="32" t="s">
         <v>268</v>
       </c>
@@ -5858,22 +5858,22 @@
       </c>
       <c r="F22" s="31"/>
       <c r="G22" s="35"/>
-      <c r="H22" s="85"/>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.6">
+      <c r="H22" s="70"/>
+    </row>
+    <row r="23" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B23" s="40"/>
       <c r="C23" s="41"/>
       <c r="D23" s="42"/>
       <c r="E23" s="42"/>
       <c r="F23" s="42"/>
       <c r="G23" s="41"/>
-      <c r="H23" s="87"/>
-    </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.6">
-      <c r="G24" s="90" t="s">
+      <c r="H23" s="72"/>
+    </row>
+    <row r="24" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="G24" s="75" t="s">
         <v>293</v>
       </c>
-      <c r="H24" s="103">
+      <c r="H24" s="87">
         <f>AVERAGE(H7:H23)</f>
         <v>5</v>
       </c>
@@ -5890,50 +5890,50 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36B29233-B656-46A0-B3DE-6C1E8F28F7E1}">
   <dimension ref="B2:H17"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="16.8" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.59765625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="36.3984375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="51.73046875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.06640625" style="1"/>
-    <col min="6" max="6" width="11.59765625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="35.1328125" style="22" customWidth="1"/>
-    <col min="8" max="8" width="13.46484375" style="103" customWidth="1"/>
-    <col min="9" max="16384" width="9.06640625" style="1"/>
+    <col min="1" max="1" width="2.5546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="36.44140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="51.77734375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.109375" style="1"/>
+    <col min="6" max="6" width="11.5546875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="35.109375" style="22" customWidth="1"/>
+    <col min="8" max="8" width="13.44140625" style="87" customWidth="1"/>
+    <col min="9" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.6">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.6">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B3" s="20" t="s">
         <v>333</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.6">
-      <c r="B4" s="74" t="s">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B4" s="105" t="s">
         <v>275</v>
       </c>
-      <c r="C4" s="74"/>
-      <c r="D4" s="74"/>
-      <c r="E4" s="74"/>
-      <c r="F4" s="74"/>
-      <c r="G4" s="74"/>
-      <c r="H4" s="74"/>
-    </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.6">
-      <c r="B5" s="79"/>
-      <c r="C5" s="79"/>
-      <c r="D5" s="79"/>
-      <c r="E5" s="79"/>
-      <c r="F5" s="79"/>
-      <c r="G5" s="79"/>
-      <c r="H5" s="79"/>
-    </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.6">
+      <c r="C4" s="105"/>
+      <c r="D4" s="105"/>
+      <c r="E4" s="105"/>
+      <c r="F4" s="105"/>
+      <c r="G4" s="105"/>
+      <c r="H4" s="105"/>
+    </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="B5" s="116"/>
+      <c r="C5" s="116"/>
+      <c r="D5" s="116"/>
+      <c r="E5" s="116"/>
+      <c r="F5" s="116"/>
+      <c r="G5" s="116"/>
+      <c r="H5" s="116"/>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B6" s="37" t="s">
         <v>40</v>
       </c>
@@ -5952,11 +5952,11 @@
       <c r="G6" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="H6" s="83" t="s">
+      <c r="H6" s="68" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="25.5" x14ac:dyDescent="0.6">
+    <row r="7" spans="2:8" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B7" s="32" t="s">
         <v>270</v>
       </c>
@@ -5971,11 +5971,11 @@
       </c>
       <c r="F7" s="31"/>
       <c r="G7" s="35"/>
-      <c r="H7" s="85">
+      <c r="H7" s="70">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="25.5" x14ac:dyDescent="0.6">
+    <row r="8" spans="2:8" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B8" s="32" t="s">
         <v>272</v>
       </c>
@@ -5990,9 +5990,9 @@
       </c>
       <c r="F8" s="31"/>
       <c r="G8" s="35"/>
-      <c r="H8" s="85"/>
-    </row>
-    <row r="9" spans="2:8" ht="25.5" x14ac:dyDescent="0.6">
+      <c r="H8" s="70"/>
+    </row>
+    <row r="9" spans="2:8" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B9" s="32" t="s">
         <v>273</v>
       </c>
@@ -6007,9 +6007,9 @@
       </c>
       <c r="F9" s="31"/>
       <c r="G9" s="35"/>
-      <c r="H9" s="85"/>
-    </row>
-    <row r="10" spans="2:8" ht="25.5" x14ac:dyDescent="0.6">
+      <c r="H9" s="70"/>
+    </row>
+    <row r="10" spans="2:8" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B10" s="32" t="s">
         <v>274</v>
       </c>
@@ -6024,9 +6024,9 @@
       </c>
       <c r="F10" s="31"/>
       <c r="G10" s="35"/>
-      <c r="H10" s="85"/>
-    </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.6">
+      <c r="H10" s="70"/>
+    </row>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B11" s="32" t="s">
         <v>276</v>
       </c>
@@ -6041,9 +6041,9 @@
       </c>
       <c r="F11" s="31"/>
       <c r="G11" s="35"/>
-      <c r="H11" s="85"/>
-    </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.6">
+      <c r="H11" s="70"/>
+    </row>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B12" s="32" t="s">
         <v>277</v>
       </c>
@@ -6058,9 +6058,9 @@
       </c>
       <c r="F12" s="31"/>
       <c r="G12" s="35"/>
-      <c r="H12" s="85"/>
-    </row>
-    <row r="13" spans="2:8" ht="25.5" x14ac:dyDescent="0.6">
+      <c r="H12" s="70"/>
+    </row>
+    <row r="13" spans="2:8" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B13" s="32" t="s">
         <v>278</v>
       </c>
@@ -6075,9 +6075,9 @@
       </c>
       <c r="F13" s="31"/>
       <c r="G13" s="35"/>
-      <c r="H13" s="85"/>
-    </row>
-    <row r="14" spans="2:8" ht="25.5" x14ac:dyDescent="0.6">
+      <c r="H13" s="70"/>
+    </row>
+    <row r="14" spans="2:8" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B14" s="32" t="s">
         <v>279</v>
       </c>
@@ -6092,9 +6092,9 @@
       </c>
       <c r="F14" s="31"/>
       <c r="G14" s="35"/>
-      <c r="H14" s="85"/>
-    </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.6">
+      <c r="H14" s="70"/>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B15" s="32" t="s">
         <v>280</v>
       </c>
@@ -6109,22 +6109,22 @@
       </c>
       <c r="F15" s="31"/>
       <c r="G15" s="35"/>
-      <c r="H15" s="85"/>
-    </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.6">
+      <c r="H15" s="70"/>
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B16" s="40"/>
       <c r="C16" s="41"/>
-      <c r="D16" s="81"/>
+      <c r="D16" s="66"/>
       <c r="E16" s="42"/>
       <c r="F16" s="42"/>
       <c r="G16" s="41"/>
-      <c r="H16" s="87"/>
-    </row>
-    <row r="17" spans="7:8" x14ac:dyDescent="0.6">
-      <c r="G17" s="90" t="s">
+      <c r="H16" s="72"/>
+    </row>
+    <row r="17" spans="7:8" x14ac:dyDescent="0.4">
+      <c r="G17" s="75" t="s">
         <v>293</v>
       </c>
-      <c r="H17" s="103">
+      <c r="H17" s="87">
         <f>AVERAGE(H7:H16)</f>
         <v>5</v>
       </c>
@@ -6141,37 +6141,37 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:G17"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="2.59765625" style="2" customWidth="1"/>
+    <col min="1" max="2" width="2.5546875" style="2" customWidth="1"/>
     <col min="3" max="4" width="46.6640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="33.46484375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="30.3984375" style="98" customWidth="1"/>
-    <col min="7" max="7" width="11.59765625" style="47" customWidth="1"/>
-    <col min="8" max="16384" width="9.06640625" style="2"/>
+    <col min="5" max="5" width="33.44140625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="30.44140625" style="82" customWidth="1"/>
+    <col min="7" max="7" width="11.5546875" style="47" customWidth="1"/>
+    <col min="8" max="16384" width="9.109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B2" s="75" t="s">
+    <row r="2" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B2" s="103" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="75"/>
-      <c r="D2" s="75"/>
-      <c r="E2" s="75"/>
-      <c r="F2" s="75"/>
-      <c r="G2" s="75"/>
-    </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.45">
-      <c r="B3" s="115" t="s">
+      <c r="C2" s="103"/>
+      <c r="D2" s="103"/>
+      <c r="E2" s="103"/>
+      <c r="F2" s="103"/>
+      <c r="G2" s="103"/>
+    </row>
+    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="B3" s="117" t="s">
         <v>332</v>
       </c>
-      <c r="C3" s="115"/>
-      <c r="D3" s="115"/>
-      <c r="E3" s="115"/>
-      <c r="F3" s="115"/>
-      <c r="G3" s="115"/>
-    </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.45">
+      <c r="C3" s="117"/>
+      <c r="D3" s="117"/>
+      <c r="E3" s="117"/>
+      <c r="F3" s="117"/>
+      <c r="G3" s="117"/>
+    </row>
+    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B5" s="17" t="s">
         <v>10</v>
       </c>
@@ -6191,7 +6191,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B6" s="15">
         <v>0</v>
       </c>
@@ -6204,12 +6204,12 @@
       <c r="E6" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="F6" s="101"/>
+      <c r="F6" s="85"/>
       <c r="G6" s="11">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B7" s="15">
         <v>1</v>
       </c>
@@ -6222,10 +6222,10 @@
       <c r="E7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="101"/>
+      <c r="F7" s="85"/>
       <c r="G7" s="11"/>
     </row>
-    <row r="8" spans="2:7" ht="114.75" x14ac:dyDescent="0.45">
+    <row r="8" spans="2:7" ht="114" x14ac:dyDescent="0.3">
       <c r="B8" s="15">
         <v>2</v>
       </c>
@@ -6238,10 +6238,10 @@
       <c r="E8" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="101"/>
+      <c r="F8" s="85"/>
       <c r="G8" s="11"/>
     </row>
-    <row r="9" spans="2:7" ht="42" x14ac:dyDescent="0.45">
+    <row r="9" spans="2:7" ht="39.6" x14ac:dyDescent="0.3">
       <c r="B9" s="15">
         <v>3</v>
       </c>
@@ -6252,10 +6252,10 @@
       <c r="E9" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F9" s="101"/>
+      <c r="F9" s="85"/>
       <c r="G9" s="11"/>
     </row>
-    <row r="10" spans="2:7" ht="54.75" x14ac:dyDescent="0.45">
+    <row r="10" spans="2:7" ht="51" x14ac:dyDescent="0.3">
       <c r="B10" s="15">
         <v>4</v>
       </c>
@@ -6266,10 +6266,10 @@
       <c r="E10" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="101"/>
+      <c r="F10" s="85"/>
       <c r="G10" s="11"/>
     </row>
-    <row r="11" spans="2:7" ht="29.25" x14ac:dyDescent="0.45">
+    <row r="11" spans="2:7" ht="28.2" x14ac:dyDescent="0.3">
       <c r="B11" s="15">
         <v>5</v>
       </c>
@@ -6280,10 +6280,10 @@
       <c r="E11" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="F11" s="101"/>
+      <c r="F11" s="85"/>
       <c r="G11" s="11"/>
     </row>
-    <row r="12" spans="2:7" ht="38.25" x14ac:dyDescent="0.45">
+    <row r="12" spans="2:7" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="B12" s="15">
         <v>6</v>
       </c>
@@ -6296,10 +6296,10 @@
       <c r="E12" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="F12" s="101"/>
+      <c r="F12" s="85"/>
       <c r="G12" s="11"/>
     </row>
-    <row r="13" spans="2:7" ht="25.5" x14ac:dyDescent="0.45">
+    <row r="13" spans="2:7" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B13" s="15">
         <v>7</v>
       </c>
@@ -6312,10 +6312,10 @@
       <c r="E13" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="F13" s="101"/>
+      <c r="F13" s="85"/>
       <c r="G13" s="11"/>
     </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="14" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B14" s="15">
         <v>8</v>
       </c>
@@ -6328,20 +6328,20 @@
       <c r="E14" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="F14" s="101"/>
+      <c r="F14" s="85"/>
       <c r="G14" s="11"/>
     </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="15" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B15" s="15">
         <v>9</v>
       </c>
       <c r="C15" s="29"/>
       <c r="D15" s="35"/>
       <c r="E15" s="3"/>
-      <c r="F15" s="101"/>
+      <c r="F15" s="85"/>
       <c r="G15" s="11"/>
     </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.45">
+    <row r="16" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B16" s="16">
         <v>10</v>
       </c>
@@ -6351,8 +6351,8 @@
       <c r="F16" s="55"/>
       <c r="G16" s="9"/>
     </row>
-    <row r="17" spans="6:7" x14ac:dyDescent="0.45">
-      <c r="F17" s="90" t="s">
+    <row r="17" spans="6:7" x14ac:dyDescent="0.3">
+      <c r="F17" s="75" t="s">
         <v>293</v>
       </c>
       <c r="G17" s="47">
@@ -6372,29 +6372,29 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCD4CBC5-BEDD-4E97-A57A-4EDFE72E7B14}">
   <dimension ref="B1:B4"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="16.8" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.59765625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="95.3984375" style="1" customWidth="1"/>
-    <col min="3" max="16384" width="9.06640625" style="1"/>
+    <col min="1" max="1" width="2.5546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="95.44140625" style="1" customWidth="1"/>
+    <col min="3" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="1" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B1" s="24" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="2" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B2" s="1" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="3" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="3" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B3" s="21" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="2:2" x14ac:dyDescent="0.6">
+    <row r="4" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B4" s="22" t="s">
         <v>25</v>
       </c>

--- a/file/table/DAPC_ProyectoCAD.xlsx
+++ b/file/table/DAPC_ProyectoCAD.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B88C970-5BA9-4668-8AB7-16D363BCB90D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{210E5FA6-870C-46AC-AAC9-3D5D5E347E50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0.Inicio" sheetId="7" r:id="rId1"/>
@@ -27,7 +27,7 @@
   </externalReferences>
   <definedNames>
     <definedName name="SumUDig" localSheetId="4">'[1]1.Técnicas'!$E$32</definedName>
-    <definedName name="SumUDig">'0.Inicio'!$E$30</definedName>
+    <definedName name="SumUDig">'0.Inicio'!$E$29</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -55,7 +55,7 @@
     <author>Test</author>
   </authors>
   <commentList>
-    <comment ref="E19" authorId="0" shapeId="0" xr:uid="{8786F758-EC5E-4426-92D1-B2FAF1BCAE4E}">
+    <comment ref="E18" authorId="0" shapeId="0" xr:uid="{8786F758-EC5E-4426-92D1-B2FAF1BCAE4E}">
       <text>
         <r>
           <rPr>
@@ -276,6 +276,30 @@
 </comments>
 </file>
 
+<file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Test</author>
+  </authors>
+  <commentList>
+    <comment ref="F5" authorId="0" shapeId="0" xr:uid="{634A2F11-6BC0-4DF5-92C2-329F8A975203}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Segoe UI Light"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Actividad de referencia en curso DAPC.
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
 <metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
@@ -299,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="533" uniqueCount="336">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="342">
   <si>
     <t>1. Especificaciones técnicas generales</t>
   </si>
@@ -404,48 +428,6 @@
   </si>
   <si>
     <t>/file/cad/Bloque_Otros.dwg</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Bloques - arquitectónicos </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>(Utilizar los bloques ejemplo del ADC de AutoCAD, o utilizar una librería de bloque externos, citando la fuente de descarga)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Bloques - eléctricos </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>(Para el dibujo de los planos eléctricos, utilizar los bloques creados a partir de las especificaciones establecidas en el Reglamento Técnico de Instalaciones Eléctricas - RETIE del Ministerio de Minas y Energía de Colombia)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Bloques - otros </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>(Utilizar una librería de bloque externos citando la fuente de descarga.)</t>
-    </r>
   </si>
   <si>
     <t>/file/</t>
@@ -1458,9 +1440,6 @@
     </r>
   </si>
   <si>
-    <t>Archivo único de dibujo del proyecto. Guardar copias de las diferentes versiones de avance creadas colocando el sufijo correspondiente al aaaammdd.</t>
-  </si>
-  <si>
     <t>/file/cad/DAPC.dwg</t>
   </si>
   <si>
@@ -1502,13 +1481,43 @@
   </si>
   <si>
     <t>Arquitectónica y estructural</t>
+  </si>
+  <si>
+    <t>M01A06</t>
+  </si>
+  <si>
+    <t>M01A05</t>
+  </si>
+  <si>
+    <t>M01A01</t>
+  </si>
+  <si>
+    <t>M01A02a</t>
+  </si>
+  <si>
+    <t>M01A04</t>
+  </si>
+  <si>
+    <t>M01A03</t>
+  </si>
+  <si>
+    <t>Utilizar los bloques ejemplo del ADC de AutoCAD, o utilizar una librería de bloque externos, citando la fuente de descarga.</t>
+  </si>
+  <si>
+    <t>Para el dibujo de los planos eléctricos, utilizar los bloques creados a partir de las especificaciones establecidas en el Reglamento Técnico de Instalaciones Eléctricas - RETIE del Ministerio de Minas y Energía de Colombia.</t>
+  </si>
+  <si>
+    <t>Utilizar una librería de bloque externos citando la fuente de descarga. Por ejemplo: cámaras de vigilancia, luces de emergencia, panel solar.</t>
+  </si>
+  <si>
+    <t>Archivo único de dibujo del proyecto. Guardar copias de las diferentes versiones de avance creadas colocando el sufijo aaaammdd.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1598,6 +1607,12 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color theme="10"/>
+      <name val="Segoe UI Light"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1613,7 +1628,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="31">
+  <borders count="35">
     <border>
       <left/>
       <right/>
@@ -2021,13 +2036,65 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-4.9989318521683403E-2"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="118">
+  <cellXfs count="133">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2219,6 +2286,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2382,6 +2452,48 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2697,19 +2809,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82EDA320-F942-4FCE-8343-60C075021E69}">
-  <dimension ref="B1:H46"/>
+  <dimension ref="B1:H45"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="2.5546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="50.5546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="15.5546875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="11.5546875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="50.77734375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="15.77734375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="12.77734375" style="2" customWidth="1"/>
     <col min="6" max="6" width="2.5546875" style="2" customWidth="1"/>
     <col min="7" max="16384" width="9.109375" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="E1" s="24"/>
+      <c r="E1" s="24" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
@@ -2718,209 +2832,216 @@
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B3" s="20" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B4" s="105" t="s">
-        <v>39</v>
-      </c>
-      <c r="C4" s="105"/>
-      <c r="D4" s="105"/>
-      <c r="E4" s="105"/>
+      <c r="B4" s="106" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="106"/>
+      <c r="D4" s="106"/>
+      <c r="E4" s="106"/>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B5" s="105"/>
-      <c r="C5" s="105"/>
-      <c r="D5" s="105"/>
-      <c r="E5" s="105"/>
+      <c r="B5" s="106"/>
+      <c r="C5" s="106"/>
+      <c r="D5" s="106"/>
+      <c r="E5" s="106"/>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B6" s="105"/>
-      <c r="C6" s="105"/>
-      <c r="D6" s="105"/>
-      <c r="E6" s="105"/>
+      <c r="B6" s="106"/>
+      <c r="C6" s="106"/>
+      <c r="D6" s="106"/>
+      <c r="E6" s="106"/>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B7" s="105"/>
-      <c r="C7" s="105"/>
-      <c r="D7" s="105"/>
-      <c r="E7" s="105"/>
+      <c r="B7" s="111" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="112"/>
+      <c r="D7" s="112"/>
+      <c r="E7" s="113"/>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="110" t="s">
+      <c r="B8" s="98" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" s="99"/>
+      <c r="D8" s="99"/>
+      <c r="E8" s="100"/>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B9" s="114" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9" s="115"/>
+      <c r="D9" s="115"/>
+      <c r="E9" s="116"/>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="98" t="s">
+        <v>13</v>
+      </c>
+      <c r="C10" s="99"/>
+      <c r="D10" s="99"/>
+      <c r="E10" s="100"/>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B11" s="101"/>
+      <c r="C11" s="102"/>
+      <c r="D11" s="102"/>
+      <c r="E11" s="103"/>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B12" s="114" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="115"/>
+      <c r="D12" s="115"/>
+      <c r="E12" s="116"/>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="98" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13" s="99"/>
+      <c r="D13" s="99"/>
+      <c r="E13" s="100"/>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B14" s="101"/>
+      <c r="C14" s="102"/>
+      <c r="D14" s="102"/>
+      <c r="E14" s="103"/>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B15" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="C15" s="23"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B16" s="18"/>
+      <c r="C16" s="18"/>
+      <c r="D16" s="18"/>
+      <c r="E16" s="18"/>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B17" s="104" t="s">
+        <v>14</v>
+      </c>
+      <c r="C17" s="104"/>
+      <c r="D17" s="104"/>
+      <c r="E17" s="104"/>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B18" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E18" s="10" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B19" s="15">
         <v>1</v>
       </c>
-      <c r="C8" s="111"/>
-      <c r="D8" s="111"/>
-      <c r="E8" s="112"/>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="97" t="s">
-        <v>12</v>
-      </c>
-      <c r="C9" s="98"/>
-      <c r="D9" s="98"/>
-      <c r="E9" s="99"/>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="113" t="s">
-        <v>2</v>
-      </c>
-      <c r="C10" s="114"/>
-      <c r="D10" s="114"/>
-      <c r="E10" s="115"/>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B11" s="97" t="s">
-        <v>13</v>
-      </c>
-      <c r="C11" s="98"/>
-      <c r="D11" s="98"/>
-      <c r="E11" s="99"/>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B12" s="100"/>
-      <c r="C12" s="101"/>
-      <c r="D12" s="101"/>
-      <c r="E12" s="102"/>
-    </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="113" t="s">
-        <v>20</v>
-      </c>
-      <c r="C13" s="114"/>
-      <c r="D13" s="114"/>
-      <c r="E13" s="115"/>
-    </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B14" s="97" t="s">
-        <v>18</v>
-      </c>
-      <c r="C14" s="98"/>
-      <c r="D14" s="98"/>
-      <c r="E14" s="99"/>
-    </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B15" s="100"/>
-      <c r="C15" s="101"/>
-      <c r="D15" s="101"/>
-      <c r="E15" s="102"/>
-    </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B16" s="23" t="s">
-        <v>21</v>
-      </c>
-      <c r="C16" s="23"/>
-      <c r="D16" s="23"/>
-      <c r="E16" s="23"/>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B17" s="18"/>
-      <c r="C17" s="18"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="18"/>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B18" s="103" t="s">
-        <v>14</v>
-      </c>
-      <c r="C18" s="103"/>
-      <c r="D18" s="103"/>
-      <c r="E18" s="103"/>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B19" s="17" t="s">
-        <v>10</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>28</v>
-      </c>
-      <c r="E19" s="10" t="s">
-        <v>4</v>
+      <c r="C19" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="27" t="s">
+        <v>3</v>
+      </c>
+      <c r="E19" s="11">
+        <f t="shared" ref="E19:E28" si="0">IFERROR(RIGHT(D19,1)*1,0)</f>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B20" s="15">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C20" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D20" s="27" t="s">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E20" s="11">
-        <f t="shared" ref="E20:E29" si="0">IFERROR(RIGHT(D20,1)*1,0)</f>
-        <v>1</v>
+        <f t="shared" si="0"/>
+        <v>4</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B21" s="15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C21" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D21" s="27" t="s">
+        <v>6</v>
+      </c>
+      <c r="E21" s="11">
+        <f t="shared" si="0"/>
         <v>5</v>
-      </c>
-      <c r="E21" s="11">
-        <f t="shared" si="0"/>
-        <v>4</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B22" s="15">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C22" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D22" s="27" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E22" s="11">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B23" s="15">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C23" s="25" t="s">
         <v>8</v>
       </c>
       <c r="D23" s="27" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E23" s="11">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B24" s="15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C24" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="D24" s="27" t="s">
-        <v>9</v>
-      </c>
+      <c r="D24" s="27"/>
       <c r="E24" s="11">
         <f t="shared" si="0"/>
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B25" s="15">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C25" s="25" t="s">
         <v>8</v>
@@ -2933,7 +3054,7 @@
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B26" s="15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C26" s="25" t="s">
         <v>8</v>
@@ -2946,7 +3067,7 @@
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B27" s="15">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C27" s="25" t="s">
         <v>8</v>
@@ -2958,271 +3079,258 @@
       </c>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B28" s="15">
-        <v>9</v>
-      </c>
-      <c r="C28" s="25" t="s">
+      <c r="B28" s="16">
+        <v>10</v>
+      </c>
+      <c r="C28" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="D28" s="27"/>
-      <c r="E28" s="11">
+      <c r="D28" s="28"/>
+      <c r="E28" s="9">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B29" s="16">
+      <c r="D29" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="E29" s="12">
+        <f>SUM(E19:E28)</f>
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B30" s="77"/>
+      <c r="C30" s="77"/>
+      <c r="D30" s="77"/>
+      <c r="E30" s="77"/>
+      <c r="F30" s="77"/>
+      <c r="G30" s="77"/>
+      <c r="H30" s="77"/>
+    </row>
+    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B31" s="105" t="s">
+        <v>282</v>
+      </c>
+      <c r="C31" s="105"/>
+      <c r="D31" s="105"/>
+      <c r="E31" s="105"/>
+      <c r="F31" s="77"/>
+      <c r="G31" s="77"/>
+      <c r="H31" s="77"/>
+    </row>
+    <row r="32" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B32" s="78" t="s">
         <v>10</v>
       </c>
-      <c r="C29" s="26" t="s">
-        <v>8</v>
-      </c>
-      <c r="D29" s="28"/>
-      <c r="E29" s="9">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="D30" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="E30" s="12">
-        <f>SUM(E20:E29)</f>
+      <c r="C32" s="107" t="s">
+        <v>37</v>
+      </c>
+      <c r="D32" s="108"/>
+      <c r="E32" s="79" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B31" s="76"/>
-      <c r="C31" s="76"/>
-      <c r="D31" s="76"/>
-      <c r="E31" s="76"/>
-      <c r="F31" s="76"/>
-      <c r="G31" s="76"/>
-      <c r="H31" s="76"/>
-    </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B32" s="104" t="s">
+      <c r="F32" s="77"/>
+      <c r="G32" s="77"/>
+      <c r="H32" s="77"/>
+    </row>
+    <row r="33" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B33" s="80">
+        <v>1</v>
+      </c>
+      <c r="C33" s="109" t="s">
+        <v>283</v>
+      </c>
+      <c r="D33" s="110"/>
+      <c r="E33" s="81">
+        <f>'1.Tecnica'!I19</f>
+        <v>5</v>
+      </c>
+      <c r="F33" s="77"/>
+      <c r="G33" s="77"/>
+      <c r="H33" s="77"/>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B34" s="80">
+        <v>2</v>
+      </c>
+      <c r="C34" s="94" t="s">
+        <v>331</v>
+      </c>
+      <c r="D34" s="95"/>
+      <c r="E34" s="81">
+        <f>'2.ArquitectonicaEstructural'!I103</f>
+        <v>5</v>
+      </c>
+      <c r="F34" s="77"/>
+      <c r="G34" s="77"/>
+      <c r="H34" s="77"/>
+    </row>
+    <row r="35" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B35" s="80">
+        <v>3</v>
+      </c>
+      <c r="C35" s="94" t="s">
+        <v>284</v>
+      </c>
+      <c r="D35" s="95"/>
+      <c r="E35" s="81">
+        <f>'3.Electrica'!I28</f>
+        <v>5</v>
+      </c>
+      <c r="F35" s="77"/>
+      <c r="G35" s="77"/>
+      <c r="H35" s="77"/>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B36" s="80">
+        <v>4</v>
+      </c>
+      <c r="C36" s="92" t="s">
+        <v>330</v>
+      </c>
+      <c r="D36" s="93"/>
+      <c r="E36" s="81">
+        <f>'4.Bodegaje'!I24</f>
+        <v>5</v>
+      </c>
+      <c r="F36" s="77"/>
+      <c r="G36" s="77"/>
+      <c r="H36" s="77"/>
+    </row>
+    <row r="37" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B37" s="80">
+        <v>4</v>
+      </c>
+      <c r="C37" s="94" t="s">
         <v>285</v>
       </c>
-      <c r="C32" s="104"/>
-      <c r="D32" s="104"/>
-      <c r="E32" s="104"/>
-      <c r="F32" s="76"/>
-      <c r="G32" s="76"/>
-      <c r="H32" s="76"/>
-    </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B33" s="77" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" s="106" t="s">
-        <v>40</v>
-      </c>
-      <c r="D33" s="107"/>
-      <c r="E33" s="78" t="s">
-        <v>27</v>
-      </c>
-      <c r="F33" s="76"/>
-      <c r="G33" s="76"/>
-      <c r="H33" s="76"/>
-    </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B34" s="79">
-        <v>1</v>
-      </c>
-      <c r="C34" s="108" t="s">
+      <c r="D37" s="95"/>
+      <c r="E37" s="81">
+        <f>'5.Planos'!I17</f>
+        <v>5</v>
+      </c>
+      <c r="F37" s="77"/>
+      <c r="G37" s="77"/>
+      <c r="H37" s="77"/>
+    </row>
+    <row r="38" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B38" s="80">
+        <v>5</v>
+      </c>
+      <c r="C38" s="94" t="s">
         <v>286</v>
       </c>
-      <c r="D34" s="109"/>
-      <c r="E34" s="80">
-        <f>'1.Tecnica'!H19</f>
+      <c r="D38" s="95"/>
+      <c r="E38" s="81">
+        <f>'5.Archivos'!I17</f>
         <v>5</v>
       </c>
-      <c r="F34" s="76"/>
-      <c r="G34" s="76"/>
-      <c r="H34" s="76"/>
-    </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B35" s="79">
-        <v>2</v>
-      </c>
-      <c r="C35" s="93" t="s">
-        <v>335</v>
-      </c>
-      <c r="D35" s="94"/>
-      <c r="E35" s="80">
-        <f>'2.ArquitectonicaEstructural'!H104</f>
+      <c r="F38" s="77"/>
+      <c r="G38" s="77"/>
+      <c r="H38" s="77"/>
+    </row>
+    <row r="39" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B39" s="80">
+        <v>6</v>
+      </c>
+      <c r="C39" s="94" t="s">
+        <v>314</v>
+      </c>
+      <c r="D39" s="95"/>
+      <c r="E39" s="90">
         <v>5</v>
       </c>
-      <c r="F35" s="76"/>
-      <c r="G35" s="76"/>
-      <c r="H35" s="76"/>
-    </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B36" s="79">
-        <v>3</v>
-      </c>
-      <c r="C36" s="93" t="s">
-        <v>287</v>
-      </c>
-      <c r="D36" s="94"/>
-      <c r="E36" s="80">
-        <f>'3.Electrica'!H28</f>
-        <v>5</v>
-      </c>
-      <c r="F36" s="76"/>
-      <c r="G36" s="76"/>
-      <c r="H36" s="76"/>
-    </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B37" s="79">
-        <v>4</v>
-      </c>
-      <c r="C37" s="91" t="s">
-        <v>334</v>
-      </c>
-      <c r="D37" s="92"/>
-      <c r="E37" s="80">
-        <f>'4.Bodegaje'!H24</f>
-        <v>5</v>
-      </c>
-      <c r="F37" s="76"/>
-      <c r="G37" s="76"/>
-      <c r="H37" s="76"/>
-    </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B38" s="79">
-        <v>4</v>
-      </c>
-      <c r="C38" s="93" t="s">
-        <v>288</v>
-      </c>
-      <c r="D38" s="94"/>
-      <c r="E38" s="80">
-        <f>'5.Planos'!H17</f>
-        <v>5</v>
-      </c>
-      <c r="F38" s="76"/>
-      <c r="G38" s="76"/>
-      <c r="H38" s="76"/>
-    </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B39" s="79">
-        <v>5</v>
-      </c>
-      <c r="C39" s="93" t="s">
-        <v>289</v>
-      </c>
-      <c r="D39" s="94"/>
-      <c r="E39" s="80">
-        <f>'5.Archivos'!G17</f>
-        <v>5</v>
-      </c>
-      <c r="F39" s="76"/>
-      <c r="G39" s="76"/>
-      <c r="H39" s="76"/>
+      <c r="F39" s="77"/>
+      <c r="G39" s="77"/>
+      <c r="H39" s="77"/>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B40" s="79">
-        <v>6</v>
-      </c>
-      <c r="C40" s="93" t="s">
-        <v>317</v>
-      </c>
-      <c r="D40" s="94"/>
+      <c r="B40" s="82">
+        <v>7</v>
+      </c>
+      <c r="C40" s="96" t="s">
+        <v>315</v>
+      </c>
+      <c r="D40" s="97"/>
       <c r="E40" s="89">
         <v>5</v>
       </c>
-      <c r="F40" s="76"/>
-      <c r="G40" s="76"/>
-      <c r="H40" s="76"/>
+      <c r="F40" s="77"/>
+      <c r="G40" s="77"/>
+      <c r="H40" s="77"/>
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B41" s="81">
-        <v>7</v>
-      </c>
-      <c r="C41" s="95" t="s">
-        <v>318</v>
-      </c>
-      <c r="D41" s="96"/>
-      <c r="E41" s="88">
+      <c r="B41" s="77"/>
+      <c r="C41" s="77"/>
+      <c r="D41" s="75" t="s">
+        <v>290</v>
+      </c>
+      <c r="E41" s="91">
+        <f>AVERAGE(E33:E40)</f>
         <v>5</v>
       </c>
-      <c r="F41" s="76"/>
-      <c r="G41" s="76"/>
-      <c r="H41" s="76"/>
+      <c r="F41" s="77"/>
+      <c r="G41" s="77"/>
+      <c r="H41" s="77"/>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B42" s="76"/>
-      <c r="C42" s="76"/>
-      <c r="D42" s="74" t="s">
-        <v>293</v>
-      </c>
-      <c r="E42" s="90">
-        <f>AVERAGE(E34:E41)</f>
-        <v>5</v>
-      </c>
-      <c r="F42" s="76"/>
-      <c r="G42" s="76"/>
-      <c r="H42" s="76"/>
+      <c r="B42" s="77"/>
+      <c r="C42" s="77"/>
+      <c r="D42" s="77"/>
+      <c r="E42" s="77"/>
+      <c r="F42" s="77"/>
+      <c r="G42" s="77"/>
+      <c r="H42" s="77"/>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B43" s="76"/>
-      <c r="C43" s="76"/>
-      <c r="D43" s="76"/>
-      <c r="E43" s="76"/>
-      <c r="F43" s="76"/>
-      <c r="G43" s="76"/>
-      <c r="H43" s="76"/>
+      <c r="B43" s="77"/>
+      <c r="C43" s="77"/>
+      <c r="D43" s="77"/>
+      <c r="E43" s="77"/>
+      <c r="F43" s="77"/>
+      <c r="G43" s="77"/>
+      <c r="H43" s="77"/>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B44" s="76"/>
-      <c r="C44" s="76"/>
-      <c r="D44" s="76"/>
-      <c r="E44" s="76"/>
-      <c r="F44" s="76"/>
-      <c r="G44" s="76"/>
-      <c r="H44" s="76"/>
+      <c r="B44" s="77"/>
+      <c r="C44" s="77"/>
+      <c r="D44" s="77"/>
+      <c r="E44" s="77"/>
+      <c r="F44" s="77"/>
+      <c r="G44" s="77"/>
+      <c r="H44" s="77"/>
     </row>
     <row r="45" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B45" s="76"/>
-      <c r="C45" s="76"/>
-      <c r="D45" s="76"/>
-      <c r="E45" s="76"/>
-      <c r="F45" s="76"/>
-      <c r="G45" s="76"/>
-      <c r="H45" s="76"/>
-    </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B46" s="76"/>
-      <c r="C46" s="76"/>
-      <c r="D46" s="76"/>
-      <c r="E46" s="76"/>
-      <c r="F46" s="76"/>
-      <c r="G46" s="76"/>
-      <c r="H46" s="76"/>
+      <c r="B45" s="77"/>
+      <c r="C45" s="77"/>
+      <c r="D45" s="77"/>
+      <c r="E45" s="77"/>
+      <c r="F45" s="77"/>
+      <c r="G45" s="77"/>
+      <c r="H45" s="77"/>
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="B4:E6"/>
+    <mergeCell ref="B4:E5"/>
+    <mergeCell ref="C32:D32"/>
     <mergeCell ref="C33:D33"/>
     <mergeCell ref="C34:D34"/>
     <mergeCell ref="C35:D35"/>
-    <mergeCell ref="C36:D36"/>
+    <mergeCell ref="B6:E6"/>
     <mergeCell ref="B7:E7"/>
     <mergeCell ref="B8:E8"/>
     <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B10:E10"/>
-    <mergeCell ref="B11:E12"/>
-    <mergeCell ref="B13:E13"/>
+    <mergeCell ref="B10:E11"/>
+    <mergeCell ref="B12:E12"/>
+    <mergeCell ref="C38:D38"/>
     <mergeCell ref="C39:D39"/>
     <mergeCell ref="C40:D40"/>
-    <mergeCell ref="C41:D41"/>
-    <mergeCell ref="B14:E15"/>
-    <mergeCell ref="B18:E18"/>
-    <mergeCell ref="B32:E32"/>
-    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="B13:E14"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="B31:E31"/>
+    <mergeCell ref="C37:D37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -3231,1875 +3339,2258 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0659C4DD-D653-4634-8C4F-29057F021A54}">
-  <dimension ref="B1:H19"/>
+  <dimension ref="B1:I19"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.5546875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="30.109375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="50.5546875" style="2" customWidth="1"/>
-    <col min="4" max="4" width="15.5546875" style="2" customWidth="1"/>
-    <col min="5" max="5" width="9.109375" style="2"/>
-    <col min="6" max="6" width="12.21875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="20.21875" style="82" customWidth="1"/>
-    <col min="8" max="8" width="12.44140625" style="47" customWidth="1"/>
-    <col min="9" max="16384" width="9.109375" style="2"/>
+    <col min="2" max="2" width="30.77734375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="50.77734375" style="2" customWidth="1"/>
+    <col min="4" max="5" width="10.77734375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="7.77734375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="3.77734375" style="65" customWidth="1"/>
+    <col min="8" max="8" width="30.77734375" style="83" customWidth="1"/>
+    <col min="9" max="9" width="12.77734375" style="47" customWidth="1"/>
+    <col min="10" max="16384" width="9.109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="2:9" x14ac:dyDescent="0.3">
       <c r="E1" s="24"/>
     </row>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="20" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B4" s="105" t="s">
-        <v>291</v>
-      </c>
-      <c r="C4" s="105"/>
-      <c r="D4" s="105"/>
-      <c r="E4" s="105"/>
-    </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B5" s="105"/>
-      <c r="C5" s="105"/>
-      <c r="D5" s="105"/>
-      <c r="E5" s="105"/>
-    </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B4" s="106" t="s">
+        <v>288</v>
+      </c>
+      <c r="C4" s="106"/>
+      <c r="D4" s="106"/>
+      <c r="E4" s="106"/>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B5" s="106"/>
+      <c r="C5" s="106"/>
+      <c r="D5" s="106"/>
+      <c r="E5" s="106"/>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B6" s="37" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C6" s="38" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D6" s="39" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E6" s="39" t="s">
-        <v>53</v>
-      </c>
-      <c r="F6" s="39" t="s">
-        <v>42</v>
-      </c>
-      <c r="G6" s="38" t="s">
+        <v>50</v>
+      </c>
+      <c r="F6" s="121" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" s="122"/>
+      <c r="H6" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="H6" s="68" t="s">
+      <c r="I6" s="69" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="B7" s="32" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="C7" s="35" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="D7" s="36">
         <v>1</v>
       </c>
       <c r="E7" s="31" t="s">
-        <v>126</v>
-      </c>
-      <c r="F7" s="31"/>
-      <c r="G7" s="35"/>
-      <c r="H7" s="70">
+        <v>123</v>
+      </c>
+      <c r="F7" s="125" t="s">
+        <v>332</v>
+      </c>
+      <c r="G7" s="119" t="str">
+        <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F7,"/Readme.md"),"Ver")</f>
+        <v>Ver</v>
+      </c>
+      <c r="H7" s="35"/>
+      <c r="I7" s="71">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B8" s="32" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="D8" s="36">
         <v>1</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>126</v>
-      </c>
-      <c r="F8" s="31"/>
-      <c r="G8" s="35"/>
-      <c r="H8" s="70"/>
-    </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+      <c r="F8" s="125" t="s">
+        <v>332</v>
+      </c>
+      <c r="G8" s="119" t="str">
+        <f t="shared" ref="G8:G18" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F8,"/Readme.md"),"Ver")</f>
+        <v>Ver</v>
+      </c>
+      <c r="H8" s="35"/>
+      <c r="I8" s="71"/>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B9" s="32" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="C9" s="35" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="D9" s="36">
         <v>1</v>
       </c>
       <c r="E9" s="31" t="s">
-        <v>126</v>
-      </c>
-      <c r="F9" s="31"/>
-      <c r="G9" s="35"/>
-      <c r="H9" s="70"/>
-    </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+      <c r="F9" s="125" t="s">
+        <v>332</v>
+      </c>
+      <c r="G9" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H9" s="35"/>
+      <c r="I9" s="71"/>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B10" s="32" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="C10" s="35" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="D10" s="36">
         <v>1</v>
       </c>
       <c r="E10" s="31" t="s">
-        <v>126</v>
-      </c>
-      <c r="F10" s="31"/>
-      <c r="G10" s="35"/>
-      <c r="H10" s="70"/>
-    </row>
-    <row r="11" spans="2:8" ht="33.6" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+      <c r="F10" s="125" t="s">
+        <v>333</v>
+      </c>
+      <c r="G10" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H10" s="35"/>
+      <c r="I10" s="71"/>
+    </row>
+    <row r="11" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
       <c r="B11" s="32" t="s">
+        <v>295</v>
+      </c>
+      <c r="C11" s="35" t="s">
         <v>298</v>
-      </c>
-      <c r="C11" s="35" t="s">
-        <v>301</v>
       </c>
       <c r="D11" s="36">
         <v>1</v>
       </c>
       <c r="E11" s="31" t="s">
-        <v>126</v>
-      </c>
-      <c r="F11" s="31"/>
-      <c r="G11" s="35"/>
-      <c r="H11" s="70"/>
-    </row>
-    <row r="12" spans="2:8" ht="57" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+      <c r="F11" s="125" t="s">
+        <v>334</v>
+      </c>
+      <c r="G11" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H11" s="35"/>
+      <c r="I11" s="71"/>
+    </row>
+    <row r="12" spans="2:9" ht="57" x14ac:dyDescent="0.3">
       <c r="B12" s="32" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="C12" s="35" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="D12" s="36">
         <v>1</v>
       </c>
       <c r="E12" s="31" t="s">
-        <v>126</v>
-      </c>
-      <c r="F12" s="31"/>
-      <c r="G12" s="35"/>
-      <c r="H12" s="70"/>
-    </row>
-    <row r="13" spans="2:8" ht="22.8" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+      <c r="F12" s="125" t="s">
+        <v>335</v>
+      </c>
+      <c r="G12" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H12" s="35"/>
+      <c r="I12" s="71"/>
+    </row>
+    <row r="13" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B13" s="32" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="C13" s="35" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D13" s="36">
         <v>1</v>
       </c>
       <c r="E13" s="31" t="s">
-        <v>126</v>
-      </c>
-      <c r="F13" s="31"/>
-      <c r="G13" s="35"/>
-      <c r="H13" s="70"/>
-    </row>
-    <row r="14" spans="2:8" ht="33.6" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+      <c r="F13" s="125" t="s">
+        <v>336</v>
+      </c>
+      <c r="G13" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H13" s="35"/>
+      <c r="I13" s="71"/>
+    </row>
+    <row r="14" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
       <c r="B14" s="32" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="C14" s="35" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="D14" s="36">
         <v>1</v>
       </c>
       <c r="E14" s="31" t="s">
-        <v>126</v>
-      </c>
-      <c r="F14" s="31"/>
-      <c r="G14" s="35"/>
-      <c r="H14" s="70"/>
-    </row>
-    <row r="15" spans="2:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+      <c r="F14" s="125" t="s">
+        <v>333</v>
+      </c>
+      <c r="G14" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H14" s="35"/>
+      <c r="I14" s="71"/>
+    </row>
+    <row r="15" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="B15" s="32" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="C15" s="35" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="D15" s="36">
         <v>1</v>
       </c>
       <c r="E15" s="31" t="s">
-        <v>126</v>
-      </c>
-      <c r="F15" s="31"/>
-      <c r="G15" s="35"/>
-      <c r="H15" s="70"/>
-    </row>
-    <row r="16" spans="2:8" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+      <c r="F15" s="125" t="s">
+        <v>337</v>
+      </c>
+      <c r="G15" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H15" s="35"/>
+      <c r="I15" s="71"/>
+    </row>
+    <row r="16" spans="2:9" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="32" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="C16" s="35" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="D16" s="36">
         <v>1</v>
       </c>
       <c r="E16" s="31" t="s">
-        <v>126</v>
-      </c>
-      <c r="F16" s="31"/>
-      <c r="G16" s="35"/>
-      <c r="H16" s="70"/>
-    </row>
-    <row r="17" spans="2:8" ht="35.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+      <c r="F16" s="125" t="s">
+        <v>337</v>
+      </c>
+      <c r="G16" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H16" s="35"/>
+      <c r="I16" s="71"/>
+    </row>
+    <row r="17" spans="2:9" ht="35.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="43" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="C17" s="44" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="D17" s="36">
         <v>1</v>
       </c>
       <c r="E17" s="31" t="s">
-        <v>126</v>
-      </c>
-      <c r="F17" s="45"/>
-      <c r="G17" s="44"/>
-      <c r="H17" s="71"/>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+      <c r="F17" s="125" t="s">
+        <v>337</v>
+      </c>
+      <c r="G17" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H17" s="44"/>
+      <c r="I17" s="72"/>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B18" s="40"/>
       <c r="C18" s="41"/>
-      <c r="D18" s="66"/>
+      <c r="D18" s="67"/>
       <c r="E18" s="42"/>
-      <c r="F18" s="42"/>
-      <c r="G18" s="41"/>
-      <c r="H18" s="72"/>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="G19" s="75" t="s">
-        <v>293</v>
-      </c>
-      <c r="H19" s="47">
-        <f>AVERAGE(H7:H18)</f>
+      <c r="F18" s="126"/>
+      <c r="G18" s="120" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H18" s="41"/>
+      <c r="I18" s="73"/>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H19" s="76" t="s">
+        <v>290</v>
+      </c>
+      <c r="I19" s="47">
+        <f>AVERAGE(I7:I18)</f>
         <v>5</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
     <mergeCell ref="B4:E5"/>
+    <mergeCell ref="F6:G6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1EE59D4-4937-4491-BD3F-7DBC007EDF85}">
-  <dimension ref="B2:H114"/>
+  <dimension ref="B2:I113"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.5546875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="27.109375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="41" style="2" customWidth="1"/>
-    <col min="4" max="6" width="9.21875" style="47" customWidth="1"/>
-    <col min="7" max="7" width="28.5546875" style="82" customWidth="1"/>
-    <col min="8" max="8" width="14.88671875" style="47" customWidth="1"/>
-    <col min="9" max="9" width="2.5546875" style="2" customWidth="1"/>
-    <col min="10" max="16384" width="9.109375" style="2"/>
+    <col min="2" max="2" width="30.77734375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="50.77734375" style="2" customWidth="1"/>
+    <col min="4" max="5" width="10.77734375" style="47" customWidth="1"/>
+    <col min="6" max="6" width="7.77734375" style="127" customWidth="1"/>
+    <col min="7" max="7" width="3.77734375" style="47" customWidth="1"/>
+    <col min="8" max="8" width="30.77734375" style="83" customWidth="1"/>
+    <col min="9" max="9" width="12.77734375" style="47" customWidth="1"/>
+    <col min="10" max="10" width="2.5546875" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="9.109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="20" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B4" s="105" t="s">
-        <v>241</v>
-      </c>
-      <c r="C4" s="105"/>
-      <c r="D4" s="105"/>
-      <c r="E4" s="105"/>
-      <c r="F4" s="105"/>
-      <c r="G4" s="105"/>
-      <c r="H4" s="105"/>
-    </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B5" s="116"/>
-      <c r="C5" s="116"/>
-      <c r="D5" s="116"/>
-      <c r="E5" s="116"/>
-      <c r="F5" s="116"/>
-      <c r="G5" s="116"/>
-      <c r="H5" s="116"/>
-    </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.3">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B4" s="106" t="s">
+        <v>238</v>
+      </c>
+      <c r="C4" s="106"/>
+      <c r="D4" s="106"/>
+      <c r="E4" s="106"/>
+      <c r="F4" s="106"/>
+      <c r="G4" s="106"/>
+      <c r="H4" s="106"/>
+      <c r="I4" s="106"/>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B5" s="117"/>
+      <c r="C5" s="117"/>
+      <c r="D5" s="117"/>
+      <c r="E5" s="117"/>
+      <c r="F5" s="117"/>
+      <c r="G5" s="117"/>
+      <c r="H5" s="117"/>
+      <c r="I5" s="117"/>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B6" s="37" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C6" s="38" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D6" s="39" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E6" s="39" t="s">
-        <v>53</v>
-      </c>
-      <c r="F6" s="39" t="s">
-        <v>42</v>
-      </c>
-      <c r="G6" s="38" t="s">
+        <v>50</v>
+      </c>
+      <c r="F6" s="123" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" s="124"/>
+      <c r="H6" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="H6" s="68" t="s">
+      <c r="I6" s="69" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B7" s="6" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C7" s="33"/>
       <c r="D7" s="34"/>
       <c r="E7" s="34"/>
-      <c r="F7" s="34"/>
-      <c r="G7" s="83"/>
-      <c r="H7" s="69"/>
-    </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="F7" s="128"/>
+      <c r="G7" s="34"/>
+      <c r="H7" s="84"/>
+      <c r="I7" s="70"/>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B8" s="32" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D8" s="36">
         <v>8</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>57</v>
-      </c>
-      <c r="F8" s="31"/>
-      <c r="G8" s="35" t="s">
-        <v>315</v>
-      </c>
-      <c r="H8" s="70">
+        <v>54</v>
+      </c>
+      <c r="F8" s="125"/>
+      <c r="G8" s="119" t="str">
+        <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F8,"/Readme.md"),"Ver")</f>
+        <v>Ver</v>
+      </c>
+      <c r="H8" s="35" t="s">
+        <v>312</v>
+      </c>
+      <c r="I8" s="71">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B9" s="32" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C9" s="35" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="D9" s="36">
         <v>10</v>
       </c>
       <c r="E9" s="31" t="s">
-        <v>57</v>
-      </c>
-      <c r="F9" s="31"/>
-      <c r="G9" s="35" t="s">
-        <v>315</v>
-      </c>
-      <c r="H9" s="70"/>
-    </row>
-    <row r="10" spans="2:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="F9" s="125"/>
+      <c r="G9" s="119" t="str">
+        <f t="shared" ref="G9:G72" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F9,"/Readme.md"),"Ver")</f>
+        <v>Ver</v>
+      </c>
+      <c r="H9" s="35" t="s">
+        <v>312</v>
+      </c>
+      <c r="I9" s="71"/>
+    </row>
+    <row r="10" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B10" s="32" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="C10" s="35" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D10" s="31">
         <f>D8+SumUDig</f>
         <v>35</v>
       </c>
       <c r="E10" s="31" t="s">
-        <v>57</v>
-      </c>
-      <c r="F10" s="31"/>
-      <c r="G10" s="35"/>
-      <c r="H10" s="70"/>
-    </row>
-    <row r="11" spans="2:8" ht="22.8" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="F10" s="125"/>
+      <c r="G10" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H10" s="35"/>
+      <c r="I10" s="71"/>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B11" s="32" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D11" s="31" cm="1">
         <f t="array" ref="D11">D9+SumUDig</f>
         <v>37</v>
       </c>
       <c r="E11" s="31" t="s">
-        <v>57</v>
-      </c>
-      <c r="F11" s="31"/>
-      <c r="G11" s="35"/>
-      <c r="H11" s="70"/>
-    </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="F11" s="125"/>
+      <c r="G11" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H11" s="35"/>
+      <c r="I11" s="71"/>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B12" s="32" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C12" s="35" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D12" s="36">
         <v>12</v>
       </c>
       <c r="E12" s="31" t="s">
-        <v>57</v>
-      </c>
-      <c r="F12" s="31"/>
-      <c r="G12" s="35" t="s">
-        <v>315</v>
-      </c>
-      <c r="H12" s="70"/>
-    </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="F12" s="125"/>
+      <c r="G12" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H12" s="35" t="s">
+        <v>312</v>
+      </c>
+      <c r="I12" s="71"/>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B13" s="32" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="C13" s="35" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="D13" s="36">
         <v>6</v>
       </c>
       <c r="E13" s="31" t="s">
-        <v>57</v>
-      </c>
-      <c r="F13" s="31"/>
-      <c r="G13" s="35" t="s">
-        <v>315</v>
-      </c>
-      <c r="H13" s="70"/>
-    </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="F13" s="125"/>
+      <c r="G13" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H13" s="35" t="s">
+        <v>312</v>
+      </c>
+      <c r="I13" s="71"/>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B14" s="32" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C14" s="35" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="D14" s="36">
         <v>12</v>
       </c>
       <c r="E14" s="31" t="s">
-        <v>57</v>
-      </c>
-      <c r="F14" s="31"/>
-      <c r="G14" s="35" t="s">
-        <v>315</v>
-      </c>
-      <c r="H14" s="70"/>
-    </row>
-    <row r="15" spans="2:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="F14" s="125"/>
+      <c r="G14" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H14" s="35" t="s">
+        <v>312</v>
+      </c>
+      <c r="I14" s="71"/>
+    </row>
+    <row r="15" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B15" s="32" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C15" s="35" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="D15" s="31">
         <f>D10</f>
         <v>35</v>
       </c>
       <c r="E15" s="31" t="s">
-        <v>57</v>
-      </c>
-      <c r="F15" s="31"/>
-      <c r="G15" s="35"/>
-      <c r="H15" s="70"/>
-    </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="F15" s="125"/>
+      <c r="G15" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H15" s="35"/>
+      <c r="I15" s="71"/>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B16" s="32" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C16" s="35" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="D16" s="31">
         <f>D11+D14+D13</f>
         <v>55</v>
       </c>
       <c r="E16" s="31" t="s">
-        <v>57</v>
-      </c>
-      <c r="F16" s="31"/>
-      <c r="G16" s="35"/>
-      <c r="H16" s="70"/>
-    </row>
-    <row r="17" spans="2:8" ht="22.8" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="F16" s="125"/>
+      <c r="G16" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H16" s="35"/>
+      <c r="I16" s="71"/>
+    </row>
+    <row r="17" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B17" s="32" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C17" s="35" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D17" s="31">
         <f>D16*D15</f>
         <v>1925</v>
       </c>
       <c r="E17" s="31" t="s">
-        <v>58</v>
-      </c>
-      <c r="F17" s="31"/>
-      <c r="G17" s="35"/>
-      <c r="H17" s="70"/>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+      <c r="F17" s="125"/>
+      <c r="G17" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H17" s="35"/>
+      <c r="I17" s="71"/>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B18" s="43" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="C18" s="44" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="D18" s="45">
         <f>D32+D30</f>
         <v>1435</v>
       </c>
       <c r="E18" s="31" t="s">
-        <v>58</v>
-      </c>
-      <c r="F18" s="45"/>
-      <c r="G18" s="44"/>
-      <c r="H18" s="71"/>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+      <c r="F18" s="129"/>
+      <c r="G18" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H18" s="44"/>
+      <c r="I18" s="72"/>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B19" s="43" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="C19" s="44" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="D19" s="45">
         <f>D32+D30+D46</f>
         <v>1495</v>
       </c>
       <c r="E19" s="31" t="s">
-        <v>58</v>
-      </c>
-      <c r="F19" s="45"/>
-      <c r="G19" s="44"/>
-      <c r="H19" s="71"/>
-    </row>
-    <row r="20" spans="2:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+      <c r="F19" s="129"/>
+      <c r="G19" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H19" s="44"/>
+      <c r="I19" s="72"/>
+    </row>
+    <row r="20" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="B20" s="43" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C20" s="44" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D20" s="45">
         <f>D18/D17</f>
         <v>0.74545454545454548</v>
       </c>
       <c r="E20" s="45" t="s">
-        <v>75</v>
-      </c>
-      <c r="F20" s="45"/>
-      <c r="G20" s="44"/>
-      <c r="H20" s="71"/>
-    </row>
-    <row r="21" spans="2:8" ht="22.8" x14ac:dyDescent="0.3">
+        <v>72</v>
+      </c>
+      <c r="F20" s="129"/>
+      <c r="G20" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H20" s="44"/>
+      <c r="I20" s="72"/>
+    </row>
+    <row r="21" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B21" s="43" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C21" s="44" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D21" s="45">
         <f>D19/D17</f>
         <v>0.77662337662337666</v>
       </c>
       <c r="E21" s="45" t="s">
-        <v>75</v>
-      </c>
-      <c r="F21" s="45"/>
-      <c r="G21" s="44"/>
-      <c r="H21" s="71"/>
-    </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
+        <v>72</v>
+      </c>
+      <c r="F21" s="129"/>
+      <c r="G21" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H21" s="44"/>
+      <c r="I21" s="72"/>
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B22" s="40"/>
       <c r="C22" s="41"/>
       <c r="D22" s="42"/>
       <c r="E22" s="42"/>
-      <c r="F22" s="42"/>
-      <c r="G22" s="41"/>
-      <c r="H22" s="72"/>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="F22" s="126"/>
+      <c r="G22" s="120" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H22" s="41"/>
+      <c r="I22" s="73"/>
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B23" s="6" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C23" s="33"/>
       <c r="D23" s="34"/>
       <c r="E23" s="34"/>
-      <c r="F23" s="34"/>
-      <c r="G23" s="83"/>
-      <c r="H23" s="69"/>
-    </row>
-    <row r="24" spans="2:8" ht="45.6" x14ac:dyDescent="0.3">
+      <c r="F23" s="128"/>
+      <c r="G23" s="34"/>
+      <c r="H23" s="84"/>
+      <c r="I23" s="70"/>
+    </row>
+    <row r="24" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="B24" s="32" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C24" s="35" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D24" s="36">
         <v>2</v>
       </c>
       <c r="E24" s="31" t="s">
-        <v>57</v>
-      </c>
-      <c r="F24" s="31"/>
-      <c r="G24" s="35"/>
-      <c r="H24" s="70">
+        <v>54</v>
+      </c>
+      <c r="F24" s="125"/>
+      <c r="G24" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H24" s="35"/>
+      <c r="I24" s="71">
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="2:8" ht="68.400000000000006" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:9" ht="57" x14ac:dyDescent="0.3">
       <c r="B25" s="32" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="C25" s="35" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="D25" s="49">
         <v>5</v>
       </c>
       <c r="E25" s="31" t="s">
-        <v>76</v>
-      </c>
-      <c r="F25" s="31"/>
-      <c r="G25" s="35"/>
-      <c r="H25" s="70"/>
-    </row>
-    <row r="26" spans="2:8" ht="45.6" x14ac:dyDescent="0.3">
+        <v>73</v>
+      </c>
+      <c r="F25" s="125"/>
+      <c r="G25" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H25" s="35"/>
+      <c r="I25" s="71"/>
+    </row>
+    <row r="26" spans="2:9" ht="45.6" x14ac:dyDescent="0.3">
       <c r="B26" s="32" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="C26" s="35" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="D26" s="31">
         <f>ROUND(ATAN(D25/100)*180/PI(),0)</f>
         <v>3</v>
       </c>
       <c r="E26" s="31" t="s">
-        <v>77</v>
-      </c>
-      <c r="F26" s="31"/>
-      <c r="G26" s="35"/>
-      <c r="H26" s="70"/>
-    </row>
-    <row r="27" spans="2:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+        <v>74</v>
+      </c>
+      <c r="F26" s="125"/>
+      <c r="G26" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H26" s="35"/>
+      <c r="I26" s="71"/>
+    </row>
+    <row r="27" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="B27" s="43" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C27" s="44" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D27" s="50">
         <v>0.6</v>
       </c>
       <c r="E27" s="45" t="s">
-        <v>57</v>
-      </c>
-      <c r="F27" s="45"/>
-      <c r="G27" s="44"/>
-      <c r="H27" s="71"/>
-    </row>
-    <row r="28" spans="2:8" ht="33.6" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="F27" s="129"/>
+      <c r="G27" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H27" s="44"/>
+      <c r="I27" s="72"/>
+    </row>
+    <row r="28" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
       <c r="B28" s="32" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="C28" s="35" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D28" s="36">
         <v>0.2</v>
       </c>
       <c r="E28" s="31" t="s">
-        <v>57</v>
-      </c>
-      <c r="F28" s="31"/>
-      <c r="G28" s="35"/>
-      <c r="H28" s="70"/>
-    </row>
-    <row r="29" spans="2:8" ht="22.8" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="F28" s="125"/>
+      <c r="G28" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H28" s="35"/>
+      <c r="I28" s="71"/>
+    </row>
+    <row r="29" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B29" s="32" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C29" s="35" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D29" s="36">
         <v>2</v>
       </c>
       <c r="E29" s="31" t="s">
-        <v>75</v>
-      </c>
-      <c r="F29" s="31"/>
-      <c r="G29" s="35"/>
-      <c r="H29" s="70"/>
-    </row>
-    <row r="30" spans="2:8" ht="33.6" x14ac:dyDescent="0.3">
+        <v>72</v>
+      </c>
+      <c r="F29" s="125"/>
+      <c r="G29" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H29" s="35"/>
+      <c r="I29" s="71"/>
+    </row>
+    <row r="30" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B30" s="43" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C30" s="44" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D30" s="45">
         <f>(D27-D28)*(D11+D24+D24)*D29</f>
         <v>32.799999999999997</v>
       </c>
       <c r="E30" s="31" t="s">
-        <v>58</v>
-      </c>
-      <c r="F30" s="45"/>
-      <c r="G30" s="44"/>
-      <c r="H30" s="71"/>
-    </row>
-    <row r="31" spans="2:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+      <c r="F30" s="129"/>
+      <c r="G30" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H30" s="44"/>
+      <c r="I30" s="72"/>
+    </row>
+    <row r="31" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="B31" s="32" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C31" s="35" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D31" s="31">
         <f>(D10*D11)-D30</f>
         <v>1262.2</v>
       </c>
       <c r="E31" s="31" t="s">
-        <v>58</v>
-      </c>
-      <c r="F31" s="31"/>
-      <c r="G31" s="35"/>
-      <c r="H31" s="70"/>
-    </row>
-    <row r="32" spans="2:8" ht="45.6" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+      <c r="F31" s="125"/>
+      <c r="G31" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H31" s="35"/>
+      <c r="I31" s="71"/>
+    </row>
+    <row r="32" spans="2:9" ht="45.6" x14ac:dyDescent="0.3">
       <c r="B32" s="32" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C32" s="35" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D32" s="31">
         <f>((D10*D11)+D10*(D24+D24))-D30</f>
         <v>1402.2</v>
       </c>
       <c r="E32" s="31" t="s">
-        <v>58</v>
-      </c>
-      <c r="F32" s="31"/>
-      <c r="G32" s="35"/>
-      <c r="H32" s="70"/>
-    </row>
-    <row r="33" spans="2:8" ht="22.8" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+      <c r="F32" s="125"/>
+      <c r="G32" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H32" s="35"/>
+      <c r="I32" s="71"/>
+    </row>
+    <row r="33" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B33" s="32" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C33" s="35" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D33" s="36">
         <v>10</v>
       </c>
       <c r="E33" s="31" t="s">
-        <v>57</v>
-      </c>
-      <c r="F33" s="31"/>
-      <c r="G33" s="35"/>
-      <c r="H33" s="70"/>
-    </row>
-    <row r="34" spans="2:8" ht="45.6" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="F33" s="125"/>
+      <c r="G33" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H33" s="35"/>
+      <c r="I33" s="71"/>
+    </row>
+    <row r="34" spans="2:9" ht="45.6" x14ac:dyDescent="0.3">
       <c r="B34" s="32" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C34" s="35" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D34" s="31">
         <f>EVEN(D31/(D33*D33))</f>
         <v>14</v>
       </c>
       <c r="E34" s="31" t="s">
-        <v>126</v>
-      </c>
-      <c r="F34" s="31"/>
-      <c r="G34" s="35"/>
-      <c r="H34" s="70"/>
-    </row>
-    <row r="35" spans="2:8" ht="22.8" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+      <c r="F34" s="125"/>
+      <c r="G34" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H34" s="35"/>
+      <c r="I34" s="71"/>
+    </row>
+    <row r="35" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B35" s="32" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="C35" s="35" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D35" s="36">
         <v>1200</v>
       </c>
       <c r="E35" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="F35" s="31"/>
-      <c r="G35" s="35"/>
-      <c r="H35" s="70"/>
-    </row>
-    <row r="36" spans="2:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+      <c r="F35" s="125"/>
+      <c r="G35" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H35" s="35"/>
+      <c r="I35" s="71"/>
+    </row>
+    <row r="36" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B36" s="32" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C36" s="35" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D36" s="31">
         <f>D35*D35/(1000*1000)</f>
         <v>1.44</v>
       </c>
       <c r="E36" s="31" t="s">
-        <v>58</v>
-      </c>
-      <c r="F36" s="31"/>
-      <c r="G36" s="35"/>
-      <c r="H36" s="70"/>
-    </row>
-    <row r="37" spans="2:8" ht="33.6" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+      <c r="F36" s="125"/>
+      <c r="G36" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H36" s="35"/>
+      <c r="I36" s="71"/>
+    </row>
+    <row r="37" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
       <c r="B37" s="32" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C37" s="35" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="D37" s="31">
         <f>D34*D36</f>
         <v>20.16</v>
       </c>
       <c r="E37" s="31" t="s">
-        <v>58</v>
-      </c>
-      <c r="F37" s="31"/>
-      <c r="G37" s="35"/>
-      <c r="H37" s="70"/>
-    </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+      <c r="F37" s="125"/>
+      <c r="G37" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H37" s="35"/>
+      <c r="I37" s="71"/>
+    </row>
+    <row r="38" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B38" s="40"/>
       <c r="C38" s="41"/>
       <c r="D38" s="42"/>
       <c r="E38" s="42"/>
-      <c r="F38" s="42"/>
-      <c r="G38" s="41"/>
-      <c r="H38" s="72"/>
-    </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="F38" s="126"/>
+      <c r="G38" s="120" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H38" s="41"/>
+      <c r="I38" s="73"/>
+    </row>
+    <row r="39" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B39" s="48" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="C39" s="33"/>
       <c r="D39" s="34"/>
       <c r="E39" s="34"/>
-      <c r="F39" s="34"/>
-      <c r="G39" s="83"/>
-      <c r="H39" s="69"/>
-    </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="F39" s="128"/>
+      <c r="G39" s="34"/>
+      <c r="H39" s="84"/>
+      <c r="I39" s="70"/>
+    </row>
+    <row r="40" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B40" s="32" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C40" s="35" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D40" s="36">
         <v>1</v>
       </c>
       <c r="E40" s="31" t="s">
-        <v>57</v>
-      </c>
-      <c r="F40" s="31"/>
-      <c r="G40" s="35"/>
-      <c r="H40" s="70">
+        <v>54</v>
+      </c>
+      <c r="F40" s="125"/>
+      <c r="G40" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H40" s="35"/>
+      <c r="I40" s="71">
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="2:8" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B41" s="32" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C41" s="35" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="D41" s="36">
         <v>15</v>
       </c>
       <c r="E41" s="31" t="s">
-        <v>57</v>
-      </c>
-      <c r="F41" s="31"/>
-      <c r="G41" s="35"/>
-      <c r="H41" s="70"/>
-    </row>
-    <row r="42" spans="2:8" ht="22.8" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="F41" s="125"/>
+      <c r="G41" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H41" s="35"/>
+      <c r="I41" s="71"/>
+    </row>
+    <row r="42" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B42" s="32" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C42" s="35" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="D42" s="31">
         <f>D11+(INT(D11/D41)*D10)</f>
         <v>107</v>
       </c>
       <c r="E42" s="31" t="s">
-        <v>57</v>
-      </c>
-      <c r="F42" s="31"/>
-      <c r="G42" s="35"/>
-      <c r="H42" s="70"/>
-    </row>
-    <row r="43" spans="2:8" ht="22.8" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="F42" s="125"/>
+      <c r="G42" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H42" s="35"/>
+      <c r="I42" s="71"/>
+    </row>
+    <row r="43" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B43" s="32" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C43" s="35" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D43" s="31">
         <f>D42*D40</f>
         <v>107</v>
       </c>
       <c r="E43" s="31" t="s">
-        <v>58</v>
-      </c>
-      <c r="F43" s="31"/>
-      <c r="G43" s="35"/>
-      <c r="H43" s="70"/>
-    </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+      <c r="F43" s="125"/>
+      <c r="G43" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H43" s="35"/>
+      <c r="I43" s="71"/>
+    </row>
+    <row r="44" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B44" s="40"/>
       <c r="C44" s="41"/>
       <c r="D44" s="42"/>
       <c r="E44" s="42"/>
-      <c r="F44" s="42"/>
-      <c r="G44" s="41"/>
-      <c r="H44" s="72"/>
-    </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="F44" s="126"/>
+      <c r="G44" s="120" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H44" s="41"/>
+      <c r="I44" s="73"/>
+    </row>
+    <row r="45" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B45" s="48" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C45" s="33"/>
       <c r="D45" s="34"/>
       <c r="E45" s="34"/>
-      <c r="F45" s="34"/>
-      <c r="G45" s="83"/>
-      <c r="H45" s="69"/>
-    </row>
-    <row r="46" spans="2:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="F45" s="128"/>
+      <c r="G45" s="34"/>
+      <c r="H45" s="84"/>
+      <c r="I45" s="70"/>
+    </row>
+    <row r="46" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B46" s="32" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C46" s="35" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D46" s="36">
         <v>60</v>
       </c>
       <c r="E46" s="31" t="s">
-        <v>58</v>
-      </c>
-      <c r="F46" s="31"/>
-      <c r="G46" s="35"/>
-      <c r="H46" s="70">
+        <v>55</v>
+      </c>
+      <c r="F46" s="125"/>
+      <c r="G46" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H46" s="35"/>
+      <c r="I46" s="71">
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="2:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="B47" s="32" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="C47" s="35" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D47" s="36">
         <v>24</v>
       </c>
       <c r="E47" s="31" t="s">
-        <v>58</v>
-      </c>
-      <c r="F47" s="31"/>
-      <c r="G47" s="35"/>
-      <c r="H47" s="70"/>
-    </row>
-    <row r="48" spans="2:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+      <c r="F47" s="125"/>
+      <c r="G47" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H47" s="35"/>
+      <c r="I47" s="71"/>
+    </row>
+    <row r="48" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B48" s="32" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C48" s="35" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D48" s="36">
         <v>3.9900000000000007</v>
       </c>
       <c r="E48" s="31" t="s">
-        <v>57</v>
-      </c>
-      <c r="F48" s="31"/>
-      <c r="G48" s="35"/>
-      <c r="H48" s="70"/>
-    </row>
-    <row r="49" spans="2:8" ht="22.8" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="F48" s="125"/>
+      <c r="G48" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H48" s="35"/>
+      <c r="I48" s="71"/>
+    </row>
+    <row r="49" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B49" s="32" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="C49" s="35" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D49" s="31">
         <f>D46-D54</f>
         <v>52.943999999999996</v>
       </c>
       <c r="E49" s="31" t="s">
+        <v>55</v>
+      </c>
+      <c r="F49" s="125"/>
+      <c r="G49" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H49" s="35"/>
+      <c r="I49" s="71"/>
+    </row>
+    <row r="50" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="B50" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="F49" s="31"/>
-      <c r="G49" s="35"/>
-      <c r="H49" s="70"/>
-    </row>
-    <row r="50" spans="2:8" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B50" s="32" t="s">
-        <v>61</v>
-      </c>
       <c r="C50" s="35" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="D50" s="36">
         <v>28</v>
       </c>
       <c r="E50" s="31" t="s">
+        <v>56</v>
+      </c>
+      <c r="F50" s="125"/>
+      <c r="G50" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H50" s="35"/>
+      <c r="I50" s="71"/>
+    </row>
+    <row r="51" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="B51" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="C51" s="35" t="s">
         <v>59</v>
-      </c>
-      <c r="F50" s="31"/>
-      <c r="G50" s="35"/>
-      <c r="H50" s="70"/>
-    </row>
-    <row r="51" spans="2:8" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B51" s="32" t="s">
-        <v>103</v>
-      </c>
-      <c r="C51" s="35" t="s">
-        <v>62</v>
       </c>
       <c r="D51" s="36">
         <v>19</v>
       </c>
       <c r="E51" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="F51" s="31"/>
-      <c r="G51" s="35"/>
-      <c r="H51" s="70"/>
-    </row>
-    <row r="52" spans="2:8" ht="22.8" x14ac:dyDescent="0.3">
+        <v>56</v>
+      </c>
+      <c r="F51" s="125"/>
+      <c r="G51" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H51" s="35"/>
+      <c r="I51" s="71"/>
+    </row>
+    <row r="52" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B52" s="32" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C52" s="35" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D52" s="31">
         <f>D48/(D51/100)</f>
         <v>21.000000000000004</v>
       </c>
       <c r="E52" s="31" t="s">
-        <v>53</v>
-      </c>
-      <c r="F52" s="31"/>
-      <c r="G52" s="35"/>
-      <c r="H52" s="70"/>
-    </row>
-    <row r="53" spans="2:8" x14ac:dyDescent="0.3">
+        <v>50</v>
+      </c>
+      <c r="F52" s="125"/>
+      <c r="G52" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H52" s="35"/>
+      <c r="I52" s="71"/>
+    </row>
+    <row r="53" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B53" s="32" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C53" s="35" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="D53" s="36">
         <v>1.2</v>
       </c>
       <c r="E53" s="31" t="s">
-        <v>57</v>
-      </c>
-      <c r="F53" s="31"/>
-      <c r="G53" s="35"/>
-      <c r="H53" s="70"/>
-    </row>
-    <row r="54" spans="2:8" ht="22.8" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="F53" s="125"/>
+      <c r="G53" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H53" s="35"/>
+      <c r="I53" s="71"/>
+    </row>
+    <row r="54" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B54" s="32" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="C54" s="35" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D54" s="46">
         <f>D53*D52*(D50/100)</f>
         <v>7.0560000000000018</v>
       </c>
       <c r="E54" s="31" t="s">
-        <v>58</v>
-      </c>
-      <c r="F54" s="31"/>
-      <c r="G54" s="35"/>
-      <c r="H54" s="70"/>
-    </row>
-    <row r="55" spans="2:8" ht="79.8" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+      <c r="F54" s="125"/>
+      <c r="G54" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H54" s="35"/>
+      <c r="I54" s="71"/>
+    </row>
+    <row r="55" spans="2:9" ht="68.400000000000006" x14ac:dyDescent="0.3">
       <c r="B55" s="32" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="C55" s="35" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="D55" s="36">
         <v>6</v>
       </c>
       <c r="E55" s="31" t="s">
-        <v>57</v>
-      </c>
-      <c r="F55" s="31"/>
-      <c r="G55" s="35"/>
-      <c r="H55" s="70"/>
-    </row>
-    <row r="56" spans="2:8" ht="91.2" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="F55" s="125"/>
+      <c r="G55" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H55" s="35"/>
+      <c r="I55" s="71"/>
+    </row>
+    <row r="56" spans="2:9" ht="68.400000000000006" x14ac:dyDescent="0.3">
       <c r="B56" s="32" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="C56" s="35" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="D56" s="36">
         <v>4.5</v>
       </c>
       <c r="E56" s="31" t="s">
-        <v>57</v>
-      </c>
-      <c r="F56" s="31"/>
-      <c r="G56" s="35"/>
-      <c r="H56" s="70"/>
-    </row>
-    <row r="57" spans="2:8" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="F56" s="125"/>
+      <c r="G56" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H56" s="35"/>
+      <c r="I56" s="71"/>
+    </row>
+    <row r="57" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B57" s="32" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="C57" s="35" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="D57" s="36">
         <v>1.2</v>
       </c>
       <c r="E57" s="31" t="s">
-        <v>57</v>
-      </c>
-      <c r="F57" s="31"/>
-      <c r="G57" s="35"/>
-      <c r="H57" s="70"/>
-    </row>
-    <row r="58" spans="2:8" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="F57" s="125"/>
+      <c r="G57" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H57" s="35"/>
+      <c r="I57" s="71"/>
+    </row>
+    <row r="58" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B58" s="32" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="C58" s="35" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="D58" s="36">
         <v>2.2999999999999998</v>
       </c>
       <c r="E58" s="31" t="s">
-        <v>57</v>
-      </c>
-      <c r="F58" s="31"/>
-      <c r="G58" s="35"/>
-      <c r="H58" s="70"/>
-    </row>
-    <row r="59" spans="2:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="F58" s="125"/>
+      <c r="G58" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H58" s="35"/>
+      <c r="I58" s="71"/>
+    </row>
+    <row r="59" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B59" s="32" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C59" s="35" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="D59" s="36">
         <v>3</v>
       </c>
       <c r="E59" s="31" t="s">
-        <v>57</v>
-      </c>
-      <c r="F59" s="31"/>
-      <c r="G59" s="35"/>
-      <c r="H59" s="70"/>
-    </row>
-    <row r="60" spans="2:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="F59" s="125"/>
+      <c r="G59" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H59" s="35"/>
+      <c r="I59" s="71"/>
+    </row>
+    <row r="60" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B60" s="32" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="C60" s="35" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D60" s="36">
         <v>2</v>
       </c>
       <c r="E60" s="31" t="s">
-        <v>57</v>
-      </c>
-      <c r="F60" s="31"/>
-      <c r="G60" s="35"/>
-      <c r="H60" s="70"/>
-    </row>
-    <row r="61" spans="2:8" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="F60" s="125"/>
+      <c r="G60" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H60" s="35"/>
+      <c r="I60" s="71"/>
+    </row>
+    <row r="61" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B61" s="40"/>
       <c r="C61" s="41"/>
       <c r="D61" s="42"/>
       <c r="E61" s="42"/>
-      <c r="F61" s="42"/>
-      <c r="G61" s="41"/>
-      <c r="H61" s="72"/>
-    </row>
-    <row r="62" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="F61" s="126"/>
+      <c r="G61" s="120" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H61" s="41"/>
+      <c r="I61" s="73"/>
+    </row>
+    <row r="62" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B62" s="51" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C62" s="52"/>
       <c r="D62" s="53"/>
       <c r="E62" s="53"/>
-      <c r="F62" s="53"/>
-      <c r="G62" s="84"/>
-      <c r="H62" s="73"/>
-    </row>
-    <row r="63" spans="2:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="F62" s="130"/>
+      <c r="G62" s="53"/>
+      <c r="H62" s="85"/>
+      <c r="I62" s="74"/>
+    </row>
+    <row r="63" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B63" s="32" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C63" s="35" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D63" s="36">
         <v>40</v>
       </c>
       <c r="E63" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="F63" s="31"/>
-      <c r="G63" s="35"/>
-      <c r="H63" s="70">
+        <v>56</v>
+      </c>
+      <c r="F63" s="125"/>
+      <c r="G63" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H63" s="35"/>
+      <c r="I63" s="71">
         <v>5</v>
       </c>
     </row>
-    <row r="64" spans="2:8" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="64" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B64" s="32" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="C64" s="35" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D64" s="46">
         <f>D18</f>
         <v>1435</v>
       </c>
       <c r="E64" s="31" t="s">
-        <v>58</v>
-      </c>
-      <c r="F64" s="31"/>
-      <c r="G64" s="35"/>
-      <c r="H64" s="70"/>
-    </row>
-    <row r="65" spans="2:8" ht="22.8" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+      <c r="F64" s="125"/>
+      <c r="G64" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H64" s="35"/>
+      <c r="I64" s="71"/>
+    </row>
+    <row r="65" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B65" s="32" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C65" s="35" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D65" s="36">
         <v>20</v>
       </c>
       <c r="E65" s="31" t="s">
-        <v>59</v>
-      </c>
-      <c r="F65" s="31"/>
-      <c r="G65" s="35"/>
-      <c r="H65" s="70"/>
-    </row>
-    <row r="66" spans="2:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+        <v>56</v>
+      </c>
+      <c r="F65" s="125"/>
+      <c r="G65" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H65" s="35"/>
+      <c r="I65" s="71"/>
+    </row>
+    <row r="66" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
       <c r="B66" s="32" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="C66" s="35" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D66" s="36">
         <v>6</v>
       </c>
       <c r="E66" s="31" t="s">
-        <v>57</v>
-      </c>
-      <c r="F66" s="31"/>
-      <c r="G66" s="35"/>
-      <c r="H66" s="70"/>
-    </row>
-    <row r="67" spans="2:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="F66" s="125"/>
+      <c r="G66" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H66" s="35"/>
+      <c r="I66" s="71"/>
+    </row>
+    <row r="67" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
       <c r="B67" s="32" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C67" s="35" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D67" s="46">
         <f>ROUND(D10/D66,0)</f>
         <v>6</v>
       </c>
       <c r="E67" s="31" t="s">
-        <v>126</v>
-      </c>
-      <c r="F67" s="31"/>
-      <c r="G67" s="35"/>
-      <c r="H67" s="70"/>
-    </row>
-    <row r="68" spans="2:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+      <c r="F67" s="125"/>
+      <c r="G67" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H67" s="35"/>
+      <c r="I67" s="71"/>
+    </row>
+    <row r="68" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
       <c r="B68" s="32" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C68" s="35" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="D68" s="46">
         <f>ROUND(D11/D66,0)</f>
         <v>6</v>
       </c>
       <c r="E68" s="31" t="s">
+        <v>123</v>
+      </c>
+      <c r="F68" s="125"/>
+      <c r="G68" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H68" s="35"/>
+      <c r="I68" s="71"/>
+    </row>
+    <row r="69" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B69" s="32" t="s">
         <v>126</v>
       </c>
-      <c r="F68" s="31"/>
-      <c r="G68" s="35"/>
-      <c r="H68" s="70"/>
-    </row>
-    <row r="69" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B69" s="32" t="s">
-        <v>129</v>
-      </c>
       <c r="C69" s="35" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D69" s="46">
         <f>D68*D67</f>
         <v>36</v>
       </c>
       <c r="E69" s="31" t="s">
-        <v>126</v>
-      </c>
-      <c r="F69" s="31"/>
-      <c r="G69" s="35"/>
-      <c r="H69" s="70"/>
-    </row>
-    <row r="70" spans="2:8" ht="45.6" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+      <c r="F69" s="125"/>
+      <c r="G69" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H69" s="35"/>
+      <c r="I69" s="71"/>
+    </row>
+    <row r="70" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="B70" s="32" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C70" s="35" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="D70" s="36">
         <v>0.3</v>
       </c>
       <c r="E70" s="31" t="s">
-        <v>57</v>
-      </c>
-      <c r="F70" s="31"/>
-      <c r="G70" s="35"/>
-      <c r="H70" s="70"/>
-    </row>
-    <row r="71" spans="2:8" ht="45.6" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="F70" s="125"/>
+      <c r="G70" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H70" s="35"/>
+      <c r="I70" s="71"/>
+    </row>
+    <row r="71" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="B71" s="32" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C71" s="35" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D71" s="36">
         <v>0.4</v>
       </c>
       <c r="E71" s="31" t="s">
-        <v>57</v>
-      </c>
-      <c r="F71" s="31"/>
-      <c r="G71" s="35"/>
-      <c r="H71" s="70"/>
-    </row>
-    <row r="72" spans="2:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="F71" s="125"/>
+      <c r="G71" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H71" s="35"/>
+      <c r="I71" s="71"/>
+    </row>
+    <row r="72" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="B72" s="32" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C72" s="35" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D72" s="36">
         <v>0.3</v>
       </c>
       <c r="E72" s="31" t="s">
-        <v>57</v>
-      </c>
-      <c r="F72" s="31"/>
-      <c r="G72" s="35"/>
-      <c r="H72" s="70"/>
-    </row>
-    <row r="73" spans="2:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="F72" s="125"/>
+      <c r="G72" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H72" s="35"/>
+      <c r="I72" s="71"/>
+    </row>
+    <row r="73" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="B73" s="32" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="C73" s="35" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="D73" s="36">
         <v>0.4</v>
       </c>
       <c r="E73" s="31" t="s">
-        <v>57</v>
-      </c>
-      <c r="F73" s="31"/>
-      <c r="G73" s="35"/>
-      <c r="H73" s="70"/>
-    </row>
-    <row r="74" spans="2:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="F73" s="125"/>
+      <c r="G73" s="119" t="str">
+        <f t="shared" ref="G73:G76" si="1">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F73,"/Readme.md"),"Ver")</f>
+        <v>Ver</v>
+      </c>
+      <c r="H73" s="35"/>
+      <c r="I73" s="71"/>
+    </row>
+    <row r="74" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="B74" s="32" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C74" s="35" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D74" s="46">
         <f>(D10-D70)/D67</f>
         <v>5.7833333333333341</v>
       </c>
       <c r="E74" s="31" t="s">
-        <v>57</v>
-      </c>
-      <c r="F74" s="31"/>
-      <c r="G74" s="35"/>
-      <c r="H74" s="70"/>
-    </row>
-    <row r="75" spans="2:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="F74" s="125"/>
+      <c r="G74" s="119" t="str">
+        <f t="shared" si="1"/>
+        <v>Ver</v>
+      </c>
+      <c r="H74" s="35"/>
+      <c r="I74" s="71"/>
+    </row>
+    <row r="75" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="B75" s="32" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C75" s="35" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D75" s="46">
         <f>(D11-D71)/D68</f>
         <v>6.1000000000000005</v>
       </c>
       <c r="E75" s="31" t="s">
-        <v>57</v>
-      </c>
-      <c r="F75" s="31"/>
-      <c r="G75" s="35"/>
-      <c r="H75" s="70"/>
-    </row>
-    <row r="76" spans="2:8" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="F75" s="125"/>
+      <c r="G75" s="119" t="str">
+        <f t="shared" si="1"/>
+        <v>Ver</v>
+      </c>
+      <c r="H75" s="35"/>
+      <c r="I75" s="71"/>
+    </row>
+    <row r="76" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B76" s="54"/>
       <c r="C76" s="55"/>
       <c r="D76" s="56"/>
       <c r="E76" s="56"/>
-      <c r="F76" s="56"/>
-      <c r="G76" s="55"/>
-      <c r="H76" s="9"/>
-    </row>
-    <row r="77" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="F76" s="131"/>
+      <c r="G76" s="120" t="str">
+        <f t="shared" si="1"/>
+        <v>Ver</v>
+      </c>
+      <c r="H76" s="55"/>
+      <c r="I76" s="9"/>
+    </row>
+    <row r="77" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B77" s="57" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="79" spans="2:8" x14ac:dyDescent="0.3">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="79" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B79" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="80" spans="2:8" x14ac:dyDescent="0.3">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="80" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B80" s="6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C80" s="14" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="81" spans="2:8" x14ac:dyDescent="0.3">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="81" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B81" s="58" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C81" s="13">
         <f>D17</f>
         <v>1925</v>
       </c>
     </row>
-    <row r="82" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="82" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B82" s="58" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C82" s="13">
         <f>D18</f>
         <v>1435</v>
       </c>
     </row>
-    <row r="83" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="83" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B83" s="58" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C83" s="13">
         <f>D46</f>
         <v>60</v>
       </c>
     </row>
-    <row r="84" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="84" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B84" s="58" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="C84" s="13">
         <f>D54</f>
         <v>7.0560000000000018</v>
       </c>
     </row>
-    <row r="85" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="85" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B85" s="58" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C85" s="13">
         <f>D49</f>
         <v>52.943999999999996</v>
       </c>
     </row>
-    <row r="86" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B86" s="59" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C86" s="60">
         <f>D19</f>
         <v>1495</v>
       </c>
     </row>
-    <row r="87" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="87" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B87" s="61" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C87" s="62">
         <f>D20</f>
         <v>0.74545454545454548</v>
       </c>
     </row>
-    <row r="88" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="88" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B88" s="54" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C88" s="5">
         <f>D21</f>
         <v>0.77662337662337666</v>
       </c>
     </row>
-    <row r="90" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="90" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B90" s="2" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="91" spans="2:8" x14ac:dyDescent="0.3">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="91" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B91" s="6" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C91" s="33" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D91" s="8" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E91" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="F91" s="34" t="s">
-        <v>42</v>
-      </c>
-      <c r="G91" s="33" t="s">
+        <v>50</v>
+      </c>
+      <c r="F91" s="121" t="s">
+        <v>39</v>
+      </c>
+      <c r="G91" s="122"/>
+      <c r="H91" s="33" t="s">
         <v>26</v>
       </c>
-      <c r="H91" s="69" t="s">
+      <c r="I91" s="70" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="92" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="92" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B92" s="32" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C92" s="29" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D92" s="64">
         <f>D64</f>
         <v>1435</v>
       </c>
       <c r="E92" s="64" t="s">
-        <v>58</v>
-      </c>
-      <c r="F92" s="31"/>
-      <c r="G92" s="35"/>
-      <c r="H92" s="70"/>
-    </row>
-    <row r="93" spans="2:8" ht="33.6" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+      <c r="F92" s="125"/>
+      <c r="G92" s="119" t="str">
+        <f t="shared" ref="G92:G102" si="2">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F92,"/Readme.md"),"Ver")</f>
+        <v>Ver</v>
+      </c>
+      <c r="H92" s="35"/>
+      <c r="I92" s="71"/>
+    </row>
+    <row r="93" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
       <c r="B93" s="32" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C93" s="29" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D93" s="64">
         <f>D92*D63</f>
         <v>57400</v>
       </c>
       <c r="E93" s="64" t="s">
-        <v>187</v>
-      </c>
-      <c r="F93" s="31"/>
-      <c r="G93" s="35"/>
-      <c r="H93" s="70"/>
-    </row>
-    <row r="94" spans="2:8" x14ac:dyDescent="0.3">
+        <v>184</v>
+      </c>
+      <c r="F93" s="125"/>
+      <c r="G93" s="119" t="str">
+        <f t="shared" si="2"/>
+        <v>Ver</v>
+      </c>
+      <c r="H93" s="35"/>
+      <c r="I93" s="71"/>
+    </row>
+    <row r="94" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B94" s="32" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="C94" s="29" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="D94" s="64">
         <f>D49</f>
         <v>52.943999999999996</v>
       </c>
       <c r="E94" s="64" t="s">
-        <v>58</v>
-      </c>
-      <c r="F94" s="64"/>
-      <c r="G94" s="85"/>
-      <c r="H94" s="11"/>
-    </row>
-    <row r="95" spans="2:8" ht="33.6" x14ac:dyDescent="0.3">
+        <v>55</v>
+      </c>
+      <c r="F94" s="132"/>
+      <c r="G94" s="119" t="str">
+        <f t="shared" si="2"/>
+        <v>Ver</v>
+      </c>
+      <c r="H94" s="86"/>
+      <c r="I94" s="11"/>
+    </row>
+    <row r="95" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B95" s="32" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="C95" s="29" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="D95" s="64">
         <f>D69</f>
         <v>36</v>
       </c>
       <c r="E95" s="64" t="s">
-        <v>126</v>
-      </c>
-      <c r="F95" s="64"/>
-      <c r="G95" s="85"/>
-      <c r="H95" s="11"/>
-    </row>
-    <row r="96" spans="2:8" ht="33.6" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+      <c r="F95" s="132"/>
+      <c r="G95" s="119" t="str">
+        <f t="shared" si="2"/>
+        <v>Ver</v>
+      </c>
+      <c r="H95" s="86"/>
+      <c r="I95" s="11"/>
+    </row>
+    <row r="96" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
       <c r="B96" s="32" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="C96" s="29" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="D96" s="64">
         <f>D95*D12</f>
         <v>432</v>
       </c>
       <c r="E96" s="64" t="s">
-        <v>57</v>
-      </c>
-      <c r="F96" s="64"/>
-      <c r="G96" s="85"/>
-      <c r="H96" s="11"/>
-    </row>
-    <row r="97" spans="2:8" ht="50.4" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="F96" s="132"/>
+      <c r="G96" s="119" t="str">
+        <f t="shared" si="2"/>
+        <v>Ver</v>
+      </c>
+      <c r="H96" s="86"/>
+      <c r="I96" s="11"/>
+    </row>
+    <row r="97" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
       <c r="B97" s="32" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="C97" s="29" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="D97" s="64">
         <f>((D67*D9)+(D68*D8))*INT(D12/D48)</f>
         <v>324</v>
       </c>
       <c r="E97" s="64" t="s">
-        <v>57</v>
-      </c>
-      <c r="F97" s="64"/>
-      <c r="G97" s="85"/>
-      <c r="H97" s="11"/>
-    </row>
-    <row r="98" spans="2:8" ht="33.6" x14ac:dyDescent="0.3">
+        <v>54</v>
+      </c>
+      <c r="F97" s="132"/>
+      <c r="G97" s="119" t="str">
+        <f t="shared" si="2"/>
+        <v>Ver</v>
+      </c>
+      <c r="H97" s="86"/>
+      <c r="I97" s="11"/>
+    </row>
+    <row r="98" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
       <c r="B98" s="32" t="s">
+        <v>201</v>
+      </c>
+      <c r="C98" s="29" t="s">
         <v>204</v>
       </c>
-      <c r="C98" s="29" t="s">
+      <c r="D98" s="68" t="s">
+        <v>203</v>
+      </c>
+      <c r="E98" s="64" t="s">
+        <v>55</v>
+      </c>
+      <c r="F98" s="132"/>
+      <c r="G98" s="119" t="str">
+        <f t="shared" si="2"/>
+        <v>Ver</v>
+      </c>
+      <c r="H98" s="86"/>
+      <c r="I98" s="11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="99" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B99" s="32" t="s">
+        <v>202</v>
+      </c>
+      <c r="C99" s="29" t="s">
+        <v>205</v>
+      </c>
+      <c r="D99" s="68">
+        <v>2</v>
+      </c>
+      <c r="E99" s="64" t="s">
+        <v>123</v>
+      </c>
+      <c r="F99" s="132"/>
+      <c r="G99" s="119" t="str">
+        <f t="shared" si="2"/>
+        <v>Ver</v>
+      </c>
+      <c r="H99" s="86"/>
+      <c r="I99" s="11"/>
+    </row>
+    <row r="100" spans="2:9" ht="50.4" x14ac:dyDescent="0.3">
+      <c r="B100" s="32" t="s">
+        <v>47</v>
+      </c>
+      <c r="C100" s="29" t="s">
+        <v>206</v>
+      </c>
+      <c r="D100" s="68" t="s">
+        <v>203</v>
+      </c>
+      <c r="E100" s="64" t="s">
+        <v>123</v>
+      </c>
+      <c r="F100" s="132"/>
+      <c r="G100" s="119" t="str">
+        <f t="shared" si="2"/>
+        <v>Ver</v>
+      </c>
+      <c r="H100" s="86"/>
+      <c r="I100" s="11"/>
+    </row>
+    <row r="101" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="B101" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="C101" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="D98" s="67" t="s">
-        <v>206</v>
-      </c>
-      <c r="E98" s="64" t="s">
-        <v>58</v>
-      </c>
-      <c r="F98" s="64"/>
-      <c r="G98" s="85"/>
-      <c r="H98" s="11">
+      <c r="D101" s="68" t="s">
+        <v>203</v>
+      </c>
+      <c r="E101" s="64" t="s">
+        <v>123</v>
+      </c>
+      <c r="F101" s="132"/>
+      <c r="G101" s="119" t="str">
+        <f t="shared" si="2"/>
+        <v>Ver</v>
+      </c>
+      <c r="H101" s="86"/>
+      <c r="I101" s="11"/>
+    </row>
+    <row r="102" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B102" s="40"/>
+      <c r="C102" s="30"/>
+      <c r="D102" s="56"/>
+      <c r="E102" s="56"/>
+      <c r="F102" s="131"/>
+      <c r="G102" s="120" t="str">
+        <f t="shared" si="2"/>
+        <v>Ver</v>
+      </c>
+      <c r="H102" s="55"/>
+      <c r="I102" s="9"/>
+    </row>
+    <row r="103" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B103" s="63"/>
+      <c r="C103" s="63"/>
+      <c r="H103" s="76" t="s">
+        <v>290</v>
+      </c>
+      <c r="I103" s="47">
+        <f>AVERAGE(I7:I102)</f>
         <v>5</v>
       </c>
     </row>
-    <row r="99" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B99" s="32" t="s">
-        <v>205</v>
-      </c>
-      <c r="C99" s="29" t="s">
-        <v>208</v>
-      </c>
-      <c r="D99" s="67">
-        <v>2</v>
-      </c>
-      <c r="E99" s="64" t="s">
-        <v>126</v>
-      </c>
-      <c r="F99" s="64"/>
-      <c r="G99" s="85"/>
-      <c r="H99" s="11"/>
-    </row>
-    <row r="100" spans="2:8" ht="67.2" x14ac:dyDescent="0.3">
-      <c r="B100" s="32" t="s">
-        <v>50</v>
-      </c>
-      <c r="C100" s="29" t="s">
-        <v>209</v>
-      </c>
-      <c r="D100" s="67" t="s">
-        <v>206</v>
-      </c>
-      <c r="E100" s="64" t="s">
-        <v>126</v>
-      </c>
-      <c r="F100" s="64"/>
-      <c r="G100" s="85"/>
-      <c r="H100" s="11"/>
-    </row>
-    <row r="101" spans="2:8" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="B101" s="32" t="s">
-        <v>51</v>
-      </c>
-      <c r="C101" s="29" t="s">
-        <v>210</v>
-      </c>
-      <c r="D101" s="67" t="s">
-        <v>206</v>
-      </c>
-      <c r="E101" s="64" t="s">
-        <v>126</v>
-      </c>
-      <c r="F101" s="64"/>
-      <c r="G101" s="85"/>
-      <c r="H101" s="11"/>
-    </row>
-    <row r="102" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B102" s="32"/>
-      <c r="C102" s="29"/>
-      <c r="D102" s="64"/>
-      <c r="E102" s="64"/>
-      <c r="F102" s="64"/>
-      <c r="G102" s="85"/>
-      <c r="H102" s="11"/>
-    </row>
-    <row r="103" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B103" s="40"/>
-      <c r="C103" s="30"/>
-      <c r="D103" s="56"/>
-      <c r="E103" s="56"/>
-      <c r="F103" s="56"/>
-      <c r="G103" s="55"/>
-      <c r="H103" s="9"/>
-    </row>
-    <row r="104" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="104" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B104" s="63"/>
       <c r="C104" s="63"/>
-      <c r="G104" s="75" t="s">
-        <v>293</v>
-      </c>
-      <c r="H104" s="47">
-        <f>AVERAGE(H7:H103)</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="105" spans="2:8" x14ac:dyDescent="0.3">
+    </row>
+    <row r="105" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B105" s="63"/>
       <c r="C105" s="63"/>
     </row>
-    <row r="106" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="106" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B106" s="63"/>
       <c r="C106" s="63"/>
     </row>
-    <row r="107" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="107" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B107" s="63"/>
       <c r="C107" s="63"/>
     </row>
-    <row r="108" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="108" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B108" s="63"/>
       <c r="C108" s="63"/>
     </row>
-    <row r="109" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="109" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B109" s="63"/>
       <c r="C109" s="63"/>
     </row>
-    <row r="110" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="110" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B110" s="63"/>
       <c r="C110" s="63"/>
     </row>
-    <row r="111" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="111" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B111" s="63"/>
       <c r="C111" s="63"/>
     </row>
-    <row r="112" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="112" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B112" s="63"/>
       <c r="C112" s="63"/>
     </row>
@@ -5107,13 +5598,11 @@
       <c r="B113" s="63"/>
       <c r="C113" s="63"/>
     </row>
-    <row r="114" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B114" s="63"/>
-      <c r="C114" s="63"/>
-    </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B4:H5"/>
+  <mergeCells count="3">
+    <mergeCell ref="B4:I5"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="F91:G91"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -5122,418 +5611,501 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDC0663E-105D-42EA-893B-DB8B7FE41FC2}">
-  <dimension ref="B2:H28"/>
+  <dimension ref="B2:I28"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.5546875" customWidth="1"/>
-    <col min="2" max="2" width="29.109375" customWidth="1"/>
-    <col min="3" max="3" width="51.77734375" customWidth="1"/>
-    <col min="4" max="4" width="11.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.5546875" customWidth="1"/>
-    <col min="7" max="7" width="35.109375" style="86" customWidth="1"/>
-    <col min="8" max="8" width="13.44140625" style="65" customWidth="1"/>
+    <col min="2" max="2" width="30.77734375" customWidth="1"/>
+    <col min="3" max="3" width="50.77734375" customWidth="1"/>
+    <col min="4" max="5" width="10.77734375" customWidth="1"/>
+    <col min="6" max="6" width="7.77734375" style="87" customWidth="1"/>
+    <col min="7" max="7" width="3.77734375" customWidth="1"/>
+    <col min="8" max="8" width="30.77734375" style="87" customWidth="1"/>
+    <col min="9" max="9" width="12.77734375" style="66" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B2" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="2:8" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B3" s="20" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="4" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="105" t="s">
-        <v>242</v>
-      </c>
-      <c r="C4" s="105"/>
-      <c r="D4" s="105"/>
-      <c r="E4" s="105"/>
-      <c r="F4" s="105"/>
-      <c r="G4" s="105"/>
-      <c r="H4" s="105"/>
-    </row>
-    <row r="5" spans="2:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="116"/>
-      <c r="C5" s="116"/>
-      <c r="D5" s="116"/>
-      <c r="E5" s="116"/>
-      <c r="F5" s="116"/>
-      <c r="G5" s="116"/>
-      <c r="H5" s="116"/>
-    </row>
-    <row r="6" spans="2:8" ht="16.8" x14ac:dyDescent="0.3">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="106" t="s">
+        <v>239</v>
+      </c>
+      <c r="C4" s="106"/>
+      <c r="D4" s="106"/>
+      <c r="E4" s="106"/>
+      <c r="F4" s="106"/>
+      <c r="G4" s="106"/>
+      <c r="H4" s="106"/>
+      <c r="I4" s="106"/>
+    </row>
+    <row r="5" spans="2:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="117"/>
+      <c r="C5" s="117"/>
+      <c r="D5" s="117"/>
+      <c r="E5" s="117"/>
+      <c r="F5" s="117"/>
+      <c r="G5" s="117"/>
+      <c r="H5" s="117"/>
+      <c r="I5" s="117"/>
+    </row>
+    <row r="6" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B6" s="37" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C6" s="38" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D6" s="39" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E6" s="39" t="s">
-        <v>53</v>
-      </c>
-      <c r="F6" s="39" t="s">
-        <v>42</v>
-      </c>
-      <c r="G6" s="38" t="s">
+        <v>50</v>
+      </c>
+      <c r="F6" s="123" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" s="124"/>
+      <c r="H6" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="H6" s="68" t="s">
+      <c r="I6" s="69" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B7" s="6" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="C7" s="33"/>
       <c r="D7" s="34"/>
       <c r="E7" s="34"/>
-      <c r="F7" s="34"/>
-      <c r="G7" s="83"/>
-      <c r="H7" s="69"/>
-    </row>
-    <row r="8" spans="2:8" ht="45.6" x14ac:dyDescent="0.3">
+      <c r="F7" s="128"/>
+      <c r="G7" s="34"/>
+      <c r="H7" s="84"/>
+      <c r="I7" s="70"/>
+    </row>
+    <row r="8" spans="2:9" ht="57" x14ac:dyDescent="0.3">
       <c r="B8" s="32" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="D8" s="31">
         <v>1</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>126</v>
-      </c>
-      <c r="F8" s="31"/>
-      <c r="G8" s="35"/>
-      <c r="H8" s="70">
+        <v>123</v>
+      </c>
+      <c r="F8" s="125"/>
+      <c r="G8" s="119" t="str">
+        <f t="shared" ref="G8:G21" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F8,"/Readme.md"),"Ver")</f>
+        <v>Ver</v>
+      </c>
+      <c r="H8" s="35"/>
+      <c r="I8" s="71">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B9" s="32" t="s">
+        <v>227</v>
+      </c>
+      <c r="C9" s="35" t="s">
         <v>230</v>
-      </c>
-      <c r="C9" s="35" t="s">
-        <v>233</v>
       </c>
       <c r="D9" s="31">
         <v>1</v>
       </c>
       <c r="E9" s="31" t="s">
-        <v>126</v>
-      </c>
-      <c r="F9" s="31"/>
-      <c r="G9" s="35"/>
-      <c r="H9" s="70"/>
-    </row>
-    <row r="10" spans="2:8" ht="16.8" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+      <c r="F9" s="125"/>
+      <c r="G9" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H9" s="35"/>
+      <c r="I9" s="71"/>
+    </row>
+    <row r="10" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B10" s="32" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C10" s="35" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="D10" s="31">
         <v>1</v>
       </c>
       <c r="E10" s="31" t="s">
-        <v>126</v>
-      </c>
-      <c r="F10" s="31"/>
-      <c r="G10" s="35"/>
-      <c r="H10" s="70"/>
-    </row>
-    <row r="11" spans="2:8" ht="22.8" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+      <c r="F10" s="125"/>
+      <c r="G10" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H10" s="35"/>
+      <c r="I10" s="71"/>
+    </row>
+    <row r="11" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B11" s="32" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="D11" s="31">
         <v>1</v>
       </c>
       <c r="E11" s="31" t="s">
-        <v>126</v>
-      </c>
-      <c r="F11" s="31"/>
-      <c r="G11" s="35"/>
-      <c r="H11" s="70"/>
-    </row>
-    <row r="12" spans="2:8" ht="22.8" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+      <c r="F11" s="125"/>
+      <c r="G11" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H11" s="35"/>
+      <c r="I11" s="71"/>
+    </row>
+    <row r="12" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B12" s="43" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C12" s="35" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="D12" s="31">
         <v>1</v>
       </c>
       <c r="E12" s="31" t="s">
-        <v>126</v>
-      </c>
-      <c r="F12" s="45"/>
-      <c r="G12" s="44"/>
-      <c r="H12" s="71"/>
-    </row>
-    <row r="13" spans="2:8" ht="16.8" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+      <c r="F12" s="129"/>
+      <c r="G12" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H12" s="44"/>
+      <c r="I12" s="72"/>
+    </row>
+    <row r="13" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B13" s="43" t="s">
+        <v>229</v>
+      </c>
+      <c r="C13" s="35" t="s">
         <v>232</v>
-      </c>
-      <c r="C13" s="35" t="s">
-        <v>235</v>
       </c>
       <c r="D13" s="31">
         <v>1</v>
       </c>
       <c r="E13" s="31" t="s">
-        <v>126</v>
-      </c>
-      <c r="F13" s="45"/>
-      <c r="G13" s="44"/>
-      <c r="H13" s="71"/>
-    </row>
-    <row r="14" spans="2:8" ht="16.8" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+      <c r="F13" s="129"/>
+      <c r="G13" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H13" s="44"/>
+      <c r="I13" s="72"/>
+    </row>
+    <row r="14" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B14" s="32" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="C14" s="35" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D14" s="31">
         <v>1</v>
       </c>
       <c r="E14" s="31" t="s">
-        <v>126</v>
-      </c>
-      <c r="F14" s="31"/>
-      <c r="G14" s="35"/>
-      <c r="H14" s="70"/>
-    </row>
-    <row r="15" spans="2:8" ht="16.8" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+      <c r="F14" s="125"/>
+      <c r="G14" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H14" s="35"/>
+      <c r="I14" s="71"/>
+    </row>
+    <row r="15" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B15" s="32" t="s">
+        <v>209</v>
+      </c>
+      <c r="C15" s="35" t="s">
         <v>212</v>
-      </c>
-      <c r="C15" s="35" t="s">
-        <v>215</v>
       </c>
       <c r="D15" s="31">
         <v>1</v>
       </c>
       <c r="E15" s="31" t="s">
-        <v>126</v>
-      </c>
-      <c r="F15" s="31"/>
-      <c r="G15" s="35"/>
-      <c r="H15" s="70"/>
-    </row>
-    <row r="16" spans="2:8" ht="16.8" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+      <c r="F15" s="125"/>
+      <c r="G15" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H15" s="35"/>
+      <c r="I15" s="71"/>
+    </row>
+    <row r="16" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B16" s="43" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C16" s="35" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D16" s="31">
         <v>1</v>
       </c>
       <c r="E16" s="31" t="s">
-        <v>126</v>
-      </c>
-      <c r="F16" s="45"/>
-      <c r="G16" s="44"/>
-      <c r="H16" s="71"/>
-    </row>
-    <row r="17" spans="2:8" ht="16.8" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+      <c r="F16" s="129"/>
+      <c r="G16" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H16" s="44"/>
+      <c r="I16" s="72"/>
+    </row>
+    <row r="17" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B17" s="43" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="C17" s="35" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D17" s="31">
         <v>1</v>
       </c>
       <c r="E17" s="31" t="s">
-        <v>126</v>
-      </c>
-      <c r="F17" s="45"/>
-      <c r="G17" s="44"/>
-      <c r="H17" s="71"/>
-    </row>
-    <row r="18" spans="2:8" ht="16.8" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+      <c r="F17" s="129"/>
+      <c r="G17" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H17" s="44"/>
+      <c r="I17" s="72"/>
+    </row>
+    <row r="18" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B18" s="43" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C18" s="35" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D18" s="31">
         <v>1</v>
       </c>
       <c r="E18" s="31" t="s">
-        <v>126</v>
-      </c>
-      <c r="F18" s="45"/>
-      <c r="G18" s="44"/>
-      <c r="H18" s="71"/>
-    </row>
-    <row r="19" spans="2:8" ht="16.8" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+      <c r="F18" s="129"/>
+      <c r="G18" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H18" s="44"/>
+      <c r="I18" s="72"/>
+    </row>
+    <row r="19" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B19" s="43" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C19" s="35" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D19" s="45">
         <v>1</v>
       </c>
       <c r="E19" s="31" t="s">
-        <v>126</v>
-      </c>
-      <c r="F19" s="45"/>
-      <c r="G19" s="44"/>
-      <c r="H19" s="71"/>
-    </row>
-    <row r="20" spans="2:8" ht="16.8" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+      <c r="F19" s="129"/>
+      <c r="G19" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H19" s="44"/>
+      <c r="I19" s="72"/>
+    </row>
+    <row r="20" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B20" s="43" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C20" s="35" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="D20" s="45">
         <v>1</v>
       </c>
       <c r="E20" s="31" t="s">
-        <v>126</v>
-      </c>
-      <c r="F20" s="45"/>
-      <c r="G20" s="44"/>
-      <c r="H20" s="71"/>
-    </row>
-    <row r="21" spans="2:8" ht="16.8" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+      <c r="F20" s="129"/>
+      <c r="G20" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H20" s="44"/>
+      <c r="I20" s="72"/>
+    </row>
+    <row r="21" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B21" s="43"/>
       <c r="C21" s="44"/>
       <c r="D21" s="45"/>
       <c r="E21" s="45"/>
-      <c r="F21" s="45"/>
-      <c r="G21" s="44"/>
-      <c r="H21" s="71"/>
-    </row>
-    <row r="22" spans="2:8" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="F21" s="129"/>
+      <c r="G21" s="120" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H21" s="44"/>
+      <c r="I21" s="72"/>
+    </row>
+    <row r="22" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B22" s="6" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="C22" s="33"/>
       <c r="D22" s="34"/>
       <c r="E22" s="34"/>
-      <c r="F22" s="34"/>
-      <c r="G22" s="83"/>
-      <c r="H22" s="69"/>
-    </row>
-    <row r="23" spans="2:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="F22" s="128"/>
+      <c r="G22" s="34"/>
+      <c r="H22" s="84"/>
+      <c r="I22" s="70"/>
+    </row>
+    <row r="23" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="B23" s="32" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="C23" s="35" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="D23" s="46">
         <f>'2.ArquitectonicaEstructural'!D31-'2.ArquitectonicaEstructural'!D37-'2.ArquitectonicaEstructural'!D43</f>
         <v>1135.04</v>
       </c>
       <c r="E23" s="31" t="s">
-        <v>58</v>
-      </c>
-      <c r="F23" s="31"/>
-      <c r="G23" s="35"/>
-      <c r="H23" s="70">
+        <v>55</v>
+      </c>
+      <c r="F23" s="125"/>
+      <c r="G23" s="119" t="str">
+        <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F23,"/Readme.md"),"Ver")</f>
+        <v>Ver</v>
+      </c>
+      <c r="H23" s="35"/>
+      <c r="I23" s="71">
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="2:8" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B24" s="32" t="s">
+        <v>217</v>
+      </c>
+      <c r="C24" s="35" t="s">
         <v>220</v>
-      </c>
-      <c r="C24" s="35" t="s">
-        <v>223</v>
       </c>
       <c r="D24" s="36">
         <v>992</v>
       </c>
       <c r="E24" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="F24" s="31"/>
-      <c r="G24" s="35"/>
-      <c r="H24" s="70"/>
-    </row>
-    <row r="25" spans="2:8" ht="16.8" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+      <c r="F24" s="125"/>
+      <c r="G24" s="119" t="str">
+        <f t="shared" ref="G24:G27" si="1">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F24,"/Readme.md"),"Ver")</f>
+        <v>Ver</v>
+      </c>
+      <c r="H24" s="35"/>
+      <c r="I24" s="71"/>
+    </row>
+    <row r="25" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B25" s="32" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C25" s="35" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="D25" s="36">
         <v>1950</v>
       </c>
       <c r="E25" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="F25" s="31"/>
-      <c r="G25" s="35"/>
-      <c r="H25" s="70"/>
-    </row>
-    <row r="26" spans="2:8" ht="45.6" x14ac:dyDescent="0.3">
+        <v>65</v>
+      </c>
+      <c r="F25" s="125"/>
+      <c r="G25" s="119" t="str">
+        <f t="shared" si="1"/>
+        <v>Ver</v>
+      </c>
+      <c r="H25" s="35"/>
+      <c r="I25" s="71"/>
+    </row>
+    <row r="26" spans="2:9" ht="45.6" x14ac:dyDescent="0.3">
       <c r="B26" s="32" t="s">
+        <v>219</v>
+      </c>
+      <c r="C26" s="35" t="s">
         <v>222</v>
-      </c>
-      <c r="C26" s="35" t="s">
-        <v>225</v>
       </c>
       <c r="D26" s="31">
         <f>INT(D23/(D24/1000*D25/1000))</f>
         <v>586</v>
       </c>
       <c r="E26" s="31" t="s">
-        <v>126</v>
-      </c>
-      <c r="F26" s="31"/>
-      <c r="G26" s="35"/>
-      <c r="H26" s="70"/>
-    </row>
-    <row r="27" spans="2:8" ht="16.8" x14ac:dyDescent="0.3">
+        <v>123</v>
+      </c>
+      <c r="F26" s="125"/>
+      <c r="G26" s="119" t="str">
+        <f t="shared" si="1"/>
+        <v>Ver</v>
+      </c>
+      <c r="H26" s="35"/>
+      <c r="I26" s="71"/>
+    </row>
+    <row r="27" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B27" s="40"/>
       <c r="C27" s="41"/>
       <c r="D27" s="42"/>
       <c r="E27" s="42"/>
-      <c r="F27" s="42"/>
-      <c r="G27" s="41"/>
-      <c r="H27" s="72"/>
-    </row>
-    <row r="28" spans="2:8" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="G28" s="75" t="s">
-        <v>293</v>
-      </c>
-      <c r="H28" s="87">
-        <f>AVERAGE(H7:H27)</f>
+      <c r="F27" s="126"/>
+      <c r="G27" s="120" t="str">
+        <f t="shared" si="1"/>
+        <v>Ver</v>
+      </c>
+      <c r="H27" s="41"/>
+      <c r="I27" s="73"/>
+    </row>
+    <row r="28" spans="2:9" ht="16.8" x14ac:dyDescent="0.4">
+      <c r="H28" s="76" t="s">
+        <v>290</v>
+      </c>
+      <c r="I28" s="88">
+        <f>AVERAGE(I7:I27)</f>
         <v>5</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B4:H5"/>
+  <mergeCells count="2">
+    <mergeCell ref="B4:I5"/>
+    <mergeCell ref="F6:G6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -5542,345 +6114,408 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61FBD0B4-938E-4D04-BE03-979DB3A57126}">
-  <dimension ref="B2:H24"/>
+  <dimension ref="B2:I24"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="16.8" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="2.5546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="29.109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="51.77734375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.109375" style="1"/>
-    <col min="6" max="6" width="11.5546875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="35.109375" style="22" customWidth="1"/>
-    <col min="8" max="8" width="13.44140625" style="87" customWidth="1"/>
-    <col min="9" max="16384" width="9.109375" style="1"/>
+    <col min="2" max="2" width="30.77734375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="50.77734375" style="1" customWidth="1"/>
+    <col min="4" max="5" width="10.77734375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="7.77734375" style="22" customWidth="1"/>
+    <col min="7" max="7" width="3.77734375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="30.77734375" style="22" customWidth="1"/>
+    <col min="9" max="9" width="12.77734375" style="88" customWidth="1"/>
+    <col min="10" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B3" s="20" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="4" spans="2:8" ht="14.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="105" t="s">
-        <v>238</v>
-      </c>
-      <c r="C4" s="105"/>
-      <c r="D4" s="105"/>
-      <c r="E4" s="105"/>
-      <c r="F4" s="105"/>
-      <c r="G4" s="105"/>
-      <c r="H4" s="105"/>
-    </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B5" s="116"/>
-      <c r="C5" s="116"/>
-      <c r="D5" s="116"/>
-      <c r="E5" s="116"/>
-      <c r="F5" s="116"/>
-      <c r="G5" s="116"/>
-      <c r="H5" s="116"/>
-    </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.4">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B4" s="106" t="s">
+        <v>235</v>
+      </c>
+      <c r="C4" s="106"/>
+      <c r="D4" s="106"/>
+      <c r="E4" s="106"/>
+      <c r="F4" s="106"/>
+      <c r="G4" s="106"/>
+      <c r="H4" s="106"/>
+      <c r="I4" s="106"/>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B5" s="117"/>
+      <c r="C5" s="117"/>
+      <c r="D5" s="117"/>
+      <c r="E5" s="117"/>
+      <c r="F5" s="117"/>
+      <c r="G5" s="117"/>
+      <c r="H5" s="117"/>
+      <c r="I5" s="117"/>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B6" s="37" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C6" s="38" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D6" s="39" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E6" s="39" t="s">
-        <v>53</v>
-      </c>
-      <c r="F6" s="39" t="s">
-        <v>42</v>
-      </c>
-      <c r="G6" s="38" t="s">
+        <v>50</v>
+      </c>
+      <c r="F6" s="123" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" s="124"/>
+      <c r="H6" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="H6" s="68" t="s">
+      <c r="I6" s="69" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B7" s="6" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C7" s="33"/>
       <c r="D7" s="34"/>
       <c r="E7" s="34"/>
-      <c r="F7" s="34"/>
-      <c r="G7" s="83"/>
-      <c r="H7" s="69"/>
-    </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="F7" s="128"/>
+      <c r="G7" s="34"/>
+      <c r="H7" s="84"/>
+      <c r="I7" s="70"/>
+    </row>
+    <row r="8" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B8" s="32" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="D8" s="36">
         <v>3</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>57</v>
-      </c>
-      <c r="F8" s="31"/>
-      <c r="G8" s="35"/>
-      <c r="H8" s="70">
+        <v>54</v>
+      </c>
+      <c r="F8" s="125"/>
+      <c r="G8" s="119" t="str">
+        <f t="shared" ref="G8:G22" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F8,"/Readme.md"),"Ver")</f>
+        <v>Ver</v>
+      </c>
+      <c r="H8" s="35"/>
+      <c r="I8" s="71">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="22.8" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B9" s="32" t="s">
+        <v>245</v>
+      </c>
+      <c r="C9" s="35" t="s">
         <v>248</v>
-      </c>
-      <c r="C9" s="35" t="s">
-        <v>251</v>
       </c>
       <c r="D9" s="36">
         <v>2.5</v>
       </c>
       <c r="E9" s="31" t="s">
-        <v>57</v>
-      </c>
-      <c r="F9" s="31"/>
-      <c r="G9" s="35"/>
-      <c r="H9" s="70"/>
-    </row>
-    <row r="10" spans="2:8" ht="22.8" x14ac:dyDescent="0.4">
+        <v>54</v>
+      </c>
+      <c r="F9" s="125"/>
+      <c r="G9" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H9" s="35"/>
+      <c r="I9" s="71"/>
+    </row>
+    <row r="10" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B10" s="32" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C10" s="35" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="D10" s="36">
         <v>4</v>
       </c>
       <c r="E10" s="31" t="s">
-        <v>247</v>
-      </c>
-      <c r="F10" s="31"/>
-      <c r="G10" s="35"/>
-      <c r="H10" s="70"/>
-    </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.4">
+        <v>244</v>
+      </c>
+      <c r="F10" s="125"/>
+      <c r="G10" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H10" s="35"/>
+      <c r="I10" s="71"/>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B11" s="32" t="s">
+        <v>246</v>
+      </c>
+      <c r="C11" s="35" t="s">
         <v>249</v>
-      </c>
-      <c r="C11" s="35" t="s">
-        <v>252</v>
       </c>
       <c r="D11" s="36">
         <v>2</v>
       </c>
       <c r="E11" s="31" t="s">
-        <v>57</v>
-      </c>
-      <c r="F11" s="31"/>
-      <c r="G11" s="35"/>
-      <c r="H11" s="70"/>
-    </row>
-    <row r="12" spans="2:8" ht="33.6" x14ac:dyDescent="0.4">
+        <v>54</v>
+      </c>
+      <c r="F11" s="125"/>
+      <c r="G11" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H11" s="35"/>
+      <c r="I11" s="71"/>
+    </row>
+    <row r="12" spans="2:9" ht="33.6" x14ac:dyDescent="0.4">
       <c r="B12" s="32" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C12" s="35" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="D12" s="31">
         <f>D10*D11</f>
         <v>8</v>
       </c>
       <c r="E12" s="31" t="s">
-        <v>57</v>
-      </c>
-      <c r="F12" s="31"/>
-      <c r="G12" s="35"/>
-      <c r="H12" s="70"/>
-    </row>
-    <row r="13" spans="2:8" ht="22.8" x14ac:dyDescent="0.4">
+        <v>54</v>
+      </c>
+      <c r="F12" s="125"/>
+      <c r="G12" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H12" s="35"/>
+      <c r="I12" s="71"/>
+    </row>
+    <row r="13" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B13" s="32" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="C13" s="35" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="D13" s="36">
         <v>8</v>
       </c>
       <c r="E13" s="31" t="s">
-        <v>57</v>
-      </c>
-      <c r="F13" s="31"/>
-      <c r="G13" s="35"/>
-      <c r="H13" s="70"/>
-    </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.4">
+        <v>54</v>
+      </c>
+      <c r="F13" s="125"/>
+      <c r="G13" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H13" s="35"/>
+      <c r="I13" s="71"/>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B14" s="32" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C14" s="35" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="D14" s="31" t="str">
         <f>IF(D12&lt;=D13, "Cumple","No cumple")</f>
         <v>Cumple</v>
       </c>
       <c r="E14" s="31" t="s">
+        <v>257</v>
+      </c>
+      <c r="F14" s="125"/>
+      <c r="G14" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H14" s="35"/>
+      <c r="I14" s="71"/>
+    </row>
+    <row r="15" spans="2:9" ht="33.6" x14ac:dyDescent="0.4">
+      <c r="B15" s="32" t="s">
+        <v>259</v>
+      </c>
+      <c r="C15" s="35" t="s">
         <v>260</v>
-      </c>
-      <c r="F14" s="31"/>
-      <c r="G14" s="35"/>
-      <c r="H14" s="70"/>
-    </row>
-    <row r="15" spans="2:8" ht="33.6" x14ac:dyDescent="0.4">
-      <c r="B15" s="32" t="s">
-        <v>262</v>
-      </c>
-      <c r="C15" s="35" t="s">
-        <v>263</v>
       </c>
       <c r="D15" s="36">
         <v>60</v>
       </c>
       <c r="E15" s="31" t="s">
-        <v>57</v>
-      </c>
-      <c r="F15" s="31"/>
-      <c r="G15" s="35"/>
-      <c r="H15" s="70"/>
-    </row>
-    <row r="16" spans="2:8" ht="33.6" x14ac:dyDescent="0.4">
+        <v>54</v>
+      </c>
+      <c r="F15" s="125"/>
+      <c r="G15" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H15" s="35"/>
+      <c r="I15" s="71"/>
+    </row>
+    <row r="16" spans="2:9" ht="33.6" x14ac:dyDescent="0.4">
       <c r="B16" s="32" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C16" s="35" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="D16" s="31">
         <f>D15*D10</f>
         <v>240</v>
       </c>
       <c r="E16" s="31" t="s">
-        <v>57</v>
-      </c>
-      <c r="F16" s="31"/>
-      <c r="G16" s="35"/>
-      <c r="H16" s="70"/>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.4">
+        <v>54</v>
+      </c>
+      <c r="F16" s="125"/>
+      <c r="G16" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H16" s="35"/>
+      <c r="I16" s="71"/>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B17" s="32"/>
       <c r="C17" s="35"/>
       <c r="D17" s="36"/>
       <c r="E17" s="31"/>
-      <c r="F17" s="31"/>
-      <c r="G17" s="35"/>
-      <c r="H17" s="70"/>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="F17" s="125"/>
+      <c r="G17" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H17" s="35"/>
+      <c r="I17" s="71"/>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B18" s="32"/>
       <c r="C18" s="35"/>
       <c r="D18" s="31"/>
       <c r="E18" s="31"/>
-      <c r="F18" s="31"/>
-      <c r="G18" s="35"/>
-      <c r="H18" s="70"/>
-    </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.4">
+      <c r="F18" s="125"/>
+      <c r="G18" s="120" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H18" s="35"/>
+      <c r="I18" s="71"/>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B19" s="6" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C19" s="33"/>
       <c r="D19" s="34"/>
       <c r="E19" s="34"/>
-      <c r="F19" s="34"/>
-      <c r="G19" s="83"/>
-      <c r="H19" s="69"/>
-    </row>
-    <row r="20" spans="2:8" ht="45.6" x14ac:dyDescent="0.4">
+      <c r="F19" s="128"/>
+      <c r="G19" s="34"/>
+      <c r="H19" s="84"/>
+      <c r="I19" s="70"/>
+    </row>
+    <row r="20" spans="2:9" ht="45.6" x14ac:dyDescent="0.4">
       <c r="B20" s="32" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="C20" s="35" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D20" s="36" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="E20" s="31" t="s">
-        <v>126</v>
-      </c>
-      <c r="F20" s="31"/>
-      <c r="G20" s="35"/>
-      <c r="H20" s="70">
+        <v>123</v>
+      </c>
+      <c r="F20" s="125"/>
+      <c r="G20" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H20" s="35"/>
+      <c r="I20" s="71">
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="2:8" ht="45.6" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:9" ht="45.6" x14ac:dyDescent="0.4">
       <c r="B21" s="32" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="C21" s="35" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D21" s="36" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="E21" s="31" t="s">
-        <v>126</v>
-      </c>
-      <c r="F21" s="31"/>
-      <c r="G21" s="35"/>
-      <c r="H21" s="70"/>
-    </row>
-    <row r="22" spans="2:8" ht="45.6" x14ac:dyDescent="0.4">
+        <v>123</v>
+      </c>
+      <c r="F21" s="125"/>
+      <c r="G21" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H21" s="35"/>
+      <c r="I21" s="71"/>
+    </row>
+    <row r="22" spans="2:9" ht="45.6" x14ac:dyDescent="0.4">
       <c r="B22" s="32" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C22" s="35" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D22" s="36" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="E22" s="31" t="s">
-        <v>126</v>
-      </c>
-      <c r="F22" s="31"/>
-      <c r="G22" s="35"/>
-      <c r="H22" s="70"/>
-    </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.4">
+        <v>123</v>
+      </c>
+      <c r="F22" s="125"/>
+      <c r="G22" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H22" s="35"/>
+      <c r="I22" s="71"/>
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B23" s="40"/>
       <c r="C23" s="41"/>
       <c r="D23" s="42"/>
       <c r="E23" s="42"/>
-      <c r="F23" s="42"/>
-      <c r="G23" s="41"/>
-      <c r="H23" s="72"/>
-    </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="G24" s="75" t="s">
-        <v>293</v>
-      </c>
-      <c r="H24" s="87">
-        <f>AVERAGE(H7:H23)</f>
+      <c r="F23" s="126"/>
+      <c r="G23" s="42"/>
+      <c r="H23" s="41"/>
+      <c r="I23" s="73"/>
+    </row>
+    <row r="24" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="H24" s="76" t="s">
+        <v>290</v>
+      </c>
+      <c r="I24" s="88">
+        <f>AVERAGE(I7:I23)</f>
         <v>5</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B4:H5"/>
+  <mergeCells count="2">
+    <mergeCell ref="B4:I5"/>
+    <mergeCell ref="F6:G6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -5889,249 +6524,293 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{36B29233-B656-46A0-B3DE-6C1E8F28F7E1}">
-  <dimension ref="B2:H17"/>
+  <dimension ref="B2:I17"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="16.8" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="2.5546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="36.44140625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="51.77734375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="11.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.109375" style="1"/>
-    <col min="6" max="6" width="11.5546875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="35.109375" style="22" customWidth="1"/>
-    <col min="8" max="8" width="13.44140625" style="87" customWidth="1"/>
-    <col min="9" max="16384" width="9.109375" style="1"/>
+    <col min="2" max="2" width="30.77734375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="50.77734375" style="1" customWidth="1"/>
+    <col min="4" max="5" width="10.77734375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="7.77734375" style="22" customWidth="1"/>
+    <col min="7" max="7" width="3.77734375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="30.77734375" style="22" customWidth="1"/>
+    <col min="9" max="9" width="12.77734375" style="88" customWidth="1"/>
+    <col min="10" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B3" s="20" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B4" s="105" t="s">
-        <v>275</v>
-      </c>
-      <c r="C4" s="105"/>
-      <c r="D4" s="105"/>
-      <c r="E4" s="105"/>
-      <c r="F4" s="105"/>
-      <c r="G4" s="105"/>
-      <c r="H4" s="105"/>
-    </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.4">
-      <c r="B5" s="116"/>
-      <c r="C5" s="116"/>
-      <c r="D5" s="116"/>
-      <c r="E5" s="116"/>
-      <c r="F5" s="116"/>
-      <c r="G5" s="116"/>
-      <c r="H5" s="116"/>
-    </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.4">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B4" s="106" t="s">
+        <v>272</v>
+      </c>
+      <c r="C4" s="106"/>
+      <c r="D4" s="106"/>
+      <c r="E4" s="106"/>
+      <c r="F4" s="106"/>
+      <c r="G4" s="106"/>
+      <c r="H4" s="106"/>
+      <c r="I4" s="106"/>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B5" s="117"/>
+      <c r="C5" s="117"/>
+      <c r="D5" s="117"/>
+      <c r="E5" s="117"/>
+      <c r="F5" s="117"/>
+      <c r="G5" s="117"/>
+      <c r="H5" s="117"/>
+      <c r="I5" s="117"/>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B6" s="37" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="C6" s="38" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="D6" s="39" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E6" s="39" t="s">
-        <v>53</v>
-      </c>
-      <c r="F6" s="39" t="s">
-        <v>42</v>
-      </c>
-      <c r="G6" s="38" t="s">
+        <v>50</v>
+      </c>
+      <c r="F6" s="121" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" s="122"/>
+      <c r="H6" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="H6" s="68" t="s">
+      <c r="I6" s="69" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="22.8" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B7" s="32" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="C7" s="35" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="D7" s="36">
         <v>1</v>
       </c>
       <c r="E7" s="31" t="s">
-        <v>126</v>
-      </c>
-      <c r="F7" s="31"/>
-      <c r="G7" s="35"/>
-      <c r="H7" s="70">
+        <v>123</v>
+      </c>
+      <c r="F7" s="125"/>
+      <c r="G7" s="119" t="str">
+        <f t="shared" ref="G7:G16" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F7,"/Readme.md"),"Ver")</f>
+        <v>Ver</v>
+      </c>
+      <c r="H7" s="35"/>
+      <c r="I7" s="71">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="22.8" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B8" s="32" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="D8" s="36">
         <v>1</v>
       </c>
       <c r="E8" s="31" t="s">
-        <v>126</v>
-      </c>
-      <c r="F8" s="31"/>
-      <c r="G8" s="35"/>
-      <c r="H8" s="70"/>
-    </row>
-    <row r="9" spans="2:8" ht="22.8" x14ac:dyDescent="0.4">
+        <v>123</v>
+      </c>
+      <c r="F8" s="125"/>
+      <c r="G8" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H8" s="35"/>
+      <c r="I8" s="71"/>
+    </row>
+    <row r="9" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B9" s="32" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="C9" s="35" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="D9" s="36">
         <v>1</v>
       </c>
       <c r="E9" s="31" t="s">
-        <v>126</v>
-      </c>
-      <c r="F9" s="31"/>
-      <c r="G9" s="35"/>
-      <c r="H9" s="70"/>
-    </row>
-    <row r="10" spans="2:8" ht="22.8" x14ac:dyDescent="0.4">
+        <v>123</v>
+      </c>
+      <c r="F9" s="125"/>
+      <c r="G9" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H9" s="35"/>
+      <c r="I9" s="71"/>
+    </row>
+    <row r="10" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B10" s="32" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C10" s="35" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="D10" s="36">
         <v>1</v>
       </c>
       <c r="E10" s="31" t="s">
-        <v>126</v>
-      </c>
-      <c r="F10" s="31"/>
-      <c r="G10" s="35"/>
-      <c r="H10" s="70"/>
-    </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.4">
+        <v>123</v>
+      </c>
+      <c r="F10" s="125"/>
+      <c r="G10" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H10" s="35"/>
+      <c r="I10" s="71"/>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B11" s="32" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="D11" s="36">
         <v>1</v>
       </c>
       <c r="E11" s="31" t="s">
-        <v>126</v>
-      </c>
-      <c r="F11" s="31"/>
-      <c r="G11" s="35"/>
-      <c r="H11" s="70"/>
-    </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.4">
+        <v>123</v>
+      </c>
+      <c r="F11" s="125"/>
+      <c r="G11" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H11" s="35"/>
+      <c r="I11" s="71"/>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B12" s="32" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="C12" s="35" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="D12" s="36">
         <v>1</v>
       </c>
       <c r="E12" s="31" t="s">
-        <v>126</v>
-      </c>
-      <c r="F12" s="31"/>
-      <c r="G12" s="35"/>
-      <c r="H12" s="70"/>
-    </row>
-    <row r="13" spans="2:8" ht="22.8" x14ac:dyDescent="0.4">
+        <v>123</v>
+      </c>
+      <c r="F12" s="125"/>
+      <c r="G12" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H12" s="35"/>
+      <c r="I12" s="71"/>
+    </row>
+    <row r="13" spans="2:9" ht="33.6" x14ac:dyDescent="0.4">
       <c r="B13" s="32" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C13" s="35" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="D13" s="36">
         <v>1</v>
       </c>
       <c r="E13" s="31" t="s">
-        <v>126</v>
-      </c>
-      <c r="F13" s="31"/>
-      <c r="G13" s="35"/>
-      <c r="H13" s="70"/>
-    </row>
-    <row r="14" spans="2:8" ht="22.8" x14ac:dyDescent="0.4">
+        <v>123</v>
+      </c>
+      <c r="F13" s="125"/>
+      <c r="G13" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H13" s="35"/>
+      <c r="I13" s="71"/>
+    </row>
+    <row r="14" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B14" s="32" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="C14" s="35" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="D14" s="36">
         <v>1</v>
       </c>
       <c r="E14" s="31" t="s">
-        <v>126</v>
-      </c>
-      <c r="F14" s="31"/>
-      <c r="G14" s="35"/>
-      <c r="H14" s="70"/>
-    </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.4">
+        <v>123</v>
+      </c>
+      <c r="F14" s="125"/>
+      <c r="G14" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H14" s="35"/>
+      <c r="I14" s="71"/>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B15" s="32" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C15" s="35" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="D15" s="36">
         <v>1</v>
       </c>
       <c r="E15" s="31" t="s">
-        <v>126</v>
-      </c>
-      <c r="F15" s="31"/>
-      <c r="G15" s="35"/>
-      <c r="H15" s="70"/>
-    </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.4">
+        <v>123</v>
+      </c>
+      <c r="F15" s="125"/>
+      <c r="G15" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H15" s="35"/>
+      <c r="I15" s="71"/>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B16" s="40"/>
       <c r="C16" s="41"/>
-      <c r="D16" s="66"/>
+      <c r="D16" s="67"/>
       <c r="E16" s="42"/>
-      <c r="F16" s="42"/>
-      <c r="G16" s="41"/>
-      <c r="H16" s="72"/>
-    </row>
-    <row r="17" spans="7:8" x14ac:dyDescent="0.4">
-      <c r="G17" s="75" t="s">
-        <v>293</v>
-      </c>
-      <c r="H17" s="87">
-        <f>AVERAGE(H7:H16)</f>
+      <c r="F16" s="126"/>
+      <c r="G16" s="120" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H16" s="41"/>
+      <c r="I16" s="73"/>
+    </row>
+    <row r="17" spans="8:9" x14ac:dyDescent="0.4">
+      <c r="H17" s="76" t="s">
+        <v>290</v>
+      </c>
+      <c r="I17" s="88">
+        <f>AVERAGE(I7:I16)</f>
         <v>5</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B4:H5"/>
+  <mergeCells count="2">
+    <mergeCell ref="B4:I5"/>
+    <mergeCell ref="F6:G6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -6139,39 +6818,46 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:G17"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B2:I17"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="2.5546875" style="2" customWidth="1"/>
-    <col min="3" max="4" width="46.6640625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="33.44140625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="30.44140625" style="82" customWidth="1"/>
-    <col min="7" max="7" width="11.5546875" style="47" customWidth="1"/>
-    <col min="8" max="16384" width="9.109375" style="2"/>
+    <col min="3" max="3" width="30.77734375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="50.77734375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="40.77734375" style="2" customWidth="1"/>
+    <col min="6" max="6" width="7.77734375" style="83" customWidth="1"/>
+    <col min="7" max="7" width="3.77734375" style="65" customWidth="1"/>
+    <col min="8" max="8" width="30.77734375" style="83" customWidth="1"/>
+    <col min="9" max="9" width="12.77734375" style="47" customWidth="1"/>
+    <col min="10" max="16384" width="9.109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B2" s="103" t="s">
+    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B2" s="104" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="103"/>
-      <c r="D2" s="103"/>
-      <c r="E2" s="103"/>
-      <c r="F2" s="103"/>
-      <c r="G2" s="103"/>
-    </row>
-    <row r="3" spans="2:7" x14ac:dyDescent="0.3">
-      <c r="B3" s="117" t="s">
-        <v>332</v>
-      </c>
-      <c r="C3" s="117"/>
-      <c r="D3" s="117"/>
-      <c r="E3" s="117"/>
-      <c r="F3" s="117"/>
-      <c r="G3" s="117"/>
-    </row>
-    <row r="5" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="C2" s="104"/>
+      <c r="D2" s="104"/>
+      <c r="E2" s="104"/>
+      <c r="F2" s="104"/>
+      <c r="G2" s="104"/>
+      <c r="H2" s="104"/>
+      <c r="I2" s="104"/>
+    </row>
+    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B3" s="118" t="s">
+        <v>328</v>
+      </c>
+      <c r="C3" s="118"/>
+      <c r="D3" s="118"/>
+      <c r="E3" s="118"/>
+      <c r="F3" s="118"/>
+      <c r="G3" s="118"/>
+      <c r="H3" s="118"/>
+      <c r="I3" s="118"/>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B5" s="17" t="s">
         <v>10</v>
       </c>
@@ -6179,37 +6865,46 @@
         <v>16</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="F5" s="121" t="s">
+        <v>39</v>
+      </c>
+      <c r="G5" s="122"/>
+      <c r="H5" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="I5" s="10" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B6" s="15">
         <v>0</v>
       </c>
       <c r="C6" s="29" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="D6" s="35" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F6" s="85"/>
-      <c r="G6" s="11">
+        <v>35</v>
+      </c>
+      <c r="F6" s="86"/>
+      <c r="G6" s="119" t="str">
+        <f t="shared" ref="G6:G16" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F6,"/Readme.md"),"Ver")</f>
+        <v>Ver</v>
+      </c>
+      <c r="H6" s="86"/>
+      <c r="I6" s="11">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B7" s="15">
         <v>1</v>
       </c>
@@ -6217,131 +6912,182 @@
         <v>19</v>
       </c>
       <c r="D7" s="35" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="85"/>
-      <c r="G7" s="11"/>
-    </row>
-    <row r="8" spans="2:7" ht="114" x14ac:dyDescent="0.3">
+      <c r="F7" s="86"/>
+      <c r="G7" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H7" s="86"/>
+      <c r="I7" s="11"/>
+    </row>
+    <row r="8" spans="2:9" ht="91.2" x14ac:dyDescent="0.3">
       <c r="B8" s="15">
         <v>2</v>
       </c>
       <c r="C8" s="29" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="D8" s="35" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="85"/>
-      <c r="G8" s="11"/>
-    </row>
-    <row r="9" spans="2:7" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="F8" s="86"/>
+      <c r="G8" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H8" s="86"/>
+      <c r="I8" s="11"/>
+    </row>
+    <row r="9" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B9" s="15">
         <v>3</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>35</v>
-      </c>
-      <c r="D9" s="35"/>
+        <v>302</v>
+      </c>
+      <c r="D9" s="35" t="s">
+        <v>338</v>
+      </c>
       <c r="E9" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="F9" s="85"/>
-      <c r="G9" s="11"/>
-    </row>
-    <row r="10" spans="2:7" ht="51" x14ac:dyDescent="0.3">
+      <c r="F9" s="86"/>
+      <c r="G9" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H9" s="86"/>
+      <c r="I9" s="11"/>
+    </row>
+    <row r="10" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="B10" s="15">
         <v>4</v>
       </c>
       <c r="C10" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" s="35"/>
+        <v>303</v>
+      </c>
+      <c r="D10" s="35" t="s">
+        <v>339</v>
+      </c>
       <c r="E10" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F10" s="85"/>
-      <c r="G10" s="11"/>
-    </row>
-    <row r="11" spans="2:7" ht="28.2" x14ac:dyDescent="0.3">
+      <c r="F10" s="86"/>
+      <c r="G10" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H10" s="86"/>
+      <c r="I10" s="11"/>
+    </row>
+    <row r="11" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B11" s="15">
         <v>5</v>
       </c>
       <c r="C11" s="29" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" s="35"/>
+        <v>304</v>
+      </c>
+      <c r="D11" s="35" t="s">
+        <v>340</v>
+      </c>
       <c r="E11" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="F11" s="85"/>
-      <c r="G11" s="11"/>
-    </row>
-    <row r="12" spans="2:7" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="F11" s="86"/>
+      <c r="G11" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H11" s="86"/>
+      <c r="I11" s="11"/>
+    </row>
+    <row r="12" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B12" s="15">
         <v>6</v>
       </c>
       <c r="C12" s="29" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="D12" s="35" t="s">
-        <v>321</v>
+        <v>341</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="F12" s="85"/>
-      <c r="G12" s="11"/>
-    </row>
-    <row r="13" spans="2:7" ht="22.8" x14ac:dyDescent="0.3">
+        <v>318</v>
+      </c>
+      <c r="F12" s="86"/>
+      <c r="G12" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H12" s="86"/>
+      <c r="I12" s="11"/>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B13" s="15">
         <v>7</v>
       </c>
       <c r="C13" s="29" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="D13" s="35" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="F13" s="85"/>
-      <c r="G13" s="11"/>
-    </row>
-    <row r="14" spans="2:7" x14ac:dyDescent="0.3">
+        <v>321</v>
+      </c>
+      <c r="F13" s="86"/>
+      <c r="G13" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H13" s="86"/>
+      <c r="I13" s="11"/>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B14" s="15">
         <v>8</v>
       </c>
       <c r="C14" s="29" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="D14" s="35" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="F14" s="85"/>
-      <c r="G14" s="11"/>
-    </row>
-    <row r="15" spans="2:7" x14ac:dyDescent="0.3">
+        <v>327</v>
+      </c>
+      <c r="F14" s="86"/>
+      <c r="G14" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H14" s="86"/>
+      <c r="I14" s="11"/>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B15" s="15">
         <v>9</v>
       </c>
       <c r="C15" s="29"/>
       <c r="D15" s="35"/>
       <c r="E15" s="3"/>
-      <c r="F15" s="85"/>
-      <c r="G15" s="11"/>
-    </row>
-    <row r="16" spans="2:7" x14ac:dyDescent="0.3">
+      <c r="F15" s="86"/>
+      <c r="G15" s="119" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H15" s="86"/>
+      <c r="I15" s="11"/>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B16" s="16">
         <v>10</v>
       </c>
@@ -6349,23 +7095,30 @@
       <c r="D16" s="41"/>
       <c r="E16" s="4"/>
       <c r="F16" s="55"/>
-      <c r="G16" s="9"/>
-    </row>
-    <row r="17" spans="6:7" x14ac:dyDescent="0.3">
-      <c r="F17" s="75" t="s">
-        <v>293</v>
-      </c>
-      <c r="G17" s="47">
-        <f>AVERAGE(G6:G16)</f>
+      <c r="G16" s="120" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H16" s="55"/>
+      <c r="I16" s="9"/>
+    </row>
+    <row r="17" spans="8:9" x14ac:dyDescent="0.3">
+      <c r="H17" s="76" t="s">
+        <v>290</v>
+      </c>
+      <c r="I17" s="47">
+        <f>AVERAGE(I6:I16)</f>
         <v>5</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B3:G3"/>
-    <mergeCell ref="B2:G2"/>
+  <mergeCells count="3">
+    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="B2:I2"/>
+    <mergeCell ref="F5:G5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6375,14 +7128,12 @@
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="16.8" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="2.5546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="95.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="100.77734375" style="1" customWidth="1"/>
     <col min="3" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B1" s="24" t="s">
-        <v>30</v>
-      </c>
+      <c r="B1" s="24"/>
     </row>
     <row r="2" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B2" s="1" t="s">

--- a/file/table/DAPC_ProyectoCAD.xlsx
+++ b/file/table/DAPC_ProyectoCAD.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{210E5FA6-870C-46AC-AAC9-3D5D5E347E50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7DA7013-7CB6-48A1-B03C-75B770E4432E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1337,9 +1337,6 @@
     <t>Repositorio digital de proyecto</t>
   </si>
   <si>
-    <t xml:space="preserve">Repositorio de datos creado, compartido y accesible. Crear en OneDrive de Campus. </t>
-  </si>
-  <si>
     <t>Plantilla o layout - Unidades de dibujo</t>
   </si>
   <si>
@@ -1511,6 +1508,9 @@
   </si>
   <si>
     <t>Archivo único de dibujo del proyecto. Guardar copias de las diferentes versiones de avance creadas colocando el sufijo aaaammdd.</t>
+  </si>
+  <si>
+    <t>Repositorio de datos creado, compartido y accesible. Crear en OneDrive de Campus. https://forms.office.com/r/gVg8DjvVFh</t>
   </si>
 </sst>
 </file>
@@ -3156,7 +3156,7 @@
         <v>2</v>
       </c>
       <c r="C34" s="94" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="D34" s="95"/>
       <c r="E34" s="81">
@@ -3188,7 +3188,7 @@
         <v>4</v>
       </c>
       <c r="C36" s="92" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="D36" s="93"/>
       <c r="E36" s="81">
@@ -3236,7 +3236,7 @@
         <v>6</v>
       </c>
       <c r="C39" s="94" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D39" s="95"/>
       <c r="E39" s="90">
@@ -3251,7 +3251,7 @@
         <v>7</v>
       </c>
       <c r="C40" s="96" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D40" s="97"/>
       <c r="E40" s="89">
@@ -3409,7 +3409,7 @@
         <v>289</v>
       </c>
       <c r="C7" s="35" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D7" s="36">
         <v>1</v>
@@ -3418,7 +3418,7 @@
         <v>123</v>
       </c>
       <c r="F7" s="125" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G7" s="119" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F7,"/Readme.md"),"Ver")</f>
@@ -3434,7 +3434,7 @@
         <v>293</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>294</v>
+        <v>341</v>
       </c>
       <c r="D8" s="36">
         <v>1</v>
@@ -3443,7 +3443,7 @@
         <v>123</v>
       </c>
       <c r="F8" s="125" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G8" s="119" t="str">
         <f t="shared" ref="G8:G18" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F8,"/Readme.md"),"Ver")</f>
@@ -3466,7 +3466,7 @@
         <v>123</v>
       </c>
       <c r="F9" s="125" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="G9" s="119" t="str">
         <f t="shared" si="0"/>
@@ -3477,10 +3477,10 @@
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B10" s="32" t="s">
+        <v>295</v>
+      </c>
+      <c r="C10" s="35" t="s">
         <v>296</v>
-      </c>
-      <c r="C10" s="35" t="s">
-        <v>297</v>
       </c>
       <c r="D10" s="36">
         <v>1</v>
@@ -3489,7 +3489,7 @@
         <v>123</v>
       </c>
       <c r="F10" s="125" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G10" s="119" t="str">
         <f t="shared" si="0"/>
@@ -3500,10 +3500,10 @@
     </row>
     <row r="11" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
       <c r="B11" s="32" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D11" s="36">
         <v>1</v>
@@ -3512,7 +3512,7 @@
         <v>123</v>
       </c>
       <c r="F11" s="125" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G11" s="119" t="str">
         <f t="shared" si="0"/>
@@ -3523,10 +3523,10 @@
     </row>
     <row r="12" spans="2:9" ht="57" x14ac:dyDescent="0.3">
       <c r="B12" s="32" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="C12" s="35" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D12" s="36">
         <v>1</v>
@@ -3535,7 +3535,7 @@
         <v>123</v>
       </c>
       <c r="F12" s="125" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="G12" s="119" t="str">
         <f t="shared" si="0"/>
@@ -3546,10 +3546,10 @@
     </row>
     <row r="13" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B13" s="32" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="C13" s="35" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D13" s="36">
         <v>1</v>
@@ -3558,7 +3558,7 @@
         <v>123</v>
       </c>
       <c r="F13" s="125" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="G13" s="119" t="str">
         <f t="shared" si="0"/>
@@ -3569,10 +3569,10 @@
     </row>
     <row r="14" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
       <c r="B14" s="32" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C14" s="35" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D14" s="36">
         <v>1</v>
@@ -3581,7 +3581,7 @@
         <v>123</v>
       </c>
       <c r="F14" s="125" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="G14" s="119" t="str">
         <f t="shared" si="0"/>
@@ -3592,10 +3592,10 @@
     </row>
     <row r="15" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="B15" s="32" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="C15" s="35" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="D15" s="36">
         <v>1</v>
@@ -3604,7 +3604,7 @@
         <v>123</v>
       </c>
       <c r="F15" s="125" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G15" s="119" t="str">
         <f t="shared" si="0"/>
@@ -3615,10 +3615,10 @@
     </row>
     <row r="16" spans="2:9" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="32" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="C16" s="35" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D16" s="36">
         <v>1</v>
@@ -3627,7 +3627,7 @@
         <v>123</v>
       </c>
       <c r="F16" s="125" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G16" s="119" t="str">
         <f t="shared" si="0"/>
@@ -3638,10 +3638,10 @@
     </row>
     <row r="17" spans="2:9" ht="35.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="43" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="C17" s="44" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D17" s="36">
         <v>1</v>
@@ -3650,7 +3650,7 @@
         <v>123</v>
       </c>
       <c r="F17" s="125" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="G17" s="119" t="str">
         <f t="shared" si="0"/>
@@ -3796,7 +3796,7 @@
         <v>Ver</v>
       </c>
       <c r="H8" s="35" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="I8" s="71">
         <v>5</v>
@@ -3821,7 +3821,7 @@
         <v>Ver</v>
       </c>
       <c r="H9" s="35" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="I9" s="71"/>
     </row>
@@ -3888,7 +3888,7 @@
         <v>Ver</v>
       </c>
       <c r="H12" s="35" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="I12" s="71"/>
     </row>
@@ -3911,7 +3911,7 @@
         <v>Ver</v>
       </c>
       <c r="H13" s="35" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="I13" s="71"/>
     </row>
@@ -3934,7 +3934,7 @@
         <v>Ver</v>
       </c>
       <c r="H14" s="35" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="I14" s="71"/>
     </row>
@@ -5682,7 +5682,7 @@
     </row>
     <row r="7" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B7" s="6" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C7" s="33"/>
       <c r="D7" s="34"/>
@@ -5697,7 +5697,7 @@
         <v>225</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D8" s="31">
         <v>1</v>
@@ -6545,7 +6545,7 @@
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B3" s="20" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.4">
@@ -6847,7 +6847,7 @@
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="118" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C3" s="118"/>
       <c r="D3" s="118"/>
@@ -6912,7 +6912,7 @@
         <v>19</v>
       </c>
       <c r="D7" s="35" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>31</v>
@@ -6930,10 +6930,10 @@
         <v>2</v>
       </c>
       <c r="C8" s="29" t="s">
+        <v>322</v>
+      </c>
+      <c r="D8" s="35" t="s">
         <v>323</v>
-      </c>
-      <c r="D8" s="35" t="s">
-        <v>324</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>15</v>
@@ -6951,10 +6951,10 @@
         <v>3</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D9" s="35" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>32</v>
@@ -6972,10 +6972,10 @@
         <v>4</v>
       </c>
       <c r="C10" s="29" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D10" s="35" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>33</v>
@@ -6993,10 +6993,10 @@
         <v>5</v>
       </c>
       <c r="C11" s="29" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D11" s="35" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>34</v>
@@ -7014,13 +7014,13 @@
         <v>6</v>
       </c>
       <c r="C12" s="29" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D12" s="35" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F12" s="86"/>
       <c r="G12" s="119" t="str">
@@ -7035,13 +7035,13 @@
         <v>7</v>
       </c>
       <c r="C13" s="29" t="s">
+        <v>318</v>
+      </c>
+      <c r="D13" s="35" t="s">
         <v>319</v>
       </c>
-      <c r="D13" s="35" t="s">
+      <c r="E13" s="3" t="s">
         <v>320</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>321</v>
       </c>
       <c r="F13" s="86"/>
       <c r="G13" s="119" t="str">
@@ -7056,13 +7056,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="29" t="s">
+        <v>324</v>
+      </c>
+      <c r="D14" s="35" t="s">
         <v>325</v>
       </c>
-      <c r="D14" s="35" t="s">
+      <c r="E14" s="3" t="s">
         <v>326</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>327</v>
       </c>
       <c r="F14" s="86"/>
       <c r="G14" s="119" t="str">

--- a/file/table/DAPC_ProyectoCAD.xlsx
+++ b/file/table/DAPC_ProyectoCAD.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7DA7013-7CB6-48A1-B03C-75B770E4432E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6CE7CF0-B114-4A91-B3E9-9A3395291C17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0.Inicio" sheetId="7" r:id="rId1"/>
@@ -19,7 +19,7 @@
     <sheet name="3.Electrica" sheetId="5" r:id="rId4"/>
     <sheet name="4.Bodegaje" sheetId="9" r:id="rId5"/>
     <sheet name="5.Planos" sheetId="6" r:id="rId6"/>
-    <sheet name="5.Archivos" sheetId="1" r:id="rId7"/>
+    <sheet name="6.Archivos" sheetId="1" r:id="rId7"/>
     <sheet name="Metadata" sheetId="3" r:id="rId8"/>
   </sheets>
   <externalReferences>
@@ -282,7 +282,7 @@
     <author>Test</author>
   </authors>
   <commentList>
-    <comment ref="F5" authorId="0" shapeId="0" xr:uid="{634A2F11-6BC0-4DF5-92C2-329F8A975203}">
+    <comment ref="F6" authorId="0" shapeId="0" xr:uid="{634A2F11-6BC0-4DF5-92C2-329F8A975203}">
       <text>
         <r>
           <rPr>
@@ -323,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="342">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="345">
   <si>
     <t>1. Especificaciones técnicas generales</t>
   </si>
@@ -523,15 +523,6 @@
     <t>mm</t>
   </si>
   <si>
-    <t>Líneas de vida</t>
-  </si>
-  <si>
-    <t>Distribución interna</t>
-  </si>
-  <si>
-    <t>Elementos estructurales</t>
-  </si>
-  <si>
     <t>Longitud del patio a lo ancho del lote.</t>
   </si>
   <si>
@@ -638,9 +629,6 @@
   </si>
   <si>
     <t>Área ocupada por escalera = ancho * número de escalones  * longitud de huella.</t>
-  </si>
-  <si>
-    <t>Especificaciones generales e índices</t>
   </si>
   <si>
     <t>Área construída</t>
@@ -757,9 +745,6 @@
     <t>Un.</t>
   </si>
   <si>
-    <t>Tabla de áreas (resumen a incluir en planos)</t>
-  </si>
-  <si>
     <t>Estructura - # de columnas a lo largo</t>
   </si>
   <si>
@@ -820,21 +805,6 @@
     <t>La cubierta debe descargar sobre la viga canal lateral a los costados utilizando sobrelapado.</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">A los costados y a lo ancho de la cubierta (incluídos voladizos), se deben dibujar canales de recolección de aguas lluvias. Diseñar con el ancho indicado. </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>Ver nota 1a.</t>
-    </r>
-  </si>
-  <si>
     <t>Viga canal - Costados</t>
   </si>
   <si>
@@ -860,9 +830,6 @@
   </si>
   <si>
     <t>Se calcula con el número de ventiladores x área de cada ventilador.</t>
-  </si>
-  <si>
-    <t>Localizadas cerca a la puerta de acceso y en costado de la bodega. Máximo ocupar 60 m² en planta, incluida el área de la escalera.</t>
   </si>
   <si>
     <t>Interno bajo cubierta solo sobre zona de oficinas. Utilizar solo baranda perimetral y sin muros. Descontar área de escalera.</t>
@@ -1066,20 +1033,6 @@
     <t>Área disponible en cubierta</t>
   </si>
   <si>
-    <r>
-      <t>Diseño de cubierta</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (dibujo y diseño a partir de la altura de la bodega)</t>
-    </r>
-  </si>
-  <si>
     <t>Panel solar - Largo</t>
   </si>
   <si>
@@ -1134,37 +1087,9 @@
     <t>Esquema solo en planta. Red de datos en zona de oficinas y puntos generales de localización de equipos de cómputo, repetidores wi-fi y cámaras.</t>
   </si>
   <si>
-    <r>
-      <t>Energía solar</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (evaluar únicamente el número de páneles que se pueden instalar y dibujarlos sobre la cubierta)</t>
-    </r>
-  </si>
-  <si>
     <t>La distribución de una bodega en un proyecto implica planificar la disposición de las áreas y elementos para optimizar el flujo de materiales, maximizar el espacio y garantizar la eficiencia operativa. Se deben considerar factores como el tipo de productos, la rotación, el tamaño del almacén y los equipos de manipulación.</t>
   </si>
   <si>
-    <r>
-      <t>Distribución interna</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (al menos se deben incluir 3 referencias distintas de transformadores eléctricos industriales)</t>
-    </r>
-  </si>
-  <si>
     <t>4. Bodegaje</t>
   </si>
   <si>
@@ -1177,9 +1102,6 @@
     <t>Separación entre estantes</t>
   </si>
   <si>
-    <t>Estantería</t>
-  </si>
-  <si>
     <t>Altura máxima de montacargas</t>
   </si>
   <si>
@@ -1252,9 +1174,6 @@
     <t>Transformador 3 - Ref: #####</t>
   </si>
   <si>
-    <t>Cuadro de cantidades (resumen a incluir en planos, no es necesario realizar costos unitarios)</t>
-  </si>
-  <si>
     <t>Plano de planta general</t>
   </si>
   <si>
@@ -1313,9 +1232,6 @@
   </si>
   <si>
     <t>Archivos</t>
-  </si>
-  <si>
-    <t>Grupos, integrantes y resúmen de calificaciones</t>
   </si>
   <si>
     <t xml:space="preserve">En un proyecto, las especificaciones técnicas son documentos que detallan las normas, requisitos, procedimientos y condiciones técnicas que deben cumplirse en la ejecución de un proyecto. Estos documentos guían la implementación del proyecto, asegurando que se cumplan los estándares de calidad y se alcancen los resultados deseados. 
@@ -1423,8 +1339,134 @@
     <t>Utilizando las especificaciones del Reglamento Técnico de Instalaciones Eléctricas - RETIE del Ministerio de Minas y Energía de Colombia, dibuje la acometida eléctrica. Dibujar en planta y en cortes. Esquema solo en planta. Conexión desde poste o subterránea desde lindero de entrada al predio en uno de los laterales.</t>
   </si>
   <si>
+    <t>/file/cad/DAPC.dwg</t>
+  </si>
+  <si>
+    <t>Plano digital del proyecto</t>
+  </si>
+  <si>
+    <t>Generados a partir de layouts e integrados en un único archivo de Acrobat .pdf.</t>
+  </si>
+  <si>
+    <t>/file/report/DAPC_Planos.pdf</t>
+  </si>
+  <si>
+    <t>Crear un logotipo en AutoCAD.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plantilla o layout AutoCAD
+</t>
+  </si>
+  <si>
+    <t>Incluye unidades de dibujo lineales en metros, angulares en grados, precisión a dos decimales, capas o layers, estilos de acotado fijos y anotativos para las diferentes escalas de impresión a usar utilizando el prefijo DAPC., formatos para impresión A0 / A4 con logotipo, código y nombre del grupo. Se deben utilizar los nombres de capas establecidos en la norma internacional estándar ISO-13567, aplicando las especificaciones del United States National CAD Stardard - v5 del National Institute of Building Sciences para los grupos A-Architectural, C-Civil, E-Electrical, S-Structural, V-Survey / Mapping y W-Distributed Energy.</t>
+  </si>
+  <si>
+    <t>Fichas técnicas</t>
+  </si>
+  <si>
+    <t>Fichas técnicas de elementos utilizandos para el dibujo.</t>
+  </si>
+  <si>
+    <t>/file/ref/*.pdf</t>
+  </si>
+  <si>
+    <t>Bodegaje</t>
+  </si>
+  <si>
+    <t>Arquitectónica y estructural</t>
+  </si>
+  <si>
+    <t>M01A06</t>
+  </si>
+  <si>
+    <t>M01A05</t>
+  </si>
+  <si>
+    <t>M01A01</t>
+  </si>
+  <si>
+    <t>M01A02a</t>
+  </si>
+  <si>
+    <t>M01A04</t>
+  </si>
+  <si>
+    <t>M01A03</t>
+  </si>
+  <si>
+    <t>Utilizar los bloques ejemplo del ADC de AutoCAD, o utilizar una librería de bloque externos, citando la fuente de descarga.</t>
+  </si>
+  <si>
+    <t>Para el dibujo de los planos eléctricos, utilizar los bloques creados a partir de las especificaciones establecidas en el Reglamento Técnico de Instalaciones Eléctricas - RETIE del Ministerio de Minas y Energía de Colombia.</t>
+  </si>
+  <si>
+    <t>Utilizar una librería de bloque externos citando la fuente de descarga. Por ejemplo: cámaras de vigilancia, luces de emergencia, panel solar.</t>
+  </si>
+  <si>
+    <t>Archivo único de dibujo del proyecto. Guardar copias de las diferentes versiones de avance creadas colocando el sufijo aaaammdd.</t>
+  </si>
+  <si>
+    <t>Repositorio de datos creado, compartido y accesible. Crear en OneDrive de Campus. https://forms.office.com/r/gVg8DjvVFh</t>
+  </si>
+  <si>
+    <t>Repositorio</t>
+  </si>
+  <si>
+    <t>Varios</t>
+  </si>
+  <si>
     <r>
-      <t xml:space="preserve">Especificaciones generales y redes </t>
+      <t xml:space="preserve">A los costados y a lo ancho de la cubierta (incluídos voladizos), se deben dibujar canales de recolección de aguas lluvias, como mínimo 0.4 metros. </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>Ver nota 1a.</t>
+    </r>
+  </si>
+  <si>
+    <t>2a. Especificaciones generales e índices arquitectónicos</t>
+  </si>
+  <si>
+    <r>
+      <t>2b. Diseño de cubierta</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (dibujo y diseño a partir de la altura de la bodega)</t>
+    </r>
+  </si>
+  <si>
+    <t>2c. Líneas de vida</t>
+  </si>
+  <si>
+    <t>2d. Distribución arquitectónica interna</t>
+  </si>
+  <si>
+    <t>Localizadas cerca a la puerta de acceso y en costado de la bodega. Máximo ocupar 60 m² en planta, incluida el área de la escalera. Internamente incluir en la distribución: sala de ventas, oficinas, sala de juntas, baños.</t>
+  </si>
+  <si>
+    <t>2e. Elementos estructurales</t>
+  </si>
+  <si>
+    <t>2d. Tabla de áreas (resumen a incluir en planos)</t>
+  </si>
+  <si>
+    <t>2f. Cuadro de cantidades (resumen a incluir en planos, no es necesario realizar costos unitarios)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">3a. Especificaciones generales y redes </t>
     </r>
     <r>
       <rPr>
@@ -1437,87 +1479,54 @@
     </r>
   </si>
   <si>
-    <t>/file/cad/DAPC.dwg</t>
-  </si>
-  <si>
-    <t>Plano digital del proyecto</t>
-  </si>
-  <si>
-    <t>Generados a partir de layouts e integrados en un único archivo de Acrobat .pdf.</t>
-  </si>
-  <si>
-    <t>/file/report/DAPC_Planos.pdf</t>
-  </si>
-  <si>
-    <t>Crear un logotipo en AutoCAD.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Plantilla o layout AutoCAD
-</t>
-  </si>
-  <si>
-    <t>Incluye unidades de dibujo lineales en metros, angulares en grados, precisión a dos decimales, capas o layers, estilos de acotado fijos y anotativos para las diferentes escalas de impresión a usar utilizando el prefijo DAPC., formatos para impresión A0 / A4 con logotipo, código y nombre del grupo. Se deben utilizar los nombres de capas establecidos en la norma internacional estándar ISO-13567, aplicando las especificaciones del United States National CAD Stardard - v5 del National Institute of Building Sciences para los grupos A-Architectural, C-Civil, E-Electrical, S-Structural, V-Survey / Mapping y W-Distributed Energy.</t>
-  </si>
-  <si>
-    <t>Fichas técnicas</t>
-  </si>
-  <si>
-    <t>Fichas técnicas de elementos utilizandos para el dibujo.</t>
-  </si>
-  <si>
-    <t>/file/ref/*.pdf</t>
-  </si>
-  <si>
-    <t>5. Archivos digitales del proyecto</t>
-  </si>
-  <si>
-    <t>4. Planos</t>
-  </si>
-  <si>
-    <t>Bodegaje</t>
-  </si>
-  <si>
-    <t>Arquitectónica y estructural</t>
-  </si>
-  <si>
-    <t>M01A06</t>
-  </si>
-  <si>
-    <t>M01A05</t>
-  </si>
-  <si>
-    <t>M01A01</t>
-  </si>
-  <si>
-    <t>M01A02a</t>
-  </si>
-  <si>
-    <t>M01A04</t>
-  </si>
-  <si>
-    <t>M01A03</t>
-  </si>
-  <si>
-    <t>Utilizar los bloques ejemplo del ADC de AutoCAD, o utilizar una librería de bloque externos, citando la fuente de descarga.</t>
-  </si>
-  <si>
-    <t>Para el dibujo de los planos eléctricos, utilizar los bloques creados a partir de las especificaciones establecidas en el Reglamento Técnico de Instalaciones Eléctricas - RETIE del Ministerio de Minas y Energía de Colombia.</t>
-  </si>
-  <si>
-    <t>Utilizar una librería de bloque externos citando la fuente de descarga. Por ejemplo: cámaras de vigilancia, luces de emergencia, panel solar.</t>
-  </si>
-  <si>
-    <t>Archivo único de dibujo del proyecto. Guardar copias de las diferentes versiones de avance creadas colocando el sufijo aaaammdd.</t>
-  </si>
-  <si>
-    <t>Repositorio de datos creado, compartido y accesible. Crear en OneDrive de Campus. https://forms.office.com/r/gVg8DjvVFh</t>
+    <r>
+      <t>3b. Energía solar</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (evaluar únicamente el número de páneles que se pueden instalar y dibujarlos sobre la cubierta)</t>
+    </r>
+  </si>
+  <si>
+    <t>4a. Estantería</t>
+  </si>
+  <si>
+    <r>
+      <t>4b. Distribución interna</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (al menos se deben incluir 3 referencias distintas de transformadores eléctricos industriales)</t>
+    </r>
+  </si>
+  <si>
+    <t>5. Planos</t>
+  </si>
+  <si>
+    <t>6. Archivos digitales del proyecto</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En un proyecto, los archivos digitales son todos aquellos documentos, datos e información que se generan y almacenan en formato digital, como parte de las actividades y resultados del proyecto. Estos archivos pueden incluir dibujos CAD, textos, imágenes, videos, hojas de cálculo, bases de datos, presentaciones, entre otros, y se utilizan para la creación, gestión, almacenamiento y distribución de la información del proyecto. </t>
+  </si>
+  <si>
+    <t>0. Grupos, integrantes y resúmen de calificaciones</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1610,6 +1619,12 @@
     <font>
       <sz val="8"/>
       <color theme="10"/>
+      <name val="Segoe UI Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF0070C0"/>
       <name val="Segoe UI Light"/>
       <family val="2"/>
     </font>
@@ -2094,7 +2109,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="133">
+  <cellXfs count="189">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2106,18 +2121,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -2127,15 +2136,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -2145,22 +2145,84 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
@@ -2170,122 +2232,6 @@
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -2295,9 +2241,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -2313,12 +2256,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
@@ -2344,9 +2281,6 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2360,9 +2294,6 @@
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -2429,24 +2360,6 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -2477,23 +2390,302 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2809,30 +3001,30 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82EDA320-F942-4FCE-8343-60C075021E69}">
-  <dimension ref="B1:H45"/>
+  <dimension ref="B1:E41"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="2.5546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="50.77734375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="15.77734375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="12.77734375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="2.5546875" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.109375" style="2"/>
+    <col min="1" max="2" width="2.5546875" style="51" customWidth="1"/>
+    <col min="3" max="3" width="50.77734375" style="51" customWidth="1"/>
+    <col min="4" max="4" width="15.77734375" style="51" customWidth="1"/>
+    <col min="5" max="5" width="12.77734375" style="51" customWidth="1"/>
+    <col min="6" max="6" width="2.5546875" style="51" customWidth="1"/>
+    <col min="7" max="16384" width="9.109375" style="51"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="E1" s="24" t="s">
+      <c r="E1" s="104" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="51" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B3" s="20" t="s">
-        <v>287</v>
+      <c r="B3" s="105" t="s">
+        <v>344</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.3">
@@ -2856,460 +3048,380 @@
       <c r="E6" s="106"/>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B7" s="111" t="s">
+      <c r="B7" s="107" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="112"/>
-      <c r="D7" s="112"/>
-      <c r="E7" s="113"/>
+      <c r="C7" s="108"/>
+      <c r="D7" s="108"/>
+      <c r="E7" s="109"/>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="98" t="s">
+      <c r="B8" s="70" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="99"/>
-      <c r="D8" s="99"/>
-      <c r="E8" s="100"/>
+      <c r="C8" s="71"/>
+      <c r="D8" s="71"/>
+      <c r="E8" s="72"/>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="114" t="s">
+      <c r="B9" s="110" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="115"/>
-      <c r="D9" s="115"/>
-      <c r="E9" s="116"/>
+      <c r="C9" s="111"/>
+      <c r="D9" s="111"/>
+      <c r="E9" s="112"/>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="98" t="s">
+      <c r="B10" s="70" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="99"/>
-      <c r="D10" s="99"/>
-      <c r="E10" s="100"/>
+      <c r="C10" s="71"/>
+      <c r="D10" s="71"/>
+      <c r="E10" s="72"/>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B11" s="101"/>
-      <c r="C11" s="102"/>
-      <c r="D11" s="102"/>
-      <c r="E11" s="103"/>
+      <c r="B11" s="73"/>
+      <c r="C11" s="74"/>
+      <c r="D11" s="74"/>
+      <c r="E11" s="75"/>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B12" s="114" t="s">
+      <c r="B12" s="110" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="115"/>
-      <c r="D12" s="115"/>
-      <c r="E12" s="116"/>
+      <c r="C12" s="111"/>
+      <c r="D12" s="111"/>
+      <c r="E12" s="112"/>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="98" t="s">
+      <c r="B13" s="70" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="99"/>
-      <c r="D13" s="99"/>
-      <c r="E13" s="100"/>
+      <c r="C13" s="71"/>
+      <c r="D13" s="71"/>
+      <c r="E13" s="72"/>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B14" s="101"/>
-      <c r="C14" s="102"/>
-      <c r="D14" s="102"/>
-      <c r="E14" s="103"/>
+      <c r="B14" s="73"/>
+      <c r="C14" s="74"/>
+      <c r="D14" s="74"/>
+      <c r="E14" s="75"/>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B15" s="23" t="s">
+      <c r="B15" s="113" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="23"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
+      <c r="C15" s="113"/>
+      <c r="D15" s="113"/>
+      <c r="E15" s="113"/>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B16" s="18"/>
-      <c r="C16" s="18"/>
-      <c r="D16" s="18"/>
-      <c r="E16" s="18"/>
-    </row>
-    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B17" s="104" t="s">
+      <c r="B16" s="114"/>
+      <c r="C16" s="114"/>
+      <c r="D16" s="114"/>
+      <c r="E16" s="114"/>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B17" s="77" t="s">
         <v>14</v>
       </c>
-      <c r="C17" s="104"/>
-      <c r="D17" s="104"/>
-      <c r="E17" s="104"/>
-    </row>
-    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B18" s="17" t="s">
+      <c r="C17" s="77"/>
+      <c r="D17" s="77"/>
+      <c r="E17" s="77"/>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B18" s="52" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="115" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D18" s="116" t="s">
         <v>28</v>
       </c>
-      <c r="E18" s="10" t="s">
+      <c r="E18" s="53" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B19" s="15">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B19" s="117">
         <v>1</v>
       </c>
-      <c r="C19" s="25" t="s">
+      <c r="C19" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="D19" s="27" t="s">
+      <c r="D19" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="E19" s="11">
+      <c r="E19" s="118">
         <f t="shared" ref="E19:E28" si="0">IFERROR(RIGHT(D19,1)*1,0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B20" s="15">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B20" s="117">
         <v>2</v>
       </c>
-      <c r="C20" s="25" t="s">
+      <c r="C20" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="D20" s="27" t="s">
+      <c r="D20" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="E20" s="11">
+      <c r="E20" s="118">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B21" s="15">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B21" s="117">
         <v>3</v>
       </c>
-      <c r="C21" s="25" t="s">
+      <c r="C21" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="D21" s="27" t="s">
+      <c r="D21" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="E21" s="11">
+      <c r="E21" s="118">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B22" s="15">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B22" s="117">
         <v>4</v>
       </c>
-      <c r="C22" s="25" t="s">
+      <c r="C22" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="D22" s="27" t="s">
+      <c r="D22" s="17" t="s">
         <v>7</v>
       </c>
-      <c r="E22" s="11">
+      <c r="E22" s="118">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B23" s="15">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B23" s="117">
         <v>5</v>
       </c>
-      <c r="C23" s="25" t="s">
+      <c r="C23" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="D23" s="27" t="s">
+      <c r="D23" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="E23" s="11">
+      <c r="E23" s="118">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B24" s="15">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B24" s="117">
         <v>6</v>
       </c>
-      <c r="C24" s="25" t="s">
+      <c r="C24" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="D24" s="27"/>
-      <c r="E24" s="11">
+      <c r="D24" s="17"/>
+      <c r="E24" s="118">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B25" s="15">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B25" s="117">
         <v>7</v>
       </c>
-      <c r="C25" s="25" t="s">
+      <c r="C25" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="D25" s="27"/>
-      <c r="E25" s="11">
+      <c r="D25" s="17"/>
+      <c r="E25" s="118">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B26" s="15">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B26" s="117">
         <v>8</v>
       </c>
-      <c r="C26" s="25" t="s">
+      <c r="C26" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="D26" s="27"/>
-      <c r="E26" s="11">
+      <c r="D26" s="17"/>
+      <c r="E26" s="118">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B27" s="15">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B27" s="117">
         <v>9</v>
       </c>
-      <c r="C27" s="25" t="s">
+      <c r="C27" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="D27" s="27"/>
-      <c r="E27" s="11">
+      <c r="D27" s="17"/>
+      <c r="E27" s="118">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B28" s="16">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B28" s="119">
         <v>10</v>
       </c>
-      <c r="C28" s="26" t="s">
+      <c r="C28" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="D28" s="28"/>
-      <c r="E28" s="9">
+      <c r="D28" s="18"/>
+      <c r="E28" s="120">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="D29" s="19" t="s">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="D29" s="121" t="s">
         <v>11</v>
       </c>
-      <c r="E29" s="12">
+      <c r="E29" s="63">
         <f>SUM(E19:E28)</f>
         <v>27</v>
       </c>
     </row>
-    <row r="30" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B30" s="77"/>
-      <c r="C30" s="77"/>
-      <c r="D30" s="77"/>
-      <c r="E30" s="77"/>
-      <c r="F30" s="77"/>
-      <c r="G30" s="77"/>
-      <c r="H30" s="77"/>
-    </row>
-    <row r="31" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B31" s="105" t="s">
-        <v>282</v>
-      </c>
-      <c r="C31" s="105"/>
-      <c r="D31" s="105"/>
-      <c r="E31" s="105"/>
-      <c r="F31" s="77"/>
-      <c r="G31" s="77"/>
-      <c r="H31" s="77"/>
-    </row>
-    <row r="32" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B32" s="78" t="s">
+    <row r="31" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B31" s="77" t="s">
+        <v>270</v>
+      </c>
+      <c r="C31" s="77"/>
+      <c r="D31" s="77"/>
+      <c r="E31" s="77"/>
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B32" s="52" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="107" t="s">
+      <c r="C32" s="79" t="s">
         <v>37</v>
       </c>
-      <c r="D32" s="108"/>
-      <c r="E32" s="79" t="s">
+      <c r="D32" s="80"/>
+      <c r="E32" s="53" t="s">
         <v>27</v>
       </c>
-      <c r="F32" s="77"/>
-      <c r="G32" s="77"/>
-      <c r="H32" s="77"/>
-    </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B33" s="80">
+    </row>
+    <row r="33" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B33" s="54">
         <v>1</v>
       </c>
-      <c r="C33" s="109" t="s">
-        <v>283</v>
-      </c>
-      <c r="D33" s="110"/>
-      <c r="E33" s="81">
+      <c r="C33" s="81" t="s">
+        <v>271</v>
+      </c>
+      <c r="D33" s="82"/>
+      <c r="E33" s="55">
         <f>'1.Tecnica'!I19</f>
         <v>5</v>
       </c>
-      <c r="F33" s="77"/>
-      <c r="G33" s="77"/>
-      <c r="H33" s="77"/>
-    </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B34" s="80">
+    </row>
+    <row r="34" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B34" s="54">
         <v>2</v>
       </c>
-      <c r="C34" s="94" t="s">
-        <v>330</v>
-      </c>
-      <c r="D34" s="95"/>
-      <c r="E34" s="81">
+      <c r="C34" s="66" t="s">
+        <v>314</v>
+      </c>
+      <c r="D34" s="67"/>
+      <c r="E34" s="55">
         <f>'2.ArquitectonicaEstructural'!I103</f>
         <v>5</v>
       </c>
-      <c r="F34" s="77"/>
-      <c r="G34" s="77"/>
-      <c r="H34" s="77"/>
-    </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B35" s="80">
+    </row>
+    <row r="35" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B35" s="54">
         <v>3</v>
       </c>
-      <c r="C35" s="94" t="s">
-        <v>284</v>
-      </c>
-      <c r="D35" s="95"/>
-      <c r="E35" s="81">
+      <c r="C35" s="66" t="s">
+        <v>272</v>
+      </c>
+      <c r="D35" s="67"/>
+      <c r="E35" s="55">
         <f>'3.Electrica'!I28</f>
         <v>5</v>
       </c>
-      <c r="F35" s="77"/>
-      <c r="G35" s="77"/>
-      <c r="H35" s="77"/>
-    </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B36" s="80">
+    </row>
+    <row r="36" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B36" s="54">
         <v>4</v>
       </c>
-      <c r="C36" s="92" t="s">
-        <v>329</v>
-      </c>
-      <c r="D36" s="93"/>
-      <c r="E36" s="81">
+      <c r="C36" s="64" t="s">
+        <v>313</v>
+      </c>
+      <c r="D36" s="65"/>
+      <c r="E36" s="55">
         <f>'4.Bodegaje'!I24</f>
         <v>5</v>
       </c>
-      <c r="F36" s="77"/>
-      <c r="G36" s="77"/>
-      <c r="H36" s="77"/>
-    </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B37" s="80">
+    </row>
+    <row r="37" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B37" s="54">
         <v>4</v>
       </c>
-      <c r="C37" s="94" t="s">
-        <v>285</v>
-      </c>
-      <c r="D37" s="95"/>
-      <c r="E37" s="81">
+      <c r="C37" s="66" t="s">
+        <v>273</v>
+      </c>
+      <c r="D37" s="67"/>
+      <c r="E37" s="55">
         <f>'5.Planos'!I17</f>
         <v>5</v>
       </c>
-      <c r="F37" s="77"/>
-      <c r="G37" s="77"/>
-      <c r="H37" s="77"/>
-    </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B38" s="80">
+    </row>
+    <row r="38" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B38" s="54">
         <v>5</v>
       </c>
-      <c r="C38" s="94" t="s">
-        <v>286</v>
-      </c>
-      <c r="D38" s="95"/>
-      <c r="E38" s="81">
-        <f>'5.Archivos'!I17</f>
+      <c r="C38" s="66" t="s">
+        <v>274</v>
+      </c>
+      <c r="D38" s="67"/>
+      <c r="E38" s="55">
+        <f>'6.Archivos'!I18</f>
         <v>5</v>
       </c>
-      <c r="F38" s="77"/>
-      <c r="G38" s="77"/>
-      <c r="H38" s="77"/>
-    </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B39" s="80">
+    </row>
+    <row r="39" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B39" s="54">
         <v>6</v>
       </c>
-      <c r="C39" s="94" t="s">
-        <v>313</v>
-      </c>
-      <c r="D39" s="95"/>
-      <c r="E39" s="90">
+      <c r="C39" s="66" t="s">
+        <v>300</v>
+      </c>
+      <c r="D39" s="67"/>
+      <c r="E39" s="103">
         <v>5</v>
       </c>
-      <c r="F39" s="77"/>
-      <c r="G39" s="77"/>
-      <c r="H39" s="77"/>
-    </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B40" s="82">
+    </row>
+    <row r="40" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B40" s="56">
         <v>7</v>
       </c>
-      <c r="C40" s="96" t="s">
-        <v>314</v>
-      </c>
-      <c r="D40" s="97"/>
-      <c r="E40" s="89">
+      <c r="C40" s="68" t="s">
+        <v>301</v>
+      </c>
+      <c r="D40" s="69"/>
+      <c r="E40" s="62">
         <v>5</v>
       </c>
-      <c r="F40" s="77"/>
-      <c r="G40" s="77"/>
-      <c r="H40" s="77"/>
-    </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B41" s="77"/>
-      <c r="C41" s="77"/>
-      <c r="D41" s="75" t="s">
-        <v>290</v>
-      </c>
-      <c r="E41" s="91">
+    </row>
+    <row r="41" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="D41" s="122" t="s">
+        <v>277</v>
+      </c>
+      <c r="E41" s="63">
         <f>AVERAGE(E33:E40)</f>
         <v>5</v>
       </c>
-      <c r="F41" s="77"/>
-      <c r="G41" s="77"/>
-      <c r="H41" s="77"/>
-    </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B42" s="77"/>
-      <c r="C42" s="77"/>
-      <c r="D42" s="77"/>
-      <c r="E42" s="77"/>
-      <c r="F42" s="77"/>
-      <c r="G42" s="77"/>
-      <c r="H42" s="77"/>
-    </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B43" s="77"/>
-      <c r="C43" s="77"/>
-      <c r="D43" s="77"/>
-      <c r="E43" s="77"/>
-      <c r="F43" s="77"/>
-      <c r="G43" s="77"/>
-      <c r="H43" s="77"/>
-    </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B44" s="77"/>
-      <c r="C44" s="77"/>
-      <c r="D44" s="77"/>
-      <c r="E44" s="77"/>
-      <c r="F44" s="77"/>
-      <c r="G44" s="77"/>
-      <c r="H44" s="77"/>
-    </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B45" s="77"/>
-      <c r="C45" s="77"/>
-      <c r="D45" s="77"/>
-      <c r="E45" s="77"/>
-      <c r="F45" s="77"/>
-      <c r="G45" s="77"/>
-      <c r="H45" s="77"/>
     </row>
   </sheetData>
   <mergeCells count="18">
@@ -3342,33 +3454,33 @@
   <dimension ref="B1:I19"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.5546875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="30.77734375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="50.77734375" style="2" customWidth="1"/>
-    <col min="4" max="5" width="10.77734375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="7.77734375" style="2" customWidth="1"/>
-    <col min="7" max="7" width="3.77734375" style="65" customWidth="1"/>
-    <col min="8" max="8" width="30.77734375" style="83" customWidth="1"/>
-    <col min="9" max="9" width="12.77734375" style="47" customWidth="1"/>
-    <col min="10" max="16384" width="9.109375" style="2"/>
+    <col min="1" max="1" width="2.5546875" style="51" customWidth="1"/>
+    <col min="2" max="2" width="30.77734375" style="51" customWidth="1"/>
+    <col min="3" max="3" width="50.77734375" style="51" customWidth="1"/>
+    <col min="4" max="5" width="10.77734375" style="51" customWidth="1"/>
+    <col min="6" max="6" width="7.77734375" style="51" customWidth="1"/>
+    <col min="7" max="7" width="3.77734375" style="51" customWidth="1"/>
+    <col min="8" max="8" width="30.77734375" style="123" customWidth="1"/>
+    <col min="9" max="9" width="12.77734375" style="124" customWidth="1"/>
+    <col min="10" max="16384" width="9.109375" style="51"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="E1" s="24"/>
+      <c r="E1" s="104"/>
     </row>
     <row r="2" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="51" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="105" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B4" s="106" t="s">
-        <v>288</v>
+        <v>275</v>
       </c>
       <c r="C4" s="106"/>
       <c r="D4" s="106"/>
@@ -3381,302 +3493,292 @@
       <c r="E5" s="106"/>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B6" s="37" t="s">
+      <c r="B6" s="125" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="38" t="s">
+      <c r="C6" s="126" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="39" t="s">
+      <c r="D6" s="127" t="s">
         <v>49</v>
       </c>
-      <c r="E6" s="39" t="s">
+      <c r="E6" s="127" t="s">
         <v>50</v>
       </c>
-      <c r="F6" s="121" t="s">
+      <c r="F6" s="128" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="122"/>
-      <c r="H6" s="38" t="s">
+      <c r="G6" s="129"/>
+      <c r="H6" s="126" t="s">
         <v>26</v>
       </c>
-      <c r="I6" s="69" t="s">
+      <c r="I6" s="130" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
-      <c r="B7" s="32" t="s">
+      <c r="B7" s="131" t="s">
+        <v>276</v>
+      </c>
+      <c r="C7" s="132" t="s">
+        <v>299</v>
+      </c>
+      <c r="D7" s="95">
+        <v>1</v>
+      </c>
+      <c r="E7" s="134" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="135" t="s">
+        <v>315</v>
+      </c>
+      <c r="G7" s="136" t="str">
+        <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F7,"/Readme.md"),"Ver")</f>
+        <v>Ver</v>
+      </c>
+      <c r="H7" s="97"/>
+      <c r="I7" s="98">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="B8" s="131" t="s">
+        <v>280</v>
+      </c>
+      <c r="C8" s="132" t="s">
+        <v>325</v>
+      </c>
+      <c r="D8" s="95">
+        <v>1</v>
+      </c>
+      <c r="E8" s="134" t="s">
+        <v>326</v>
+      </c>
+      <c r="F8" s="135" t="s">
+        <v>315</v>
+      </c>
+      <c r="G8" s="136" t="str">
+        <f t="shared" ref="G8:G18" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F8,"/Readme.md"),"Ver")</f>
+        <v>Ver</v>
+      </c>
+      <c r="H8" s="97"/>
+      <c r="I8" s="98"/>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B9" s="131" t="s">
+        <v>278</v>
+      </c>
+      <c r="C9" s="132" t="s">
+        <v>279</v>
+      </c>
+      <c r="D9" s="95" t="s">
+        <v>327</v>
+      </c>
+      <c r="E9" s="134"/>
+      <c r="F9" s="135" t="s">
+        <v>315</v>
+      </c>
+      <c r="G9" s="136" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H9" s="97"/>
+      <c r="I9" s="98"/>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B10" s="131" t="s">
+        <v>282</v>
+      </c>
+      <c r="C10" s="132" t="s">
+        <v>283</v>
+      </c>
+      <c r="D10" s="95">
+        <v>1</v>
+      </c>
+      <c r="E10" s="134" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" s="135" t="s">
+        <v>316</v>
+      </c>
+      <c r="G10" s="136" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H10" s="97"/>
+      <c r="I10" s="98"/>
+    </row>
+    <row r="11" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="B11" s="131" t="s">
+        <v>281</v>
+      </c>
+      <c r="C11" s="132" t="s">
+        <v>284</v>
+      </c>
+      <c r="D11" s="95" t="s">
+        <v>327</v>
+      </c>
+      <c r="E11" s="134"/>
+      <c r="F11" s="135" t="s">
+        <v>317</v>
+      </c>
+      <c r="G11" s="136" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H11" s="97"/>
+      <c r="I11" s="98"/>
+    </row>
+    <row r="12" spans="2:9" ht="57" x14ac:dyDescent="0.3">
+      <c r="B12" s="131" t="s">
+        <v>291</v>
+      </c>
+      <c r="C12" s="132" t="s">
+        <v>285</v>
+      </c>
+      <c r="D12" s="95" t="s">
+        <v>327</v>
+      </c>
+      <c r="E12" s="134"/>
+      <c r="F12" s="135" t="s">
+        <v>318</v>
+      </c>
+      <c r="G12" s="136" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H12" s="97"/>
+      <c r="I12" s="98"/>
+    </row>
+    <row r="13" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="B13" s="131" t="s">
+        <v>292</v>
+      </c>
+      <c r="C13" s="132" t="s">
+        <v>286</v>
+      </c>
+      <c r="D13" s="95" t="s">
+        <v>327</v>
+      </c>
+      <c r="E13" s="134"/>
+      <c r="F13" s="135" t="s">
+        <v>319</v>
+      </c>
+      <c r="G13" s="136" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H13" s="97"/>
+      <c r="I13" s="98"/>
+    </row>
+    <row r="14" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="B14" s="131" t="s">
+        <v>293</v>
+      </c>
+      <c r="C14" s="132" t="s">
+        <v>287</v>
+      </c>
+      <c r="D14" s="95" t="s">
+        <v>327</v>
+      </c>
+      <c r="E14" s="134"/>
+      <c r="F14" s="135" t="s">
+        <v>316</v>
+      </c>
+      <c r="G14" s="136" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H14" s="97"/>
+      <c r="I14" s="98"/>
+    </row>
+    <row r="15" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="B15" s="131" t="s">
+        <v>288</v>
+      </c>
+      <c r="C15" s="132" t="s">
+        <v>294</v>
+      </c>
+      <c r="D15" s="95">
+        <v>1</v>
+      </c>
+      <c r="E15" s="134" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15" s="135" t="s">
+        <v>320</v>
+      </c>
+      <c r="G15" s="136" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H15" s="97"/>
+      <c r="I15" s="98"/>
+    </row>
+    <row r="16" spans="2:9" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="131" t="s">
         <v>289</v>
       </c>
-      <c r="C7" s="35" t="s">
-        <v>312</v>
-      </c>
-      <c r="D7" s="36">
+      <c r="C16" s="132" t="s">
+        <v>295</v>
+      </c>
+      <c r="D16" s="95">
         <v>1</v>
       </c>
-      <c r="E7" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="F7" s="125" t="s">
-        <v>331</v>
-      </c>
-      <c r="G7" s="119" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F7,"/Readme.md"),"Ver")</f>
-        <v>Ver</v>
-      </c>
-      <c r="H7" s="35"/>
-      <c r="I7" s="71">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B8" s="32" t="s">
-        <v>293</v>
-      </c>
-      <c r="C8" s="35" t="s">
-        <v>341</v>
-      </c>
-      <c r="D8" s="36">
+      <c r="E16" s="134" t="s">
+        <v>16</v>
+      </c>
+      <c r="F16" s="135" t="s">
+        <v>320</v>
+      </c>
+      <c r="G16" s="136" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H16" s="97"/>
+      <c r="I16" s="98"/>
+    </row>
+    <row r="17" spans="2:9" ht="35.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="138" t="s">
+        <v>290</v>
+      </c>
+      <c r="C17" s="139" t="s">
+        <v>296</v>
+      </c>
+      <c r="D17" s="95">
         <v>1</v>
       </c>
-      <c r="E8" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="F8" s="125" t="s">
-        <v>331</v>
-      </c>
-      <c r="G8" s="119" t="str">
-        <f t="shared" ref="G8:G18" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F8,"/Readme.md"),"Ver")</f>
-        <v>Ver</v>
-      </c>
-      <c r="H8" s="35"/>
-      <c r="I8" s="71"/>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B9" s="32" t="s">
-        <v>291</v>
-      </c>
-      <c r="C9" s="35" t="s">
-        <v>292</v>
-      </c>
-      <c r="D9" s="36">
-        <v>1</v>
-      </c>
-      <c r="E9" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="F9" s="125" t="s">
-        <v>331</v>
-      </c>
-      <c r="G9" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H9" s="35"/>
-      <c r="I9" s="71"/>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B10" s="32" t="s">
-        <v>295</v>
-      </c>
-      <c r="C10" s="35" t="s">
-        <v>296</v>
-      </c>
-      <c r="D10" s="36">
-        <v>1</v>
-      </c>
-      <c r="E10" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="F10" s="125" t="s">
-        <v>332</v>
-      </c>
-      <c r="G10" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H10" s="35"/>
-      <c r="I10" s="71"/>
-    </row>
-    <row r="11" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="B11" s="32" t="s">
-        <v>294</v>
-      </c>
-      <c r="C11" s="35" t="s">
-        <v>297</v>
-      </c>
-      <c r="D11" s="36">
-        <v>1</v>
-      </c>
-      <c r="E11" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="F11" s="125" t="s">
-        <v>333</v>
-      </c>
-      <c r="G11" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H11" s="35"/>
-      <c r="I11" s="71"/>
-    </row>
-    <row r="12" spans="2:9" ht="57" x14ac:dyDescent="0.3">
-      <c r="B12" s="32" t="s">
-        <v>304</v>
-      </c>
-      <c r="C12" s="35" t="s">
-        <v>298</v>
-      </c>
-      <c r="D12" s="36">
-        <v>1</v>
-      </c>
-      <c r="E12" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="F12" s="125" t="s">
-        <v>334</v>
-      </c>
-      <c r="G12" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H12" s="35"/>
-      <c r="I12" s="71"/>
-    </row>
-    <row r="13" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B13" s="32" t="s">
-        <v>305</v>
-      </c>
-      <c r="C13" s="35" t="s">
-        <v>299</v>
-      </c>
-      <c r="D13" s="36">
-        <v>1</v>
-      </c>
-      <c r="E13" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="F13" s="125" t="s">
-        <v>335</v>
-      </c>
-      <c r="G13" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H13" s="35"/>
-      <c r="I13" s="71"/>
-    </row>
-    <row r="14" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="B14" s="32" t="s">
-        <v>306</v>
-      </c>
-      <c r="C14" s="35" t="s">
-        <v>300</v>
-      </c>
-      <c r="D14" s="36">
-        <v>1</v>
-      </c>
-      <c r="E14" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="F14" s="125" t="s">
-        <v>332</v>
-      </c>
-      <c r="G14" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H14" s="35"/>
-      <c r="I14" s="71"/>
-    </row>
-    <row r="15" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
-      <c r="B15" s="32" t="s">
-        <v>301</v>
-      </c>
-      <c r="C15" s="35" t="s">
-        <v>307</v>
-      </c>
-      <c r="D15" s="36">
-        <v>1</v>
-      </c>
-      <c r="E15" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="F15" s="125" t="s">
-        <v>336</v>
-      </c>
-      <c r="G15" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H15" s="35"/>
-      <c r="I15" s="71"/>
-    </row>
-    <row r="16" spans="2:9" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="32" t="s">
-        <v>302</v>
-      </c>
-      <c r="C16" s="35" t="s">
-        <v>308</v>
-      </c>
-      <c r="D16" s="36">
-        <v>1</v>
-      </c>
-      <c r="E16" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="F16" s="125" t="s">
-        <v>336</v>
-      </c>
-      <c r="G16" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H16" s="35"/>
-      <c r="I16" s="71"/>
-    </row>
-    <row r="17" spans="2:9" ht="35.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="43" t="s">
-        <v>303</v>
-      </c>
-      <c r="C17" s="44" t="s">
-        <v>309</v>
-      </c>
-      <c r="D17" s="36">
-        <v>1</v>
-      </c>
-      <c r="E17" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="F17" s="125" t="s">
-        <v>336</v>
-      </c>
-      <c r="G17" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H17" s="44"/>
-      <c r="I17" s="72"/>
+      <c r="E17" s="134" t="s">
+        <v>16</v>
+      </c>
+      <c r="F17" s="135" t="s">
+        <v>320</v>
+      </c>
+      <c r="G17" s="136" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H17" s="99"/>
+      <c r="I17" s="100"/>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B18" s="40"/>
-      <c r="C18" s="41"/>
-      <c r="D18" s="67"/>
-      <c r="E18" s="42"/>
-      <c r="F18" s="126"/>
-      <c r="G18" s="120" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H18" s="41"/>
-      <c r="I18" s="73"/>
+      <c r="B18" s="140"/>
+      <c r="C18" s="141"/>
+      <c r="D18" s="96"/>
+      <c r="E18" s="142"/>
+      <c r="F18" s="143"/>
+      <c r="G18" s="144" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H18" s="101"/>
+      <c r="I18" s="102"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="H19" s="76" t="s">
-        <v>290</v>
-      </c>
-      <c r="I19" s="47">
+      <c r="H19" s="145" t="s">
+        <v>277</v>
+      </c>
+      <c r="I19" s="124">
         <f>AVERAGE(I7:I18)</f>
         <v>5</v>
       </c>
@@ -3697,31 +3799,31 @@
   <dimension ref="B2:I113"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.5546875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="30.77734375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="50.77734375" style="2" customWidth="1"/>
-    <col min="4" max="5" width="10.77734375" style="47" customWidth="1"/>
-    <col min="6" max="6" width="7.77734375" style="127" customWidth="1"/>
-    <col min="7" max="7" width="3.77734375" style="47" customWidth="1"/>
-    <col min="8" max="8" width="30.77734375" style="83" customWidth="1"/>
-    <col min="9" max="9" width="12.77734375" style="47" customWidth="1"/>
-    <col min="10" max="10" width="2.5546875" style="2" customWidth="1"/>
-    <col min="11" max="16384" width="9.109375" style="2"/>
+    <col min="1" max="1" width="2.5546875" style="51" customWidth="1"/>
+    <col min="2" max="2" width="30.77734375" style="51" customWidth="1"/>
+    <col min="3" max="3" width="50.77734375" style="51" customWidth="1"/>
+    <col min="4" max="5" width="10.77734375" style="124" customWidth="1"/>
+    <col min="6" max="6" width="7.77734375" style="146" customWidth="1"/>
+    <col min="7" max="7" width="3.77734375" style="124" customWidth="1"/>
+    <col min="8" max="8" width="30.77734375" style="123" customWidth="1"/>
+    <col min="9" max="9" width="12.77734375" style="124" customWidth="1"/>
+    <col min="10" max="10" width="2.5546875" style="51" customWidth="1"/>
+    <col min="11" max="16384" width="9.109375" style="51"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="51" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B3" s="20" t="s">
-        <v>168</v>
+      <c r="B3" s="105" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B4" s="106" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
       <c r="C4" s="106"/>
       <c r="D4" s="106"/>
@@ -3732,1871 +3834,1901 @@
       <c r="I4" s="106"/>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B5" s="117"/>
-      <c r="C5" s="117"/>
-      <c r="D5" s="117"/>
-      <c r="E5" s="117"/>
-      <c r="F5" s="117"/>
-      <c r="G5" s="117"/>
-      <c r="H5" s="117"/>
-      <c r="I5" s="117"/>
+      <c r="B5" s="147"/>
+      <c r="C5" s="147"/>
+      <c r="D5" s="147"/>
+      <c r="E5" s="147"/>
+      <c r="F5" s="147"/>
+      <c r="G5" s="147"/>
+      <c r="H5" s="147"/>
+      <c r="I5" s="147"/>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B6" s="37" t="s">
+      <c r="B6" s="125" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="38" t="s">
+      <c r="C6" s="126" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="39" t="s">
+      <c r="D6" s="127" t="s">
         <v>49</v>
       </c>
-      <c r="E6" s="39" t="s">
+      <c r="E6" s="127" t="s">
         <v>50</v>
       </c>
-      <c r="F6" s="123" t="s">
+      <c r="F6" s="148" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="124"/>
-      <c r="H6" s="38" t="s">
+      <c r="G6" s="149"/>
+      <c r="H6" s="126" t="s">
         <v>26</v>
       </c>
-      <c r="I6" s="69" t="s">
+      <c r="I6" s="130" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B7" s="6" t="s">
-        <v>105</v>
-      </c>
-      <c r="C7" s="33"/>
-      <c r="D7" s="34"/>
-      <c r="E7" s="34"/>
-      <c r="F7" s="128"/>
-      <c r="G7" s="34"/>
-      <c r="H7" s="84"/>
-      <c r="I7" s="70"/>
+      <c r="B7" s="150" t="s">
+        <v>329</v>
+      </c>
+      <c r="C7" s="151"/>
+      <c r="D7" s="152"/>
+      <c r="E7" s="152"/>
+      <c r="F7" s="153"/>
+      <c r="G7" s="152"/>
+      <c r="H7" s="154"/>
+      <c r="I7" s="155"/>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B8" s="32" t="s">
-        <v>169</v>
-      </c>
-      <c r="C8" s="35" t="s">
-        <v>171</v>
-      </c>
-      <c r="D8" s="36">
+      <c r="B8" s="131" t="s">
+        <v>162</v>
+      </c>
+      <c r="C8" s="132" t="s">
+        <v>164</v>
+      </c>
+      <c r="D8" s="133">
         <v>8</v>
       </c>
-      <c r="E8" s="31" t="s">
+      <c r="E8" s="134" t="s">
         <v>54</v>
       </c>
-      <c r="F8" s="125"/>
-      <c r="G8" s="119" t="str">
+      <c r="F8" s="135" t="s">
+        <v>317</v>
+      </c>
+      <c r="G8" s="136" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F8,"/Readme.md"),"Ver")</f>
         <v>Ver</v>
       </c>
-      <c r="H8" s="35" t="s">
-        <v>311</v>
-      </c>
-      <c r="I8" s="71">
+      <c r="H8" s="132" t="s">
+        <v>298</v>
+      </c>
+      <c r="I8" s="137">
         <v>5</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B9" s="32" t="s">
-        <v>170</v>
-      </c>
-      <c r="C9" s="35" t="s">
-        <v>172</v>
-      </c>
-      <c r="D9" s="36">
+      <c r="B9" s="131" t="s">
+        <v>163</v>
+      </c>
+      <c r="C9" s="132" t="s">
+        <v>165</v>
+      </c>
+      <c r="D9" s="133">
         <v>10</v>
       </c>
-      <c r="E9" s="31" t="s">
+      <c r="E9" s="134" t="s">
         <v>54</v>
       </c>
-      <c r="F9" s="125"/>
-      <c r="G9" s="119" t="str">
+      <c r="F9" s="135" t="s">
+        <v>317</v>
+      </c>
+      <c r="G9" s="136" t="str">
         <f t="shared" ref="G9:G72" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F9,"/Readme.md"),"Ver")</f>
         <v>Ver</v>
       </c>
-      <c r="H9" s="35" t="s">
-        <v>311</v>
-      </c>
-      <c r="I9" s="71"/>
+      <c r="H9" s="132" t="s">
+        <v>298</v>
+      </c>
+      <c r="I9" s="137"/>
     </row>
     <row r="10" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B10" s="32" t="s">
-        <v>175</v>
-      </c>
-      <c r="C10" s="35" t="s">
-        <v>173</v>
-      </c>
-      <c r="D10" s="31">
+      <c r="B10" s="131" t="s">
+        <v>168</v>
+      </c>
+      <c r="C10" s="132" t="s">
+        <v>166</v>
+      </c>
+      <c r="D10" s="134">
         <f>D8+SumUDig</f>
         <v>35</v>
       </c>
-      <c r="E10" s="31" t="s">
+      <c r="E10" s="134" t="s">
         <v>54</v>
       </c>
-      <c r="F10" s="125"/>
-      <c r="G10" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H10" s="35"/>
-      <c r="I10" s="71"/>
+      <c r="F10" s="135" t="s">
+        <v>317</v>
+      </c>
+      <c r="G10" s="136" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H10" s="132"/>
+      <c r="I10" s="137"/>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B11" s="32" t="s">
-        <v>176</v>
-      </c>
-      <c r="C11" s="35" t="s">
-        <v>174</v>
-      </c>
-      <c r="D11" s="31" cm="1">
+      <c r="B11" s="131" t="s">
+        <v>169</v>
+      </c>
+      <c r="C11" s="132" t="s">
+        <v>167</v>
+      </c>
+      <c r="D11" s="134" cm="1">
         <f t="array" ref="D11">D9+SumUDig</f>
         <v>37</v>
       </c>
-      <c r="E11" s="31" t="s">
+      <c r="E11" s="134" t="s">
         <v>54</v>
       </c>
-      <c r="F11" s="125"/>
-      <c r="G11" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H11" s="35"/>
-      <c r="I11" s="71"/>
+      <c r="F11" s="135" t="s">
+        <v>317</v>
+      </c>
+      <c r="G11" s="136" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H11" s="132"/>
+      <c r="I11" s="137"/>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B12" s="32" t="s">
+      <c r="B12" s="131" t="s">
         <v>40</v>
       </c>
-      <c r="C12" s="35" t="s">
-        <v>185</v>
-      </c>
-      <c r="D12" s="36">
+      <c r="C12" s="132" t="s">
+        <v>178</v>
+      </c>
+      <c r="D12" s="133">
         <v>12</v>
       </c>
-      <c r="E12" s="31" t="s">
+      <c r="E12" s="134" t="s">
         <v>54</v>
       </c>
-      <c r="F12" s="125"/>
-      <c r="G12" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H12" s="35" t="s">
-        <v>311</v>
-      </c>
-      <c r="I12" s="71"/>
+      <c r="F12" s="135" t="s">
+        <v>317</v>
+      </c>
+      <c r="G12" s="136" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H12" s="132" t="s">
+        <v>298</v>
+      </c>
+      <c r="I12" s="137"/>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B13" s="32" t="s">
+      <c r="B13" s="131" t="s">
         <v>61</v>
       </c>
-      <c r="C13" s="35" t="s">
-        <v>70</v>
-      </c>
-      <c r="D13" s="36">
+      <c r="C13" s="132" t="s">
+        <v>67</v>
+      </c>
+      <c r="D13" s="133">
         <v>6</v>
       </c>
-      <c r="E13" s="31" t="s">
+      <c r="E13" s="134" t="s">
         <v>54</v>
       </c>
-      <c r="F13" s="125"/>
-      <c r="G13" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H13" s="35" t="s">
-        <v>311</v>
-      </c>
-      <c r="I13" s="71"/>
+      <c r="F13" s="135" t="s">
+        <v>317</v>
+      </c>
+      <c r="G13" s="136" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H13" s="132" t="s">
+        <v>298</v>
+      </c>
+      <c r="I13" s="137"/>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B14" s="32" t="s">
+      <c r="B14" s="131" t="s">
         <v>41</v>
       </c>
-      <c r="C14" s="35" t="s">
-        <v>69</v>
-      </c>
-      <c r="D14" s="36">
+      <c r="C14" s="132" t="s">
+        <v>66</v>
+      </c>
+      <c r="D14" s="133">
         <v>12</v>
       </c>
-      <c r="E14" s="31" t="s">
+      <c r="E14" s="134" t="s">
         <v>54</v>
       </c>
-      <c r="F14" s="125"/>
-      <c r="G14" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H14" s="35" t="s">
-        <v>311</v>
-      </c>
-      <c r="I14" s="71"/>
+      <c r="F14" s="135" t="s">
+        <v>317</v>
+      </c>
+      <c r="G14" s="136" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H14" s="132" t="s">
+        <v>298</v>
+      </c>
+      <c r="I14" s="137"/>
     </row>
     <row r="15" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B15" s="32" t="s">
+      <c r="B15" s="131" t="s">
         <v>53</v>
       </c>
-      <c r="C15" s="35" t="s">
+      <c r="C15" s="132" t="s">
         <v>62</v>
       </c>
-      <c r="D15" s="31">
+      <c r="D15" s="134">
         <f>D10</f>
         <v>35</v>
       </c>
-      <c r="E15" s="31" t="s">
+      <c r="E15" s="134" t="s">
         <v>54</v>
       </c>
-      <c r="F15" s="125"/>
-      <c r="G15" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H15" s="35"/>
-      <c r="I15" s="71"/>
+      <c r="F15" s="135" t="s">
+        <v>317</v>
+      </c>
+      <c r="G15" s="136" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H15" s="132"/>
+      <c r="I15" s="137"/>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B16" s="32" t="s">
+      <c r="B16" s="131" t="s">
         <v>52</v>
       </c>
-      <c r="C16" s="35" t="s">
+      <c r="C16" s="132" t="s">
         <v>60</v>
       </c>
-      <c r="D16" s="31">
+      <c r="D16" s="134">
         <f>D11+D14+D13</f>
         <v>55</v>
       </c>
-      <c r="E16" s="31" t="s">
+      <c r="E16" s="134" t="s">
         <v>54</v>
       </c>
-      <c r="F16" s="125"/>
-      <c r="G16" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H16" s="35"/>
-      <c r="I16" s="71"/>
+      <c r="F16" s="135" t="s">
+        <v>317</v>
+      </c>
+      <c r="G16" s="136" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H16" s="132"/>
+      <c r="I16" s="137"/>
     </row>
     <row r="17" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B17" s="32" t="s">
+      <c r="B17" s="131" t="s">
         <v>51</v>
       </c>
-      <c r="C17" s="35" t="s">
-        <v>139</v>
-      </c>
-      <c r="D17" s="31">
+      <c r="C17" s="132" t="s">
+        <v>134</v>
+      </c>
+      <c r="D17" s="134">
         <f>D16*D15</f>
         <v>1925</v>
       </c>
-      <c r="E17" s="31" t="s">
+      <c r="E17" s="134" t="s">
         <v>55</v>
       </c>
-      <c r="F17" s="125"/>
-      <c r="G17" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H17" s="35"/>
-      <c r="I17" s="71"/>
+      <c r="F17" s="135" t="s">
+        <v>317</v>
+      </c>
+      <c r="G17" s="136" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H17" s="132"/>
+      <c r="I17" s="137"/>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B18" s="43" t="s">
-        <v>108</v>
-      </c>
-      <c r="C18" s="44" t="s">
-        <v>109</v>
-      </c>
-      <c r="D18" s="45">
+      <c r="B18" s="138" t="s">
+        <v>104</v>
+      </c>
+      <c r="C18" s="139" t="s">
+        <v>105</v>
+      </c>
+      <c r="D18" s="156">
         <f>D32+D30</f>
         <v>1435</v>
       </c>
-      <c r="E18" s="31" t="s">
+      <c r="E18" s="134" t="s">
         <v>55</v>
       </c>
-      <c r="F18" s="129"/>
-      <c r="G18" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H18" s="44"/>
-      <c r="I18" s="72"/>
+      <c r="F18" s="135" t="s">
+        <v>317</v>
+      </c>
+      <c r="G18" s="136" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H18" s="139"/>
+      <c r="I18" s="157"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B19" s="43" t="s">
-        <v>106</v>
-      </c>
-      <c r="C19" s="44" t="s">
-        <v>140</v>
-      </c>
-      <c r="D19" s="45">
+      <c r="B19" s="138" t="s">
+        <v>102</v>
+      </c>
+      <c r="C19" s="139" t="s">
+        <v>135</v>
+      </c>
+      <c r="D19" s="156">
         <f>D32+D30+D46</f>
         <v>1495</v>
       </c>
-      <c r="E19" s="31" t="s">
+      <c r="E19" s="134" t="s">
         <v>55</v>
       </c>
-      <c r="F19" s="129"/>
-      <c r="G19" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H19" s="44"/>
-      <c r="I19" s="72"/>
+      <c r="F19" s="135" t="s">
+        <v>317</v>
+      </c>
+      <c r="G19" s="136" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H19" s="139"/>
+      <c r="I19" s="157"/>
     </row>
     <row r="20" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
-      <c r="B20" s="43" t="s">
-        <v>71</v>
-      </c>
-      <c r="C20" s="44" t="s">
-        <v>141</v>
-      </c>
-      <c r="D20" s="45">
+      <c r="B20" s="138" t="s">
+        <v>68</v>
+      </c>
+      <c r="C20" s="139" t="s">
+        <v>136</v>
+      </c>
+      <c r="D20" s="156">
         <f>D18/D17</f>
         <v>0.74545454545454548</v>
       </c>
-      <c r="E20" s="45" t="s">
-        <v>72</v>
-      </c>
-      <c r="F20" s="129"/>
-      <c r="G20" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H20" s="44"/>
-      <c r="I20" s="72"/>
+      <c r="E20" s="156" t="s">
+        <v>69</v>
+      </c>
+      <c r="F20" s="135" t="s">
+        <v>317</v>
+      </c>
+      <c r="G20" s="136" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H20" s="139"/>
+      <c r="I20" s="157"/>
     </row>
     <row r="21" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B21" s="43" t="s">
-        <v>107</v>
-      </c>
-      <c r="C21" s="44" t="s">
-        <v>142</v>
-      </c>
-      <c r="D21" s="45">
+      <c r="B21" s="138" t="s">
+        <v>103</v>
+      </c>
+      <c r="C21" s="139" t="s">
+        <v>137</v>
+      </c>
+      <c r="D21" s="156">
         <f>D19/D17</f>
         <v>0.77662337662337666</v>
       </c>
-      <c r="E21" s="45" t="s">
+      <c r="E21" s="156" t="s">
+        <v>69</v>
+      </c>
+      <c r="F21" s="135" t="s">
+        <v>317</v>
+      </c>
+      <c r="G21" s="136" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H21" s="139"/>
+      <c r="I21" s="157"/>
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B22" s="140"/>
+      <c r="C22" s="141"/>
+      <c r="D22" s="142"/>
+      <c r="E22" s="142"/>
+      <c r="F22" s="143"/>
+      <c r="G22" s="144" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H22" s="141"/>
+      <c r="I22" s="158"/>
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B23" s="150" t="s">
+        <v>330</v>
+      </c>
+      <c r="C23" s="151"/>
+      <c r="D23" s="152"/>
+      <c r="E23" s="152"/>
+      <c r="F23" s="153"/>
+      <c r="G23" s="152"/>
+      <c r="H23" s="154"/>
+      <c r="I23" s="155"/>
+    </row>
+    <row r="24" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="B24" s="131" t="s">
+        <v>73</v>
+      </c>
+      <c r="C24" s="132" t="s">
+        <v>138</v>
+      </c>
+      <c r="D24" s="133">
+        <v>2</v>
+      </c>
+      <c r="E24" s="134" t="s">
+        <v>54</v>
+      </c>
+      <c r="F24" s="135"/>
+      <c r="G24" s="136" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H24" s="132" t="s">
+        <v>298</v>
+      </c>
+      <c r="I24" s="137">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9" ht="57" x14ac:dyDescent="0.3">
+      <c r="B25" s="131" t="s">
+        <v>74</v>
+      </c>
+      <c r="C25" s="132" t="s">
+        <v>84</v>
+      </c>
+      <c r="D25" s="38">
+        <v>5</v>
+      </c>
+      <c r="E25" s="134" t="s">
+        <v>70</v>
+      </c>
+      <c r="F25" s="135"/>
+      <c r="G25" s="136" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H25" s="132"/>
+      <c r="I25" s="137"/>
+    </row>
+    <row r="26" spans="2:9" ht="45.6" x14ac:dyDescent="0.3">
+      <c r="B26" s="131" t="s">
+        <v>75</v>
+      </c>
+      <c r="C26" s="132" t="s">
         <v>72</v>
       </c>
-      <c r="F21" s="129"/>
-      <c r="G21" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H21" s="44"/>
-      <c r="I21" s="72"/>
-    </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B22" s="40"/>
-      <c r="C22" s="41"/>
-      <c r="D22" s="42"/>
-      <c r="E22" s="42"/>
-      <c r="F22" s="126"/>
-      <c r="G22" s="120" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H22" s="41"/>
-      <c r="I22" s="73"/>
-    </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B23" s="6" t="s">
-        <v>215</v>
-      </c>
-      <c r="C23" s="33"/>
-      <c r="D23" s="34"/>
-      <c r="E23" s="34"/>
-      <c r="F23" s="128"/>
-      <c r="G23" s="34"/>
-      <c r="H23" s="84"/>
-      <c r="I23" s="70"/>
-    </row>
-    <row r="24" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
-      <c r="B24" s="32" t="s">
-        <v>76</v>
-      </c>
-      <c r="C24" s="35" t="s">
-        <v>143</v>
-      </c>
-      <c r="D24" s="36">
-        <v>2</v>
-      </c>
-      <c r="E24" s="31" t="s">
-        <v>54</v>
-      </c>
-      <c r="F24" s="125"/>
-      <c r="G24" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H24" s="35"/>
-      <c r="I24" s="71">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="2:9" ht="57" x14ac:dyDescent="0.3">
-      <c r="B25" s="32" t="s">
-        <v>77</v>
-      </c>
-      <c r="C25" s="35" t="s">
-        <v>87</v>
-      </c>
-      <c r="D25" s="49">
-        <v>5</v>
-      </c>
-      <c r="E25" s="31" t="s">
-        <v>73</v>
-      </c>
-      <c r="F25" s="125"/>
-      <c r="G25" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H25" s="35"/>
-      <c r="I25" s="71"/>
-    </row>
-    <row r="26" spans="2:9" ht="45.6" x14ac:dyDescent="0.3">
-      <c r="B26" s="32" t="s">
-        <v>78</v>
-      </c>
-      <c r="C26" s="35" t="s">
-        <v>75</v>
-      </c>
-      <c r="D26" s="31">
+      <c r="D26" s="134">
         <f>ROUND(ATAN(D25/100)*180/PI(),0)</f>
         <v>3</v>
       </c>
-      <c r="E26" s="31" t="s">
-        <v>74</v>
-      </c>
-      <c r="F26" s="125"/>
-      <c r="G26" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H26" s="35"/>
-      <c r="I26" s="71"/>
-    </row>
-    <row r="27" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
-      <c r="B27" s="43" t="s">
-        <v>80</v>
-      </c>
-      <c r="C27" s="44" t="s">
-        <v>145</v>
-      </c>
-      <c r="D27" s="50">
+      <c r="E26" s="134" t="s">
+        <v>71</v>
+      </c>
+      <c r="F26" s="135"/>
+      <c r="G26" s="136" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H26" s="132"/>
+      <c r="I26" s="137"/>
+    </row>
+    <row r="27" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="B27" s="138" t="s">
+        <v>77</v>
+      </c>
+      <c r="C27" s="139" t="s">
+        <v>328</v>
+      </c>
+      <c r="D27" s="159">
         <v>0.6</v>
       </c>
-      <c r="E27" s="45" t="s">
+      <c r="E27" s="156" t="s">
         <v>54</v>
       </c>
-      <c r="F27" s="129"/>
-      <c r="G27" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H27" s="44"/>
-      <c r="I27" s="72"/>
+      <c r="F27" s="160"/>
+      <c r="G27" s="136" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H27" s="139"/>
+      <c r="I27" s="157"/>
     </row>
     <row r="28" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="B28" s="32" t="s">
-        <v>79</v>
-      </c>
-      <c r="C28" s="35" t="s">
-        <v>144</v>
-      </c>
-      <c r="D28" s="36">
+      <c r="B28" s="131" t="s">
+        <v>76</v>
+      </c>
+      <c r="C28" s="132" t="s">
+        <v>139</v>
+      </c>
+      <c r="D28" s="133">
         <v>0.2</v>
       </c>
-      <c r="E28" s="31" t="s">
+      <c r="E28" s="134" t="s">
         <v>54</v>
       </c>
-      <c r="F28" s="125"/>
-      <c r="G28" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H28" s="35"/>
-      <c r="I28" s="71"/>
+      <c r="F28" s="135"/>
+      <c r="G28" s="136" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H28" s="132"/>
+      <c r="I28" s="137"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B29" s="32" t="s">
-        <v>146</v>
-      </c>
-      <c r="C29" s="35" t="s">
-        <v>148</v>
-      </c>
-      <c r="D29" s="36">
+      <c r="B29" s="131" t="s">
+        <v>140</v>
+      </c>
+      <c r="C29" s="132" t="s">
+        <v>142</v>
+      </c>
+      <c r="D29" s="133">
         <v>2</v>
       </c>
-      <c r="E29" s="31" t="s">
-        <v>72</v>
-      </c>
-      <c r="F29" s="125"/>
-      <c r="G29" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H29" s="35"/>
-      <c r="I29" s="71"/>
+      <c r="E29" s="134" t="s">
+        <v>69</v>
+      </c>
+      <c r="F29" s="135"/>
+      <c r="G29" s="136" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H29" s="132"/>
+      <c r="I29" s="137"/>
     </row>
     <row r="30" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B30" s="43" t="s">
-        <v>81</v>
-      </c>
-      <c r="C30" s="44" t="s">
-        <v>147</v>
-      </c>
-      <c r="D30" s="45">
+      <c r="B30" s="138" t="s">
+        <v>78</v>
+      </c>
+      <c r="C30" s="139" t="s">
+        <v>141</v>
+      </c>
+      <c r="D30" s="156">
         <f>(D27-D28)*(D11+D24+D24)*D29</f>
         <v>32.799999999999997</v>
       </c>
-      <c r="E30" s="31" t="s">
+      <c r="E30" s="134" t="s">
         <v>55</v>
       </c>
-      <c r="F30" s="129"/>
-      <c r="G30" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H30" s="44"/>
-      <c r="I30" s="72"/>
+      <c r="F30" s="160"/>
+      <c r="G30" s="136" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H30" s="139"/>
+      <c r="I30" s="157"/>
     </row>
     <row r="31" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
-      <c r="B31" s="32" t="s">
-        <v>149</v>
-      </c>
-      <c r="C31" s="35" t="s">
-        <v>151</v>
-      </c>
-      <c r="D31" s="31">
+      <c r="B31" s="131" t="s">
+        <v>143</v>
+      </c>
+      <c r="C31" s="132" t="s">
+        <v>145</v>
+      </c>
+      <c r="D31" s="134">
         <f>(D10*D11)-D30</f>
         <v>1262.2</v>
       </c>
-      <c r="E31" s="31" t="s">
+      <c r="E31" s="134" t="s">
         <v>55</v>
       </c>
-      <c r="F31" s="125"/>
-      <c r="G31" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H31" s="35"/>
-      <c r="I31" s="71"/>
+      <c r="F31" s="135"/>
+      <c r="G31" s="136" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H31" s="132"/>
+      <c r="I31" s="137"/>
     </row>
     <row r="32" spans="2:9" ht="45.6" x14ac:dyDescent="0.3">
-      <c r="B32" s="32" t="s">
-        <v>150</v>
-      </c>
-      <c r="C32" s="35" t="s">
-        <v>152</v>
-      </c>
-      <c r="D32" s="31">
+      <c r="B32" s="131" t="s">
+        <v>144</v>
+      </c>
+      <c r="C32" s="132" t="s">
+        <v>146</v>
+      </c>
+      <c r="D32" s="134">
         <f>((D10*D11)+D10*(D24+D24))-D30</f>
         <v>1402.2</v>
       </c>
-      <c r="E32" s="31" t="s">
+      <c r="E32" s="134" t="s">
         <v>55</v>
       </c>
-      <c r="F32" s="125"/>
-      <c r="G32" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H32" s="35"/>
-      <c r="I32" s="71"/>
+      <c r="F32" s="135"/>
+      <c r="G32" s="136" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H32" s="132"/>
+      <c r="I32" s="137"/>
     </row>
     <row r="33" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B33" s="32" t="s">
-        <v>82</v>
-      </c>
-      <c r="C33" s="35" t="s">
-        <v>132</v>
-      </c>
-      <c r="D33" s="36">
+      <c r="B33" s="131" t="s">
+        <v>79</v>
+      </c>
+      <c r="C33" s="132" t="s">
+        <v>127</v>
+      </c>
+      <c r="D33" s="133">
         <v>10</v>
       </c>
-      <c r="E33" s="31" t="s">
+      <c r="E33" s="134" t="s">
         <v>54</v>
       </c>
-      <c r="F33" s="125"/>
-      <c r="G33" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H33" s="35"/>
-      <c r="I33" s="71"/>
+      <c r="F33" s="135"/>
+      <c r="G33" s="136" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H33" s="132"/>
+      <c r="I33" s="137"/>
     </row>
     <row r="34" spans="2:9" ht="45.6" x14ac:dyDescent="0.3">
-      <c r="B34" s="32" t="s">
-        <v>83</v>
-      </c>
-      <c r="C34" s="35" t="s">
-        <v>153</v>
-      </c>
-      <c r="D34" s="31">
+      <c r="B34" s="131" t="s">
+        <v>80</v>
+      </c>
+      <c r="C34" s="132" t="s">
+        <v>147</v>
+      </c>
+      <c r="D34" s="134">
         <f>EVEN(D31/(D33*D33))</f>
         <v>14</v>
       </c>
-      <c r="E34" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="F34" s="125"/>
-      <c r="G34" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H34" s="35"/>
-      <c r="I34" s="71"/>
+      <c r="E34" s="134" t="s">
+        <v>119</v>
+      </c>
+      <c r="F34" s="135"/>
+      <c r="G34" s="136" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H34" s="132"/>
+      <c r="I34" s="137"/>
     </row>
     <row r="35" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B35" s="32" t="s">
-        <v>84</v>
-      </c>
-      <c r="C35" s="35" t="s">
+      <c r="B35" s="131" t="s">
+        <v>81</v>
+      </c>
+      <c r="C35" s="132" t="s">
         <v>64</v>
       </c>
-      <c r="D35" s="36">
+      <c r="D35" s="133">
         <v>1200</v>
       </c>
-      <c r="E35" s="31" t="s">
+      <c r="E35" s="134" t="s">
         <v>65</v>
       </c>
-      <c r="F35" s="125"/>
-      <c r="G35" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H35" s="35"/>
-      <c r="I35" s="71"/>
+      <c r="F35" s="135"/>
+      <c r="G35" s="136" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H35" s="132"/>
+      <c r="I35" s="137"/>
     </row>
     <row r="36" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B36" s="32" t="s">
-        <v>85</v>
-      </c>
-      <c r="C36" s="35" t="s">
+      <c r="B36" s="131" t="s">
+        <v>82</v>
+      </c>
+      <c r="C36" s="132" t="s">
         <v>63</v>
       </c>
-      <c r="D36" s="31">
+      <c r="D36" s="134">
         <f>D35*D35/(1000*1000)</f>
         <v>1.44</v>
       </c>
-      <c r="E36" s="31" t="s">
+      <c r="E36" s="134" t="s">
         <v>55</v>
       </c>
-      <c r="F36" s="125"/>
-      <c r="G36" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H36" s="35"/>
-      <c r="I36" s="71"/>
+      <c r="F36" s="135"/>
+      <c r="G36" s="136" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H36" s="132"/>
+      <c r="I36" s="137"/>
     </row>
     <row r="37" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="B37" s="32" t="s">
-        <v>86</v>
-      </c>
-      <c r="C37" s="35" t="s">
-        <v>154</v>
-      </c>
-      <c r="D37" s="31">
+      <c r="B37" s="131" t="s">
+        <v>83</v>
+      </c>
+      <c r="C37" s="132" t="s">
+        <v>148</v>
+      </c>
+      <c r="D37" s="134">
         <f>D34*D36</f>
         <v>20.16</v>
       </c>
-      <c r="E37" s="31" t="s">
+      <c r="E37" s="134" t="s">
         <v>55</v>
       </c>
-      <c r="F37" s="125"/>
-      <c r="G37" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H37" s="35"/>
-      <c r="I37" s="71"/>
+      <c r="F37" s="135"/>
+      <c r="G37" s="136" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H37" s="132"/>
+      <c r="I37" s="137"/>
     </row>
     <row r="38" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B38" s="40"/>
-      <c r="C38" s="41"/>
-      <c r="D38" s="42"/>
-      <c r="E38" s="42"/>
-      <c r="F38" s="126"/>
-      <c r="G38" s="120" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H38" s="41"/>
-      <c r="I38" s="73"/>
+      <c r="B38" s="140"/>
+      <c r="C38" s="141"/>
+      <c r="D38" s="142"/>
+      <c r="E38" s="142"/>
+      <c r="F38" s="143"/>
+      <c r="G38" s="144" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H38" s="141"/>
+      <c r="I38" s="158"/>
     </row>
     <row r="39" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B39" s="48" t="s">
-        <v>66</v>
-      </c>
-      <c r="C39" s="33"/>
-      <c r="D39" s="34"/>
-      <c r="E39" s="34"/>
-      <c r="F39" s="128"/>
-      <c r="G39" s="34"/>
-      <c r="H39" s="84"/>
-      <c r="I39" s="70"/>
+      <c r="B39" s="161" t="s">
+        <v>331</v>
+      </c>
+      <c r="C39" s="151"/>
+      <c r="D39" s="152"/>
+      <c r="E39" s="152"/>
+      <c r="F39" s="153"/>
+      <c r="G39" s="152"/>
+      <c r="H39" s="154"/>
+      <c r="I39" s="155"/>
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B40" s="32" t="s">
-        <v>88</v>
-      </c>
-      <c r="C40" s="35" t="s">
-        <v>92</v>
-      </c>
-      <c r="D40" s="36">
+      <c r="B40" s="131" t="s">
+        <v>85</v>
+      </c>
+      <c r="C40" s="132" t="s">
+        <v>89</v>
+      </c>
+      <c r="D40" s="133">
         <v>1</v>
       </c>
-      <c r="E40" s="31" t="s">
+      <c r="E40" s="134" t="s">
         <v>54</v>
       </c>
-      <c r="F40" s="125"/>
-      <c r="G40" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H40" s="35"/>
-      <c r="I40" s="71">
+      <c r="F40" s="135"/>
+      <c r="G40" s="136" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H40" s="132"/>
+      <c r="I40" s="137">
         <v>5</v>
       </c>
     </row>
     <row r="41" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B41" s="32" t="s">
-        <v>89</v>
-      </c>
-      <c r="C41" s="35" t="s">
-        <v>93</v>
-      </c>
-      <c r="D41" s="36">
+      <c r="B41" s="131" t="s">
+        <v>86</v>
+      </c>
+      <c r="C41" s="132" t="s">
+        <v>90</v>
+      </c>
+      <c r="D41" s="133">
         <v>15</v>
       </c>
-      <c r="E41" s="31" t="s">
+      <c r="E41" s="134" t="s">
         <v>54</v>
       </c>
-      <c r="F41" s="125"/>
-      <c r="G41" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H41" s="35"/>
-      <c r="I41" s="71"/>
+      <c r="F41" s="135"/>
+      <c r="G41" s="136" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H41" s="132"/>
+      <c r="I41" s="137"/>
     </row>
     <row r="42" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B42" s="32" t="s">
-        <v>90</v>
-      </c>
-      <c r="C42" s="35" t="s">
-        <v>94</v>
-      </c>
-      <c r="D42" s="31">
+      <c r="B42" s="131" t="s">
+        <v>87</v>
+      </c>
+      <c r="C42" s="132" t="s">
+        <v>91</v>
+      </c>
+      <c r="D42" s="134">
         <f>D11+(INT(D11/D41)*D10)</f>
         <v>107</v>
       </c>
-      <c r="E42" s="31" t="s">
+      <c r="E42" s="134" t="s">
         <v>54</v>
       </c>
-      <c r="F42" s="125"/>
-      <c r="G42" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H42" s="35"/>
-      <c r="I42" s="71"/>
+      <c r="F42" s="135"/>
+      <c r="G42" s="136" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H42" s="132"/>
+      <c r="I42" s="137"/>
     </row>
     <row r="43" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B43" s="32" t="s">
-        <v>91</v>
-      </c>
-      <c r="C43" s="35" t="s">
-        <v>95</v>
-      </c>
-      <c r="D43" s="31">
+      <c r="B43" s="131" t="s">
+        <v>88</v>
+      </c>
+      <c r="C43" s="132" t="s">
+        <v>92</v>
+      </c>
+      <c r="D43" s="134">
         <f>D42*D40</f>
         <v>107</v>
       </c>
-      <c r="E43" s="31" t="s">
+      <c r="E43" s="134" t="s">
         <v>55</v>
       </c>
-      <c r="F43" s="125"/>
-      <c r="G43" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H43" s="35"/>
-      <c r="I43" s="71"/>
+      <c r="F43" s="135"/>
+      <c r="G43" s="136" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H43" s="132"/>
+      <c r="I43" s="137"/>
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B44" s="40"/>
-      <c r="C44" s="41"/>
-      <c r="D44" s="42"/>
-      <c r="E44" s="42"/>
-      <c r="F44" s="126"/>
-      <c r="G44" s="120" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H44" s="41"/>
-      <c r="I44" s="73"/>
+      <c r="B44" s="140"/>
+      <c r="C44" s="141"/>
+      <c r="D44" s="142"/>
+      <c r="E44" s="142"/>
+      <c r="F44" s="143"/>
+      <c r="G44" s="144" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H44" s="141"/>
+      <c r="I44" s="158"/>
     </row>
     <row r="45" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B45" s="48" t="s">
-        <v>67</v>
-      </c>
-      <c r="C45" s="33"/>
-      <c r="D45" s="34"/>
-      <c r="E45" s="34"/>
-      <c r="F45" s="128"/>
-      <c r="G45" s="34"/>
-      <c r="H45" s="84"/>
-      <c r="I45" s="70"/>
-    </row>
-    <row r="46" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B46" s="32" t="s">
+      <c r="B45" s="150" t="s">
+        <v>332</v>
+      </c>
+      <c r="C45" s="151"/>
+      <c r="D45" s="152"/>
+      <c r="E45" s="152"/>
+      <c r="F45" s="153"/>
+      <c r="G45" s="152"/>
+      <c r="H45" s="154"/>
+      <c r="I45" s="155"/>
+    </row>
+    <row r="46" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="B46" s="131" t="s">
         <v>42</v>
       </c>
-      <c r="C46" s="35" t="s">
-        <v>155</v>
-      </c>
-      <c r="D46" s="36">
+      <c r="C46" s="132" t="s">
+        <v>333</v>
+      </c>
+      <c r="D46" s="133">
         <v>60</v>
       </c>
-      <c r="E46" s="31" t="s">
+      <c r="E46" s="134" t="s">
         <v>55</v>
       </c>
-      <c r="F46" s="125"/>
-      <c r="G46" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H46" s="35"/>
-      <c r="I46" s="71">
+      <c r="F46" s="135"/>
+      <c r="G46" s="136" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H46" s="132"/>
+      <c r="I46" s="137">
         <v>5</v>
       </c>
     </row>
     <row r="47" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
-      <c r="B47" s="32" t="s">
+      <c r="B47" s="131" t="s">
         <v>43</v>
       </c>
-      <c r="C47" s="35" t="s">
+      <c r="C47" s="132" t="s">
         <v>44</v>
       </c>
-      <c r="D47" s="36">
+      <c r="D47" s="133">
         <v>24</v>
       </c>
-      <c r="E47" s="31" t="s">
+      <c r="E47" s="134" t="s">
         <v>55</v>
       </c>
-      <c r="F47" s="125"/>
-      <c r="G47" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H47" s="35"/>
-      <c r="I47" s="71"/>
+      <c r="F47" s="135"/>
+      <c r="G47" s="136" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H47" s="132"/>
+      <c r="I47" s="137"/>
     </row>
     <row r="48" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B48" s="32" t="s">
-        <v>96</v>
-      </c>
-      <c r="C48" s="35" t="s">
-        <v>133</v>
-      </c>
-      <c r="D48" s="36">
+      <c r="B48" s="131" t="s">
+        <v>93</v>
+      </c>
+      <c r="C48" s="132" t="s">
+        <v>128</v>
+      </c>
+      <c r="D48" s="133">
         <v>3.9900000000000007</v>
       </c>
-      <c r="E48" s="31" t="s">
+      <c r="E48" s="134" t="s">
         <v>54</v>
       </c>
-      <c r="F48" s="125"/>
-      <c r="G48" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H48" s="35"/>
-      <c r="I48" s="71"/>
+      <c r="F48" s="135"/>
+      <c r="G48" s="136" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H48" s="132"/>
+      <c r="I48" s="137"/>
     </row>
     <row r="49" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B49" s="32" t="s">
-        <v>97</v>
-      </c>
-      <c r="C49" s="35" t="s">
-        <v>156</v>
-      </c>
-      <c r="D49" s="31">
+      <c r="B49" s="131" t="s">
+        <v>94</v>
+      </c>
+      <c r="C49" s="132" t="s">
+        <v>149</v>
+      </c>
+      <c r="D49" s="134">
         <f>D46-D54</f>
         <v>52.943999999999996</v>
       </c>
-      <c r="E49" s="31" t="s">
+      <c r="E49" s="134" t="s">
         <v>55</v>
       </c>
-      <c r="F49" s="125"/>
-      <c r="G49" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H49" s="35"/>
-      <c r="I49" s="71"/>
+      <c r="F49" s="135"/>
+      <c r="G49" s="136" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H49" s="132"/>
+      <c r="I49" s="137"/>
     </row>
     <row r="50" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B50" s="32" t="s">
+      <c r="B50" s="131" t="s">
         <v>58</v>
       </c>
-      <c r="C50" s="35" t="s">
+      <c r="C50" s="132" t="s">
         <v>57</v>
       </c>
-      <c r="D50" s="36">
+      <c r="D50" s="133">
         <v>28</v>
       </c>
-      <c r="E50" s="31" t="s">
+      <c r="E50" s="134" t="s">
         <v>56</v>
       </c>
-      <c r="F50" s="125"/>
-      <c r="G50" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H50" s="35"/>
-      <c r="I50" s="71"/>
+      <c r="F50" s="135"/>
+      <c r="G50" s="136" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H50" s="132"/>
+      <c r="I50" s="137"/>
     </row>
     <row r="51" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B51" s="32" t="s">
-        <v>100</v>
-      </c>
-      <c r="C51" s="35" t="s">
+      <c r="B51" s="131" t="s">
+        <v>97</v>
+      </c>
+      <c r="C51" s="132" t="s">
         <v>59</v>
       </c>
-      <c r="D51" s="36">
+      <c r="D51" s="133">
         <v>19</v>
       </c>
-      <c r="E51" s="31" t="s">
+      <c r="E51" s="134" t="s">
         <v>56</v>
       </c>
-      <c r="F51" s="125"/>
-      <c r="G51" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H51" s="35"/>
-      <c r="I51" s="71"/>
+      <c r="F51" s="135"/>
+      <c r="G51" s="136" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H51" s="132"/>
+      <c r="I51" s="137"/>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B52" s="32" t="s">
-        <v>98</v>
-      </c>
-      <c r="C52" s="35" t="s">
-        <v>99</v>
-      </c>
-      <c r="D52" s="31">
+      <c r="B52" s="131" t="s">
+        <v>95</v>
+      </c>
+      <c r="C52" s="132" t="s">
+        <v>96</v>
+      </c>
+      <c r="D52" s="134">
         <f>D48/(D51/100)</f>
         <v>21.000000000000004</v>
       </c>
-      <c r="E52" s="31" t="s">
+      <c r="E52" s="134" t="s">
         <v>50</v>
       </c>
-      <c r="F52" s="125"/>
-      <c r="G52" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H52" s="35"/>
-      <c r="I52" s="71"/>
+      <c r="F52" s="135"/>
+      <c r="G52" s="136" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H52" s="132"/>
+      <c r="I52" s="137"/>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B53" s="32" t="s">
+      <c r="B53" s="131" t="s">
+        <v>98</v>
+      </c>
+      <c r="C53" s="132" t="s">
+        <v>99</v>
+      </c>
+      <c r="D53" s="133">
+        <v>1.2</v>
+      </c>
+      <c r="E53" s="134" t="s">
+        <v>54</v>
+      </c>
+      <c r="F53" s="135"/>
+      <c r="G53" s="136" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H53" s="132"/>
+      <c r="I53" s="137"/>
+    </row>
+    <row r="54" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="B54" s="131" t="s">
+        <v>100</v>
+      </c>
+      <c r="C54" s="132" t="s">
         <v>101</v>
       </c>
-      <c r="C53" s="35" t="s">
-        <v>102</v>
-      </c>
-      <c r="D53" s="36">
-        <v>1.2</v>
-      </c>
-      <c r="E53" s="31" t="s">
-        <v>54</v>
-      </c>
-      <c r="F53" s="125"/>
-      <c r="G53" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H53" s="35"/>
-      <c r="I53" s="71"/>
-    </row>
-    <row r="54" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B54" s="32" t="s">
-        <v>103</v>
-      </c>
-      <c r="C54" s="35" t="s">
-        <v>104</v>
-      </c>
-      <c r="D54" s="46">
+      <c r="D54" s="162">
         <f>D53*D52*(D50/100)</f>
         <v>7.0560000000000018</v>
       </c>
-      <c r="E54" s="31" t="s">
+      <c r="E54" s="134" t="s">
         <v>55</v>
       </c>
-      <c r="F54" s="125"/>
-      <c r="G54" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H54" s="35"/>
-      <c r="I54" s="71"/>
+      <c r="F54" s="135"/>
+      <c r="G54" s="136" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H54" s="132"/>
+      <c r="I54" s="137"/>
     </row>
     <row r="55" spans="2:9" ht="68.400000000000006" x14ac:dyDescent="0.3">
-      <c r="B55" s="32" t="s">
-        <v>134</v>
-      </c>
-      <c r="C55" s="35" t="s">
-        <v>197</v>
-      </c>
-      <c r="D55" s="36">
+      <c r="B55" s="131" t="s">
+        <v>129</v>
+      </c>
+      <c r="C55" s="132" t="s">
+        <v>190</v>
+      </c>
+      <c r="D55" s="133">
         <v>6</v>
       </c>
-      <c r="E55" s="31" t="s">
+      <c r="E55" s="134" t="s">
         <v>54</v>
       </c>
-      <c r="F55" s="125"/>
-      <c r="G55" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H55" s="35"/>
-      <c r="I55" s="71"/>
+      <c r="F55" s="135"/>
+      <c r="G55" s="136" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H55" s="132"/>
+      <c r="I55" s="137"/>
     </row>
     <row r="56" spans="2:9" ht="68.400000000000006" x14ac:dyDescent="0.3">
-      <c r="B56" s="32" t="s">
-        <v>135</v>
-      </c>
-      <c r="C56" s="35" t="s">
-        <v>198</v>
-      </c>
-      <c r="D56" s="36">
+      <c r="B56" s="131" t="s">
+        <v>130</v>
+      </c>
+      <c r="C56" s="132" t="s">
+        <v>191</v>
+      </c>
+      <c r="D56" s="133">
         <v>4.5</v>
       </c>
-      <c r="E56" s="31" t="s">
+      <c r="E56" s="134" t="s">
         <v>54</v>
       </c>
-      <c r="F56" s="125"/>
-      <c r="G56" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H56" s="35"/>
-      <c r="I56" s="71"/>
+      <c r="F56" s="135"/>
+      <c r="G56" s="136" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H56" s="132"/>
+      <c r="I56" s="137"/>
     </row>
     <row r="57" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B57" s="32" t="s">
-        <v>137</v>
-      </c>
-      <c r="C57" s="35" t="s">
-        <v>136</v>
-      </c>
-      <c r="D57" s="36">
+      <c r="B57" s="131" t="s">
+        <v>132</v>
+      </c>
+      <c r="C57" s="132" t="s">
+        <v>131</v>
+      </c>
+      <c r="D57" s="133">
         <v>1.2</v>
       </c>
-      <c r="E57" s="31" t="s">
+      <c r="E57" s="134" t="s">
         <v>54</v>
       </c>
-      <c r="F57" s="125"/>
-      <c r="G57" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H57" s="35"/>
-      <c r="I57" s="71"/>
+      <c r="F57" s="135"/>
+      <c r="G57" s="136" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H57" s="132"/>
+      <c r="I57" s="137"/>
     </row>
     <row r="58" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B58" s="32" t="s">
-        <v>195</v>
-      </c>
-      <c r="C58" s="35" t="s">
-        <v>196</v>
-      </c>
-      <c r="D58" s="36">
+      <c r="B58" s="131" t="s">
+        <v>188</v>
+      </c>
+      <c r="C58" s="132" t="s">
+        <v>189</v>
+      </c>
+      <c r="D58" s="133">
         <v>2.2999999999999998</v>
       </c>
-      <c r="E58" s="31" t="s">
+      <c r="E58" s="134" t="s">
         <v>54</v>
       </c>
-      <c r="F58" s="125"/>
-      <c r="G58" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H58" s="35"/>
-      <c r="I58" s="71"/>
+      <c r="F58" s="135"/>
+      <c r="G58" s="136" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H58" s="132"/>
+      <c r="I58" s="137"/>
     </row>
     <row r="59" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B59" s="32" t="s">
-        <v>138</v>
-      </c>
-      <c r="C59" s="35" t="s">
-        <v>199</v>
-      </c>
-      <c r="D59" s="36">
+      <c r="B59" s="131" t="s">
+        <v>133</v>
+      </c>
+      <c r="C59" s="132" t="s">
+        <v>192</v>
+      </c>
+      <c r="D59" s="133">
         <v>3</v>
       </c>
-      <c r="E59" s="31" t="s">
+      <c r="E59" s="134" t="s">
         <v>54</v>
       </c>
-      <c r="F59" s="125"/>
-      <c r="G59" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H59" s="35"/>
-      <c r="I59" s="71"/>
+      <c r="F59" s="135"/>
+      <c r="G59" s="136" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H59" s="132"/>
+      <c r="I59" s="137"/>
     </row>
     <row r="60" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B60" s="32" t="s">
-        <v>194</v>
-      </c>
-      <c r="C60" s="35" t="s">
-        <v>200</v>
-      </c>
-      <c r="D60" s="36">
+      <c r="B60" s="131" t="s">
+        <v>187</v>
+      </c>
+      <c r="C60" s="132" t="s">
+        <v>193</v>
+      </c>
+      <c r="D60" s="133">
         <v>2</v>
       </c>
-      <c r="E60" s="31" t="s">
+      <c r="E60" s="134" t="s">
         <v>54</v>
       </c>
-      <c r="F60" s="125"/>
-      <c r="G60" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H60" s="35"/>
-      <c r="I60" s="71"/>
+      <c r="F60" s="135"/>
+      <c r="G60" s="136" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H60" s="132"/>
+      <c r="I60" s="137"/>
     </row>
     <row r="61" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B61" s="40"/>
-      <c r="C61" s="41"/>
-      <c r="D61" s="42"/>
-      <c r="E61" s="42"/>
-      <c r="F61" s="126"/>
-      <c r="G61" s="120" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H61" s="41"/>
-      <c r="I61" s="73"/>
+      <c r="B61" s="140"/>
+      <c r="C61" s="141"/>
+      <c r="D61" s="142"/>
+      <c r="E61" s="142"/>
+      <c r="F61" s="143"/>
+      <c r="G61" s="144" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H61" s="141"/>
+      <c r="I61" s="158"/>
     </row>
     <row r="62" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B62" s="51" t="s">
-        <v>68</v>
-      </c>
-      <c r="C62" s="52"/>
-      <c r="D62" s="53"/>
-      <c r="E62" s="53"/>
-      <c r="F62" s="130"/>
-      <c r="G62" s="53"/>
-      <c r="H62" s="85"/>
-      <c r="I62" s="74"/>
+      <c r="B62" s="163" t="s">
+        <v>334</v>
+      </c>
+      <c r="C62" s="164"/>
+      <c r="D62" s="165"/>
+      <c r="E62" s="165"/>
+      <c r="F62" s="166"/>
+      <c r="G62" s="165"/>
+      <c r="H62" s="167"/>
+      <c r="I62" s="168"/>
     </row>
     <row r="63" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B63" s="32" t="s">
-        <v>178</v>
-      </c>
-      <c r="C63" s="35" t="s">
-        <v>111</v>
-      </c>
-      <c r="D63" s="36">
+      <c r="B63" s="131" t="s">
+        <v>171</v>
+      </c>
+      <c r="C63" s="132" t="s">
+        <v>107</v>
+      </c>
+      <c r="D63" s="133">
         <v>40</v>
       </c>
-      <c r="E63" s="31" t="s">
+      <c r="E63" s="134" t="s">
         <v>56</v>
       </c>
-      <c r="F63" s="125"/>
-      <c r="G63" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H63" s="35"/>
-      <c r="I63" s="71">
+      <c r="F63" s="135"/>
+      <c r="G63" s="136" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H63" s="132"/>
+      <c r="I63" s="137">
         <v>5</v>
       </c>
     </row>
     <row r="64" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B64" s="32" t="s">
-        <v>177</v>
-      </c>
-      <c r="C64" s="35" t="s">
-        <v>179</v>
-      </c>
-      <c r="D64" s="46">
+      <c r="B64" s="131" t="s">
+        <v>170</v>
+      </c>
+      <c r="C64" s="132" t="s">
+        <v>172</v>
+      </c>
+      <c r="D64" s="162">
         <f>D18</f>
         <v>1435</v>
       </c>
-      <c r="E64" s="31" t="s">
+      <c r="E64" s="134" t="s">
         <v>55</v>
       </c>
-      <c r="F64" s="125"/>
-      <c r="G64" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H64" s="35"/>
-      <c r="I64" s="71"/>
+      <c r="F64" s="135"/>
+      <c r="G64" s="136" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H64" s="132"/>
+      <c r="I64" s="137"/>
     </row>
     <row r="65" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B65" s="32" t="s">
+      <c r="B65" s="131" t="s">
+        <v>106</v>
+      </c>
+      <c r="C65" s="132" t="s">
+        <v>108</v>
+      </c>
+      <c r="D65" s="133">
+        <v>20</v>
+      </c>
+      <c r="E65" s="134" t="s">
+        <v>56</v>
+      </c>
+      <c r="F65" s="135"/>
+      <c r="G65" s="136" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H65" s="132"/>
+      <c r="I65" s="137"/>
+    </row>
+    <row r="66" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="B66" s="131" t="s">
+        <v>117</v>
+      </c>
+      <c r="C66" s="132" t="s">
         <v>110</v>
       </c>
-      <c r="C65" s="35" t="s">
-        <v>112</v>
-      </c>
-      <c r="D65" s="36">
-        <v>20</v>
-      </c>
-      <c r="E65" s="31" t="s">
-        <v>56</v>
-      </c>
-      <c r="F65" s="125"/>
-      <c r="G65" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H65" s="35"/>
-      <c r="I65" s="71"/>
-    </row>
-    <row r="66" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="B66" s="32" t="s">
-        <v>121</v>
-      </c>
-      <c r="C66" s="35" t="s">
-        <v>114</v>
-      </c>
-      <c r="D66" s="36">
+      <c r="D66" s="133">
         <v>6</v>
       </c>
-      <c r="E66" s="31" t="s">
+      <c r="E66" s="134" t="s">
         <v>54</v>
       </c>
-      <c r="F66" s="125"/>
-      <c r="G66" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H66" s="35"/>
-      <c r="I66" s="71"/>
+      <c r="F66" s="135"/>
+      <c r="G66" s="136" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H66" s="132"/>
+      <c r="I66" s="137"/>
     </row>
     <row r="67" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="B67" s="32" t="s">
-        <v>122</v>
-      </c>
-      <c r="C67" s="35" t="s">
-        <v>157</v>
-      </c>
-      <c r="D67" s="46">
+      <c r="B67" s="131" t="s">
+        <v>118</v>
+      </c>
+      <c r="C67" s="132" t="s">
+        <v>150</v>
+      </c>
+      <c r="D67" s="162">
         <f>ROUND(D10/D66,0)</f>
         <v>6</v>
       </c>
-      <c r="E67" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="F67" s="125"/>
-      <c r="G67" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H67" s="35"/>
-      <c r="I67" s="71"/>
+      <c r="E67" s="134" t="s">
+        <v>119</v>
+      </c>
+      <c r="F67" s="135"/>
+      <c r="G67" s="136" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H67" s="132"/>
+      <c r="I67" s="137"/>
     </row>
     <row r="68" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="B68" s="32" t="s">
-        <v>125</v>
-      </c>
-      <c r="C68" s="35" t="s">
-        <v>158</v>
-      </c>
-      <c r="D68" s="46">
+      <c r="B68" s="131" t="s">
+        <v>120</v>
+      </c>
+      <c r="C68" s="132" t="s">
+        <v>151</v>
+      </c>
+      <c r="D68" s="162">
         <f>ROUND(D11/D66,0)</f>
         <v>6</v>
       </c>
-      <c r="E68" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="F68" s="125"/>
-      <c r="G68" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H68" s="35"/>
-      <c r="I68" s="71"/>
+      <c r="E68" s="134" t="s">
+        <v>119</v>
+      </c>
+      <c r="F68" s="135"/>
+      <c r="G68" s="136" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H68" s="132"/>
+      <c r="I68" s="137"/>
     </row>
     <row r="69" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B69" s="32" t="s">
-        <v>126</v>
-      </c>
-      <c r="C69" s="35" t="s">
-        <v>127</v>
-      </c>
-      <c r="D69" s="46">
+      <c r="B69" s="131" t="s">
+        <v>121</v>
+      </c>
+      <c r="C69" s="132" t="s">
+        <v>122</v>
+      </c>
+      <c r="D69" s="162">
         <f>D68*D67</f>
         <v>36</v>
       </c>
-      <c r="E69" s="31" t="s">
+      <c r="E69" s="134" t="s">
+        <v>119</v>
+      </c>
+      <c r="F69" s="135"/>
+      <c r="G69" s="136" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H69" s="132"/>
+      <c r="I69" s="137"/>
+    </row>
+    <row r="70" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="B70" s="131" t="s">
+        <v>109</v>
+      </c>
+      <c r="C70" s="132" t="s">
+        <v>152</v>
+      </c>
+      <c r="D70" s="133">
+        <v>0.3</v>
+      </c>
+      <c r="E70" s="134" t="s">
+        <v>54</v>
+      </c>
+      <c r="F70" s="135"/>
+      <c r="G70" s="136" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H70" s="132"/>
+      <c r="I70" s="137"/>
+    </row>
+    <row r="71" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="B71" s="131" t="s">
+        <v>111</v>
+      </c>
+      <c r="C71" s="132" t="s">
+        <v>153</v>
+      </c>
+      <c r="D71" s="133">
+        <v>0.4</v>
+      </c>
+      <c r="E71" s="134" t="s">
+        <v>54</v>
+      </c>
+      <c r="F71" s="135"/>
+      <c r="G71" s="136" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H71" s="132"/>
+      <c r="I71" s="137"/>
+    </row>
+    <row r="72" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="B72" s="131" t="s">
+        <v>113</v>
+      </c>
+      <c r="C72" s="132" t="s">
+        <v>115</v>
+      </c>
+      <c r="D72" s="133">
+        <v>0.3</v>
+      </c>
+      <c r="E72" s="134" t="s">
+        <v>54</v>
+      </c>
+      <c r="F72" s="135"/>
+      <c r="G72" s="136" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H72" s="132"/>
+      <c r="I72" s="137"/>
+    </row>
+    <row r="73" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="B73" s="131" t="s">
+        <v>114</v>
+      </c>
+      <c r="C73" s="132" t="s">
+        <v>116</v>
+      </c>
+      <c r="D73" s="133">
+        <v>0.4</v>
+      </c>
+      <c r="E73" s="134" t="s">
+        <v>54</v>
+      </c>
+      <c r="F73" s="135"/>
+      <c r="G73" s="136" t="str">
+        <f t="shared" ref="G73:G76" si="1">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F73,"/Readme.md"),"Ver")</f>
+        <v>Ver</v>
+      </c>
+      <c r="H73" s="132"/>
+      <c r="I73" s="137"/>
+    </row>
+    <row r="74" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="B74" s="131" t="s">
         <v>123</v>
       </c>
-      <c r="F69" s="125"/>
-      <c r="G69" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H69" s="35"/>
-      <c r="I69" s="71"/>
-    </row>
-    <row r="70" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
-      <c r="B70" s="32" t="s">
-        <v>113</v>
-      </c>
-      <c r="C70" s="35" t="s">
-        <v>159</v>
-      </c>
-      <c r="D70" s="36">
-        <v>0.3</v>
-      </c>
-      <c r="E70" s="31" t="s">
-        <v>54</v>
-      </c>
-      <c r="F70" s="125"/>
-      <c r="G70" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H70" s="35"/>
-      <c r="I70" s="71"/>
-    </row>
-    <row r="71" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
-      <c r="B71" s="32" t="s">
-        <v>115</v>
-      </c>
-      <c r="C71" s="35" t="s">
-        <v>160</v>
-      </c>
-      <c r="D71" s="36">
-        <v>0.4</v>
-      </c>
-      <c r="E71" s="31" t="s">
-        <v>54</v>
-      </c>
-      <c r="F71" s="125"/>
-      <c r="G71" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H71" s="35"/>
-      <c r="I71" s="71"/>
-    </row>
-    <row r="72" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
-      <c r="B72" s="32" t="s">
-        <v>117</v>
-      </c>
-      <c r="C72" s="35" t="s">
-        <v>119</v>
-      </c>
-      <c r="D72" s="36">
-        <v>0.3</v>
-      </c>
-      <c r="E72" s="31" t="s">
-        <v>54</v>
-      </c>
-      <c r="F72" s="125"/>
-      <c r="G72" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H72" s="35"/>
-      <c r="I72" s="71"/>
-    </row>
-    <row r="73" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
-      <c r="B73" s="32" t="s">
-        <v>118</v>
-      </c>
-      <c r="C73" s="35" t="s">
-        <v>120</v>
-      </c>
-      <c r="D73" s="36">
-        <v>0.4</v>
-      </c>
-      <c r="E73" s="31" t="s">
-        <v>54</v>
-      </c>
-      <c r="F73" s="125"/>
-      <c r="G73" s="119" t="str">
-        <f t="shared" ref="G73:G76" si="1">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F73,"/Readme.md"),"Ver")</f>
-        <v>Ver</v>
-      </c>
-      <c r="H73" s="35"/>
-      <c r="I73" s="71"/>
-    </row>
-    <row r="74" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
-      <c r="B74" s="32" t="s">
-        <v>128</v>
-      </c>
-      <c r="C74" s="35" t="s">
-        <v>130</v>
-      </c>
-      <c r="D74" s="46">
+      <c r="C74" s="132" t="s">
+        <v>125</v>
+      </c>
+      <c r="D74" s="162">
         <f>(D10-D70)/D67</f>
         <v>5.7833333333333341</v>
       </c>
-      <c r="E74" s="31" t="s">
+      <c r="E74" s="134" t="s">
         <v>54</v>
       </c>
-      <c r="F74" s="125"/>
-      <c r="G74" s="119" t="str">
+      <c r="F74" s="135"/>
+      <c r="G74" s="136" t="str">
         <f t="shared" si="1"/>
         <v>Ver</v>
       </c>
-      <c r="H74" s="35"/>
-      <c r="I74" s="71"/>
+      <c r="H74" s="132"/>
+      <c r="I74" s="137"/>
     </row>
     <row r="75" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
-      <c r="B75" s="32" t="s">
-        <v>129</v>
-      </c>
-      <c r="C75" s="35" t="s">
-        <v>131</v>
-      </c>
-      <c r="D75" s="46">
+      <c r="B75" s="131" t="s">
+        <v>124</v>
+      </c>
+      <c r="C75" s="132" t="s">
+        <v>126</v>
+      </c>
+      <c r="D75" s="162">
         <f>(D11-D71)/D68</f>
         <v>6.1000000000000005</v>
       </c>
-      <c r="E75" s="31" t="s">
+      <c r="E75" s="134" t="s">
         <v>54</v>
       </c>
-      <c r="F75" s="125"/>
-      <c r="G75" s="119" t="str">
+      <c r="F75" s="135"/>
+      <c r="G75" s="136" t="str">
         <f t="shared" si="1"/>
         <v>Ver</v>
       </c>
-      <c r="H75" s="35"/>
-      <c r="I75" s="71"/>
+      <c r="H75" s="132"/>
+      <c r="I75" s="137"/>
     </row>
     <row r="76" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B76" s="54"/>
-      <c r="C76" s="55"/>
-      <c r="D76" s="56"/>
-      <c r="E76" s="56"/>
-      <c r="F76" s="131"/>
-      <c r="G76" s="120" t="str">
+      <c r="B76" s="169"/>
+      <c r="C76" s="170"/>
+      <c r="D76" s="171"/>
+      <c r="E76" s="171"/>
+      <c r="F76" s="172"/>
+      <c r="G76" s="144" t="str">
         <f t="shared" si="1"/>
         <v>Ver</v>
       </c>
-      <c r="H76" s="55"/>
-      <c r="I76" s="9"/>
+      <c r="H76" s="170"/>
+      <c r="I76" s="120"/>
     </row>
     <row r="77" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B77" s="57" t="s">
-        <v>116</v>
+      <c r="B77" s="173" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="79" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B79" s="2" t="s">
-        <v>124</v>
+      <c r="B79" s="51" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="80" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B80" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="C80" s="14" t="s">
-        <v>162</v>
+      <c r="B80" s="150" t="s">
+        <v>154</v>
+      </c>
+      <c r="C80" s="174" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="81" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B81" s="58" t="s">
-        <v>163</v>
-      </c>
-      <c r="C81" s="13">
+      <c r="B81" s="175" t="s">
+        <v>156</v>
+      </c>
+      <c r="C81" s="176">
         <f>D17</f>
         <v>1925</v>
       </c>
     </row>
     <row r="82" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B82" s="58" t="s">
-        <v>166</v>
-      </c>
-      <c r="C82" s="13">
+      <c r="B82" s="175" t="s">
+        <v>159</v>
+      </c>
+      <c r="C82" s="176">
         <f>D18</f>
         <v>1435</v>
       </c>
     </row>
     <row r="83" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B83" s="58" t="s">
-        <v>165</v>
-      </c>
-      <c r="C83" s="13">
+      <c r="B83" s="175" t="s">
+        <v>158</v>
+      </c>
+      <c r="C83" s="176">
         <f>D46</f>
         <v>60</v>
       </c>
     </row>
     <row r="84" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B84" s="58" t="s">
+      <c r="B84" s="175" t="s">
         <v>46</v>
       </c>
-      <c r="C84" s="13">
+      <c r="C84" s="176">
         <f>D54</f>
         <v>7.0560000000000018</v>
       </c>
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B85" s="58" t="s">
+      <c r="B85" s="175" t="s">
         <v>45</v>
       </c>
-      <c r="C85" s="13">
+      <c r="C85" s="176">
         <f>D49</f>
         <v>52.943999999999996</v>
       </c>
     </row>
     <row r="86" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B86" s="59" t="s">
-        <v>164</v>
-      </c>
-      <c r="C86" s="60">
+      <c r="B86" s="177" t="s">
+        <v>157</v>
+      </c>
+      <c r="C86" s="178">
         <f>D19</f>
         <v>1495</v>
       </c>
     </row>
     <row r="87" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B87" s="61" t="s">
-        <v>71</v>
-      </c>
-      <c r="C87" s="62">
+      <c r="B87" s="179" t="s">
+        <v>68</v>
+      </c>
+      <c r="C87" s="180">
         <f>D20</f>
         <v>0.74545454545454548</v>
       </c>
     </row>
     <row r="88" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B88" s="54" t="s">
-        <v>107</v>
-      </c>
-      <c r="C88" s="5">
+      <c r="B88" s="169" t="s">
+        <v>103</v>
+      </c>
+      <c r="C88" s="181">
         <f>D21</f>
         <v>0.77662337662337666</v>
       </c>
     </row>
     <row r="90" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B90" s="2" t="s">
-        <v>266</v>
+      <c r="B90" s="51" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="91" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B91" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="C91" s="33" t="s">
+      <c r="B91" s="150" t="s">
+        <v>154</v>
+      </c>
+      <c r="C91" s="151" t="s">
         <v>38</v>
       </c>
-      <c r="D91" s="8" t="s">
+      <c r="D91" s="116" t="s">
         <v>49</v>
       </c>
-      <c r="E91" s="8" t="s">
+      <c r="E91" s="116" t="s">
         <v>50</v>
       </c>
-      <c r="F91" s="121" t="s">
+      <c r="F91" s="128" t="s">
         <v>39</v>
       </c>
-      <c r="G91" s="122"/>
-      <c r="H91" s="33" t="s">
+      <c r="G91" s="129"/>
+      <c r="H91" s="151" t="s">
         <v>26</v>
       </c>
-      <c r="I91" s="70" t="s">
+      <c r="I91" s="155" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="92" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B92" s="32" t="s">
-        <v>181</v>
-      </c>
-      <c r="C92" s="29" t="s">
-        <v>180</v>
-      </c>
-      <c r="D92" s="64">
+      <c r="B92" s="131" t="s">
+        <v>174</v>
+      </c>
+      <c r="C92" s="182" t="s">
+        <v>173</v>
+      </c>
+      <c r="D92" s="183">
         <f>D64</f>
         <v>1435</v>
       </c>
-      <c r="E92" s="64" t="s">
+      <c r="E92" s="183" t="s">
         <v>55</v>
       </c>
-      <c r="F92" s="125"/>
-      <c r="G92" s="119" t="str">
+      <c r="F92" s="135"/>
+      <c r="G92" s="136" t="str">
         <f t="shared" ref="G92:G102" si="2">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F92,"/Readme.md"),"Ver")</f>
         <v>Ver</v>
       </c>
-      <c r="H92" s="35"/>
-      <c r="I92" s="71"/>
+      <c r="H92" s="132"/>
+      <c r="I92" s="137"/>
     </row>
     <row r="93" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="B93" s="32" t="s">
-        <v>182</v>
-      </c>
-      <c r="C93" s="29" t="s">
-        <v>183</v>
-      </c>
-      <c r="D93" s="64">
+      <c r="B93" s="131" t="s">
+        <v>175</v>
+      </c>
+      <c r="C93" s="182" t="s">
+        <v>176</v>
+      </c>
+      <c r="D93" s="183">
         <f>D92*D63</f>
         <v>57400</v>
       </c>
-      <c r="E93" s="64" t="s">
-        <v>184</v>
-      </c>
-      <c r="F93" s="125"/>
-      <c r="G93" s="119" t="str">
+      <c r="E93" s="183" t="s">
+        <v>177</v>
+      </c>
+      <c r="F93" s="135"/>
+      <c r="G93" s="136" t="str">
         <f t="shared" si="2"/>
         <v>Ver</v>
       </c>
-      <c r="H93" s="35"/>
-      <c r="I93" s="71"/>
+      <c r="H93" s="132"/>
+      <c r="I93" s="137"/>
     </row>
     <row r="94" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B94" s="32" t="s">
-        <v>193</v>
-      </c>
-      <c r="C94" s="29" t="s">
-        <v>192</v>
-      </c>
-      <c r="D94" s="64">
+      <c r="B94" s="131" t="s">
+        <v>186</v>
+      </c>
+      <c r="C94" s="182" t="s">
+        <v>185</v>
+      </c>
+      <c r="D94" s="183">
         <f>D49</f>
         <v>52.943999999999996</v>
       </c>
-      <c r="E94" s="64" t="s">
+      <c r="E94" s="183" t="s">
         <v>55</v>
       </c>
-      <c r="F94" s="132"/>
-      <c r="G94" s="119" t="str">
+      <c r="F94" s="184"/>
+      <c r="G94" s="136" t="str">
         <f t="shared" si="2"/>
         <v>Ver</v>
       </c>
-      <c r="H94" s="86"/>
-      <c r="I94" s="11"/>
+      <c r="H94" s="185"/>
+      <c r="I94" s="118"/>
     </row>
     <row r="95" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B95" s="32" t="s">
-        <v>186</v>
-      </c>
-      <c r="C95" s="29" t="s">
-        <v>187</v>
-      </c>
-      <c r="D95" s="64">
+      <c r="B95" s="131" t="s">
+        <v>179</v>
+      </c>
+      <c r="C95" s="182" t="s">
+        <v>180</v>
+      </c>
+      <c r="D95" s="183">
         <f>D69</f>
         <v>36</v>
       </c>
-      <c r="E95" s="64" t="s">
-        <v>123</v>
-      </c>
-      <c r="F95" s="132"/>
-      <c r="G95" s="119" t="str">
+      <c r="E95" s="183" t="s">
+        <v>119</v>
+      </c>
+      <c r="F95" s="184"/>
+      <c r="G95" s="136" t="str">
         <f t="shared" si="2"/>
         <v>Ver</v>
       </c>
-      <c r="H95" s="86"/>
-      <c r="I95" s="11"/>
+      <c r="H95" s="185"/>
+      <c r="I95" s="118"/>
     </row>
     <row r="96" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="B96" s="32" t="s">
-        <v>188</v>
-      </c>
-      <c r="C96" s="29" t="s">
-        <v>189</v>
-      </c>
-      <c r="D96" s="64">
+      <c r="B96" s="131" t="s">
+        <v>181</v>
+      </c>
+      <c r="C96" s="182" t="s">
+        <v>182</v>
+      </c>
+      <c r="D96" s="183">
         <f>D95*D12</f>
         <v>432</v>
       </c>
-      <c r="E96" s="64" t="s">
+      <c r="E96" s="183" t="s">
         <v>54</v>
       </c>
-      <c r="F96" s="132"/>
-      <c r="G96" s="119" t="str">
+      <c r="F96" s="184"/>
+      <c r="G96" s="136" t="str">
         <f t="shared" si="2"/>
         <v>Ver</v>
       </c>
-      <c r="H96" s="86"/>
-      <c r="I96" s="11"/>
+      <c r="H96" s="185"/>
+      <c r="I96" s="118"/>
     </row>
     <row r="97" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="B97" s="32" t="s">
-        <v>190</v>
-      </c>
-      <c r="C97" s="29" t="s">
-        <v>191</v>
-      </c>
-      <c r="D97" s="64">
+      <c r="B97" s="131" t="s">
+        <v>183</v>
+      </c>
+      <c r="C97" s="182" t="s">
+        <v>184</v>
+      </c>
+      <c r="D97" s="183">
         <f>((D67*D9)+(D68*D8))*INT(D12/D48)</f>
         <v>324</v>
       </c>
-      <c r="E97" s="64" t="s">
+      <c r="E97" s="183" t="s">
         <v>54</v>
       </c>
-      <c r="F97" s="132"/>
-      <c r="G97" s="119" t="str">
+      <c r="F97" s="184"/>
+      <c r="G97" s="136" t="str">
         <f t="shared" si="2"/>
         <v>Ver</v>
       </c>
-      <c r="H97" s="86"/>
-      <c r="I97" s="11"/>
+      <c r="H97" s="185"/>
+      <c r="I97" s="118"/>
     </row>
     <row r="98" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="B98" s="32" t="s">
-        <v>201</v>
-      </c>
-      <c r="C98" s="29" t="s">
-        <v>204</v>
-      </c>
-      <c r="D98" s="68" t="s">
-        <v>203</v>
-      </c>
-      <c r="E98" s="64" t="s">
+      <c r="B98" s="131" t="s">
+        <v>194</v>
+      </c>
+      <c r="C98" s="182" t="s">
+        <v>197</v>
+      </c>
+      <c r="D98" s="186" t="s">
+        <v>196</v>
+      </c>
+      <c r="E98" s="183" t="s">
         <v>55</v>
       </c>
-      <c r="F98" s="132"/>
-      <c r="G98" s="119" t="str">
+      <c r="F98" s="184"/>
+      <c r="G98" s="136" t="str">
         <f t="shared" si="2"/>
         <v>Ver</v>
       </c>
-      <c r="H98" s="86"/>
-      <c r="I98" s="11">
+      <c r="H98" s="185"/>
+      <c r="I98" s="118">
         <v>5</v>
       </c>
     </row>
     <row r="99" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B99" s="32" t="s">
-        <v>202</v>
-      </c>
-      <c r="C99" s="29" t="s">
-        <v>205</v>
-      </c>
-      <c r="D99" s="68">
+      <c r="B99" s="131" t="s">
+        <v>195</v>
+      </c>
+      <c r="C99" s="182" t="s">
+        <v>198</v>
+      </c>
+      <c r="D99" s="186">
         <v>2</v>
       </c>
-      <c r="E99" s="64" t="s">
-        <v>123</v>
-      </c>
-      <c r="F99" s="132"/>
-      <c r="G99" s="119" t="str">
+      <c r="E99" s="183" t="s">
+        <v>119</v>
+      </c>
+      <c r="F99" s="184"/>
+      <c r="G99" s="136" t="str">
         <f t="shared" si="2"/>
         <v>Ver</v>
       </c>
-      <c r="H99" s="86"/>
-      <c r="I99" s="11"/>
+      <c r="H99" s="185"/>
+      <c r="I99" s="118"/>
     </row>
     <row r="100" spans="2:9" ht="50.4" x14ac:dyDescent="0.3">
-      <c r="B100" s="32" t="s">
+      <c r="B100" s="131" t="s">
         <v>47</v>
       </c>
-      <c r="C100" s="29" t="s">
-        <v>206</v>
-      </c>
-      <c r="D100" s="68" t="s">
-        <v>203</v>
-      </c>
-      <c r="E100" s="64" t="s">
-        <v>123</v>
-      </c>
-      <c r="F100" s="132"/>
-      <c r="G100" s="119" t="str">
+      <c r="C100" s="182" t="s">
+        <v>199</v>
+      </c>
+      <c r="D100" s="186" t="s">
+        <v>196</v>
+      </c>
+      <c r="E100" s="183" t="s">
+        <v>119</v>
+      </c>
+      <c r="F100" s="184"/>
+      <c r="G100" s="136" t="str">
         <f t="shared" si="2"/>
         <v>Ver</v>
       </c>
-      <c r="H100" s="86"/>
-      <c r="I100" s="11"/>
+      <c r="H100" s="185"/>
+      <c r="I100" s="118"/>
     </row>
     <row r="101" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="B101" s="32" t="s">
+      <c r="B101" s="131" t="s">
         <v>48</v>
       </c>
-      <c r="C101" s="29" t="s">
-        <v>207</v>
-      </c>
-      <c r="D101" s="68" t="s">
-        <v>203</v>
-      </c>
-      <c r="E101" s="64" t="s">
-        <v>123</v>
-      </c>
-      <c r="F101" s="132"/>
-      <c r="G101" s="119" t="str">
+      <c r="C101" s="182" t="s">
+        <v>200</v>
+      </c>
+      <c r="D101" s="186" t="s">
+        <v>196</v>
+      </c>
+      <c r="E101" s="183" t="s">
+        <v>119</v>
+      </c>
+      <c r="F101" s="184"/>
+      <c r="G101" s="136" t="str">
         <f t="shared" si="2"/>
         <v>Ver</v>
       </c>
-      <c r="H101" s="86"/>
-      <c r="I101" s="11"/>
+      <c r="H101" s="185"/>
+      <c r="I101" s="118"/>
     </row>
     <row r="102" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B102" s="40"/>
-      <c r="C102" s="30"/>
-      <c r="D102" s="56"/>
-      <c r="E102" s="56"/>
-      <c r="F102" s="131"/>
-      <c r="G102" s="120" t="str">
+      <c r="B102" s="140"/>
+      <c r="C102" s="187"/>
+      <c r="D102" s="171"/>
+      <c r="E102" s="171"/>
+      <c r="F102" s="172"/>
+      <c r="G102" s="144" t="str">
         <f t="shared" si="2"/>
         <v>Ver</v>
       </c>
-      <c r="H102" s="55"/>
-      <c r="I102" s="9"/>
+      <c r="H102" s="170"/>
+      <c r="I102" s="120"/>
     </row>
     <row r="103" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B103" s="63"/>
-      <c r="C103" s="63"/>
-      <c r="H103" s="76" t="s">
-        <v>290</v>
-      </c>
-      <c r="I103" s="47">
+      <c r="B103" s="188"/>
+      <c r="C103" s="188"/>
+      <c r="H103" s="145" t="s">
+        <v>277</v>
+      </c>
+      <c r="I103" s="124">
         <f>AVERAGE(I7:I102)</f>
         <v>5</v>
       </c>
     </row>
     <row r="104" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B104" s="63"/>
-      <c r="C104" s="63"/>
+      <c r="B104" s="188"/>
+      <c r="C104" s="188"/>
     </row>
     <row r="105" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B105" s="63"/>
-      <c r="C105" s="63"/>
+      <c r="B105" s="188"/>
+      <c r="C105" s="188"/>
     </row>
     <row r="106" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B106" s="63"/>
-      <c r="C106" s="63"/>
+      <c r="B106" s="188"/>
+      <c r="C106" s="188"/>
     </row>
     <row r="107" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B107" s="63"/>
-      <c r="C107" s="63"/>
+      <c r="B107" s="188"/>
+      <c r="C107" s="188"/>
     </row>
     <row r="108" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B108" s="63"/>
-      <c r="C108" s="63"/>
+      <c r="B108" s="188"/>
+      <c r="C108" s="188"/>
     </row>
     <row r="109" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B109" s="63"/>
-      <c r="C109" s="63"/>
+      <c r="B109" s="188"/>
+      <c r="C109" s="188"/>
     </row>
     <row r="110" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B110" s="63"/>
-      <c r="C110" s="63"/>
+      <c r="B110" s="188"/>
+      <c r="C110" s="188"/>
     </row>
     <row r="111" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B111" s="63"/>
-      <c r="C111" s="63"/>
+      <c r="B111" s="188"/>
+      <c r="C111" s="188"/>
     </row>
     <row r="112" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B112" s="63"/>
-      <c r="C112" s="63"/>
+      <c r="B112" s="188"/>
+      <c r="C112" s="188"/>
     </row>
     <row r="113" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B113" s="63"/>
-      <c r="C113" s="63"/>
+      <c r="B113" s="188"/>
+      <c r="C113" s="188"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -5618,10 +5750,10 @@
     <col min="2" max="2" width="30.77734375" customWidth="1"/>
     <col min="3" max="3" width="50.77734375" customWidth="1"/>
     <col min="4" max="5" width="10.77734375" customWidth="1"/>
-    <col min="6" max="6" width="7.77734375" style="87" customWidth="1"/>
+    <col min="6" max="6" width="7.77734375" style="60" customWidth="1"/>
     <col min="7" max="7" width="3.77734375" customWidth="1"/>
-    <col min="8" max="8" width="30.77734375" style="87" customWidth="1"/>
-    <col min="9" max="9" width="12.77734375" style="66" customWidth="1"/>
+    <col min="8" max="8" width="30.77734375" style="60" customWidth="1"/>
+    <col min="9" max="9" width="12.77734375" style="43" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
@@ -5630,474 +5762,474 @@
       </c>
     </row>
     <row r="3" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="B3" s="20" t="s">
-        <v>167</v>
+      <c r="B3" s="13" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="4" spans="2:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="106" t="s">
-        <v>239</v>
-      </c>
-      <c r="C4" s="106"/>
-      <c r="D4" s="106"/>
-      <c r="E4" s="106"/>
-      <c r="F4" s="106"/>
-      <c r="G4" s="106"/>
-      <c r="H4" s="106"/>
-      <c r="I4" s="106"/>
+      <c r="B4" s="78" t="s">
+        <v>229</v>
+      </c>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
     </row>
     <row r="5" spans="2:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="117"/>
-      <c r="C5" s="117"/>
-      <c r="D5" s="117"/>
-      <c r="E5" s="117"/>
-      <c r="F5" s="117"/>
-      <c r="G5" s="117"/>
-      <c r="H5" s="117"/>
-      <c r="I5" s="117"/>
+      <c r="B5" s="83"/>
+      <c r="C5" s="83"/>
+      <c r="D5" s="83"/>
+      <c r="E5" s="83"/>
+      <c r="F5" s="83"/>
+      <c r="G5" s="83"/>
+      <c r="H5" s="83"/>
+      <c r="I5" s="83"/>
     </row>
     <row r="6" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="B6" s="37" t="s">
+      <c r="B6" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="38" t="s">
+      <c r="C6" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="39" t="s">
+      <c r="D6" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="E6" s="39" t="s">
+      <c r="E6" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="F6" s="123" t="s">
+      <c r="F6" s="89" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="124"/>
-      <c r="H6" s="38" t="s">
+      <c r="G6" s="90"/>
+      <c r="H6" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="I6" s="69" t="s">
+      <c r="I6" s="45" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="B7" s="6" t="s">
-        <v>316</v>
-      </c>
-      <c r="C7" s="33"/>
-      <c r="D7" s="34"/>
-      <c r="E7" s="34"/>
-      <c r="F7" s="128"/>
-      <c r="G7" s="34"/>
-      <c r="H7" s="84"/>
-      <c r="I7" s="70"/>
+      <c r="B7" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="C7" s="23"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="93"/>
+      <c r="G7" s="24"/>
+      <c r="H7" s="58"/>
+      <c r="I7" s="46"/>
     </row>
     <row r="8" spans="2:9" ht="57" x14ac:dyDescent="0.3">
-      <c r="B8" s="32" t="s">
+      <c r="B8" s="22" t="s">
+        <v>217</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>302</v>
+      </c>
+      <c r="D8" s="21">
+        <v>1</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="F8" s="91"/>
+      <c r="G8" s="85" t="str">
+        <f t="shared" ref="G8:G21" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F8,"/Readme.md"),"Ver")</f>
+        <v>Ver</v>
+      </c>
+      <c r="H8" s="25"/>
+      <c r="I8" s="47">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="B9" s="22" t="s">
+        <v>219</v>
+      </c>
+      <c r="C9" s="25" t="s">
+        <v>222</v>
+      </c>
+      <c r="D9" s="21">
+        <v>1</v>
+      </c>
+      <c r="E9" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="F9" s="91"/>
+      <c r="G9" s="85" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H9" s="25"/>
+      <c r="I9" s="47"/>
+    </row>
+    <row r="10" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="B10" s="22" t="s">
+        <v>218</v>
+      </c>
+      <c r="C10" s="25" t="s">
+        <v>222</v>
+      </c>
+      <c r="D10" s="21">
+        <v>1</v>
+      </c>
+      <c r="E10" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="F10" s="91"/>
+      <c r="G10" s="85" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H10" s="25"/>
+      <c r="I10" s="47"/>
+    </row>
+    <row r="11" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="B11" s="22" t="s">
+        <v>220</v>
+      </c>
+      <c r="C11" s="25" t="s">
         <v>225</v>
       </c>
-      <c r="C8" s="35" t="s">
-        <v>315</v>
-      </c>
-      <c r="D8" s="31">
+      <c r="D11" s="21">
         <v>1</v>
       </c>
-      <c r="E8" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="F8" s="125"/>
-      <c r="G8" s="119" t="str">
-        <f t="shared" ref="G8:G21" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F8,"/Readme.md"),"Ver")</f>
-        <v>Ver</v>
-      </c>
-      <c r="H8" s="35"/>
-      <c r="I8" s="71">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="B9" s="32" t="s">
-        <v>227</v>
-      </c>
-      <c r="C9" s="35" t="s">
-        <v>230</v>
-      </c>
-      <c r="D9" s="31">
+      <c r="E11" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="F11" s="91"/>
+      <c r="G11" s="85" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H11" s="25"/>
+      <c r="I11" s="47"/>
+    </row>
+    <row r="12" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="B12" s="33" t="s">
+        <v>206</v>
+      </c>
+      <c r="C12" s="25" t="s">
+        <v>223</v>
+      </c>
+      <c r="D12" s="21">
         <v>1</v>
       </c>
-      <c r="E9" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="F9" s="125"/>
-      <c r="G9" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H9" s="35"/>
-      <c r="I9" s="71"/>
-    </row>
-    <row r="10" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="B10" s="32" t="s">
-        <v>226</v>
-      </c>
-      <c r="C10" s="35" t="s">
-        <v>230</v>
-      </c>
-      <c r="D10" s="31">
+      <c r="E12" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="F12" s="94"/>
+      <c r="G12" s="85" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H12" s="34"/>
+      <c r="I12" s="48"/>
+    </row>
+    <row r="13" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="B13" s="33" t="s">
+        <v>221</v>
+      </c>
+      <c r="C13" s="25" t="s">
+        <v>224</v>
+      </c>
+      <c r="D13" s="21">
         <v>1</v>
       </c>
-      <c r="E10" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="F10" s="125"/>
-      <c r="G10" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H10" s="35"/>
-      <c r="I10" s="71"/>
-    </row>
-    <row r="11" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B11" s="32" t="s">
-        <v>228</v>
-      </c>
-      <c r="C11" s="35" t="s">
-        <v>233</v>
-      </c>
-      <c r="D11" s="31">
+      <c r="E13" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="F13" s="94"/>
+      <c r="G13" s="85" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H13" s="34"/>
+      <c r="I13" s="48"/>
+    </row>
+    <row r="14" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="B14" s="22" t="s">
+        <v>201</v>
+      </c>
+      <c r="C14" s="25" t="s">
+        <v>205</v>
+      </c>
+      <c r="D14" s="21">
         <v>1</v>
       </c>
-      <c r="E11" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="F11" s="125"/>
-      <c r="G11" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H11" s="35"/>
-      <c r="I11" s="71"/>
-    </row>
-    <row r="12" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B12" s="43" t="s">
-        <v>213</v>
-      </c>
-      <c r="C12" s="35" t="s">
-        <v>231</v>
-      </c>
-      <c r="D12" s="31">
+      <c r="E14" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="F14" s="91"/>
+      <c r="G14" s="85" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H14" s="25"/>
+      <c r="I14" s="47"/>
+    </row>
+    <row r="15" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="B15" s="22" t="s">
+        <v>202</v>
+      </c>
+      <c r="C15" s="25" t="s">
+        <v>205</v>
+      </c>
+      <c r="D15" s="21">
         <v>1</v>
       </c>
-      <c r="E12" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="F12" s="129"/>
-      <c r="G12" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H12" s="44"/>
-      <c r="I12" s="72"/>
-    </row>
-    <row r="13" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="B13" s="43" t="s">
-        <v>229</v>
-      </c>
-      <c r="C13" s="35" t="s">
-        <v>232</v>
-      </c>
-      <c r="D13" s="31">
+      <c r="E15" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="F15" s="91"/>
+      <c r="G15" s="85" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H15" s="25"/>
+      <c r="I15" s="47"/>
+    </row>
+    <row r="16" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="B16" s="33" t="s">
+        <v>203</v>
+      </c>
+      <c r="C16" s="25" t="s">
+        <v>205</v>
+      </c>
+      <c r="D16" s="21">
         <v>1</v>
       </c>
-      <c r="E13" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="F13" s="129"/>
-      <c r="G13" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H13" s="44"/>
-      <c r="I13" s="72"/>
-    </row>
-    <row r="14" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="B14" s="32" t="s">
-        <v>208</v>
-      </c>
-      <c r="C14" s="35" t="s">
-        <v>212</v>
-      </c>
-      <c r="D14" s="31">
+      <c r="E16" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="F16" s="94"/>
+      <c r="G16" s="85" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H16" s="34"/>
+      <c r="I16" s="48"/>
+    </row>
+    <row r="17" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="B17" s="33" t="s">
+        <v>266</v>
+      </c>
+      <c r="C17" s="25" t="s">
+        <v>205</v>
+      </c>
+      <c r="D17" s="21">
         <v>1</v>
       </c>
-      <c r="E14" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="F14" s="125"/>
-      <c r="G14" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H14" s="35"/>
-      <c r="I14" s="71"/>
-    </row>
-    <row r="15" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="B15" s="32" t="s">
-        <v>209</v>
-      </c>
-      <c r="C15" s="35" t="s">
-        <v>212</v>
-      </c>
-      <c r="D15" s="31">
+      <c r="E17" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="F17" s="94"/>
+      <c r="G17" s="85" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H17" s="34"/>
+      <c r="I17" s="48"/>
+    </row>
+    <row r="18" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="B18" s="33" t="s">
+        <v>204</v>
+      </c>
+      <c r="C18" s="25" t="s">
+        <v>205</v>
+      </c>
+      <c r="D18" s="21">
         <v>1</v>
       </c>
-      <c r="E15" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="F15" s="125"/>
-      <c r="G15" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H15" s="35"/>
-      <c r="I15" s="71"/>
-    </row>
-    <row r="16" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="B16" s="43" t="s">
+      <c r="E18" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="F18" s="94"/>
+      <c r="G18" s="85" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H18" s="34"/>
+      <c r="I18" s="48"/>
+    </row>
+    <row r="19" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="B19" s="33" t="s">
+        <v>215</v>
+      </c>
+      <c r="C19" s="25" t="s">
+        <v>205</v>
+      </c>
+      <c r="D19" s="35">
+        <v>1</v>
+      </c>
+      <c r="E19" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="F19" s="94"/>
+      <c r="G19" s="85" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H19" s="34"/>
+      <c r="I19" s="48"/>
+    </row>
+    <row r="20" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="B20" s="33" t="s">
+        <v>216</v>
+      </c>
+      <c r="C20" s="25" t="s">
+        <v>205</v>
+      </c>
+      <c r="D20" s="35">
+        <v>1</v>
+      </c>
+      <c r="E20" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="F20" s="94"/>
+      <c r="G20" s="85" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H20" s="34"/>
+      <c r="I20" s="48"/>
+    </row>
+    <row r="21" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="B21" s="33"/>
+      <c r="C21" s="34"/>
+      <c r="D21" s="35"/>
+      <c r="E21" s="35"/>
+      <c r="F21" s="94"/>
+      <c r="G21" s="86" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H21" s="34"/>
+      <c r="I21" s="48"/>
+    </row>
+    <row r="22" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="B22" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="C22" s="23"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="93"/>
+      <c r="G22" s="24"/>
+      <c r="H22" s="58"/>
+      <c r="I22" s="46"/>
+    </row>
+    <row r="23" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="B23" s="22" t="s">
+        <v>207</v>
+      </c>
+      <c r="C23" s="25" t="s">
         <v>210</v>
       </c>
-      <c r="C16" s="35" t="s">
-        <v>212</v>
-      </c>
-      <c r="D16" s="31">
-        <v>1</v>
-      </c>
-      <c r="E16" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="F16" s="129"/>
-      <c r="G16" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H16" s="44"/>
-      <c r="I16" s="72"/>
-    </row>
-    <row r="17" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="B17" s="43" t="s">
-        <v>278</v>
-      </c>
-      <c r="C17" s="35" t="s">
-        <v>212</v>
-      </c>
-      <c r="D17" s="31">
-        <v>1</v>
-      </c>
-      <c r="E17" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="F17" s="129"/>
-      <c r="G17" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H17" s="44"/>
-      <c r="I17" s="72"/>
-    </row>
-    <row r="18" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="B18" s="43" t="s">
-        <v>211</v>
-      </c>
-      <c r="C18" s="35" t="s">
-        <v>212</v>
-      </c>
-      <c r="D18" s="31">
-        <v>1</v>
-      </c>
-      <c r="E18" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="F18" s="129"/>
-      <c r="G18" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H18" s="44"/>
-      <c r="I18" s="72"/>
-    </row>
-    <row r="19" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="B19" s="43" t="s">
-        <v>223</v>
-      </c>
-      <c r="C19" s="35" t="s">
-        <v>212</v>
-      </c>
-      <c r="D19" s="45">
-        <v>1</v>
-      </c>
-      <c r="E19" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="F19" s="129"/>
-      <c r="G19" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H19" s="44"/>
-      <c r="I19" s="72"/>
-    </row>
-    <row r="20" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="B20" s="43" t="s">
-        <v>224</v>
-      </c>
-      <c r="C20" s="35" t="s">
-        <v>212</v>
-      </c>
-      <c r="D20" s="45">
-        <v>1</v>
-      </c>
-      <c r="E20" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="F20" s="129"/>
-      <c r="G20" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H20" s="44"/>
-      <c r="I20" s="72"/>
-    </row>
-    <row r="21" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="B21" s="43"/>
-      <c r="C21" s="44"/>
-      <c r="D21" s="45"/>
-      <c r="E21" s="45"/>
-      <c r="F21" s="129"/>
-      <c r="G21" s="120" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H21" s="44"/>
-      <c r="I21" s="72"/>
-    </row>
-    <row r="22" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="B22" s="6" t="s">
-        <v>234</v>
-      </c>
-      <c r="C22" s="33"/>
-      <c r="D22" s="34"/>
-      <c r="E22" s="34"/>
-      <c r="F22" s="128"/>
-      <c r="G22" s="34"/>
-      <c r="H22" s="84"/>
-      <c r="I22" s="70"/>
-    </row>
-    <row r="23" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
-      <c r="B23" s="32" t="s">
-        <v>214</v>
-      </c>
-      <c r="C23" s="35" t="s">
-        <v>218</v>
-      </c>
-      <c r="D23" s="46">
+      <c r="D23" s="36">
         <f>'2.ArquitectonicaEstructural'!D31-'2.ArquitectonicaEstructural'!D37-'2.ArquitectonicaEstructural'!D43</f>
         <v>1135.04</v>
       </c>
-      <c r="E23" s="31" t="s">
+      <c r="E23" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="F23" s="125"/>
-      <c r="G23" s="119" t="str">
+      <c r="F23" s="91"/>
+      <c r="G23" s="85" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F23,"/Readme.md"),"Ver")</f>
         <v>Ver</v>
       </c>
-      <c r="H23" s="35"/>
-      <c r="I23" s="71">
+      <c r="H23" s="25"/>
+      <c r="I23" s="47">
         <v>5</v>
       </c>
     </row>
     <row r="24" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="B24" s="32" t="s">
-        <v>217</v>
-      </c>
-      <c r="C24" s="35" t="s">
-        <v>220</v>
-      </c>
-      <c r="D24" s="36">
+      <c r="B24" s="22" t="s">
+        <v>209</v>
+      </c>
+      <c r="C24" s="25" t="s">
+        <v>212</v>
+      </c>
+      <c r="D24" s="26">
         <v>992</v>
       </c>
-      <c r="E24" s="31" t="s">
+      <c r="E24" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="F24" s="125"/>
-      <c r="G24" s="119" t="str">
+      <c r="F24" s="91"/>
+      <c r="G24" s="85" t="str">
         <f t="shared" ref="G24:G27" si="1">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F24,"/Readme.md"),"Ver")</f>
         <v>Ver</v>
       </c>
-      <c r="H24" s="35"/>
-      <c r="I24" s="71"/>
+      <c r="H24" s="25"/>
+      <c r="I24" s="47"/>
     </row>
     <row r="25" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="B25" s="32" t="s">
-        <v>216</v>
-      </c>
-      <c r="C25" s="35" t="s">
-        <v>221</v>
-      </c>
-      <c r="D25" s="36">
+      <c r="B25" s="22" t="s">
+        <v>208</v>
+      </c>
+      <c r="C25" s="25" t="s">
+        <v>213</v>
+      </c>
+      <c r="D25" s="26">
         <v>1950</v>
       </c>
-      <c r="E25" s="31" t="s">
+      <c r="E25" s="21" t="s">
         <v>65</v>
       </c>
-      <c r="F25" s="125"/>
-      <c r="G25" s="119" t="str">
+      <c r="F25" s="91"/>
+      <c r="G25" s="85" t="str">
         <f t="shared" si="1"/>
         <v>Ver</v>
       </c>
-      <c r="H25" s="35"/>
-      <c r="I25" s="71"/>
+      <c r="H25" s="25"/>
+      <c r="I25" s="47"/>
     </row>
     <row r="26" spans="2:9" ht="45.6" x14ac:dyDescent="0.3">
-      <c r="B26" s="32" t="s">
-        <v>219</v>
-      </c>
-      <c r="C26" s="35" t="s">
-        <v>222</v>
-      </c>
-      <c r="D26" s="31">
+      <c r="B26" s="22" t="s">
+        <v>211</v>
+      </c>
+      <c r="C26" s="25" t="s">
+        <v>214</v>
+      </c>
+      <c r="D26" s="21">
         <f>INT(D23/(D24/1000*D25/1000))</f>
         <v>586</v>
       </c>
-      <c r="E26" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="F26" s="125"/>
-      <c r="G26" s="119" t="str">
+      <c r="E26" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="F26" s="91"/>
+      <c r="G26" s="85" t="str">
         <f t="shared" si="1"/>
         <v>Ver</v>
       </c>
-      <c r="H26" s="35"/>
-      <c r="I26" s="71"/>
+      <c r="H26" s="25"/>
+      <c r="I26" s="47"/>
     </row>
     <row r="27" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="B27" s="40"/>
-      <c r="C27" s="41"/>
-      <c r="D27" s="42"/>
-      <c r="E27" s="42"/>
-      <c r="F27" s="126"/>
-      <c r="G27" s="120" t="str">
+      <c r="B27" s="30"/>
+      <c r="C27" s="31"/>
+      <c r="D27" s="32"/>
+      <c r="E27" s="32"/>
+      <c r="F27" s="92"/>
+      <c r="G27" s="86" t="str">
         <f t="shared" si="1"/>
         <v>Ver</v>
       </c>
-      <c r="H27" s="41"/>
-      <c r="I27" s="73"/>
+      <c r="H27" s="31"/>
+      <c r="I27" s="49"/>
     </row>
     <row r="28" spans="2:9" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="H28" s="76" t="s">
-        <v>290</v>
-      </c>
-      <c r="I28" s="88">
+      <c r="H28" s="50" t="s">
+        <v>277</v>
+      </c>
+      <c r="I28" s="61">
         <f>AVERAGE(I7:I27)</f>
         <v>5</v>
       </c>
@@ -6121,10 +6253,10 @@
     <col min="2" max="2" width="30.77734375" style="1" customWidth="1"/>
     <col min="3" max="3" width="50.77734375" style="1" customWidth="1"/>
     <col min="4" max="5" width="10.77734375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="7.77734375" style="22" customWidth="1"/>
+    <col min="6" max="6" width="7.77734375" style="15" customWidth="1"/>
     <col min="7" max="7" width="3.77734375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="30.77734375" style="22" customWidth="1"/>
-    <col min="9" max="9" width="12.77734375" style="88" customWidth="1"/>
+    <col min="8" max="8" width="30.77734375" style="15" customWidth="1"/>
+    <col min="9" max="9" width="12.77734375" style="61" customWidth="1"/>
     <col min="10" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
@@ -6134,380 +6266,380 @@
       </c>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="13" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B4" s="78" t="s">
+        <v>226</v>
+      </c>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B5" s="83"/>
+      <c r="C5" s="83"/>
+      <c r="D5" s="83"/>
+      <c r="E5" s="83"/>
+      <c r="F5" s="83"/>
+      <c r="G5" s="83"/>
+      <c r="H5" s="83"/>
+      <c r="I5" s="83"/>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B6" s="27" t="s">
+        <v>37</v>
+      </c>
+      <c r="C6" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="E6" s="29" t="s">
+        <v>50</v>
+      </c>
+      <c r="F6" s="89" t="s">
+        <v>39</v>
+      </c>
+      <c r="G6" s="90"/>
+      <c r="H6" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="I6" s="45" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B7" s="5" t="s">
+        <v>339</v>
+      </c>
+      <c r="C7" s="23"/>
+      <c r="D7" s="24"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="93"/>
+      <c r="G7" s="24"/>
+      <c r="H7" s="58"/>
+      <c r="I7" s="46"/>
+    </row>
+    <row r="8" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
+      <c r="B8" s="22" t="s">
+        <v>230</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>236</v>
+      </c>
+      <c r="D8" s="26">
+        <v>3</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="F8" s="91"/>
+      <c r="G8" s="85" t="str">
+        <f t="shared" ref="G8:G22" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F8,"/Readme.md"),"Ver")</f>
+        <v>Ver</v>
+      </c>
+      <c r="H8" s="25"/>
+      <c r="I8" s="47">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
+      <c r="B9" s="22" t="s">
+        <v>234</v>
+      </c>
+      <c r="C9" s="25" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="4" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="106" t="s">
+      <c r="D9" s="26">
+        <v>2.5</v>
+      </c>
+      <c r="E9" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="F9" s="91"/>
+      <c r="G9" s="85" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H9" s="25"/>
+      <c r="I9" s="47"/>
+    </row>
+    <row r="10" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
+      <c r="B10" s="22" t="s">
+        <v>232</v>
+      </c>
+      <c r="C10" s="25" t="s">
+        <v>243</v>
+      </c>
+      <c r="D10" s="26">
+        <v>4</v>
+      </c>
+      <c r="E10" s="21" t="s">
+        <v>233</v>
+      </c>
+      <c r="F10" s="91"/>
+      <c r="G10" s="85" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H10" s="25"/>
+      <c r="I10" s="47"/>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B11" s="22" t="s">
         <v>235</v>
       </c>
-      <c r="C4" s="106"/>
-      <c r="D4" s="106"/>
-      <c r="E4" s="106"/>
-      <c r="F4" s="106"/>
-      <c r="G4" s="106"/>
-      <c r="H4" s="106"/>
-      <c r="I4" s="106"/>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B5" s="117"/>
-      <c r="C5" s="117"/>
-      <c r="D5" s="117"/>
-      <c r="E5" s="117"/>
-      <c r="F5" s="117"/>
-      <c r="G5" s="117"/>
-      <c r="H5" s="117"/>
-      <c r="I5" s="117"/>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B6" s="37" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6" s="38" t="s">
-        <v>38</v>
-      </c>
-      <c r="D6" s="39" t="s">
-        <v>49</v>
-      </c>
-      <c r="E6" s="39" t="s">
-        <v>50</v>
-      </c>
-      <c r="F6" s="123" t="s">
-        <v>39</v>
-      </c>
-      <c r="G6" s="124"/>
-      <c r="H6" s="38" t="s">
-        <v>26</v>
-      </c>
-      <c r="I6" s="69" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B7" s="6" t="s">
-        <v>241</v>
-      </c>
-      <c r="C7" s="33"/>
-      <c r="D7" s="34"/>
-      <c r="E7" s="34"/>
-      <c r="F7" s="128"/>
-      <c r="G7" s="34"/>
-      <c r="H7" s="84"/>
-      <c r="I7" s="70"/>
-    </row>
-    <row r="8" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
-      <c r="B8" s="32" t="s">
+      <c r="C11" s="25" t="s">
+        <v>238</v>
+      </c>
+      <c r="D11" s="26">
+        <v>2</v>
+      </c>
+      <c r="E11" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="F11" s="91"/>
+      <c r="G11" s="85" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H11" s="25"/>
+      <c r="I11" s="47"/>
+    </row>
+    <row r="12" spans="2:9" ht="33.6" x14ac:dyDescent="0.4">
+      <c r="B12" s="22" t="s">
         <v>240</v>
       </c>
-      <c r="C8" s="35" t="s">
-        <v>247</v>
-      </c>
-      <c r="D8" s="36">
-        <v>3</v>
-      </c>
-      <c r="E8" s="31" t="s">
-        <v>54</v>
-      </c>
-      <c r="F8" s="125"/>
-      <c r="G8" s="119" t="str">
-        <f t="shared" ref="G8:G22" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F8,"/Readme.md"),"Ver")</f>
-        <v>Ver</v>
-      </c>
-      <c r="H8" s="35"/>
-      <c r="I8" s="71">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
-      <c r="B9" s="32" t="s">
-        <v>245</v>
-      </c>
-      <c r="C9" s="35" t="s">
-        <v>248</v>
-      </c>
-      <c r="D9" s="36">
-        <v>2.5</v>
-      </c>
-      <c r="E9" s="31" t="s">
-        <v>54</v>
-      </c>
-      <c r="F9" s="125"/>
-      <c r="G9" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H9" s="35"/>
-      <c r="I9" s="71"/>
-    </row>
-    <row r="10" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
-      <c r="B10" s="32" t="s">
-        <v>243</v>
-      </c>
-      <c r="C10" s="35" t="s">
-        <v>254</v>
-      </c>
-      <c r="D10" s="36">
-        <v>4</v>
-      </c>
-      <c r="E10" s="31" t="s">
+      <c r="C12" s="25" t="s">
         <v>244</v>
       </c>
-      <c r="F10" s="125"/>
-      <c r="G10" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H10" s="35"/>
-      <c r="I10" s="71"/>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B11" s="32" t="s">
-        <v>246</v>
-      </c>
-      <c r="C11" s="35" t="s">
-        <v>249</v>
-      </c>
-      <c r="D11" s="36">
-        <v>2</v>
-      </c>
-      <c r="E11" s="31" t="s">
-        <v>54</v>
-      </c>
-      <c r="F11" s="125"/>
-      <c r="G11" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H11" s="35"/>
-      <c r="I11" s="71"/>
-    </row>
-    <row r="12" spans="2:9" ht="33.6" x14ac:dyDescent="0.4">
-      <c r="B12" s="32" t="s">
-        <v>251</v>
-      </c>
-      <c r="C12" s="35" t="s">
-        <v>255</v>
-      </c>
-      <c r="D12" s="31">
+      <c r="D12" s="21">
         <f>D10*D11</f>
         <v>8</v>
       </c>
-      <c r="E12" s="31" t="s">
+      <c r="E12" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="F12" s="125"/>
-      <c r="G12" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H12" s="35"/>
-      <c r="I12" s="71"/>
+      <c r="F12" s="91"/>
+      <c r="G12" s="85" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H12" s="25"/>
+      <c r="I12" s="47"/>
     </row>
     <row r="13" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
-      <c r="B13" s="32" t="s">
-        <v>242</v>
-      </c>
-      <c r="C13" s="35" t="s">
-        <v>250</v>
-      </c>
-      <c r="D13" s="36">
+      <c r="B13" s="22" t="s">
+        <v>231</v>
+      </c>
+      <c r="C13" s="25" t="s">
+        <v>239</v>
+      </c>
+      <c r="D13" s="26">
         <v>8</v>
       </c>
-      <c r="E13" s="31" t="s">
+      <c r="E13" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="F13" s="125"/>
-      <c r="G13" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H13" s="35"/>
-      <c r="I13" s="71"/>
+      <c r="F13" s="91"/>
+      <c r="G13" s="85" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H13" s="25"/>
+      <c r="I13" s="47"/>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B14" s="32" t="s">
-        <v>256</v>
-      </c>
-      <c r="C14" s="35" t="s">
-        <v>258</v>
-      </c>
-      <c r="D14" s="31" t="str">
+      <c r="B14" s="22" t="s">
+        <v>245</v>
+      </c>
+      <c r="C14" s="25" t="s">
+        <v>247</v>
+      </c>
+      <c r="D14" s="21" t="str">
         <f>IF(D12&lt;=D13, "Cumple","No cumple")</f>
         <v>Cumple</v>
       </c>
-      <c r="E14" s="31" t="s">
-        <v>257</v>
-      </c>
-      <c r="F14" s="125"/>
-      <c r="G14" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H14" s="35"/>
-      <c r="I14" s="71"/>
+      <c r="E14" s="21" t="s">
+        <v>246</v>
+      </c>
+      <c r="F14" s="91"/>
+      <c r="G14" s="85" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H14" s="25"/>
+      <c r="I14" s="47"/>
     </row>
     <row r="15" spans="2:9" ht="33.6" x14ac:dyDescent="0.4">
-      <c r="B15" s="32" t="s">
-        <v>259</v>
-      </c>
-      <c r="C15" s="35" t="s">
-        <v>260</v>
-      </c>
-      <c r="D15" s="36">
+      <c r="B15" s="22" t="s">
+        <v>248</v>
+      </c>
+      <c r="C15" s="25" t="s">
+        <v>249</v>
+      </c>
+      <c r="D15" s="26">
         <v>60</v>
       </c>
-      <c r="E15" s="31" t="s">
+      <c r="E15" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="F15" s="125"/>
-      <c r="G15" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H15" s="35"/>
-      <c r="I15" s="71"/>
+      <c r="F15" s="91"/>
+      <c r="G15" s="85" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H15" s="25"/>
+      <c r="I15" s="47"/>
     </row>
     <row r="16" spans="2:9" ht="33.6" x14ac:dyDescent="0.4">
-      <c r="B16" s="32" t="s">
-        <v>261</v>
-      </c>
-      <c r="C16" s="35" t="s">
-        <v>262</v>
-      </c>
-      <c r="D16" s="31">
+      <c r="B16" s="22" t="s">
+        <v>250</v>
+      </c>
+      <c r="C16" s="25" t="s">
+        <v>251</v>
+      </c>
+      <c r="D16" s="21">
         <f>D15*D10</f>
         <v>240</v>
       </c>
-      <c r="E16" s="31" t="s">
+      <c r="E16" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="F16" s="125"/>
-      <c r="G16" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H16" s="35"/>
-      <c r="I16" s="71"/>
+      <c r="F16" s="91"/>
+      <c r="G16" s="85" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H16" s="25"/>
+      <c r="I16" s="47"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B17" s="32"/>
-      <c r="C17" s="35"/>
-      <c r="D17" s="36"/>
-      <c r="E17" s="31"/>
-      <c r="F17" s="125"/>
-      <c r="G17" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H17" s="35"/>
-      <c r="I17" s="71"/>
+      <c r="B17" s="22"/>
+      <c r="C17" s="25"/>
+      <c r="D17" s="26"/>
+      <c r="E17" s="21"/>
+      <c r="F17" s="91"/>
+      <c r="G17" s="85" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H17" s="25"/>
+      <c r="I17" s="47"/>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B18" s="32"/>
-      <c r="C18" s="35"/>
-      <c r="D18" s="31"/>
-      <c r="E18" s="31"/>
-      <c r="F18" s="125"/>
-      <c r="G18" s="120" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H18" s="35"/>
-      <c r="I18" s="71"/>
+      <c r="B18" s="22"/>
+      <c r="C18" s="25"/>
+      <c r="D18" s="21"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="91"/>
+      <c r="G18" s="86" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H18" s="25"/>
+      <c r="I18" s="47"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B19" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="C19" s="33"/>
-      <c r="D19" s="34"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="128"/>
-      <c r="G19" s="34"/>
-      <c r="H19" s="84"/>
-      <c r="I19" s="70"/>
+      <c r="B19" s="5" t="s">
+        <v>340</v>
+      </c>
+      <c r="C19" s="23"/>
+      <c r="D19" s="24"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="93"/>
+      <c r="G19" s="24"/>
+      <c r="H19" s="58"/>
+      <c r="I19" s="46"/>
     </row>
     <row r="20" spans="2:9" ht="45.6" x14ac:dyDescent="0.4">
-      <c r="B20" s="32" t="s">
-        <v>263</v>
-      </c>
-      <c r="C20" s="35" t="s">
+      <c r="B20" s="22" t="s">
         <v>252</v>
       </c>
-      <c r="D20" s="36" t="s">
+      <c r="C20" s="25" t="s">
+        <v>241</v>
+      </c>
+      <c r="D20" s="26" t="s">
+        <v>242</v>
+      </c>
+      <c r="E20" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="F20" s="91"/>
+      <c r="G20" s="85" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H20" s="25"/>
+      <c r="I20" s="47">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="2:9" ht="45.6" x14ac:dyDescent="0.4">
+      <c r="B21" s="22" t="s">
         <v>253</v>
       </c>
-      <c r="E20" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="F20" s="125"/>
-      <c r="G20" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H20" s="35"/>
-      <c r="I20" s="71">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="2:9" ht="45.6" x14ac:dyDescent="0.4">
-      <c r="B21" s="32" t="s">
-        <v>264</v>
-      </c>
-      <c r="C21" s="35" t="s">
-        <v>252</v>
-      </c>
-      <c r="D21" s="36" t="s">
-        <v>253</v>
-      </c>
-      <c r="E21" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="F21" s="125"/>
-      <c r="G21" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H21" s="35"/>
-      <c r="I21" s="71"/>
+      <c r="C21" s="25" t="s">
+        <v>241</v>
+      </c>
+      <c r="D21" s="26" t="s">
+        <v>242</v>
+      </c>
+      <c r="E21" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="F21" s="91"/>
+      <c r="G21" s="85" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H21" s="25"/>
+      <c r="I21" s="47"/>
     </row>
     <row r="22" spans="2:9" ht="45.6" x14ac:dyDescent="0.4">
-      <c r="B22" s="32" t="s">
-        <v>265</v>
-      </c>
-      <c r="C22" s="35" t="s">
-        <v>252</v>
-      </c>
-      <c r="D22" s="36" t="s">
-        <v>253</v>
-      </c>
-      <c r="E22" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="F22" s="125"/>
-      <c r="G22" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H22" s="35"/>
-      <c r="I22" s="71"/>
+      <c r="B22" s="22" t="s">
+        <v>254</v>
+      </c>
+      <c r="C22" s="25" t="s">
+        <v>241</v>
+      </c>
+      <c r="D22" s="26" t="s">
+        <v>242</v>
+      </c>
+      <c r="E22" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="F22" s="91"/>
+      <c r="G22" s="85" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H22" s="25"/>
+      <c r="I22" s="47"/>
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B23" s="40"/>
-      <c r="C23" s="41"/>
-      <c r="D23" s="42"/>
-      <c r="E23" s="42"/>
-      <c r="F23" s="126"/>
-      <c r="G23" s="42"/>
-      <c r="H23" s="41"/>
-      <c r="I23" s="73"/>
+      <c r="B23" s="30"/>
+      <c r="C23" s="31"/>
+      <c r="D23" s="32"/>
+      <c r="E23" s="32"/>
+      <c r="F23" s="92"/>
+      <c r="G23" s="32"/>
+      <c r="H23" s="31"/>
+      <c r="I23" s="49"/>
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="H24" s="76" t="s">
-        <v>290</v>
-      </c>
-      <c r="I24" s="88">
+      <c r="H24" s="50" t="s">
+        <v>277</v>
+      </c>
+      <c r="I24" s="61">
         <f>AVERAGE(I7:I23)</f>
         <v>5</v>
       </c>
@@ -6531,10 +6663,10 @@
     <col min="2" max="2" width="30.77734375" style="1" customWidth="1"/>
     <col min="3" max="3" width="50.77734375" style="1" customWidth="1"/>
     <col min="4" max="5" width="10.77734375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="7.77734375" style="22" customWidth="1"/>
+    <col min="6" max="6" width="7.77734375" style="15" customWidth="1"/>
     <col min="7" max="7" width="3.77734375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="30.77734375" style="22" customWidth="1"/>
-    <col min="9" max="9" width="12.77734375" style="88" customWidth="1"/>
+    <col min="8" max="8" width="30.77734375" style="15" customWidth="1"/>
+    <col min="9" max="9" width="12.77734375" style="61" customWidth="1"/>
     <col min="10" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
@@ -6544,265 +6676,265 @@
       </c>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B3" s="20" t="s">
-        <v>328</v>
+      <c r="B3" s="13" t="s">
+        <v>341</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B4" s="106" t="s">
-        <v>272</v>
-      </c>
-      <c r="C4" s="106"/>
-      <c r="D4" s="106"/>
-      <c r="E4" s="106"/>
-      <c r="F4" s="106"/>
-      <c r="G4" s="106"/>
-      <c r="H4" s="106"/>
-      <c r="I4" s="106"/>
+      <c r="B4" s="78" t="s">
+        <v>260</v>
+      </c>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B5" s="117"/>
-      <c r="C5" s="117"/>
-      <c r="D5" s="117"/>
-      <c r="E5" s="117"/>
-      <c r="F5" s="117"/>
-      <c r="G5" s="117"/>
-      <c r="H5" s="117"/>
-      <c r="I5" s="117"/>
+      <c r="B5" s="83"/>
+      <c r="C5" s="83"/>
+      <c r="D5" s="83"/>
+      <c r="E5" s="83"/>
+      <c r="F5" s="83"/>
+      <c r="G5" s="83"/>
+      <c r="H5" s="83"/>
+      <c r="I5" s="83"/>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B6" s="37" t="s">
+      <c r="B6" s="27" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="38" t="s">
+      <c r="C6" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="39" t="s">
+      <c r="D6" s="29" t="s">
         <v>49</v>
       </c>
-      <c r="E6" s="39" t="s">
+      <c r="E6" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="F6" s="121" t="s">
+      <c r="F6" s="87" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="122"/>
-      <c r="H6" s="38" t="s">
+      <c r="G6" s="88"/>
+      <c r="H6" s="28" t="s">
         <v>26</v>
       </c>
-      <c r="I6" s="69" t="s">
+      <c r="I6" s="45" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
-      <c r="B7" s="32" t="s">
+      <c r="B7" s="22" t="s">
+        <v>255</v>
+      </c>
+      <c r="C7" s="25" t="s">
+        <v>256</v>
+      </c>
+      <c r="D7" s="26">
+        <v>1</v>
+      </c>
+      <c r="E7" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="F7" s="91"/>
+      <c r="G7" s="85" t="str">
+        <f t="shared" ref="G7:G16" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F7,"/Readme.md"),"Ver")</f>
+        <v>Ver</v>
+      </c>
+      <c r="H7" s="25"/>
+      <c r="I7" s="47">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
+      <c r="B8" s="22" t="s">
+        <v>257</v>
+      </c>
+      <c r="C8" s="25" t="s">
         <v>267</v>
       </c>
-      <c r="C7" s="35" t="s">
+      <c r="D8" s="26">
+        <v>1</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="F8" s="91"/>
+      <c r="G8" s="85" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H8" s="25"/>
+      <c r="I8" s="47"/>
+    </row>
+    <row r="9" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
+      <c r="B9" s="22" t="s">
+        <v>258</v>
+      </c>
+      <c r="C9" s="25" t="s">
         <v>268</v>
       </c>
-      <c r="D7" s="36">
+      <c r="D9" s="26">
         <v>1</v>
       </c>
-      <c r="E7" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="F7" s="125"/>
-      <c r="G7" s="119" t="str">
-        <f t="shared" ref="G7:G16" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F7,"/Readme.md"),"Ver")</f>
-        <v>Ver</v>
-      </c>
-      <c r="H7" s="35"/>
-      <c r="I7" s="71">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
-      <c r="B8" s="32" t="s">
+      <c r="E9" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="F9" s="91"/>
+      <c r="G9" s="85" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H9" s="25"/>
+      <c r="I9" s="47"/>
+    </row>
+    <row r="10" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
+      <c r="B10" s="22" t="s">
+        <v>259</v>
+      </c>
+      <c r="C10" s="25" t="s">
         <v>269</v>
       </c>
-      <c r="C8" s="35" t="s">
-        <v>279</v>
-      </c>
-      <c r="D8" s="36">
+      <c r="D10" s="26">
         <v>1</v>
       </c>
-      <c r="E8" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="F8" s="125"/>
-      <c r="G8" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H8" s="35"/>
-      <c r="I8" s="71"/>
-    </row>
-    <row r="9" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
-      <c r="B9" s="32" t="s">
-        <v>270</v>
-      </c>
-      <c r="C9" s="35" t="s">
-        <v>280</v>
-      </c>
-      <c r="D9" s="36">
+      <c r="E10" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="F10" s="91"/>
+      <c r="G10" s="85" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H10" s="25"/>
+      <c r="I10" s="47"/>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B11" s="22" t="s">
+        <v>261</v>
+      </c>
+      <c r="C11" s="25" t="s">
+        <v>222</v>
+      </c>
+      <c r="D11" s="26">
         <v>1</v>
       </c>
-      <c r="E9" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="F9" s="125"/>
-      <c r="G9" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H9" s="35"/>
-      <c r="I9" s="71"/>
-    </row>
-    <row r="10" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
-      <c r="B10" s="32" t="s">
-        <v>271</v>
-      </c>
-      <c r="C10" s="35" t="s">
-        <v>281</v>
-      </c>
-      <c r="D10" s="36">
+      <c r="E11" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="F11" s="91"/>
+      <c r="G11" s="85" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H11" s="25"/>
+      <c r="I11" s="47"/>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B12" s="22" t="s">
+        <v>262</v>
+      </c>
+      <c r="C12" s="25" t="s">
+        <v>222</v>
+      </c>
+      <c r="D12" s="26">
         <v>1</v>
       </c>
-      <c r="E10" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="F10" s="125"/>
-      <c r="G10" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H10" s="35"/>
-      <c r="I10" s="71"/>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B11" s="32" t="s">
-        <v>273</v>
-      </c>
-      <c r="C11" s="35" t="s">
-        <v>230</v>
-      </c>
-      <c r="D11" s="36">
+      <c r="E12" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="F12" s="91"/>
+      <c r="G12" s="85" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H12" s="25"/>
+      <c r="I12" s="47"/>
+    </row>
+    <row r="13" spans="2:9" ht="33.6" x14ac:dyDescent="0.4">
+      <c r="B13" s="22" t="s">
+        <v>263</v>
+      </c>
+      <c r="C13" s="25" t="s">
+        <v>225</v>
+      </c>
+      <c r="D13" s="26">
         <v>1</v>
       </c>
-      <c r="E11" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="F11" s="125"/>
-      <c r="G11" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H11" s="35"/>
-      <c r="I11" s="71"/>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B12" s="32" t="s">
-        <v>274</v>
-      </c>
-      <c r="C12" s="35" t="s">
-        <v>230</v>
-      </c>
-      <c r="D12" s="36">
+      <c r="E13" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="F13" s="91"/>
+      <c r="G13" s="85" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H13" s="25"/>
+      <c r="I13" s="47"/>
+    </row>
+    <row r="14" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
+      <c r="B14" s="22" t="s">
+        <v>264</v>
+      </c>
+      <c r="C14" s="25" t="s">
+        <v>223</v>
+      </c>
+      <c r="D14" s="26">
         <v>1</v>
       </c>
-      <c r="E12" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="F12" s="125"/>
-      <c r="G12" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H12" s="35"/>
-      <c r="I12" s="71"/>
-    </row>
-    <row r="13" spans="2:9" ht="33.6" x14ac:dyDescent="0.4">
-      <c r="B13" s="32" t="s">
-        <v>275</v>
-      </c>
-      <c r="C13" s="35" t="s">
-        <v>233</v>
-      </c>
-      <c r="D13" s="36">
+      <c r="E14" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="F14" s="91"/>
+      <c r="G14" s="85" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H14" s="25"/>
+      <c r="I14" s="47"/>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B15" s="22" t="s">
+        <v>265</v>
+      </c>
+      <c r="C15" s="25" t="s">
+        <v>224</v>
+      </c>
+      <c r="D15" s="26">
         <v>1</v>
       </c>
-      <c r="E13" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="F13" s="125"/>
-      <c r="G13" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H13" s="35"/>
-      <c r="I13" s="71"/>
-    </row>
-    <row r="14" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
-      <c r="B14" s="32" t="s">
-        <v>276</v>
-      </c>
-      <c r="C14" s="35" t="s">
-        <v>231</v>
-      </c>
-      <c r="D14" s="36">
-        <v>1</v>
-      </c>
-      <c r="E14" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="F14" s="125"/>
-      <c r="G14" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H14" s="35"/>
-      <c r="I14" s="71"/>
-    </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B15" s="32" t="s">
+      <c r="E15" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="F15" s="91"/>
+      <c r="G15" s="85" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H15" s="25"/>
+      <c r="I15" s="47"/>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B16" s="30"/>
+      <c r="C16" s="31"/>
+      <c r="D16" s="44"/>
+      <c r="E16" s="32"/>
+      <c r="F16" s="92"/>
+      <c r="G16" s="86" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H16" s="31"/>
+      <c r="I16" s="49"/>
+    </row>
+    <row r="17" spans="8:9" x14ac:dyDescent="0.4">
+      <c r="H17" s="50" t="s">
         <v>277</v>
       </c>
-      <c r="C15" s="35" t="s">
-        <v>232</v>
-      </c>
-      <c r="D15" s="36">
-        <v>1</v>
-      </c>
-      <c r="E15" s="31" t="s">
-        <v>123</v>
-      </c>
-      <c r="F15" s="125"/>
-      <c r="G15" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H15" s="35"/>
-      <c r="I15" s="71"/>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B16" s="40"/>
-      <c r="C16" s="41"/>
-      <c r="D16" s="67"/>
-      <c r="E16" s="42"/>
-      <c r="F16" s="126"/>
-      <c r="G16" s="120" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H16" s="41"/>
-      <c r="I16" s="73"/>
-    </row>
-    <row r="17" spans="8:9" x14ac:dyDescent="0.4">
-      <c r="H17" s="76" t="s">
-        <v>290</v>
-      </c>
-      <c r="I17" s="88">
+      <c r="I17" s="61">
         <f>AVERAGE(I7:I16)</f>
         <v>5</v>
       </c>
@@ -6819,303 +6951,326 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:I17"/>
+  <dimension ref="B2:I18"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="2.5546875" style="2" customWidth="1"/>
     <col min="3" max="3" width="30.77734375" style="2" customWidth="1"/>
     <col min="4" max="4" width="50.77734375" style="2" customWidth="1"/>
     <col min="5" max="5" width="40.77734375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="7.77734375" style="83" customWidth="1"/>
-    <col min="7" max="7" width="3.77734375" style="65" customWidth="1"/>
-    <col min="8" max="8" width="30.77734375" style="83" customWidth="1"/>
-    <col min="9" max="9" width="12.77734375" style="47" customWidth="1"/>
+    <col min="6" max="6" width="7.77734375" style="57" customWidth="1"/>
+    <col min="7" max="7" width="3.77734375" style="42" customWidth="1"/>
+    <col min="8" max="8" width="30.77734375" style="57" customWidth="1"/>
+    <col min="9" max="9" width="12.77734375" style="37" customWidth="1"/>
     <col min="10" max="16384" width="9.109375" style="2"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B2" s="104" t="s">
+      <c r="B2" s="76" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="104"/>
-      <c r="D2" s="104"/>
-      <c r="E2" s="104"/>
-      <c r="F2" s="104"/>
-      <c r="G2" s="104"/>
-      <c r="H2" s="104"/>
-      <c r="I2" s="104"/>
+      <c r="C2" s="76"/>
+      <c r="D2" s="76"/>
+      <c r="E2" s="76"/>
+      <c r="F2" s="76"/>
+      <c r="G2" s="76"/>
+      <c r="H2" s="76"/>
+      <c r="I2" s="76"/>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B3" s="118" t="s">
-        <v>327</v>
-      </c>
-      <c r="C3" s="118"/>
-      <c r="D3" s="118"/>
-      <c r="E3" s="118"/>
-      <c r="F3" s="118"/>
-      <c r="G3" s="118"/>
-      <c r="H3" s="118"/>
-      <c r="I3" s="118"/>
+      <c r="B3" s="84" t="s">
+        <v>342</v>
+      </c>
+      <c r="C3" s="84"/>
+      <c r="D3" s="84"/>
+      <c r="E3" s="84"/>
+      <c r="F3" s="84"/>
+      <c r="G3" s="84"/>
+      <c r="H3" s="84"/>
+      <c r="I3" s="84"/>
+    </row>
+    <row r="4" spans="2:9" s="42" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="78" t="s">
+        <v>343</v>
+      </c>
+      <c r="C4" s="78"/>
+      <c r="D4" s="78"/>
+      <c r="E4" s="78"/>
+      <c r="F4" s="78"/>
+      <c r="G4" s="78"/>
+      <c r="H4" s="78"/>
+      <c r="I4" s="78"/>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B5" s="17" t="s">
+      <c r="B5" s="83"/>
+      <c r="C5" s="83"/>
+      <c r="D5" s="83"/>
+      <c r="E5" s="83"/>
+      <c r="F5" s="83"/>
+      <c r="G5" s="83"/>
+      <c r="H5" s="83"/>
+      <c r="I5" s="83"/>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B6" s="12" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C6" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D6" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E6" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="F5" s="121" t="s">
+      <c r="F6" s="87" t="s">
         <v>39</v>
       </c>
-      <c r="G5" s="122"/>
-      <c r="H5" s="7" t="s">
+      <c r="G6" s="88"/>
+      <c r="H6" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="I5" s="10" t="s">
+      <c r="I6" s="8" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B6" s="15">
+    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B7" s="10">
         <v>0</v>
       </c>
-      <c r="C6" s="29" t="s">
-        <v>291</v>
-      </c>
-      <c r="D6" s="35" t="s">
-        <v>292</v>
-      </c>
-      <c r="E6" s="3" t="s">
+      <c r="C7" s="19" t="s">
+        <v>278</v>
+      </c>
+      <c r="D7" s="25" t="s">
+        <v>279</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="F6" s="86"/>
-      <c r="G6" s="119" t="str">
-        <f t="shared" ref="G6:G16" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F6,"/Readme.md"),"Ver")</f>
-        <v>Ver</v>
-      </c>
-      <c r="H6" s="86"/>
-      <c r="I6" s="11">
+      <c r="F7" s="59"/>
+      <c r="G7" s="85" t="str">
+        <f t="shared" ref="G7:G17" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F7,"/Readme.md"),"Ver")</f>
+        <v>Ver</v>
+      </c>
+      <c r="H7" s="59"/>
+      <c r="I7" s="9">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B7" s="15">
+    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B8" s="10">
         <v>1</v>
       </c>
-      <c r="C7" s="29" t="s">
+      <c r="C8" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="35" t="s">
+      <c r="D8" s="25" t="s">
+        <v>307</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" s="59"/>
+      <c r="G8" s="85" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H8" s="59"/>
+      <c r="I8" s="9"/>
+    </row>
+    <row r="9" spans="2:9" ht="91.2" x14ac:dyDescent="0.3">
+      <c r="B9" s="10">
+        <v>2</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>308</v>
+      </c>
+      <c r="D9" s="25" t="s">
+        <v>309</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" s="59"/>
+      <c r="G9" s="85" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H9" s="59"/>
+      <c r="I9" s="9"/>
+    </row>
+    <row r="10" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="B10" s="10">
+        <v>3</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>288</v>
+      </c>
+      <c r="D10" s="25" t="s">
         <v>321</v>
       </c>
-      <c r="E7" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F7" s="86"/>
-      <c r="G7" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H7" s="86"/>
-      <c r="I7" s="11"/>
-    </row>
-    <row r="8" spans="2:9" ht="91.2" x14ac:dyDescent="0.3">
-      <c r="B8" s="15">
-        <v>2</v>
-      </c>
-      <c r="C8" s="29" t="s">
+      <c r="E10" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F10" s="59"/>
+      <c r="G10" s="85" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H10" s="59"/>
+      <c r="I10" s="9"/>
+    </row>
+    <row r="11" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="B11" s="10">
+        <v>4</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>289</v>
+      </c>
+      <c r="D11" s="25" t="s">
         <v>322</v>
       </c>
-      <c r="D8" s="35" t="s">
+      <c r="E11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F11" s="59"/>
+      <c r="G11" s="85" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H11" s="59"/>
+      <c r="I11" s="9"/>
+    </row>
+    <row r="12" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="B12" s="10">
+        <v>5</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>290</v>
+      </c>
+      <c r="D12" s="25" t="s">
         <v>323</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F8" s="86"/>
-      <c r="G8" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H8" s="86"/>
-      <c r="I8" s="11"/>
-    </row>
-    <row r="9" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B9" s="15">
-        <v>3</v>
-      </c>
-      <c r="C9" s="29" t="s">
-        <v>301</v>
-      </c>
-      <c r="D9" s="35" t="s">
-        <v>337</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="F9" s="86"/>
-      <c r="G9" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H9" s="86"/>
-      <c r="I9" s="11"/>
-    </row>
-    <row r="10" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
-      <c r="B10" s="15">
-        <v>4</v>
-      </c>
-      <c r="C10" s="29" t="s">
-        <v>302</v>
-      </c>
-      <c r="D10" s="35" t="s">
-        <v>338</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F10" s="86"/>
-      <c r="G10" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H10" s="86"/>
-      <c r="I10" s="11"/>
-    </row>
-    <row r="11" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B11" s="15">
+      <c r="E12" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F12" s="59"/>
+      <c r="G12" s="85" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H12" s="59"/>
+      <c r="I12" s="9"/>
+    </row>
+    <row r="13" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="B13" s="10">
+        <v>6</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>297</v>
+      </c>
+      <c r="D13" s="25" t="s">
+        <v>324</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="F13" s="59"/>
+      <c r="G13" s="85" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H13" s="59"/>
+      <c r="I13" s="9"/>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B14" s="10">
+        <v>7</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>304</v>
+      </c>
+      <c r="D14" s="25" t="s">
+        <v>305</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="F14" s="59"/>
+      <c r="G14" s="85" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H14" s="59"/>
+      <c r="I14" s="9"/>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B15" s="10">
+        <v>8</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>310</v>
+      </c>
+      <c r="D15" s="25" t="s">
+        <v>311</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="F15" s="59"/>
+      <c r="G15" s="85" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H15" s="59"/>
+      <c r="I15" s="9"/>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B16" s="10">
+        <v>9</v>
+      </c>
+      <c r="C16" s="19"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="59"/>
+      <c r="G16" s="85" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H16" s="59"/>
+      <c r="I16" s="9"/>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B17" s="11">
+        <v>10</v>
+      </c>
+      <c r="C17" s="20"/>
+      <c r="D17" s="31"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="39"/>
+      <c r="G17" s="86" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H17" s="39"/>
+      <c r="I17" s="7"/>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H18" s="50" t="s">
+        <v>277</v>
+      </c>
+      <c r="I18" s="37">
+        <f>AVERAGE(I7:I17)</f>
         <v>5</v>
       </c>
-      <c r="C11" s="29" t="s">
-        <v>303</v>
-      </c>
-      <c r="D11" s="35" t="s">
-        <v>339</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F11" s="86"/>
-      <c r="G11" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H11" s="86"/>
-      <c r="I11" s="11"/>
-    </row>
-    <row r="12" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B12" s="15">
-        <v>6</v>
-      </c>
-      <c r="C12" s="29" t="s">
-        <v>310</v>
-      </c>
-      <c r="D12" s="35" t="s">
-        <v>340</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="F12" s="86"/>
-      <c r="G12" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H12" s="86"/>
-      <c r="I12" s="11"/>
-    </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B13" s="15">
-        <v>7</v>
-      </c>
-      <c r="C13" s="29" t="s">
-        <v>318</v>
-      </c>
-      <c r="D13" s="35" t="s">
-        <v>319</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="F13" s="86"/>
-      <c r="G13" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H13" s="86"/>
-      <c r="I13" s="11"/>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B14" s="15">
-        <v>8</v>
-      </c>
-      <c r="C14" s="29" t="s">
-        <v>324</v>
-      </c>
-      <c r="D14" s="35" t="s">
-        <v>325</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="F14" s="86"/>
-      <c r="G14" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H14" s="86"/>
-      <c r="I14" s="11"/>
-    </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B15" s="15">
-        <v>9</v>
-      </c>
-      <c r="C15" s="29"/>
-      <c r="D15" s="35"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="86"/>
-      <c r="G15" s="119" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H15" s="86"/>
-      <c r="I15" s="11"/>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B16" s="16">
-        <v>10</v>
-      </c>
-      <c r="C16" s="30"/>
-      <c r="D16" s="41"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="55"/>
-      <c r="G16" s="120" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H16" s="55"/>
-      <c r="I16" s="9"/>
-    </row>
-    <row r="17" spans="8:9" x14ac:dyDescent="0.3">
-      <c r="H17" s="76" t="s">
-        <v>290</v>
-      </c>
-      <c r="I17" s="47">
-        <f>AVERAGE(I6:I16)</f>
-        <v>5</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="B3:I3"/>
     <mergeCell ref="B2:I2"/>
-    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="F6:G6"/>
+    <mergeCell ref="B4:I5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -7133,7 +7288,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B1" s="24"/>
+      <c r="B1" s="16"/>
     </row>
     <row r="2" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B2" s="1" t="s">
@@ -7141,12 +7296,12 @@
       </c>
     </row>
     <row r="3" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="14" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B4" s="22" t="s">
+      <c r="B4" s="15" t="s">
         <v>25</v>
       </c>
     </row>

--- a/file/table/DAPC_ProyectoCAD.xlsx
+++ b/file/table/DAPC_ProyectoCAD.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6CE7CF0-B114-4A91-B3E9-9A3395291C17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECA9298B-9461-449A-9123-D424DFBEAB93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -131,20 +131,6 @@
       </text>
     </comment>
     <comment ref="F6" authorId="0" shapeId="0" xr:uid="{85292CD4-4682-4AA7-84E2-85458BBE80E0}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Segoe UI Light"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Actividad de referencia en curso DAPC.
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="F91" authorId="0" shapeId="0" xr:uid="{58FB072B-AFAB-4EFA-BE22-BCCEF0C50642}">
       <text>
         <r>
           <rPr>
@@ -282,7 +268,7 @@
     <author>Test</author>
   </authors>
   <commentList>
-    <comment ref="F6" authorId="0" shapeId="0" xr:uid="{634A2F11-6BC0-4DF5-92C2-329F8A975203}">
+    <comment ref="E6" authorId="0" shapeId="0" xr:uid="{634A2F11-6BC0-4DF5-92C2-329F8A975203}">
       <text>
         <r>
           <rPr>
@@ -323,7 +309,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="345">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="347">
   <si>
     <t>1. Especificaciones técnicas generales</t>
   </si>
@@ -413,9 +399,6 @@
   </si>
   <si>
     <t>Nombre alumno</t>
-  </si>
-  <si>
-    <t>v.20250723</t>
   </si>
   <si>
     <t>/file/cad/Logotipo.dwg</t>
@@ -1323,29 +1306,10 @@
     </r>
   </si>
   <si>
-    <r>
-      <t>Otros instructor</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <rFont val="Segoe UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (participación en clase, dedicación, calidad del proyecto)</t>
-    </r>
-  </si>
-  <si>
     <t>Utilizando las especificaciones del Reglamento Técnico de Instalaciones Eléctricas - RETIE del Ministerio de Minas y Energía de Colombia, dibuje la acometida eléctrica. Dibujar en planta y en cortes. Esquema solo en planta. Conexión desde poste o subterránea desde lindero de entrada al predio en uno de los laterales.</t>
   </si>
   <si>
     <t>/file/cad/DAPC.dwg</t>
-  </si>
-  <si>
-    <t>Plano digital del proyecto</t>
-  </si>
-  <si>
-    <t>Generados a partir de layouts e integrados en un único archivo de Acrobat .pdf.</t>
   </si>
   <si>
     <t>/file/report/DAPC_Planos.pdf</t>
@@ -1459,9 +1423,6 @@
     <t>2e. Elementos estructurales</t>
   </si>
   <si>
-    <t>2d. Tabla de áreas (resumen a incluir en planos)</t>
-  </si>
-  <si>
     <t>2f. Cuadro de cantidades (resumen a incluir en planos, no es necesario realizar costos unitarios)</t>
   </si>
   <si>
@@ -1520,6 +1481,37 @@
   </si>
   <si>
     <t>0. Grupos, integrantes y resúmen de calificaciones</t>
+  </si>
+  <si>
+    <t>M01A02b</t>
+  </si>
+  <si>
+    <t>M01A02c</t>
+  </si>
+  <si>
+    <t>Planos digitales del proyecto</t>
+  </si>
+  <si>
+    <t>Generados a partir de layouts e integrados en un único archivo de Acrobat .pdf: Plano de planta general, Plano de cubiertas y fachadas, Plano de corte longitudinal, Plano de corte transversal, Planos de redes (Red eléctrica interna 110v. Red eléctrica interna 220v, Red de datos usando cableado, Red foto-voltáica, Red vigilancia. En los planos arquitectónicos y eléctricos incluir el detalle de la acometída eléctrica, para rayos, polo a tierra, tomacorrientes, interruptores, luminarias, cámaras de vigilancia.)</t>
+  </si>
+  <si>
+    <t>2g. Tabla de áreas (resumen a incluir en planos)</t>
+  </si>
+  <si>
+    <r>
+      <t>Otros instructor</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <rFont val="Segoe UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (participación en clase, dedicación, calidad y organización del proyecto)</t>
+    </r>
+  </si>
+  <si>
+    <t>v.20250725</t>
   </si>
 </sst>
 </file>
@@ -2109,7 +2101,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="189">
+  <cellXfs count="183">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2124,9 +2116,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -2134,15 +2123,6 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2162,12 +2142,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2235,6 +2209,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2600,9 +2580,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -2673,9 +2650,6 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -2684,8 +2658,8 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -3004,421 +2978,421 @@
   <dimension ref="B1:E41"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="2.5546875" style="51" customWidth="1"/>
-    <col min="3" max="3" width="50.77734375" style="51" customWidth="1"/>
-    <col min="4" max="4" width="15.77734375" style="51" customWidth="1"/>
-    <col min="5" max="5" width="12.77734375" style="51" customWidth="1"/>
-    <col min="6" max="6" width="2.5546875" style="51" customWidth="1"/>
-    <col min="7" max="16384" width="9.109375" style="51"/>
+    <col min="1" max="2" width="2.5546875" style="47" customWidth="1"/>
+    <col min="3" max="3" width="50.77734375" style="47" customWidth="1"/>
+    <col min="4" max="4" width="15.77734375" style="47" customWidth="1"/>
+    <col min="5" max="5" width="12.77734375" style="47" customWidth="1"/>
+    <col min="6" max="6" width="2.5546875" style="47" customWidth="1"/>
+    <col min="7" max="16384" width="9.109375" style="47"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="E1" s="104" t="s">
-        <v>30</v>
+      <c r="E1" s="100" t="s">
+        <v>346</v>
       </c>
     </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B2" s="51" t="s">
+      <c r="B2" s="47" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B3" s="105" t="s">
-        <v>344</v>
+      <c r="B3" s="101" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B4" s="106" t="s">
-        <v>36</v>
-      </c>
-      <c r="C4" s="106"/>
-      <c r="D4" s="106"/>
-      <c r="E4" s="106"/>
+      <c r="B4" s="102" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" s="102"/>
+      <c r="D4" s="102"/>
+      <c r="E4" s="102"/>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B5" s="106"/>
-      <c r="C5" s="106"/>
-      <c r="D5" s="106"/>
-      <c r="E5" s="106"/>
+      <c r="B5" s="102"/>
+      <c r="C5" s="102"/>
+      <c r="D5" s="102"/>
+      <c r="E5" s="102"/>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B6" s="106"/>
-      <c r="C6" s="106"/>
-      <c r="D6" s="106"/>
-      <c r="E6" s="106"/>
+      <c r="B6" s="102"/>
+      <c r="C6" s="102"/>
+      <c r="D6" s="102"/>
+      <c r="E6" s="102"/>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B7" s="107" t="s">
+      <c r="B7" s="103" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="108"/>
-      <c r="D7" s="108"/>
-      <c r="E7" s="109"/>
+      <c r="C7" s="104"/>
+      <c r="D7" s="104"/>
+      <c r="E7" s="105"/>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="70" t="s">
+      <c r="B8" s="66" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="71"/>
-      <c r="D8" s="71"/>
-      <c r="E8" s="72"/>
+      <c r="C8" s="67"/>
+      <c r="D8" s="67"/>
+      <c r="E8" s="68"/>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="110" t="s">
+      <c r="B9" s="106" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="111"/>
-      <c r="D9" s="111"/>
-      <c r="E9" s="112"/>
+      <c r="C9" s="107"/>
+      <c r="D9" s="107"/>
+      <c r="E9" s="108"/>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="70" t="s">
+      <c r="B10" s="66" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="71"/>
-      <c r="D10" s="71"/>
-      <c r="E10" s="72"/>
+      <c r="C10" s="67"/>
+      <c r="D10" s="67"/>
+      <c r="E10" s="68"/>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B11" s="73"/>
-      <c r="C11" s="74"/>
-      <c r="D11" s="74"/>
-      <c r="E11" s="75"/>
+      <c r="B11" s="69"/>
+      <c r="C11" s="70"/>
+      <c r="D11" s="70"/>
+      <c r="E11" s="71"/>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B12" s="110" t="s">
+      <c r="B12" s="106" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="111"/>
-      <c r="D12" s="111"/>
-      <c r="E12" s="112"/>
+      <c r="C12" s="107"/>
+      <c r="D12" s="107"/>
+      <c r="E12" s="108"/>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="70" t="s">
+      <c r="B13" s="66" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="71"/>
-      <c r="D13" s="71"/>
-      <c r="E13" s="72"/>
+      <c r="C13" s="67"/>
+      <c r="D13" s="67"/>
+      <c r="E13" s="68"/>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B14" s="73"/>
-      <c r="C14" s="74"/>
-      <c r="D14" s="74"/>
-      <c r="E14" s="75"/>
+      <c r="B14" s="69"/>
+      <c r="C14" s="70"/>
+      <c r="D14" s="70"/>
+      <c r="E14" s="71"/>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B15" s="113" t="s">
+      <c r="B15" s="109" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="113"/>
-      <c r="D15" s="113"/>
-      <c r="E15" s="113"/>
+      <c r="C15" s="109"/>
+      <c r="D15" s="109"/>
+      <c r="E15" s="109"/>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B16" s="114"/>
-      <c r="C16" s="114"/>
-      <c r="D16" s="114"/>
-      <c r="E16" s="114"/>
+      <c r="B16" s="110"/>
+      <c r="C16" s="110"/>
+      <c r="D16" s="110"/>
+      <c r="E16" s="110"/>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B17" s="77" t="s">
+      <c r="B17" s="73" t="s">
         <v>14</v>
       </c>
-      <c r="C17" s="77"/>
-      <c r="D17" s="77"/>
-      <c r="E17" s="77"/>
+      <c r="C17" s="73"/>
+      <c r="D17" s="73"/>
+      <c r="E17" s="73"/>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B18" s="52" t="s">
+      <c r="B18" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="115" t="s">
+      <c r="C18" s="111" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="116" t="s">
+      <c r="D18" s="112" t="s">
         <v>28</v>
       </c>
-      <c r="E18" s="53" t="s">
+      <c r="E18" s="49" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B19" s="117">
+      <c r="B19" s="113">
         <v>1</v>
       </c>
-      <c r="C19" s="40" t="s">
+      <c r="C19" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="D19" s="17" t="s">
+      <c r="D19" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="E19" s="118">
+      <c r="E19" s="114">
         <f t="shared" ref="E19:E28" si="0">IFERROR(RIGHT(D19,1)*1,0)</f>
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="117">
+      <c r="B20" s="113">
         <v>2</v>
       </c>
-      <c r="C20" s="40" t="s">
+      <c r="C20" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="D20" s="17" t="s">
+      <c r="D20" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="E20" s="118">
+      <c r="E20" s="114">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B21" s="117">
+      <c r="B21" s="113">
         <v>3</v>
       </c>
-      <c r="C21" s="40" t="s">
+      <c r="C21" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="D21" s="17" t="s">
+      <c r="D21" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="E21" s="118">
+      <c r="E21" s="114">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="117">
+      <c r="B22" s="113">
         <v>4</v>
       </c>
-      <c r="C22" s="40" t="s">
+      <c r="C22" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="D22" s="17" t="s">
+      <c r="D22" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="E22" s="118">
+      <c r="E22" s="114">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B23" s="117">
+      <c r="B23" s="113">
         <v>5</v>
       </c>
-      <c r="C23" s="40" t="s">
+      <c r="C23" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="D23" s="17" t="s">
+      <c r="D23" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E23" s="118">
+      <c r="E23" s="114">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B24" s="117">
+      <c r="B24" s="113">
         <v>6</v>
       </c>
-      <c r="C24" s="40" t="s">
+      <c r="C24" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="D24" s="17"/>
-      <c r="E24" s="118">
+      <c r="D24" s="13"/>
+      <c r="E24" s="114">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B25" s="117">
+      <c r="B25" s="113">
         <v>7</v>
       </c>
-      <c r="C25" s="40" t="s">
+      <c r="C25" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="D25" s="17"/>
-      <c r="E25" s="118">
+      <c r="D25" s="13"/>
+      <c r="E25" s="114">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B26" s="117">
+      <c r="B26" s="113">
         <v>8</v>
       </c>
-      <c r="C26" s="40" t="s">
+      <c r="C26" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="D26" s="17"/>
-      <c r="E26" s="118">
+      <c r="D26" s="13"/>
+      <c r="E26" s="114">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B27" s="117">
+      <c r="B27" s="113">
         <v>9</v>
       </c>
-      <c r="C27" s="40" t="s">
+      <c r="C27" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="D27" s="17"/>
-      <c r="E27" s="118">
+      <c r="D27" s="13"/>
+      <c r="E27" s="114">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B28" s="119">
+      <c r="B28" s="115">
         <v>10</v>
       </c>
-      <c r="C28" s="41" t="s">
+      <c r="C28" s="35" t="s">
         <v>8</v>
       </c>
-      <c r="D28" s="18"/>
-      <c r="E28" s="120">
+      <c r="D28" s="14"/>
+      <c r="E28" s="116">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="D29" s="121" t="s">
+      <c r="D29" s="117" t="s">
         <v>11</v>
       </c>
-      <c r="E29" s="63">
+      <c r="E29" s="59">
         <f>SUM(E19:E28)</f>
         <v>27</v>
       </c>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B31" s="77" t="s">
+      <c r="B31" s="73" t="s">
+        <v>269</v>
+      </c>
+      <c r="C31" s="73"/>
+      <c r="D31" s="73"/>
+      <c r="E31" s="73"/>
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B32" s="48" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="75" t="s">
+        <v>36</v>
+      </c>
+      <c r="D32" s="76"/>
+      <c r="E32" s="49" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B33" s="50">
+        <v>1</v>
+      </c>
+      <c r="C33" s="77" t="s">
         <v>270</v>
       </c>
-      <c r="C31" s="77"/>
-      <c r="D31" s="77"/>
-      <c r="E31" s="77"/>
-    </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B32" s="52" t="s">
-        <v>10</v>
-      </c>
-      <c r="C32" s="79" t="s">
-        <v>37</v>
-      </c>
-      <c r="D32" s="80"/>
-      <c r="E32" s="53" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B33" s="54">
-        <v>1</v>
-      </c>
-      <c r="C33" s="81" t="s">
-        <v>271</v>
-      </c>
-      <c r="D33" s="82"/>
-      <c r="E33" s="55">
+      <c r="D33" s="78"/>
+      <c r="E33" s="51">
         <f>'1.Tecnica'!I19</f>
         <v>5</v>
       </c>
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B34" s="54">
+      <c r="B34" s="50">
         <v>2</v>
       </c>
-      <c r="C34" s="66" t="s">
-        <v>314</v>
-      </c>
-      <c r="D34" s="67"/>
-      <c r="E34" s="55">
-        <f>'2.ArquitectonicaEstructural'!I103</f>
+      <c r="C34" s="62" t="s">
+        <v>310</v>
+      </c>
+      <c r="D34" s="63"/>
+      <c r="E34" s="51">
+        <f>'1.Tecnica'!I19</f>
         <v>5</v>
       </c>
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B35" s="54">
+      <c r="B35" s="50">
         <v>3</v>
       </c>
-      <c r="C35" s="66" t="s">
-        <v>272</v>
-      </c>
-      <c r="D35" s="67"/>
-      <c r="E35" s="55">
+      <c r="C35" s="62" t="s">
+        <v>271</v>
+      </c>
+      <c r="D35" s="63"/>
+      <c r="E35" s="51">
         <f>'3.Electrica'!I28</f>
         <v>5</v>
       </c>
     </row>
     <row r="36" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B36" s="54">
+      <c r="B36" s="50">
         <v>4</v>
       </c>
-      <c r="C36" s="64" t="s">
-        <v>313</v>
-      </c>
-      <c r="D36" s="65"/>
-      <c r="E36" s="55">
-        <f>'4.Bodegaje'!I24</f>
+      <c r="C36" s="60" t="s">
+        <v>309</v>
+      </c>
+      <c r="D36" s="61"/>
+      <c r="E36" s="51">
+        <f>'4.Bodegaje'!I23</f>
         <v>5</v>
       </c>
     </row>
     <row r="37" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B37" s="54">
+      <c r="B37" s="50">
         <v>4</v>
       </c>
-      <c r="C37" s="66" t="s">
-        <v>273</v>
-      </c>
-      <c r="D37" s="67"/>
-      <c r="E37" s="55">
+      <c r="C37" s="62" t="s">
+        <v>272</v>
+      </c>
+      <c r="D37" s="63"/>
+      <c r="E37" s="51">
         <f>'5.Planos'!I17</f>
         <v>5</v>
       </c>
     </row>
     <row r="38" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B38" s="54">
+      <c r="B38" s="50">
         <v>5</v>
       </c>
-      <c r="C38" s="66" t="s">
-        <v>274</v>
-      </c>
-      <c r="D38" s="67"/>
-      <c r="E38" s="55">
-        <f>'6.Archivos'!I18</f>
+      <c r="C38" s="62" t="s">
+        <v>273</v>
+      </c>
+      <c r="D38" s="63"/>
+      <c r="E38" s="51">
+        <f>'6.Archivos'!H17</f>
         <v>5</v>
       </c>
     </row>
     <row r="39" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B39" s="54">
+      <c r="B39" s="50">
         <v>6</v>
       </c>
-      <c r="C39" s="66" t="s">
-        <v>300</v>
-      </c>
-      <c r="D39" s="67"/>
-      <c r="E39" s="103">
+      <c r="C39" s="62" t="s">
+        <v>299</v>
+      </c>
+      <c r="D39" s="63"/>
+      <c r="E39" s="99">
         <v>5</v>
       </c>
     </row>
     <row r="40" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B40" s="56">
+      <c r="B40" s="52">
         <v>7</v>
       </c>
-      <c r="C40" s="68" t="s">
-        <v>301</v>
-      </c>
-      <c r="D40" s="69"/>
-      <c r="E40" s="62">
+      <c r="C40" s="64" t="s">
+        <v>345</v>
+      </c>
+      <c r="D40" s="65"/>
+      <c r="E40" s="58">
         <v>5</v>
       </c>
     </row>
     <row r="41" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="D41" s="122" t="s">
-        <v>277</v>
-      </c>
-      <c r="E41" s="63">
+      <c r="D41" s="118" t="s">
+        <v>276</v>
+      </c>
+      <c r="E41" s="59">
         <f>AVERAGE(E33:E40)</f>
         <v>5</v>
       </c>
@@ -3445,6 +3419,9 @@
     <mergeCell ref="C37:D37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="D19:D28" numberStoredAsText="1"/>
+  </ignoredErrors>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
@@ -3454,331 +3431,332 @@
   <dimension ref="B1:I19"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.5546875" style="51" customWidth="1"/>
-    <col min="2" max="2" width="30.77734375" style="51" customWidth="1"/>
-    <col min="3" max="3" width="50.77734375" style="51" customWidth="1"/>
-    <col min="4" max="5" width="10.77734375" style="51" customWidth="1"/>
-    <col min="6" max="6" width="7.77734375" style="51" customWidth="1"/>
-    <col min="7" max="7" width="3.77734375" style="51" customWidth="1"/>
-    <col min="8" max="8" width="30.77734375" style="123" customWidth="1"/>
-    <col min="9" max="9" width="12.77734375" style="124" customWidth="1"/>
-    <col min="10" max="16384" width="9.109375" style="51"/>
+    <col min="1" max="1" width="2.5546875" style="47" customWidth="1"/>
+    <col min="2" max="2" width="30.77734375" style="47" customWidth="1"/>
+    <col min="3" max="3" width="50.77734375" style="47" customWidth="1"/>
+    <col min="4" max="5" width="10.77734375" style="47" customWidth="1"/>
+    <col min="6" max="6" width="7.77734375" style="47" customWidth="1"/>
+    <col min="7" max="7" width="3.77734375" style="47" customWidth="1"/>
+    <col min="8" max="8" width="30.77734375" style="119" customWidth="1"/>
+    <col min="9" max="9" width="12.77734375" style="120" customWidth="1"/>
+    <col min="10" max="10" width="2.77734375" style="47" customWidth="1"/>
+    <col min="11" max="16384" width="9.109375" style="47"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="E1" s="104"/>
+      <c r="E1" s="100"/>
     </row>
     <row r="2" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B2" s="51" t="s">
+      <c r="B2" s="47" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B3" s="105" t="s">
+      <c r="B3" s="101" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B4" s="106" t="s">
+      <c r="B4" s="102" t="s">
+        <v>274</v>
+      </c>
+      <c r="C4" s="102"/>
+      <c r="D4" s="102"/>
+      <c r="E4" s="102"/>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B5" s="102"/>
+      <c r="C5" s="102"/>
+      <c r="D5" s="102"/>
+      <c r="E5" s="102"/>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B6" s="121" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="122" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="123" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" s="123" t="s">
+        <v>49</v>
+      </c>
+      <c r="F6" s="124" t="s">
+        <v>38</v>
+      </c>
+      <c r="G6" s="125"/>
+      <c r="H6" s="122" t="s">
+        <v>26</v>
+      </c>
+      <c r="I6" s="126" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="B7" s="127" t="s">
         <v>275</v>
       </c>
-      <c r="C4" s="106"/>
-      <c r="D4" s="106"/>
-      <c r="E4" s="106"/>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B5" s="106"/>
-      <c r="C5" s="106"/>
-      <c r="D5" s="106"/>
-      <c r="E5" s="106"/>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B6" s="125" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6" s="126" t="s">
-        <v>38</v>
-      </c>
-      <c r="D6" s="127" t="s">
-        <v>49</v>
-      </c>
-      <c r="E6" s="127" t="s">
-        <v>50</v>
-      </c>
-      <c r="F6" s="128" t="s">
-        <v>39</v>
-      </c>
-      <c r="G6" s="129"/>
-      <c r="H6" s="126" t="s">
-        <v>26</v>
-      </c>
-      <c r="I6" s="130" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
-      <c r="B7" s="131" t="s">
+      <c r="C7" s="128" t="s">
+        <v>298</v>
+      </c>
+      <c r="D7" s="91">
+        <v>1</v>
+      </c>
+      <c r="E7" s="130" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="131" t="s">
+        <v>311</v>
+      </c>
+      <c r="G7" s="132" t="str">
+        <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F7,"/Readme.md"),"Ver")</f>
+        <v>Ver</v>
+      </c>
+      <c r="H7" s="93"/>
+      <c r="I7" s="94">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="B8" s="127" t="s">
+        <v>279</v>
+      </c>
+      <c r="C8" s="128" t="s">
+        <v>321</v>
+      </c>
+      <c r="D8" s="91">
+        <v>1</v>
+      </c>
+      <c r="E8" s="130" t="s">
+        <v>322</v>
+      </c>
+      <c r="F8" s="131" t="s">
+        <v>311</v>
+      </c>
+      <c r="G8" s="132" t="str">
+        <f t="shared" ref="G8:G18" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F8,"/Readme.md"),"Ver")</f>
+        <v>Ver</v>
+      </c>
+      <c r="H8" s="93"/>
+      <c r="I8" s="94"/>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B9" s="127" t="s">
+        <v>277</v>
+      </c>
+      <c r="C9" s="128" t="s">
+        <v>278</v>
+      </c>
+      <c r="D9" s="91" t="s">
+        <v>323</v>
+      </c>
+      <c r="E9" s="130"/>
+      <c r="F9" s="131" t="s">
+        <v>311</v>
+      </c>
+      <c r="G9" s="132" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H9" s="93"/>
+      <c r="I9" s="94"/>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B10" s="127" t="s">
+        <v>281</v>
+      </c>
+      <c r="C10" s="128" t="s">
+        <v>282</v>
+      </c>
+      <c r="D10" s="91">
+        <v>1</v>
+      </c>
+      <c r="E10" s="130" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" s="131" t="s">
+        <v>312</v>
+      </c>
+      <c r="G10" s="132" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H10" s="93"/>
+      <c r="I10" s="94"/>
+    </row>
+    <row r="11" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="B11" s="127" t="s">
+        <v>280</v>
+      </c>
+      <c r="C11" s="128" t="s">
+        <v>283</v>
+      </c>
+      <c r="D11" s="91" t="s">
+        <v>323</v>
+      </c>
+      <c r="E11" s="130"/>
+      <c r="F11" s="131" t="s">
+        <v>313</v>
+      </c>
+      <c r="G11" s="132" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H11" s="93"/>
+      <c r="I11" s="94"/>
+    </row>
+    <row r="12" spans="2:9" ht="57" x14ac:dyDescent="0.3">
+      <c r="B12" s="127" t="s">
+        <v>290</v>
+      </c>
+      <c r="C12" s="128" t="s">
+        <v>284</v>
+      </c>
+      <c r="D12" s="91" t="s">
+        <v>323</v>
+      </c>
+      <c r="E12" s="130"/>
+      <c r="F12" s="131" t="s">
+        <v>314</v>
+      </c>
+      <c r="G12" s="132" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H12" s="93"/>
+      <c r="I12" s="94"/>
+    </row>
+    <row r="13" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="B13" s="127" t="s">
+        <v>291</v>
+      </c>
+      <c r="C13" s="128" t="s">
+        <v>285</v>
+      </c>
+      <c r="D13" s="91" t="s">
+        <v>323</v>
+      </c>
+      <c r="E13" s="130"/>
+      <c r="F13" s="131" t="s">
+        <v>315</v>
+      </c>
+      <c r="G13" s="132" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H13" s="93"/>
+      <c r="I13" s="94"/>
+    </row>
+    <row r="14" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="B14" s="127" t="s">
+        <v>292</v>
+      </c>
+      <c r="C14" s="128" t="s">
+        <v>286</v>
+      </c>
+      <c r="D14" s="91" t="s">
+        <v>323</v>
+      </c>
+      <c r="E14" s="130"/>
+      <c r="F14" s="131" t="s">
+        <v>312</v>
+      </c>
+      <c r="G14" s="132" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H14" s="93"/>
+      <c r="I14" s="94"/>
+    </row>
+    <row r="15" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="B15" s="127" t="s">
+        <v>287</v>
+      </c>
+      <c r="C15" s="128" t="s">
+        <v>293</v>
+      </c>
+      <c r="D15" s="91">
+        <v>1</v>
+      </c>
+      <c r="E15" s="130" t="s">
+        <v>16</v>
+      </c>
+      <c r="F15" s="131" t="s">
+        <v>316</v>
+      </c>
+      <c r="G15" s="132" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H15" s="93"/>
+      <c r="I15" s="94"/>
+    </row>
+    <row r="16" spans="2:9" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="127" t="s">
+        <v>288</v>
+      </c>
+      <c r="C16" s="128" t="s">
+        <v>294</v>
+      </c>
+      <c r="D16" s="91">
+        <v>1</v>
+      </c>
+      <c r="E16" s="130" t="s">
+        <v>16</v>
+      </c>
+      <c r="F16" s="131" t="s">
+        <v>316</v>
+      </c>
+      <c r="G16" s="132" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H16" s="93"/>
+      <c r="I16" s="94"/>
+    </row>
+    <row r="17" spans="2:9" ht="35.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="134" t="s">
+        <v>289</v>
+      </c>
+      <c r="C17" s="135" t="s">
+        <v>295</v>
+      </c>
+      <c r="D17" s="91">
+        <v>1</v>
+      </c>
+      <c r="E17" s="130" t="s">
+        <v>16</v>
+      </c>
+      <c r="F17" s="131" t="s">
+        <v>316</v>
+      </c>
+      <c r="G17" s="132" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H17" s="95"/>
+      <c r="I17" s="96"/>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B18" s="136"/>
+      <c r="C18" s="137"/>
+      <c r="D18" s="92"/>
+      <c r="E18" s="138"/>
+      <c r="F18" s="139"/>
+      <c r="G18" s="140" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H18" s="97"/>
+      <c r="I18" s="98"/>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H19" s="141" t="s">
         <v>276</v>
       </c>
-      <c r="C7" s="132" t="s">
-        <v>299</v>
-      </c>
-      <c r="D7" s="95">
-        <v>1</v>
-      </c>
-      <c r="E7" s="134" t="s">
-        <v>16</v>
-      </c>
-      <c r="F7" s="135" t="s">
-        <v>315</v>
-      </c>
-      <c r="G7" s="136" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F7,"/Readme.md"),"Ver")</f>
-        <v>Ver</v>
-      </c>
-      <c r="H7" s="97"/>
-      <c r="I7" s="98">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B8" s="131" t="s">
-        <v>280</v>
-      </c>
-      <c r="C8" s="132" t="s">
-        <v>325</v>
-      </c>
-      <c r="D8" s="95">
-        <v>1</v>
-      </c>
-      <c r="E8" s="134" t="s">
-        <v>326</v>
-      </c>
-      <c r="F8" s="135" t="s">
-        <v>315</v>
-      </c>
-      <c r="G8" s="136" t="str">
-        <f t="shared" ref="G8:G18" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F8,"/Readme.md"),"Ver")</f>
-        <v>Ver</v>
-      </c>
-      <c r="H8" s="97"/>
-      <c r="I8" s="98"/>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B9" s="131" t="s">
-        <v>278</v>
-      </c>
-      <c r="C9" s="132" t="s">
-        <v>279</v>
-      </c>
-      <c r="D9" s="95" t="s">
-        <v>327</v>
-      </c>
-      <c r="E9" s="134"/>
-      <c r="F9" s="135" t="s">
-        <v>315</v>
-      </c>
-      <c r="G9" s="136" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H9" s="97"/>
-      <c r="I9" s="98"/>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B10" s="131" t="s">
-        <v>282</v>
-      </c>
-      <c r="C10" s="132" t="s">
-        <v>283</v>
-      </c>
-      <c r="D10" s="95">
-        <v>1</v>
-      </c>
-      <c r="E10" s="134" t="s">
-        <v>16</v>
-      </c>
-      <c r="F10" s="135" t="s">
-        <v>316</v>
-      </c>
-      <c r="G10" s="136" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H10" s="97"/>
-      <c r="I10" s="98"/>
-    </row>
-    <row r="11" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="B11" s="131" t="s">
-        <v>281</v>
-      </c>
-      <c r="C11" s="132" t="s">
-        <v>284</v>
-      </c>
-      <c r="D11" s="95" t="s">
-        <v>327</v>
-      </c>
-      <c r="E11" s="134"/>
-      <c r="F11" s="135" t="s">
-        <v>317</v>
-      </c>
-      <c r="G11" s="136" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H11" s="97"/>
-      <c r="I11" s="98"/>
-    </row>
-    <row r="12" spans="2:9" ht="57" x14ac:dyDescent="0.3">
-      <c r="B12" s="131" t="s">
-        <v>291</v>
-      </c>
-      <c r="C12" s="132" t="s">
-        <v>285</v>
-      </c>
-      <c r="D12" s="95" t="s">
-        <v>327</v>
-      </c>
-      <c r="E12" s="134"/>
-      <c r="F12" s="135" t="s">
-        <v>318</v>
-      </c>
-      <c r="G12" s="136" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H12" s="97"/>
-      <c r="I12" s="98"/>
-    </row>
-    <row r="13" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B13" s="131" t="s">
-        <v>292</v>
-      </c>
-      <c r="C13" s="132" t="s">
-        <v>286</v>
-      </c>
-      <c r="D13" s="95" t="s">
-        <v>327</v>
-      </c>
-      <c r="E13" s="134"/>
-      <c r="F13" s="135" t="s">
-        <v>319</v>
-      </c>
-      <c r="G13" s="136" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H13" s="97"/>
-      <c r="I13" s="98"/>
-    </row>
-    <row r="14" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="B14" s="131" t="s">
-        <v>293</v>
-      </c>
-      <c r="C14" s="132" t="s">
-        <v>287</v>
-      </c>
-      <c r="D14" s="95" t="s">
-        <v>327</v>
-      </c>
-      <c r="E14" s="134"/>
-      <c r="F14" s="135" t="s">
-        <v>316</v>
-      </c>
-      <c r="G14" s="136" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H14" s="97"/>
-      <c r="I14" s="98"/>
-    </row>
-    <row r="15" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
-      <c r="B15" s="131" t="s">
-        <v>288</v>
-      </c>
-      <c r="C15" s="132" t="s">
-        <v>294</v>
-      </c>
-      <c r="D15" s="95">
-        <v>1</v>
-      </c>
-      <c r="E15" s="134" t="s">
-        <v>16</v>
-      </c>
-      <c r="F15" s="135" t="s">
-        <v>320</v>
-      </c>
-      <c r="G15" s="136" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H15" s="97"/>
-      <c r="I15" s="98"/>
-    </row>
-    <row r="16" spans="2:9" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="131" t="s">
-        <v>289</v>
-      </c>
-      <c r="C16" s="132" t="s">
-        <v>295</v>
-      </c>
-      <c r="D16" s="95">
-        <v>1</v>
-      </c>
-      <c r="E16" s="134" t="s">
-        <v>16</v>
-      </c>
-      <c r="F16" s="135" t="s">
-        <v>320</v>
-      </c>
-      <c r="G16" s="136" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H16" s="97"/>
-      <c r="I16" s="98"/>
-    </row>
-    <row r="17" spans="2:9" ht="35.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="138" t="s">
-        <v>290</v>
-      </c>
-      <c r="C17" s="139" t="s">
-        <v>296</v>
-      </c>
-      <c r="D17" s="95">
-        <v>1</v>
-      </c>
-      <c r="E17" s="134" t="s">
-        <v>16</v>
-      </c>
-      <c r="F17" s="135" t="s">
-        <v>320</v>
-      </c>
-      <c r="G17" s="136" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H17" s="99"/>
-      <c r="I17" s="100"/>
-    </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B18" s="140"/>
-      <c r="C18" s="141"/>
-      <c r="D18" s="96"/>
-      <c r="E18" s="142"/>
-      <c r="F18" s="143"/>
-      <c r="G18" s="144" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H18" s="101"/>
-      <c r="I18" s="102"/>
-    </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="H19" s="145" t="s">
-        <v>277</v>
-      </c>
-      <c r="I19" s="124">
+      <c r="I19" s="120">
         <f>AVERAGE(I7:I18)</f>
         <v>5</v>
       </c>
@@ -3796,1945 +3774,1997 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1EE59D4-4937-4491-BD3F-7DBC007EDF85}">
-  <dimension ref="B2:I113"/>
+  <dimension ref="B2:I100"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.5546875" style="51" customWidth="1"/>
-    <col min="2" max="2" width="30.77734375" style="51" customWidth="1"/>
-    <col min="3" max="3" width="50.77734375" style="51" customWidth="1"/>
-    <col min="4" max="5" width="10.77734375" style="124" customWidth="1"/>
-    <col min="6" max="6" width="7.77734375" style="146" customWidth="1"/>
-    <col min="7" max="7" width="3.77734375" style="124" customWidth="1"/>
-    <col min="8" max="8" width="30.77734375" style="123" customWidth="1"/>
-    <col min="9" max="9" width="12.77734375" style="124" customWidth="1"/>
-    <col min="10" max="10" width="2.5546875" style="51" customWidth="1"/>
-    <col min="11" max="16384" width="9.109375" style="51"/>
+    <col min="1" max="1" width="2.5546875" style="47" customWidth="1"/>
+    <col min="2" max="2" width="30.77734375" style="47" customWidth="1"/>
+    <col min="3" max="3" width="50.77734375" style="47" customWidth="1"/>
+    <col min="4" max="5" width="10.77734375" style="120" customWidth="1"/>
+    <col min="6" max="6" width="7.77734375" style="142" customWidth="1"/>
+    <col min="7" max="7" width="3.77734375" style="120" customWidth="1"/>
+    <col min="8" max="8" width="30.77734375" style="119" customWidth="1"/>
+    <col min="9" max="9" width="12.77734375" style="120" customWidth="1"/>
+    <col min="10" max="10" width="2.5546875" style="47" customWidth="1"/>
+    <col min="11" max="16384" width="9.109375" style="47"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B2" s="51" t="s">
+      <c r="B2" s="47" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B3" s="105" t="s">
+      <c r="B3" s="101" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B4" s="102" t="s">
+        <v>227</v>
+      </c>
+      <c r="C4" s="102"/>
+      <c r="D4" s="102"/>
+      <c r="E4" s="102"/>
+      <c r="F4" s="102"/>
+      <c r="G4" s="102"/>
+      <c r="H4" s="102"/>
+      <c r="I4" s="102"/>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B5" s="143"/>
+      <c r="C5" s="143"/>
+      <c r="D5" s="143"/>
+      <c r="E5" s="143"/>
+      <c r="F5" s="143"/>
+      <c r="G5" s="143"/>
+      <c r="H5" s="143"/>
+      <c r="I5" s="143"/>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B6" s="121" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="122" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="123" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" s="123" t="s">
+        <v>49</v>
+      </c>
+      <c r="F6" s="144" t="s">
+        <v>38</v>
+      </c>
+      <c r="G6" s="145"/>
+      <c r="H6" s="122" t="s">
+        <v>26</v>
+      </c>
+      <c r="I6" s="126" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B7" s="146" t="s">
+        <v>325</v>
+      </c>
+      <c r="C7" s="147"/>
+      <c r="D7" s="148"/>
+      <c r="E7" s="148"/>
+      <c r="F7" s="149"/>
+      <c r="G7" s="148"/>
+      <c r="H7" s="150"/>
+      <c r="I7" s="151"/>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B8" s="127" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B4" s="106" t="s">
-        <v>228</v>
-      </c>
-      <c r="C4" s="106"/>
-      <c r="D4" s="106"/>
-      <c r="E4" s="106"/>
-      <c r="F4" s="106"/>
-      <c r="G4" s="106"/>
-      <c r="H4" s="106"/>
-      <c r="I4" s="106"/>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B5" s="147"/>
-      <c r="C5" s="147"/>
-      <c r="D5" s="147"/>
-      <c r="E5" s="147"/>
-      <c r="F5" s="147"/>
-      <c r="G5" s="147"/>
-      <c r="H5" s="147"/>
-      <c r="I5" s="147"/>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B6" s="125" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6" s="126" t="s">
-        <v>38</v>
-      </c>
-      <c r="D6" s="127" t="s">
-        <v>49</v>
-      </c>
-      <c r="E6" s="127" t="s">
-        <v>50</v>
-      </c>
-      <c r="F6" s="148" t="s">
-        <v>39</v>
-      </c>
-      <c r="G6" s="149"/>
-      <c r="H6" s="126" t="s">
-        <v>26</v>
-      </c>
-      <c r="I6" s="130" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B7" s="150" t="s">
-        <v>329</v>
-      </c>
-      <c r="C7" s="151"/>
-      <c r="D7" s="152"/>
-      <c r="E7" s="152"/>
-      <c r="F7" s="153"/>
-      <c r="G7" s="152"/>
-      <c r="H7" s="154"/>
-      <c r="I7" s="155"/>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B8" s="131" t="s">
+      <c r="C8" s="128" t="s">
+        <v>163</v>
+      </c>
+      <c r="D8" s="129">
+        <v>8</v>
+      </c>
+      <c r="E8" s="130" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" s="131" t="s">
+        <v>313</v>
+      </c>
+      <c r="G8" s="132" t="str">
+        <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F8,"/Readme.md"),"Ver")</f>
+        <v>Ver</v>
+      </c>
+      <c r="H8" s="128" t="s">
+        <v>297</v>
+      </c>
+      <c r="I8" s="133">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B9" s="127" t="s">
         <v>162</v>
       </c>
-      <c r="C8" s="132" t="s">
+      <c r="C9" s="128" t="s">
         <v>164</v>
       </c>
-      <c r="D8" s="133">
-        <v>8</v>
-      </c>
-      <c r="E8" s="134" t="s">
-        <v>54</v>
-      </c>
-      <c r="F8" s="135" t="s">
-        <v>317</v>
-      </c>
-      <c r="G8" s="136" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F8,"/Readme.md"),"Ver")</f>
-        <v>Ver</v>
-      </c>
-      <c r="H8" s="132" t="s">
-        <v>298</v>
-      </c>
-      <c r="I8" s="137">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B9" s="131" t="s">
-        <v>163</v>
-      </c>
-      <c r="C9" s="132" t="s">
+      <c r="D9" s="129">
+        <v>10</v>
+      </c>
+      <c r="E9" s="130" t="s">
+        <v>53</v>
+      </c>
+      <c r="F9" s="131" t="s">
+        <v>313</v>
+      </c>
+      <c r="G9" s="132" t="str">
+        <f t="shared" ref="G9:G72" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F9,"/Readme.md"),"Ver")</f>
+        <v>Ver</v>
+      </c>
+      <c r="H9" s="128" t="s">
+        <v>297</v>
+      </c>
+      <c r="I9" s="133"/>
+    </row>
+    <row r="10" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="B10" s="127" t="s">
+        <v>167</v>
+      </c>
+      <c r="C10" s="128" t="s">
         <v>165</v>
       </c>
-      <c r="D9" s="133">
-        <v>10</v>
-      </c>
-      <c r="E9" s="134" t="s">
-        <v>54</v>
-      </c>
-      <c r="F9" s="135" t="s">
-        <v>317</v>
-      </c>
-      <c r="G9" s="136" t="str">
-        <f t="shared" ref="G9:G72" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F9,"/Readme.md"),"Ver")</f>
-        <v>Ver</v>
-      </c>
-      <c r="H9" s="132" t="s">
-        <v>298</v>
-      </c>
-      <c r="I9" s="137"/>
-    </row>
-    <row r="10" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B10" s="131" t="s">
-        <v>168</v>
-      </c>
-      <c r="C10" s="132" t="s">
-        <v>166</v>
-      </c>
-      <c r="D10" s="134">
+      <c r="D10" s="130">
         <f>D8+SumUDig</f>
         <v>35</v>
       </c>
-      <c r="E10" s="134" t="s">
-        <v>54</v>
-      </c>
-      <c r="F10" s="135" t="s">
-        <v>317</v>
-      </c>
-      <c r="G10" s="136" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H10" s="132"/>
-      <c r="I10" s="137"/>
+      <c r="E10" s="130" t="s">
+        <v>53</v>
+      </c>
+      <c r="F10" s="131" t="s">
+        <v>313</v>
+      </c>
+      <c r="G10" s="132" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H10" s="128"/>
+      <c r="I10" s="133"/>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B11" s="131" t="s">
-        <v>169</v>
-      </c>
-      <c r="C11" s="132" t="s">
-        <v>167</v>
-      </c>
-      <c r="D11" s="134" cm="1">
+      <c r="B11" s="127" t="s">
+        <v>168</v>
+      </c>
+      <c r="C11" s="128" t="s">
+        <v>166</v>
+      </c>
+      <c r="D11" s="130" cm="1">
         <f t="array" ref="D11">D9+SumUDig</f>
         <v>37</v>
       </c>
-      <c r="E11" s="134" t="s">
-        <v>54</v>
-      </c>
-      <c r="F11" s="135" t="s">
-        <v>317</v>
-      </c>
-      <c r="G11" s="136" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H11" s="132"/>
-      <c r="I11" s="137"/>
+      <c r="E11" s="130" t="s">
+        <v>53</v>
+      </c>
+      <c r="F11" s="131" t="s">
+        <v>313</v>
+      </c>
+      <c r="G11" s="132" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H11" s="128"/>
+      <c r="I11" s="133"/>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B12" s="131" t="s">
+      <c r="B12" s="127" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="128" t="s">
+        <v>177</v>
+      </c>
+      <c r="D12" s="129">
+        <v>12</v>
+      </c>
+      <c r="E12" s="130" t="s">
+        <v>53</v>
+      </c>
+      <c r="F12" s="131" t="s">
+        <v>313</v>
+      </c>
+      <c r="G12" s="132" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H12" s="128" t="s">
+        <v>297</v>
+      </c>
+      <c r="I12" s="133"/>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B13" s="127" t="s">
+        <v>60</v>
+      </c>
+      <c r="C13" s="128" t="s">
+        <v>66</v>
+      </c>
+      <c r="D13" s="129">
+        <v>6</v>
+      </c>
+      <c r="E13" s="130" t="s">
+        <v>53</v>
+      </c>
+      <c r="F13" s="131" t="s">
+        <v>313</v>
+      </c>
+      <c r="G13" s="132" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H13" s="128" t="s">
+        <v>297</v>
+      </c>
+      <c r="I13" s="133"/>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B14" s="127" t="s">
         <v>40</v>
       </c>
-      <c r="C12" s="132" t="s">
-        <v>178</v>
-      </c>
-      <c r="D12" s="133">
+      <c r="C14" s="128" t="s">
+        <v>65</v>
+      </c>
+      <c r="D14" s="129">
         <v>12</v>
       </c>
-      <c r="E12" s="134" t="s">
-        <v>54</v>
-      </c>
-      <c r="F12" s="135" t="s">
-        <v>317</v>
-      </c>
-      <c r="G12" s="136" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H12" s="132" t="s">
-        <v>298</v>
-      </c>
-      <c r="I12" s="137"/>
-    </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B13" s="131" t="s">
+      <c r="E14" s="130" t="s">
+        <v>53</v>
+      </c>
+      <c r="F14" s="131" t="s">
+        <v>313</v>
+      </c>
+      <c r="G14" s="132" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H14" s="128" t="s">
+        <v>297</v>
+      </c>
+      <c r="I14" s="133"/>
+    </row>
+    <row r="15" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="B15" s="127" t="s">
+        <v>52</v>
+      </c>
+      <c r="C15" s="128" t="s">
         <v>61</v>
       </c>
-      <c r="C13" s="132" t="s">
-        <v>67</v>
-      </c>
-      <c r="D13" s="133">
-        <v>6</v>
-      </c>
-      <c r="E13" s="134" t="s">
-        <v>54</v>
-      </c>
-      <c r="F13" s="135" t="s">
-        <v>317</v>
-      </c>
-      <c r="G13" s="136" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H13" s="132" t="s">
-        <v>298</v>
-      </c>
-      <c r="I13" s="137"/>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B14" s="131" t="s">
-        <v>41</v>
-      </c>
-      <c r="C14" s="132" t="s">
-        <v>66</v>
-      </c>
-      <c r="D14" s="133">
-        <v>12</v>
-      </c>
-      <c r="E14" s="134" t="s">
-        <v>54</v>
-      </c>
-      <c r="F14" s="135" t="s">
-        <v>317</v>
-      </c>
-      <c r="G14" s="136" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H14" s="132" t="s">
-        <v>298</v>
-      </c>
-      <c r="I14" s="137"/>
-    </row>
-    <row r="15" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B15" s="131" t="s">
-        <v>53</v>
-      </c>
-      <c r="C15" s="132" t="s">
-        <v>62</v>
-      </c>
-      <c r="D15" s="134">
+      <c r="D15" s="130">
         <f>D10</f>
         <v>35</v>
       </c>
-      <c r="E15" s="134" t="s">
-        <v>54</v>
-      </c>
-      <c r="F15" s="135" t="s">
-        <v>317</v>
-      </c>
-      <c r="G15" s="136" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H15" s="132"/>
-      <c r="I15" s="137"/>
+      <c r="E15" s="130" t="s">
+        <v>53</v>
+      </c>
+      <c r="F15" s="131" t="s">
+        <v>313</v>
+      </c>
+      <c r="G15" s="132" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H15" s="128"/>
+      <c r="I15" s="133"/>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B16" s="131" t="s">
-        <v>52</v>
-      </c>
-      <c r="C16" s="132" t="s">
-        <v>60</v>
-      </c>
-      <c r="D16" s="134">
+      <c r="B16" s="127" t="s">
+        <v>51</v>
+      </c>
+      <c r="C16" s="128" t="s">
+        <v>59</v>
+      </c>
+      <c r="D16" s="130">
         <f>D11+D14+D13</f>
         <v>55</v>
       </c>
-      <c r="E16" s="134" t="s">
-        <v>54</v>
-      </c>
-      <c r="F16" s="135" t="s">
-        <v>317</v>
-      </c>
-      <c r="G16" s="136" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H16" s="132"/>
-      <c r="I16" s="137"/>
+      <c r="E16" s="130" t="s">
+        <v>53</v>
+      </c>
+      <c r="F16" s="131" t="s">
+        <v>313</v>
+      </c>
+      <c r="G16" s="132" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H16" s="128"/>
+      <c r="I16" s="133"/>
     </row>
     <row r="17" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B17" s="131" t="s">
-        <v>51</v>
-      </c>
-      <c r="C17" s="132" t="s">
-        <v>134</v>
-      </c>
-      <c r="D17" s="134">
+      <c r="B17" s="127" t="s">
+        <v>50</v>
+      </c>
+      <c r="C17" s="128" t="s">
+        <v>133</v>
+      </c>
+      <c r="D17" s="130">
         <f>D16*D15</f>
         <v>1925</v>
       </c>
-      <c r="E17" s="134" t="s">
-        <v>55</v>
-      </c>
-      <c r="F17" s="135" t="s">
-        <v>317</v>
-      </c>
-      <c r="G17" s="136" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H17" s="132"/>
-      <c r="I17" s="137"/>
+      <c r="E17" s="130" t="s">
+        <v>54</v>
+      </c>
+      <c r="F17" s="131" t="s">
+        <v>313</v>
+      </c>
+      <c r="G17" s="132" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H17" s="128"/>
+      <c r="I17" s="133"/>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B18" s="138" t="s">
+      <c r="B18" s="134" t="s">
+        <v>103</v>
+      </c>
+      <c r="C18" s="135" t="s">
         <v>104</v>
       </c>
-      <c r="C18" s="139" t="s">
-        <v>105</v>
-      </c>
-      <c r="D18" s="156">
+      <c r="D18" s="152">
         <f>D32+D30</f>
         <v>1435</v>
       </c>
-      <c r="E18" s="134" t="s">
-        <v>55</v>
-      </c>
-      <c r="F18" s="135" t="s">
-        <v>317</v>
-      </c>
-      <c r="G18" s="136" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H18" s="139"/>
-      <c r="I18" s="157"/>
+      <c r="E18" s="130" t="s">
+        <v>54</v>
+      </c>
+      <c r="F18" s="131" t="s">
+        <v>313</v>
+      </c>
+      <c r="G18" s="132" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H18" s="135"/>
+      <c r="I18" s="153"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B19" s="138" t="s">
-        <v>102</v>
-      </c>
-      <c r="C19" s="139" t="s">
-        <v>135</v>
-      </c>
-      <c r="D19" s="156">
+      <c r="B19" s="134" t="s">
+        <v>101</v>
+      </c>
+      <c r="C19" s="135" t="s">
+        <v>134</v>
+      </c>
+      <c r="D19" s="152">
         <f>D32+D30+D46</f>
         <v>1495</v>
       </c>
-      <c r="E19" s="134" t="s">
-        <v>55</v>
-      </c>
-      <c r="F19" s="135" t="s">
-        <v>317</v>
-      </c>
-      <c r="G19" s="136" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H19" s="139"/>
-      <c r="I19" s="157"/>
+      <c r="E19" s="130" t="s">
+        <v>54</v>
+      </c>
+      <c r="F19" s="131" t="s">
+        <v>313</v>
+      </c>
+      <c r="G19" s="132" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H19" s="135"/>
+      <c r="I19" s="153"/>
     </row>
     <row r="20" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
-      <c r="B20" s="138" t="s">
-        <v>68</v>
-      </c>
-      <c r="C20" s="139" t="s">
-        <v>136</v>
-      </c>
-      <c r="D20" s="156">
+      <c r="B20" s="134" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="135" t="s">
+        <v>135</v>
+      </c>
+      <c r="D20" s="152">
         <f>D18/D17</f>
         <v>0.74545454545454548</v>
       </c>
-      <c r="E20" s="156" t="s">
-        <v>69</v>
-      </c>
-      <c r="F20" s="135" t="s">
-        <v>317</v>
-      </c>
-      <c r="G20" s="136" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H20" s="139"/>
-      <c r="I20" s="157"/>
+      <c r="E20" s="152" t="s">
+        <v>68</v>
+      </c>
+      <c r="F20" s="131" t="s">
+        <v>313</v>
+      </c>
+      <c r="G20" s="132" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H20" s="135"/>
+      <c r="I20" s="153"/>
     </row>
     <row r="21" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B21" s="138" t="s">
-        <v>103</v>
-      </c>
-      <c r="C21" s="139" t="s">
-        <v>137</v>
-      </c>
-      <c r="D21" s="156">
+      <c r="B21" s="134" t="s">
+        <v>102</v>
+      </c>
+      <c r="C21" s="135" t="s">
+        <v>136</v>
+      </c>
+      <c r="D21" s="152">
         <f>D19/D17</f>
         <v>0.77662337662337666</v>
       </c>
-      <c r="E21" s="156" t="s">
+      <c r="E21" s="152" t="s">
+        <v>68</v>
+      </c>
+      <c r="F21" s="131" t="s">
+        <v>313</v>
+      </c>
+      <c r="G21" s="132" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H21" s="135"/>
+      <c r="I21" s="153"/>
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B22" s="136"/>
+      <c r="C22" s="137"/>
+      <c r="D22" s="138"/>
+      <c r="E22" s="138"/>
+      <c r="F22" s="139"/>
+      <c r="G22" s="140" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H22" s="137"/>
+      <c r="I22" s="154"/>
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B23" s="146" t="s">
+        <v>326</v>
+      </c>
+      <c r="C23" s="147"/>
+      <c r="D23" s="148"/>
+      <c r="E23" s="148"/>
+      <c r="F23" s="149"/>
+      <c r="G23" s="148"/>
+      <c r="H23" s="150"/>
+      <c r="I23" s="151"/>
+    </row>
+    <row r="24" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="B24" s="127" t="s">
+        <v>72</v>
+      </c>
+      <c r="C24" s="128" t="s">
+        <v>137</v>
+      </c>
+      <c r="D24" s="129">
+        <v>2</v>
+      </c>
+      <c r="E24" s="130" t="s">
+        <v>53</v>
+      </c>
+      <c r="F24" s="131" t="s">
+        <v>340</v>
+      </c>
+      <c r="G24" s="132" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H24" s="128" t="s">
+        <v>297</v>
+      </c>
+      <c r="I24" s="133">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9" ht="57" x14ac:dyDescent="0.3">
+      <c r="B25" s="127" t="s">
+        <v>73</v>
+      </c>
+      <c r="C25" s="128" t="s">
+        <v>83</v>
+      </c>
+      <c r="D25" s="32">
+        <v>5</v>
+      </c>
+      <c r="E25" s="130" t="s">
         <v>69</v>
       </c>
-      <c r="F21" s="135" t="s">
-        <v>317</v>
-      </c>
-      <c r="G21" s="136" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H21" s="139"/>
-      <c r="I21" s="157"/>
-    </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B22" s="140"/>
-      <c r="C22" s="141"/>
-      <c r="D22" s="142"/>
-      <c r="E22" s="142"/>
-      <c r="F22" s="143"/>
-      <c r="G22" s="144" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H22" s="141"/>
-      <c r="I22" s="158"/>
-    </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B23" s="150" t="s">
-        <v>330</v>
-      </c>
-      <c r="C23" s="151"/>
-      <c r="D23" s="152"/>
-      <c r="E23" s="152"/>
-      <c r="F23" s="153"/>
-      <c r="G23" s="152"/>
-      <c r="H23" s="154"/>
-      <c r="I23" s="155"/>
-    </row>
-    <row r="24" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
-      <c r="B24" s="131" t="s">
-        <v>73</v>
-      </c>
-      <c r="C24" s="132" t="s">
-        <v>138</v>
-      </c>
-      <c r="D24" s="133">
-        <v>2</v>
-      </c>
-      <c r="E24" s="134" t="s">
-        <v>54</v>
-      </c>
-      <c r="F24" s="135"/>
-      <c r="G24" s="136" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H24" s="132" t="s">
-        <v>298</v>
-      </c>
-      <c r="I24" s="137">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="2:9" ht="57" x14ac:dyDescent="0.3">
-      <c r="B25" s="131" t="s">
+      <c r="F25" s="131" t="s">
+        <v>340</v>
+      </c>
+      <c r="G25" s="132" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H25" s="128"/>
+      <c r="I25" s="133"/>
+    </row>
+    <row r="26" spans="2:9" ht="45.6" x14ac:dyDescent="0.3">
+      <c r="B26" s="127" t="s">
         <v>74</v>
       </c>
-      <c r="C25" s="132" t="s">
-        <v>84</v>
-      </c>
-      <c r="D25" s="38">
-        <v>5</v>
-      </c>
-      <c r="E25" s="134" t="s">
-        <v>70</v>
-      </c>
-      <c r="F25" s="135"/>
-      <c r="G25" s="136" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H25" s="132"/>
-      <c r="I25" s="137"/>
-    </row>
-    <row r="26" spans="2:9" ht="45.6" x14ac:dyDescent="0.3">
-      <c r="B26" s="131" t="s">
-        <v>75</v>
-      </c>
-      <c r="C26" s="132" t="s">
-        <v>72</v>
-      </c>
-      <c r="D26" s="134">
+      <c r="C26" s="128" t="s">
+        <v>71</v>
+      </c>
+      <c r="D26" s="130">
         <f>ROUND(ATAN(D25/100)*180/PI(),0)</f>
         <v>3</v>
       </c>
-      <c r="E26" s="134" t="s">
-        <v>71</v>
-      </c>
-      <c r="F26" s="135"/>
-      <c r="G26" s="136" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H26" s="132"/>
-      <c r="I26" s="137"/>
+      <c r="E26" s="130" t="s">
+        <v>70</v>
+      </c>
+      <c r="F26" s="131" t="s">
+        <v>340</v>
+      </c>
+      <c r="G26" s="132" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H26" s="128"/>
+      <c r="I26" s="133"/>
     </row>
     <row r="27" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B27" s="138" t="s">
+      <c r="B27" s="134" t="s">
+        <v>76</v>
+      </c>
+      <c r="C27" s="135" t="s">
+        <v>324</v>
+      </c>
+      <c r="D27" s="155">
+        <v>0.6</v>
+      </c>
+      <c r="E27" s="152" t="s">
+        <v>53</v>
+      </c>
+      <c r="F27" s="131" t="s">
+        <v>340</v>
+      </c>
+      <c r="G27" s="132" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H27" s="135"/>
+      <c r="I27" s="153"/>
+    </row>
+    <row r="28" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="B28" s="127" t="s">
+        <v>75</v>
+      </c>
+      <c r="C28" s="128" t="s">
+        <v>138</v>
+      </c>
+      <c r="D28" s="129">
+        <v>0.2</v>
+      </c>
+      <c r="E28" s="130" t="s">
+        <v>53</v>
+      </c>
+      <c r="F28" s="131" t="s">
+        <v>340</v>
+      </c>
+      <c r="G28" s="132" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H28" s="128"/>
+      <c r="I28" s="133"/>
+    </row>
+    <row r="29" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B29" s="127" t="s">
+        <v>139</v>
+      </c>
+      <c r="C29" s="128" t="s">
+        <v>141</v>
+      </c>
+      <c r="D29" s="129">
+        <v>2</v>
+      </c>
+      <c r="E29" s="130" t="s">
+        <v>68</v>
+      </c>
+      <c r="F29" s="131" t="s">
+        <v>340</v>
+      </c>
+      <c r="G29" s="132" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H29" s="128"/>
+      <c r="I29" s="133"/>
+    </row>
+    <row r="30" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="B30" s="134" t="s">
         <v>77</v>
       </c>
-      <c r="C27" s="139" t="s">
-        <v>328</v>
-      </c>
-      <c r="D27" s="159">
-        <v>0.6</v>
-      </c>
-      <c r="E27" s="156" t="s">
-        <v>54</v>
-      </c>
-      <c r="F27" s="160"/>
-      <c r="G27" s="136" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H27" s="139"/>
-      <c r="I27" s="157"/>
-    </row>
-    <row r="28" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="B28" s="131" t="s">
-        <v>76</v>
-      </c>
-      <c r="C28" s="132" t="s">
-        <v>139</v>
-      </c>
-      <c r="D28" s="133">
-        <v>0.2</v>
-      </c>
-      <c r="E28" s="134" t="s">
-        <v>54</v>
-      </c>
-      <c r="F28" s="135"/>
-      <c r="G28" s="136" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H28" s="132"/>
-      <c r="I28" s="137"/>
-    </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B29" s="131" t="s">
+      <c r="C30" s="135" t="s">
         <v>140</v>
       </c>
-      <c r="C29" s="132" t="s">
-        <v>142</v>
-      </c>
-      <c r="D29" s="133">
-        <v>2</v>
-      </c>
-      <c r="E29" s="134" t="s">
-        <v>69</v>
-      </c>
-      <c r="F29" s="135"/>
-      <c r="G29" s="136" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H29" s="132"/>
-      <c r="I29" s="137"/>
-    </row>
-    <row r="30" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B30" s="138" t="s">
-        <v>78</v>
-      </c>
-      <c r="C30" s="139" t="s">
-        <v>141</v>
-      </c>
-      <c r="D30" s="156">
+      <c r="D30" s="152">
         <f>(D27-D28)*(D11+D24+D24)*D29</f>
         <v>32.799999999999997</v>
       </c>
-      <c r="E30" s="134" t="s">
-        <v>55</v>
-      </c>
-      <c r="F30" s="160"/>
-      <c r="G30" s="136" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H30" s="139"/>
-      <c r="I30" s="157"/>
+      <c r="E30" s="130" t="s">
+        <v>54</v>
+      </c>
+      <c r="F30" s="131" t="s">
+        <v>340</v>
+      </c>
+      <c r="G30" s="132" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H30" s="135"/>
+      <c r="I30" s="153"/>
     </row>
     <row r="31" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
-      <c r="B31" s="131" t="s">
-        <v>143</v>
-      </c>
-      <c r="C31" s="132" t="s">
-        <v>145</v>
-      </c>
-      <c r="D31" s="134">
+      <c r="B31" s="127" t="s">
+        <v>142</v>
+      </c>
+      <c r="C31" s="128" t="s">
+        <v>144</v>
+      </c>
+      <c r="D31" s="130">
         <f>(D10*D11)-D30</f>
         <v>1262.2</v>
       </c>
-      <c r="E31" s="134" t="s">
-        <v>55</v>
-      </c>
-      <c r="F31" s="135"/>
-      <c r="G31" s="136" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H31" s="132"/>
-      <c r="I31" s="137"/>
+      <c r="E31" s="130" t="s">
+        <v>54</v>
+      </c>
+      <c r="F31" s="131" t="s">
+        <v>340</v>
+      </c>
+      <c r="G31" s="132" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H31" s="128"/>
+      <c r="I31" s="133"/>
     </row>
     <row r="32" spans="2:9" ht="45.6" x14ac:dyDescent="0.3">
-      <c r="B32" s="131" t="s">
-        <v>144</v>
-      </c>
-      <c r="C32" s="132" t="s">
-        <v>146</v>
-      </c>
-      <c r="D32" s="134">
+      <c r="B32" s="127" t="s">
+        <v>143</v>
+      </c>
+      <c r="C32" s="128" t="s">
+        <v>145</v>
+      </c>
+      <c r="D32" s="130">
         <f>((D10*D11)+D10*(D24+D24))-D30</f>
         <v>1402.2</v>
       </c>
-      <c r="E32" s="134" t="s">
-        <v>55</v>
-      </c>
-      <c r="F32" s="135"/>
-      <c r="G32" s="136" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H32" s="132"/>
-      <c r="I32" s="137"/>
+      <c r="E32" s="130" t="s">
+        <v>54</v>
+      </c>
+      <c r="F32" s="131" t="s">
+        <v>340</v>
+      </c>
+      <c r="G32" s="132" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H32" s="128"/>
+      <c r="I32" s="133"/>
     </row>
     <row r="33" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B33" s="131" t="s">
+      <c r="B33" s="127" t="s">
+        <v>78</v>
+      </c>
+      <c r="C33" s="128" t="s">
+        <v>126</v>
+      </c>
+      <c r="D33" s="129">
+        <v>10</v>
+      </c>
+      <c r="E33" s="130" t="s">
+        <v>53</v>
+      </c>
+      <c r="F33" s="131" t="s">
+        <v>340</v>
+      </c>
+      <c r="G33" s="132" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H33" s="128"/>
+      <c r="I33" s="133"/>
+    </row>
+    <row r="34" spans="2:9" ht="45.6" x14ac:dyDescent="0.3">
+      <c r="B34" s="127" t="s">
         <v>79</v>
       </c>
-      <c r="C33" s="132" t="s">
-        <v>127</v>
-      </c>
-      <c r="D33" s="133">
-        <v>10</v>
-      </c>
-      <c r="E33" s="134" t="s">
-        <v>54</v>
-      </c>
-      <c r="F33" s="135"/>
-      <c r="G33" s="136" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H33" s="132"/>
-      <c r="I33" s="137"/>
-    </row>
-    <row r="34" spans="2:9" ht="45.6" x14ac:dyDescent="0.3">
-      <c r="B34" s="131" t="s">
-        <v>80</v>
-      </c>
-      <c r="C34" s="132" t="s">
-        <v>147</v>
-      </c>
-      <c r="D34" s="134">
+      <c r="C34" s="128" t="s">
+        <v>146</v>
+      </c>
+      <c r="D34" s="130">
         <f>EVEN(D31/(D33*D33))</f>
         <v>14</v>
       </c>
-      <c r="E34" s="134" t="s">
-        <v>119</v>
-      </c>
-      <c r="F34" s="135"/>
-      <c r="G34" s="136" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H34" s="132"/>
-      <c r="I34" s="137"/>
+      <c r="E34" s="130" t="s">
+        <v>118</v>
+      </c>
+      <c r="F34" s="131" t="s">
+        <v>340</v>
+      </c>
+      <c r="G34" s="132" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H34" s="128"/>
+      <c r="I34" s="133"/>
     </row>
     <row r="35" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B35" s="131" t="s">
+      <c r="B35" s="127" t="s">
+        <v>80</v>
+      </c>
+      <c r="C35" s="128" t="s">
+        <v>63</v>
+      </c>
+      <c r="D35" s="129">
+        <v>1200</v>
+      </c>
+      <c r="E35" s="130" t="s">
+        <v>64</v>
+      </c>
+      <c r="F35" s="131" t="s">
+        <v>340</v>
+      </c>
+      <c r="G35" s="132" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H35" s="128"/>
+      <c r="I35" s="133"/>
+    </row>
+    <row r="36" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="B36" s="127" t="s">
         <v>81</v>
       </c>
-      <c r="C35" s="132" t="s">
-        <v>64</v>
-      </c>
-      <c r="D35" s="133">
-        <v>1200</v>
-      </c>
-      <c r="E35" s="134" t="s">
-        <v>65</v>
-      </c>
-      <c r="F35" s="135"/>
-      <c r="G35" s="136" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H35" s="132"/>
-      <c r="I35" s="137"/>
-    </row>
-    <row r="36" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B36" s="131" t="s">
-        <v>82</v>
-      </c>
-      <c r="C36" s="132" t="s">
-        <v>63</v>
-      </c>
-      <c r="D36" s="134">
+      <c r="C36" s="128" t="s">
+        <v>62</v>
+      </c>
+      <c r="D36" s="130">
         <f>D35*D35/(1000*1000)</f>
         <v>1.44</v>
       </c>
-      <c r="E36" s="134" t="s">
-        <v>55</v>
-      </c>
-      <c r="F36" s="135"/>
-      <c r="G36" s="136" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H36" s="132"/>
-      <c r="I36" s="137"/>
+      <c r="E36" s="130" t="s">
+        <v>54</v>
+      </c>
+      <c r="F36" s="131" t="s">
+        <v>340</v>
+      </c>
+      <c r="G36" s="132" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H36" s="128"/>
+      <c r="I36" s="133"/>
     </row>
     <row r="37" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="B37" s="131" t="s">
-        <v>83</v>
-      </c>
-      <c r="C37" s="132" t="s">
-        <v>148</v>
-      </c>
-      <c r="D37" s="134">
+      <c r="B37" s="127" t="s">
+        <v>82</v>
+      </c>
+      <c r="C37" s="128" t="s">
+        <v>147</v>
+      </c>
+      <c r="D37" s="130">
         <f>D34*D36</f>
         <v>20.16</v>
       </c>
-      <c r="E37" s="134" t="s">
-        <v>55</v>
-      </c>
-      <c r="F37" s="135"/>
-      <c r="G37" s="136" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H37" s="132"/>
-      <c r="I37" s="137"/>
+      <c r="E37" s="130" t="s">
+        <v>54</v>
+      </c>
+      <c r="F37" s="131" t="s">
+        <v>340</v>
+      </c>
+      <c r="G37" s="132" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H37" s="128"/>
+      <c r="I37" s="133"/>
     </row>
     <row r="38" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B38" s="140"/>
-      <c r="C38" s="141"/>
-      <c r="D38" s="142"/>
-      <c r="E38" s="142"/>
-      <c r="F38" s="143"/>
-      <c r="G38" s="144" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H38" s="141"/>
-      <c r="I38" s="158"/>
+      <c r="B38" s="136"/>
+      <c r="C38" s="137"/>
+      <c r="D38" s="138"/>
+      <c r="E38" s="138"/>
+      <c r="F38" s="139"/>
+      <c r="G38" s="140" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H38" s="137"/>
+      <c r="I38" s="154"/>
     </row>
     <row r="39" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B39" s="161" t="s">
-        <v>331</v>
-      </c>
-      <c r="C39" s="151"/>
-      <c r="D39" s="152"/>
-      <c r="E39" s="152"/>
-      <c r="F39" s="153"/>
-      <c r="G39" s="152"/>
-      <c r="H39" s="154"/>
-      <c r="I39" s="155"/>
+      <c r="B39" s="156" t="s">
+        <v>327</v>
+      </c>
+      <c r="C39" s="147"/>
+      <c r="D39" s="148"/>
+      <c r="E39" s="148"/>
+      <c r="F39" s="149"/>
+      <c r="G39" s="148"/>
+      <c r="H39" s="150"/>
+      <c r="I39" s="151"/>
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B40" s="131" t="s">
+      <c r="B40" s="127" t="s">
+        <v>84</v>
+      </c>
+      <c r="C40" s="128" t="s">
+        <v>88</v>
+      </c>
+      <c r="D40" s="129">
+        <v>1</v>
+      </c>
+      <c r="E40" s="130" t="s">
+        <v>53</v>
+      </c>
+      <c r="F40" s="131" t="s">
+        <v>340</v>
+      </c>
+      <c r="G40" s="132" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H40" s="128"/>
+      <c r="I40" s="133">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="B41" s="127" t="s">
         <v>85</v>
       </c>
-      <c r="C40" s="132" t="s">
+      <c r="C41" s="128" t="s">
         <v>89</v>
       </c>
-      <c r="D40" s="133">
-        <v>1</v>
-      </c>
-      <c r="E40" s="134" t="s">
-        <v>54</v>
-      </c>
-      <c r="F40" s="135"/>
-      <c r="G40" s="136" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H40" s="132"/>
-      <c r="I40" s="137">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="41" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B41" s="131" t="s">
+      <c r="D41" s="129">
+        <v>15</v>
+      </c>
+      <c r="E41" s="130" t="s">
+        <v>53</v>
+      </c>
+      <c r="F41" s="131" t="s">
+        <v>340</v>
+      </c>
+      <c r="G41" s="132" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H41" s="128"/>
+      <c r="I41" s="133"/>
+    </row>
+    <row r="42" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="B42" s="127" t="s">
         <v>86</v>
       </c>
-      <c r="C41" s="132" t="s">
+      <c r="C42" s="128" t="s">
         <v>90</v>
       </c>
-      <c r="D41" s="133">
-        <v>15</v>
-      </c>
-      <c r="E41" s="134" t="s">
-        <v>54</v>
-      </c>
-      <c r="F41" s="135"/>
-      <c r="G41" s="136" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H41" s="132"/>
-      <c r="I41" s="137"/>
-    </row>
-    <row r="42" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B42" s="131" t="s">
-        <v>87</v>
-      </c>
-      <c r="C42" s="132" t="s">
-        <v>91</v>
-      </c>
-      <c r="D42" s="134">
+      <c r="D42" s="130">
         <f>D11+(INT(D11/D41)*D10)</f>
         <v>107</v>
       </c>
-      <c r="E42" s="134" t="s">
-        <v>54</v>
-      </c>
-      <c r="F42" s="135"/>
-      <c r="G42" s="136" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H42" s="132"/>
-      <c r="I42" s="137"/>
+      <c r="E42" s="130" t="s">
+        <v>53</v>
+      </c>
+      <c r="F42" s="131" t="s">
+        <v>340</v>
+      </c>
+      <c r="G42" s="132" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H42" s="128"/>
+      <c r="I42" s="133"/>
     </row>
     <row r="43" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B43" s="131" t="s">
-        <v>88</v>
-      </c>
-      <c r="C43" s="132" t="s">
-        <v>92</v>
-      </c>
-      <c r="D43" s="134">
+      <c r="B43" s="127" t="s">
+        <v>87</v>
+      </c>
+      <c r="C43" s="128" t="s">
+        <v>91</v>
+      </c>
+      <c r="D43" s="130">
         <f>D42*D40</f>
         <v>107</v>
       </c>
-      <c r="E43" s="134" t="s">
-        <v>55</v>
-      </c>
-      <c r="F43" s="135"/>
-      <c r="G43" s="136" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H43" s="132"/>
-      <c r="I43" s="137"/>
+      <c r="E43" s="130" t="s">
+        <v>54</v>
+      </c>
+      <c r="F43" s="131" t="s">
+        <v>340</v>
+      </c>
+      <c r="G43" s="132" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H43" s="128"/>
+      <c r="I43" s="133"/>
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B44" s="140"/>
-      <c r="C44" s="141"/>
-      <c r="D44" s="142"/>
-      <c r="E44" s="142"/>
-      <c r="F44" s="143"/>
-      <c r="G44" s="144" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H44" s="141"/>
-      <c r="I44" s="158"/>
+      <c r="B44" s="136"/>
+      <c r="C44" s="137"/>
+      <c r="D44" s="138"/>
+      <c r="E44" s="138"/>
+      <c r="F44" s="139"/>
+      <c r="G44" s="140" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H44" s="137"/>
+      <c r="I44" s="154"/>
     </row>
     <row r="45" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B45" s="150" t="s">
-        <v>332</v>
-      </c>
-      <c r="C45" s="151"/>
-      <c r="D45" s="152"/>
-      <c r="E45" s="152"/>
-      <c r="F45" s="153"/>
-      <c r="G45" s="152"/>
-      <c r="H45" s="154"/>
-      <c r="I45" s="155"/>
+      <c r="B45" s="146" t="s">
+        <v>328</v>
+      </c>
+      <c r="C45" s="147"/>
+      <c r="D45" s="148"/>
+      <c r="E45" s="148"/>
+      <c r="F45" s="149"/>
+      <c r="G45" s="148"/>
+      <c r="H45" s="150"/>
+      <c r="I45" s="151"/>
     </row>
     <row r="46" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
-      <c r="B46" s="131" t="s">
+      <c r="B46" s="127" t="s">
+        <v>41</v>
+      </c>
+      <c r="C46" s="128" t="s">
+        <v>329</v>
+      </c>
+      <c r="D46" s="129">
+        <v>60</v>
+      </c>
+      <c r="E46" s="130" t="s">
+        <v>54</v>
+      </c>
+      <c r="F46" s="131" t="s">
+        <v>340</v>
+      </c>
+      <c r="G46" s="132" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H46" s="128"/>
+      <c r="I46" s="133">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="B47" s="127" t="s">
         <v>42</v>
       </c>
-      <c r="C46" s="132" t="s">
-        <v>333</v>
-      </c>
-      <c r="D46" s="133">
-        <v>60</v>
-      </c>
-      <c r="E46" s="134" t="s">
-        <v>55</v>
-      </c>
-      <c r="F46" s="135"/>
-      <c r="G46" s="136" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H46" s="132"/>
-      <c r="I46" s="137">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="47" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
-      <c r="B47" s="131" t="s">
+      <c r="C47" s="128" t="s">
         <v>43</v>
       </c>
-      <c r="C47" s="132" t="s">
-        <v>44</v>
-      </c>
-      <c r="D47" s="133">
+      <c r="D47" s="129">
         <v>24</v>
       </c>
-      <c r="E47" s="134" t="s">
-        <v>55</v>
-      </c>
-      <c r="F47" s="135"/>
-      <c r="G47" s="136" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H47" s="132"/>
-      <c r="I47" s="137"/>
+      <c r="E47" s="130" t="s">
+        <v>54</v>
+      </c>
+      <c r="F47" s="131" t="s">
+        <v>340</v>
+      </c>
+      <c r="G47" s="132" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H47" s="128"/>
+      <c r="I47" s="133"/>
     </row>
     <row r="48" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B48" s="131" t="s">
+      <c r="B48" s="127" t="s">
+        <v>92</v>
+      </c>
+      <c r="C48" s="128" t="s">
+        <v>127</v>
+      </c>
+      <c r="D48" s="129">
+        <v>3.9900000000000007</v>
+      </c>
+      <c r="E48" s="130" t="s">
+        <v>53</v>
+      </c>
+      <c r="F48" s="131" t="s">
+        <v>340</v>
+      </c>
+      <c r="G48" s="132" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H48" s="128"/>
+      <c r="I48" s="133"/>
+    </row>
+    <row r="49" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="B49" s="127" t="s">
         <v>93</v>
       </c>
-      <c r="C48" s="132" t="s">
-        <v>128</v>
-      </c>
-      <c r="D48" s="133">
-        <v>3.9900000000000007</v>
-      </c>
-      <c r="E48" s="134" t="s">
-        <v>54</v>
-      </c>
-      <c r="F48" s="135"/>
-      <c r="G48" s="136" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H48" s="132"/>
-      <c r="I48" s="137"/>
-    </row>
-    <row r="49" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B49" s="131" t="s">
-        <v>94</v>
-      </c>
-      <c r="C49" s="132" t="s">
-        <v>149</v>
-      </c>
-      <c r="D49" s="134">
+      <c r="C49" s="128" t="s">
+        <v>148</v>
+      </c>
+      <c r="D49" s="130">
         <f>D46-D54</f>
         <v>52.943999999999996</v>
       </c>
-      <c r="E49" s="134" t="s">
+      <c r="E49" s="130" t="s">
+        <v>54</v>
+      </c>
+      <c r="F49" s="131" t="s">
+        <v>340</v>
+      </c>
+      <c r="G49" s="132" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H49" s="128"/>
+      <c r="I49" s="133"/>
+    </row>
+    <row r="50" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="B50" s="127" t="s">
+        <v>57</v>
+      </c>
+      <c r="C50" s="128" t="s">
+        <v>56</v>
+      </c>
+      <c r="D50" s="129">
+        <v>28</v>
+      </c>
+      <c r="E50" s="130" t="s">
         <v>55</v>
       </c>
-      <c r="F49" s="135"/>
-      <c r="G49" s="136" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H49" s="132"/>
-      <c r="I49" s="137"/>
-    </row>
-    <row r="50" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B50" s="131" t="s">
+      <c r="F50" s="131" t="s">
+        <v>340</v>
+      </c>
+      <c r="G50" s="132" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H50" s="128"/>
+      <c r="I50" s="133"/>
+    </row>
+    <row r="51" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="B51" s="127" t="s">
+        <v>96</v>
+      </c>
+      <c r="C51" s="128" t="s">
         <v>58</v>
       </c>
-      <c r="C50" s="132" t="s">
-        <v>57</v>
-      </c>
-      <c r="D50" s="133">
-        <v>28</v>
-      </c>
-      <c r="E50" s="134" t="s">
-        <v>56</v>
-      </c>
-      <c r="F50" s="135"/>
-      <c r="G50" s="136" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H50" s="132"/>
-      <c r="I50" s="137"/>
-    </row>
-    <row r="51" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B51" s="131" t="s">
-        <v>97</v>
-      </c>
-      <c r="C51" s="132" t="s">
-        <v>59</v>
-      </c>
-      <c r="D51" s="133">
+      <c r="D51" s="129">
         <v>19</v>
       </c>
-      <c r="E51" s="134" t="s">
-        <v>56</v>
-      </c>
-      <c r="F51" s="135"/>
-      <c r="G51" s="136" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H51" s="132"/>
-      <c r="I51" s="137"/>
+      <c r="E51" s="130" t="s">
+        <v>55</v>
+      </c>
+      <c r="F51" s="131" t="s">
+        <v>340</v>
+      </c>
+      <c r="G51" s="132" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H51" s="128"/>
+      <c r="I51" s="133"/>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B52" s="131" t="s">
+      <c r="B52" s="127" t="s">
+        <v>94</v>
+      </c>
+      <c r="C52" s="128" t="s">
         <v>95</v>
       </c>
-      <c r="C52" s="132" t="s">
-        <v>96</v>
-      </c>
-      <c r="D52" s="134">
+      <c r="D52" s="130">
         <f>D48/(D51/100)</f>
         <v>21.000000000000004</v>
       </c>
-      <c r="E52" s="134" t="s">
-        <v>50</v>
-      </c>
-      <c r="F52" s="135"/>
-      <c r="G52" s="136" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H52" s="132"/>
-      <c r="I52" s="137"/>
+      <c r="E52" s="130" t="s">
+        <v>49</v>
+      </c>
+      <c r="F52" s="131" t="s">
+        <v>340</v>
+      </c>
+      <c r="G52" s="132" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H52" s="128"/>
+      <c r="I52" s="133"/>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B53" s="131" t="s">
+      <c r="B53" s="127" t="s">
+        <v>97</v>
+      </c>
+      <c r="C53" s="128" t="s">
         <v>98</v>
       </c>
-      <c r="C53" s="132" t="s">
+      <c r="D53" s="129">
+        <v>1.2</v>
+      </c>
+      <c r="E53" s="130" t="s">
+        <v>53</v>
+      </c>
+      <c r="F53" s="131" t="s">
+        <v>340</v>
+      </c>
+      <c r="G53" s="132" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H53" s="128"/>
+      <c r="I53" s="133"/>
+    </row>
+    <row r="54" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="B54" s="127" t="s">
         <v>99</v>
       </c>
-      <c r="D53" s="133">
-        <v>1.2</v>
-      </c>
-      <c r="E53" s="134" t="s">
-        <v>54</v>
-      </c>
-      <c r="F53" s="135"/>
-      <c r="G53" s="136" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H53" s="132"/>
-      <c r="I53" s="137"/>
-    </row>
-    <row r="54" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B54" s="131" t="s">
+      <c r="C54" s="128" t="s">
         <v>100</v>
       </c>
-      <c r="C54" s="132" t="s">
-        <v>101</v>
-      </c>
-      <c r="D54" s="162">
+      <c r="D54" s="157">
         <f>D53*D52*(D50/100)</f>
         <v>7.0560000000000018</v>
       </c>
-      <c r="E54" s="134" t="s">
+      <c r="E54" s="130" t="s">
+        <v>54</v>
+      </c>
+      <c r="F54" s="131" t="s">
+        <v>340</v>
+      </c>
+      <c r="G54" s="132" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H54" s="128"/>
+      <c r="I54" s="133"/>
+    </row>
+    <row r="55" spans="2:9" ht="68.400000000000006" x14ac:dyDescent="0.3">
+      <c r="B55" s="127" t="s">
+        <v>128</v>
+      </c>
+      <c r="C55" s="128" t="s">
+        <v>189</v>
+      </c>
+      <c r="D55" s="129">
+        <v>6</v>
+      </c>
+      <c r="E55" s="130" t="s">
+        <v>53</v>
+      </c>
+      <c r="F55" s="131" t="s">
+        <v>340</v>
+      </c>
+      <c r="G55" s="132" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H55" s="128"/>
+      <c r="I55" s="133"/>
+    </row>
+    <row r="56" spans="2:9" ht="68.400000000000006" x14ac:dyDescent="0.3">
+      <c r="B56" s="127" t="s">
+        <v>129</v>
+      </c>
+      <c r="C56" s="128" t="s">
+        <v>190</v>
+      </c>
+      <c r="D56" s="129">
+        <v>4.5</v>
+      </c>
+      <c r="E56" s="130" t="s">
+        <v>53</v>
+      </c>
+      <c r="F56" s="131" t="s">
+        <v>340</v>
+      </c>
+      <c r="G56" s="132" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H56" s="128"/>
+      <c r="I56" s="133"/>
+    </row>
+    <row r="57" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B57" s="127" t="s">
+        <v>131</v>
+      </c>
+      <c r="C57" s="128" t="s">
+        <v>130</v>
+      </c>
+      <c r="D57" s="129">
+        <v>1.2</v>
+      </c>
+      <c r="E57" s="130" t="s">
+        <v>53</v>
+      </c>
+      <c r="F57" s="131" t="s">
+        <v>340</v>
+      </c>
+      <c r="G57" s="132" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H57" s="128"/>
+      <c r="I57" s="133"/>
+    </row>
+    <row r="58" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B58" s="127" t="s">
+        <v>187</v>
+      </c>
+      <c r="C58" s="128" t="s">
+        <v>188</v>
+      </c>
+      <c r="D58" s="129">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="E58" s="130" t="s">
+        <v>53</v>
+      </c>
+      <c r="F58" s="131" t="s">
+        <v>340</v>
+      </c>
+      <c r="G58" s="132" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H58" s="128"/>
+      <c r="I58" s="133"/>
+    </row>
+    <row r="59" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="B59" s="127" t="s">
+        <v>132</v>
+      </c>
+      <c r="C59" s="128" t="s">
+        <v>191</v>
+      </c>
+      <c r="D59" s="129">
+        <v>3</v>
+      </c>
+      <c r="E59" s="130" t="s">
+        <v>53</v>
+      </c>
+      <c r="F59" s="131" t="s">
+        <v>340</v>
+      </c>
+      <c r="G59" s="132" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H59" s="128"/>
+      <c r="I59" s="133"/>
+    </row>
+    <row r="60" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="B60" s="127" t="s">
+        <v>186</v>
+      </c>
+      <c r="C60" s="128" t="s">
+        <v>192</v>
+      </c>
+      <c r="D60" s="129">
+        <v>2</v>
+      </c>
+      <c r="E60" s="130" t="s">
+        <v>53</v>
+      </c>
+      <c r="F60" s="131" t="s">
+        <v>340</v>
+      </c>
+      <c r="G60" s="132" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H60" s="128"/>
+      <c r="I60" s="133"/>
+    </row>
+    <row r="61" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B61" s="136"/>
+      <c r="C61" s="137"/>
+      <c r="D61" s="138"/>
+      <c r="E61" s="138"/>
+      <c r="F61" s="139"/>
+      <c r="G61" s="140" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H61" s="137"/>
+      <c r="I61" s="154"/>
+    </row>
+    <row r="62" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B62" s="158" t="s">
+        <v>330</v>
+      </c>
+      <c r="C62" s="159"/>
+      <c r="D62" s="160"/>
+      <c r="E62" s="160"/>
+      <c r="F62" s="161"/>
+      <c r="G62" s="160"/>
+      <c r="H62" s="162"/>
+      <c r="I62" s="163"/>
+    </row>
+    <row r="63" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="B63" s="127" t="s">
+        <v>170</v>
+      </c>
+      <c r="C63" s="128" t="s">
+        <v>106</v>
+      </c>
+      <c r="D63" s="129">
+        <v>40</v>
+      </c>
+      <c r="E63" s="130" t="s">
         <v>55</v>
       </c>
-      <c r="F54" s="135"/>
-      <c r="G54" s="136" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H54" s="132"/>
-      <c r="I54" s="137"/>
-    </row>
-    <row r="55" spans="2:9" ht="68.400000000000006" x14ac:dyDescent="0.3">
-      <c r="B55" s="131" t="s">
-        <v>129</v>
-      </c>
-      <c r="C55" s="132" t="s">
-        <v>190</v>
-      </c>
-      <c r="D55" s="133">
-        <v>6</v>
-      </c>
-      <c r="E55" s="134" t="s">
-        <v>54</v>
-      </c>
-      <c r="F55" s="135"/>
-      <c r="G55" s="136" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H55" s="132"/>
-      <c r="I55" s="137"/>
-    </row>
-    <row r="56" spans="2:9" ht="68.400000000000006" x14ac:dyDescent="0.3">
-      <c r="B56" s="131" t="s">
-        <v>130</v>
-      </c>
-      <c r="C56" s="132" t="s">
-        <v>191</v>
-      </c>
-      <c r="D56" s="133">
-        <v>4.5</v>
-      </c>
-      <c r="E56" s="134" t="s">
-        <v>54</v>
-      </c>
-      <c r="F56" s="135"/>
-      <c r="G56" s="136" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H56" s="132"/>
-      <c r="I56" s="137"/>
-    </row>
-    <row r="57" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B57" s="131" t="s">
-        <v>132</v>
-      </c>
-      <c r="C57" s="132" t="s">
-        <v>131</v>
-      </c>
-      <c r="D57" s="133">
-        <v>1.2</v>
-      </c>
-      <c r="E57" s="134" t="s">
-        <v>54</v>
-      </c>
-      <c r="F57" s="135"/>
-      <c r="G57" s="136" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H57" s="132"/>
-      <c r="I57" s="137"/>
-    </row>
-    <row r="58" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B58" s="131" t="s">
-        <v>188</v>
-      </c>
-      <c r="C58" s="132" t="s">
-        <v>189</v>
-      </c>
-      <c r="D58" s="133">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="E58" s="134" t="s">
-        <v>54</v>
-      </c>
-      <c r="F58" s="135"/>
-      <c r="G58" s="136" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H58" s="132"/>
-      <c r="I58" s="137"/>
-    </row>
-    <row r="59" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B59" s="131" t="s">
-        <v>133</v>
-      </c>
-      <c r="C59" s="132" t="s">
-        <v>192</v>
-      </c>
-      <c r="D59" s="133">
-        <v>3</v>
-      </c>
-      <c r="E59" s="134" t="s">
-        <v>54</v>
-      </c>
-      <c r="F59" s="135"/>
-      <c r="G59" s="136" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H59" s="132"/>
-      <c r="I59" s="137"/>
-    </row>
-    <row r="60" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B60" s="131" t="s">
-        <v>187</v>
-      </c>
-      <c r="C60" s="132" t="s">
-        <v>193</v>
-      </c>
-      <c r="D60" s="133">
-        <v>2</v>
-      </c>
-      <c r="E60" s="134" t="s">
-        <v>54</v>
-      </c>
-      <c r="F60" s="135"/>
-      <c r="G60" s="136" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H60" s="132"/>
-      <c r="I60" s="137"/>
-    </row>
-    <row r="61" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B61" s="140"/>
-      <c r="C61" s="141"/>
-      <c r="D61" s="142"/>
-      <c r="E61" s="142"/>
-      <c r="F61" s="143"/>
-      <c r="G61" s="144" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H61" s="141"/>
-      <c r="I61" s="158"/>
-    </row>
-    <row r="62" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B62" s="163" t="s">
-        <v>334</v>
-      </c>
-      <c r="C62" s="164"/>
-      <c r="D62" s="165"/>
-      <c r="E62" s="165"/>
-      <c r="F62" s="166"/>
-      <c r="G62" s="165"/>
-      <c r="H62" s="167"/>
-      <c r="I62" s="168"/>
-    </row>
-    <row r="63" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B63" s="131" t="s">
+      <c r="F63" s="131" t="s">
+        <v>340</v>
+      </c>
+      <c r="G63" s="132" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H63" s="128"/>
+      <c r="I63" s="133">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B64" s="127" t="s">
+        <v>169</v>
+      </c>
+      <c r="C64" s="128" t="s">
         <v>171</v>
       </c>
-      <c r="C63" s="132" t="s">
-        <v>107</v>
-      </c>
-      <c r="D63" s="133">
-        <v>40</v>
-      </c>
-      <c r="E63" s="134" t="s">
-        <v>56</v>
-      </c>
-      <c r="F63" s="135"/>
-      <c r="G63" s="136" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H63" s="132"/>
-      <c r="I63" s="137">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="64" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B64" s="131" t="s">
-        <v>170</v>
-      </c>
-      <c r="C64" s="132" t="s">
-        <v>172</v>
-      </c>
-      <c r="D64" s="162">
+      <c r="D64" s="157">
         <f>D18</f>
         <v>1435</v>
       </c>
-      <c r="E64" s="134" t="s">
+      <c r="E64" s="130" t="s">
+        <v>54</v>
+      </c>
+      <c r="F64" s="131" t="s">
+        <v>340</v>
+      </c>
+      <c r="G64" s="132" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H64" s="128"/>
+      <c r="I64" s="133"/>
+    </row>
+    <row r="65" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="B65" s="127" t="s">
+        <v>105</v>
+      </c>
+      <c r="C65" s="128" t="s">
+        <v>107</v>
+      </c>
+      <c r="D65" s="129">
+        <v>20</v>
+      </c>
+      <c r="E65" s="130" t="s">
         <v>55</v>
       </c>
-      <c r="F64" s="135"/>
-      <c r="G64" s="136" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H64" s="132"/>
-      <c r="I64" s="137"/>
-    </row>
-    <row r="65" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B65" s="131" t="s">
-        <v>106</v>
-      </c>
-      <c r="C65" s="132" t="s">
-        <v>108</v>
-      </c>
-      <c r="D65" s="133">
-        <v>20</v>
-      </c>
-      <c r="E65" s="134" t="s">
-        <v>56</v>
-      </c>
-      <c r="F65" s="135"/>
-      <c r="G65" s="136" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H65" s="132"/>
-      <c r="I65" s="137"/>
+      <c r="F65" s="131" t="s">
+        <v>340</v>
+      </c>
+      <c r="G65" s="132" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H65" s="128"/>
+      <c r="I65" s="133"/>
     </row>
     <row r="66" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="B66" s="131" t="s">
+      <c r="B66" s="127" t="s">
+        <v>116</v>
+      </c>
+      <c r="C66" s="128" t="s">
+        <v>109</v>
+      </c>
+      <c r="D66" s="129">
+        <v>6</v>
+      </c>
+      <c r="E66" s="130" t="s">
+        <v>53</v>
+      </c>
+      <c r="F66" s="131" t="s">
+        <v>340</v>
+      </c>
+      <c r="G66" s="132" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H66" s="128"/>
+      <c r="I66" s="133"/>
+    </row>
+    <row r="67" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="B67" s="127" t="s">
         <v>117</v>
       </c>
-      <c r="C66" s="132" t="s">
-        <v>110</v>
-      </c>
-      <c r="D66" s="133">
-        <v>6</v>
-      </c>
-      <c r="E66" s="134" t="s">
-        <v>54</v>
-      </c>
-      <c r="F66" s="135"/>
-      <c r="G66" s="136" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H66" s="132"/>
-      <c r="I66" s="137"/>
-    </row>
-    <row r="67" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="B67" s="131" t="s">
-        <v>118</v>
-      </c>
-      <c r="C67" s="132" t="s">
-        <v>150</v>
-      </c>
-      <c r="D67" s="162">
+      <c r="C67" s="128" t="s">
+        <v>149</v>
+      </c>
+      <c r="D67" s="157">
         <f>ROUND(D10/D66,0)</f>
         <v>6</v>
       </c>
-      <c r="E67" s="134" t="s">
+      <c r="E67" s="130" t="s">
+        <v>118</v>
+      </c>
+      <c r="F67" s="131" t="s">
+        <v>340</v>
+      </c>
+      <c r="G67" s="132" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H67" s="128"/>
+      <c r="I67" s="133"/>
+    </row>
+    <row r="68" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="B68" s="127" t="s">
         <v>119</v>
       </c>
-      <c r="F67" s="135"/>
-      <c r="G67" s="136" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H67" s="132"/>
-      <c r="I67" s="137"/>
-    </row>
-    <row r="68" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="B68" s="131" t="s">
-        <v>120</v>
-      </c>
-      <c r="C68" s="132" t="s">
-        <v>151</v>
-      </c>
-      <c r="D68" s="162">
+      <c r="C68" s="128" t="s">
+        <v>150</v>
+      </c>
+      <c r="D68" s="157">
         <f>ROUND(D11/D66,0)</f>
         <v>6</v>
       </c>
-      <c r="E68" s="134" t="s">
-        <v>119</v>
-      </c>
-      <c r="F68" s="135"/>
-      <c r="G68" s="136" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H68" s="132"/>
-      <c r="I68" s="137"/>
+      <c r="E68" s="130" t="s">
+        <v>118</v>
+      </c>
+      <c r="F68" s="131" t="s">
+        <v>340</v>
+      </c>
+      <c r="G68" s="132" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H68" s="128"/>
+      <c r="I68" s="133"/>
     </row>
     <row r="69" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B69" s="131" t="s">
+      <c r="B69" s="127" t="s">
+        <v>120</v>
+      </c>
+      <c r="C69" s="128" t="s">
         <v>121</v>
       </c>
-      <c r="C69" s="132" t="s">
-        <v>122</v>
-      </c>
-      <c r="D69" s="162">
+      <c r="D69" s="157">
         <f>D68*D67</f>
         <v>36</v>
       </c>
-      <c r="E69" s="134" t="s">
-        <v>119</v>
-      </c>
-      <c r="F69" s="135"/>
-      <c r="G69" s="136" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H69" s="132"/>
-      <c r="I69" s="137"/>
+      <c r="E69" s="130" t="s">
+        <v>118</v>
+      </c>
+      <c r="F69" s="131" t="s">
+        <v>340</v>
+      </c>
+      <c r="G69" s="132" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H69" s="128"/>
+      <c r="I69" s="133"/>
     </row>
     <row r="70" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
-      <c r="B70" s="131" t="s">
-        <v>109</v>
-      </c>
-      <c r="C70" s="132" t="s">
+      <c r="B70" s="127" t="s">
+        <v>108</v>
+      </c>
+      <c r="C70" s="128" t="s">
+        <v>151</v>
+      </c>
+      <c r="D70" s="129">
+        <v>0.3</v>
+      </c>
+      <c r="E70" s="130" t="s">
+        <v>53</v>
+      </c>
+      <c r="F70" s="131" t="s">
+        <v>340</v>
+      </c>
+      <c r="G70" s="132" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H70" s="128"/>
+      <c r="I70" s="133"/>
+    </row>
+    <row r="71" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="B71" s="127" t="s">
+        <v>110</v>
+      </c>
+      <c r="C71" s="128" t="s">
         <v>152</v>
       </c>
-      <c r="D70" s="133">
+      <c r="D71" s="129">
+        <v>0.4</v>
+      </c>
+      <c r="E71" s="130" t="s">
+        <v>53</v>
+      </c>
+      <c r="F71" s="131" t="s">
+        <v>340</v>
+      </c>
+      <c r="G71" s="132" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H71" s="128"/>
+      <c r="I71" s="133"/>
+    </row>
+    <row r="72" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="B72" s="127" t="s">
+        <v>112</v>
+      </c>
+      <c r="C72" s="128" t="s">
+        <v>114</v>
+      </c>
+      <c r="D72" s="129">
         <v>0.3</v>
       </c>
-      <c r="E70" s="134" t="s">
-        <v>54</v>
-      </c>
-      <c r="F70" s="135"/>
-      <c r="G70" s="136" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H70" s="132"/>
-      <c r="I70" s="137"/>
-    </row>
-    <row r="71" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
-      <c r="B71" s="131" t="s">
-        <v>111</v>
-      </c>
-      <c r="C71" s="132" t="s">
-        <v>153</v>
-      </c>
-      <c r="D71" s="133">
+      <c r="E72" s="130" t="s">
+        <v>53</v>
+      </c>
+      <c r="F72" s="131" t="s">
+        <v>340</v>
+      </c>
+      <c r="G72" s="132" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H72" s="128"/>
+      <c r="I72" s="133"/>
+    </row>
+    <row r="73" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="B73" s="127" t="s">
+        <v>113</v>
+      </c>
+      <c r="C73" s="128" t="s">
+        <v>115</v>
+      </c>
+      <c r="D73" s="129">
         <v>0.4</v>
       </c>
-      <c r="E71" s="134" t="s">
-        <v>54</v>
-      </c>
-      <c r="F71" s="135"/>
-      <c r="G71" s="136" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H71" s="132"/>
-      <c r="I71" s="137"/>
-    </row>
-    <row r="72" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
-      <c r="B72" s="131" t="s">
-        <v>113</v>
-      </c>
-      <c r="C72" s="132" t="s">
-        <v>115</v>
-      </c>
-      <c r="D72" s="133">
-        <v>0.3</v>
-      </c>
-      <c r="E72" s="134" t="s">
-        <v>54</v>
-      </c>
-      <c r="F72" s="135"/>
-      <c r="G72" s="136" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H72" s="132"/>
-      <c r="I72" s="137"/>
-    </row>
-    <row r="73" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
-      <c r="B73" s="131" t="s">
-        <v>114</v>
-      </c>
-      <c r="C73" s="132" t="s">
-        <v>116</v>
-      </c>
-      <c r="D73" s="133">
-        <v>0.4</v>
-      </c>
-      <c r="E73" s="134" t="s">
-        <v>54</v>
-      </c>
-      <c r="F73" s="135"/>
-      <c r="G73" s="136" t="str">
+      <c r="E73" s="130" t="s">
+        <v>53</v>
+      </c>
+      <c r="F73" s="131" t="s">
+        <v>340</v>
+      </c>
+      <c r="G73" s="132" t="str">
         <f t="shared" ref="G73:G76" si="1">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F73,"/Readme.md"),"Ver")</f>
         <v>Ver</v>
       </c>
-      <c r="H73" s="132"/>
-      <c r="I73" s="137"/>
+      <c r="H73" s="128"/>
+      <c r="I73" s="133"/>
     </row>
     <row r="74" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
-      <c r="B74" s="131" t="s">
-        <v>123</v>
-      </c>
-      <c r="C74" s="132" t="s">
-        <v>125</v>
-      </c>
-      <c r="D74" s="162">
+      <c r="B74" s="127" t="s">
+        <v>122</v>
+      </c>
+      <c r="C74" s="128" t="s">
+        <v>124</v>
+      </c>
+      <c r="D74" s="157">
         <f>(D10-D70)/D67</f>
         <v>5.7833333333333341</v>
       </c>
-      <c r="E74" s="134" t="s">
-        <v>54</v>
-      </c>
-      <c r="F74" s="135"/>
-      <c r="G74" s="136" t="str">
+      <c r="E74" s="130" t="s">
+        <v>53</v>
+      </c>
+      <c r="F74" s="131" t="s">
+        <v>340</v>
+      </c>
+      <c r="G74" s="132" t="str">
         <f t="shared" si="1"/>
         <v>Ver</v>
       </c>
-      <c r="H74" s="132"/>
-      <c r="I74" s="137"/>
+      <c r="H74" s="128"/>
+      <c r="I74" s="133"/>
     </row>
     <row r="75" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
-      <c r="B75" s="131" t="s">
-        <v>124</v>
-      </c>
-      <c r="C75" s="132" t="s">
-        <v>126</v>
-      </c>
-      <c r="D75" s="162">
+      <c r="B75" s="127" t="s">
+        <v>123</v>
+      </c>
+      <c r="C75" s="128" t="s">
+        <v>125</v>
+      </c>
+      <c r="D75" s="157">
         <f>(D11-D71)/D68</f>
         <v>6.1000000000000005</v>
       </c>
-      <c r="E75" s="134" t="s">
+      <c r="E75" s="130" t="s">
+        <v>53</v>
+      </c>
+      <c r="F75" s="131" t="s">
+        <v>340</v>
+      </c>
+      <c r="G75" s="132" t="str">
+        <f t="shared" si="1"/>
+        <v>Ver</v>
+      </c>
+      <c r="H75" s="128"/>
+      <c r="I75" s="133"/>
+    </row>
+    <row r="76" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B76" s="164"/>
+      <c r="C76" s="165"/>
+      <c r="D76" s="166"/>
+      <c r="E76" s="166"/>
+      <c r="F76" s="167"/>
+      <c r="G76" s="140" t="str">
+        <f t="shared" si="1"/>
+        <v>Ver</v>
+      </c>
+      <c r="H76" s="165"/>
+      <c r="I76" s="116"/>
+    </row>
+    <row r="77" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B77" s="182" t="s">
+        <v>331</v>
+      </c>
+      <c r="C77" s="159"/>
+      <c r="D77" s="160"/>
+      <c r="E77" s="160"/>
+      <c r="F77" s="161"/>
+      <c r="G77" s="160"/>
+      <c r="H77" s="162"/>
+      <c r="I77" s="163"/>
+    </row>
+    <row r="78" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B78" s="127" t="s">
+        <v>173</v>
+      </c>
+      <c r="C78" s="177" t="s">
+        <v>172</v>
+      </c>
+      <c r="D78" s="178">
+        <f>D64</f>
+        <v>1435</v>
+      </c>
+      <c r="E78" s="178" t="s">
         <v>54</v>
       </c>
-      <c r="F75" s="135"/>
-      <c r="G75" s="136" t="str">
-        <f t="shared" si="1"/>
-        <v>Ver</v>
-      </c>
-      <c r="H75" s="132"/>
-      <c r="I75" s="137"/>
-    </row>
-    <row r="76" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B76" s="169"/>
-      <c r="C76" s="170"/>
-      <c r="D76" s="171"/>
-      <c r="E76" s="171"/>
-      <c r="F76" s="172"/>
-      <c r="G76" s="144" t="str">
-        <f t="shared" si="1"/>
-        <v>Ver</v>
-      </c>
-      <c r="H76" s="170"/>
-      <c r="I76" s="120"/>
-    </row>
-    <row r="77" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B77" s="173" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="79" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B79" s="51" t="s">
-        <v>335</v>
-      </c>
+      <c r="F78" s="131" t="s">
+        <v>313</v>
+      </c>
+      <c r="G78" s="132" t="str">
+        <f t="shared" ref="G78:G88" si="2">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F78,"/Readme.md"),"Ver")</f>
+        <v>Ver</v>
+      </c>
+      <c r="H78" s="128"/>
+      <c r="I78" s="133"/>
+    </row>
+    <row r="79" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="B79" s="127" t="s">
+        <v>174</v>
+      </c>
+      <c r="C79" s="177" t="s">
+        <v>175</v>
+      </c>
+      <c r="D79" s="178">
+        <f>D78*D63</f>
+        <v>57400</v>
+      </c>
+      <c r="E79" s="178" t="s">
+        <v>176</v>
+      </c>
+      <c r="F79" s="131" t="s">
+        <v>313</v>
+      </c>
+      <c r="G79" s="132" t="str">
+        <f t="shared" si="2"/>
+        <v>Ver</v>
+      </c>
+      <c r="H79" s="128"/>
+      <c r="I79" s="133"/>
     </row>
     <row r="80" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B80" s="150" t="s">
+      <c r="B80" s="127" t="s">
+        <v>185</v>
+      </c>
+      <c r="C80" s="177" t="s">
+        <v>184</v>
+      </c>
+      <c r="D80" s="178">
+        <f>D49</f>
+        <v>52.943999999999996</v>
+      </c>
+      <c r="E80" s="178" t="s">
+        <v>54</v>
+      </c>
+      <c r="F80" s="131" t="s">
+        <v>313</v>
+      </c>
+      <c r="G80" s="132" t="str">
+        <f t="shared" si="2"/>
+        <v>Ver</v>
+      </c>
+      <c r="H80" s="179"/>
+      <c r="I80" s="114"/>
+    </row>
+    <row r="81" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B81" s="127" t="s">
+        <v>178</v>
+      </c>
+      <c r="C81" s="177" t="s">
+        <v>179</v>
+      </c>
+      <c r="D81" s="178">
+        <f>D69</f>
+        <v>36</v>
+      </c>
+      <c r="E81" s="178" t="s">
+        <v>118</v>
+      </c>
+      <c r="F81" s="131" t="s">
+        <v>313</v>
+      </c>
+      <c r="G81" s="132" t="str">
+        <f t="shared" si="2"/>
+        <v>Ver</v>
+      </c>
+      <c r="H81" s="179"/>
+      <c r="I81" s="114"/>
+    </row>
+    <row r="82" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="B82" s="127" t="s">
+        <v>180</v>
+      </c>
+      <c r="C82" s="177" t="s">
+        <v>181</v>
+      </c>
+      <c r="D82" s="178">
+        <f>D81*D12</f>
+        <v>432</v>
+      </c>
+      <c r="E82" s="178" t="s">
+        <v>53</v>
+      </c>
+      <c r="F82" s="131" t="s">
+        <v>313</v>
+      </c>
+      <c r="G82" s="132" t="str">
+        <f t="shared" si="2"/>
+        <v>Ver</v>
+      </c>
+      <c r="H82" s="179"/>
+      <c r="I82" s="114"/>
+    </row>
+    <row r="83" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="B83" s="127" t="s">
+        <v>182</v>
+      </c>
+      <c r="C83" s="177" t="s">
+        <v>183</v>
+      </c>
+      <c r="D83" s="178">
+        <f>((D67*D9)+(D68*D8))*INT(D12/D48)</f>
+        <v>324</v>
+      </c>
+      <c r="E83" s="178" t="s">
+        <v>53</v>
+      </c>
+      <c r="F83" s="131" t="s">
+        <v>313</v>
+      </c>
+      <c r="G83" s="132" t="str">
+        <f t="shared" si="2"/>
+        <v>Ver</v>
+      </c>
+      <c r="H83" s="179"/>
+      <c r="I83" s="114"/>
+    </row>
+    <row r="84" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="B84" s="127" t="s">
+        <v>193</v>
+      </c>
+      <c r="C84" s="177" t="s">
+        <v>196</v>
+      </c>
+      <c r="D84" s="180" t="s">
+        <v>195</v>
+      </c>
+      <c r="E84" s="178" t="s">
+        <v>54</v>
+      </c>
+      <c r="F84" s="131" t="s">
+        <v>313</v>
+      </c>
+      <c r="G84" s="132" t="str">
+        <f t="shared" si="2"/>
+        <v>Ver</v>
+      </c>
+      <c r="H84" s="179"/>
+      <c r="I84" s="114">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="85" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B85" s="127" t="s">
+        <v>194</v>
+      </c>
+      <c r="C85" s="177" t="s">
+        <v>197</v>
+      </c>
+      <c r="D85" s="180">
+        <v>2</v>
+      </c>
+      <c r="E85" s="178" t="s">
+        <v>118</v>
+      </c>
+      <c r="F85" s="131" t="s">
+        <v>313</v>
+      </c>
+      <c r="G85" s="132" t="str">
+        <f t="shared" si="2"/>
+        <v>Ver</v>
+      </c>
+      <c r="H85" s="179"/>
+      <c r="I85" s="114"/>
+    </row>
+    <row r="86" spans="2:9" ht="50.4" x14ac:dyDescent="0.3">
+      <c r="B86" s="127" t="s">
+        <v>46</v>
+      </c>
+      <c r="C86" s="177" t="s">
+        <v>198</v>
+      </c>
+      <c r="D86" s="180" t="s">
+        <v>195</v>
+      </c>
+      <c r="E86" s="178" t="s">
+        <v>118</v>
+      </c>
+      <c r="F86" s="131" t="s">
+        <v>313</v>
+      </c>
+      <c r="G86" s="132" t="str">
+        <f t="shared" si="2"/>
+        <v>Ver</v>
+      </c>
+      <c r="H86" s="179"/>
+      <c r="I86" s="114"/>
+    </row>
+    <row r="87" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="B87" s="127" t="s">
+        <v>47</v>
+      </c>
+      <c r="C87" s="177" t="s">
+        <v>199</v>
+      </c>
+      <c r="D87" s="180" t="s">
+        <v>195</v>
+      </c>
+      <c r="E87" s="178" t="s">
+        <v>118</v>
+      </c>
+      <c r="F87" s="131" t="s">
+        <v>313</v>
+      </c>
+      <c r="G87" s="132" t="str">
+        <f t="shared" si="2"/>
+        <v>Ver</v>
+      </c>
+      <c r="H87" s="179"/>
+      <c r="I87" s="114"/>
+    </row>
+    <row r="88" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B88" s="136"/>
+      <c r="C88" s="181"/>
+      <c r="D88" s="166"/>
+      <c r="E88" s="166"/>
+      <c r="F88" s="167"/>
+      <c r="G88" s="140" t="str">
+        <f t="shared" si="2"/>
+        <v>Ver</v>
+      </c>
+      <c r="H88" s="165"/>
+      <c r="I88" s="116"/>
+    </row>
+    <row r="89" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B89" s="168" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="90" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H90" s="141" t="s">
+        <v>276</v>
+      </c>
+      <c r="I90" s="120">
+        <f>AVERAGE(I7:I88)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="91" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B91" s="47" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="92" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B92" s="146" t="s">
+        <v>153</v>
+      </c>
+      <c r="C92" s="169" t="s">
         <v>154</v>
       </c>
-      <c r="C80" s="174" t="s">
+    </row>
+    <row r="93" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B93" s="170" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="81" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B81" s="175" t="s">
-        <v>156</v>
-      </c>
-      <c r="C81" s="176">
+      <c r="C93" s="171">
         <f>D17</f>
         <v>1925</v>
       </c>
     </row>
-    <row r="82" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B82" s="175" t="s">
-        <v>159</v>
-      </c>
-      <c r="C82" s="176">
+    <row r="94" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B94" s="170" t="s">
+        <v>158</v>
+      </c>
+      <c r="C94" s="171">
         <f>D18</f>
         <v>1435</v>
       </c>
     </row>
-    <row r="83" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B83" s="175" t="s">
-        <v>158</v>
-      </c>
-      <c r="C83" s="176">
+    <row r="95" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B95" s="170" t="s">
+        <v>157</v>
+      </c>
+      <c r="C95" s="171">
         <f>D46</f>
         <v>60</v>
       </c>
     </row>
-    <row r="84" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B84" s="175" t="s">
-        <v>46</v>
-      </c>
-      <c r="C84" s="176">
+    <row r="96" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B96" s="170" t="s">
+        <v>45</v>
+      </c>
+      <c r="C96" s="171">
         <f>D54</f>
         <v>7.0560000000000018</v>
       </c>
     </row>
-    <row r="85" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B85" s="175" t="s">
-        <v>45</v>
-      </c>
-      <c r="C85" s="176">
+    <row r="97" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B97" s="170" t="s">
+        <v>44</v>
+      </c>
+      <c r="C97" s="171">
         <f>D49</f>
         <v>52.943999999999996</v>
       </c>
     </row>
-    <row r="86" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B86" s="177" t="s">
-        <v>157</v>
-      </c>
-      <c r="C86" s="178">
+    <row r="98" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B98" s="172" t="s">
+        <v>156</v>
+      </c>
+      <c r="C98" s="173">
         <f>D19</f>
         <v>1495</v>
       </c>
     </row>
-    <row r="87" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B87" s="179" t="s">
-        <v>68</v>
-      </c>
-      <c r="C87" s="180">
+    <row r="99" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B99" s="174" t="s">
+        <v>67</v>
+      </c>
+      <c r="C99" s="175">
         <f>D20</f>
         <v>0.74545454545454548</v>
       </c>
     </row>
-    <row r="88" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B88" s="169" t="s">
-        <v>103</v>
-      </c>
-      <c r="C88" s="181">
+    <row r="100" spans="2:3" x14ac:dyDescent="0.3">
+      <c r="B100" s="164" t="s">
+        <v>102</v>
+      </c>
+      <c r="C100" s="176">
         <f>D21</f>
         <v>0.77662337662337666</v>
       </c>
     </row>
-    <row r="90" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B90" s="51" t="s">
-        <v>336</v>
-      </c>
-    </row>
-    <row r="91" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B91" s="150" t="s">
-        <v>154</v>
-      </c>
-      <c r="C91" s="151" t="s">
-        <v>38</v>
-      </c>
-      <c r="D91" s="116" t="s">
-        <v>49</v>
-      </c>
-      <c r="E91" s="116" t="s">
-        <v>50</v>
-      </c>
-      <c r="F91" s="128" t="s">
-        <v>39</v>
-      </c>
-      <c r="G91" s="129"/>
-      <c r="H91" s="151" t="s">
-        <v>26</v>
-      </c>
-      <c r="I91" s="155" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="92" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B92" s="131" t="s">
-        <v>174</v>
-      </c>
-      <c r="C92" s="182" t="s">
-        <v>173</v>
-      </c>
-      <c r="D92" s="183">
-        <f>D64</f>
-        <v>1435</v>
-      </c>
-      <c r="E92" s="183" t="s">
-        <v>55</v>
-      </c>
-      <c r="F92" s="135"/>
-      <c r="G92" s="136" t="str">
-        <f t="shared" ref="G92:G102" si="2">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F92,"/Readme.md"),"Ver")</f>
-        <v>Ver</v>
-      </c>
-      <c r="H92" s="132"/>
-      <c r="I92" s="137"/>
-    </row>
-    <row r="93" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="B93" s="131" t="s">
-        <v>175</v>
-      </c>
-      <c r="C93" s="182" t="s">
-        <v>176</v>
-      </c>
-      <c r="D93" s="183">
-        <f>D92*D63</f>
-        <v>57400</v>
-      </c>
-      <c r="E93" s="183" t="s">
-        <v>177</v>
-      </c>
-      <c r="F93" s="135"/>
-      <c r="G93" s="136" t="str">
-        <f t="shared" si="2"/>
-        <v>Ver</v>
-      </c>
-      <c r="H93" s="132"/>
-      <c r="I93" s="137"/>
-    </row>
-    <row r="94" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B94" s="131" t="s">
-        <v>186</v>
-      </c>
-      <c r="C94" s="182" t="s">
-        <v>185</v>
-      </c>
-      <c r="D94" s="183">
-        <f>D49</f>
-        <v>52.943999999999996</v>
-      </c>
-      <c r="E94" s="183" t="s">
-        <v>55</v>
-      </c>
-      <c r="F94" s="184"/>
-      <c r="G94" s="136" t="str">
-        <f t="shared" si="2"/>
-        <v>Ver</v>
-      </c>
-      <c r="H94" s="185"/>
-      <c r="I94" s="118"/>
-    </row>
-    <row r="95" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B95" s="131" t="s">
-        <v>179</v>
-      </c>
-      <c r="C95" s="182" t="s">
-        <v>180</v>
-      </c>
-      <c r="D95" s="183">
-        <f>D69</f>
-        <v>36</v>
-      </c>
-      <c r="E95" s="183" t="s">
-        <v>119</v>
-      </c>
-      <c r="F95" s="184"/>
-      <c r="G95" s="136" t="str">
-        <f t="shared" si="2"/>
-        <v>Ver</v>
-      </c>
-      <c r="H95" s="185"/>
-      <c r="I95" s="118"/>
-    </row>
-    <row r="96" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="B96" s="131" t="s">
-        <v>181</v>
-      </c>
-      <c r="C96" s="182" t="s">
-        <v>182</v>
-      </c>
-      <c r="D96" s="183">
-        <f>D95*D12</f>
-        <v>432</v>
-      </c>
-      <c r="E96" s="183" t="s">
-        <v>54</v>
-      </c>
-      <c r="F96" s="184"/>
-      <c r="G96" s="136" t="str">
-        <f t="shared" si="2"/>
-        <v>Ver</v>
-      </c>
-      <c r="H96" s="185"/>
-      <c r="I96" s="118"/>
-    </row>
-    <row r="97" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="B97" s="131" t="s">
-        <v>183</v>
-      </c>
-      <c r="C97" s="182" t="s">
-        <v>184</v>
-      </c>
-      <c r="D97" s="183">
-        <f>((D67*D9)+(D68*D8))*INT(D12/D48)</f>
-        <v>324</v>
-      </c>
-      <c r="E97" s="183" t="s">
-        <v>54</v>
-      </c>
-      <c r="F97" s="184"/>
-      <c r="G97" s="136" t="str">
-        <f t="shared" si="2"/>
-        <v>Ver</v>
-      </c>
-      <c r="H97" s="185"/>
-      <c r="I97" s="118"/>
-    </row>
-    <row r="98" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="B98" s="131" t="s">
-        <v>194</v>
-      </c>
-      <c r="C98" s="182" t="s">
-        <v>197</v>
-      </c>
-      <c r="D98" s="186" t="s">
-        <v>196</v>
-      </c>
-      <c r="E98" s="183" t="s">
-        <v>55</v>
-      </c>
-      <c r="F98" s="184"/>
-      <c r="G98" s="136" t="str">
-        <f t="shared" si="2"/>
-        <v>Ver</v>
-      </c>
-      <c r="H98" s="185"/>
-      <c r="I98" s="118">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="99" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B99" s="131" t="s">
-        <v>195</v>
-      </c>
-      <c r="C99" s="182" t="s">
-        <v>198</v>
-      </c>
-      <c r="D99" s="186">
-        <v>2</v>
-      </c>
-      <c r="E99" s="183" t="s">
-        <v>119</v>
-      </c>
-      <c r="F99" s="184"/>
-      <c r="G99" s="136" t="str">
-        <f t="shared" si="2"/>
-        <v>Ver</v>
-      </c>
-      <c r="H99" s="185"/>
-      <c r="I99" s="118"/>
-    </row>
-    <row r="100" spans="2:9" ht="50.4" x14ac:dyDescent="0.3">
-      <c r="B100" s="131" t="s">
-        <v>47</v>
-      </c>
-      <c r="C100" s="182" t="s">
-        <v>199</v>
-      </c>
-      <c r="D100" s="186" t="s">
-        <v>196</v>
-      </c>
-      <c r="E100" s="183" t="s">
-        <v>119</v>
-      </c>
-      <c r="F100" s="184"/>
-      <c r="G100" s="136" t="str">
-        <f t="shared" si="2"/>
-        <v>Ver</v>
-      </c>
-      <c r="H100" s="185"/>
-      <c r="I100" s="118"/>
-    </row>
-    <row r="101" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="B101" s="131" t="s">
-        <v>48</v>
-      </c>
-      <c r="C101" s="182" t="s">
-        <v>200</v>
-      </c>
-      <c r="D101" s="186" t="s">
-        <v>196</v>
-      </c>
-      <c r="E101" s="183" t="s">
-        <v>119</v>
-      </c>
-      <c r="F101" s="184"/>
-      <c r="G101" s="136" t="str">
-        <f t="shared" si="2"/>
-        <v>Ver</v>
-      </c>
-      <c r="H101" s="185"/>
-      <c r="I101" s="118"/>
-    </row>
-    <row r="102" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B102" s="140"/>
-      <c r="C102" s="187"/>
-      <c r="D102" s="171"/>
-      <c r="E102" s="171"/>
-      <c r="F102" s="172"/>
-      <c r="G102" s="144" t="str">
-        <f t="shared" si="2"/>
-        <v>Ver</v>
-      </c>
-      <c r="H102" s="170"/>
-      <c r="I102" s="120"/>
-    </row>
-    <row r="103" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B103" s="188"/>
-      <c r="C103" s="188"/>
-      <c r="H103" s="145" t="s">
-        <v>277</v>
-      </c>
-      <c r="I103" s="124">
-        <f>AVERAGE(I7:I102)</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="104" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B104" s="188"/>
-      <c r="C104" s="188"/>
-    </row>
-    <row r="105" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B105" s="188"/>
-      <c r="C105" s="188"/>
-    </row>
-    <row r="106" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B106" s="188"/>
-      <c r="C106" s="188"/>
-    </row>
-    <row r="107" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B107" s="188"/>
-      <c r="C107" s="188"/>
-    </row>
-    <row r="108" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B108" s="188"/>
-      <c r="C108" s="188"/>
-    </row>
-    <row r="109" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B109" s="188"/>
-      <c r="C109" s="188"/>
-    </row>
-    <row r="110" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B110" s="188"/>
-      <c r="C110" s="188"/>
-    </row>
-    <row r="111" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B111" s="188"/>
-      <c r="C111" s="188"/>
-    </row>
-    <row r="112" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B112" s="188"/>
-      <c r="C112" s="188"/>
-    </row>
-    <row r="113" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B113" s="188"/>
-      <c r="C113" s="188"/>
-    </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="2">
     <mergeCell ref="B4:I5"/>
     <mergeCell ref="F6:G6"/>
-    <mergeCell ref="F91:G91"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -5750,10 +5780,11 @@
     <col min="2" max="2" width="30.77734375" customWidth="1"/>
     <col min="3" max="3" width="50.77734375" customWidth="1"/>
     <col min="4" max="5" width="10.77734375" customWidth="1"/>
-    <col min="6" max="6" width="7.77734375" style="60" customWidth="1"/>
+    <col min="6" max="6" width="7.77734375" style="56" customWidth="1"/>
     <col min="7" max="7" width="3.77734375" customWidth="1"/>
-    <col min="8" max="8" width="30.77734375" style="60" customWidth="1"/>
-    <col min="9" max="9" width="12.77734375" style="43" customWidth="1"/>
+    <col min="8" max="8" width="30.77734375" style="56" customWidth="1"/>
+    <col min="9" max="9" width="12.77734375" style="39" customWidth="1"/>
+    <col min="10" max="10" width="2.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
@@ -5762,474 +5793,508 @@
       </c>
     </row>
     <row r="3" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="B3" s="13" t="s">
-        <v>160</v>
+      <c r="B3" s="9" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="4" spans="2:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="78" t="s">
-        <v>229</v>
-      </c>
-      <c r="C4" s="78"/>
-      <c r="D4" s="78"/>
-      <c r="E4" s="78"/>
-      <c r="F4" s="78"/>
-      <c r="G4" s="78"/>
-      <c r="H4" s="78"/>
-      <c r="I4" s="78"/>
+      <c r="B4" s="74" t="s">
+        <v>228</v>
+      </c>
+      <c r="C4" s="74"/>
+      <c r="D4" s="74"/>
+      <c r="E4" s="74"/>
+      <c r="F4" s="74"/>
+      <c r="G4" s="74"/>
+      <c r="H4" s="74"/>
+      <c r="I4" s="74"/>
     </row>
     <row r="5" spans="2:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="83"/>
-      <c r="C5" s="83"/>
-      <c r="D5" s="83"/>
-      <c r="E5" s="83"/>
-      <c r="F5" s="83"/>
-      <c r="G5" s="83"/>
-      <c r="H5" s="83"/>
-      <c r="I5" s="83"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
     </row>
     <row r="6" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="B6" s="27" t="s">
+      <c r="B6" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="28" t="s">
+      <c r="D6" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="F6" s="85" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="29" t="s">
-        <v>49</v>
-      </c>
-      <c r="E6" s="29" t="s">
-        <v>50</v>
-      </c>
-      <c r="F6" s="89" t="s">
-        <v>39</v>
-      </c>
-      <c r="G6" s="90"/>
-      <c r="H6" s="28" t="s">
+      <c r="G6" s="86"/>
+      <c r="H6" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="I6" s="45" t="s">
+      <c r="I6" s="41" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B7" s="5" t="s">
-        <v>337</v>
-      </c>
-      <c r="C7" s="23"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="93"/>
-      <c r="G7" s="24"/>
-      <c r="H7" s="58"/>
-      <c r="I7" s="46"/>
+        <v>332</v>
+      </c>
+      <c r="C7" s="17"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="89"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="54"/>
+      <c r="I7" s="42"/>
     </row>
     <row r="8" spans="2:9" ht="57" x14ac:dyDescent="0.3">
-      <c r="B8" s="22" t="s">
+      <c r="B8" s="16" t="s">
+        <v>216</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>300</v>
+      </c>
+      <c r="D8" s="15">
+        <v>1</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="F8" s="87" t="s">
+        <v>340</v>
+      </c>
+      <c r="G8" s="81" t="str">
+        <f t="shared" ref="G8:G21" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F8,"/Readme.md"),"Ver")</f>
+        <v>Ver</v>
+      </c>
+      <c r="H8" s="19"/>
+      <c r="I8" s="43">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="B9" s="16" t="s">
+        <v>218</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="D9" s="15">
+        <v>1</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="F9" s="87" t="s">
+        <v>341</v>
+      </c>
+      <c r="G9" s="81" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H9" s="19"/>
+      <c r="I9" s="43"/>
+    </row>
+    <row r="10" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="B10" s="16" t="s">
         <v>217</v>
       </c>
-      <c r="C8" s="25" t="s">
-        <v>302</v>
-      </c>
-      <c r="D8" s="21">
+      <c r="C10" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="D10" s="15">
         <v>1</v>
       </c>
-      <c r="E8" s="21" t="s">
-        <v>119</v>
-      </c>
-      <c r="F8" s="91"/>
-      <c r="G8" s="85" t="str">
-        <f t="shared" ref="G8:G21" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F8,"/Readme.md"),"Ver")</f>
-        <v>Ver</v>
-      </c>
-      <c r="H8" s="25"/>
-      <c r="I8" s="47">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="B9" s="22" t="s">
+      <c r="E10" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="F10" s="87" t="s">
+        <v>341</v>
+      </c>
+      <c r="G10" s="81" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H10" s="19"/>
+      <c r="I10" s="43"/>
+    </row>
+    <row r="11" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="B11" s="16" t="s">
         <v>219</v>
       </c>
-      <c r="C9" s="25" t="s">
+      <c r="C11" s="19" t="s">
+        <v>224</v>
+      </c>
+      <c r="D11" s="15">
+        <v>1</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="F11" s="87" t="s">
+        <v>341</v>
+      </c>
+      <c r="G11" s="81" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H11" s="19"/>
+      <c r="I11" s="43"/>
+    </row>
+    <row r="12" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="B12" s="27" t="s">
+        <v>205</v>
+      </c>
+      <c r="C12" s="19" t="s">
         <v>222</v>
       </c>
-      <c r="D9" s="21">
+      <c r="D12" s="15">
         <v>1</v>
       </c>
-      <c r="E9" s="21" t="s">
-        <v>119</v>
-      </c>
-      <c r="F9" s="91"/>
-      <c r="G9" s="85" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H9" s="25"/>
-      <c r="I9" s="47"/>
-    </row>
-    <row r="10" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="B10" s="22" t="s">
-        <v>218</v>
-      </c>
-      <c r="C10" s="25" t="s">
-        <v>222</v>
-      </c>
-      <c r="D10" s="21">
+      <c r="E12" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="F12" s="87" t="s">
+        <v>341</v>
+      </c>
+      <c r="G12" s="81" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H12" s="28"/>
+      <c r="I12" s="44"/>
+    </row>
+    <row r="13" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="B13" s="27" t="s">
+        <v>220</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>223</v>
+      </c>
+      <c r="D13" s="15">
         <v>1</v>
       </c>
-      <c r="E10" s="21" t="s">
-        <v>119</v>
-      </c>
-      <c r="F10" s="91"/>
-      <c r="G10" s="85" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H10" s="25"/>
-      <c r="I10" s="47"/>
-    </row>
-    <row r="11" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B11" s="22" t="s">
-        <v>220</v>
-      </c>
-      <c r="C11" s="25" t="s">
-        <v>225</v>
-      </c>
-      <c r="D11" s="21">
+      <c r="E13" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="F13" s="87" t="s">
+        <v>341</v>
+      </c>
+      <c r="G13" s="81" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H13" s="28"/>
+      <c r="I13" s="44"/>
+    </row>
+    <row r="14" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="B14" s="16" t="s">
+        <v>200</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>204</v>
+      </c>
+      <c r="D14" s="15">
         <v>1</v>
       </c>
-      <c r="E11" s="21" t="s">
-        <v>119</v>
-      </c>
-      <c r="F11" s="91"/>
-      <c r="G11" s="85" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H11" s="25"/>
-      <c r="I11" s="47"/>
-    </row>
-    <row r="12" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B12" s="33" t="s">
-        <v>206</v>
-      </c>
-      <c r="C12" s="25" t="s">
-        <v>223</v>
-      </c>
-      <c r="D12" s="21">
+      <c r="E14" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="F14" s="87" t="s">
+        <v>316</v>
+      </c>
+      <c r="G14" s="81" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H14" s="19"/>
+      <c r="I14" s="43"/>
+    </row>
+    <row r="15" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="B15" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>204</v>
+      </c>
+      <c r="D15" s="15">
         <v>1</v>
       </c>
-      <c r="E12" s="21" t="s">
-        <v>119</v>
-      </c>
-      <c r="F12" s="94"/>
-      <c r="G12" s="85" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H12" s="34"/>
-      <c r="I12" s="48"/>
-    </row>
-    <row r="13" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="B13" s="33" t="s">
-        <v>221</v>
-      </c>
-      <c r="C13" s="25" t="s">
-        <v>224</v>
-      </c>
-      <c r="D13" s="21">
+      <c r="E15" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="F15" s="87" t="s">
+        <v>316</v>
+      </c>
+      <c r="G15" s="81" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H15" s="19"/>
+      <c r="I15" s="43"/>
+    </row>
+    <row r="16" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="B16" s="27" t="s">
+        <v>202</v>
+      </c>
+      <c r="C16" s="19" t="s">
+        <v>204</v>
+      </c>
+      <c r="D16" s="15">
         <v>1</v>
       </c>
-      <c r="E13" s="21" t="s">
-        <v>119</v>
-      </c>
-      <c r="F13" s="94"/>
-      <c r="G13" s="85" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H13" s="34"/>
-      <c r="I13" s="48"/>
-    </row>
-    <row r="14" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="B14" s="22" t="s">
-        <v>201</v>
-      </c>
-      <c r="C14" s="25" t="s">
-        <v>205</v>
-      </c>
-      <c r="D14" s="21">
+      <c r="E16" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="F16" s="87" t="s">
+        <v>316</v>
+      </c>
+      <c r="G16" s="81" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H16" s="28"/>
+      <c r="I16" s="44"/>
+    </row>
+    <row r="17" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="B17" s="27" t="s">
+        <v>265</v>
+      </c>
+      <c r="C17" s="19" t="s">
+        <v>204</v>
+      </c>
+      <c r="D17" s="15">
         <v>1</v>
       </c>
-      <c r="E14" s="21" t="s">
-        <v>119</v>
-      </c>
-      <c r="F14" s="91"/>
-      <c r="G14" s="85" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H14" s="25"/>
-      <c r="I14" s="47"/>
-    </row>
-    <row r="15" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="B15" s="22" t="s">
-        <v>202</v>
-      </c>
-      <c r="C15" s="25" t="s">
-        <v>205</v>
-      </c>
-      <c r="D15" s="21">
+      <c r="E17" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="F17" s="87" t="s">
+        <v>316</v>
+      </c>
+      <c r="G17" s="81" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H17" s="28"/>
+      <c r="I17" s="44"/>
+    </row>
+    <row r="18" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="B18" s="27" t="s">
+        <v>203</v>
+      </c>
+      <c r="C18" s="19" t="s">
+        <v>204</v>
+      </c>
+      <c r="D18" s="15">
         <v>1</v>
       </c>
-      <c r="E15" s="21" t="s">
-        <v>119</v>
-      </c>
-      <c r="F15" s="91"/>
-      <c r="G15" s="85" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H15" s="25"/>
-      <c r="I15" s="47"/>
-    </row>
-    <row r="16" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="B16" s="33" t="s">
-        <v>203</v>
-      </c>
-      <c r="C16" s="25" t="s">
-        <v>205</v>
-      </c>
-      <c r="D16" s="21">
+      <c r="E18" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="F18" s="87" t="s">
+        <v>316</v>
+      </c>
+      <c r="G18" s="81" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H18" s="28"/>
+      <c r="I18" s="44"/>
+    </row>
+    <row r="19" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="B19" s="27" t="s">
+        <v>214</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>204</v>
+      </c>
+      <c r="D19" s="29">
         <v>1</v>
       </c>
-      <c r="E16" s="21" t="s">
-        <v>119</v>
-      </c>
-      <c r="F16" s="94"/>
-      <c r="G16" s="85" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H16" s="34"/>
-      <c r="I16" s="48"/>
-    </row>
-    <row r="17" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="B17" s="33" t="s">
-        <v>266</v>
-      </c>
-      <c r="C17" s="25" t="s">
-        <v>205</v>
-      </c>
-      <c r="D17" s="21">
+      <c r="E19" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="F19" s="87" t="s">
+        <v>340</v>
+      </c>
+      <c r="G19" s="81" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H19" s="28"/>
+      <c r="I19" s="44"/>
+    </row>
+    <row r="20" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="B20" s="27" t="s">
+        <v>215</v>
+      </c>
+      <c r="C20" s="19" t="s">
+        <v>204</v>
+      </c>
+      <c r="D20" s="29">
         <v>1</v>
       </c>
-      <c r="E17" s="21" t="s">
-        <v>119</v>
-      </c>
-      <c r="F17" s="94"/>
-      <c r="G17" s="85" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H17" s="34"/>
-      <c r="I17" s="48"/>
-    </row>
-    <row r="18" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="B18" s="33" t="s">
-        <v>204</v>
-      </c>
-      <c r="C18" s="25" t="s">
-        <v>205</v>
-      </c>
-      <c r="D18" s="21">
-        <v>1</v>
-      </c>
-      <c r="E18" s="21" t="s">
-        <v>119</v>
-      </c>
-      <c r="F18" s="94"/>
-      <c r="G18" s="85" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H18" s="34"/>
-      <c r="I18" s="48"/>
-    </row>
-    <row r="19" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="B19" s="33" t="s">
-        <v>215</v>
-      </c>
-      <c r="C19" s="25" t="s">
-        <v>205</v>
-      </c>
-      <c r="D19" s="35">
-        <v>1</v>
-      </c>
-      <c r="E19" s="21" t="s">
-        <v>119</v>
-      </c>
-      <c r="F19" s="94"/>
-      <c r="G19" s="85" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H19" s="34"/>
-      <c r="I19" s="48"/>
-    </row>
-    <row r="20" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="B20" s="33" t="s">
-        <v>216</v>
-      </c>
-      <c r="C20" s="25" t="s">
-        <v>205</v>
-      </c>
-      <c r="D20" s="35">
-        <v>1</v>
-      </c>
-      <c r="E20" s="21" t="s">
-        <v>119</v>
-      </c>
-      <c r="F20" s="94"/>
-      <c r="G20" s="85" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H20" s="34"/>
-      <c r="I20" s="48"/>
+      <c r="E20" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="F20" s="87" t="s">
+        <v>340</v>
+      </c>
+      <c r="G20" s="81" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H20" s="28"/>
+      <c r="I20" s="44"/>
     </row>
     <row r="21" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="B21" s="33"/>
-      <c r="C21" s="34"/>
-      <c r="D21" s="35"/>
-      <c r="E21" s="35"/>
-      <c r="F21" s="94"/>
-      <c r="G21" s="86" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H21" s="34"/>
-      <c r="I21" s="48"/>
+      <c r="B21" s="27"/>
+      <c r="C21" s="28"/>
+      <c r="D21" s="29"/>
+      <c r="E21" s="29"/>
+      <c r="F21" s="90"/>
+      <c r="G21" s="82" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H21" s="28"/>
+      <c r="I21" s="44"/>
     </row>
     <row r="22" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B22" s="5" t="s">
-        <v>338</v>
-      </c>
-      <c r="C22" s="23"/>
-      <c r="D22" s="24"/>
-      <c r="E22" s="24"/>
-      <c r="F22" s="93"/>
-      <c r="G22" s="24"/>
-      <c r="H22" s="58"/>
-      <c r="I22" s="46"/>
+        <v>333</v>
+      </c>
+      <c r="C22" s="17"/>
+      <c r="D22" s="18"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="89"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="54"/>
+      <c r="I22" s="42"/>
     </row>
     <row r="23" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
-      <c r="B23" s="22" t="s">
-        <v>207</v>
-      </c>
-      <c r="C23" s="25" t="s">
-        <v>210</v>
-      </c>
-      <c r="D23" s="36">
+      <c r="B23" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="C23" s="19" t="s">
+        <v>209</v>
+      </c>
+      <c r="D23" s="30">
         <f>'2.ArquitectonicaEstructural'!D31-'2.ArquitectonicaEstructural'!D37-'2.ArquitectonicaEstructural'!D43</f>
         <v>1135.04</v>
       </c>
-      <c r="E23" s="21" t="s">
-        <v>55</v>
-      </c>
-      <c r="F23" s="91"/>
-      <c r="G23" s="85" t="str">
+      <c r="E23" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="F23" s="87" t="s">
+        <v>313</v>
+      </c>
+      <c r="G23" s="81" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F23,"/Readme.md"),"Ver")</f>
         <v>Ver</v>
       </c>
-      <c r="H23" s="25"/>
-      <c r="I23" s="47">
+      <c r="H23" s="19"/>
+      <c r="I23" s="43">
         <v>5</v>
       </c>
     </row>
     <row r="24" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="B24" s="22" t="s">
-        <v>209</v>
-      </c>
-      <c r="C24" s="25" t="s">
+      <c r="B24" s="16" t="s">
+        <v>208</v>
+      </c>
+      <c r="C24" s="19" t="s">
+        <v>211</v>
+      </c>
+      <c r="D24" s="20">
+        <v>992</v>
+      </c>
+      <c r="E24" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="F24" s="87" t="s">
+        <v>313</v>
+      </c>
+      <c r="G24" s="81" t="str">
+        <f t="shared" ref="G24:G27" si="1">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F24,"/Readme.md"),"Ver")</f>
+        <v>Ver</v>
+      </c>
+      <c r="H24" s="19"/>
+      <c r="I24" s="43"/>
+    </row>
+    <row r="25" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="B25" s="16" t="s">
+        <v>207</v>
+      </c>
+      <c r="C25" s="19" t="s">
         <v>212</v>
       </c>
-      <c r="D24" s="26">
-        <v>992</v>
-      </c>
-      <c r="E24" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="F24" s="91"/>
-      <c r="G24" s="85" t="str">
-        <f t="shared" ref="G24:G27" si="1">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F24,"/Readme.md"),"Ver")</f>
-        <v>Ver</v>
-      </c>
-      <c r="H24" s="25"/>
-      <c r="I24" s="47"/>
-    </row>
-    <row r="25" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="B25" s="22" t="s">
-        <v>208</v>
-      </c>
-      <c r="C25" s="25" t="s">
+      <c r="D25" s="20">
+        <v>1950</v>
+      </c>
+      <c r="E25" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="F25" s="87" t="s">
+        <v>313</v>
+      </c>
+      <c r="G25" s="81" t="str">
+        <f t="shared" si="1"/>
+        <v>Ver</v>
+      </c>
+      <c r="H25" s="19"/>
+      <c r="I25" s="43"/>
+    </row>
+    <row r="26" spans="2:9" ht="45.6" x14ac:dyDescent="0.3">
+      <c r="B26" s="16" t="s">
+        <v>210</v>
+      </c>
+      <c r="C26" s="19" t="s">
         <v>213</v>
       </c>
-      <c r="D25" s="26">
-        <v>1950</v>
-      </c>
-      <c r="E25" s="21" t="s">
-        <v>65</v>
-      </c>
-      <c r="F25" s="91"/>
-      <c r="G25" s="85" t="str">
-        <f t="shared" si="1"/>
-        <v>Ver</v>
-      </c>
-      <c r="H25" s="25"/>
-      <c r="I25" s="47"/>
-    </row>
-    <row r="26" spans="2:9" ht="45.6" x14ac:dyDescent="0.3">
-      <c r="B26" s="22" t="s">
-        <v>211</v>
-      </c>
-      <c r="C26" s="25" t="s">
-        <v>214</v>
-      </c>
-      <c r="D26" s="21">
+      <c r="D26" s="15">
         <f>INT(D23/(D24/1000*D25/1000))</f>
         <v>586</v>
       </c>
-      <c r="E26" s="21" t="s">
-        <v>119</v>
-      </c>
-      <c r="F26" s="91"/>
-      <c r="G26" s="85" t="str">
+      <c r="E26" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="F26" s="87" t="s">
+        <v>313</v>
+      </c>
+      <c r="G26" s="81" t="str">
         <f t="shared" si="1"/>
         <v>Ver</v>
       </c>
-      <c r="H26" s="25"/>
-      <c r="I26" s="47"/>
+      <c r="H26" s="19"/>
+      <c r="I26" s="43"/>
     </row>
     <row r="27" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="B27" s="30"/>
-      <c r="C27" s="31"/>
-      <c r="D27" s="32"/>
-      <c r="E27" s="32"/>
-      <c r="F27" s="92"/>
-      <c r="G27" s="86" t="str">
+      <c r="B27" s="24"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="26"/>
+      <c r="E27" s="26"/>
+      <c r="F27" s="88"/>
+      <c r="G27" s="82" t="str">
         <f t="shared" si="1"/>
         <v>Ver</v>
       </c>
-      <c r="H27" s="31"/>
-      <c r="I27" s="49"/>
+      <c r="H27" s="25"/>
+      <c r="I27" s="45"/>
     </row>
     <row r="28" spans="2:9" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="H28" s="50" t="s">
-        <v>277</v>
-      </c>
-      <c r="I28" s="61">
+      <c r="H28" s="46" t="s">
+        <v>276</v>
+      </c>
+      <c r="I28" s="57">
         <f>AVERAGE(I7:I27)</f>
         <v>5</v>
       </c>
@@ -6246,18 +6311,19 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61FBD0B4-938E-4D04-BE03-979DB3A57126}">
-  <dimension ref="B2:I24"/>
+  <dimension ref="B2:I23"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="16.8" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="2.5546875" style="1" customWidth="1"/>
     <col min="2" max="2" width="30.77734375" style="1" customWidth="1"/>
     <col min="3" max="3" width="50.77734375" style="1" customWidth="1"/>
     <col min="4" max="5" width="10.77734375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="7.77734375" style="15" customWidth="1"/>
+    <col min="6" max="6" width="7.77734375" style="11" customWidth="1"/>
     <col min="7" max="7" width="3.77734375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="30.77734375" style="15" customWidth="1"/>
-    <col min="9" max="9" width="12.77734375" style="61" customWidth="1"/>
-    <col min="10" max="16384" width="9.109375" style="1"/>
+    <col min="8" max="8" width="30.77734375" style="11" customWidth="1"/>
+    <col min="9" max="9" width="12.77734375" style="57" customWidth="1"/>
+    <col min="10" max="10" width="2.77734375" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:9" x14ac:dyDescent="0.4">
@@ -6266,381 +6332,392 @@
       </c>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B3" s="13" t="s">
-        <v>227</v>
+      <c r="B3" s="9" t="s">
+        <v>226</v>
       </c>
     </row>
     <row r="4" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="78" t="s">
-        <v>226</v>
-      </c>
-      <c r="C4" s="78"/>
-      <c r="D4" s="78"/>
-      <c r="E4" s="78"/>
-      <c r="F4" s="78"/>
-      <c r="G4" s="78"/>
-      <c r="H4" s="78"/>
-      <c r="I4" s="78"/>
+      <c r="B4" s="74" t="s">
+        <v>225</v>
+      </c>
+      <c r="C4" s="74"/>
+      <c r="D4" s="74"/>
+      <c r="E4" s="74"/>
+      <c r="F4" s="74"/>
+      <c r="G4" s="74"/>
+      <c r="H4" s="74"/>
+      <c r="I4" s="74"/>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B5" s="83"/>
-      <c r="C5" s="83"/>
-      <c r="D5" s="83"/>
-      <c r="E5" s="83"/>
-      <c r="F5" s="83"/>
-      <c r="G5" s="83"/>
-      <c r="H5" s="83"/>
-      <c r="I5" s="83"/>
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B6" s="27" t="s">
+      <c r="B6" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="22" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="28" t="s">
+      <c r="D6" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="F6" s="85" t="s">
         <v>38</v>
       </c>
-      <c r="D6" s="29" t="s">
-        <v>49</v>
-      </c>
-      <c r="E6" s="29" t="s">
-        <v>50</v>
-      </c>
-      <c r="F6" s="89" t="s">
-        <v>39</v>
-      </c>
-      <c r="G6" s="90"/>
-      <c r="H6" s="28" t="s">
+      <c r="G6" s="86"/>
+      <c r="H6" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="I6" s="45" t="s">
+      <c r="I6" s="41" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B7" s="5" t="s">
-        <v>339</v>
-      </c>
-      <c r="C7" s="23"/>
-      <c r="D7" s="24"/>
-      <c r="E7" s="24"/>
-      <c r="F7" s="93"/>
-      <c r="G7" s="24"/>
-      <c r="H7" s="58"/>
-      <c r="I7" s="46"/>
+        <v>334</v>
+      </c>
+      <c r="C7" s="17"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="89"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="54"/>
+      <c r="I7" s="42"/>
     </row>
     <row r="8" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
-      <c r="B8" s="22" t="s">
-        <v>230</v>
-      </c>
-      <c r="C8" s="25" t="s">
+      <c r="B8" s="16" t="s">
+        <v>229</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>235</v>
+      </c>
+      <c r="D8" s="20">
+        <v>3</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" s="87" t="s">
+        <v>340</v>
+      </c>
+      <c r="G8" s="81" t="str">
+        <f t="shared" ref="G8:G21" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F8,"/Readme.md"),"Ver")</f>
+        <v>Ver</v>
+      </c>
+      <c r="H8" s="19"/>
+      <c r="I8" s="43">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
+      <c r="B9" s="16" t="s">
+        <v>233</v>
+      </c>
+      <c r="C9" s="19" t="s">
         <v>236</v>
       </c>
-      <c r="D8" s="26">
-        <v>3</v>
-      </c>
-      <c r="E8" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="F8" s="91"/>
-      <c r="G8" s="85" t="str">
-        <f t="shared" ref="G8:G22" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F8,"/Readme.md"),"Ver")</f>
-        <v>Ver</v>
-      </c>
-      <c r="H8" s="25"/>
-      <c r="I8" s="47">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
-      <c r="B9" s="22" t="s">
+      <c r="D9" s="20">
+        <v>2.5</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F9" s="87" t="s">
+        <v>340</v>
+      </c>
+      <c r="G9" s="81" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H9" s="19"/>
+      <c r="I9" s="43"/>
+    </row>
+    <row r="10" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
+      <c r="B10" s="16" t="s">
+        <v>231</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>242</v>
+      </c>
+      <c r="D10" s="20">
+        <v>4</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>232</v>
+      </c>
+      <c r="F10" s="87" t="s">
+        <v>340</v>
+      </c>
+      <c r="G10" s="81" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H10" s="19"/>
+      <c r="I10" s="43"/>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B11" s="16" t="s">
         <v>234</v>
       </c>
-      <c r="C9" s="25" t="s">
+      <c r="C11" s="19" t="s">
         <v>237</v>
       </c>
-      <c r="D9" s="26">
-        <v>2.5</v>
-      </c>
-      <c r="E9" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="F9" s="91"/>
-      <c r="G9" s="85" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H9" s="25"/>
-      <c r="I9" s="47"/>
-    </row>
-    <row r="10" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
-      <c r="B10" s="22" t="s">
-        <v>232</v>
-      </c>
-      <c r="C10" s="25" t="s">
+      <c r="D11" s="20">
+        <v>2</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F11" s="87" t="s">
+        <v>340</v>
+      </c>
+      <c r="G11" s="81" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H11" s="19"/>
+      <c r="I11" s="43"/>
+    </row>
+    <row r="12" spans="2:9" ht="33.6" x14ac:dyDescent="0.4">
+      <c r="B12" s="16" t="s">
+        <v>239</v>
+      </c>
+      <c r="C12" s="19" t="s">
         <v>243</v>
       </c>
-      <c r="D10" s="26">
-        <v>4</v>
-      </c>
-      <c r="E10" s="21" t="s">
-        <v>233</v>
-      </c>
-      <c r="F10" s="91"/>
-      <c r="G10" s="85" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H10" s="25"/>
-      <c r="I10" s="47"/>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B11" s="22" t="s">
-        <v>235</v>
-      </c>
-      <c r="C11" s="25" t="s">
-        <v>238</v>
-      </c>
-      <c r="D11" s="26">
-        <v>2</v>
-      </c>
-      <c r="E11" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="F11" s="91"/>
-      <c r="G11" s="85" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H11" s="25"/>
-      <c r="I11" s="47"/>
-    </row>
-    <row r="12" spans="2:9" ht="33.6" x14ac:dyDescent="0.4">
-      <c r="B12" s="22" t="s">
-        <v>240</v>
-      </c>
-      <c r="C12" s="25" t="s">
-        <v>244</v>
-      </c>
-      <c r="D12" s="21">
+      <c r="D12" s="15">
         <f>D10*D11</f>
         <v>8</v>
       </c>
-      <c r="E12" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="F12" s="91"/>
-      <c r="G12" s="85" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H12" s="25"/>
-      <c r="I12" s="47"/>
+      <c r="E12" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F12" s="87" t="s">
+        <v>340</v>
+      </c>
+      <c r="G12" s="81" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H12" s="19"/>
+      <c r="I12" s="43"/>
     </row>
     <row r="13" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
-      <c r="B13" s="22" t="s">
-        <v>231</v>
-      </c>
-      <c r="C13" s="25" t="s">
-        <v>239</v>
-      </c>
-      <c r="D13" s="26">
+      <c r="B13" s="16" t="s">
+        <v>230</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="D13" s="20">
         <v>8</v>
       </c>
-      <c r="E13" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="F13" s="91"/>
-      <c r="G13" s="85" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H13" s="25"/>
-      <c r="I13" s="47"/>
+      <c r="E13" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F13" s="87" t="s">
+        <v>340</v>
+      </c>
+      <c r="G13" s="81" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H13" s="19"/>
+      <c r="I13" s="43"/>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B14" s="22" t="s">
-        <v>245</v>
-      </c>
-      <c r="C14" s="25" t="s">
-        <v>247</v>
-      </c>
-      <c r="D14" s="21" t="str">
+      <c r="B14" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>246</v>
+      </c>
+      <c r="D14" s="15" t="str">
         <f>IF(D12&lt;=D13, "Cumple","No cumple")</f>
         <v>Cumple</v>
       </c>
-      <c r="E14" s="21" t="s">
-        <v>246</v>
-      </c>
-      <c r="F14" s="91"/>
-      <c r="G14" s="85" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H14" s="25"/>
-      <c r="I14" s="47"/>
+      <c r="E14" s="15" t="s">
+        <v>245</v>
+      </c>
+      <c r="F14" s="87" t="s">
+        <v>340</v>
+      </c>
+      <c r="G14" s="81" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H14" s="19"/>
+      <c r="I14" s="43"/>
     </row>
     <row r="15" spans="2:9" ht="33.6" x14ac:dyDescent="0.4">
-      <c r="B15" s="22" t="s">
+      <c r="B15" s="16" t="s">
+        <v>247</v>
+      </c>
+      <c r="C15" s="19" t="s">
         <v>248</v>
       </c>
-      <c r="C15" s="25" t="s">
+      <c r="D15" s="20">
+        <v>60</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F15" s="87" t="s">
+        <v>340</v>
+      </c>
+      <c r="G15" s="81" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H15" s="19"/>
+      <c r="I15" s="43"/>
+    </row>
+    <row r="16" spans="2:9" ht="33.6" x14ac:dyDescent="0.4">
+      <c r="B16" s="16" t="s">
         <v>249</v>
       </c>
-      <c r="D15" s="26">
-        <v>60</v>
-      </c>
-      <c r="E15" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="F15" s="91"/>
-      <c r="G15" s="85" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H15" s="25"/>
-      <c r="I15" s="47"/>
-    </row>
-    <row r="16" spans="2:9" ht="33.6" x14ac:dyDescent="0.4">
-      <c r="B16" s="22" t="s">
+      <c r="C16" s="19" t="s">
         <v>250</v>
       </c>
-      <c r="C16" s="25" t="s">
-        <v>251</v>
-      </c>
-      <c r="D16" s="21">
+      <c r="D16" s="15">
         <f>D15*D10</f>
         <v>240</v>
       </c>
-      <c r="E16" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="F16" s="91"/>
-      <c r="G16" s="85" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H16" s="25"/>
-      <c r="I16" s="47"/>
+      <c r="E16" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="F16" s="87" t="s">
+        <v>340</v>
+      </c>
+      <c r="G16" s="81" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H16" s="19"/>
+      <c r="I16" s="43"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B17" s="22"/>
-      <c r="C17" s="25"/>
-      <c r="D17" s="26"/>
-      <c r="E17" s="21"/>
-      <c r="F17" s="91"/>
-      <c r="G17" s="85" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H17" s="25"/>
-      <c r="I17" s="47"/>
+      <c r="B17" s="16"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="87"/>
+      <c r="G17" s="82" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H17" s="19"/>
+      <c r="I17" s="43"/>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B18" s="22"/>
-      <c r="C18" s="25"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="91"/>
-      <c r="G18" s="86" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H18" s="25"/>
-      <c r="I18" s="47"/>
-    </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B19" s="5" t="s">
+      <c r="B18" s="5" t="s">
+        <v>335</v>
+      </c>
+      <c r="C18" s="17"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="89"/>
+      <c r="G18" s="18"/>
+      <c r="H18" s="54"/>
+      <c r="I18" s="42"/>
+    </row>
+    <row r="19" spans="2:9" ht="45.6" x14ac:dyDescent="0.4">
+      <c r="B19" s="16" t="s">
+        <v>251</v>
+      </c>
+      <c r="C19" s="19" t="s">
+        <v>240</v>
+      </c>
+      <c r="D19" s="20" t="s">
+        <v>241</v>
+      </c>
+      <c r="E19" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="F19" s="87" t="s">
         <v>340</v>
       </c>
-      <c r="C19" s="23"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="24"/>
-      <c r="F19" s="93"/>
-      <c r="G19" s="24"/>
-      <c r="H19" s="58"/>
-      <c r="I19" s="46"/>
+      <c r="G19" s="81" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H19" s="19"/>
+      <c r="I19" s="43">
+        <v>5</v>
+      </c>
     </row>
     <row r="20" spans="2:9" ht="45.6" x14ac:dyDescent="0.4">
-      <c r="B20" s="22" t="s">
+      <c r="B20" s="16" t="s">
         <v>252</v>
       </c>
-      <c r="C20" s="25" t="s">
+      <c r="C20" s="19" t="s">
+        <v>240</v>
+      </c>
+      <c r="D20" s="20" t="s">
         <v>241</v>
       </c>
-      <c r="D20" s="26" t="s">
-        <v>242</v>
-      </c>
-      <c r="E20" s="21" t="s">
-        <v>119</v>
-      </c>
-      <c r="F20" s="91"/>
-      <c r="G20" s="85" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H20" s="25"/>
-      <c r="I20" s="47">
-        <v>5</v>
-      </c>
+      <c r="E20" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="F20" s="87" t="s">
+        <v>340</v>
+      </c>
+      <c r="G20" s="81" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H20" s="19"/>
+      <c r="I20" s="43"/>
     </row>
     <row r="21" spans="2:9" ht="45.6" x14ac:dyDescent="0.4">
-      <c r="B21" s="22" t="s">
+      <c r="B21" s="16" t="s">
         <v>253</v>
       </c>
-      <c r="C21" s="25" t="s">
+      <c r="C21" s="19" t="s">
+        <v>240</v>
+      </c>
+      <c r="D21" s="20" t="s">
         <v>241</v>
       </c>
-      <c r="D21" s="26" t="s">
-        <v>242</v>
-      </c>
-      <c r="E21" s="21" t="s">
-        <v>119</v>
-      </c>
-      <c r="F21" s="91"/>
-      <c r="G21" s="85" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H21" s="25"/>
-      <c r="I21" s="47"/>
-    </row>
-    <row r="22" spans="2:9" ht="45.6" x14ac:dyDescent="0.4">
-      <c r="B22" s="22" t="s">
-        <v>254</v>
-      </c>
-      <c r="C22" s="25" t="s">
-        <v>241</v>
-      </c>
-      <c r="D22" s="26" t="s">
-        <v>242</v>
-      </c>
-      <c r="E22" s="21" t="s">
-        <v>119</v>
-      </c>
-      <c r="F22" s="91"/>
-      <c r="G22" s="85" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
+      <c r="E21" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="F21" s="87" t="s">
+        <v>340</v>
+      </c>
+      <c r="G21" s="81" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H21" s="19"/>
+      <c r="I21" s="43"/>
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B22" s="24"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="26"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="88"/>
+      <c r="G22" s="26"/>
       <c r="H22" s="25"/>
-      <c r="I22" s="47"/>
+      <c r="I22" s="45"/>
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B23" s="30"/>
-      <c r="C23" s="31"/>
-      <c r="D23" s="32"/>
-      <c r="E23" s="32"/>
-      <c r="F23" s="92"/>
-      <c r="G23" s="32"/>
-      <c r="H23" s="31"/>
-      <c r="I23" s="49"/>
-    </row>
-    <row r="24" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="H24" s="50" t="s">
-        <v>277</v>
-      </c>
-      <c r="I24" s="61">
-        <f>AVERAGE(I7:I23)</f>
+      <c r="H23" s="46" t="s">
+        <v>276</v>
+      </c>
+      <c r="I23" s="57">
+        <f>AVERAGE(I7:I22)</f>
         <v>5</v>
       </c>
     </row>
@@ -6663,11 +6740,12 @@
     <col min="2" max="2" width="30.77734375" style="1" customWidth="1"/>
     <col min="3" max="3" width="50.77734375" style="1" customWidth="1"/>
     <col min="4" max="5" width="10.77734375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="7.77734375" style="15" customWidth="1"/>
+    <col min="6" max="6" width="7.77734375" style="11" customWidth="1"/>
     <col min="7" max="7" width="3.77734375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="30.77734375" style="15" customWidth="1"/>
-    <col min="9" max="9" width="12.77734375" style="61" customWidth="1"/>
-    <col min="10" max="16384" width="9.109375" style="1"/>
+    <col min="8" max="8" width="30.77734375" style="11" customWidth="1"/>
+    <col min="9" max="9" width="12.77734375" style="57" customWidth="1"/>
+    <col min="10" max="10" width="2.77734375" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="9.109375" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:9" x14ac:dyDescent="0.4">
@@ -6676,265 +6754,283 @@
       </c>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B3" s="13" t="s">
-        <v>341</v>
+      <c r="B3" s="9" t="s">
+        <v>336</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B4" s="78" t="s">
+      <c r="B4" s="74" t="s">
+        <v>259</v>
+      </c>
+      <c r="C4" s="74"/>
+      <c r="D4" s="74"/>
+      <c r="E4" s="74"/>
+      <c r="F4" s="74"/>
+      <c r="G4" s="74"/>
+      <c r="H4" s="74"/>
+      <c r="I4" s="74"/>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+      <c r="I5" s="79"/>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B6" s="21" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="22" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" s="23" t="s">
+        <v>49</v>
+      </c>
+      <c r="F6" s="83" t="s">
+        <v>38</v>
+      </c>
+      <c r="G6" s="84"/>
+      <c r="H6" s="22" t="s">
+        <v>26</v>
+      </c>
+      <c r="I6" s="41" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
+      <c r="B7" s="16" t="s">
+        <v>254</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>255</v>
+      </c>
+      <c r="D7" s="20">
+        <v>1</v>
+      </c>
+      <c r="E7" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="F7" s="87" t="s">
+        <v>312</v>
+      </c>
+      <c r="G7" s="81" t="str">
+        <f t="shared" ref="G7:G16" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F7,"/Readme.md"),"Ver")</f>
+        <v>Ver</v>
+      </c>
+      <c r="H7" s="19"/>
+      <c r="I7" s="43">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
+      <c r="B8" s="16" t="s">
+        <v>256</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>266</v>
+      </c>
+      <c r="D8" s="20">
+        <v>1</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="F8" s="87" t="s">
+        <v>312</v>
+      </c>
+      <c r="G8" s="81" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H8" s="19"/>
+      <c r="I8" s="43"/>
+    </row>
+    <row r="9" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
+      <c r="B9" s="16" t="s">
+        <v>257</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>267</v>
+      </c>
+      <c r="D9" s="20">
+        <v>1</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="F9" s="87" t="s">
+        <v>312</v>
+      </c>
+      <c r="G9" s="81" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H9" s="19"/>
+      <c r="I9" s="43"/>
+    </row>
+    <row r="10" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
+      <c r="B10" s="16" t="s">
+        <v>258</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>268</v>
+      </c>
+      <c r="D10" s="20">
+        <v>1</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="F10" s="87" t="s">
+        <v>312</v>
+      </c>
+      <c r="G10" s="81" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H10" s="19"/>
+      <c r="I10" s="43"/>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B11" s="16" t="s">
         <v>260</v>
       </c>
-      <c r="C4" s="78"/>
-      <c r="D4" s="78"/>
-      <c r="E4" s="78"/>
-      <c r="F4" s="78"/>
-      <c r="G4" s="78"/>
-      <c r="H4" s="78"/>
-      <c r="I4" s="78"/>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B5" s="83"/>
-      <c r="C5" s="83"/>
-      <c r="D5" s="83"/>
-      <c r="E5" s="83"/>
-      <c r="F5" s="83"/>
-      <c r="G5" s="83"/>
-      <c r="H5" s="83"/>
-      <c r="I5" s="83"/>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B6" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="D6" s="29" t="s">
-        <v>49</v>
-      </c>
-      <c r="E6" s="29" t="s">
-        <v>50</v>
-      </c>
-      <c r="F6" s="87" t="s">
-        <v>39</v>
-      </c>
-      <c r="G6" s="88"/>
-      <c r="H6" s="28" t="s">
-        <v>26</v>
-      </c>
-      <c r="I6" s="45" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
-      <c r="B7" s="22" t="s">
-        <v>255</v>
-      </c>
-      <c r="C7" s="25" t="s">
-        <v>256</v>
-      </c>
-      <c r="D7" s="26">
+      <c r="C11" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="D11" s="20">
         <v>1</v>
       </c>
-      <c r="E7" s="21" t="s">
-        <v>119</v>
-      </c>
-      <c r="F7" s="91"/>
-      <c r="G7" s="85" t="str">
-        <f t="shared" ref="G7:G16" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F7,"/Readme.md"),"Ver")</f>
-        <v>Ver</v>
-      </c>
-      <c r="H7" s="25"/>
-      <c r="I7" s="47">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
-      <c r="B8" s="22" t="s">
-        <v>257</v>
-      </c>
-      <c r="C8" s="25" t="s">
-        <v>267</v>
-      </c>
-      <c r="D8" s="26">
+      <c r="E11" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="F11" s="87" t="s">
+        <v>312</v>
+      </c>
+      <c r="G11" s="81" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H11" s="19"/>
+      <c r="I11" s="43"/>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B12" s="16" t="s">
+        <v>261</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>221</v>
+      </c>
+      <c r="D12" s="20">
         <v>1</v>
       </c>
-      <c r="E8" s="21" t="s">
-        <v>119</v>
-      </c>
-      <c r="F8" s="91"/>
-      <c r="G8" s="85" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H8" s="25"/>
-      <c r="I8" s="47"/>
-    </row>
-    <row r="9" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
-      <c r="B9" s="22" t="s">
-        <v>258</v>
-      </c>
-      <c r="C9" s="25" t="s">
-        <v>268</v>
-      </c>
-      <c r="D9" s="26">
+      <c r="E12" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="F12" s="87" t="s">
+        <v>312</v>
+      </c>
+      <c r="G12" s="81" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H12" s="19"/>
+      <c r="I12" s="43"/>
+    </row>
+    <row r="13" spans="2:9" ht="33.6" x14ac:dyDescent="0.4">
+      <c r="B13" s="16" t="s">
+        <v>262</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>224</v>
+      </c>
+      <c r="D13" s="20">
         <v>1</v>
       </c>
-      <c r="E9" s="21" t="s">
-        <v>119</v>
-      </c>
-      <c r="F9" s="91"/>
-      <c r="G9" s="85" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H9" s="25"/>
-      <c r="I9" s="47"/>
-    </row>
-    <row r="10" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
-      <c r="B10" s="22" t="s">
-        <v>259</v>
-      </c>
-      <c r="C10" s="25" t="s">
-        <v>269</v>
-      </c>
-      <c r="D10" s="26">
+      <c r="E13" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="F13" s="87" t="s">
+        <v>312</v>
+      </c>
+      <c r="G13" s="81" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H13" s="19"/>
+      <c r="I13" s="43"/>
+    </row>
+    <row r="14" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
+      <c r="B14" s="16" t="s">
+        <v>263</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>222</v>
+      </c>
+      <c r="D14" s="20">
         <v>1</v>
       </c>
-      <c r="E10" s="21" t="s">
-        <v>119</v>
-      </c>
-      <c r="F10" s="91"/>
-      <c r="G10" s="85" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H10" s="25"/>
-      <c r="I10" s="47"/>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B11" s="22" t="s">
-        <v>261</v>
-      </c>
-      <c r="C11" s="25" t="s">
-        <v>222</v>
-      </c>
-      <c r="D11" s="26">
+      <c r="E14" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="F14" s="87" t="s">
+        <v>312</v>
+      </c>
+      <c r="G14" s="81" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H14" s="19"/>
+      <c r="I14" s="43"/>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B15" s="16" t="s">
+        <v>264</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>223</v>
+      </c>
+      <c r="D15" s="20">
         <v>1</v>
       </c>
-      <c r="E11" s="21" t="s">
-        <v>119</v>
-      </c>
-      <c r="F11" s="91"/>
-      <c r="G11" s="85" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H11" s="25"/>
-      <c r="I11" s="47"/>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B12" s="22" t="s">
-        <v>262</v>
-      </c>
-      <c r="C12" s="25" t="s">
-        <v>222</v>
-      </c>
-      <c r="D12" s="26">
-        <v>1</v>
-      </c>
-      <c r="E12" s="21" t="s">
-        <v>119</v>
-      </c>
-      <c r="F12" s="91"/>
-      <c r="G12" s="85" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H12" s="25"/>
-      <c r="I12" s="47"/>
-    </row>
-    <row r="13" spans="2:9" ht="33.6" x14ac:dyDescent="0.4">
-      <c r="B13" s="22" t="s">
-        <v>263</v>
-      </c>
-      <c r="C13" s="25" t="s">
-        <v>225</v>
-      </c>
-      <c r="D13" s="26">
-        <v>1</v>
-      </c>
-      <c r="E13" s="21" t="s">
-        <v>119</v>
-      </c>
-      <c r="F13" s="91"/>
-      <c r="G13" s="85" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H13" s="25"/>
-      <c r="I13" s="47"/>
-    </row>
-    <row r="14" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
-      <c r="B14" s="22" t="s">
-        <v>264</v>
-      </c>
-      <c r="C14" s="25" t="s">
-        <v>223</v>
-      </c>
-      <c r="D14" s="26">
-        <v>1</v>
-      </c>
-      <c r="E14" s="21" t="s">
-        <v>119</v>
-      </c>
-      <c r="F14" s="91"/>
-      <c r="G14" s="85" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H14" s="25"/>
-      <c r="I14" s="47"/>
-    </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B15" s="22" t="s">
-        <v>265</v>
-      </c>
-      <c r="C15" s="25" t="s">
-        <v>224</v>
-      </c>
-      <c r="D15" s="26">
-        <v>1</v>
-      </c>
-      <c r="E15" s="21" t="s">
-        <v>119</v>
-      </c>
-      <c r="F15" s="91"/>
-      <c r="G15" s="85" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H15" s="25"/>
-      <c r="I15" s="47"/>
+      <c r="E15" s="15" t="s">
+        <v>118</v>
+      </c>
+      <c r="F15" s="87" t="s">
+        <v>312</v>
+      </c>
+      <c r="G15" s="81" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H15" s="19"/>
+      <c r="I15" s="43"/>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B16" s="30"/>
-      <c r="C16" s="31"/>
-      <c r="D16" s="44"/>
-      <c r="E16" s="32"/>
-      <c r="F16" s="92"/>
-      <c r="G16" s="86" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H16" s="31"/>
-      <c r="I16" s="49"/>
+      <c r="B16" s="24"/>
+      <c r="C16" s="25"/>
+      <c r="D16" s="40"/>
+      <c r="E16" s="26"/>
+      <c r="F16" s="88"/>
+      <c r="G16" s="82" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H16" s="25"/>
+      <c r="I16" s="45"/>
     </row>
     <row r="17" spans="8:9" x14ac:dyDescent="0.4">
-      <c r="H17" s="50" t="s">
-        <v>277</v>
-      </c>
-      <c r="I17" s="61">
+      <c r="H17" s="46" t="s">
+        <v>276</v>
+      </c>
+      <c r="I17" s="57">
         <f>AVERAGE(I7:I16)</f>
         <v>5</v>
       </c>
@@ -6951,326 +7047,291 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:I18"/>
+  <dimension ref="B2:H17"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="2.5546875" style="2" customWidth="1"/>
-    <col min="3" max="3" width="30.77734375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="50.77734375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="40.77734375" style="2" customWidth="1"/>
-    <col min="6" max="6" width="7.77734375" style="57" customWidth="1"/>
-    <col min="7" max="7" width="3.77734375" style="42" customWidth="1"/>
-    <col min="8" max="8" width="30.77734375" style="57" customWidth="1"/>
-    <col min="9" max="9" width="12.77734375" style="37" customWidth="1"/>
+    <col min="1" max="1" width="2.5546875" style="2" customWidth="1"/>
+    <col min="2" max="2" width="30.77734375" style="2" customWidth="1"/>
+    <col min="3" max="3" width="50.77734375" style="2" customWidth="1"/>
+    <col min="4" max="4" width="40.77734375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="7.77734375" style="53" customWidth="1"/>
+    <col min="6" max="6" width="3.77734375" style="36" customWidth="1"/>
+    <col min="7" max="7" width="30.77734375" style="53" customWidth="1"/>
+    <col min="8" max="8" width="12.77734375" style="31" customWidth="1"/>
+    <col min="9" max="9" width="2.77734375" style="2" customWidth="1"/>
     <col min="10" max="16384" width="9.109375" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B2" s="76" t="s">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B2" s="72" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="76"/>
-      <c r="D2" s="76"/>
-      <c r="E2" s="76"/>
-      <c r="F2" s="76"/>
-      <c r="G2" s="76"/>
-      <c r="H2" s="76"/>
-      <c r="I2" s="76"/>
-    </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B3" s="84" t="s">
-        <v>342</v>
-      </c>
-      <c r="C3" s="84"/>
-      <c r="D3" s="84"/>
-      <c r="E3" s="84"/>
-      <c r="F3" s="84"/>
-      <c r="G3" s="84"/>
-      <c r="H3" s="84"/>
-      <c r="I3" s="84"/>
-    </row>
-    <row r="4" spans="2:9" s="42" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="78" t="s">
-        <v>343</v>
-      </c>
-      <c r="C4" s="78"/>
-      <c r="D4" s="78"/>
-      <c r="E4" s="78"/>
-      <c r="F4" s="78"/>
-      <c r="G4" s="78"/>
-      <c r="H4" s="78"/>
-      <c r="I4" s="78"/>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B5" s="83"/>
-      <c r="C5" s="83"/>
-      <c r="D5" s="83"/>
-      <c r="E5" s="83"/>
-      <c r="F5" s="83"/>
-      <c r="G5" s="83"/>
-      <c r="H5" s="83"/>
-      <c r="I5" s="83"/>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B6" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="6" t="s">
+      <c r="C2" s="72"/>
+      <c r="D2" s="72"/>
+      <c r="E2" s="72"/>
+      <c r="F2" s="72"/>
+      <c r="G2" s="72"/>
+      <c r="H2" s="72"/>
+    </row>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B3" s="80" t="s">
+        <v>337</v>
+      </c>
+      <c r="C3" s="80"/>
+      <c r="D3" s="80"/>
+      <c r="E3" s="80"/>
+      <c r="F3" s="80"/>
+      <c r="G3" s="80"/>
+      <c r="H3" s="80"/>
+    </row>
+    <row r="4" spans="2:8" s="36" customFormat="1" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="74" t="s">
+        <v>338</v>
+      </c>
+      <c r="C4" s="74"/>
+      <c r="D4" s="74"/>
+      <c r="E4" s="74"/>
+      <c r="F4" s="74"/>
+      <c r="G4" s="74"/>
+      <c r="H4" s="74"/>
+    </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B5" s="79"/>
+      <c r="C5" s="79"/>
+      <c r="D5" s="79"/>
+      <c r="E5" s="79"/>
+      <c r="F5" s="79"/>
+      <c r="G5" s="79"/>
+      <c r="H5" s="79"/>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B6" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="C6" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="83" t="s">
         <v>38</v>
       </c>
-      <c r="E6" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" s="87" t="s">
-        <v>39</v>
-      </c>
-      <c r="G6" s="88"/>
-      <c r="H6" s="6" t="s">
+      <c r="F6" s="84"/>
+      <c r="G6" s="38" t="s">
         <v>26</v>
       </c>
-      <c r="I6" s="8" t="s">
+      <c r="H6" s="7" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B7" s="10">
-        <v>0</v>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B7" s="16" t="s">
+        <v>277</v>
       </c>
       <c r="C7" s="19" t="s">
         <v>278</v>
       </c>
-      <c r="D7" s="25" t="s">
-        <v>279</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F7" s="59"/>
-      <c r="G7" s="85" t="str">
-        <f t="shared" ref="G7:G17" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F7,"/Readme.md"),"Ver")</f>
-        <v>Ver</v>
-      </c>
-      <c r="H7" s="59"/>
-      <c r="I7" s="9">
+      <c r="D7" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="E7" s="131" t="s">
+        <v>311</v>
+      </c>
+      <c r="F7" s="81" t="str">
+        <f t="shared" ref="F7:F16" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",E7,"/Readme.md"),"Ver")</f>
+        <v>Ver</v>
+      </c>
+      <c r="G7" s="55"/>
+      <c r="H7" s="8">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B8" s="10">
-        <v>1</v>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B8" s="16" t="s">
+        <v>19</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>19</v>
-      </c>
-      <c r="D8" s="25" t="s">
+        <v>303</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" s="131" t="s">
+        <v>311</v>
+      </c>
+      <c r="F8" s="81" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="G8" s="55"/>
+      <c r="H8" s="8"/>
+    </row>
+    <row r="9" spans="2:8" ht="91.2" x14ac:dyDescent="0.3">
+      <c r="B9" s="16" t="s">
+        <v>304</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>305</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" s="131" t="s">
+        <v>312</v>
+      </c>
+      <c r="F9" s="81" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="G9" s="55"/>
+      <c r="H9" s="8"/>
+    </row>
+    <row r="10" spans="2:8" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="B10" s="16" t="s">
+        <v>287</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>317</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" s="131" t="s">
+        <v>316</v>
+      </c>
+      <c r="F10" s="81" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="G10" s="55"/>
+      <c r="H10" s="8"/>
+    </row>
+    <row r="11" spans="2:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="B11" s="16" t="s">
+        <v>288</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>318</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" s="131" t="s">
+        <v>316</v>
+      </c>
+      <c r="F11" s="81" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="G11" s="55"/>
+      <c r="H11" s="8"/>
+    </row>
+    <row r="12" spans="2:8" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="B12" s="16" t="s">
+        <v>289</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>319</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E12" s="131" t="s">
+        <v>316</v>
+      </c>
+      <c r="F12" s="81" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="G12" s="55"/>
+      <c r="H12" s="8"/>
+    </row>
+    <row r="13" spans="2:8" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="B13" s="16" t="s">
+        <v>296</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>320</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="E13" s="131" t="s">
+        <v>313</v>
+      </c>
+      <c r="F13" s="81" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="G13" s="55"/>
+      <c r="H13" s="8"/>
+    </row>
+    <row r="14" spans="2:8" ht="79.8" x14ac:dyDescent="0.3">
+      <c r="B14" s="16" t="s">
+        <v>342</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>343</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="E14" s="131" t="s">
+        <v>312</v>
+      </c>
+      <c r="F14" s="81" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="G14" s="55"/>
+      <c r="H14" s="8"/>
+    </row>
+    <row r="15" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B15" s="16" t="s">
+        <v>306</v>
+      </c>
+      <c r="C15" s="19" t="s">
         <v>307</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="F8" s="59"/>
-      <c r="G8" s="85" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H8" s="59"/>
-      <c r="I8" s="9"/>
-    </row>
-    <row r="9" spans="2:9" ht="91.2" x14ac:dyDescent="0.3">
-      <c r="B9" s="10">
-        <v>2</v>
-      </c>
-      <c r="C9" s="19" t="s">
+      <c r="D15" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="D9" s="25" t="s">
-        <v>309</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F9" s="59"/>
-      <c r="G9" s="85" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H9" s="59"/>
-      <c r="I9" s="9"/>
-    </row>
-    <row r="10" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B10" s="10">
-        <v>3</v>
-      </c>
-      <c r="C10" s="19" t="s">
-        <v>288</v>
-      </c>
-      <c r="D10" s="25" t="s">
-        <v>321</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="F10" s="59"/>
-      <c r="G10" s="85" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H10" s="59"/>
-      <c r="I10" s="9"/>
-    </row>
-    <row r="11" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
-      <c r="B11" s="10">
-        <v>4</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>289</v>
-      </c>
-      <c r="D11" s="25" t="s">
-        <v>322</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F11" s="59"/>
-      <c r="G11" s="85" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H11" s="59"/>
-      <c r="I11" s="9"/>
-    </row>
-    <row r="12" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B12" s="10">
-        <v>5</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>290</v>
-      </c>
-      <c r="D12" s="25" t="s">
-        <v>323</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F12" s="59"/>
-      <c r="G12" s="85" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H12" s="59"/>
-      <c r="I12" s="9"/>
-    </row>
-    <row r="13" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B13" s="10">
-        <v>6</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>297</v>
-      </c>
-      <c r="D13" s="25" t="s">
-        <v>324</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="F13" s="59"/>
-      <c r="G13" s="85" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H13" s="59"/>
-      <c r="I13" s="9"/>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B14" s="10">
-        <v>7</v>
-      </c>
-      <c r="C14" s="19" t="s">
-        <v>304</v>
-      </c>
-      <c r="D14" s="25" t="s">
-        <v>305</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="F14" s="59"/>
-      <c r="G14" s="85" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H14" s="59"/>
-      <c r="I14" s="9"/>
-    </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B15" s="10">
-        <v>8</v>
-      </c>
-      <c r="C15" s="19" t="s">
-        <v>310</v>
-      </c>
-      <c r="D15" s="25" t="s">
-        <v>311</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="F15" s="59"/>
-      <c r="G15" s="85" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H15" s="59"/>
-      <c r="I15" s="9"/>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B16" s="10">
-        <v>9</v>
-      </c>
-      <c r="C16" s="19"/>
-      <c r="D16" s="25"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="59"/>
-      <c r="G16" s="85" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H16" s="59"/>
-      <c r="I16" s="9"/>
-    </row>
-    <row r="17" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B17" s="11">
-        <v>10</v>
-      </c>
-      <c r="C17" s="20"/>
-      <c r="D17" s="31"/>
-      <c r="E17" s="4"/>
-      <c r="F17" s="39"/>
-      <c r="G17" s="86" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H17" s="39"/>
-      <c r="I17" s="7"/>
-    </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="H18" s="50" t="s">
-        <v>277</v>
-      </c>
-      <c r="I18" s="37">
-        <f>AVERAGE(I7:I17)</f>
+      <c r="E15" s="55"/>
+      <c r="F15" s="81" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="G15" s="55"/>
+      <c r="H15" s="8"/>
+    </row>
+    <row r="16" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B16" s="24"/>
+      <c r="C16" s="25"/>
+      <c r="D16" s="4"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="82" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="G16" s="33"/>
+      <c r="H16" s="6"/>
+    </row>
+    <row r="17" spans="7:8" x14ac:dyDescent="0.3">
+      <c r="G17" s="46" t="s">
+        <v>276</v>
+      </c>
+      <c r="H17" s="31">
+        <f>AVERAGE(H7:H16)</f>
         <v>5</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="B3:I3"/>
-    <mergeCell ref="B2:I2"/>
-    <mergeCell ref="F6:G6"/>
-    <mergeCell ref="B4:I5"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B3:H3"/>
+    <mergeCell ref="B4:H5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -7288,7 +7349,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B1" s="16"/>
+      <c r="B1" s="12"/>
     </row>
     <row r="2" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B2" s="1" t="s">
@@ -7296,12 +7357,12 @@
       </c>
     </row>
     <row r="3" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="10" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.4">
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="11" t="s">
         <v>25</v>
       </c>
     </row>

--- a/file/table/DAPC_ProyectoCAD.xlsx
+++ b/file/table/DAPC_ProyectoCAD.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECA9298B-9461-449A-9123-D424DFBEAB93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2435E275-F9E6-4B4C-B1D6-0A964095D000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0.Inicio" sheetId="7" r:id="rId1"/>
@@ -26,6 +26,8 @@
     <externalReference r:id="rId9"/>
   </externalReferences>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1.Tecnica'!$B$6:$I$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2.ArquitectonicaEstructural'!$B$6:$I$100</definedName>
     <definedName name="SumUDig" localSheetId="4">'[1]1.Técnicas'!$E$32</definedName>
     <definedName name="SumUDig">'0.Inicio'!$E$29</definedName>
   </definedNames>
@@ -825,21 +827,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Utilizar como referencia un ancho mínimo 30 centímetros. Dibujar ancho en el sentido del ancho de la bodega. Para columnas en concreto investigar especificaciones de refuerzo y dibujar detalle estructural. </t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>Ver nota 1a.</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">Utilizar como referencia un largo mínimo 30 centímetros. Dibujar largo en el sentido del largo de la bodega. Para columnas en concreto investigar especificaciones de refuerzo y dibujar detalle estructural. </t>
     </r>
     <r>
@@ -1288,9 +1275,6 @@
   </si>
   <si>
     <t>Mantener este valor para el proyecto.</t>
-  </si>
-  <si>
-    <t>Los estudiantes deberán definir el nombre de su grupo de proyecto y crear un logotipo en AutoCAD (guardar como /file/cad/logotipo.dwg). El código, logotipo y nombre del grupo deberán incluirse en todos los planos generados.</t>
   </si>
   <si>
     <r>
@@ -1512,6 +1496,24 @@
   </si>
   <si>
     <t>v.20250725</t>
+  </si>
+  <si>
+    <t>Los estudiantes deberán definir el nombre de su grupo de proyecto (utilice un nombre corporativo corto) y crear un logotipo en AutoCAD (guardar como /file/cad/logotipo.dwg). El código, logotipo y nombre del grupo deberán incluirse en todos los planos generados. El grupo se deberá mantener durante todo el semestre académico.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Utilizar como referencia un ancho mínimo 25 centímetros. Dibujar ancho en el sentido del ancho de la bodega. Para columnas en concreto investigar especificaciones de refuerzo y dibujar detalle estructural. </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>Ver nota 1a.</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -2988,7 +2990,7 @@
   <sheetData>
     <row r="1" spans="2:5" x14ac:dyDescent="0.3">
       <c r="E1" s="100" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
     </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.3">
@@ -2998,7 +3000,7 @@
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B3" s="101" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.3">
@@ -3268,7 +3270,7 @@
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B31" s="73" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C31" s="73"/>
       <c r="D31" s="73"/>
@@ -3291,7 +3293,7 @@
         <v>1</v>
       </c>
       <c r="C33" s="77" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="D33" s="78"/>
       <c r="E33" s="51">
@@ -3304,7 +3306,7 @@
         <v>2</v>
       </c>
       <c r="C34" s="62" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="D34" s="63"/>
       <c r="E34" s="51">
@@ -3317,7 +3319,7 @@
         <v>3</v>
       </c>
       <c r="C35" s="62" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D35" s="63"/>
       <c r="E35" s="51">
@@ -3330,7 +3332,7 @@
         <v>4</v>
       </c>
       <c r="C36" s="60" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="D36" s="61"/>
       <c r="E36" s="51">
@@ -3343,7 +3345,7 @@
         <v>4</v>
       </c>
       <c r="C37" s="62" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D37" s="63"/>
       <c r="E37" s="51">
@@ -3356,7 +3358,7 @@
         <v>5</v>
       </c>
       <c r="C38" s="62" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D38" s="63"/>
       <c r="E38" s="51">
@@ -3369,7 +3371,7 @@
         <v>6</v>
       </c>
       <c r="C39" s="62" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="D39" s="63"/>
       <c r="E39" s="99">
@@ -3381,7 +3383,7 @@
         <v>7</v>
       </c>
       <c r="C40" s="64" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="D40" s="65"/>
       <c r="E40" s="58">
@@ -3390,7 +3392,7 @@
     </row>
     <row r="41" spans="2:5" x14ac:dyDescent="0.3">
       <c r="D41" s="118" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="E41" s="59">
         <f>AVERAGE(E33:E40)</f>
@@ -3458,7 +3460,7 @@
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B4" s="102" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C4" s="102"/>
       <c r="D4" s="102"/>
@@ -3494,12 +3496,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:9" ht="57" x14ac:dyDescent="0.3">
       <c r="B7" s="127" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C7" s="128" t="s">
-        <v>298</v>
+        <v>345</v>
       </c>
       <c r="D7" s="91">
         <v>1</v>
@@ -3508,7 +3510,7 @@
         <v>16</v>
       </c>
       <c r="F7" s="131" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="G7" s="132" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F7,"/Readme.md"),"Ver")</f>
@@ -3521,19 +3523,19 @@
     </row>
     <row r="8" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B8" s="127" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="C8" s="128" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="D8" s="91">
         <v>1</v>
       </c>
       <c r="E8" s="130" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="F8" s="131" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="G8" s="132" t="str">
         <f t="shared" ref="G8:G18" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F8,"/Readme.md"),"Ver")</f>
@@ -3544,17 +3546,17 @@
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B9" s="127" t="s">
+        <v>276</v>
+      </c>
+      <c r="C9" s="128" t="s">
         <v>277</v>
       </c>
-      <c r="C9" s="128" t="s">
-        <v>278</v>
-      </c>
       <c r="D9" s="91" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E9" s="130"/>
       <c r="F9" s="131" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="G9" s="132" t="str">
         <f t="shared" si="0"/>
@@ -3565,10 +3567,10 @@
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B10" s="127" t="s">
+        <v>280</v>
+      </c>
+      <c r="C10" s="128" t="s">
         <v>281</v>
-      </c>
-      <c r="C10" s="128" t="s">
-        <v>282</v>
       </c>
       <c r="D10" s="91">
         <v>1</v>
@@ -3577,7 +3579,7 @@
         <v>16</v>
       </c>
       <c r="F10" s="131" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="G10" s="132" t="str">
         <f t="shared" si="0"/>
@@ -3588,17 +3590,17 @@
     </row>
     <row r="11" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
       <c r="B11" s="127" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C11" s="128" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D11" s="91" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E11" s="130"/>
       <c r="F11" s="131" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G11" s="132" t="str">
         <f t="shared" si="0"/>
@@ -3609,17 +3611,17 @@
     </row>
     <row r="12" spans="2:9" ht="57" x14ac:dyDescent="0.3">
       <c r="B12" s="127" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C12" s="128" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D12" s="91" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E12" s="130"/>
       <c r="F12" s="131" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="G12" s="132" t="str">
         <f t="shared" si="0"/>
@@ -3630,17 +3632,17 @@
     </row>
     <row r="13" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B13" s="127" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C13" s="128" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D13" s="91" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E13" s="130"/>
       <c r="F13" s="131" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="G13" s="132" t="str">
         <f t="shared" si="0"/>
@@ -3651,17 +3653,17 @@
     </row>
     <row r="14" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
       <c r="B14" s="127" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C14" s="128" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D14" s="91" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="E14" s="130"/>
       <c r="F14" s="131" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="G14" s="132" t="str">
         <f t="shared" si="0"/>
@@ -3672,10 +3674,10 @@
     </row>
     <row r="15" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="B15" s="127" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C15" s="128" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D15" s="91">
         <v>1</v>
@@ -3684,7 +3686,7 @@
         <v>16</v>
       </c>
       <c r="F15" s="131" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="G15" s="132" t="str">
         <f t="shared" si="0"/>
@@ -3695,10 +3697,10 @@
     </row>
     <row r="16" spans="2:9" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="127" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C16" s="128" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D16" s="91">
         <v>1</v>
@@ -3707,7 +3709,7 @@
         <v>16</v>
       </c>
       <c r="F16" s="131" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="G16" s="132" t="str">
         <f t="shared" si="0"/>
@@ -3718,10 +3720,10 @@
     </row>
     <row r="17" spans="2:9" ht="35.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="134" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C17" s="135" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D17" s="91">
         <v>1</v>
@@ -3730,7 +3732,7 @@
         <v>16</v>
       </c>
       <c r="F17" s="131" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="G17" s="132" t="str">
         <f t="shared" si="0"/>
@@ -3754,7 +3756,7 @@
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.3">
       <c r="H19" s="141" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I19" s="120">
         <f>AVERAGE(I7:I18)</f>
@@ -3762,6 +3764,9 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="B6:I19" xr:uid="{0659C4DD-D653-4634-8C4F-29057F021A54}">
+    <filterColumn colId="4" showButton="0"/>
+  </autoFilter>
   <mergeCells count="2">
     <mergeCell ref="B4:E5"/>
     <mergeCell ref="F6:G6"/>
@@ -3796,12 +3801,12 @@
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="101" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B4" s="102" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C4" s="102"/>
       <c r="D4" s="102"/>
@@ -3847,7 +3852,7 @@
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B7" s="146" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C7" s="147"/>
       <c r="D7" s="148"/>
@@ -3859,10 +3864,10 @@
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B8" s="127" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C8" s="128" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D8" s="129">
         <v>8</v>
@@ -3871,14 +3876,14 @@
         <v>53</v>
       </c>
       <c r="F8" s="131" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G8" s="132" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F8,"/Readme.md"),"Ver")</f>
         <v>Ver</v>
       </c>
       <c r="H8" s="128" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I8" s="133">
         <v>5</v>
@@ -3886,10 +3891,10 @@
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B9" s="127" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C9" s="128" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D9" s="129">
         <v>10</v>
@@ -3898,23 +3903,23 @@
         <v>53</v>
       </c>
       <c r="F9" s="131" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G9" s="132" t="str">
         <f t="shared" ref="G9:G72" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F9,"/Readme.md"),"Ver")</f>
         <v>Ver</v>
       </c>
       <c r="H9" s="128" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I9" s="133"/>
     </row>
     <row r="10" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B10" s="127" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C10" s="128" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D10" s="130">
         <f>D8+SumUDig</f>
@@ -3924,7 +3929,7 @@
         <v>53</v>
       </c>
       <c r="F10" s="131" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G10" s="132" t="str">
         <f t="shared" si="0"/>
@@ -3935,10 +3940,10 @@
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B11" s="127" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C11" s="128" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D11" s="130" cm="1">
         <f t="array" ref="D11">D9+SumUDig</f>
@@ -3948,7 +3953,7 @@
         <v>53</v>
       </c>
       <c r="F11" s="131" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G11" s="132" t="str">
         <f t="shared" si="0"/>
@@ -3962,7 +3967,7 @@
         <v>39</v>
       </c>
       <c r="C12" s="128" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D12" s="129">
         <v>12</v>
@@ -3971,14 +3976,14 @@
         <v>53</v>
       </c>
       <c r="F12" s="131" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G12" s="132" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H12" s="128" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I12" s="133"/>
     </row>
@@ -3996,14 +4001,14 @@
         <v>53</v>
       </c>
       <c r="F13" s="131" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G13" s="132" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H13" s="128" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I13" s="133"/>
     </row>
@@ -4021,14 +4026,14 @@
         <v>53</v>
       </c>
       <c r="F14" s="131" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G14" s="132" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H14" s="128" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I14" s="133"/>
     </row>
@@ -4047,7 +4052,7 @@
         <v>53</v>
       </c>
       <c r="F15" s="131" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G15" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4071,7 +4076,7 @@
         <v>53</v>
       </c>
       <c r="F16" s="131" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G16" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4095,7 +4100,7 @@
         <v>54</v>
       </c>
       <c r="F17" s="131" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G17" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4119,7 +4124,7 @@
         <v>54</v>
       </c>
       <c r="F18" s="131" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G18" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4143,7 +4148,7 @@
         <v>54</v>
       </c>
       <c r="F19" s="131" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G19" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4167,7 +4172,7 @@
         <v>68</v>
       </c>
       <c r="F20" s="131" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G20" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4191,7 +4196,7 @@
         <v>68</v>
       </c>
       <c r="F21" s="131" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G21" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4215,7 +4220,7 @@
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B23" s="146" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="C23" s="147"/>
       <c r="D23" s="148"/>
@@ -4239,14 +4244,14 @@
         <v>53</v>
       </c>
       <c r="F24" s="131" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G24" s="132" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H24" s="128" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="I24" s="133">
         <v>5</v>
@@ -4266,7 +4271,7 @@
         <v>69</v>
       </c>
       <c r="F25" s="131" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G25" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4290,7 +4295,7 @@
         <v>70</v>
       </c>
       <c r="F26" s="131" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G26" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4304,7 +4309,7 @@
         <v>76</v>
       </c>
       <c r="C27" s="135" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D27" s="155">
         <v>0.6</v>
@@ -4313,7 +4318,7 @@
         <v>53</v>
       </c>
       <c r="F27" s="131" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G27" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4336,7 +4341,7 @@
         <v>53</v>
       </c>
       <c r="F28" s="131" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G28" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4359,7 +4364,7 @@
         <v>68</v>
       </c>
       <c r="F29" s="131" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G29" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4383,7 +4388,7 @@
         <v>54</v>
       </c>
       <c r="F30" s="131" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G30" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4407,7 +4412,7 @@
         <v>54</v>
       </c>
       <c r="F31" s="131" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G31" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4431,7 +4436,7 @@
         <v>54</v>
       </c>
       <c r="F32" s="131" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G32" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4454,7 +4459,7 @@
         <v>53</v>
       </c>
       <c r="F33" s="131" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G33" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4478,7 +4483,7 @@
         <v>118</v>
       </c>
       <c r="F34" s="131" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G34" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4501,7 +4506,7 @@
         <v>64</v>
       </c>
       <c r="F35" s="131" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G35" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4525,7 +4530,7 @@
         <v>54</v>
       </c>
       <c r="F36" s="131" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G36" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4549,7 +4554,7 @@
         <v>54</v>
       </c>
       <c r="F37" s="131" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G37" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4573,7 +4578,7 @@
     </row>
     <row r="39" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B39" s="156" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C39" s="147"/>
       <c r="D39" s="148"/>
@@ -4597,7 +4602,7 @@
         <v>53</v>
       </c>
       <c r="F40" s="131" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G40" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4622,7 +4627,7 @@
         <v>53</v>
       </c>
       <c r="F41" s="131" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G41" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4646,7 +4651,7 @@
         <v>53</v>
       </c>
       <c r="F42" s="131" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G42" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4670,7 +4675,7 @@
         <v>54</v>
       </c>
       <c r="F43" s="131" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G43" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4694,7 +4699,7 @@
     </row>
     <row r="45" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B45" s="146" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="C45" s="147"/>
       <c r="D45" s="148"/>
@@ -4709,7 +4714,7 @@
         <v>41</v>
       </c>
       <c r="C46" s="128" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="D46" s="129">
         <v>60</v>
@@ -4718,7 +4723,7 @@
         <v>54</v>
       </c>
       <c r="F46" s="131" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G46" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4743,7 +4748,7 @@
         <v>54</v>
       </c>
       <c r="F47" s="131" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G47" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4766,7 +4771,7 @@
         <v>53</v>
       </c>
       <c r="F48" s="131" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G48" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4790,7 +4795,7 @@
         <v>54</v>
       </c>
       <c r="F49" s="131" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G49" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4813,7 +4818,7 @@
         <v>55</v>
       </c>
       <c r="F50" s="131" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G50" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4836,7 +4841,7 @@
         <v>55</v>
       </c>
       <c r="F51" s="131" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G51" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4860,7 +4865,7 @@
         <v>49</v>
       </c>
       <c r="F52" s="131" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G52" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4883,7 +4888,7 @@
         <v>53</v>
       </c>
       <c r="F53" s="131" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G53" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4907,7 +4912,7 @@
         <v>54</v>
       </c>
       <c r="F54" s="131" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G54" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4921,7 +4926,7 @@
         <v>128</v>
       </c>
       <c r="C55" s="128" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D55" s="129">
         <v>6</v>
@@ -4930,7 +4935,7 @@
         <v>53</v>
       </c>
       <c r="F55" s="131" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G55" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4944,7 +4949,7 @@
         <v>129</v>
       </c>
       <c r="C56" s="128" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D56" s="129">
         <v>4.5</v>
@@ -4953,7 +4958,7 @@
         <v>53</v>
       </c>
       <c r="F56" s="131" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G56" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4976,7 +4981,7 @@
         <v>53</v>
       </c>
       <c r="F57" s="131" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G57" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4987,10 +4992,10 @@
     </row>
     <row r="58" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B58" s="127" t="s">
+        <v>186</v>
+      </c>
+      <c r="C58" s="128" t="s">
         <v>187</v>
-      </c>
-      <c r="C58" s="128" t="s">
-        <v>188</v>
       </c>
       <c r="D58" s="129">
         <v>2.2999999999999998</v>
@@ -4999,7 +5004,7 @@
         <v>53</v>
       </c>
       <c r="F58" s="131" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G58" s="132" t="str">
         <f t="shared" si="0"/>
@@ -5013,7 +5018,7 @@
         <v>132</v>
       </c>
       <c r="C59" s="128" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D59" s="129">
         <v>3</v>
@@ -5022,7 +5027,7 @@
         <v>53</v>
       </c>
       <c r="F59" s="131" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G59" s="132" t="str">
         <f t="shared" si="0"/>
@@ -5033,10 +5038,10 @@
     </row>
     <row r="60" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B60" s="127" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C60" s="128" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D60" s="129">
         <v>2</v>
@@ -5045,7 +5050,7 @@
         <v>53</v>
       </c>
       <c r="F60" s="131" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G60" s="132" t="str">
         <f t="shared" si="0"/>
@@ -5069,7 +5074,7 @@
     </row>
     <row r="62" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B62" s="158" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="C62" s="159"/>
       <c r="D62" s="160"/>
@@ -5081,7 +5086,7 @@
     </row>
     <row r="63" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B63" s="127" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C63" s="128" t="s">
         <v>106</v>
@@ -5093,7 +5098,7 @@
         <v>55</v>
       </c>
       <c r="F63" s="131" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G63" s="132" t="str">
         <f t="shared" si="0"/>
@@ -5106,10 +5111,10 @@
     </row>
     <row r="64" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B64" s="127" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C64" s="128" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D64" s="157">
         <f>D18</f>
@@ -5119,7 +5124,7 @@
         <v>54</v>
       </c>
       <c r="F64" s="131" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G64" s="132" t="str">
         <f t="shared" si="0"/>
@@ -5142,7 +5147,7 @@
         <v>55</v>
       </c>
       <c r="F65" s="131" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G65" s="132" t="str">
         <f t="shared" si="0"/>
@@ -5165,7 +5170,7 @@
         <v>53</v>
       </c>
       <c r="F66" s="131" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G66" s="132" t="str">
         <f t="shared" si="0"/>
@@ -5189,7 +5194,7 @@
         <v>118</v>
       </c>
       <c r="F67" s="131" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G67" s="132" t="str">
         <f t="shared" si="0"/>
@@ -5213,7 +5218,7 @@
         <v>118</v>
       </c>
       <c r="F68" s="131" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G68" s="132" t="str">
         <f t="shared" si="0"/>
@@ -5237,7 +5242,7 @@
         <v>118</v>
       </c>
       <c r="F69" s="131" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G69" s="132" t="str">
         <f t="shared" si="0"/>
@@ -5251,16 +5256,16 @@
         <v>108</v>
       </c>
       <c r="C70" s="128" t="s">
-        <v>151</v>
+        <v>346</v>
       </c>
       <c r="D70" s="129">
-        <v>0.3</v>
+        <v>0.25</v>
       </c>
       <c r="E70" s="130" t="s">
         <v>53</v>
       </c>
       <c r="F70" s="131" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G70" s="132" t="str">
         <f t="shared" si="0"/>
@@ -5274,7 +5279,7 @@
         <v>110</v>
       </c>
       <c r="C71" s="128" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D71" s="129">
         <v>0.4</v>
@@ -5283,7 +5288,7 @@
         <v>53</v>
       </c>
       <c r="F71" s="131" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G71" s="132" t="str">
         <f t="shared" si="0"/>
@@ -5300,13 +5305,13 @@
         <v>114</v>
       </c>
       <c r="D72" s="129">
-        <v>0.3</v>
+        <v>0.15</v>
       </c>
       <c r="E72" s="130" t="s">
         <v>53</v>
       </c>
       <c r="F72" s="131" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G72" s="132" t="str">
         <f t="shared" si="0"/>
@@ -5329,7 +5334,7 @@
         <v>53</v>
       </c>
       <c r="F73" s="131" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G73" s="132" t="str">
         <f t="shared" ref="G73:G76" si="1">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F73,"/Readme.md"),"Ver")</f>
@@ -5347,13 +5352,13 @@
       </c>
       <c r="D74" s="157">
         <f>(D10-D70)/D67</f>
-        <v>5.7833333333333341</v>
+        <v>5.791666666666667</v>
       </c>
       <c r="E74" s="130" t="s">
         <v>53</v>
       </c>
       <c r="F74" s="131" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G74" s="132" t="str">
         <f t="shared" si="1"/>
@@ -5377,7 +5382,7 @@
         <v>53</v>
       </c>
       <c r="F75" s="131" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G75" s="132" t="str">
         <f t="shared" si="1"/>
@@ -5401,7 +5406,7 @@
     </row>
     <row r="77" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B77" s="182" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C77" s="159"/>
       <c r="D77" s="160"/>
@@ -5413,10 +5418,10 @@
     </row>
     <row r="78" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B78" s="127" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C78" s="177" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D78" s="178">
         <f>D64</f>
@@ -5426,7 +5431,7 @@
         <v>54</v>
       </c>
       <c r="F78" s="131" t="s">
-        <v>313</v>
+        <v>338</v>
       </c>
       <c r="G78" s="132" t="str">
         <f t="shared" ref="G78:G88" si="2">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F78,"/Readme.md"),"Ver")</f>
@@ -5437,20 +5442,20 @@
     </row>
     <row r="79" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
       <c r="B79" s="127" t="s">
+        <v>173</v>
+      </c>
+      <c r="C79" s="177" t="s">
         <v>174</v>
-      </c>
-      <c r="C79" s="177" t="s">
-        <v>175</v>
       </c>
       <c r="D79" s="178">
         <f>D78*D63</f>
         <v>57400</v>
       </c>
       <c r="E79" s="178" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F79" s="131" t="s">
-        <v>313</v>
+        <v>338</v>
       </c>
       <c r="G79" s="132" t="str">
         <f t="shared" si="2"/>
@@ -5461,10 +5466,10 @@
     </row>
     <row r="80" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B80" s="127" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C80" s="177" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D80" s="178">
         <f>D49</f>
@@ -5474,7 +5479,7 @@
         <v>54</v>
       </c>
       <c r="F80" s="131" t="s">
-        <v>313</v>
+        <v>338</v>
       </c>
       <c r="G80" s="132" t="str">
         <f t="shared" si="2"/>
@@ -5485,10 +5490,10 @@
     </row>
     <row r="81" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B81" s="127" t="s">
+        <v>177</v>
+      </c>
+      <c r="C81" s="177" t="s">
         <v>178</v>
-      </c>
-      <c r="C81" s="177" t="s">
-        <v>179</v>
       </c>
       <c r="D81" s="178">
         <f>D69</f>
@@ -5498,7 +5503,7 @@
         <v>118</v>
       </c>
       <c r="F81" s="131" t="s">
-        <v>313</v>
+        <v>338</v>
       </c>
       <c r="G81" s="132" t="str">
         <f t="shared" si="2"/>
@@ -5509,10 +5514,10 @@
     </row>
     <row r="82" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
       <c r="B82" s="127" t="s">
+        <v>179</v>
+      </c>
+      <c r="C82" s="177" t="s">
         <v>180</v>
-      </c>
-      <c r="C82" s="177" t="s">
-        <v>181</v>
       </c>
       <c r="D82" s="178">
         <f>D81*D12</f>
@@ -5522,7 +5527,7 @@
         <v>53</v>
       </c>
       <c r="F82" s="131" t="s">
-        <v>313</v>
+        <v>338</v>
       </c>
       <c r="G82" s="132" t="str">
         <f t="shared" si="2"/>
@@ -5533,10 +5538,10 @@
     </row>
     <row r="83" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
       <c r="B83" s="127" t="s">
+        <v>181</v>
+      </c>
+      <c r="C83" s="177" t="s">
         <v>182</v>
-      </c>
-      <c r="C83" s="177" t="s">
-        <v>183</v>
       </c>
       <c r="D83" s="178">
         <f>((D67*D9)+(D68*D8))*INT(D12/D48)</f>
@@ -5546,7 +5551,7 @@
         <v>53</v>
       </c>
       <c r="F83" s="131" t="s">
-        <v>313</v>
+        <v>338</v>
       </c>
       <c r="G83" s="132" t="str">
         <f t="shared" si="2"/>
@@ -5557,19 +5562,19 @@
     </row>
     <row r="84" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
       <c r="B84" s="127" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="C84" s="177" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D84" s="180" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E84" s="178" t="s">
         <v>54</v>
       </c>
       <c r="F84" s="131" t="s">
-        <v>313</v>
+        <v>338</v>
       </c>
       <c r="G84" s="132" t="str">
         <f t="shared" si="2"/>
@@ -5582,10 +5587,10 @@
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B85" s="127" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C85" s="177" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="D85" s="180">
         <v>2</v>
@@ -5594,7 +5599,7 @@
         <v>118</v>
       </c>
       <c r="F85" s="131" t="s">
-        <v>313</v>
+        <v>338</v>
       </c>
       <c r="G85" s="132" t="str">
         <f t="shared" si="2"/>
@@ -5608,16 +5613,16 @@
         <v>46</v>
       </c>
       <c r="C86" s="177" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D86" s="180" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E86" s="178" t="s">
         <v>118</v>
       </c>
       <c r="F86" s="131" t="s">
-        <v>313</v>
+        <v>338</v>
       </c>
       <c r="G86" s="132" t="str">
         <f t="shared" si="2"/>
@@ -5631,16 +5636,16 @@
         <v>47</v>
       </c>
       <c r="C87" s="177" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D87" s="180" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="E87" s="178" t="s">
         <v>118</v>
       </c>
       <c r="F87" s="131" t="s">
-        <v>313</v>
+        <v>338</v>
       </c>
       <c r="G87" s="132" t="str">
         <f t="shared" si="2"/>
@@ -5669,7 +5674,7 @@
     </row>
     <row r="90" spans="2:9" x14ac:dyDescent="0.3">
       <c r="H90" s="141" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I90" s="120">
         <f>AVERAGE(I7:I88)</f>
@@ -5678,20 +5683,20 @@
     </row>
     <row r="91" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B91" s="47" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
     </row>
     <row r="92" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B92" s="146" t="s">
+        <v>152</v>
+      </c>
+      <c r="C92" s="169" t="s">
         <v>153</v>
-      </c>
-      <c r="C92" s="169" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="93" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B93" s="170" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C93" s="171">
         <f>D17</f>
@@ -5700,7 +5705,7 @@
     </row>
     <row r="94" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B94" s="170" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C94" s="171">
         <f>D18</f>
@@ -5709,7 +5714,7 @@
     </row>
     <row r="95" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B95" s="170" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C95" s="171">
         <f>D46</f>
@@ -5736,7 +5741,7 @@
     </row>
     <row r="98" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B98" s="172" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C98" s="173">
         <f>D19</f>
@@ -5762,6 +5767,9 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="B6:I100" xr:uid="{D1EE59D4-4937-4491-BD3F-7DBC007EDF85}">
+    <filterColumn colId="4" showButton="0"/>
+  </autoFilter>
   <mergeCells count="2">
     <mergeCell ref="B4:I5"/>
     <mergeCell ref="F6:G6"/>
@@ -5794,12 +5802,12 @@
     </row>
     <row r="3" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B3" s="9" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="4" spans="2:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="74" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C4" s="74"/>
       <c r="D4" s="74"/>
@@ -5845,7 +5853,7 @@
     </row>
     <row r="7" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B7" s="5" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C7" s="17"/>
       <c r="D7" s="18"/>
@@ -5857,10 +5865,10 @@
     </row>
     <row r="8" spans="2:9" ht="57" x14ac:dyDescent="0.3">
       <c r="B8" s="16" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="D8" s="15">
         <v>1</v>
@@ -5869,7 +5877,7 @@
         <v>118</v>
       </c>
       <c r="F8" s="87" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G8" s="81" t="str">
         <f t="shared" ref="G8:G21" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F8,"/Readme.md"),"Ver")</f>
@@ -5882,10 +5890,10 @@
     </row>
     <row r="9" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B9" s="16" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D9" s="15">
         <v>1</v>
@@ -5894,7 +5902,7 @@
         <v>118</v>
       </c>
       <c r="F9" s="87" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="G9" s="81" t="str">
         <f t="shared" si="0"/>
@@ -5905,10 +5913,10 @@
     </row>
     <row r="10" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B10" s="16" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D10" s="15">
         <v>1</v>
@@ -5917,7 +5925,7 @@
         <v>118</v>
       </c>
       <c r="F10" s="87" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="G10" s="81" t="str">
         <f t="shared" si="0"/>
@@ -5928,10 +5936,10 @@
     </row>
     <row r="11" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B11" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D11" s="15">
         <v>1</v>
@@ -5940,7 +5948,7 @@
         <v>118</v>
       </c>
       <c r="F11" s="87" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="G11" s="81" t="str">
         <f t="shared" si="0"/>
@@ -5951,10 +5959,10 @@
     </row>
     <row r="12" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B12" s="27" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D12" s="15">
         <v>1</v>
@@ -5963,7 +5971,7 @@
         <v>118</v>
       </c>
       <c r="F12" s="87" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="G12" s="81" t="str">
         <f t="shared" si="0"/>
@@ -5974,10 +5982,10 @@
     </row>
     <row r="13" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B13" s="27" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D13" s="15">
         <v>1</v>
@@ -5986,7 +5994,7 @@
         <v>118</v>
       </c>
       <c r="F13" s="87" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="G13" s="81" t="str">
         <f t="shared" si="0"/>
@@ -5997,10 +6005,10 @@
     </row>
     <row r="14" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B14" s="16" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D14" s="15">
         <v>1</v>
@@ -6009,7 +6017,7 @@
         <v>118</v>
       </c>
       <c r="F14" s="87" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="G14" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6020,10 +6028,10 @@
     </row>
     <row r="15" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B15" s="16" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D15" s="15">
         <v>1</v>
@@ -6032,7 +6040,7 @@
         <v>118</v>
       </c>
       <c r="F15" s="87" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="G15" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6043,10 +6051,10 @@
     </row>
     <row r="16" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B16" s="27" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D16" s="15">
         <v>1</v>
@@ -6055,7 +6063,7 @@
         <v>118</v>
       </c>
       <c r="F16" s="87" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="G16" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6066,10 +6074,10 @@
     </row>
     <row r="17" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B17" s="27" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D17" s="15">
         <v>1</v>
@@ -6078,7 +6086,7 @@
         <v>118</v>
       </c>
       <c r="F17" s="87" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="G17" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6089,10 +6097,10 @@
     </row>
     <row r="18" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B18" s="27" t="s">
+        <v>202</v>
+      </c>
+      <c r="C18" s="19" t="s">
         <v>203</v>
-      </c>
-      <c r="C18" s="19" t="s">
-        <v>204</v>
       </c>
       <c r="D18" s="15">
         <v>1</v>
@@ -6101,7 +6109,7 @@
         <v>118</v>
       </c>
       <c r="F18" s="87" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="G18" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6112,10 +6120,10 @@
     </row>
     <row r="19" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B19" s="27" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D19" s="29">
         <v>1</v>
@@ -6124,7 +6132,7 @@
         <v>118</v>
       </c>
       <c r="F19" s="87" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G19" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6135,10 +6143,10 @@
     </row>
     <row r="20" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B20" s="27" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D20" s="29">
         <v>1</v>
@@ -6147,7 +6155,7 @@
         <v>118</v>
       </c>
       <c r="F20" s="87" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G20" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6171,7 +6179,7 @@
     </row>
     <row r="22" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B22" s="5" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="C22" s="17"/>
       <c r="D22" s="18"/>
@@ -6183,10 +6191,10 @@
     </row>
     <row r="23" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="B23" s="16" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D23" s="30">
         <f>'2.ArquitectonicaEstructural'!D31-'2.ArquitectonicaEstructural'!D37-'2.ArquitectonicaEstructural'!D43</f>
@@ -6196,7 +6204,7 @@
         <v>54</v>
       </c>
       <c r="F23" s="87" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G23" s="81" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F23,"/Readme.md"),"Ver")</f>
@@ -6209,10 +6217,10 @@
     </row>
     <row r="24" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B24" s="16" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D24" s="20">
         <v>992</v>
@@ -6221,7 +6229,7 @@
         <v>64</v>
       </c>
       <c r="F24" s="87" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G24" s="81" t="str">
         <f t="shared" ref="G24:G27" si="1">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F24,"/Readme.md"),"Ver")</f>
@@ -6232,10 +6240,10 @@
     </row>
     <row r="25" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B25" s="16" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D25" s="20">
         <v>1950</v>
@@ -6244,7 +6252,7 @@
         <v>64</v>
       </c>
       <c r="F25" s="87" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G25" s="81" t="str">
         <f t="shared" si="1"/>
@@ -6255,10 +6263,10 @@
     </row>
     <row r="26" spans="2:9" ht="45.6" x14ac:dyDescent="0.3">
       <c r="B26" s="16" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D26" s="15">
         <f>INT(D23/(D24/1000*D25/1000))</f>
@@ -6268,7 +6276,7 @@
         <v>118</v>
       </c>
       <c r="F26" s="87" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="G26" s="81" t="str">
         <f t="shared" si="1"/>
@@ -6292,7 +6300,7 @@
     </row>
     <row r="28" spans="2:9" ht="16.8" x14ac:dyDescent="0.4">
       <c r="H28" s="46" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I28" s="57">
         <f>AVERAGE(I7:I27)</f>
@@ -6333,12 +6341,12 @@
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B3" s="9" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="4" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B4" s="74" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C4" s="74"/>
       <c r="D4" s="74"/>
@@ -6384,7 +6392,7 @@
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B7" s="5" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C7" s="17"/>
       <c r="D7" s="18"/>
@@ -6396,10 +6404,10 @@
     </row>
     <row r="8" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B8" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D8" s="20">
         <v>3</v>
@@ -6408,7 +6416,7 @@
         <v>53</v>
       </c>
       <c r="F8" s="87" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G8" s="81" t="str">
         <f t="shared" ref="G8:G21" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F8,"/Readme.md"),"Ver")</f>
@@ -6421,10 +6429,10 @@
     </row>
     <row r="9" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B9" s="16" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D9" s="20">
         <v>2.5</v>
@@ -6433,7 +6441,7 @@
         <v>53</v>
       </c>
       <c r="F9" s="87" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G9" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6444,19 +6452,19 @@
     </row>
     <row r="10" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B10" s="16" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D10" s="20">
         <v>4</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F10" s="87" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G10" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6467,10 +6475,10 @@
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B11" s="16" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D11" s="20">
         <v>2</v>
@@ -6479,7 +6487,7 @@
         <v>53</v>
       </c>
       <c r="F11" s="87" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G11" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6490,10 +6498,10 @@
     </row>
     <row r="12" spans="2:9" ht="33.6" x14ac:dyDescent="0.4">
       <c r="B12" s="16" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D12" s="15">
         <f>D10*D11</f>
@@ -6503,7 +6511,7 @@
         <v>53</v>
       </c>
       <c r="F12" s="87" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G12" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6514,10 +6522,10 @@
     </row>
     <row r="13" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B13" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D13" s="20">
         <v>8</v>
@@ -6526,7 +6534,7 @@
         <v>53</v>
       </c>
       <c r="F13" s="87" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G13" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6537,20 +6545,20 @@
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B14" s="16" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D14" s="15" t="str">
         <f>IF(D12&lt;=D13, "Cumple","No cumple")</f>
         <v>Cumple</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="F14" s="87" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G14" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6561,10 +6569,10 @@
     </row>
     <row r="15" spans="2:9" ht="33.6" x14ac:dyDescent="0.4">
       <c r="B15" s="16" t="s">
+        <v>246</v>
+      </c>
+      <c r="C15" s="19" t="s">
         <v>247</v>
-      </c>
-      <c r="C15" s="19" t="s">
-        <v>248</v>
       </c>
       <c r="D15" s="20">
         <v>60</v>
@@ -6573,7 +6581,7 @@
         <v>53</v>
       </c>
       <c r="F15" s="87" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G15" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6584,10 +6592,10 @@
     </row>
     <row r="16" spans="2:9" ht="33.6" x14ac:dyDescent="0.4">
       <c r="B16" s="16" t="s">
+        <v>248</v>
+      </c>
+      <c r="C16" s="19" t="s">
         <v>249</v>
-      </c>
-      <c r="C16" s="19" t="s">
-        <v>250</v>
       </c>
       <c r="D16" s="15">
         <f>D15*D10</f>
@@ -6597,7 +6605,7 @@
         <v>53</v>
       </c>
       <c r="F16" s="87" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G16" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6621,7 +6629,7 @@
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B18" s="5" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="C18" s="17"/>
       <c r="D18" s="18"/>
@@ -6633,19 +6641,19 @@
     </row>
     <row r="19" spans="2:9" ht="45.6" x14ac:dyDescent="0.4">
       <c r="B19" s="16" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C19" s="19" t="s">
+        <v>239</v>
+      </c>
+      <c r="D19" s="20" t="s">
         <v>240</v>
-      </c>
-      <c r="D19" s="20" t="s">
-        <v>241</v>
       </c>
       <c r="E19" s="15" t="s">
         <v>118</v>
       </c>
       <c r="F19" s="87" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G19" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6658,19 +6666,19 @@
     </row>
     <row r="20" spans="2:9" ht="45.6" x14ac:dyDescent="0.4">
       <c r="B20" s="16" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C20" s="19" t="s">
+        <v>239</v>
+      </c>
+      <c r="D20" s="20" t="s">
         <v>240</v>
-      </c>
-      <c r="D20" s="20" t="s">
-        <v>241</v>
       </c>
       <c r="E20" s="15" t="s">
         <v>118</v>
       </c>
       <c r="F20" s="87" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G20" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6681,19 +6689,19 @@
     </row>
     <row r="21" spans="2:9" ht="45.6" x14ac:dyDescent="0.4">
       <c r="B21" s="16" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C21" s="19" t="s">
+        <v>239</v>
+      </c>
+      <c r="D21" s="20" t="s">
         <v>240</v>
-      </c>
-      <c r="D21" s="20" t="s">
-        <v>241</v>
       </c>
       <c r="E21" s="15" t="s">
         <v>118</v>
       </c>
       <c r="F21" s="87" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="G21" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6714,7 +6722,7 @@
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.4">
       <c r="H23" s="46" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I23" s="57">
         <f>AVERAGE(I7:I22)</f>
@@ -6755,12 +6763,12 @@
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B3" s="9" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B4" s="74" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C4" s="74"/>
       <c r="D4" s="74"/>
@@ -6806,10 +6814,10 @@
     </row>
     <row r="7" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B7" s="16" t="s">
+        <v>253</v>
+      </c>
+      <c r="C7" s="19" t="s">
         <v>254</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>255</v>
       </c>
       <c r="D7" s="20">
         <v>1</v>
@@ -6818,7 +6826,7 @@
         <v>118</v>
       </c>
       <c r="F7" s="87" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="G7" s="81" t="str">
         <f t="shared" ref="G7:G16" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F7,"/Readme.md"),"Ver")</f>
@@ -6831,10 +6839,10 @@
     </row>
     <row r="8" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B8" s="16" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D8" s="20">
         <v>1</v>
@@ -6843,7 +6851,7 @@
         <v>118</v>
       </c>
       <c r="F8" s="87" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="G8" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6854,10 +6862,10 @@
     </row>
     <row r="9" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B9" s="16" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D9" s="20">
         <v>1</v>
@@ -6866,7 +6874,7 @@
         <v>118</v>
       </c>
       <c r="F9" s="87" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="G9" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6877,10 +6885,10 @@
     </row>
     <row r="10" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B10" s="16" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D10" s="20">
         <v>1</v>
@@ -6889,7 +6897,7 @@
         <v>118</v>
       </c>
       <c r="F10" s="87" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="G10" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6900,10 +6908,10 @@
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B11" s="16" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D11" s="20">
         <v>1</v>
@@ -6912,7 +6920,7 @@
         <v>118</v>
       </c>
       <c r="F11" s="87" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="G11" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6923,10 +6931,10 @@
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B12" s="16" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D12" s="20">
         <v>1</v>
@@ -6935,7 +6943,7 @@
         <v>118</v>
       </c>
       <c r="F12" s="87" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="G12" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6946,10 +6954,10 @@
     </row>
     <row r="13" spans="2:9" ht="33.6" x14ac:dyDescent="0.4">
       <c r="B13" s="16" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D13" s="20">
         <v>1</v>
@@ -6958,7 +6966,7 @@
         <v>118</v>
       </c>
       <c r="F13" s="87" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="G13" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6969,10 +6977,10 @@
     </row>
     <row r="14" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B14" s="16" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D14" s="20">
         <v>1</v>
@@ -6981,7 +6989,7 @@
         <v>118</v>
       </c>
       <c r="F14" s="87" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="G14" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6992,10 +7000,10 @@
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B15" s="16" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D15" s="20">
         <v>1</v>
@@ -7004,7 +7012,7 @@
         <v>118</v>
       </c>
       <c r="F15" s="87" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="G15" s="81" t="str">
         <f t="shared" si="0"/>
@@ -7028,7 +7036,7 @@
     </row>
     <row r="17" spans="8:9" x14ac:dyDescent="0.4">
       <c r="H17" s="46" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="I17" s="57">
         <f>AVERAGE(I7:I16)</f>
@@ -7075,7 +7083,7 @@
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B3" s="80" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C3" s="80"/>
       <c r="D3" s="80"/>
@@ -7086,7 +7094,7 @@
     </row>
     <row r="4" spans="2:8" s="36" customFormat="1" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="74" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="C4" s="74"/>
       <c r="D4" s="74"/>
@@ -7127,16 +7135,16 @@
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B7" s="16" t="s">
+        <v>276</v>
+      </c>
+      <c r="C7" s="19" t="s">
         <v>277</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>278</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>34</v>
       </c>
       <c r="E7" s="131" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F7" s="81" t="str">
         <f t="shared" ref="F7:F16" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",E7,"/Readme.md"),"Ver")</f>
@@ -7152,13 +7160,13 @@
         <v>19</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>30</v>
       </c>
       <c r="E8" s="131" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F8" s="81" t="str">
         <f t="shared" si="0"/>
@@ -7169,16 +7177,16 @@
     </row>
     <row r="9" spans="2:8" ht="91.2" x14ac:dyDescent="0.3">
       <c r="B9" s="16" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E9" s="131" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="F9" s="81" t="str">
         <f t="shared" si="0"/>
@@ -7189,16 +7197,16 @@
     </row>
     <row r="10" spans="2:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B10" s="16" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>31</v>
       </c>
       <c r="E10" s="131" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="F10" s="81" t="str">
         <f t="shared" si="0"/>
@@ -7209,16 +7217,16 @@
     </row>
     <row r="11" spans="2:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="B11" s="16" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>32</v>
       </c>
       <c r="E11" s="131" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="F11" s="81" t="str">
         <f t="shared" si="0"/>
@@ -7229,16 +7237,16 @@
     </row>
     <row r="12" spans="2:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B12" s="16" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>33</v>
       </c>
       <c r="E12" s="131" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="F12" s="81" t="str">
         <f t="shared" si="0"/>
@@ -7249,16 +7257,16 @@
     </row>
     <row r="13" spans="2:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B13" s="16" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="E13" s="131" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F13" s="81" t="str">
         <f t="shared" si="0"/>
@@ -7269,16 +7277,16 @@
     </row>
     <row r="14" spans="2:8" ht="79.8" x14ac:dyDescent="0.3">
       <c r="B14" s="16" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E14" s="131" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="F14" s="81" t="str">
         <f t="shared" si="0"/>
@@ -7289,13 +7297,13 @@
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B15" s="16" t="s">
+        <v>304</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>305</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>306</v>
-      </c>
-      <c r="C15" s="19" t="s">
-        <v>307</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>308</v>
       </c>
       <c r="E15" s="55"/>
       <c r="F15" s="81" t="str">
@@ -7319,7 +7327,7 @@
     </row>
     <row r="17" spans="7:8" x14ac:dyDescent="0.3">
       <c r="G17" s="46" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H17" s="31">
         <f>AVERAGE(H7:H16)</f>

--- a/file/table/DAPC_ProyectoCAD.xlsx
+++ b/file/table/DAPC_ProyectoCAD.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2435E275-F9E6-4B4C-B1D6-0A964095D000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5D55ADD-F040-4C34-A8F1-6A95E602EA2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/file/table/DAPC_ProyectoCAD.xlsx
+++ b/file/table/DAPC_ProyectoCAD.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5D55ADD-F040-4C34-A8F1-6A95E602EA2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{483FD17B-125F-4378-8242-F4E84B0139B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -499,9 +499,6 @@
     <t>Ancho total del lote. Igual al ancho de la bodega debido a que no se permiten voladizos laterales ni sobre extensiones de la cubierta.</t>
   </si>
   <si>
-    <t>Ver especificaciones técnicas en archivo /file/ref/FT_D37-AXP-AXD-AXM-104.pdf. Utilizar cuadrado con lado igual al diametro externo ØC.</t>
-  </si>
-  <si>
     <t>Ver especificaciones técnicas en archivo /file/ref/FT_D37-AXP-AXD-AXM-104.pdf.</t>
   </si>
   <si>
@@ -565,9 +562,6 @@
     <t xml:space="preserve">Pendiente mínima de inclinación de la cubierta para asegurar el buen drenaje del agua provendiente de la lluvia o precipitación. Cómo referencia, para láminas metálicas continuas, algunos fabricantes recomiendan pendientes tan bajas como 2%, mientras que para cubiertas con solapes, se sugiere una pendiente mínima del 10% para evitar filtraciones. </t>
   </si>
   <si>
-    <t>Ancho</t>
-  </si>
-  <si>
     <t>Separación</t>
   </si>
   <si>
@@ -581,9 +575,6 @@
   </si>
   <si>
     <t>Separación de corredores a lo largo de la cubierta. Cómo mínimo cada 15 metros.</t>
-  </si>
-  <si>
-    <t>Líneas a lo largo de toda la cubierta cubriendo todo el ancho y en forma de cruz. No incluir en voladizo de cubierta.</t>
   </si>
   <si>
     <t>Área total ocupada. Descontar del ánálisis de áreas de páneles solares.</t>
@@ -1395,9 +1386,6 @@
     </r>
   </si>
   <si>
-    <t>2c. Líneas de vida</t>
-  </si>
-  <si>
     <t>2d. Distribución arquitectónica interna</t>
   </si>
   <si>
@@ -1514,6 +1502,18 @@
       </rPr>
       <t>Ver nota 1a.</t>
     </r>
+  </si>
+  <si>
+    <t>Ver especificaciones técnicas en archivo /file/ref/FT_D37-AXP-AXD-AXM-104.pdf. Utilizar cuadrado con lado igual al diametro externo ØC. Dibujar elemento en planta y en alzado usando líneas y curvas.</t>
+  </si>
+  <si>
+    <t>2c. Líneas de vida y pasarelas</t>
+  </si>
+  <si>
+    <t>Ancho pasarela</t>
+  </si>
+  <si>
+    <t>Líneas y pasarelas a lo largo de toda la cubierta cubriendo todo el ancho y en forma de cruz. No incluir en voladizo de cubierta.</t>
   </si>
 </sst>
 </file>
@@ -2990,7 +2990,7 @@
   <sheetData>
     <row r="1" spans="2:5" x14ac:dyDescent="0.3">
       <c r="E1" s="100" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
     </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.3">
@@ -3000,7 +3000,7 @@
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B3" s="101" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.3">
@@ -3270,7 +3270,7 @@
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B31" s="73" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="C31" s="73"/>
       <c r="D31" s="73"/>
@@ -3293,7 +3293,7 @@
         <v>1</v>
       </c>
       <c r="C33" s="77" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="D33" s="78"/>
       <c r="E33" s="51">
@@ -3306,7 +3306,7 @@
         <v>2</v>
       </c>
       <c r="C34" s="62" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="D34" s="63"/>
       <c r="E34" s="51">
@@ -3319,7 +3319,7 @@
         <v>3</v>
       </c>
       <c r="C35" s="62" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="D35" s="63"/>
       <c r="E35" s="51">
@@ -3332,7 +3332,7 @@
         <v>4</v>
       </c>
       <c r="C36" s="60" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="D36" s="61"/>
       <c r="E36" s="51">
@@ -3345,7 +3345,7 @@
         <v>4</v>
       </c>
       <c r="C37" s="62" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="D37" s="63"/>
       <c r="E37" s="51">
@@ -3358,7 +3358,7 @@
         <v>5</v>
       </c>
       <c r="C38" s="62" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="D38" s="63"/>
       <c r="E38" s="51">
@@ -3371,7 +3371,7 @@
         <v>6</v>
       </c>
       <c r="C39" s="62" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="D39" s="63"/>
       <c r="E39" s="99">
@@ -3383,7 +3383,7 @@
         <v>7</v>
       </c>
       <c r="C40" s="64" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="D40" s="65"/>
       <c r="E40" s="58">
@@ -3392,7 +3392,7 @@
     </row>
     <row r="41" spans="2:5" x14ac:dyDescent="0.3">
       <c r="D41" s="118" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="E41" s="59">
         <f>AVERAGE(E33:E40)</f>
@@ -3460,7 +3460,7 @@
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B4" s="102" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="C4" s="102"/>
       <c r="D4" s="102"/>
@@ -3498,10 +3498,10 @@
     </row>
     <row r="7" spans="2:9" ht="57" x14ac:dyDescent="0.3">
       <c r="B7" s="127" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C7" s="128" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="D7" s="91">
         <v>1</v>
@@ -3510,7 +3510,7 @@
         <v>16</v>
       </c>
       <c r="F7" s="131" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="G7" s="132" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F7,"/Readme.md"),"Ver")</f>
@@ -3523,19 +3523,19 @@
     </row>
     <row r="8" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B8" s="127" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="C8" s="128" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="D8" s="91">
         <v>1</v>
       </c>
       <c r="E8" s="130" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="F8" s="131" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="G8" s="132" t="str">
         <f t="shared" ref="G8:G18" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F8,"/Readme.md"),"Ver")</f>
@@ -3546,17 +3546,17 @@
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B9" s="127" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C9" s="128" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="D9" s="91" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="E9" s="130"/>
       <c r="F9" s="131" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="G9" s="132" t="str">
         <f t="shared" si="0"/>
@@ -3567,10 +3567,10 @@
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B10" s="127" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C10" s="128" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="D10" s="91">
         <v>1</v>
@@ -3579,7 +3579,7 @@
         <v>16</v>
       </c>
       <c r="F10" s="131" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G10" s="132" t="str">
         <f t="shared" si="0"/>
@@ -3590,17 +3590,17 @@
     </row>
     <row r="11" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
       <c r="B11" s="127" t="s">
+        <v>276</v>
+      </c>
+      <c r="C11" s="128" t="s">
         <v>279</v>
       </c>
-      <c r="C11" s="128" t="s">
-        <v>282</v>
-      </c>
       <c r="D11" s="91" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="E11" s="130"/>
       <c r="F11" s="131" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G11" s="132" t="str">
         <f t="shared" si="0"/>
@@ -3611,17 +3611,17 @@
     </row>
     <row r="12" spans="2:9" ht="57" x14ac:dyDescent="0.3">
       <c r="B12" s="127" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C12" s="128" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="D12" s="91" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="E12" s="130"/>
       <c r="F12" s="131" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="G12" s="132" t="str">
         <f t="shared" si="0"/>
@@ -3632,17 +3632,17 @@
     </row>
     <row r="13" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B13" s="127" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="C13" s="128" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="D13" s="91" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="E13" s="130"/>
       <c r="F13" s="131" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="G13" s="132" t="str">
         <f t="shared" si="0"/>
@@ -3653,17 +3653,17 @@
     </row>
     <row r="14" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
       <c r="B14" s="127" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="C14" s="128" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="D14" s="91" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="E14" s="130"/>
       <c r="F14" s="131" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G14" s="132" t="str">
         <f t="shared" si="0"/>
@@ -3674,10 +3674,10 @@
     </row>
     <row r="15" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="B15" s="127" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="C15" s="128" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="D15" s="91">
         <v>1</v>
@@ -3686,7 +3686,7 @@
         <v>16</v>
       </c>
       <c r="F15" s="131" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="G15" s="132" t="str">
         <f t="shared" si="0"/>
@@ -3697,10 +3697,10 @@
     </row>
     <row r="16" spans="2:9" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="127" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="C16" s="128" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="D16" s="91">
         <v>1</v>
@@ -3709,7 +3709,7 @@
         <v>16</v>
       </c>
       <c r="F16" s="131" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="G16" s="132" t="str">
         <f t="shared" si="0"/>
@@ -3720,10 +3720,10 @@
     </row>
     <row r="17" spans="2:9" ht="35.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="134" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="C17" s="135" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="D17" s="91">
         <v>1</v>
@@ -3732,7 +3732,7 @@
         <v>16</v>
       </c>
       <c r="F17" s="131" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="G17" s="132" t="str">
         <f t="shared" si="0"/>
@@ -3756,7 +3756,7 @@
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.3">
       <c r="H19" s="141" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="I19" s="120">
         <f>AVERAGE(I7:I18)</f>
@@ -3801,12 +3801,12 @@
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B3" s="101" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B4" s="102" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="C4" s="102"/>
       <c r="D4" s="102"/>
@@ -3852,7 +3852,7 @@
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B7" s="146" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="C7" s="147"/>
       <c r="D7" s="148"/>
@@ -3864,10 +3864,10 @@
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B8" s="127" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C8" s="128" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="D8" s="129">
         <v>8</v>
@@ -3876,14 +3876,14 @@
         <v>53</v>
       </c>
       <c r="F8" s="131" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G8" s="132" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F8,"/Readme.md"),"Ver")</f>
         <v>Ver</v>
       </c>
       <c r="H8" s="128" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="I8" s="133">
         <v>5</v>
@@ -3891,10 +3891,10 @@
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B9" s="127" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C9" s="128" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D9" s="129">
         <v>10</v>
@@ -3903,23 +3903,23 @@
         <v>53</v>
       </c>
       <c r="F9" s="131" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G9" s="132" t="str">
         <f t="shared" ref="G9:G72" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F9,"/Readme.md"),"Ver")</f>
         <v>Ver</v>
       </c>
       <c r="H9" s="128" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="I9" s="133"/>
     </row>
     <row r="10" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B10" s="127" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="C10" s="128" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D10" s="130">
         <f>D8+SumUDig</f>
@@ -3929,7 +3929,7 @@
         <v>53</v>
       </c>
       <c r="F10" s="131" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G10" s="132" t="str">
         <f t="shared" si="0"/>
@@ -3940,10 +3940,10 @@
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B11" s="127" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C11" s="128" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D11" s="130" cm="1">
         <f t="array" ref="D11">D9+SumUDig</f>
@@ -3953,7 +3953,7 @@
         <v>53</v>
       </c>
       <c r="F11" s="131" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G11" s="132" t="str">
         <f t="shared" si="0"/>
@@ -3967,7 +3967,7 @@
         <v>39</v>
       </c>
       <c r="C12" s="128" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="D12" s="129">
         <v>12</v>
@@ -3976,14 +3976,14 @@
         <v>53</v>
       </c>
       <c r="F12" s="131" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G12" s="132" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H12" s="128" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="I12" s="133"/>
     </row>
@@ -3992,7 +3992,7 @@
         <v>60</v>
       </c>
       <c r="C13" s="128" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D13" s="129">
         <v>6</v>
@@ -4001,14 +4001,14 @@
         <v>53</v>
       </c>
       <c r="F13" s="131" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G13" s="132" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H13" s="128" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="I13" s="133"/>
     </row>
@@ -4017,7 +4017,7 @@
         <v>40</v>
       </c>
       <c r="C14" s="128" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D14" s="129">
         <v>12</v>
@@ -4026,14 +4026,14 @@
         <v>53</v>
       </c>
       <c r="F14" s="131" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G14" s="132" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H14" s="128" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="I14" s="133"/>
     </row>
@@ -4052,7 +4052,7 @@
         <v>53</v>
       </c>
       <c r="F15" s="131" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G15" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4076,7 +4076,7 @@
         <v>53</v>
       </c>
       <c r="F16" s="131" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G16" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4090,7 +4090,7 @@
         <v>50</v>
       </c>
       <c r="C17" s="128" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="D17" s="130">
         <f>D16*D15</f>
@@ -4100,7 +4100,7 @@
         <v>54</v>
       </c>
       <c r="F17" s="131" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G17" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4111,10 +4111,10 @@
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B18" s="134" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C18" s="135" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="D18" s="152">
         <f>D32+D30</f>
@@ -4124,7 +4124,7 @@
         <v>54</v>
       </c>
       <c r="F18" s="131" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G18" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4135,10 +4135,10 @@
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B19" s="134" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="C19" s="135" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="D19" s="152">
         <f>D32+D30+D46</f>
@@ -4148,7 +4148,7 @@
         <v>54</v>
       </c>
       <c r="F19" s="131" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G19" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4159,20 +4159,20 @@
     </row>
     <row r="20" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="B20" s="134" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C20" s="135" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="D20" s="152">
         <f>D18/D17</f>
         <v>0.74545454545454548</v>
       </c>
       <c r="E20" s="152" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F20" s="131" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G20" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4183,20 +4183,20 @@
     </row>
     <row r="21" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B21" s="134" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C21" s="135" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="D21" s="152">
         <f>D19/D17</f>
         <v>0.77662337662337666</v>
       </c>
       <c r="E21" s="152" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F21" s="131" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G21" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4220,7 +4220,7 @@
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B23" s="146" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="C23" s="147"/>
       <c r="D23" s="148"/>
@@ -4232,10 +4232,10 @@
     </row>
     <row r="24" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="B24" s="127" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C24" s="128" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="D24" s="129">
         <v>2</v>
@@ -4244,14 +4244,14 @@
         <v>53</v>
       </c>
       <c r="F24" s="131" t="s">
-        <v>338</v>
+        <v>308</v>
       </c>
       <c r="G24" s="132" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H24" s="128" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="I24" s="133">
         <v>5</v>
@@ -4259,19 +4259,19 @@
     </row>
     <row r="25" spans="2:9" ht="57" x14ac:dyDescent="0.3">
       <c r="B25" s="127" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C25" s="128" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D25" s="32">
         <v>5</v>
       </c>
       <c r="E25" s="130" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F25" s="131" t="s">
-        <v>338</v>
+        <v>308</v>
       </c>
       <c r="G25" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4282,20 +4282,20 @@
     </row>
     <row r="26" spans="2:9" ht="45.6" x14ac:dyDescent="0.3">
       <c r="B26" s="127" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C26" s="128" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D26" s="130">
         <f>ROUND(ATAN(D25/100)*180/PI(),0)</f>
         <v>3</v>
       </c>
       <c r="E26" s="130" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F26" s="131" t="s">
-        <v>338</v>
+        <v>308</v>
       </c>
       <c r="G26" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4306,10 +4306,10 @@
     </row>
     <row r="27" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B27" s="134" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C27" s="135" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="D27" s="155">
         <v>0.6</v>
@@ -4318,7 +4318,7 @@
         <v>53</v>
       </c>
       <c r="F27" s="131" t="s">
-        <v>338</v>
+        <v>308</v>
       </c>
       <c r="G27" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4329,10 +4329,10 @@
     </row>
     <row r="28" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
       <c r="B28" s="127" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C28" s="128" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="D28" s="129">
         <v>0.2</v>
@@ -4341,7 +4341,7 @@
         <v>53</v>
       </c>
       <c r="F28" s="131" t="s">
-        <v>338</v>
+        <v>308</v>
       </c>
       <c r="G28" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4352,19 +4352,19 @@
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B29" s="127" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="C29" s="128" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D29" s="129">
         <v>2</v>
       </c>
       <c r="E29" s="130" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F29" s="131" t="s">
-        <v>338</v>
+        <v>308</v>
       </c>
       <c r="G29" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4375,10 +4375,10 @@
     </row>
     <row r="30" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B30" s="134" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C30" s="135" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="D30" s="152">
         <f>(D27-D28)*(D11+D24+D24)*D29</f>
@@ -4388,7 +4388,7 @@
         <v>54</v>
       </c>
       <c r="F30" s="131" t="s">
-        <v>338</v>
+        <v>308</v>
       </c>
       <c r="G30" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4399,10 +4399,10 @@
     </row>
     <row r="31" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="B31" s="127" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="C31" s="128" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D31" s="130">
         <f>(D10*D11)-D30</f>
@@ -4412,7 +4412,7 @@
         <v>54</v>
       </c>
       <c r="F31" s="131" t="s">
-        <v>338</v>
+        <v>308</v>
       </c>
       <c r="G31" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4423,10 +4423,10 @@
     </row>
     <row r="32" spans="2:9" ht="45.6" x14ac:dyDescent="0.3">
       <c r="B32" s="127" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="C32" s="128" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="D32" s="130">
         <f>((D10*D11)+D10*(D24+D24))-D30</f>
@@ -4436,7 +4436,7 @@
         <v>54</v>
       </c>
       <c r="F32" s="131" t="s">
-        <v>338</v>
+        <v>308</v>
       </c>
       <c r="G32" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4447,10 +4447,10 @@
     </row>
     <row r="33" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B33" s="127" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C33" s="128" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D33" s="129">
         <v>10</v>
@@ -4459,7 +4459,7 @@
         <v>53</v>
       </c>
       <c r="F33" s="131" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G33" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4470,20 +4470,20 @@
     </row>
     <row r="34" spans="2:9" ht="45.6" x14ac:dyDescent="0.3">
       <c r="B34" s="127" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C34" s="128" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D34" s="130">
         <f>EVEN(D31/(D33*D33))</f>
         <v>14</v>
       </c>
       <c r="E34" s="130" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F34" s="131" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G34" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4494,19 +4494,19 @@
     </row>
     <row r="35" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B35" s="127" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="C35" s="128" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D35" s="129">
         <v>1200</v>
       </c>
       <c r="E35" s="130" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F35" s="131" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G35" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4515,12 +4515,12 @@
       <c r="H35" s="128"/>
       <c r="I35" s="133"/>
     </row>
-    <row r="36" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="B36" s="127" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C36" s="128" t="s">
-        <v>62</v>
+        <v>343</v>
       </c>
       <c r="D36" s="130">
         <f>D35*D35/(1000*1000)</f>
@@ -4530,7 +4530,7 @@
         <v>54</v>
       </c>
       <c r="F36" s="131" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G36" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4541,10 +4541,10 @@
     </row>
     <row r="37" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
       <c r="B37" s="127" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C37" s="128" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="D37" s="130">
         <f>D34*D36</f>
@@ -4554,7 +4554,7 @@
         <v>54</v>
       </c>
       <c r="F37" s="131" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G37" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4578,7 +4578,7 @@
     </row>
     <row r="39" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B39" s="156" t="s">
-        <v>325</v>
+        <v>344</v>
       </c>
       <c r="C39" s="147"/>
       <c r="D39" s="148"/>
@@ -4590,10 +4590,10 @@
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B40" s="127" t="s">
-        <v>84</v>
+        <v>345</v>
       </c>
       <c r="C40" s="128" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D40" s="129">
         <v>1</v>
@@ -4602,7 +4602,7 @@
         <v>53</v>
       </c>
       <c r="F40" s="131" t="s">
-        <v>338</v>
+        <v>308</v>
       </c>
       <c r="G40" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4615,10 +4615,10 @@
     </row>
     <row r="41" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B41" s="127" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C41" s="128" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D41" s="129">
         <v>15</v>
@@ -4627,7 +4627,7 @@
         <v>53</v>
       </c>
       <c r="F41" s="131" t="s">
-        <v>338</v>
+        <v>308</v>
       </c>
       <c r="G41" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4638,10 +4638,10 @@
     </row>
     <row r="42" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B42" s="127" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C42" s="128" t="s">
-        <v>90</v>
+        <v>346</v>
       </c>
       <c r="D42" s="130">
         <f>D11+(INT(D11/D41)*D10)</f>
@@ -4651,7 +4651,7 @@
         <v>53</v>
       </c>
       <c r="F42" s="131" t="s">
-        <v>338</v>
+        <v>308</v>
       </c>
       <c r="G42" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4662,10 +4662,10 @@
     </row>
     <row r="43" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B43" s="127" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C43" s="128" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="D43" s="130">
         <f>D42*D40</f>
@@ -4675,7 +4675,7 @@
         <v>54</v>
       </c>
       <c r="F43" s="131" t="s">
-        <v>338</v>
+        <v>308</v>
       </c>
       <c r="G43" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4699,7 +4699,7 @@
     </row>
     <row r="45" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B45" s="146" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="C45" s="147"/>
       <c r="D45" s="148"/>
@@ -4714,7 +4714,7 @@
         <v>41</v>
       </c>
       <c r="C46" s="128" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="D46" s="129">
         <v>60</v>
@@ -4723,7 +4723,7 @@
         <v>54</v>
       </c>
       <c r="F46" s="131" t="s">
-        <v>338</v>
+        <v>308</v>
       </c>
       <c r="G46" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4748,7 +4748,7 @@
         <v>54</v>
       </c>
       <c r="F47" s="131" t="s">
-        <v>338</v>
+        <v>308</v>
       </c>
       <c r="G47" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4759,10 +4759,10 @@
     </row>
     <row r="48" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B48" s="127" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C48" s="128" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="D48" s="129">
         <v>3.9900000000000007</v>
@@ -4771,7 +4771,7 @@
         <v>53</v>
       </c>
       <c r="F48" s="131" t="s">
-        <v>338</v>
+        <v>308</v>
       </c>
       <c r="G48" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4782,10 +4782,10 @@
     </row>
     <row r="49" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B49" s="127" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C49" s="128" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="D49" s="130">
         <f>D46-D54</f>
@@ -4795,7 +4795,7 @@
         <v>54</v>
       </c>
       <c r="F49" s="131" t="s">
-        <v>338</v>
+        <v>308</v>
       </c>
       <c r="G49" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4818,7 +4818,7 @@
         <v>55</v>
       </c>
       <c r="F50" s="131" t="s">
-        <v>338</v>
+        <v>308</v>
       </c>
       <c r="G50" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4829,7 +4829,7 @@
     </row>
     <row r="51" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B51" s="127" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C51" s="128" t="s">
         <v>58</v>
@@ -4841,7 +4841,7 @@
         <v>55</v>
       </c>
       <c r="F51" s="131" t="s">
-        <v>338</v>
+        <v>308</v>
       </c>
       <c r="G51" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4852,10 +4852,10 @@
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B52" s="127" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C52" s="128" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D52" s="130">
         <f>D48/(D51/100)</f>
@@ -4865,7 +4865,7 @@
         <v>49</v>
       </c>
       <c r="F52" s="131" t="s">
-        <v>338</v>
+        <v>308</v>
       </c>
       <c r="G52" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4876,10 +4876,10 @@
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B53" s="127" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C53" s="128" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D53" s="129">
         <v>1.2</v>
@@ -4888,7 +4888,7 @@
         <v>53</v>
       </c>
       <c r="F53" s="131" t="s">
-        <v>338</v>
+        <v>308</v>
       </c>
       <c r="G53" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4899,10 +4899,10 @@
     </row>
     <row r="54" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B54" s="127" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="C54" s="128" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D54" s="157">
         <f>D53*D52*(D50/100)</f>
@@ -4912,7 +4912,7 @@
         <v>54</v>
       </c>
       <c r="F54" s="131" t="s">
-        <v>338</v>
+        <v>308</v>
       </c>
       <c r="G54" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4923,10 +4923,10 @@
     </row>
     <row r="55" spans="2:9" ht="68.400000000000006" x14ac:dyDescent="0.3">
       <c r="B55" s="127" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="C55" s="128" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="D55" s="129">
         <v>6</v>
@@ -4935,7 +4935,7 @@
         <v>53</v>
       </c>
       <c r="F55" s="131" t="s">
-        <v>338</v>
+        <v>311</v>
       </c>
       <c r="G55" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4946,10 +4946,10 @@
     </row>
     <row r="56" spans="2:9" ht="68.400000000000006" x14ac:dyDescent="0.3">
       <c r="B56" s="127" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="C56" s="128" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="D56" s="129">
         <v>4.5</v>
@@ -4958,7 +4958,7 @@
         <v>53</v>
       </c>
       <c r="F56" s="131" t="s">
-        <v>338</v>
+        <v>311</v>
       </c>
       <c r="G56" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4969,10 +4969,10 @@
     </row>
     <row r="57" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B57" s="127" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="C57" s="128" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="D57" s="129">
         <v>1.2</v>
@@ -4981,7 +4981,7 @@
         <v>53</v>
       </c>
       <c r="F57" s="131" t="s">
-        <v>338</v>
+        <v>311</v>
       </c>
       <c r="G57" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4992,10 +4992,10 @@
     </row>
     <row r="58" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B58" s="127" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="C58" s="128" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="D58" s="129">
         <v>2.2999999999999998</v>
@@ -5004,7 +5004,7 @@
         <v>53</v>
       </c>
       <c r="F58" s="131" t="s">
-        <v>338</v>
+        <v>311</v>
       </c>
       <c r="G58" s="132" t="str">
         <f t="shared" si="0"/>
@@ -5015,10 +5015,10 @@
     </row>
     <row r="59" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B59" s="127" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="C59" s="128" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="D59" s="129">
         <v>3</v>
@@ -5027,7 +5027,7 @@
         <v>53</v>
       </c>
       <c r="F59" s="131" t="s">
-        <v>338</v>
+        <v>311</v>
       </c>
       <c r="G59" s="132" t="str">
         <f t="shared" si="0"/>
@@ -5038,10 +5038,10 @@
     </row>
     <row r="60" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B60" s="127" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="C60" s="128" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="D60" s="129">
         <v>2</v>
@@ -5050,7 +5050,7 @@
         <v>53</v>
       </c>
       <c r="F60" s="131" t="s">
-        <v>338</v>
+        <v>311</v>
       </c>
       <c r="G60" s="132" t="str">
         <f t="shared" si="0"/>
@@ -5074,7 +5074,7 @@
     </row>
     <row r="62" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B62" s="158" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="C62" s="159"/>
       <c r="D62" s="160"/>
@@ -5086,10 +5086,10 @@
     </row>
     <row r="63" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B63" s="127" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="C63" s="128" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D63" s="129">
         <v>40</v>
@@ -5098,7 +5098,7 @@
         <v>55</v>
       </c>
       <c r="F63" s="131" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G63" s="132" t="str">
         <f t="shared" si="0"/>
@@ -5111,10 +5111,10 @@
     </row>
     <row r="64" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B64" s="127" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="C64" s="128" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="D64" s="157">
         <f>D18</f>
@@ -5124,7 +5124,7 @@
         <v>54</v>
       </c>
       <c r="F64" s="131" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G64" s="132" t="str">
         <f t="shared" si="0"/>
@@ -5135,10 +5135,10 @@
     </row>
     <row r="65" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B65" s="127" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="C65" s="128" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="D65" s="129">
         <v>20</v>
@@ -5147,7 +5147,7 @@
         <v>55</v>
       </c>
       <c r="F65" s="131" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G65" s="132" t="str">
         <f t="shared" si="0"/>
@@ -5158,10 +5158,10 @@
     </row>
     <row r="66" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
       <c r="B66" s="127" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="C66" s="128" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="D66" s="129">
         <v>6</v>
@@ -5170,7 +5170,7 @@
         <v>53</v>
       </c>
       <c r="F66" s="131" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G66" s="132" t="str">
         <f t="shared" si="0"/>
@@ -5181,20 +5181,20 @@
     </row>
     <row r="67" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
       <c r="B67" s="127" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="C67" s="128" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="D67" s="157">
         <f>ROUND(D10/D66,0)</f>
         <v>6</v>
       </c>
       <c r="E67" s="130" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F67" s="131" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G67" s="132" t="str">
         <f t="shared" si="0"/>
@@ -5205,20 +5205,20 @@
     </row>
     <row r="68" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
       <c r="B68" s="127" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="C68" s="128" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D68" s="157">
         <f>ROUND(D11/D66,0)</f>
         <v>6</v>
       </c>
       <c r="E68" s="130" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F68" s="131" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G68" s="132" t="str">
         <f t="shared" si="0"/>
@@ -5229,20 +5229,20 @@
     </row>
     <row r="69" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B69" s="127" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="C69" s="128" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D69" s="157">
         <f>D68*D67</f>
         <v>36</v>
       </c>
       <c r="E69" s="130" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F69" s="131" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G69" s="132" t="str">
         <f t="shared" si="0"/>
@@ -5253,10 +5253,10 @@
     </row>
     <row r="70" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="B70" s="127" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="C70" s="128" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="D70" s="129">
         <v>0.25</v>
@@ -5265,7 +5265,7 @@
         <v>53</v>
       </c>
       <c r="F70" s="131" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G70" s="132" t="str">
         <f t="shared" si="0"/>
@@ -5276,10 +5276,10 @@
     </row>
     <row r="71" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="B71" s="127" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C71" s="128" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="D71" s="129">
         <v>0.4</v>
@@ -5288,7 +5288,7 @@
         <v>53</v>
       </c>
       <c r="F71" s="131" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G71" s="132" t="str">
         <f t="shared" si="0"/>
@@ -5299,10 +5299,10 @@
     </row>
     <row r="72" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="B72" s="127" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C72" s="128" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="D72" s="129">
         <v>0.15</v>
@@ -5311,7 +5311,7 @@
         <v>53</v>
       </c>
       <c r="F72" s="131" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G72" s="132" t="str">
         <f t="shared" si="0"/>
@@ -5322,10 +5322,10 @@
     </row>
     <row r="73" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="B73" s="127" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="C73" s="128" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="D73" s="129">
         <v>0.4</v>
@@ -5334,7 +5334,7 @@
         <v>53</v>
       </c>
       <c r="F73" s="131" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G73" s="132" t="str">
         <f t="shared" ref="G73:G76" si="1">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F73,"/Readme.md"),"Ver")</f>
@@ -5345,10 +5345,10 @@
     </row>
     <row r="74" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="B74" s="127" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="C74" s="128" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="D74" s="157">
         <f>(D10-D70)/D67</f>
@@ -5358,7 +5358,7 @@
         <v>53</v>
       </c>
       <c r="F74" s="131" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G74" s="132" t="str">
         <f t="shared" si="1"/>
@@ -5369,10 +5369,10 @@
     </row>
     <row r="75" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="B75" s="127" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="C75" s="128" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="D75" s="157">
         <f>(D11-D71)/D68</f>
@@ -5382,7 +5382,7 @@
         <v>53</v>
       </c>
       <c r="F75" s="131" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G75" s="132" t="str">
         <f t="shared" si="1"/>
@@ -5406,7 +5406,7 @@
     </row>
     <row r="77" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B77" s="182" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="C77" s="159"/>
       <c r="D77" s="160"/>
@@ -5418,10 +5418,10 @@
     </row>
     <row r="78" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B78" s="127" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C78" s="177" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D78" s="178">
         <f>D64</f>
@@ -5431,7 +5431,7 @@
         <v>54</v>
       </c>
       <c r="F78" s="131" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G78" s="132" t="str">
         <f t="shared" ref="G78:G88" si="2">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F78,"/Readme.md"),"Ver")</f>
@@ -5442,20 +5442,20 @@
     </row>
     <row r="79" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
       <c r="B79" s="127" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C79" s="177" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D79" s="178">
         <f>D78*D63</f>
         <v>57400</v>
       </c>
       <c r="E79" s="178" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="F79" s="131" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G79" s="132" t="str">
         <f t="shared" si="2"/>
@@ -5466,10 +5466,10 @@
     </row>
     <row r="80" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B80" s="127" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C80" s="177" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D80" s="178">
         <f>D49</f>
@@ -5479,7 +5479,7 @@
         <v>54</v>
       </c>
       <c r="F80" s="131" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G80" s="132" t="str">
         <f t="shared" si="2"/>
@@ -5490,20 +5490,20 @@
     </row>
     <row r="81" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B81" s="127" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="C81" s="177" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="D81" s="178">
         <f>D69</f>
         <v>36</v>
       </c>
       <c r="E81" s="178" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F81" s="131" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G81" s="132" t="str">
         <f t="shared" si="2"/>
@@ -5514,10 +5514,10 @@
     </row>
     <row r="82" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
       <c r="B82" s="127" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C82" s="177" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="D82" s="178">
         <f>D81*D12</f>
@@ -5527,7 +5527,7 @@
         <v>53</v>
       </c>
       <c r="F82" s="131" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G82" s="132" t="str">
         <f t="shared" si="2"/>
@@ -5538,10 +5538,10 @@
     </row>
     <row r="83" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
       <c r="B83" s="127" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="C83" s="177" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D83" s="178">
         <f>((D67*D9)+(D68*D8))*INT(D12/D48)</f>
@@ -5551,7 +5551,7 @@
         <v>53</v>
       </c>
       <c r="F83" s="131" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G83" s="132" t="str">
         <f t="shared" si="2"/>
@@ -5562,19 +5562,19 @@
     </row>
     <row r="84" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
       <c r="B84" s="127" t="s">
+        <v>189</v>
+      </c>
+      <c r="C84" s="177" t="s">
         <v>192</v>
       </c>
-      <c r="C84" s="177" t="s">
-        <v>195</v>
-      </c>
       <c r="D84" s="180" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E84" s="178" t="s">
         <v>54</v>
       </c>
       <c r="F84" s="131" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G84" s="132" t="str">
         <f t="shared" si="2"/>
@@ -5587,19 +5587,19 @@
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B85" s="127" t="s">
+        <v>190</v>
+      </c>
+      <c r="C85" s="177" t="s">
         <v>193</v>
-      </c>
-      <c r="C85" s="177" t="s">
-        <v>196</v>
       </c>
       <c r="D85" s="180">
         <v>2</v>
       </c>
       <c r="E85" s="178" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F85" s="131" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G85" s="132" t="str">
         <f t="shared" si="2"/>
@@ -5613,16 +5613,16 @@
         <v>46</v>
       </c>
       <c r="C86" s="177" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D86" s="180" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E86" s="178" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F86" s="131" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G86" s="132" t="str">
         <f t="shared" si="2"/>
@@ -5636,16 +5636,16 @@
         <v>47</v>
       </c>
       <c r="C87" s="177" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D87" s="180" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="E87" s="178" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F87" s="131" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G87" s="132" t="str">
         <f t="shared" si="2"/>
@@ -5669,12 +5669,12 @@
     </row>
     <row r="89" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B89" s="168" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="90" spans="2:9" x14ac:dyDescent="0.3">
       <c r="H90" s="141" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="I90" s="120">
         <f>AVERAGE(I7:I88)</f>
@@ -5683,20 +5683,20 @@
     </row>
     <row r="91" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B91" s="47" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
     </row>
     <row r="92" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B92" s="146" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C92" s="169" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="93" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B93" s="170" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="C93" s="171">
         <f>D17</f>
@@ -5705,7 +5705,7 @@
     </row>
     <row r="94" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B94" s="170" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C94" s="171">
         <f>D18</f>
@@ -5714,7 +5714,7 @@
     </row>
     <row r="95" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B95" s="170" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="C95" s="171">
         <f>D46</f>
@@ -5741,7 +5741,7 @@
     </row>
     <row r="98" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B98" s="172" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C98" s="173">
         <f>D19</f>
@@ -5750,7 +5750,7 @@
     </row>
     <row r="99" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B99" s="174" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C99" s="175">
         <f>D20</f>
@@ -5759,7 +5759,7 @@
     </row>
     <row r="100" spans="2:3" x14ac:dyDescent="0.3">
       <c r="B100" s="164" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="C100" s="176">
         <f>D21</f>
@@ -5802,12 +5802,12 @@
     </row>
     <row r="3" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B3" s="9" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="4" spans="2:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="74" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="C4" s="74"/>
       <c r="D4" s="74"/>
@@ -5853,7 +5853,7 @@
     </row>
     <row r="7" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B7" s="5" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C7" s="17"/>
       <c r="D7" s="18"/>
@@ -5865,19 +5865,19 @@
     </row>
     <row r="8" spans="2:9" ht="57" x14ac:dyDescent="0.3">
       <c r="B8" s="16" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D8" s="15">
         <v>1</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F8" s="87" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G8" s="81" t="str">
         <f t="shared" ref="G8:G21" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F8,"/Readme.md"),"Ver")</f>
@@ -5890,19 +5890,19 @@
     </row>
     <row r="9" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B9" s="16" t="s">
+        <v>214</v>
+      </c>
+      <c r="C9" s="19" t="s">
         <v>217</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>220</v>
       </c>
       <c r="D9" s="15">
         <v>1</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F9" s="87" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="G9" s="81" t="str">
         <f t="shared" si="0"/>
@@ -5913,19 +5913,19 @@
     </row>
     <row r="10" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B10" s="16" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="D10" s="15">
         <v>1</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F10" s="87" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="G10" s="81" t="str">
         <f t="shared" si="0"/>
@@ -5936,19 +5936,19 @@
     </row>
     <row r="11" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B11" s="16" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D11" s="15">
         <v>1</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F11" s="87" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="G11" s="81" t="str">
         <f t="shared" si="0"/>
@@ -5959,19 +5959,19 @@
     </row>
     <row r="12" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B12" s="27" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="D12" s="15">
         <v>1</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F12" s="87" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="G12" s="81" t="str">
         <f t="shared" si="0"/>
@@ -5982,19 +5982,19 @@
     </row>
     <row r="13" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B13" s="27" t="s">
+        <v>216</v>
+      </c>
+      <c r="C13" s="19" t="s">
         <v>219</v>
-      </c>
-      <c r="C13" s="19" t="s">
-        <v>222</v>
       </c>
       <c r="D13" s="15">
         <v>1</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F13" s="87" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="G13" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6005,19 +6005,19 @@
     </row>
     <row r="14" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B14" s="16" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D14" s="15">
         <v>1</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F14" s="87" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="G14" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6028,19 +6028,19 @@
     </row>
     <row r="15" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B15" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="C15" s="19" t="s">
         <v>200</v>
-      </c>
-      <c r="C15" s="19" t="s">
-        <v>203</v>
       </c>
       <c r="D15" s="15">
         <v>1</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F15" s="87" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="G15" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6051,19 +6051,19 @@
     </row>
     <row r="16" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B16" s="27" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D16" s="15">
         <v>1</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F16" s="87" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="G16" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6074,19 +6074,19 @@
     </row>
     <row r="17" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B17" s="27" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D17" s="15">
         <v>1</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F17" s="87" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="G17" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6097,19 +6097,19 @@
     </row>
     <row r="18" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B18" s="27" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="C18" s="19" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D18" s="15">
         <v>1</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F18" s="87" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="G18" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6120,19 +6120,19 @@
     </row>
     <row r="19" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B19" s="27" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D19" s="29">
         <v>1</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F19" s="87" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G19" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6143,19 +6143,19 @@
     </row>
     <row r="20" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B20" s="27" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D20" s="29">
         <v>1</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F20" s="87" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G20" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6179,7 +6179,7 @@
     </row>
     <row r="22" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B22" s="5" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C22" s="17"/>
       <c r="D22" s="18"/>
@@ -6191,10 +6191,10 @@
     </row>
     <row r="23" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="B23" s="16" t="s">
+        <v>202</v>
+      </c>
+      <c r="C23" s="19" t="s">
         <v>205</v>
-      </c>
-      <c r="C23" s="19" t="s">
-        <v>208</v>
       </c>
       <c r="D23" s="30">
         <f>'2.ArquitectonicaEstructural'!D31-'2.ArquitectonicaEstructural'!D37-'2.ArquitectonicaEstructural'!D43</f>
@@ -6204,7 +6204,7 @@
         <v>54</v>
       </c>
       <c r="F23" s="87" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G23" s="81" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F23,"/Readme.md"),"Ver")</f>
@@ -6217,19 +6217,19 @@
     </row>
     <row r="24" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B24" s="16" t="s">
+        <v>204</v>
+      </c>
+      <c r="C24" s="19" t="s">
         <v>207</v>
-      </c>
-      <c r="C24" s="19" t="s">
-        <v>210</v>
       </c>
       <c r="D24" s="20">
         <v>992</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F24" s="87" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G24" s="81" t="str">
         <f t="shared" ref="G24:G27" si="1">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F24,"/Readme.md"),"Ver")</f>
@@ -6240,19 +6240,19 @@
     </row>
     <row r="25" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B25" s="16" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="D25" s="20">
         <v>1950</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F25" s="87" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G25" s="81" t="str">
         <f t="shared" si="1"/>
@@ -6263,20 +6263,20 @@
     </row>
     <row r="26" spans="2:9" ht="45.6" x14ac:dyDescent="0.3">
       <c r="B26" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="C26" s="19" t="s">
         <v>209</v>
-      </c>
-      <c r="C26" s="19" t="s">
-        <v>212</v>
       </c>
       <c r="D26" s="15">
         <f>INT(D23/(D24/1000*D25/1000))</f>
         <v>586</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F26" s="87" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G26" s="81" t="str">
         <f t="shared" si="1"/>
@@ -6300,7 +6300,7 @@
     </row>
     <row r="28" spans="2:9" ht="16.8" x14ac:dyDescent="0.4">
       <c r="H28" s="46" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="I28" s="57">
         <f>AVERAGE(I7:I27)</f>
@@ -6341,12 +6341,12 @@
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B3" s="9" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
     </row>
     <row r="4" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B4" s="74" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="C4" s="74"/>
       <c r="D4" s="74"/>
@@ -6392,7 +6392,7 @@
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B7" s="5" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="C7" s="17"/>
       <c r="D7" s="18"/>
@@ -6404,10 +6404,10 @@
     </row>
     <row r="8" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B8" s="16" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="D8" s="20">
         <v>3</v>
@@ -6416,7 +6416,7 @@
         <v>53</v>
       </c>
       <c r="F8" s="87" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G8" s="81" t="str">
         <f t="shared" ref="G8:G21" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F8,"/Readme.md"),"Ver")</f>
@@ -6429,10 +6429,10 @@
     </row>
     <row r="9" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B9" s="16" t="s">
+        <v>229</v>
+      </c>
+      <c r="C9" s="19" t="s">
         <v>232</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>235</v>
       </c>
       <c r="D9" s="20">
         <v>2.5</v>
@@ -6441,7 +6441,7 @@
         <v>53</v>
       </c>
       <c r="F9" s="87" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G9" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6452,19 +6452,19 @@
     </row>
     <row r="10" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B10" s="16" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="D10" s="20">
         <v>4</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="F10" s="87" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G10" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6475,10 +6475,10 @@
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B11" s="16" t="s">
+        <v>230</v>
+      </c>
+      <c r="C11" s="19" t="s">
         <v>233</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>236</v>
       </c>
       <c r="D11" s="20">
         <v>2</v>
@@ -6487,7 +6487,7 @@
         <v>53</v>
       </c>
       <c r="F11" s="87" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G11" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6498,10 +6498,10 @@
     </row>
     <row r="12" spans="2:9" ht="33.6" x14ac:dyDescent="0.4">
       <c r="B12" s="16" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="D12" s="15">
         <f>D10*D11</f>
@@ -6511,7 +6511,7 @@
         <v>53</v>
       </c>
       <c r="F12" s="87" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G12" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6522,10 +6522,10 @@
     </row>
     <row r="13" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B13" s="16" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="D13" s="20">
         <v>8</v>
@@ -6534,7 +6534,7 @@
         <v>53</v>
       </c>
       <c r="F13" s="87" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G13" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6545,20 +6545,20 @@
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B14" s="16" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="D14" s="15" t="str">
         <f>IF(D12&lt;=D13, "Cumple","No cumple")</f>
         <v>Cumple</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="F14" s="87" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G14" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6569,10 +6569,10 @@
     </row>
     <row r="15" spans="2:9" ht="33.6" x14ac:dyDescent="0.4">
       <c r="B15" s="16" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="D15" s="20">
         <v>60</v>
@@ -6581,7 +6581,7 @@
         <v>53</v>
       </c>
       <c r="F15" s="87" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G15" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6592,10 +6592,10 @@
     </row>
     <row r="16" spans="2:9" ht="33.6" x14ac:dyDescent="0.4">
       <c r="B16" s="16" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="D16" s="15">
         <f>D15*D10</f>
@@ -6605,7 +6605,7 @@
         <v>53</v>
       </c>
       <c r="F16" s="87" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G16" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6629,7 +6629,7 @@
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B18" s="5" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="C18" s="17"/>
       <c r="D18" s="18"/>
@@ -6641,19 +6641,19 @@
     </row>
     <row r="19" spans="2:9" ht="45.6" x14ac:dyDescent="0.4">
       <c r="B19" s="16" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="D19" s="20" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F19" s="87" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G19" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6666,19 +6666,19 @@
     </row>
     <row r="20" spans="2:9" ht="45.6" x14ac:dyDescent="0.4">
       <c r="B20" s="16" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="D20" s="20" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F20" s="87" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G20" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6689,19 +6689,19 @@
     </row>
     <row r="21" spans="2:9" ht="45.6" x14ac:dyDescent="0.4">
       <c r="B21" s="16" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="D21" s="20" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="E21" s="15" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F21" s="87" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="G21" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6722,7 +6722,7 @@
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.4">
       <c r="H23" s="46" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="I23" s="57">
         <f>AVERAGE(I7:I22)</f>
@@ -6763,12 +6763,12 @@
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B3" s="9" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B4" s="74" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C4" s="74"/>
       <c r="D4" s="74"/>
@@ -6814,19 +6814,19 @@
     </row>
     <row r="7" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B7" s="16" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="D7" s="20">
         <v>1</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F7" s="87" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G7" s="81" t="str">
         <f t="shared" ref="G7:G16" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F7,"/Readme.md"),"Ver")</f>
@@ -6839,19 +6839,19 @@
     </row>
     <row r="8" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B8" s="16" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="D8" s="20">
         <v>1</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F8" s="87" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G8" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6862,19 +6862,19 @@
     </row>
     <row r="9" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B9" s="16" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="D9" s="20">
         <v>1</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F9" s="87" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G9" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6885,19 +6885,19 @@
     </row>
     <row r="10" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B10" s="16" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="D10" s="20">
         <v>1</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F10" s="87" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G10" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6908,19 +6908,19 @@
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B11" s="16" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="D11" s="20">
         <v>1</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F11" s="87" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G11" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6931,19 +6931,19 @@
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B12" s="16" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="D12" s="20">
         <v>1</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F12" s="87" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G12" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6954,19 +6954,19 @@
     </row>
     <row r="13" spans="2:9" ht="33.6" x14ac:dyDescent="0.4">
       <c r="B13" s="16" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D13" s="20">
         <v>1</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F13" s="87" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G13" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6977,19 +6977,19 @@
     </row>
     <row r="14" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B14" s="16" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="D14" s="20">
         <v>1</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F14" s="87" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G14" s="81" t="str">
         <f t="shared" si="0"/>
@@ -7000,19 +7000,19 @@
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B15" s="16" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D15" s="20">
         <v>1</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F15" s="87" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="G15" s="81" t="str">
         <f t="shared" si="0"/>
@@ -7036,7 +7036,7 @@
     </row>
     <row r="17" spans="8:9" x14ac:dyDescent="0.4">
       <c r="H17" s="46" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="I17" s="57">
         <f>AVERAGE(I7:I16)</f>
@@ -7083,7 +7083,7 @@
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B3" s="80" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="C3" s="80"/>
       <c r="D3" s="80"/>
@@ -7094,7 +7094,7 @@
     </row>
     <row r="4" spans="2:8" s="36" customFormat="1" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="74" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="C4" s="74"/>
       <c r="D4" s="74"/>
@@ -7135,16 +7135,16 @@
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B7" s="16" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>34</v>
       </c>
       <c r="E7" s="131" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="F7" s="81" t="str">
         <f t="shared" ref="F7:F16" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",E7,"/Readme.md"),"Ver")</f>
@@ -7160,13 +7160,13 @@
         <v>19</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>30</v>
       </c>
       <c r="E8" s="131" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="F8" s="81" t="str">
         <f t="shared" si="0"/>
@@ -7177,16 +7177,16 @@
     </row>
     <row r="9" spans="2:8" ht="91.2" x14ac:dyDescent="0.3">
       <c r="B9" s="16" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E9" s="131" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="F9" s="81" t="str">
         <f t="shared" si="0"/>
@@ -7197,16 +7197,16 @@
     </row>
     <row r="10" spans="2:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B10" s="16" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>31</v>
       </c>
       <c r="E10" s="131" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="F10" s="81" t="str">
         <f t="shared" si="0"/>
@@ -7217,16 +7217,16 @@
     </row>
     <row r="11" spans="2:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="B11" s="16" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>32</v>
       </c>
       <c r="E11" s="131" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="F11" s="81" t="str">
         <f t="shared" si="0"/>
@@ -7237,16 +7237,16 @@
     </row>
     <row r="12" spans="2:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B12" s="16" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>33</v>
       </c>
       <c r="E12" s="131" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="F12" s="81" t="str">
         <f t="shared" si="0"/>
@@ -7257,16 +7257,16 @@
     </row>
     <row r="13" spans="2:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B13" s="16" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="E13" s="131" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="F13" s="81" t="str">
         <f t="shared" si="0"/>
@@ -7277,16 +7277,16 @@
     </row>
     <row r="14" spans="2:8" ht="79.8" x14ac:dyDescent="0.3">
       <c r="B14" s="16" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="E14" s="131" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="F14" s="81" t="str">
         <f t="shared" si="0"/>
@@ -7297,13 +7297,13 @@
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B15" s="16" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="E15" s="55"/>
       <c r="F15" s="81" t="str">
@@ -7327,7 +7327,7 @@
     </row>
     <row r="17" spans="7:8" x14ac:dyDescent="0.3">
       <c r="G17" s="46" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="H17" s="31">
         <f>AVERAGE(H7:H16)</f>

--- a/file/table/DAPC_ProyectoCAD.xlsx
+++ b/file/table/DAPC_ProyectoCAD.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{483FD17B-125F-4378-8242-F4E84B0139B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51DE0064-4996-4CB4-BD57-84D74EA0F7EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/file/table/DAPC_ProyectoCAD.xlsx
+++ b/file/table/DAPC_ProyectoCAD.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51DE0064-4996-4CB4-BD57-84D74EA0F7EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{889924E1-C1A6-4802-9114-4E00DC671DF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0.Inicio" sheetId="7" r:id="rId1"/>
@@ -28,6 +28,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'1.Tecnica'!$B$6:$I$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'2.ArquitectonicaEstructural'!$B$6:$I$100</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'3.Electrica'!$B$6:$I$27</definedName>
     <definedName name="SumUDig" localSheetId="4">'[1]1.Técnicas'!$E$32</definedName>
     <definedName name="SumUDig">'0.Inicio'!$E$29</definedName>
   </definedNames>
@@ -311,7 +312,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="347">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="346">
   <si>
     <t>1. Especificaciones técnicas generales</t>
   </si>
@@ -1015,9 +1016,6 @@
     <t>Área disponible en cubierta / área por pánel. Calcular como valor entero debido a que los páneles son unidades selladas. El número de páneles debe ser verificado dibujando su localización y verificando que queden embebidos dentro de las áreas remanentes de la cubierta.</t>
   </si>
   <si>
-    <t>Para rayos</t>
-  </si>
-  <si>
     <t>Polo a tierra</t>
   </si>
   <si>
@@ -1458,9 +1456,6 @@
     <t>M01A02b</t>
   </si>
   <si>
-    <t>M01A02c</t>
-  </si>
-  <si>
     <t>Planos digitales del proyecto</t>
   </si>
   <si>
@@ -1514,6 +1509,9 @@
   </si>
   <si>
     <t>Líneas y pasarelas a lo largo de toda la cubierta cubriendo todo el ancho y en forma de cruz. No incluir en voladizo de cubierta.</t>
+  </si>
+  <si>
+    <t>Pararrayos</t>
   </si>
 </sst>
 </file>
@@ -2990,7 +2988,7 @@
   <sheetData>
     <row r="1" spans="2:5" x14ac:dyDescent="0.3">
       <c r="E1" s="100" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
     </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.3">
@@ -3000,7 +2998,7 @@
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B3" s="101" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.3">
@@ -3270,7 +3268,7 @@
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B31" s="73" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="C31" s="73"/>
       <c r="D31" s="73"/>
@@ -3293,7 +3291,7 @@
         <v>1</v>
       </c>
       <c r="C33" s="77" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D33" s="78"/>
       <c r="E33" s="51">
@@ -3306,7 +3304,7 @@
         <v>2</v>
       </c>
       <c r="C34" s="62" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D34" s="63"/>
       <c r="E34" s="51">
@@ -3319,7 +3317,7 @@
         <v>3</v>
       </c>
       <c r="C35" s="62" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D35" s="63"/>
       <c r="E35" s="51">
@@ -3332,7 +3330,7 @@
         <v>4</v>
       </c>
       <c r="C36" s="60" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D36" s="61"/>
       <c r="E36" s="51">
@@ -3345,7 +3343,7 @@
         <v>4</v>
       </c>
       <c r="C37" s="62" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D37" s="63"/>
       <c r="E37" s="51">
@@ -3358,7 +3356,7 @@
         <v>5</v>
       </c>
       <c r="C38" s="62" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="D38" s="63"/>
       <c r="E38" s="51">
@@ -3371,7 +3369,7 @@
         <v>6</v>
       </c>
       <c r="C39" s="62" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D39" s="63"/>
       <c r="E39" s="99">
@@ -3383,7 +3381,7 @@
         <v>7</v>
       </c>
       <c r="C40" s="64" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="D40" s="65"/>
       <c r="E40" s="58">
@@ -3392,7 +3390,7 @@
     </row>
     <row r="41" spans="2:5" x14ac:dyDescent="0.3">
       <c r="D41" s="118" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E41" s="59">
         <f>AVERAGE(E33:E40)</f>
@@ -3460,7 +3458,7 @@
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B4" s="102" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C4" s="102"/>
       <c r="D4" s="102"/>
@@ -3498,10 +3496,10 @@
     </row>
     <row r="7" spans="2:9" ht="57" x14ac:dyDescent="0.3">
       <c r="B7" s="127" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="C7" s="128" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D7" s="91">
         <v>1</v>
@@ -3510,7 +3508,7 @@
         <v>16</v>
       </c>
       <c r="F7" s="131" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G7" s="132" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F7,"/Readme.md"),"Ver")</f>
@@ -3523,19 +3521,19 @@
     </row>
     <row r="8" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B8" s="127" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C8" s="128" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="D8" s="91">
         <v>1</v>
       </c>
       <c r="E8" s="130" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F8" s="131" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G8" s="132" t="str">
         <f t="shared" ref="G8:G18" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F8,"/Readme.md"),"Ver")</f>
@@ -3546,17 +3544,17 @@
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B9" s="127" t="s">
+        <v>272</v>
+      </c>
+      <c r="C9" s="128" t="s">
         <v>273</v>
       </c>
-      <c r="C9" s="128" t="s">
-        <v>274</v>
-      </c>
       <c r="D9" s="91" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E9" s="130"/>
       <c r="F9" s="131" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G9" s="132" t="str">
         <f t="shared" si="0"/>
@@ -3567,10 +3565,10 @@
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B10" s="127" t="s">
+        <v>276</v>
+      </c>
+      <c r="C10" s="128" t="s">
         <v>277</v>
-      </c>
-      <c r="C10" s="128" t="s">
-        <v>278</v>
       </c>
       <c r="D10" s="91">
         <v>1</v>
@@ -3579,7 +3577,7 @@
         <v>16</v>
       </c>
       <c r="F10" s="131" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G10" s="132" t="str">
         <f t="shared" si="0"/>
@@ -3590,17 +3588,17 @@
     </row>
     <row r="11" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
       <c r="B11" s="127" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C11" s="128" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D11" s="91" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E11" s="130"/>
       <c r="F11" s="131" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G11" s="132" t="str">
         <f t="shared" si="0"/>
@@ -3611,17 +3609,17 @@
     </row>
     <row r="12" spans="2:9" ht="57" x14ac:dyDescent="0.3">
       <c r="B12" s="127" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C12" s="128" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D12" s="91" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E12" s="130"/>
       <c r="F12" s="131" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="G12" s="132" t="str">
         <f t="shared" si="0"/>
@@ -3632,17 +3630,17 @@
     </row>
     <row r="13" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B13" s="127" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C13" s="128" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D13" s="91" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E13" s="130"/>
       <c r="F13" s="131" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G13" s="132" t="str">
         <f t="shared" si="0"/>
@@ -3653,17 +3651,17 @@
     </row>
     <row r="14" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
       <c r="B14" s="127" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C14" s="128" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D14" s="91" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="E14" s="130"/>
       <c r="F14" s="131" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G14" s="132" t="str">
         <f t="shared" si="0"/>
@@ -3674,10 +3672,10 @@
     </row>
     <row r="15" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="B15" s="127" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C15" s="128" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D15" s="91">
         <v>1</v>
@@ -3686,7 +3684,7 @@
         <v>16</v>
       </c>
       <c r="F15" s="131" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G15" s="132" t="str">
         <f t="shared" si="0"/>
@@ -3697,10 +3695,10 @@
     </row>
     <row r="16" spans="2:9" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="127" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C16" s="128" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D16" s="91">
         <v>1</v>
@@ -3709,7 +3707,7 @@
         <v>16</v>
       </c>
       <c r="F16" s="131" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G16" s="132" t="str">
         <f t="shared" si="0"/>
@@ -3720,10 +3718,10 @@
     </row>
     <row r="17" spans="2:9" ht="35.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="134" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C17" s="135" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D17" s="91">
         <v>1</v>
@@ -3732,7 +3730,7 @@
         <v>16</v>
       </c>
       <c r="F17" s="131" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G17" s="132" t="str">
         <f t="shared" si="0"/>
@@ -3756,7 +3754,7 @@
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.3">
       <c r="H19" s="141" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I19" s="120">
         <f>AVERAGE(I7:I18)</f>
@@ -3806,7 +3804,7 @@
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B4" s="102" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C4" s="102"/>
       <c r="D4" s="102"/>
@@ -3852,7 +3850,7 @@
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B7" s="146" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C7" s="147"/>
       <c r="D7" s="148"/>
@@ -3876,14 +3874,14 @@
         <v>53</v>
       </c>
       <c r="F8" s="131" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G8" s="132" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F8,"/Readme.md"),"Ver")</f>
         <v>Ver</v>
       </c>
       <c r="H8" s="128" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="I8" s="133">
         <v>5</v>
@@ -3903,14 +3901,14 @@
         <v>53</v>
       </c>
       <c r="F9" s="131" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G9" s="132" t="str">
         <f t="shared" ref="G9:G72" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F9,"/Readme.md"),"Ver")</f>
         <v>Ver</v>
       </c>
       <c r="H9" s="128" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="I9" s="133"/>
     </row>
@@ -3929,7 +3927,7 @@
         <v>53</v>
       </c>
       <c r="F10" s="131" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G10" s="132" t="str">
         <f t="shared" si="0"/>
@@ -3953,7 +3951,7 @@
         <v>53</v>
       </c>
       <c r="F11" s="131" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G11" s="132" t="str">
         <f t="shared" si="0"/>
@@ -3976,14 +3974,14 @@
         <v>53</v>
       </c>
       <c r="F12" s="131" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G12" s="132" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H12" s="128" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="I12" s="133"/>
     </row>
@@ -4001,14 +3999,14 @@
         <v>53</v>
       </c>
       <c r="F13" s="131" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G13" s="132" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H13" s="128" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="I13" s="133"/>
     </row>
@@ -4026,14 +4024,14 @@
         <v>53</v>
       </c>
       <c r="F14" s="131" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G14" s="132" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H14" s="128" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="I14" s="133"/>
     </row>
@@ -4052,7 +4050,7 @@
         <v>53</v>
       </c>
       <c r="F15" s="131" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G15" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4076,7 +4074,7 @@
         <v>53</v>
       </c>
       <c r="F16" s="131" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G16" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4100,7 +4098,7 @@
         <v>54</v>
       </c>
       <c r="F17" s="131" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G17" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4124,7 +4122,7 @@
         <v>54</v>
       </c>
       <c r="F18" s="131" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G18" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4148,7 +4146,7 @@
         <v>54</v>
       </c>
       <c r="F19" s="131" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G19" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4172,7 +4170,7 @@
         <v>67</v>
       </c>
       <c r="F20" s="131" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G20" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4196,7 +4194,7 @@
         <v>67</v>
       </c>
       <c r="F21" s="131" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G21" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4220,7 +4218,7 @@
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B23" s="146" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C23" s="147"/>
       <c r="D23" s="148"/>
@@ -4244,14 +4242,14 @@
         <v>53</v>
       </c>
       <c r="F24" s="131" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G24" s="132" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H24" s="128" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="I24" s="133">
         <v>5</v>
@@ -4271,7 +4269,7 @@
         <v>68</v>
       </c>
       <c r="F25" s="131" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G25" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4295,7 +4293,7 @@
         <v>69</v>
       </c>
       <c r="F26" s="131" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G26" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4309,7 +4307,7 @@
         <v>75</v>
       </c>
       <c r="C27" s="135" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="D27" s="155">
         <v>0.6</v>
@@ -4318,7 +4316,7 @@
         <v>53</v>
       </c>
       <c r="F27" s="131" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G27" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4341,7 +4339,7 @@
         <v>53</v>
       </c>
       <c r="F28" s="131" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G28" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4364,7 +4362,7 @@
         <v>67</v>
       </c>
       <c r="F29" s="131" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G29" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4388,7 +4386,7 @@
         <v>54</v>
       </c>
       <c r="F30" s="131" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G30" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4412,7 +4410,7 @@
         <v>54</v>
       </c>
       <c r="F31" s="131" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G31" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4436,7 +4434,7 @@
         <v>54</v>
       </c>
       <c r="F32" s="131" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G32" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4459,7 +4457,7 @@
         <v>53</v>
       </c>
       <c r="F33" s="131" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G33" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4483,7 +4481,7 @@
         <v>115</v>
       </c>
       <c r="F34" s="131" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G34" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4506,7 +4504,7 @@
         <v>63</v>
       </c>
       <c r="F35" s="131" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G35" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4520,7 +4518,7 @@
         <v>80</v>
       </c>
       <c r="C36" s="128" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="D36" s="130">
         <f>D35*D35/(1000*1000)</f>
@@ -4530,7 +4528,7 @@
         <v>54</v>
       </c>
       <c r="F36" s="131" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G36" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4554,7 +4552,7 @@
         <v>54</v>
       </c>
       <c r="F37" s="131" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G37" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4578,7 +4576,7 @@
     </row>
     <row r="39" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B39" s="156" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C39" s="147"/>
       <c r="D39" s="148"/>
@@ -4590,7 +4588,7 @@
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B40" s="127" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C40" s="128" t="s">
         <v>86</v>
@@ -4602,7 +4600,7 @@
         <v>53</v>
       </c>
       <c r="F40" s="131" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G40" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4627,7 +4625,7 @@
         <v>53</v>
       </c>
       <c r="F41" s="131" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G41" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4641,7 +4639,7 @@
         <v>84</v>
       </c>
       <c r="C42" s="128" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="D42" s="130">
         <f>D11+(INT(D11/D41)*D10)</f>
@@ -4651,7 +4649,7 @@
         <v>53</v>
       </c>
       <c r="F42" s="131" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G42" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4675,7 +4673,7 @@
         <v>54</v>
       </c>
       <c r="F43" s="131" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G43" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4699,7 +4697,7 @@
     </row>
     <row r="45" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B45" s="146" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="C45" s="147"/>
       <c r="D45" s="148"/>
@@ -4714,7 +4712,7 @@
         <v>41</v>
       </c>
       <c r="C46" s="128" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D46" s="129">
         <v>60</v>
@@ -4723,7 +4721,7 @@
         <v>54</v>
       </c>
       <c r="F46" s="131" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G46" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4748,7 +4746,7 @@
         <v>54</v>
       </c>
       <c r="F47" s="131" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G47" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4771,7 +4769,7 @@
         <v>53</v>
       </c>
       <c r="F48" s="131" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G48" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4795,7 +4793,7 @@
         <v>54</v>
       </c>
       <c r="F49" s="131" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G49" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4818,7 +4816,7 @@
         <v>55</v>
       </c>
       <c r="F50" s="131" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G50" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4841,7 +4839,7 @@
         <v>55</v>
       </c>
       <c r="F51" s="131" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G51" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4865,7 +4863,7 @@
         <v>49</v>
       </c>
       <c r="F52" s="131" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G52" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4888,7 +4886,7 @@
         <v>53</v>
       </c>
       <c r="F53" s="131" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G53" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4912,7 +4910,7 @@
         <v>54</v>
       </c>
       <c r="F54" s="131" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G54" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4935,7 +4933,7 @@
         <v>53</v>
       </c>
       <c r="F55" s="131" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G55" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4958,7 +4956,7 @@
         <v>53</v>
       </c>
       <c r="F56" s="131" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G56" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4981,7 +4979,7 @@
         <v>53</v>
       </c>
       <c r="F57" s="131" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G57" s="132" t="str">
         <f t="shared" si="0"/>
@@ -5004,7 +5002,7 @@
         <v>53</v>
       </c>
       <c r="F58" s="131" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G58" s="132" t="str">
         <f t="shared" si="0"/>
@@ -5027,7 +5025,7 @@
         <v>53</v>
       </c>
       <c r="F59" s="131" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G59" s="132" t="str">
         <f t="shared" si="0"/>
@@ -5050,7 +5048,7 @@
         <v>53</v>
       </c>
       <c r="F60" s="131" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="G60" s="132" t="str">
         <f t="shared" si="0"/>
@@ -5074,7 +5072,7 @@
     </row>
     <row r="62" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B62" s="158" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C62" s="159"/>
       <c r="D62" s="160"/>
@@ -5098,7 +5096,7 @@
         <v>55</v>
       </c>
       <c r="F63" s="131" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G63" s="132" t="str">
         <f t="shared" si="0"/>
@@ -5124,7 +5122,7 @@
         <v>54</v>
       </c>
       <c r="F64" s="131" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G64" s="132" t="str">
         <f t="shared" si="0"/>
@@ -5147,7 +5145,7 @@
         <v>55</v>
       </c>
       <c r="F65" s="131" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G65" s="132" t="str">
         <f t="shared" si="0"/>
@@ -5170,7 +5168,7 @@
         <v>53</v>
       </c>
       <c r="F66" s="131" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G66" s="132" t="str">
         <f t="shared" si="0"/>
@@ -5194,7 +5192,7 @@
         <v>115</v>
       </c>
       <c r="F67" s="131" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G67" s="132" t="str">
         <f t="shared" si="0"/>
@@ -5218,7 +5216,7 @@
         <v>115</v>
       </c>
       <c r="F68" s="131" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G68" s="132" t="str">
         <f t="shared" si="0"/>
@@ -5242,7 +5240,7 @@
         <v>115</v>
       </c>
       <c r="F69" s="131" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G69" s="132" t="str">
         <f t="shared" si="0"/>
@@ -5256,7 +5254,7 @@
         <v>105</v>
       </c>
       <c r="C70" s="128" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="D70" s="129">
         <v>0.25</v>
@@ -5265,7 +5263,7 @@
         <v>53</v>
       </c>
       <c r="F70" s="131" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G70" s="132" t="str">
         <f t="shared" si="0"/>
@@ -5288,7 +5286,7 @@
         <v>53</v>
       </c>
       <c r="F71" s="131" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G71" s="132" t="str">
         <f t="shared" si="0"/>
@@ -5311,7 +5309,7 @@
         <v>53</v>
       </c>
       <c r="F72" s="131" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G72" s="132" t="str">
         <f t="shared" si="0"/>
@@ -5334,7 +5332,7 @@
         <v>53</v>
       </c>
       <c r="F73" s="131" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G73" s="132" t="str">
         <f t="shared" ref="G73:G76" si="1">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F73,"/Readme.md"),"Ver")</f>
@@ -5358,7 +5356,7 @@
         <v>53</v>
       </c>
       <c r="F74" s="131" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G74" s="132" t="str">
         <f t="shared" si="1"/>
@@ -5382,7 +5380,7 @@
         <v>53</v>
       </c>
       <c r="F75" s="131" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G75" s="132" t="str">
         <f t="shared" si="1"/>
@@ -5406,7 +5404,7 @@
     </row>
     <row r="77" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B77" s="182" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C77" s="159"/>
       <c r="D77" s="160"/>
@@ -5431,7 +5429,7 @@
         <v>54</v>
       </c>
       <c r="F78" s="131" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G78" s="132" t="str">
         <f t="shared" ref="G78:G88" si="2">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F78,"/Readme.md"),"Ver")</f>
@@ -5455,7 +5453,7 @@
         <v>172</v>
       </c>
       <c r="F79" s="131" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G79" s="132" t="str">
         <f t="shared" si="2"/>
@@ -5479,7 +5477,7 @@
         <v>54</v>
       </c>
       <c r="F80" s="131" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G80" s="132" t="str">
         <f t="shared" si="2"/>
@@ -5503,7 +5501,7 @@
         <v>115</v>
       </c>
       <c r="F81" s="131" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G81" s="132" t="str">
         <f t="shared" si="2"/>
@@ -5527,7 +5525,7 @@
         <v>53</v>
       </c>
       <c r="F82" s="131" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G82" s="132" t="str">
         <f t="shared" si="2"/>
@@ -5551,7 +5549,7 @@
         <v>53</v>
       </c>
       <c r="F83" s="131" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G83" s="132" t="str">
         <f t="shared" si="2"/>
@@ -5574,7 +5572,7 @@
         <v>54</v>
       </c>
       <c r="F84" s="131" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G84" s="132" t="str">
         <f t="shared" si="2"/>
@@ -5599,7 +5597,7 @@
         <v>115</v>
       </c>
       <c r="F85" s="131" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G85" s="132" t="str">
         <f t="shared" si="2"/>
@@ -5622,7 +5620,7 @@
         <v>115</v>
       </c>
       <c r="F86" s="131" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G86" s="132" t="str">
         <f t="shared" si="2"/>
@@ -5645,7 +5643,7 @@
         <v>115</v>
       </c>
       <c r="F87" s="131" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G87" s="132" t="str">
         <f t="shared" si="2"/>
@@ -5674,7 +5672,7 @@
     </row>
     <row r="90" spans="2:9" x14ac:dyDescent="0.3">
       <c r="H90" s="141" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I90" s="120">
         <f>AVERAGE(I7:I88)</f>
@@ -5683,7 +5681,7 @@
     </row>
     <row r="91" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B91" s="47" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
     </row>
     <row r="92" spans="2:9" x14ac:dyDescent="0.3">
@@ -5807,7 +5805,7 @@
     </row>
     <row r="4" spans="2:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="74" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C4" s="74"/>
       <c r="D4" s="74"/>
@@ -5853,7 +5851,7 @@
     </row>
     <row r="7" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B7" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C7" s="17"/>
       <c r="D7" s="18"/>
@@ -5865,10 +5863,10 @@
     </row>
     <row r="8" spans="2:9" ht="57" x14ac:dyDescent="0.3">
       <c r="B8" s="16" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D8" s="15">
         <v>1</v>
@@ -5877,7 +5875,7 @@
         <v>115</v>
       </c>
       <c r="F8" s="87" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G8" s="81" t="str">
         <f t="shared" ref="G8:G21" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F8,"/Readme.md"),"Ver")</f>
@@ -5890,10 +5888,10 @@
     </row>
     <row r="9" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B9" s="16" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D9" s="15">
         <v>1</v>
@@ -5902,7 +5900,7 @@
         <v>115</v>
       </c>
       <c r="F9" s="87" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="G9" s="81" t="str">
         <f t="shared" si="0"/>
@@ -5913,10 +5911,10 @@
     </row>
     <row r="10" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B10" s="16" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D10" s="15">
         <v>1</v>
@@ -5925,7 +5923,7 @@
         <v>115</v>
       </c>
       <c r="F10" s="87" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="G10" s="81" t="str">
         <f t="shared" si="0"/>
@@ -5936,10 +5934,10 @@
     </row>
     <row r="11" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B11" s="16" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D11" s="15">
         <v>1</v>
@@ -5948,7 +5946,7 @@
         <v>115</v>
       </c>
       <c r="F11" s="87" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="G11" s="81" t="str">
         <f t="shared" si="0"/>
@@ -5962,7 +5960,7 @@
         <v>201</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D12" s="15">
         <v>1</v>
@@ -5971,7 +5969,7 @@
         <v>115</v>
       </c>
       <c r="F12" s="87" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="G12" s="81" t="str">
         <f t="shared" si="0"/>
@@ -5982,10 +5980,10 @@
     </row>
     <row r="13" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B13" s="27" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D13" s="15">
         <v>1</v>
@@ -5994,7 +5992,7 @@
         <v>115</v>
       </c>
       <c r="F13" s="87" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="G13" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6017,7 +6015,7 @@
         <v>115</v>
       </c>
       <c r="F14" s="87" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G14" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6040,7 +6038,7 @@
         <v>115</v>
       </c>
       <c r="F15" s="87" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G15" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6063,7 +6061,7 @@
         <v>115</v>
       </c>
       <c r="F16" s="87" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G16" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6074,7 +6072,7 @@
     </row>
     <row r="17" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B17" s="27" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C17" s="19" t="s">
         <v>200</v>
@@ -6086,7 +6084,7 @@
         <v>115</v>
       </c>
       <c r="F17" s="87" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G17" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6109,7 +6107,7 @@
         <v>115</v>
       </c>
       <c r="F18" s="87" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="G18" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6120,7 +6118,7 @@
     </row>
     <row r="19" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B19" s="27" t="s">
-        <v>210</v>
+        <v>345</v>
       </c>
       <c r="C19" s="19" t="s">
         <v>200</v>
@@ -6132,7 +6130,7 @@
         <v>115</v>
       </c>
       <c r="F19" s="87" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G19" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6143,7 +6141,7 @@
     </row>
     <row r="20" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B20" s="27" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C20" s="19" t="s">
         <v>200</v>
@@ -6155,7 +6153,7 @@
         <v>115</v>
       </c>
       <c r="F20" s="87" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G20" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6179,7 +6177,7 @@
     </row>
     <row r="22" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B22" s="5" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C22" s="17"/>
       <c r="D22" s="18"/>
@@ -6204,7 +6202,7 @@
         <v>54</v>
       </c>
       <c r="F23" s="87" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G23" s="81" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F23,"/Readme.md"),"Ver")</f>
@@ -6229,7 +6227,7 @@
         <v>63</v>
       </c>
       <c r="F24" s="87" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G24" s="81" t="str">
         <f t="shared" ref="G24:G27" si="1">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F24,"/Readme.md"),"Ver")</f>
@@ -6252,7 +6250,7 @@
         <v>63</v>
       </c>
       <c r="F25" s="87" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G25" s="81" t="str">
         <f t="shared" si="1"/>
@@ -6276,7 +6274,7 @@
         <v>115</v>
       </c>
       <c r="F26" s="87" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G26" s="81" t="str">
         <f t="shared" si="1"/>
@@ -6300,7 +6298,7 @@
     </row>
     <row r="28" spans="2:9" ht="16.8" x14ac:dyDescent="0.4">
       <c r="H28" s="46" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I28" s="57">
         <f>AVERAGE(I7:I27)</f>
@@ -6308,6 +6306,9 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="B6:I27" xr:uid="{CDC0663E-105D-42EA-893B-DB8B7FE41FC2}">
+    <filterColumn colId="4" showButton="0"/>
+  </autoFilter>
   <mergeCells count="2">
     <mergeCell ref="B4:I5"/>
     <mergeCell ref="F6:G6"/>
@@ -6341,12 +6342,12 @@
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B3" s="9" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="4" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B4" s="74" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C4" s="74"/>
       <c r="D4" s="74"/>
@@ -6392,7 +6393,7 @@
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B7" s="5" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C7" s="17"/>
       <c r="D7" s="18"/>
@@ -6404,10 +6405,10 @@
     </row>
     <row r="8" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B8" s="16" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D8" s="20">
         <v>3</v>
@@ -6416,7 +6417,7 @@
         <v>53</v>
       </c>
       <c r="F8" s="87" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G8" s="81" t="str">
         <f t="shared" ref="G8:G21" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F8,"/Readme.md"),"Ver")</f>
@@ -6429,10 +6430,10 @@
     </row>
     <row r="9" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B9" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D9" s="20">
         <v>2.5</v>
@@ -6441,7 +6442,7 @@
         <v>53</v>
       </c>
       <c r="F9" s="87" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G9" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6452,19 +6453,19 @@
     </row>
     <row r="10" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B10" s="16" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D10" s="20">
         <v>4</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="F10" s="87" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G10" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6475,10 +6476,10 @@
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B11" s="16" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D11" s="20">
         <v>2</v>
@@ -6487,7 +6488,7 @@
         <v>53</v>
       </c>
       <c r="F11" s="87" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G11" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6498,10 +6499,10 @@
     </row>
     <row r="12" spans="2:9" ht="33.6" x14ac:dyDescent="0.4">
       <c r="B12" s="16" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D12" s="15">
         <f>D10*D11</f>
@@ -6511,7 +6512,7 @@
         <v>53</v>
       </c>
       <c r="F12" s="87" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G12" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6522,10 +6523,10 @@
     </row>
     <row r="13" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B13" s="16" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D13" s="20">
         <v>8</v>
@@ -6534,7 +6535,7 @@
         <v>53</v>
       </c>
       <c r="F13" s="87" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G13" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6545,20 +6546,20 @@
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B14" s="16" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="D14" s="15" t="str">
         <f>IF(D12&lt;=D13, "Cumple","No cumple")</f>
         <v>Cumple</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="F14" s="87" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G14" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6569,10 +6570,10 @@
     </row>
     <row r="15" spans="2:9" ht="33.6" x14ac:dyDescent="0.4">
       <c r="B15" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="C15" s="19" t="s">
         <v>243</v>
-      </c>
-      <c r="C15" s="19" t="s">
-        <v>244</v>
       </c>
       <c r="D15" s="20">
         <v>60</v>
@@ -6581,7 +6582,7 @@
         <v>53</v>
       </c>
       <c r="F15" s="87" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G15" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6592,10 +6593,10 @@
     </row>
     <row r="16" spans="2:9" ht="33.6" x14ac:dyDescent="0.4">
       <c r="B16" s="16" t="s">
+        <v>244</v>
+      </c>
+      <c r="C16" s="19" t="s">
         <v>245</v>
-      </c>
-      <c r="C16" s="19" t="s">
-        <v>246</v>
       </c>
       <c r="D16" s="15">
         <f>D15*D10</f>
@@ -6605,7 +6606,7 @@
         <v>53</v>
       </c>
       <c r="F16" s="87" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G16" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6629,7 +6630,7 @@
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B18" s="5" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C18" s="17"/>
       <c r="D18" s="18"/>
@@ -6641,19 +6642,19 @@
     </row>
     <row r="19" spans="2:9" ht="45.6" x14ac:dyDescent="0.4">
       <c r="B19" s="16" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C19" s="19" t="s">
+        <v>235</v>
+      </c>
+      <c r="D19" s="20" t="s">
         <v>236</v>
-      </c>
-      <c r="D19" s="20" t="s">
-        <v>237</v>
       </c>
       <c r="E19" s="15" t="s">
         <v>115</v>
       </c>
       <c r="F19" s="87" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G19" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6666,19 +6667,19 @@
     </row>
     <row r="20" spans="2:9" ht="45.6" x14ac:dyDescent="0.4">
       <c r="B20" s="16" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C20" s="19" t="s">
+        <v>235</v>
+      </c>
+      <c r="D20" s="20" t="s">
         <v>236</v>
-      </c>
-      <c r="D20" s="20" t="s">
-        <v>237</v>
       </c>
       <c r="E20" s="15" t="s">
         <v>115</v>
       </c>
       <c r="F20" s="87" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G20" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6689,19 +6690,19 @@
     </row>
     <row r="21" spans="2:9" ht="45.6" x14ac:dyDescent="0.4">
       <c r="B21" s="16" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C21" s="19" t="s">
+        <v>235</v>
+      </c>
+      <c r="D21" s="20" t="s">
         <v>236</v>
-      </c>
-      <c r="D21" s="20" t="s">
-        <v>237</v>
       </c>
       <c r="E21" s="15" t="s">
         <v>115</v>
       </c>
       <c r="F21" s="87" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G21" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6722,7 +6723,7 @@
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.4">
       <c r="H23" s="46" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I23" s="57">
         <f>AVERAGE(I7:I22)</f>
@@ -6763,12 +6764,12 @@
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B3" s="9" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B4" s="74" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C4" s="74"/>
       <c r="D4" s="74"/>
@@ -6814,10 +6815,10 @@
     </row>
     <row r="7" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B7" s="16" t="s">
+        <v>249</v>
+      </c>
+      <c r="C7" s="19" t="s">
         <v>250</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>251</v>
       </c>
       <c r="D7" s="20">
         <v>1</v>
@@ -6826,7 +6827,7 @@
         <v>115</v>
       </c>
       <c r="F7" s="87" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G7" s="81" t="str">
         <f t="shared" ref="G7:G16" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F7,"/Readme.md"),"Ver")</f>
@@ -6839,10 +6840,10 @@
     </row>
     <row r="8" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B8" s="16" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D8" s="20">
         <v>1</v>
@@ -6851,7 +6852,7 @@
         <v>115</v>
       </c>
       <c r="F8" s="87" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G8" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6862,10 +6863,10 @@
     </row>
     <row r="9" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B9" s="16" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D9" s="20">
         <v>1</v>
@@ -6874,7 +6875,7 @@
         <v>115</v>
       </c>
       <c r="F9" s="87" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G9" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6885,10 +6886,10 @@
     </row>
     <row r="10" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B10" s="16" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="D10" s="20">
         <v>1</v>
@@ -6897,7 +6898,7 @@
         <v>115</v>
       </c>
       <c r="F10" s="87" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G10" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6908,10 +6909,10 @@
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B11" s="16" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D11" s="20">
         <v>1</v>
@@ -6920,7 +6921,7 @@
         <v>115</v>
       </c>
       <c r="F11" s="87" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G11" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6931,10 +6932,10 @@
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B12" s="16" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D12" s="20">
         <v>1</v>
@@ -6943,7 +6944,7 @@
         <v>115</v>
       </c>
       <c r="F12" s="87" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G12" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6954,10 +6955,10 @@
     </row>
     <row r="13" spans="2:9" ht="33.6" x14ac:dyDescent="0.4">
       <c r="B13" s="16" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D13" s="20">
         <v>1</v>
@@ -6966,7 +6967,7 @@
         <v>115</v>
       </c>
       <c r="F13" s="87" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G13" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6977,10 +6978,10 @@
     </row>
     <row r="14" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B14" s="16" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D14" s="20">
         <v>1</v>
@@ -6989,7 +6990,7 @@
         <v>115</v>
       </c>
       <c r="F14" s="87" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G14" s="81" t="str">
         <f t="shared" si="0"/>
@@ -7000,10 +7001,10 @@
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B15" s="16" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D15" s="20">
         <v>1</v>
@@ -7012,7 +7013,7 @@
         <v>115</v>
       </c>
       <c r="F15" s="87" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G15" s="81" t="str">
         <f t="shared" si="0"/>
@@ -7036,7 +7037,7 @@
     </row>
     <row r="17" spans="8:9" x14ac:dyDescent="0.4">
       <c r="H17" s="46" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I17" s="57">
         <f>AVERAGE(I7:I16)</f>
@@ -7083,7 +7084,7 @@
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B3" s="80" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C3" s="80"/>
       <c r="D3" s="80"/>
@@ -7094,7 +7095,7 @@
     </row>
     <row r="4" spans="2:8" s="36" customFormat="1" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="74" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C4" s="74"/>
       <c r="D4" s="74"/>
@@ -7135,16 +7136,16 @@
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B7" s="16" t="s">
+        <v>272</v>
+      </c>
+      <c r="C7" s="19" t="s">
         <v>273</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>274</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>34</v>
       </c>
       <c r="E7" s="131" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F7" s="81" t="str">
         <f t="shared" ref="F7:F16" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",E7,"/Readme.md"),"Ver")</f>
@@ -7160,13 +7161,13 @@
         <v>19</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>30</v>
       </c>
       <c r="E8" s="131" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F8" s="81" t="str">
         <f t="shared" si="0"/>
@@ -7177,16 +7178,16 @@
     </row>
     <row r="9" spans="2:8" ht="91.2" x14ac:dyDescent="0.3">
       <c r="B9" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="C9" s="19" t="s">
         <v>299</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>300</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E9" s="131" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F9" s="81" t="str">
         <f t="shared" si="0"/>
@@ -7197,16 +7198,16 @@
     </row>
     <row r="10" spans="2:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B10" s="16" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>31</v>
       </c>
       <c r="E10" s="131" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F10" s="81" t="str">
         <f t="shared" si="0"/>
@@ -7217,16 +7218,16 @@
     </row>
     <row r="11" spans="2:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="B11" s="16" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>32</v>
       </c>
       <c r="E11" s="131" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F11" s="81" t="str">
         <f t="shared" si="0"/>
@@ -7237,16 +7238,16 @@
     </row>
     <row r="12" spans="2:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B12" s="16" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>33</v>
       </c>
       <c r="E12" s="131" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F12" s="81" t="str">
         <f t="shared" si="0"/>
@@ -7257,16 +7258,16 @@
     </row>
     <row r="13" spans="2:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B13" s="16" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E13" s="131" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F13" s="81" t="str">
         <f t="shared" si="0"/>
@@ -7277,16 +7278,16 @@
     </row>
     <row r="14" spans="2:8" ht="79.8" x14ac:dyDescent="0.3">
       <c r="B14" s="16" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E14" s="131" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F14" s="81" t="str">
         <f t="shared" si="0"/>
@@ -7297,13 +7298,13 @@
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B15" s="16" t="s">
+        <v>300</v>
+      </c>
+      <c r="C15" s="19" t="s">
         <v>301</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="D15" s="3" t="s">
         <v>302</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>303</v>
       </c>
       <c r="E15" s="55"/>
       <c r="F15" s="81" t="str">
@@ -7327,7 +7328,7 @@
     </row>
     <row r="17" spans="7:8" x14ac:dyDescent="0.3">
       <c r="G17" s="46" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H17" s="31">
         <f>AVERAGE(H7:H16)</f>

--- a/file/table/DAPC_ProyectoCAD.xlsx
+++ b/file/table/DAPC_ProyectoCAD.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{889924E1-C1A6-4802-9114-4E00DC671DF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40A8EB8F-93FB-419D-8FD5-C04F566FF9CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0.Inicio" sheetId="7" r:id="rId1"/>
@@ -312,7 +312,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="658" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="349">
   <si>
     <t>1. Especificaciones técnicas generales</t>
   </si>
@@ -1512,6 +1512,15 @@
   </si>
   <si>
     <t>Pararrayos</t>
+  </si>
+  <si>
+    <t>/file/cad/DAPC_AIALayerName.xlsx</t>
+  </si>
+  <si>
+    <t>Layers</t>
+  </si>
+  <si>
+    <t>Nombres y configuraciones de capas o Layers en AutoCAD. Investigue que colores y grosores pueden ser aplicados en las disciplinas a utilizar en el curso y complete el catálogo suministrado.</t>
   </si>
 </sst>
 </file>
@@ -2101,7 +2110,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="183">
+  <cellXfs count="186">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2660,6 +2669,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -3360,7 +3378,7 @@
       </c>
       <c r="D38" s="63"/>
       <c r="E38" s="51">
-        <f>'6.Archivos'!H17</f>
+        <f>'6.Archivos'!H18</f>
         <v>5</v>
       </c>
     </row>
@@ -6015,7 +6033,7 @@
         <v>115</v>
       </c>
       <c r="F14" s="87" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="G14" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6038,7 +6056,7 @@
         <v>115</v>
       </c>
       <c r="F15" s="87" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="G15" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6061,7 +6079,7 @@
         <v>115</v>
       </c>
       <c r="F16" s="87" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="G16" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6084,7 +6102,7 @@
         <v>115</v>
       </c>
       <c r="F17" s="87" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="G17" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6107,7 +6125,7 @@
         <v>115</v>
       </c>
       <c r="F18" s="87" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="G18" s="81" t="str">
         <f t="shared" si="0"/>
@@ -7056,7 +7074,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:H17"/>
+  <dimension ref="B2:H18"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.5546875" style="2" customWidth="1"/>
@@ -7148,7 +7166,7 @@
         <v>305</v>
       </c>
       <c r="F7" s="81" t="str">
-        <f t="shared" ref="F7:F16" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",E7,"/Readme.md"),"Ver")</f>
+        <f t="shared" ref="F7:F17" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",E7,"/Readme.md"),"Ver")</f>
         <v>Ver</v>
       </c>
       <c r="G7" s="55"/>
@@ -7314,24 +7332,44 @@
       <c r="G15" s="55"/>
       <c r="H15" s="8"/>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B16" s="24"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="33"/>
-      <c r="F16" s="82" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="G16" s="33"/>
-      <c r="H16" s="6"/>
-    </row>
-    <row r="17" spans="7:8" x14ac:dyDescent="0.3">
-      <c r="G17" s="46" t="s">
+    <row r="16" spans="2:8" s="36" customFormat="1" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="B16" s="27" t="s">
+        <v>347</v>
+      </c>
+      <c r="C16" s="28" t="s">
+        <v>348</v>
+      </c>
+      <c r="D16" s="183" t="s">
+        <v>346</v>
+      </c>
+      <c r="E16" s="131" t="s">
+        <v>308</v>
+      </c>
+      <c r="F16" s="81" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="G16" s="184"/>
+      <c r="H16" s="185"/>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="B17" s="24"/>
+      <c r="C17" s="25"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="82" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="G17" s="33"/>
+      <c r="H17" s="6"/>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
+      <c r="G18" s="46" t="s">
         <v>271</v>
       </c>
-      <c r="H17" s="31">
-        <f>AVERAGE(H7:H16)</f>
+      <c r="H18" s="31">
+        <f>AVERAGE(H7:H17)</f>
         <v>5</v>
       </c>
     </row>

--- a/file/table/DAPC_ProyectoCAD.xlsx
+++ b/file/table/DAPC_ProyectoCAD.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40A8EB8F-93FB-419D-8FD5-C04F566FF9CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E0D70E6-6294-4E99-A775-D1C41A6BD266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0.Inicio" sheetId="7" r:id="rId1"/>
@@ -881,9 +881,6 @@
     <t>Largo de bodega - Proyecto</t>
   </si>
   <si>
-    <t>Placa de contra piso - Área</t>
-  </si>
-  <si>
     <t>Placa de cimentación- Espesor</t>
   </si>
   <si>
@@ -1424,23 +1421,6 @@
     </r>
   </si>
   <si>
-    <t>4a. Estantería</t>
-  </si>
-  <si>
-    <r>
-      <t>4b. Distribución interna</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (al menos se deben incluir 3 referencias distintas de transformadores eléctricos industriales)</t>
-    </r>
-  </si>
-  <si>
     <t>5. Planos</t>
   </si>
   <si>
@@ -1521,6 +1501,26 @@
   </si>
   <si>
     <t>Nombres y configuraciones de capas o Layers en AutoCAD. Investigue que colores y grosores pueden ser aplicados en las disciplinas a utilizar en el curso y complete el catálogo suministrado.</t>
+  </si>
+  <si>
+    <t>Placa de cimentación - Área</t>
+  </si>
+  <si>
+    <r>
+      <t>4b. Inventario</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (al menos se deben incluir 3 referencias distintas de transformadores eléctricos industriales)</t>
+    </r>
+  </si>
+  <si>
+    <t>4a. Estantería industrial</t>
   </si>
 </sst>
 </file>
@@ -3006,7 +3006,7 @@
   <sheetData>
     <row r="1" spans="2:5" x14ac:dyDescent="0.3">
       <c r="E1" s="100" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
     </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.3">
@@ -3016,7 +3016,7 @@
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B3" s="101" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.3">
@@ -3286,7 +3286,7 @@
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B31" s="73" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C31" s="73"/>
       <c r="D31" s="73"/>
@@ -3309,7 +3309,7 @@
         <v>1</v>
       </c>
       <c r="C33" s="77" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="D33" s="78"/>
       <c r="E33" s="51">
@@ -3322,7 +3322,7 @@
         <v>2</v>
       </c>
       <c r="C34" s="62" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D34" s="63"/>
       <c r="E34" s="51">
@@ -3335,7 +3335,7 @@
         <v>3</v>
       </c>
       <c r="C35" s="62" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="D35" s="63"/>
       <c r="E35" s="51">
@@ -3348,7 +3348,7 @@
         <v>4</v>
       </c>
       <c r="C36" s="60" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D36" s="61"/>
       <c r="E36" s="51">
@@ -3361,7 +3361,7 @@
         <v>4</v>
       </c>
       <c r="C37" s="62" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="D37" s="63"/>
       <c r="E37" s="51">
@@ -3374,7 +3374,7 @@
         <v>5</v>
       </c>
       <c r="C38" s="62" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="D38" s="63"/>
       <c r="E38" s="51">
@@ -3387,7 +3387,7 @@
         <v>6</v>
       </c>
       <c r="C39" s="62" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D39" s="63"/>
       <c r="E39" s="99">
@@ -3399,7 +3399,7 @@
         <v>7</v>
       </c>
       <c r="C40" s="64" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="D40" s="65"/>
       <c r="E40" s="58">
@@ -3408,7 +3408,7 @@
     </row>
     <row r="41" spans="2:5" x14ac:dyDescent="0.3">
       <c r="D41" s="118" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E41" s="59">
         <f>AVERAGE(E33:E40)</f>
@@ -3476,7 +3476,7 @@
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B4" s="102" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="C4" s="102"/>
       <c r="D4" s="102"/>
@@ -3514,10 +3514,10 @@
     </row>
     <row r="7" spans="2:9" ht="57" x14ac:dyDescent="0.3">
       <c r="B7" s="127" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="C7" s="128" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="D7" s="91">
         <v>1</v>
@@ -3526,7 +3526,7 @@
         <v>16</v>
       </c>
       <c r="F7" s="131" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G7" s="132" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F7,"/Readme.md"),"Ver")</f>
@@ -3539,19 +3539,19 @@
     </row>
     <row r="8" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B8" s="127" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C8" s="128" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="D8" s="91">
         <v>1</v>
       </c>
       <c r="E8" s="130" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F8" s="131" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G8" s="132" t="str">
         <f t="shared" ref="G8:G18" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F8,"/Readme.md"),"Ver")</f>
@@ -3562,17 +3562,17 @@
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B9" s="127" t="s">
+        <v>271</v>
+      </c>
+      <c r="C9" s="128" t="s">
         <v>272</v>
       </c>
-      <c r="C9" s="128" t="s">
-        <v>273</v>
-      </c>
       <c r="D9" s="91" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E9" s="130"/>
       <c r="F9" s="131" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="G9" s="132" t="str">
         <f t="shared" si="0"/>
@@ -3583,10 +3583,10 @@
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B10" s="127" t="s">
+        <v>275</v>
+      </c>
+      <c r="C10" s="128" t="s">
         <v>276</v>
-      </c>
-      <c r="C10" s="128" t="s">
-        <v>277</v>
       </c>
       <c r="D10" s="91">
         <v>1</v>
@@ -3595,7 +3595,7 @@
         <v>16</v>
       </c>
       <c r="F10" s="131" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G10" s="132" t="str">
         <f t="shared" si="0"/>
@@ -3606,17 +3606,17 @@
     </row>
     <row r="11" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
       <c r="B11" s="127" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C11" s="128" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D11" s="91" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E11" s="130"/>
       <c r="F11" s="131" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G11" s="132" t="str">
         <f t="shared" si="0"/>
@@ -3627,17 +3627,17 @@
     </row>
     <row r="12" spans="2:9" ht="57" x14ac:dyDescent="0.3">
       <c r="B12" s="127" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C12" s="128" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D12" s="91" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E12" s="130"/>
       <c r="F12" s="131" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="G12" s="132" t="str">
         <f t="shared" si="0"/>
@@ -3648,17 +3648,17 @@
     </row>
     <row r="13" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B13" s="127" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C13" s="128" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D13" s="91" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E13" s="130"/>
       <c r="F13" s="131" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="G13" s="132" t="str">
         <f t="shared" si="0"/>
@@ -3669,17 +3669,17 @@
     </row>
     <row r="14" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
       <c r="B14" s="127" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C14" s="128" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D14" s="91" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="E14" s="130"/>
       <c r="F14" s="131" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G14" s="132" t="str">
         <f t="shared" si="0"/>
@@ -3690,10 +3690,10 @@
     </row>
     <row r="15" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="B15" s="127" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C15" s="128" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D15" s="91">
         <v>1</v>
@@ -3702,7 +3702,7 @@
         <v>16</v>
       </c>
       <c r="F15" s="131" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G15" s="132" t="str">
         <f t="shared" si="0"/>
@@ -3713,10 +3713,10 @@
     </row>
     <row r="16" spans="2:9" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B16" s="127" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C16" s="128" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D16" s="91">
         <v>1</v>
@@ -3725,7 +3725,7 @@
         <v>16</v>
       </c>
       <c r="F16" s="131" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G16" s="132" t="str">
         <f t="shared" si="0"/>
@@ -3736,10 +3736,10 @@
     </row>
     <row r="17" spans="2:9" ht="35.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B17" s="134" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C17" s="135" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D17" s="91">
         <v>1</v>
@@ -3748,7 +3748,7 @@
         <v>16</v>
       </c>
       <c r="F17" s="131" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G17" s="132" t="str">
         <f t="shared" si="0"/>
@@ -3772,7 +3772,7 @@
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.3">
       <c r="H19" s="141" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I19" s="120">
         <f>AVERAGE(I7:I18)</f>
@@ -3822,7 +3822,7 @@
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B4" s="102" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C4" s="102"/>
       <c r="D4" s="102"/>
@@ -3868,7 +3868,7 @@
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B7" s="146" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C7" s="147"/>
       <c r="D7" s="148"/>
@@ -3892,14 +3892,14 @@
         <v>53</v>
       </c>
       <c r="F8" s="131" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G8" s="132" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F8,"/Readme.md"),"Ver")</f>
         <v>Ver</v>
       </c>
       <c r="H8" s="128" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="I8" s="133">
         <v>5</v>
@@ -3919,14 +3919,14 @@
         <v>53</v>
       </c>
       <c r="F9" s="131" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G9" s="132" t="str">
         <f t="shared" ref="G9:G72" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F9,"/Readme.md"),"Ver")</f>
         <v>Ver</v>
       </c>
       <c r="H9" s="128" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="I9" s="133"/>
     </row>
@@ -3945,7 +3945,7 @@
         <v>53</v>
       </c>
       <c r="F10" s="131" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G10" s="132" t="str">
         <f t="shared" si="0"/>
@@ -3969,7 +3969,7 @@
         <v>53</v>
       </c>
       <c r="F11" s="131" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G11" s="132" t="str">
         <f t="shared" si="0"/>
@@ -3983,7 +3983,7 @@
         <v>39</v>
       </c>
       <c r="C12" s="128" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D12" s="129">
         <v>12</v>
@@ -3992,14 +3992,14 @@
         <v>53</v>
       </c>
       <c r="F12" s="131" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G12" s="132" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H12" s="128" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="I12" s="133"/>
     </row>
@@ -4017,14 +4017,14 @@
         <v>53</v>
       </c>
       <c r="F13" s="131" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G13" s="132" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H13" s="128" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="I13" s="133"/>
     </row>
@@ -4042,14 +4042,14 @@
         <v>53</v>
       </c>
       <c r="F14" s="131" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G14" s="132" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H14" s="128" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="I14" s="133"/>
     </row>
@@ -4068,7 +4068,7 @@
         <v>53</v>
       </c>
       <c r="F15" s="131" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G15" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4092,7 +4092,7 @@
         <v>53</v>
       </c>
       <c r="F16" s="131" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G16" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4116,7 +4116,7 @@
         <v>54</v>
       </c>
       <c r="F17" s="131" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G17" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4140,7 +4140,7 @@
         <v>54</v>
       </c>
       <c r="F18" s="131" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G18" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4164,7 +4164,7 @@
         <v>54</v>
       </c>
       <c r="F19" s="131" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G19" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4188,7 +4188,7 @@
         <v>67</v>
       </c>
       <c r="F20" s="131" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G20" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4212,7 +4212,7 @@
         <v>67</v>
       </c>
       <c r="F21" s="131" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G21" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4236,7 +4236,7 @@
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B23" s="146" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C23" s="147"/>
       <c r="D23" s="148"/>
@@ -4260,14 +4260,14 @@
         <v>53</v>
       </c>
       <c r="F24" s="131" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G24" s="132" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H24" s="128" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="I24" s="133">
         <v>5</v>
@@ -4287,7 +4287,7 @@
         <v>68</v>
       </c>
       <c r="F25" s="131" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G25" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4311,7 +4311,7 @@
         <v>69</v>
       </c>
       <c r="F26" s="131" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G26" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4325,7 +4325,7 @@
         <v>75</v>
       </c>
       <c r="C27" s="135" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D27" s="155">
         <v>0.6</v>
@@ -4334,7 +4334,7 @@
         <v>53</v>
       </c>
       <c r="F27" s="131" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G27" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4357,7 +4357,7 @@
         <v>53</v>
       </c>
       <c r="F28" s="131" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G28" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4380,7 +4380,7 @@
         <v>67</v>
       </c>
       <c r="F29" s="131" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G29" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4404,7 +4404,7 @@
         <v>54</v>
       </c>
       <c r="F30" s="131" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G30" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4428,7 +4428,7 @@
         <v>54</v>
       </c>
       <c r="F31" s="131" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G31" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4452,7 +4452,7 @@
         <v>54</v>
       </c>
       <c r="F32" s="131" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G32" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4475,7 +4475,7 @@
         <v>53</v>
       </c>
       <c r="F33" s="131" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G33" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4499,7 +4499,7 @@
         <v>115</v>
       </c>
       <c r="F34" s="131" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G34" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4522,7 +4522,7 @@
         <v>63</v>
       </c>
       <c r="F35" s="131" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G35" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4536,7 +4536,7 @@
         <v>80</v>
       </c>
       <c r="C36" s="128" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="D36" s="130">
         <f>D35*D35/(1000*1000)</f>
@@ -4546,7 +4546,7 @@
         <v>54</v>
       </c>
       <c r="F36" s="131" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G36" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4570,7 +4570,7 @@
         <v>54</v>
       </c>
       <c r="F37" s="131" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G37" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4594,7 +4594,7 @@
     </row>
     <row r="39" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B39" s="156" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="C39" s="147"/>
       <c r="D39" s="148"/>
@@ -4606,7 +4606,7 @@
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B40" s="127" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="C40" s="128" t="s">
         <v>86</v>
@@ -4618,7 +4618,7 @@
         <v>53</v>
       </c>
       <c r="F40" s="131" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G40" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4643,7 +4643,7 @@
         <v>53</v>
       </c>
       <c r="F41" s="131" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G41" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4657,7 +4657,7 @@
         <v>84</v>
       </c>
       <c r="C42" s="128" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="D42" s="130">
         <f>D11+(INT(D11/D41)*D10)</f>
@@ -4667,7 +4667,7 @@
         <v>53</v>
       </c>
       <c r="F42" s="131" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G42" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4691,7 +4691,7 @@
         <v>54</v>
       </c>
       <c r="F43" s="131" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G43" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4715,7 +4715,7 @@
     </row>
     <row r="45" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B45" s="146" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C45" s="147"/>
       <c r="D45" s="148"/>
@@ -4730,7 +4730,7 @@
         <v>41</v>
       </c>
       <c r="C46" s="128" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D46" s="129">
         <v>60</v>
@@ -4739,7 +4739,7 @@
         <v>54</v>
       </c>
       <c r="F46" s="131" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G46" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4764,7 +4764,7 @@
         <v>54</v>
       </c>
       <c r="F47" s="131" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G47" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4787,7 +4787,7 @@
         <v>53</v>
       </c>
       <c r="F48" s="131" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G48" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4811,7 +4811,7 @@
         <v>54</v>
       </c>
       <c r="F49" s="131" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G49" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4834,7 +4834,7 @@
         <v>55</v>
       </c>
       <c r="F50" s="131" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G50" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4857,7 +4857,7 @@
         <v>55</v>
       </c>
       <c r="F51" s="131" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G51" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4881,7 +4881,7 @@
         <v>49</v>
       </c>
       <c r="F52" s="131" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G52" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4904,7 +4904,7 @@
         <v>53</v>
       </c>
       <c r="F53" s="131" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G53" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4928,7 +4928,7 @@
         <v>54</v>
       </c>
       <c r="F54" s="131" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G54" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4942,7 +4942,7 @@
         <v>125</v>
       </c>
       <c r="C55" s="128" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D55" s="129">
         <v>6</v>
@@ -4951,7 +4951,7 @@
         <v>53</v>
       </c>
       <c r="F55" s="131" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G55" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4965,7 +4965,7 @@
         <v>126</v>
       </c>
       <c r="C56" s="128" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D56" s="129">
         <v>4.5</v>
@@ -4974,7 +4974,7 @@
         <v>53</v>
       </c>
       <c r="F56" s="131" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G56" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4997,7 +4997,7 @@
         <v>53</v>
       </c>
       <c r="F57" s="131" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G57" s="132" t="str">
         <f t="shared" si="0"/>
@@ -5008,10 +5008,10 @@
     </row>
     <row r="58" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B58" s="127" t="s">
+        <v>182</v>
+      </c>
+      <c r="C58" s="128" t="s">
         <v>183</v>
-      </c>
-      <c r="C58" s="128" t="s">
-        <v>184</v>
       </c>
       <c r="D58" s="129">
         <v>2.2999999999999998</v>
@@ -5020,7 +5020,7 @@
         <v>53</v>
       </c>
       <c r="F58" s="131" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G58" s="132" t="str">
         <f t="shared" si="0"/>
@@ -5034,7 +5034,7 @@
         <v>129</v>
       </c>
       <c r="C59" s="128" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D59" s="129">
         <v>3</v>
@@ -5043,7 +5043,7 @@
         <v>53</v>
       </c>
       <c r="F59" s="131" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G59" s="132" t="str">
         <f t="shared" si="0"/>
@@ -5054,10 +5054,10 @@
     </row>
     <row r="60" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B60" s="127" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C60" s="128" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D60" s="129">
         <v>2</v>
@@ -5066,7 +5066,7 @@
         <v>53</v>
       </c>
       <c r="F60" s="131" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G60" s="132" t="str">
         <f t="shared" si="0"/>
@@ -5090,7 +5090,7 @@
     </row>
     <row r="62" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B62" s="158" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C62" s="159"/>
       <c r="D62" s="160"/>
@@ -5102,7 +5102,7 @@
     </row>
     <row r="63" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B63" s="127" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C63" s="128" t="s">
         <v>103</v>
@@ -5114,7 +5114,7 @@
         <v>55</v>
       </c>
       <c r="F63" s="131" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G63" s="132" t="str">
         <f t="shared" si="0"/>
@@ -5127,10 +5127,10 @@
     </row>
     <row r="64" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B64" s="127" t="s">
-        <v>165</v>
+        <v>346</v>
       </c>
       <c r="C64" s="128" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D64" s="157">
         <f>D18</f>
@@ -5140,7 +5140,7 @@
         <v>54</v>
       </c>
       <c r="F64" s="131" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G64" s="132" t="str">
         <f t="shared" si="0"/>
@@ -5163,7 +5163,7 @@
         <v>55</v>
       </c>
       <c r="F65" s="131" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G65" s="132" t="str">
         <f t="shared" si="0"/>
@@ -5186,7 +5186,7 @@
         <v>53</v>
       </c>
       <c r="F66" s="131" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G66" s="132" t="str">
         <f t="shared" si="0"/>
@@ -5210,7 +5210,7 @@
         <v>115</v>
       </c>
       <c r="F67" s="131" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G67" s="132" t="str">
         <f t="shared" si="0"/>
@@ -5234,7 +5234,7 @@
         <v>115</v>
       </c>
       <c r="F68" s="131" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G68" s="132" t="str">
         <f t="shared" si="0"/>
@@ -5258,7 +5258,7 @@
         <v>115</v>
       </c>
       <c r="F69" s="131" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G69" s="132" t="str">
         <f t="shared" si="0"/>
@@ -5272,7 +5272,7 @@
         <v>105</v>
       </c>
       <c r="C70" s="128" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="D70" s="129">
         <v>0.25</v>
@@ -5281,7 +5281,7 @@
         <v>53</v>
       </c>
       <c r="F70" s="131" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G70" s="132" t="str">
         <f t="shared" si="0"/>
@@ -5304,7 +5304,7 @@
         <v>53</v>
       </c>
       <c r="F71" s="131" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G71" s="132" t="str">
         <f t="shared" si="0"/>
@@ -5327,7 +5327,7 @@
         <v>53</v>
       </c>
       <c r="F72" s="131" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G72" s="132" t="str">
         <f t="shared" si="0"/>
@@ -5350,7 +5350,7 @@
         <v>53</v>
       </c>
       <c r="F73" s="131" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G73" s="132" t="str">
         <f t="shared" ref="G73:G76" si="1">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F73,"/Readme.md"),"Ver")</f>
@@ -5374,7 +5374,7 @@
         <v>53</v>
       </c>
       <c r="F74" s="131" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G74" s="132" t="str">
         <f t="shared" si="1"/>
@@ -5398,7 +5398,7 @@
         <v>53</v>
       </c>
       <c r="F75" s="131" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G75" s="132" t="str">
         <f t="shared" si="1"/>
@@ -5422,7 +5422,7 @@
     </row>
     <row r="77" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B77" s="182" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C77" s="159"/>
       <c r="D77" s="160"/>
@@ -5434,10 +5434,10 @@
     </row>
     <row r="78" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B78" s="127" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C78" s="177" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D78" s="178">
         <f>D64</f>
@@ -5447,7 +5447,7 @@
         <v>54</v>
       </c>
       <c r="F78" s="131" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G78" s="132" t="str">
         <f t="shared" ref="G78:G88" si="2">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F78,"/Readme.md"),"Ver")</f>
@@ -5458,20 +5458,20 @@
     </row>
     <row r="79" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
       <c r="B79" s="127" t="s">
+        <v>169</v>
+      </c>
+      <c r="C79" s="177" t="s">
         <v>170</v>
-      </c>
-      <c r="C79" s="177" t="s">
-        <v>171</v>
       </c>
       <c r="D79" s="178">
         <f>D78*D63</f>
         <v>57400</v>
       </c>
       <c r="E79" s="178" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F79" s="131" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G79" s="132" t="str">
         <f t="shared" si="2"/>
@@ -5482,10 +5482,10 @@
     </row>
     <row r="80" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B80" s="127" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C80" s="177" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D80" s="178">
         <f>D49</f>
@@ -5495,7 +5495,7 @@
         <v>54</v>
       </c>
       <c r="F80" s="131" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G80" s="132" t="str">
         <f t="shared" si="2"/>
@@ -5506,10 +5506,10 @@
     </row>
     <row r="81" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B81" s="127" t="s">
+        <v>173</v>
+      </c>
+      <c r="C81" s="177" t="s">
         <v>174</v>
-      </c>
-      <c r="C81" s="177" t="s">
-        <v>175</v>
       </c>
       <c r="D81" s="178">
         <f>D69</f>
@@ -5519,7 +5519,7 @@
         <v>115</v>
       </c>
       <c r="F81" s="131" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G81" s="132" t="str">
         <f t="shared" si="2"/>
@@ -5530,10 +5530,10 @@
     </row>
     <row r="82" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
       <c r="B82" s="127" t="s">
+        <v>175</v>
+      </c>
+      <c r="C82" s="177" t="s">
         <v>176</v>
-      </c>
-      <c r="C82" s="177" t="s">
-        <v>177</v>
       </c>
       <c r="D82" s="178">
         <f>D81*D12</f>
@@ -5543,7 +5543,7 @@
         <v>53</v>
       </c>
       <c r="F82" s="131" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G82" s="132" t="str">
         <f t="shared" si="2"/>
@@ -5554,10 +5554,10 @@
     </row>
     <row r="83" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
       <c r="B83" s="127" t="s">
+        <v>177</v>
+      </c>
+      <c r="C83" s="177" t="s">
         <v>178</v>
-      </c>
-      <c r="C83" s="177" t="s">
-        <v>179</v>
       </c>
       <c r="D83" s="178">
         <f>((D67*D9)+(D68*D8))*INT(D12/D48)</f>
@@ -5567,7 +5567,7 @@
         <v>53</v>
       </c>
       <c r="F83" s="131" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G83" s="132" t="str">
         <f t="shared" si="2"/>
@@ -5578,19 +5578,19 @@
     </row>
     <row r="84" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
       <c r="B84" s="127" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C84" s="177" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D84" s="180" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E84" s="178" t="s">
         <v>54</v>
       </c>
       <c r="F84" s="131" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G84" s="132" t="str">
         <f t="shared" si="2"/>
@@ -5603,10 +5603,10 @@
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B85" s="127" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C85" s="177" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D85" s="180">
         <v>2</v>
@@ -5615,7 +5615,7 @@
         <v>115</v>
       </c>
       <c r="F85" s="131" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G85" s="132" t="str">
         <f t="shared" si="2"/>
@@ -5629,16 +5629,16 @@
         <v>46</v>
       </c>
       <c r="C86" s="177" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D86" s="180" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E86" s="178" t="s">
         <v>115</v>
       </c>
       <c r="F86" s="131" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G86" s="132" t="str">
         <f t="shared" si="2"/>
@@ -5652,16 +5652,16 @@
         <v>47</v>
       </c>
       <c r="C87" s="177" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D87" s="180" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="E87" s="178" t="s">
         <v>115</v>
       </c>
       <c r="F87" s="131" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G87" s="132" t="str">
         <f t="shared" si="2"/>
@@ -5690,7 +5690,7 @@
     </row>
     <row r="90" spans="2:9" x14ac:dyDescent="0.3">
       <c r="H90" s="141" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I90" s="120">
         <f>AVERAGE(I7:I88)</f>
@@ -5699,7 +5699,7 @@
     </row>
     <row r="91" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B91" s="47" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
     </row>
     <row r="92" spans="2:9" x14ac:dyDescent="0.3">
@@ -5823,7 +5823,7 @@
     </row>
     <row r="4" spans="2:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="74" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C4" s="74"/>
       <c r="D4" s="74"/>
@@ -5869,7 +5869,7 @@
     </row>
     <row r="7" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B7" s="5" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C7" s="17"/>
       <c r="D7" s="18"/>
@@ -5881,10 +5881,10 @@
     </row>
     <row r="8" spans="2:9" ht="57" x14ac:dyDescent="0.3">
       <c r="B8" s="16" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D8" s="15">
         <v>1</v>
@@ -5893,7 +5893,7 @@
         <v>115</v>
       </c>
       <c r="F8" s="87" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G8" s="81" t="str">
         <f t="shared" ref="G8:G21" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F8,"/Readme.md"),"Ver")</f>
@@ -5906,10 +5906,10 @@
     </row>
     <row r="9" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B9" s="16" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D9" s="15">
         <v>1</v>
@@ -5918,7 +5918,7 @@
         <v>115</v>
       </c>
       <c r="F9" s="87" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G9" s="81" t="str">
         <f t="shared" si="0"/>
@@ -5929,10 +5929,10 @@
     </row>
     <row r="10" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B10" s="16" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D10" s="15">
         <v>1</v>
@@ -5941,7 +5941,7 @@
         <v>115</v>
       </c>
       <c r="F10" s="87" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G10" s="81" t="str">
         <f t="shared" si="0"/>
@@ -5952,10 +5952,10 @@
     </row>
     <row r="11" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B11" s="16" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D11" s="15">
         <v>1</v>
@@ -5964,7 +5964,7 @@
         <v>115</v>
       </c>
       <c r="F11" s="87" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G11" s="81" t="str">
         <f t="shared" si="0"/>
@@ -5975,10 +5975,10 @@
     </row>
     <row r="12" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B12" s="27" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D12" s="15">
         <v>1</v>
@@ -5987,7 +5987,7 @@
         <v>115</v>
       </c>
       <c r="F12" s="87" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G12" s="81" t="str">
         <f t="shared" si="0"/>
@@ -5998,10 +5998,10 @@
     </row>
     <row r="13" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B13" s="27" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D13" s="15">
         <v>1</v>
@@ -6010,7 +6010,7 @@
         <v>115</v>
       </c>
       <c r="F13" s="87" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G13" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6021,10 +6021,10 @@
     </row>
     <row r="14" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B14" s="16" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D14" s="15">
         <v>1</v>
@@ -6033,7 +6033,7 @@
         <v>115</v>
       </c>
       <c r="F14" s="87" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G14" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6044,10 +6044,10 @@
     </row>
     <row r="15" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B15" s="16" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D15" s="15">
         <v>1</v>
@@ -6056,7 +6056,7 @@
         <v>115</v>
       </c>
       <c r="F15" s="87" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G15" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6067,10 +6067,10 @@
     </row>
     <row r="16" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B16" s="27" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D16" s="15">
         <v>1</v>
@@ -6079,7 +6079,7 @@
         <v>115</v>
       </c>
       <c r="F16" s="87" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G16" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6090,10 +6090,10 @@
     </row>
     <row r="17" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B17" s="27" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D17" s="15">
         <v>1</v>
@@ -6102,7 +6102,7 @@
         <v>115</v>
       </c>
       <c r="F17" s="87" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G17" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6113,10 +6113,10 @@
     </row>
     <row r="18" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B18" s="27" t="s">
+        <v>198</v>
+      </c>
+      <c r="C18" s="19" t="s">
         <v>199</v>
-      </c>
-      <c r="C18" s="19" t="s">
-        <v>200</v>
       </c>
       <c r="D18" s="15">
         <v>1</v>
@@ -6125,7 +6125,7 @@
         <v>115</v>
       </c>
       <c r="F18" s="87" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G18" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6136,10 +6136,10 @@
     </row>
     <row r="19" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B19" s="27" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D19" s="29">
         <v>1</v>
@@ -6148,7 +6148,7 @@
         <v>115</v>
       </c>
       <c r="F19" s="87" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G19" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6159,10 +6159,10 @@
     </row>
     <row r="20" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B20" s="27" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D20" s="29">
         <v>1</v>
@@ -6171,7 +6171,7 @@
         <v>115</v>
       </c>
       <c r="F20" s="87" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G20" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6195,7 +6195,7 @@
     </row>
     <row r="22" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B22" s="5" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="C22" s="17"/>
       <c r="D22" s="18"/>
@@ -6207,10 +6207,10 @@
     </row>
     <row r="23" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="B23" s="16" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D23" s="30">
         <f>'2.ArquitectonicaEstructural'!D31-'2.ArquitectonicaEstructural'!D37-'2.ArquitectonicaEstructural'!D43</f>
@@ -6220,7 +6220,7 @@
         <v>54</v>
       </c>
       <c r="F23" s="87" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G23" s="81" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F23,"/Readme.md"),"Ver")</f>
@@ -6233,10 +6233,10 @@
     </row>
     <row r="24" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B24" s="16" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D24" s="20">
         <v>992</v>
@@ -6245,7 +6245,7 @@
         <v>63</v>
       </c>
       <c r="F24" s="87" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G24" s="81" t="str">
         <f t="shared" ref="G24:G27" si="1">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F24,"/Readme.md"),"Ver")</f>
@@ -6256,10 +6256,10 @@
     </row>
     <row r="25" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B25" s="16" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D25" s="20">
         <v>1950</v>
@@ -6268,7 +6268,7 @@
         <v>63</v>
       </c>
       <c r="F25" s="87" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G25" s="81" t="str">
         <f t="shared" si="1"/>
@@ -6279,10 +6279,10 @@
     </row>
     <row r="26" spans="2:9" ht="45.6" x14ac:dyDescent="0.3">
       <c r="B26" s="16" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="D26" s="15">
         <f>INT(D23/(D24/1000*D25/1000))</f>
@@ -6292,7 +6292,7 @@
         <v>115</v>
       </c>
       <c r="F26" s="87" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="G26" s="81" t="str">
         <f t="shared" si="1"/>
@@ -6316,7 +6316,7 @@
     </row>
     <row r="28" spans="2:9" ht="16.8" x14ac:dyDescent="0.4">
       <c r="H28" s="46" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I28" s="57">
         <f>AVERAGE(I7:I27)</f>
@@ -6360,12 +6360,12 @@
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B3" s="9" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
     </row>
     <row r="4" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B4" s="74" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C4" s="74"/>
       <c r="D4" s="74"/>
@@ -6411,7 +6411,7 @@
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B7" s="5" t="s">
-        <v>327</v>
+        <v>348</v>
       </c>
       <c r="C7" s="17"/>
       <c r="D7" s="18"/>
@@ -6423,10 +6423,10 @@
     </row>
     <row r="8" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B8" s="16" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D8" s="20">
         <v>3</v>
@@ -6435,7 +6435,7 @@
         <v>53</v>
       </c>
       <c r="F8" s="87" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G8" s="81" t="str">
         <f t="shared" ref="G8:G21" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F8,"/Readme.md"),"Ver")</f>
@@ -6448,10 +6448,10 @@
     </row>
     <row r="9" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B9" s="16" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D9" s="20">
         <v>2.5</v>
@@ -6460,7 +6460,7 @@
         <v>53</v>
       </c>
       <c r="F9" s="87" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G9" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6471,19 +6471,19 @@
     </row>
     <row r="10" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B10" s="16" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D10" s="20">
         <v>4</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="F10" s="87" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G10" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6494,10 +6494,10 @@
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B11" s="16" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D11" s="20">
         <v>2</v>
@@ -6506,7 +6506,7 @@
         <v>53</v>
       </c>
       <c r="F11" s="87" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G11" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6517,10 +6517,10 @@
     </row>
     <row r="12" spans="2:9" ht="33.6" x14ac:dyDescent="0.4">
       <c r="B12" s="16" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D12" s="15">
         <f>D10*D11</f>
@@ -6530,7 +6530,7 @@
         <v>53</v>
       </c>
       <c r="F12" s="87" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G12" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6541,10 +6541,10 @@
     </row>
     <row r="13" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B13" s="16" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D13" s="20">
         <v>8</v>
@@ -6553,7 +6553,7 @@
         <v>53</v>
       </c>
       <c r="F13" s="87" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G13" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6564,20 +6564,20 @@
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B14" s="16" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="D14" s="15" t="str">
         <f>IF(D12&lt;=D13, "Cumple","No cumple")</f>
         <v>Cumple</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="F14" s="87" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G14" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6588,10 +6588,10 @@
     </row>
     <row r="15" spans="2:9" ht="33.6" x14ac:dyDescent="0.4">
       <c r="B15" s="16" t="s">
+        <v>241</v>
+      </c>
+      <c r="C15" s="19" t="s">
         <v>242</v>
-      </c>
-      <c r="C15" s="19" t="s">
-        <v>243</v>
       </c>
       <c r="D15" s="20">
         <v>60</v>
@@ -6600,7 +6600,7 @@
         <v>53</v>
       </c>
       <c r="F15" s="87" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G15" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6611,10 +6611,10 @@
     </row>
     <row r="16" spans="2:9" ht="33.6" x14ac:dyDescent="0.4">
       <c r="B16" s="16" t="s">
+        <v>243</v>
+      </c>
+      <c r="C16" s="19" t="s">
         <v>244</v>
-      </c>
-      <c r="C16" s="19" t="s">
-        <v>245</v>
       </c>
       <c r="D16" s="15">
         <f>D15*D10</f>
@@ -6624,7 +6624,7 @@
         <v>53</v>
       </c>
       <c r="F16" s="87" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G16" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6648,7 +6648,7 @@
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B18" s="5" t="s">
-        <v>328</v>
+        <v>347</v>
       </c>
       <c r="C18" s="17"/>
       <c r="D18" s="18"/>
@@ -6660,19 +6660,19 @@
     </row>
     <row r="19" spans="2:9" ht="45.6" x14ac:dyDescent="0.4">
       <c r="B19" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C19" s="19" t="s">
+        <v>234</v>
+      </c>
+      <c r="D19" s="20" t="s">
         <v>235</v>
-      </c>
-      <c r="D19" s="20" t="s">
-        <v>236</v>
       </c>
       <c r="E19" s="15" t="s">
         <v>115</v>
       </c>
       <c r="F19" s="87" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G19" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6685,19 +6685,19 @@
     </row>
     <row r="20" spans="2:9" ht="45.6" x14ac:dyDescent="0.4">
       <c r="B20" s="16" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C20" s="19" t="s">
+        <v>234</v>
+      </c>
+      <c r="D20" s="20" t="s">
         <v>235</v>
-      </c>
-      <c r="D20" s="20" t="s">
-        <v>236</v>
       </c>
       <c r="E20" s="15" t="s">
         <v>115</v>
       </c>
       <c r="F20" s="87" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G20" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6708,19 +6708,19 @@
     </row>
     <row r="21" spans="2:9" ht="45.6" x14ac:dyDescent="0.4">
       <c r="B21" s="16" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="C21" s="19" t="s">
+        <v>234</v>
+      </c>
+      <c r="D21" s="20" t="s">
         <v>235</v>
-      </c>
-      <c r="D21" s="20" t="s">
-        <v>236</v>
       </c>
       <c r="E21" s="15" t="s">
         <v>115</v>
       </c>
       <c r="F21" s="87" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="G21" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6741,7 +6741,7 @@
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.4">
       <c r="H23" s="46" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I23" s="57">
         <f>AVERAGE(I7:I22)</f>
@@ -6782,12 +6782,12 @@
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B3" s="9" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B4" s="74" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="C4" s="74"/>
       <c r="D4" s="74"/>
@@ -6833,10 +6833,10 @@
     </row>
     <row r="7" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B7" s="16" t="s">
+        <v>248</v>
+      </c>
+      <c r="C7" s="19" t="s">
         <v>249</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>250</v>
       </c>
       <c r="D7" s="20">
         <v>1</v>
@@ -6845,7 +6845,7 @@
         <v>115</v>
       </c>
       <c r="F7" s="87" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G7" s="81" t="str">
         <f t="shared" ref="G7:G16" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F7,"/Readme.md"),"Ver")</f>
@@ -6858,10 +6858,10 @@
     </row>
     <row r="8" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B8" s="16" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D8" s="20">
         <v>1</v>
@@ -6870,7 +6870,7 @@
         <v>115</v>
       </c>
       <c r="F8" s="87" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G8" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6881,10 +6881,10 @@
     </row>
     <row r="9" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B9" s="16" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D9" s="20">
         <v>1</v>
@@ -6893,7 +6893,7 @@
         <v>115</v>
       </c>
       <c r="F9" s="87" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G9" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6904,10 +6904,10 @@
     </row>
     <row r="10" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B10" s="16" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D10" s="20">
         <v>1</v>
@@ -6916,7 +6916,7 @@
         <v>115</v>
       </c>
       <c r="F10" s="87" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G10" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6927,10 +6927,10 @@
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B11" s="16" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D11" s="20">
         <v>1</v>
@@ -6939,7 +6939,7 @@
         <v>115</v>
       </c>
       <c r="F11" s="87" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G11" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6950,10 +6950,10 @@
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B12" s="16" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D12" s="20">
         <v>1</v>
@@ -6962,7 +6962,7 @@
         <v>115</v>
       </c>
       <c r="F12" s="87" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G12" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6973,10 +6973,10 @@
     </row>
     <row r="13" spans="2:9" ht="33.6" x14ac:dyDescent="0.4">
       <c r="B13" s="16" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D13" s="20">
         <v>1</v>
@@ -6985,7 +6985,7 @@
         <v>115</v>
       </c>
       <c r="F13" s="87" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G13" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6996,10 +6996,10 @@
     </row>
     <row r="14" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B14" s="16" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D14" s="20">
         <v>1</v>
@@ -7008,7 +7008,7 @@
         <v>115</v>
       </c>
       <c r="F14" s="87" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G14" s="81" t="str">
         <f t="shared" si="0"/>
@@ -7019,10 +7019,10 @@
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B15" s="16" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D15" s="20">
         <v>1</v>
@@ -7031,7 +7031,7 @@
         <v>115</v>
       </c>
       <c r="F15" s="87" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="G15" s="81" t="str">
         <f t="shared" si="0"/>
@@ -7055,7 +7055,7 @@
     </row>
     <row r="17" spans="8:9" x14ac:dyDescent="0.4">
       <c r="H17" s="46" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="I17" s="57">
         <f>AVERAGE(I7:I16)</f>
@@ -7102,7 +7102,7 @@
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B3" s="80" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="C3" s="80"/>
       <c r="D3" s="80"/>
@@ -7113,7 +7113,7 @@
     </row>
     <row r="4" spans="2:8" s="36" customFormat="1" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="74" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="C4" s="74"/>
       <c r="D4" s="74"/>
@@ -7154,16 +7154,16 @@
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B7" s="16" t="s">
+        <v>271</v>
+      </c>
+      <c r="C7" s="19" t="s">
         <v>272</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>273</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>34</v>
       </c>
       <c r="E7" s="131" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F7" s="81" t="str">
         <f t="shared" ref="F7:F17" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",E7,"/Readme.md"),"Ver")</f>
@@ -7179,13 +7179,13 @@
         <v>19</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>30</v>
       </c>
       <c r="E8" s="131" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F8" s="81" t="str">
         <f t="shared" si="0"/>
@@ -7196,16 +7196,16 @@
     </row>
     <row r="9" spans="2:8" ht="91.2" x14ac:dyDescent="0.3">
       <c r="B9" s="16" t="s">
+        <v>297</v>
+      </c>
+      <c r="C9" s="19" t="s">
         <v>298</v>
-      </c>
-      <c r="C9" s="19" t="s">
-        <v>299</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E9" s="131" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F9" s="81" t="str">
         <f t="shared" si="0"/>
@@ -7216,16 +7216,16 @@
     </row>
     <row r="10" spans="2:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B10" s="16" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>31</v>
       </c>
       <c r="E10" s="131" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F10" s="81" t="str">
         <f t="shared" si="0"/>
@@ -7236,16 +7236,16 @@
     </row>
     <row r="11" spans="2:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="B11" s="16" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>32</v>
       </c>
       <c r="E11" s="131" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F11" s="81" t="str">
         <f t="shared" si="0"/>
@@ -7256,16 +7256,16 @@
     </row>
     <row r="12" spans="2:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B12" s="16" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>33</v>
       </c>
       <c r="E12" s="131" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F12" s="81" t="str">
         <f t="shared" si="0"/>
@@ -7276,16 +7276,16 @@
     </row>
     <row r="13" spans="2:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B13" s="16" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E13" s="131" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F13" s="81" t="str">
         <f t="shared" si="0"/>
@@ -7296,16 +7296,16 @@
     </row>
     <row r="14" spans="2:8" ht="79.8" x14ac:dyDescent="0.3">
       <c r="B14" s="16" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E14" s="131" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F14" s="81" t="str">
         <f t="shared" si="0"/>
@@ -7316,13 +7316,13 @@
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B15" s="16" t="s">
+        <v>299</v>
+      </c>
+      <c r="C15" s="19" t="s">
         <v>300</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="D15" s="3" t="s">
         <v>301</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>302</v>
       </c>
       <c r="E15" s="55"/>
       <c r="F15" s="81" t="str">
@@ -7334,16 +7334,16 @@
     </row>
     <row r="16" spans="2:8" s="36" customFormat="1" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="B16" s="27" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="C16" s="28" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="D16" s="183" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="E16" s="131" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F16" s="81" t="str">
         <f t="shared" si="0"/>
@@ -7366,7 +7366,7 @@
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.3">
       <c r="G18" s="46" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H18" s="31">
         <f>AVERAGE(H7:H17)</f>

--- a/file/table/DAPC_ProyectoCAD.xlsx
+++ b/file/table/DAPC_ProyectoCAD.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E0D70E6-6294-4E99-A775-D1C41A6BD266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEBD2E19-9899-48EE-8C7C-B7431A8F1C78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0.Inicio" sheetId="7" r:id="rId1"/>
@@ -312,7 +312,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="349">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="350">
   <si>
     <t>1. Especificaciones técnicas generales</t>
   </si>
@@ -1436,6 +1436,9 @@
     <t>M01A02b</t>
   </si>
   <si>
+    <t>M01A02c</t>
+  </si>
+  <si>
     <t>Planos digitales del proyecto</t>
   </si>
   <si>
@@ -1459,9 +1462,6 @@
   </si>
   <si>
     <t>v.20250725</t>
-  </si>
-  <si>
-    <t>Los estudiantes deberán definir el nombre de su grupo de proyecto (utilice un nombre corporativo corto) y crear un logotipo en AutoCAD (guardar como /file/cad/logotipo.dwg). El código, logotipo y nombre del grupo deberán incluirse en todos los planos generados. El grupo se deberá mantener durante todo el semestre académico.</t>
   </si>
   <si>
     <r>
@@ -1521,6 +1521,9 @@
   </si>
   <si>
     <t>4a. Estantería industrial</t>
+  </si>
+  <si>
+    <t>Los estudiantes deberán definir el nombre de su grupo de proyecto (utilice un nombre corporativo corto) y crear un logotipo en AutoCAD (guardar como /file/cad/logotipo.dwg). El código, logotipo y nombre del grupo deberán incluirse en todos los planos generados. El grupo se deberá mantener durante todo el semestre académico. Incorpore en el diseño del logotipo, una de las curvas especiales vistas.</t>
   </si>
 </sst>
 </file>
@@ -3006,7 +3009,7 @@
   <sheetData>
     <row r="1" spans="2:5" x14ac:dyDescent="0.3">
       <c r="E1" s="100" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.3">
@@ -3399,7 +3402,7 @@
         <v>7</v>
       </c>
       <c r="C40" s="64" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D40" s="65"/>
       <c r="E40" s="58">
@@ -3512,12 +3515,12 @@
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="57" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:9" ht="68.400000000000006" x14ac:dyDescent="0.3">
       <c r="B7" s="127" t="s">
         <v>269</v>
       </c>
       <c r="C7" s="128" t="s">
-        <v>336</v>
+        <v>349</v>
       </c>
       <c r="D7" s="91">
         <v>1</v>
@@ -3526,7 +3529,7 @@
         <v>16</v>
       </c>
       <c r="F7" s="131" t="s">
-        <v>304</v>
+        <v>331</v>
       </c>
       <c r="G7" s="132" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F7,"/Readme.md"),"Ver")</f>
@@ -5699,7 +5702,7 @@
     </row>
     <row r="91" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B91" s="47" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="92" spans="2:9" x14ac:dyDescent="0.3">
@@ -7296,10 +7299,10 @@
     </row>
     <row r="14" spans="2:8" ht="79.8" x14ac:dyDescent="0.3">
       <c r="B14" s="16" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>295</v>

--- a/file/table/DAPC_ProyectoCAD.xlsx
+++ b/file/table/DAPC_ProyectoCAD.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEBD2E19-9899-48EE-8C7C-B7431A8F1C78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6F4EC0F-BDDA-4491-B7E1-77C934E54681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0.Inicio" sheetId="7" r:id="rId1"/>
@@ -312,7 +312,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="352">
   <si>
     <t>1. Especificaciones técnicas generales</t>
   </si>
@@ -1524,6 +1524,12 @@
   </si>
   <si>
     <t>Los estudiantes deberán definir el nombre de su grupo de proyecto (utilice un nombre corporativo corto) y crear un logotipo en AutoCAD (guardar como /file/cad/logotipo.dwg). El código, logotipo y nombre del grupo deberán incluirse en todos los planos generados. El grupo se deberá mantener durante todo el semestre académico. Incorpore en el diseño del logotipo, una de las curvas especiales vistas.</t>
+  </si>
+  <si>
+    <t>Localizados en planta y en cortes. Dibujar en 2D y 3D. Actividades M01A02b y M01A02d.</t>
+  </si>
+  <si>
+    <t>M01A02d</t>
   </si>
 </sst>
 </file>
@@ -6137,12 +6143,12 @@
       <c r="H18" s="28"/>
       <c r="I18" s="44"/>
     </row>
-    <row r="19" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B19" s="27" t="s">
         <v>342</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>199</v>
+        <v>350</v>
       </c>
       <c r="D19" s="29">
         <v>1</v>
@@ -6151,7 +6157,7 @@
         <v>115</v>
       </c>
       <c r="F19" s="87" t="s">
-        <v>330</v>
+        <v>351</v>
       </c>
       <c r="G19" s="81" t="str">
         <f t="shared" si="0"/>

--- a/file/table/DAPC_ProyectoCAD.xlsx
+++ b/file/table/DAPC_ProyectoCAD.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6F4EC0F-BDDA-4491-B7E1-77C934E54681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DFCC8B3-7AA0-45C4-85D1-EBF574D51873}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1526,10 +1526,10 @@
     <t>Los estudiantes deberán definir el nombre de su grupo de proyecto (utilice un nombre corporativo corto) y crear un logotipo en AutoCAD (guardar como /file/cad/logotipo.dwg). El código, logotipo y nombre del grupo deberán incluirse en todos los planos generados. El grupo se deberá mantener durante todo el semestre académico. Incorpore en el diseño del logotipo, una de las curvas especiales vistas.</t>
   </si>
   <si>
-    <t>Localizados en planta y en cortes. Dibujar en 2D y 3D. Actividades M01A02b y M01A02d.</t>
-  </si>
-  <si>
     <t>M01A02d</t>
+  </si>
+  <si>
+    <t>Localizados en planta y en cortes. Dibujar en 2D y 3D. Actividades M01A02b y M01A02d. Presente los elementos directriecz para la generación del elemento 3D.</t>
   </si>
 </sst>
 </file>
@@ -6143,12 +6143,12 @@
       <c r="H18" s="28"/>
       <c r="I18" s="44"/>
     </row>
-    <row r="19" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="B19" s="27" t="s">
         <v>342</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="D19" s="29">
         <v>1</v>
@@ -6157,7 +6157,7 @@
         <v>115</v>
       </c>
       <c r="F19" s="87" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="G19" s="81" t="str">
         <f t="shared" si="0"/>

--- a/file/table/DAPC_ProyectoCAD.xlsx
+++ b/file/table/DAPC_ProyectoCAD.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DFCC8B3-7AA0-45C4-85D1-EBF574D51873}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D67AA6DE-892D-444D-9C0B-37BD3FE2BB37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1529,7 +1529,7 @@
     <t>M01A02d</t>
   </si>
   <si>
-    <t>Localizados en planta y en cortes. Dibujar en 2D y 3D. Actividades M01A02b y M01A02d. Presente los elementos directriecz para la generación del elemento 3D.</t>
+    <t>Localizados en planta y en cortes. Dibujar en 2D y 3D. Actividades M01A02b y M01A02d. Presente los elementos directrices para la generación del elemento 3D.</t>
   </si>
 </sst>
 </file>

--- a/file/table/DAPC_ProyectoCAD.xlsx
+++ b/file/table/DAPC_ProyectoCAD.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D67AA6DE-892D-444D-9C0B-37BD3FE2BB37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2C97D91-FD98-4E46-A4A9-5819D50E0C17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1394,20 +1394,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">3a. Especificaciones generales y redes </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color theme="1"/>
-        <rFont val="Segoe UI Light"/>
-        <family val="2"/>
-      </rPr>
-      <t>(en este curso, no es necesario crear los planos de instalaciones hidráulicas, sanitarias y contra incendios)</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t>3b. Energía solar</t>
     </r>
     <r>
@@ -1530,6 +1516,20 @@
   </si>
   <si>
     <t>Localizados en planta y en cortes. Dibujar en 2D y 3D. Actividades M01A02b y M01A02d. Presente los elementos directrices para la generación del elemento 3D.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">3a. Especificaciones generales y redes o instalaciones </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Light"/>
+        <family val="2"/>
+      </rPr>
+      <t>(en este curso, no es necesario crear los planos de instalaciones hidráulicas, sanitarias y contra incendios)</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -3015,7 +3015,7 @@
   <sheetData>
     <row r="1" spans="2:5" x14ac:dyDescent="0.3">
       <c r="E1" s="100" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.3">
@@ -3025,7 +3025,7 @@
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B3" s="101" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.3">
@@ -3408,7 +3408,7 @@
         <v>7</v>
       </c>
       <c r="C40" s="64" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D40" s="65"/>
       <c r="E40" s="58">
@@ -3526,7 +3526,7 @@
         <v>269</v>
       </c>
       <c r="C7" s="128" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="D7" s="91">
         <v>1</v>
@@ -3535,7 +3535,7 @@
         <v>16</v>
       </c>
       <c r="F7" s="131" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G7" s="132" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F7,"/Readme.md"),"Ver")</f>
@@ -4484,7 +4484,7 @@
         <v>53</v>
       </c>
       <c r="F33" s="131" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G33" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4508,7 +4508,7 @@
         <v>115</v>
       </c>
       <c r="F34" s="131" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G34" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4531,7 +4531,7 @@
         <v>63</v>
       </c>
       <c r="F35" s="131" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G35" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4545,7 +4545,7 @@
         <v>80</v>
       </c>
       <c r="C36" s="128" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D36" s="130">
         <f>D35*D35/(1000*1000)</f>
@@ -4555,7 +4555,7 @@
         <v>54</v>
       </c>
       <c r="F36" s="131" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G36" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4579,7 +4579,7 @@
         <v>54</v>
       </c>
       <c r="F37" s="131" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G37" s="132" t="str">
         <f t="shared" si="0"/>
@@ -4603,7 +4603,7 @@
     </row>
     <row r="39" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B39" s="156" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C39" s="147"/>
       <c r="D39" s="148"/>
@@ -4615,7 +4615,7 @@
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B40" s="127" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="C40" s="128" t="s">
         <v>86</v>
@@ -4666,7 +4666,7 @@
         <v>84</v>
       </c>
       <c r="C42" s="128" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D42" s="130">
         <f>D11+(INT(D11/D41)*D10)</f>
@@ -5123,7 +5123,7 @@
         <v>55</v>
       </c>
       <c r="F63" s="131" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G63" s="132" t="str">
         <f t="shared" si="0"/>
@@ -5136,7 +5136,7 @@
     </row>
     <row r="64" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B64" s="127" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C64" s="128" t="s">
         <v>166</v>
@@ -5149,7 +5149,7 @@
         <v>54</v>
       </c>
       <c r="F64" s="131" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G64" s="132" t="str">
         <f t="shared" si="0"/>
@@ -5172,7 +5172,7 @@
         <v>55</v>
       </c>
       <c r="F65" s="131" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G65" s="132" t="str">
         <f t="shared" si="0"/>
@@ -5195,7 +5195,7 @@
         <v>53</v>
       </c>
       <c r="F66" s="131" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G66" s="132" t="str">
         <f t="shared" si="0"/>
@@ -5219,7 +5219,7 @@
         <v>115</v>
       </c>
       <c r="F67" s="131" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G67" s="132" t="str">
         <f t="shared" si="0"/>
@@ -5243,7 +5243,7 @@
         <v>115</v>
       </c>
       <c r="F68" s="131" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G68" s="132" t="str">
         <f t="shared" si="0"/>
@@ -5267,7 +5267,7 @@
         <v>115</v>
       </c>
       <c r="F69" s="131" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G69" s="132" t="str">
         <f t="shared" si="0"/>
@@ -5281,7 +5281,7 @@
         <v>105</v>
       </c>
       <c r="C70" s="128" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D70" s="129">
         <v>0.25</v>
@@ -5290,7 +5290,7 @@
         <v>53</v>
       </c>
       <c r="F70" s="131" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G70" s="132" t="str">
         <f t="shared" si="0"/>
@@ -5313,7 +5313,7 @@
         <v>53</v>
       </c>
       <c r="F71" s="131" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G71" s="132" t="str">
         <f t="shared" si="0"/>
@@ -5336,7 +5336,7 @@
         <v>53</v>
       </c>
       <c r="F72" s="131" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G72" s="132" t="str">
         <f t="shared" si="0"/>
@@ -5359,7 +5359,7 @@
         <v>53</v>
       </c>
       <c r="F73" s="131" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G73" s="132" t="str">
         <f t="shared" ref="G73:G76" si="1">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F73,"/Readme.md"),"Ver")</f>
@@ -5383,7 +5383,7 @@
         <v>53</v>
       </c>
       <c r="F74" s="131" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G74" s="132" t="str">
         <f t="shared" si="1"/>
@@ -5407,7 +5407,7 @@
         <v>53</v>
       </c>
       <c r="F75" s="131" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G75" s="132" t="str">
         <f t="shared" si="1"/>
@@ -5456,7 +5456,7 @@
         <v>54</v>
       </c>
       <c r="F78" s="131" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G78" s="132" t="str">
         <f t="shared" ref="G78:G88" si="2">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F78,"/Readme.md"),"Ver")</f>
@@ -5480,7 +5480,7 @@
         <v>171</v>
       </c>
       <c r="F79" s="131" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G79" s="132" t="str">
         <f t="shared" si="2"/>
@@ -5504,7 +5504,7 @@
         <v>54</v>
       </c>
       <c r="F80" s="131" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G80" s="132" t="str">
         <f t="shared" si="2"/>
@@ -5528,7 +5528,7 @@
         <v>115</v>
       </c>
       <c r="F81" s="131" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G81" s="132" t="str">
         <f t="shared" si="2"/>
@@ -5552,7 +5552,7 @@
         <v>53</v>
       </c>
       <c r="F82" s="131" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G82" s="132" t="str">
         <f t="shared" si="2"/>
@@ -5576,7 +5576,7 @@
         <v>53</v>
       </c>
       <c r="F83" s="131" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G83" s="132" t="str">
         <f t="shared" si="2"/>
@@ -5599,7 +5599,7 @@
         <v>54</v>
       </c>
       <c r="F84" s="131" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G84" s="132" t="str">
         <f t="shared" si="2"/>
@@ -5624,7 +5624,7 @@
         <v>115</v>
       </c>
       <c r="F85" s="131" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G85" s="132" t="str">
         <f t="shared" si="2"/>
@@ -5647,7 +5647,7 @@
         <v>115</v>
       </c>
       <c r="F86" s="131" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G86" s="132" t="str">
         <f t="shared" si="2"/>
@@ -5670,7 +5670,7 @@
         <v>115</v>
       </c>
       <c r="F87" s="131" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G87" s="132" t="str">
         <f t="shared" si="2"/>
@@ -5708,7 +5708,7 @@
     </row>
     <row r="91" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B91" s="47" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="92" spans="2:9" x14ac:dyDescent="0.3">
@@ -5878,7 +5878,7 @@
     </row>
     <row r="7" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B7" s="5" t="s">
-        <v>324</v>
+        <v>351</v>
       </c>
       <c r="C7" s="17"/>
       <c r="D7" s="18"/>
@@ -5902,7 +5902,7 @@
         <v>115</v>
       </c>
       <c r="F8" s="87" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G8" s="81" t="str">
         <f t="shared" ref="G8:G21" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F8,"/Readme.md"),"Ver")</f>
@@ -5927,7 +5927,7 @@
         <v>115</v>
       </c>
       <c r="F9" s="87" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G9" s="81" t="str">
         <f t="shared" si="0"/>
@@ -5950,7 +5950,7 @@
         <v>115</v>
       </c>
       <c r="F10" s="87" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G10" s="81" t="str">
         <f t="shared" si="0"/>
@@ -5973,7 +5973,7 @@
         <v>115</v>
       </c>
       <c r="F11" s="87" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G11" s="81" t="str">
         <f t="shared" si="0"/>
@@ -5996,7 +5996,7 @@
         <v>115</v>
       </c>
       <c r="F12" s="87" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G12" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6019,7 +6019,7 @@
         <v>115</v>
       </c>
       <c r="F13" s="87" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G13" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6145,10 +6145,10 @@
     </row>
     <row r="19" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="B19" s="27" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D19" s="29">
         <v>1</v>
@@ -6157,7 +6157,7 @@
         <v>115</v>
       </c>
       <c r="F19" s="87" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="G19" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6180,7 +6180,7 @@
         <v>115</v>
       </c>
       <c r="F20" s="87" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G20" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6204,7 +6204,7 @@
     </row>
     <row r="22" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B22" s="5" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C22" s="17"/>
       <c r="D22" s="18"/>
@@ -6420,7 +6420,7 @@
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B7" s="5" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C7" s="17"/>
       <c r="D7" s="18"/>
@@ -6444,7 +6444,7 @@
         <v>53</v>
       </c>
       <c r="F8" s="87" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G8" s="81" t="str">
         <f t="shared" ref="G8:G21" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F8,"/Readme.md"),"Ver")</f>
@@ -6469,7 +6469,7 @@
         <v>53</v>
       </c>
       <c r="F9" s="87" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G9" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6492,7 +6492,7 @@
         <v>226</v>
       </c>
       <c r="F10" s="87" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G10" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6515,7 +6515,7 @@
         <v>53</v>
       </c>
       <c r="F11" s="87" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G11" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6539,7 +6539,7 @@
         <v>53</v>
       </c>
       <c r="F12" s="87" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G12" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6562,7 +6562,7 @@
         <v>53</v>
       </c>
       <c r="F13" s="87" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G13" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6586,7 +6586,7 @@
         <v>239</v>
       </c>
       <c r="F14" s="87" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G14" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6609,7 +6609,7 @@
         <v>53</v>
       </c>
       <c r="F15" s="87" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G15" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6633,7 +6633,7 @@
         <v>53</v>
       </c>
       <c r="F16" s="87" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G16" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6657,7 +6657,7 @@
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B18" s="5" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C18" s="17"/>
       <c r="D18" s="18"/>
@@ -6681,7 +6681,7 @@
         <v>115</v>
       </c>
       <c r="F19" s="87" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G19" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6706,7 +6706,7 @@
         <v>115</v>
       </c>
       <c r="F20" s="87" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G20" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6729,7 +6729,7 @@
         <v>115</v>
       </c>
       <c r="F21" s="87" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="G21" s="81" t="str">
         <f t="shared" si="0"/>
@@ -6791,7 +6791,7 @@
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B3" s="9" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.4">
@@ -7111,7 +7111,7 @@
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B3" s="80" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="C3" s="80"/>
       <c r="D3" s="80"/>
@@ -7122,7 +7122,7 @@
     </row>
     <row r="4" spans="2:8" s="36" customFormat="1" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="74" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C4" s="74"/>
       <c r="D4" s="74"/>
@@ -7305,10 +7305,10 @@
     </row>
     <row r="14" spans="2:8" ht="79.8" x14ac:dyDescent="0.3">
       <c r="B14" s="16" t="s">
+        <v>331</v>
+      </c>
+      <c r="C14" s="19" t="s">
         <v>332</v>
-      </c>
-      <c r="C14" s="19" t="s">
-        <v>333</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>295</v>
@@ -7343,13 +7343,13 @@
     </row>
     <row r="16" spans="2:8" s="36" customFormat="1" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="B16" s="27" t="s">
+        <v>343</v>
+      </c>
+      <c r="C16" s="28" t="s">
         <v>344</v>
       </c>
-      <c r="C16" s="28" t="s">
-        <v>345</v>
-      </c>
       <c r="D16" s="183" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="E16" s="131" t="s">
         <v>307</v>

--- a/file/table/DAPC_ProyectoCAD.xlsx
+++ b/file/table/DAPC_ProyectoCAD.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2C97D91-FD98-4E46-A4A9-5819D50E0C17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4EB6E26-1BF2-4562-B01D-7EF0F9663201}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -312,7 +312,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="352">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="380">
   <si>
     <t>1. Especificaciones técnicas generales</t>
   </si>
@@ -986,9 +986,6 @@
     <t>Localizados en planta y en cortes.</t>
   </si>
   <si>
-    <t>Red foto-voltáica</t>
-  </si>
-  <si>
     <t>Área disponible en cubierta</t>
   </si>
   <si>
@@ -1019,18 +1016,6 @@
     <t>Acometida eléctrica</t>
   </si>
   <si>
-    <t>Red eléctrica interna 220v</t>
-  </si>
-  <si>
-    <t>Red eléctrica interna 110v</t>
-  </si>
-  <si>
-    <t>Red de datos usando cableado</t>
-  </si>
-  <si>
-    <t>Red vigilancia</t>
-  </si>
-  <si>
     <t>Esquema solo en planta. Redes eléctricas internas.</t>
   </si>
   <si>
@@ -1158,9 +1143,6 @@
   </si>
   <si>
     <t>Plano de red foto-voltáica</t>
-  </si>
-  <si>
-    <t>Plano de red vigilancia</t>
   </si>
   <si>
     <t>Cámaras de vigilancia</t>
@@ -1225,9 +1207,6 @@
   </si>
   <si>
     <t>Crear estilos propios fijos y anotativos para las diferentes escalas de impresión a usar, utilizar el prefijo DAPC.</t>
-  </si>
-  <si>
-    <t>A0 / A4, horizontal y vertical. Formatos adicionales pueden ser incluídos en la plantilla.</t>
   </si>
   <si>
     <t>Bloques - arquitectónicos</t>
@@ -1483,9 +1462,6 @@
     <t>/file/cad/DAPC_AIALayerName.xlsx</t>
   </si>
   <si>
-    <t>Layers</t>
-  </si>
-  <si>
     <t>Nombres y configuraciones de capas o Layers en AutoCAD. Investigue que colores y grosores pueden ser aplicados en las disciplinas a utilizar en el curso y complete el catálogo suministrado.</t>
   </si>
   <si>
@@ -1531,12 +1507,120 @@
       <t>(en este curso, no es necesario crear los planos de instalaciones hidráulicas, sanitarias y contra incendios)</t>
     </r>
   </si>
+  <si>
+    <t>ISO-A0 / ISO-A4, horizontal y vertical. Formatos adicionales pueden ser incluídos en la plantilla.</t>
+  </si>
+  <si>
+    <t>Plano de red vigilancia o seguridad</t>
+  </si>
+  <si>
+    <t>Capas o layers</t>
+  </si>
+  <si>
+    <t>Red eléctrica interna 110v*</t>
+  </si>
+  <si>
+    <t>Red eléctrica interna 220v*</t>
+  </si>
+  <si>
+    <t>Red de datos usando cableado*</t>
+  </si>
+  <si>
+    <t>Red foto-voltáica*</t>
+  </si>
+  <si>
+    <t>Red vigilancia*</t>
+  </si>
+  <si>
+    <t>* Incluya notas descriptivas de localización del conducto, tubería o canaleta, utilice los siguientes códigos:</t>
+  </si>
+  <si>
+    <t>tpp</t>
+  </si>
+  <si>
+    <t>tpc</t>
+  </si>
+  <si>
+    <t>tpm</t>
+  </si>
+  <si>
+    <t>td</t>
+  </si>
+  <si>
+    <t>Nota</t>
+  </si>
+  <si>
+    <t>Descripción</t>
+  </si>
+  <si>
+    <t>Por placa o piso</t>
+  </si>
+  <si>
+    <t>Por cielorraso, anclada o descolgada</t>
+  </si>
+  <si>
+    <t>Por muro</t>
+  </si>
+  <si>
+    <t>Descolgada sin cielorraso</t>
+  </si>
+  <si>
+    <t>* Seguido de la nota descriptva de localización, indique el material, utilice los siguientes códigos:</t>
+  </si>
+  <si>
+    <t>PVC</t>
+  </si>
+  <si>
+    <t>Aluminio</t>
+  </si>
+  <si>
+    <t>Metálica en aluminio</t>
+  </si>
+  <si>
+    <t>Plástica en policloruro de vinilo.</t>
+  </si>
+  <si>
+    <t>Polietileno</t>
+  </si>
+  <si>
+    <t>Fibra de vidrio</t>
+  </si>
+  <si>
+    <t>Polipropileno o nylon</t>
+  </si>
+  <si>
+    <t>Resistente a alta temperatura</t>
+  </si>
+  <si>
+    <t>Acero Galv.</t>
+  </si>
+  <si>
+    <t>Acero IMC</t>
+  </si>
+  <si>
+    <t>Acero EMT</t>
+  </si>
+  <si>
+    <t>Metálica en acero galvanizado.</t>
+  </si>
+  <si>
+    <t>Metálica en acero intermedio con resistencia mecánica.</t>
+  </si>
+  <si>
+    <t>Metálica en acero EMT con baja resistencia mecánica.</t>
+  </si>
+  <si>
+    <t>Polímero termoplástico.</t>
+  </si>
+  <si>
+    <t>Hebras de vidrio entrelazadas.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1618,13 +1702,6 @@
       <color theme="1"/>
       <name val="Segoe UI Light"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
@@ -2119,7 +2196,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="186">
+  <cellXfs count="191">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2233,9 +2310,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
@@ -2284,7 +2358,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2295,6 +2368,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -2364,10 +2440,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2402,7 +2478,7 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -2410,7 +2486,7 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -2418,7 +2494,7 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
@@ -2526,7 +2602,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -2550,7 +2626,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
@@ -2688,6 +2764,18 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -3005,147 +3093,147 @@
   <dimension ref="B1:E41"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="2.5546875" style="47" customWidth="1"/>
-    <col min="3" max="3" width="50.77734375" style="47" customWidth="1"/>
-    <col min="4" max="4" width="15.77734375" style="47" customWidth="1"/>
-    <col min="5" max="5" width="12.77734375" style="47" customWidth="1"/>
-    <col min="6" max="6" width="2.5546875" style="47" customWidth="1"/>
-    <col min="7" max="16384" width="9.109375" style="47"/>
+    <col min="1" max="2" width="2.5546875" style="46" customWidth="1"/>
+    <col min="3" max="3" width="50.77734375" style="46" customWidth="1"/>
+    <col min="4" max="4" width="15.77734375" style="46" customWidth="1"/>
+    <col min="5" max="5" width="12.77734375" style="46" customWidth="1"/>
+    <col min="6" max="6" width="2.5546875" style="46" customWidth="1"/>
+    <col min="7" max="16384" width="9.109375" style="46"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="E1" s="100" t="s">
-        <v>335</v>
+      <c r="E1" s="99" t="s">
+        <v>328</v>
       </c>
     </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="46" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B3" s="101" t="s">
-        <v>328</v>
+      <c r="B3" s="100" t="s">
+        <v>321</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B4" s="102" t="s">
+      <c r="B4" s="101" t="s">
         <v>35</v>
       </c>
-      <c r="C4" s="102"/>
-      <c r="D4" s="102"/>
-      <c r="E4" s="102"/>
+      <c r="C4" s="101"/>
+      <c r="D4" s="101"/>
+      <c r="E4" s="101"/>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B5" s="102"/>
-      <c r="C5" s="102"/>
-      <c r="D5" s="102"/>
-      <c r="E5" s="102"/>
+      <c r="B5" s="101"/>
+      <c r="C5" s="101"/>
+      <c r="D5" s="101"/>
+      <c r="E5" s="101"/>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B6" s="102"/>
-      <c r="C6" s="102"/>
-      <c r="D6" s="102"/>
-      <c r="E6" s="102"/>
+      <c r="B6" s="101"/>
+      <c r="C6" s="101"/>
+      <c r="D6" s="101"/>
+      <c r="E6" s="101"/>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B7" s="103" t="s">
+      <c r="B7" s="102" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="104"/>
-      <c r="D7" s="104"/>
-      <c r="E7" s="105"/>
+      <c r="C7" s="103"/>
+      <c r="D7" s="103"/>
+      <c r="E7" s="104"/>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="66" t="s">
+      <c r="B8" s="65" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="67"/>
-      <c r="D8" s="67"/>
-      <c r="E8" s="68"/>
+      <c r="C8" s="66"/>
+      <c r="D8" s="66"/>
+      <c r="E8" s="67"/>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="106" t="s">
+      <c r="B9" s="105" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="107"/>
-      <c r="D9" s="107"/>
-      <c r="E9" s="108"/>
+      <c r="C9" s="106"/>
+      <c r="D9" s="106"/>
+      <c r="E9" s="107"/>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="66" t="s">
+      <c r="B10" s="65" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="67"/>
-      <c r="D10" s="67"/>
-      <c r="E10" s="68"/>
+      <c r="C10" s="66"/>
+      <c r="D10" s="66"/>
+      <c r="E10" s="67"/>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B11" s="69"/>
-      <c r="C11" s="70"/>
-      <c r="D11" s="70"/>
-      <c r="E11" s="71"/>
+      <c r="B11" s="68"/>
+      <c r="C11" s="69"/>
+      <c r="D11" s="69"/>
+      <c r="E11" s="70"/>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B12" s="106" t="s">
+      <c r="B12" s="105" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="107"/>
-      <c r="D12" s="107"/>
-      <c r="E12" s="108"/>
+      <c r="C12" s="106"/>
+      <c r="D12" s="106"/>
+      <c r="E12" s="107"/>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="66" t="s">
+      <c r="B13" s="65" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="67"/>
-      <c r="D13" s="67"/>
-      <c r="E13" s="68"/>
+      <c r="C13" s="66"/>
+      <c r="D13" s="66"/>
+      <c r="E13" s="67"/>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B14" s="69"/>
-      <c r="C14" s="70"/>
-      <c r="D14" s="70"/>
-      <c r="E14" s="71"/>
+      <c r="B14" s="68"/>
+      <c r="C14" s="69"/>
+      <c r="D14" s="69"/>
+      <c r="E14" s="70"/>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B15" s="109" t="s">
+      <c r="B15" s="108" t="s">
         <v>21</v>
       </c>
-      <c r="C15" s="109"/>
-      <c r="D15" s="109"/>
-      <c r="E15" s="109"/>
+      <c r="C15" s="108"/>
+      <c r="D15" s="108"/>
+      <c r="E15" s="108"/>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B16" s="110"/>
-      <c r="C16" s="110"/>
-      <c r="D16" s="110"/>
-      <c r="E16" s="110"/>
+      <c r="B16" s="109"/>
+      <c r="C16" s="109"/>
+      <c r="D16" s="109"/>
+      <c r="E16" s="109"/>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B17" s="73" t="s">
+      <c r="B17" s="72" t="s">
         <v>14</v>
       </c>
-      <c r="C17" s="73"/>
-      <c r="D17" s="73"/>
-      <c r="E17" s="73"/>
+      <c r="C17" s="72"/>
+      <c r="D17" s="72"/>
+      <c r="E17" s="72"/>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B18" s="48" t="s">
+      <c r="B18" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="111" t="s">
+      <c r="C18" s="110" t="s">
         <v>29</v>
       </c>
-      <c r="D18" s="112" t="s">
+      <c r="D18" s="111" t="s">
         <v>28</v>
       </c>
-      <c r="E18" s="49" t="s">
+      <c r="E18" s="48" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B19" s="113">
+      <c r="B19" s="112">
         <v>1</v>
       </c>
       <c r="C19" s="34" t="s">
@@ -3154,13 +3242,13 @@
       <c r="D19" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="E19" s="114">
+      <c r="E19" s="113">
         <f t="shared" ref="E19:E28" si="0">IFERROR(RIGHT(D19,1)*1,0)</f>
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="113">
+      <c r="B20" s="112">
         <v>2</v>
       </c>
       <c r="C20" s="34" t="s">
@@ -3169,13 +3257,13 @@
       <c r="D20" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="E20" s="114">
+      <c r="E20" s="113">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B21" s="113">
+      <c r="B21" s="112">
         <v>3</v>
       </c>
       <c r="C21" s="34" t="s">
@@ -3184,13 +3272,13 @@
       <c r="D21" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="E21" s="114">
+      <c r="E21" s="113">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="113">
+      <c r="B22" s="112">
         <v>4</v>
       </c>
       <c r="C22" s="34" t="s">
@@ -3199,13 +3287,13 @@
       <c r="D22" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="E22" s="114">
+      <c r="E22" s="113">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B23" s="113">
+      <c r="B23" s="112">
         <v>5</v>
       </c>
       <c r="C23" s="34" t="s">
@@ -3214,212 +3302,212 @@
       <c r="D23" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E23" s="114">
+      <c r="E23" s="113">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B24" s="113">
+      <c r="B24" s="112">
         <v>6</v>
       </c>
       <c r="C24" s="34" t="s">
         <v>8</v>
       </c>
       <c r="D24" s="13"/>
-      <c r="E24" s="114">
+      <c r="E24" s="113">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B25" s="113">
+      <c r="B25" s="112">
         <v>7</v>
       </c>
       <c r="C25" s="34" t="s">
         <v>8</v>
       </c>
       <c r="D25" s="13"/>
-      <c r="E25" s="114">
+      <c r="E25" s="113">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B26" s="113">
+      <c r="B26" s="112">
         <v>8</v>
       </c>
       <c r="C26" s="34" t="s">
         <v>8</v>
       </c>
       <c r="D26" s="13"/>
-      <c r="E26" s="114">
+      <c r="E26" s="113">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B27" s="113">
+      <c r="B27" s="112">
         <v>9</v>
       </c>
       <c r="C27" s="34" t="s">
         <v>8</v>
       </c>
       <c r="D27" s="13"/>
-      <c r="E27" s="114">
+      <c r="E27" s="113">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B28" s="115">
+      <c r="B28" s="114">
         <v>10</v>
       </c>
       <c r="C28" s="35" t="s">
         <v>8</v>
       </c>
       <c r="D28" s="14"/>
-      <c r="E28" s="116">
+      <c r="E28" s="115">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="D29" s="117" t="s">
+      <c r="D29" s="116" t="s">
         <v>11</v>
       </c>
-      <c r="E29" s="59">
+      <c r="E29" s="57">
         <f>SUM(E19:E28)</f>
         <v>27</v>
       </c>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B31" s="73" t="s">
-        <v>263</v>
-      </c>
-      <c r="C31" s="73"/>
-      <c r="D31" s="73"/>
-      <c r="E31" s="73"/>
+      <c r="B31" s="72" t="s">
+        <v>257</v>
+      </c>
+      <c r="C31" s="72"/>
+      <c r="D31" s="72"/>
+      <c r="E31" s="72"/>
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B32" s="48" t="s">
+      <c r="B32" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="75" t="s">
+      <c r="C32" s="74" t="s">
         <v>36</v>
       </c>
-      <c r="D32" s="76"/>
-      <c r="E32" s="49" t="s">
+      <c r="D32" s="75"/>
+      <c r="E32" s="48" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B33" s="50">
+      <c r="B33" s="49">
         <v>1</v>
       </c>
-      <c r="C33" s="77" t="s">
-        <v>264</v>
-      </c>
-      <c r="D33" s="78"/>
-      <c r="E33" s="51">
+      <c r="C33" s="76" t="s">
+        <v>258</v>
+      </c>
+      <c r="D33" s="77"/>
+      <c r="E33" s="50">
         <f>'1.Tecnica'!I19</f>
         <v>5</v>
       </c>
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B34" s="50">
+      <c r="B34" s="49">
         <v>2</v>
       </c>
-      <c r="C34" s="62" t="s">
-        <v>303</v>
-      </c>
-      <c r="D34" s="63"/>
-      <c r="E34" s="51">
+      <c r="C34" s="61" t="s">
+        <v>296</v>
+      </c>
+      <c r="D34" s="62"/>
+      <c r="E34" s="50">
         <f>'1.Tecnica'!I19</f>
         <v>5</v>
       </c>
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B35" s="50">
+      <c r="B35" s="49">
         <v>3</v>
       </c>
-      <c r="C35" s="62" t="s">
-        <v>265</v>
-      </c>
-      <c r="D35" s="63"/>
-      <c r="E35" s="51">
+      <c r="C35" s="61" t="s">
+        <v>259</v>
+      </c>
+      <c r="D35" s="62"/>
+      <c r="E35" s="50">
         <f>'3.Electrica'!I28</f>
         <v>5</v>
       </c>
     </row>
     <row r="36" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B36" s="50">
+      <c r="B36" s="49">
         <v>4</v>
       </c>
-      <c r="C36" s="60" t="s">
-        <v>302</v>
-      </c>
-      <c r="D36" s="61"/>
-      <c r="E36" s="51">
+      <c r="C36" s="59" t="s">
+        <v>295</v>
+      </c>
+      <c r="D36" s="60"/>
+      <c r="E36" s="50">
         <f>'4.Bodegaje'!I23</f>
         <v>5</v>
       </c>
     </row>
     <row r="37" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B37" s="50">
+      <c r="B37" s="49">
         <v>4</v>
       </c>
-      <c r="C37" s="62" t="s">
-        <v>266</v>
-      </c>
-      <c r="D37" s="63"/>
-      <c r="E37" s="51">
+      <c r="C37" s="61" t="s">
+        <v>260</v>
+      </c>
+      <c r="D37" s="62"/>
+      <c r="E37" s="50">
         <f>'5.Planos'!I17</f>
         <v>5</v>
       </c>
     </row>
     <row r="38" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B38" s="50">
+      <c r="B38" s="49">
         <v>5</v>
       </c>
-      <c r="C38" s="62" t="s">
-        <v>267</v>
-      </c>
-      <c r="D38" s="63"/>
-      <c r="E38" s="51">
+      <c r="C38" s="61" t="s">
+        <v>261</v>
+      </c>
+      <c r="D38" s="62"/>
+      <c r="E38" s="50">
         <f>'6.Archivos'!H18</f>
         <v>5</v>
       </c>
     </row>
     <row r="39" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B39" s="50">
+      <c r="B39" s="49">
         <v>6</v>
       </c>
-      <c r="C39" s="62" t="s">
-        <v>292</v>
-      </c>
-      <c r="D39" s="63"/>
-      <c r="E39" s="99">
+      <c r="C39" s="61" t="s">
+        <v>285</v>
+      </c>
+      <c r="D39" s="62"/>
+      <c r="E39" s="98">
         <v>5</v>
       </c>
     </row>
     <row r="40" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B40" s="52">
+      <c r="B40" s="51">
         <v>7</v>
       </c>
-      <c r="C40" s="64" t="s">
-        <v>334</v>
-      </c>
-      <c r="D40" s="65"/>
-      <c r="E40" s="58">
+      <c r="C40" s="63" t="s">
+        <v>327</v>
+      </c>
+      <c r="D40" s="64"/>
+      <c r="E40" s="56">
         <v>5</v>
       </c>
     </row>
     <row r="41" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="D41" s="118" t="s">
-        <v>270</v>
-      </c>
-      <c r="E41" s="59">
+      <c r="D41" s="117" t="s">
+        <v>264</v>
+      </c>
+      <c r="E41" s="57">
         <f>AVERAGE(E33:E40)</f>
         <v>5</v>
       </c>
@@ -3458,332 +3546,332 @@
   <dimension ref="B1:I19"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.5546875" style="47" customWidth="1"/>
-    <col min="2" max="2" width="30.77734375" style="47" customWidth="1"/>
-    <col min="3" max="3" width="50.77734375" style="47" customWidth="1"/>
-    <col min="4" max="5" width="10.77734375" style="47" customWidth="1"/>
-    <col min="6" max="6" width="7.77734375" style="47" customWidth="1"/>
-    <col min="7" max="7" width="3.77734375" style="47" customWidth="1"/>
-    <col min="8" max="8" width="30.77734375" style="119" customWidth="1"/>
-    <col min="9" max="9" width="12.77734375" style="120" customWidth="1"/>
-    <col min="10" max="10" width="2.77734375" style="47" customWidth="1"/>
-    <col min="11" max="16384" width="9.109375" style="47"/>
+    <col min="1" max="1" width="2.5546875" style="46" customWidth="1"/>
+    <col min="2" max="2" width="30.77734375" style="46" customWidth="1"/>
+    <col min="3" max="3" width="50.77734375" style="46" customWidth="1"/>
+    <col min="4" max="5" width="10.77734375" style="46" customWidth="1"/>
+    <col min="6" max="6" width="7.77734375" style="46" customWidth="1"/>
+    <col min="7" max="7" width="3.77734375" style="46" customWidth="1"/>
+    <col min="8" max="8" width="30.77734375" style="118" customWidth="1"/>
+    <col min="9" max="9" width="12.77734375" style="119" customWidth="1"/>
+    <col min="10" max="10" width="2.77734375" style="46" customWidth="1"/>
+    <col min="11" max="16384" width="9.109375" style="46"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="E1" s="100"/>
+      <c r="E1" s="99"/>
     </row>
     <row r="2" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="46" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B3" s="101" t="s">
+      <c r="B3" s="100" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B4" s="102" t="s">
+      <c r="B4" s="101" t="s">
+        <v>262</v>
+      </c>
+      <c r="C4" s="101"/>
+      <c r="D4" s="101"/>
+      <c r="E4" s="101"/>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B5" s="101"/>
+      <c r="C5" s="101"/>
+      <c r="D5" s="101"/>
+      <c r="E5" s="101"/>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B6" s="120" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="121" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="122" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" s="122" t="s">
+        <v>49</v>
+      </c>
+      <c r="F6" s="123" t="s">
+        <v>38</v>
+      </c>
+      <c r="G6" s="124"/>
+      <c r="H6" s="121" t="s">
+        <v>26</v>
+      </c>
+      <c r="I6" s="125" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" ht="68.400000000000006" x14ac:dyDescent="0.3">
+      <c r="B7" s="126" t="s">
+        <v>263</v>
+      </c>
+      <c r="C7" s="127" t="s">
+        <v>340</v>
+      </c>
+      <c r="D7" s="90">
+        <v>1</v>
+      </c>
+      <c r="E7" s="129" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="130" t="s">
+        <v>323</v>
+      </c>
+      <c r="G7" s="131" t="str">
+        <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F7,"/Readme.md"),"Ver")</f>
+        <v>Ver</v>
+      </c>
+      <c r="H7" s="92"/>
+      <c r="I7" s="93">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="B8" s="126" t="s">
+        <v>267</v>
+      </c>
+      <c r="C8" s="127" t="s">
+        <v>307</v>
+      </c>
+      <c r="D8" s="90">
+        <v>1</v>
+      </c>
+      <c r="E8" s="129" t="s">
+        <v>308</v>
+      </c>
+      <c r="F8" s="130" t="s">
+        <v>297</v>
+      </c>
+      <c r="G8" s="131" t="str">
+        <f t="shared" ref="G8:G18" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F8,"/Readme.md"),"Ver")</f>
+        <v>Ver</v>
+      </c>
+      <c r="H8" s="92"/>
+      <c r="I8" s="93"/>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B9" s="126" t="s">
+        <v>265</v>
+      </c>
+      <c r="C9" s="127" t="s">
+        <v>266</v>
+      </c>
+      <c r="D9" s="90" t="s">
+        <v>309</v>
+      </c>
+      <c r="E9" s="129"/>
+      <c r="F9" s="130" t="s">
+        <v>297</v>
+      </c>
+      <c r="G9" s="131" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H9" s="92"/>
+      <c r="I9" s="93"/>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B10" s="126" t="s">
+        <v>269</v>
+      </c>
+      <c r="C10" s="127" t="s">
+        <v>270</v>
+      </c>
+      <c r="D10" s="90">
+        <v>1</v>
+      </c>
+      <c r="E10" s="129" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" s="130" t="s">
+        <v>298</v>
+      </c>
+      <c r="G10" s="131" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H10" s="92"/>
+      <c r="I10" s="93"/>
+    </row>
+    <row r="11" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="B11" s="126" t="s">
         <v>268</v>
       </c>
-      <c r="C4" s="102"/>
-      <c r="D4" s="102"/>
-      <c r="E4" s="102"/>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B5" s="102"/>
-      <c r="C5" s="102"/>
-      <c r="D5" s="102"/>
-      <c r="E5" s="102"/>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B6" s="121" t="s">
-        <v>36</v>
-      </c>
-      <c r="C6" s="122" t="s">
-        <v>37</v>
-      </c>
-      <c r="D6" s="123" t="s">
-        <v>48</v>
-      </c>
-      <c r="E6" s="123" t="s">
-        <v>49</v>
-      </c>
-      <c r="F6" s="124" t="s">
-        <v>38</v>
-      </c>
-      <c r="G6" s="125"/>
-      <c r="H6" s="122" t="s">
-        <v>26</v>
-      </c>
-      <c r="I6" s="126" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" ht="68.400000000000006" x14ac:dyDescent="0.3">
-      <c r="B7" s="127" t="s">
-        <v>269</v>
-      </c>
-      <c r="C7" s="128" t="s">
-        <v>348</v>
-      </c>
-      <c r="D7" s="91">
+      <c r="C11" s="127" t="s">
+        <v>271</v>
+      </c>
+      <c r="D11" s="90" t="s">
+        <v>309</v>
+      </c>
+      <c r="E11" s="129"/>
+      <c r="F11" s="130" t="s">
+        <v>299</v>
+      </c>
+      <c r="G11" s="131" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H11" s="92"/>
+      <c r="I11" s="93"/>
+    </row>
+    <row r="12" spans="2:9" ht="57" x14ac:dyDescent="0.3">
+      <c r="B12" s="126" t="s">
+        <v>277</v>
+      </c>
+      <c r="C12" s="127" t="s">
+        <v>272</v>
+      </c>
+      <c r="D12" s="90" t="s">
+        <v>309</v>
+      </c>
+      <c r="E12" s="129"/>
+      <c r="F12" s="130" t="s">
+        <v>300</v>
+      </c>
+      <c r="G12" s="131" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H12" s="92"/>
+      <c r="I12" s="93"/>
+    </row>
+    <row r="13" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="B13" s="126" t="s">
+        <v>278</v>
+      </c>
+      <c r="C13" s="127" t="s">
+        <v>273</v>
+      </c>
+      <c r="D13" s="90" t="s">
+        <v>309</v>
+      </c>
+      <c r="E13" s="129"/>
+      <c r="F13" s="130" t="s">
+        <v>301</v>
+      </c>
+      <c r="G13" s="131" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H13" s="92"/>
+      <c r="I13" s="93"/>
+    </row>
+    <row r="14" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="B14" s="126" t="s">
+        <v>279</v>
+      </c>
+      <c r="C14" s="127" t="s">
+        <v>344</v>
+      </c>
+      <c r="D14" s="90" t="s">
+        <v>309</v>
+      </c>
+      <c r="E14" s="129"/>
+      <c r="F14" s="130" t="s">
+        <v>298</v>
+      </c>
+      <c r="G14" s="131" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H14" s="92"/>
+      <c r="I14" s="93"/>
+    </row>
+    <row r="15" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="B15" s="126" t="s">
+        <v>274</v>
+      </c>
+      <c r="C15" s="127" t="s">
+        <v>280</v>
+      </c>
+      <c r="D15" s="90">
         <v>1</v>
       </c>
-      <c r="E7" s="130" t="s">
+      <c r="E15" s="129" t="s">
         <v>16</v>
       </c>
-      <c r="F7" s="131" t="s">
-        <v>330</v>
-      </c>
-      <c r="G7" s="132" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F7,"/Readme.md"),"Ver")</f>
-        <v>Ver</v>
-      </c>
-      <c r="H7" s="93"/>
-      <c r="I7" s="94">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B8" s="127" t="s">
-        <v>273</v>
-      </c>
-      <c r="C8" s="128" t="s">
-        <v>314</v>
-      </c>
-      <c r="D8" s="91">
+      <c r="F15" s="130" t="s">
+        <v>302</v>
+      </c>
+      <c r="G15" s="131" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H15" s="92"/>
+      <c r="I15" s="93"/>
+    </row>
+    <row r="16" spans="2:9" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="126" t="s">
+        <v>275</v>
+      </c>
+      <c r="C16" s="127" t="s">
+        <v>281</v>
+      </c>
+      <c r="D16" s="90">
         <v>1</v>
       </c>
-      <c r="E8" s="130" t="s">
-        <v>315</v>
-      </c>
-      <c r="F8" s="131" t="s">
-        <v>304</v>
-      </c>
-      <c r="G8" s="132" t="str">
-        <f t="shared" ref="G8:G18" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F8,"/Readme.md"),"Ver")</f>
-        <v>Ver</v>
-      </c>
-      <c r="H8" s="93"/>
-      <c r="I8" s="94"/>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B9" s="127" t="s">
-        <v>271</v>
-      </c>
-      <c r="C9" s="128" t="s">
-        <v>272</v>
-      </c>
-      <c r="D9" s="91" t="s">
-        <v>316</v>
-      </c>
-      <c r="E9" s="130"/>
-      <c r="F9" s="131" t="s">
-        <v>304</v>
-      </c>
-      <c r="G9" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H9" s="93"/>
-      <c r="I9" s="94"/>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B10" s="127" t="s">
-        <v>275</v>
-      </c>
-      <c r="C10" s="128" t="s">
+      <c r="E16" s="129" t="s">
+        <v>16</v>
+      </c>
+      <c r="F16" s="130" t="s">
+        <v>302</v>
+      </c>
+      <c r="G16" s="131" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H16" s="92"/>
+      <c r="I16" s="93"/>
+    </row>
+    <row r="17" spans="2:9" ht="35.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="133" t="s">
         <v>276</v>
       </c>
-      <c r="D10" s="91">
+      <c r="C17" s="134" t="s">
+        <v>282</v>
+      </c>
+      <c r="D17" s="90">
         <v>1</v>
       </c>
-      <c r="E10" s="130" t="s">
+      <c r="E17" s="129" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="131" t="s">
-        <v>305</v>
-      </c>
-      <c r="G10" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H10" s="93"/>
-      <c r="I10" s="94"/>
-    </row>
-    <row r="11" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="B11" s="127" t="s">
-        <v>274</v>
-      </c>
-      <c r="C11" s="128" t="s">
-        <v>277</v>
-      </c>
-      <c r="D11" s="91" t="s">
-        <v>316</v>
-      </c>
-      <c r="E11" s="130"/>
-      <c r="F11" s="131" t="s">
-        <v>306</v>
-      </c>
-      <c r="G11" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H11" s="93"/>
-      <c r="I11" s="94"/>
-    </row>
-    <row r="12" spans="2:9" ht="57" x14ac:dyDescent="0.3">
-      <c r="B12" s="127" t="s">
-        <v>284</v>
-      </c>
-      <c r="C12" s="128" t="s">
-        <v>278</v>
-      </c>
-      <c r="D12" s="91" t="s">
-        <v>316</v>
-      </c>
-      <c r="E12" s="130"/>
-      <c r="F12" s="131" t="s">
-        <v>307</v>
-      </c>
-      <c r="G12" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H12" s="93"/>
-      <c r="I12" s="94"/>
-    </row>
-    <row r="13" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B13" s="127" t="s">
-        <v>285</v>
-      </c>
-      <c r="C13" s="128" t="s">
-        <v>279</v>
-      </c>
-      <c r="D13" s="91" t="s">
-        <v>316</v>
-      </c>
-      <c r="E13" s="130"/>
-      <c r="F13" s="131" t="s">
-        <v>308</v>
-      </c>
-      <c r="G13" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H13" s="93"/>
-      <c r="I13" s="94"/>
-    </row>
-    <row r="14" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="B14" s="127" t="s">
-        <v>286</v>
-      </c>
-      <c r="C14" s="128" t="s">
-        <v>280</v>
-      </c>
-      <c r="D14" s="91" t="s">
-        <v>316</v>
-      </c>
-      <c r="E14" s="130"/>
-      <c r="F14" s="131" t="s">
-        <v>305</v>
-      </c>
-      <c r="G14" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H14" s="93"/>
-      <c r="I14" s="94"/>
-    </row>
-    <row r="15" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
-      <c r="B15" s="127" t="s">
-        <v>281</v>
-      </c>
-      <c r="C15" s="128" t="s">
-        <v>287</v>
-      </c>
-      <c r="D15" s="91">
-        <v>1</v>
-      </c>
-      <c r="E15" s="130" t="s">
-        <v>16</v>
-      </c>
-      <c r="F15" s="131" t="s">
-        <v>309</v>
-      </c>
-      <c r="G15" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H15" s="93"/>
-      <c r="I15" s="94"/>
-    </row>
-    <row r="16" spans="2:9" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="127" t="s">
-        <v>282</v>
-      </c>
-      <c r="C16" s="128" t="s">
-        <v>288</v>
-      </c>
-      <c r="D16" s="91">
-        <v>1</v>
-      </c>
-      <c r="E16" s="130" t="s">
-        <v>16</v>
-      </c>
-      <c r="F16" s="131" t="s">
-        <v>309</v>
-      </c>
-      <c r="G16" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H16" s="93"/>
-      <c r="I16" s="94"/>
-    </row>
-    <row r="17" spans="2:9" ht="35.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="134" t="s">
-        <v>283</v>
-      </c>
-      <c r="C17" s="135" t="s">
-        <v>289</v>
-      </c>
-      <c r="D17" s="91">
-        <v>1</v>
-      </c>
-      <c r="E17" s="130" t="s">
-        <v>16</v>
-      </c>
-      <c r="F17" s="131" t="s">
-        <v>309</v>
-      </c>
-      <c r="G17" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H17" s="95"/>
-      <c r="I17" s="96"/>
+      <c r="F17" s="130" t="s">
+        <v>302</v>
+      </c>
+      <c r="G17" s="131" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H17" s="94"/>
+      <c r="I17" s="95"/>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B18" s="136"/>
-      <c r="C18" s="137"/>
-      <c r="D18" s="92"/>
-      <c r="E18" s="138"/>
-      <c r="F18" s="139"/>
-      <c r="G18" s="140" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H18" s="97"/>
-      <c r="I18" s="98"/>
+      <c r="B18" s="135"/>
+      <c r="C18" s="136"/>
+      <c r="D18" s="91"/>
+      <c r="E18" s="137"/>
+      <c r="F18" s="138"/>
+      <c r="G18" s="139" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H18" s="96"/>
+      <c r="I18" s="97"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="H19" s="141" t="s">
-        <v>270</v>
-      </c>
-      <c r="I19" s="120">
+      <c r="H19" s="140" t="s">
+        <v>264</v>
+      </c>
+      <c r="I19" s="119">
         <f>AVERAGE(I7:I18)</f>
         <v>5</v>
       </c>
@@ -3807,1986 +3895,1986 @@
   <dimension ref="B2:I100"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.5546875" style="47" customWidth="1"/>
-    <col min="2" max="2" width="30.77734375" style="47" customWidth="1"/>
-    <col min="3" max="3" width="50.77734375" style="47" customWidth="1"/>
-    <col min="4" max="5" width="10.77734375" style="120" customWidth="1"/>
-    <col min="6" max="6" width="7.77734375" style="142" customWidth="1"/>
-    <col min="7" max="7" width="3.77734375" style="120" customWidth="1"/>
-    <col min="8" max="8" width="30.77734375" style="119" customWidth="1"/>
-    <col min="9" max="9" width="12.77734375" style="120" customWidth="1"/>
-    <col min="10" max="10" width="2.5546875" style="47" customWidth="1"/>
-    <col min="11" max="16384" width="9.109375" style="47"/>
+    <col min="1" max="1" width="2.5546875" style="46" customWidth="1"/>
+    <col min="2" max="2" width="30.77734375" style="46" customWidth="1"/>
+    <col min="3" max="3" width="50.77734375" style="46" customWidth="1"/>
+    <col min="4" max="5" width="10.77734375" style="119" customWidth="1"/>
+    <col min="6" max="6" width="7.77734375" style="141" customWidth="1"/>
+    <col min="7" max="7" width="3.77734375" style="119" customWidth="1"/>
+    <col min="8" max="8" width="30.77734375" style="118" customWidth="1"/>
+    <col min="9" max="9" width="12.77734375" style="119" customWidth="1"/>
+    <col min="10" max="10" width="2.5546875" style="46" customWidth="1"/>
+    <col min="11" max="16384" width="9.109375" style="46"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="46" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B3" s="101" t="s">
+      <c r="B3" s="100" t="s">
         <v>156</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B4" s="102" t="s">
-        <v>221</v>
-      </c>
-      <c r="C4" s="102"/>
-      <c r="D4" s="102"/>
-      <c r="E4" s="102"/>
-      <c r="F4" s="102"/>
-      <c r="G4" s="102"/>
-      <c r="H4" s="102"/>
-      <c r="I4" s="102"/>
+      <c r="B4" s="101" t="s">
+        <v>216</v>
+      </c>
+      <c r="C4" s="101"/>
+      <c r="D4" s="101"/>
+      <c r="E4" s="101"/>
+      <c r="F4" s="101"/>
+      <c r="G4" s="101"/>
+      <c r="H4" s="101"/>
+      <c r="I4" s="101"/>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B5" s="143"/>
-      <c r="C5" s="143"/>
-      <c r="D5" s="143"/>
-      <c r="E5" s="143"/>
-      <c r="F5" s="143"/>
-      <c r="G5" s="143"/>
-      <c r="H5" s="143"/>
-      <c r="I5" s="143"/>
+      <c r="B5" s="142"/>
+      <c r="C5" s="142"/>
+      <c r="D5" s="142"/>
+      <c r="E5" s="142"/>
+      <c r="F5" s="142"/>
+      <c r="G5" s="142"/>
+      <c r="H5" s="142"/>
+      <c r="I5" s="142"/>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B6" s="121" t="s">
+      <c r="B6" s="120" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="122" t="s">
+      <c r="C6" s="121" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="123" t="s">
+      <c r="D6" s="122" t="s">
         <v>48</v>
       </c>
-      <c r="E6" s="123" t="s">
+      <c r="E6" s="122" t="s">
         <v>49</v>
       </c>
-      <c r="F6" s="144" t="s">
+      <c r="F6" s="143" t="s">
         <v>38</v>
       </c>
-      <c r="G6" s="145"/>
-      <c r="H6" s="122" t="s">
+      <c r="G6" s="144"/>
+      <c r="H6" s="121" t="s">
         <v>26</v>
       </c>
-      <c r="I6" s="126" t="s">
+      <c r="I6" s="125" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B7" s="146" t="s">
-        <v>318</v>
-      </c>
-      <c r="C7" s="147"/>
-      <c r="D7" s="148"/>
-      <c r="E7" s="148"/>
-      <c r="F7" s="149"/>
-      <c r="G7" s="148"/>
-      <c r="H7" s="150"/>
-      <c r="I7" s="151"/>
+      <c r="B7" s="145" t="s">
+        <v>311</v>
+      </c>
+      <c r="C7" s="146"/>
+      <c r="D7" s="147"/>
+      <c r="E7" s="147"/>
+      <c r="F7" s="148"/>
+      <c r="G7" s="147"/>
+      <c r="H7" s="149"/>
+      <c r="I7" s="150"/>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B8" s="127" t="s">
+      <c r="B8" s="126" t="s">
         <v>157</v>
       </c>
-      <c r="C8" s="128" t="s">
+      <c r="C8" s="127" t="s">
         <v>159</v>
       </c>
-      <c r="D8" s="129">
+      <c r="D8" s="128">
         <v>8</v>
       </c>
-      <c r="E8" s="130" t="s">
+      <c r="E8" s="129" t="s">
         <v>53</v>
       </c>
-      <c r="F8" s="131" t="s">
-        <v>306</v>
-      </c>
-      <c r="G8" s="132" t="str">
+      <c r="F8" s="130" t="s">
+        <v>299</v>
+      </c>
+      <c r="G8" s="131" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F8,"/Readme.md"),"Ver")</f>
         <v>Ver</v>
       </c>
-      <c r="H8" s="128" t="s">
-        <v>291</v>
-      </c>
-      <c r="I8" s="133">
+      <c r="H8" s="127" t="s">
+        <v>284</v>
+      </c>
+      <c r="I8" s="132">
         <v>5</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B9" s="127" t="s">
+      <c r="B9" s="126" t="s">
         <v>158</v>
       </c>
-      <c r="C9" s="128" t="s">
+      <c r="C9" s="127" t="s">
         <v>160</v>
       </c>
-      <c r="D9" s="129">
+      <c r="D9" s="128">
         <v>10</v>
       </c>
-      <c r="E9" s="130" t="s">
+      <c r="E9" s="129" t="s">
         <v>53</v>
       </c>
-      <c r="F9" s="131" t="s">
-        <v>306</v>
-      </c>
-      <c r="G9" s="132" t="str">
+      <c r="F9" s="130" t="s">
+        <v>299</v>
+      </c>
+      <c r="G9" s="131" t="str">
         <f t="shared" ref="G9:G72" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F9,"/Readme.md"),"Ver")</f>
         <v>Ver</v>
       </c>
-      <c r="H9" s="128" t="s">
-        <v>291</v>
-      </c>
-      <c r="I9" s="133"/>
+      <c r="H9" s="127" t="s">
+        <v>284</v>
+      </c>
+      <c r="I9" s="132"/>
     </row>
     <row r="10" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B10" s="127" t="s">
+      <c r="B10" s="126" t="s">
         <v>163</v>
       </c>
-      <c r="C10" s="128" t="s">
+      <c r="C10" s="127" t="s">
         <v>161</v>
       </c>
-      <c r="D10" s="130">
+      <c r="D10" s="129">
         <f>D8+SumUDig</f>
         <v>35</v>
       </c>
-      <c r="E10" s="130" t="s">
+      <c r="E10" s="129" t="s">
         <v>53</v>
       </c>
-      <c r="F10" s="131" t="s">
-        <v>306</v>
-      </c>
-      <c r="G10" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H10" s="128"/>
-      <c r="I10" s="133"/>
+      <c r="F10" s="130" t="s">
+        <v>299</v>
+      </c>
+      <c r="G10" s="131" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H10" s="127"/>
+      <c r="I10" s="132"/>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B11" s="127" t="s">
+      <c r="B11" s="126" t="s">
         <v>164</v>
       </c>
-      <c r="C11" s="128" t="s">
+      <c r="C11" s="127" t="s">
         <v>162</v>
       </c>
-      <c r="D11" s="130" cm="1">
+      <c r="D11" s="129" cm="1">
         <f t="array" ref="D11">D9+SumUDig</f>
         <v>37</v>
       </c>
-      <c r="E11" s="130" t="s">
+      <c r="E11" s="129" t="s">
         <v>53</v>
       </c>
-      <c r="F11" s="131" t="s">
-        <v>306</v>
-      </c>
-      <c r="G11" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H11" s="128"/>
-      <c r="I11" s="133"/>
+      <c r="F11" s="130" t="s">
+        <v>299</v>
+      </c>
+      <c r="G11" s="131" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H11" s="127"/>
+      <c r="I11" s="132"/>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B12" s="127" t="s">
+      <c r="B12" s="126" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="128" t="s">
+      <c r="C12" s="127" t="s">
         <v>172</v>
       </c>
-      <c r="D12" s="129">
+      <c r="D12" s="128">
         <v>12</v>
       </c>
-      <c r="E12" s="130" t="s">
+      <c r="E12" s="129" t="s">
         <v>53</v>
       </c>
-      <c r="F12" s="131" t="s">
-        <v>306</v>
-      </c>
-      <c r="G12" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H12" s="128" t="s">
-        <v>291</v>
-      </c>
-      <c r="I12" s="133"/>
+      <c r="F12" s="130" t="s">
+        <v>299</v>
+      </c>
+      <c r="G12" s="131" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H12" s="127" t="s">
+        <v>284</v>
+      </c>
+      <c r="I12" s="132"/>
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B13" s="127" t="s">
+      <c r="B13" s="126" t="s">
         <v>60</v>
       </c>
-      <c r="C13" s="128" t="s">
+      <c r="C13" s="127" t="s">
         <v>65</v>
       </c>
-      <c r="D13" s="129">
+      <c r="D13" s="128">
         <v>6</v>
       </c>
-      <c r="E13" s="130" t="s">
+      <c r="E13" s="129" t="s">
         <v>53</v>
       </c>
-      <c r="F13" s="131" t="s">
-        <v>306</v>
-      </c>
-      <c r="G13" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H13" s="128" t="s">
-        <v>291</v>
-      </c>
-      <c r="I13" s="133"/>
+      <c r="F13" s="130" t="s">
+        <v>299</v>
+      </c>
+      <c r="G13" s="131" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H13" s="127" t="s">
+        <v>284</v>
+      </c>
+      <c r="I13" s="132"/>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B14" s="127" t="s">
+      <c r="B14" s="126" t="s">
         <v>40</v>
       </c>
-      <c r="C14" s="128" t="s">
+      <c r="C14" s="127" t="s">
         <v>64</v>
       </c>
-      <c r="D14" s="129">
+      <c r="D14" s="128">
         <v>12</v>
       </c>
-      <c r="E14" s="130" t="s">
+      <c r="E14" s="129" t="s">
         <v>53</v>
       </c>
-      <c r="F14" s="131" t="s">
-        <v>306</v>
-      </c>
-      <c r="G14" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H14" s="128" t="s">
-        <v>291</v>
-      </c>
-      <c r="I14" s="133"/>
+      <c r="F14" s="130" t="s">
+        <v>299</v>
+      </c>
+      <c r="G14" s="131" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H14" s="127" t="s">
+        <v>284</v>
+      </c>
+      <c r="I14" s="132"/>
     </row>
     <row r="15" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B15" s="127" t="s">
+      <c r="B15" s="126" t="s">
         <v>52</v>
       </c>
-      <c r="C15" s="128" t="s">
+      <c r="C15" s="127" t="s">
         <v>61</v>
       </c>
-      <c r="D15" s="130">
+      <c r="D15" s="129">
         <f>D10</f>
         <v>35</v>
       </c>
-      <c r="E15" s="130" t="s">
+      <c r="E15" s="129" t="s">
         <v>53</v>
       </c>
-      <c r="F15" s="131" t="s">
-        <v>306</v>
-      </c>
-      <c r="G15" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H15" s="128"/>
-      <c r="I15" s="133"/>
+      <c r="F15" s="130" t="s">
+        <v>299</v>
+      </c>
+      <c r="G15" s="131" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H15" s="127"/>
+      <c r="I15" s="132"/>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B16" s="127" t="s">
+      <c r="B16" s="126" t="s">
         <v>51</v>
       </c>
-      <c r="C16" s="128" t="s">
+      <c r="C16" s="127" t="s">
         <v>59</v>
       </c>
-      <c r="D16" s="130">
+      <c r="D16" s="129">
         <f>D11+D14+D13</f>
         <v>55</v>
       </c>
-      <c r="E16" s="130" t="s">
+      <c r="E16" s="129" t="s">
         <v>53</v>
       </c>
-      <c r="F16" s="131" t="s">
-        <v>306</v>
-      </c>
-      <c r="G16" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H16" s="128"/>
-      <c r="I16" s="133"/>
+      <c r="F16" s="130" t="s">
+        <v>299</v>
+      </c>
+      <c r="G16" s="131" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H16" s="127"/>
+      <c r="I16" s="132"/>
     </row>
     <row r="17" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B17" s="127" t="s">
+      <c r="B17" s="126" t="s">
         <v>50</v>
       </c>
-      <c r="C17" s="128" t="s">
+      <c r="C17" s="127" t="s">
         <v>130</v>
       </c>
-      <c r="D17" s="130">
+      <c r="D17" s="129">
         <f>D16*D15</f>
         <v>1925</v>
       </c>
-      <c r="E17" s="130" t="s">
+      <c r="E17" s="129" t="s">
         <v>54</v>
       </c>
-      <c r="F17" s="131" t="s">
-        <v>306</v>
-      </c>
-      <c r="G17" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H17" s="128"/>
-      <c r="I17" s="133"/>
+      <c r="F17" s="130" t="s">
+        <v>299</v>
+      </c>
+      <c r="G17" s="131" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H17" s="127"/>
+      <c r="I17" s="132"/>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B18" s="134" t="s">
+      <c r="B18" s="133" t="s">
         <v>100</v>
       </c>
-      <c r="C18" s="135" t="s">
+      <c r="C18" s="134" t="s">
         <v>101</v>
       </c>
-      <c r="D18" s="152">
+      <c r="D18" s="151">
         <f>D32+D30</f>
         <v>1435</v>
       </c>
-      <c r="E18" s="130" t="s">
+      <c r="E18" s="129" t="s">
         <v>54</v>
       </c>
-      <c r="F18" s="131" t="s">
-        <v>306</v>
-      </c>
-      <c r="G18" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H18" s="135"/>
-      <c r="I18" s="153"/>
+      <c r="F18" s="130" t="s">
+        <v>299</v>
+      </c>
+      <c r="G18" s="131" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H18" s="134"/>
+      <c r="I18" s="152"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B19" s="134" t="s">
+      <c r="B19" s="133" t="s">
         <v>98</v>
       </c>
-      <c r="C19" s="135" t="s">
+      <c r="C19" s="134" t="s">
         <v>131</v>
       </c>
-      <c r="D19" s="152">
+      <c r="D19" s="151">
         <f>D32+D30+D46</f>
         <v>1495</v>
       </c>
-      <c r="E19" s="130" t="s">
+      <c r="E19" s="129" t="s">
         <v>54</v>
       </c>
-      <c r="F19" s="131" t="s">
-        <v>306</v>
-      </c>
-      <c r="G19" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H19" s="135"/>
-      <c r="I19" s="153"/>
+      <c r="F19" s="130" t="s">
+        <v>299</v>
+      </c>
+      <c r="G19" s="131" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H19" s="134"/>
+      <c r="I19" s="152"/>
     </row>
     <row r="20" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
-      <c r="B20" s="134" t="s">
+      <c r="B20" s="133" t="s">
         <v>66</v>
       </c>
-      <c r="C20" s="135" t="s">
+      <c r="C20" s="134" t="s">
         <v>132</v>
       </c>
-      <c r="D20" s="152">
+      <c r="D20" s="151">
         <f>D18/D17</f>
         <v>0.74545454545454548</v>
       </c>
-      <c r="E20" s="152" t="s">
+      <c r="E20" s="151" t="s">
         <v>67</v>
       </c>
-      <c r="F20" s="131" t="s">
-        <v>306</v>
-      </c>
-      <c r="G20" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H20" s="135"/>
-      <c r="I20" s="153"/>
+      <c r="F20" s="130" t="s">
+        <v>299</v>
+      </c>
+      <c r="G20" s="131" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H20" s="134"/>
+      <c r="I20" s="152"/>
     </row>
     <row r="21" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B21" s="134" t="s">
+      <c r="B21" s="133" t="s">
         <v>99</v>
       </c>
-      <c r="C21" s="135" t="s">
+      <c r="C21" s="134" t="s">
         <v>133</v>
       </c>
-      <c r="D21" s="152">
+      <c r="D21" s="151">
         <f>D19/D17</f>
         <v>0.77662337662337666</v>
       </c>
-      <c r="E21" s="152" t="s">
+      <c r="E21" s="151" t="s">
         <v>67</v>
       </c>
-      <c r="F21" s="131" t="s">
-        <v>306</v>
-      </c>
-      <c r="G21" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H21" s="135"/>
-      <c r="I21" s="153"/>
+      <c r="F21" s="130" t="s">
+        <v>299</v>
+      </c>
+      <c r="G21" s="131" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H21" s="134"/>
+      <c r="I21" s="152"/>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B22" s="136"/>
-      <c r="C22" s="137"/>
-      <c r="D22" s="138"/>
-      <c r="E22" s="138"/>
-      <c r="F22" s="139"/>
-      <c r="G22" s="140" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H22" s="137"/>
-      <c r="I22" s="154"/>
+      <c r="B22" s="135"/>
+      <c r="C22" s="136"/>
+      <c r="D22" s="137"/>
+      <c r="E22" s="137"/>
+      <c r="F22" s="138"/>
+      <c r="G22" s="139" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H22" s="136"/>
+      <c r="I22" s="153"/>
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B23" s="146" t="s">
-        <v>319</v>
-      </c>
-      <c r="C23" s="147"/>
-      <c r="D23" s="148"/>
-      <c r="E23" s="148"/>
-      <c r="F23" s="149"/>
-      <c r="G23" s="148"/>
-      <c r="H23" s="150"/>
-      <c r="I23" s="151"/>
+      <c r="B23" s="145" t="s">
+        <v>312</v>
+      </c>
+      <c r="C23" s="146"/>
+      <c r="D23" s="147"/>
+      <c r="E23" s="147"/>
+      <c r="F23" s="148"/>
+      <c r="G23" s="147"/>
+      <c r="H23" s="149"/>
+      <c r="I23" s="150"/>
     </row>
     <row r="24" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
-      <c r="B24" s="127" t="s">
+      <c r="B24" s="126" t="s">
         <v>71</v>
       </c>
-      <c r="C24" s="128" t="s">
+      <c r="C24" s="127" t="s">
         <v>134</v>
       </c>
-      <c r="D24" s="129">
+      <c r="D24" s="128">
         <v>2</v>
       </c>
-      <c r="E24" s="130" t="s">
+      <c r="E24" s="129" t="s">
         <v>53</v>
       </c>
-      <c r="F24" s="131" t="s">
-        <v>306</v>
-      </c>
-      <c r="G24" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H24" s="128" t="s">
-        <v>291</v>
-      </c>
-      <c r="I24" s="133">
+      <c r="F24" s="130" t="s">
+        <v>299</v>
+      </c>
+      <c r="G24" s="131" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H24" s="127" t="s">
+        <v>284</v>
+      </c>
+      <c r="I24" s="132">
         <v>5</v>
       </c>
     </row>
     <row r="25" spans="2:9" ht="57" x14ac:dyDescent="0.3">
-      <c r="B25" s="127" t="s">
+      <c r="B25" s="126" t="s">
         <v>72</v>
       </c>
-      <c r="C25" s="128" t="s">
+      <c r="C25" s="127" t="s">
         <v>82</v>
       </c>
       <c r="D25" s="32">
         <v>5</v>
       </c>
-      <c r="E25" s="130" t="s">
+      <c r="E25" s="129" t="s">
         <v>68</v>
       </c>
-      <c r="F25" s="131" t="s">
-        <v>306</v>
-      </c>
-      <c r="G25" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H25" s="128"/>
-      <c r="I25" s="133"/>
+      <c r="F25" s="130" t="s">
+        <v>299</v>
+      </c>
+      <c r="G25" s="131" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H25" s="127"/>
+      <c r="I25" s="132"/>
     </row>
     <row r="26" spans="2:9" ht="45.6" x14ac:dyDescent="0.3">
-      <c r="B26" s="127" t="s">
+      <c r="B26" s="126" t="s">
         <v>73</v>
       </c>
-      <c r="C26" s="128" t="s">
+      <c r="C26" s="127" t="s">
         <v>70</v>
       </c>
-      <c r="D26" s="130">
+      <c r="D26" s="129">
         <f>ROUND(ATAN(D25/100)*180/PI(),0)</f>
         <v>3</v>
       </c>
-      <c r="E26" s="130" t="s">
+      <c r="E26" s="129" t="s">
         <v>69</v>
       </c>
-      <c r="F26" s="131" t="s">
-        <v>306</v>
-      </c>
-      <c r="G26" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H26" s="128"/>
-      <c r="I26" s="133"/>
+      <c r="F26" s="130" t="s">
+        <v>299</v>
+      </c>
+      <c r="G26" s="131" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H26" s="127"/>
+      <c r="I26" s="132"/>
     </row>
     <row r="27" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B27" s="134" t="s">
+      <c r="B27" s="133" t="s">
         <v>75</v>
       </c>
-      <c r="C27" s="135" t="s">
-        <v>317</v>
-      </c>
-      <c r="D27" s="155">
+      <c r="C27" s="134" t="s">
+        <v>310</v>
+      </c>
+      <c r="D27" s="154">
         <v>0.6</v>
       </c>
-      <c r="E27" s="152" t="s">
+      <c r="E27" s="151" t="s">
         <v>53</v>
       </c>
-      <c r="F27" s="131" t="s">
-        <v>306</v>
-      </c>
-      <c r="G27" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H27" s="135"/>
-      <c r="I27" s="153"/>
+      <c r="F27" s="130" t="s">
+        <v>299</v>
+      </c>
+      <c r="G27" s="131" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H27" s="134"/>
+      <c r="I27" s="152"/>
     </row>
     <row r="28" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="B28" s="127" t="s">
+      <c r="B28" s="126" t="s">
         <v>74</v>
       </c>
-      <c r="C28" s="128" t="s">
+      <c r="C28" s="127" t="s">
         <v>135</v>
       </c>
-      <c r="D28" s="129">
+      <c r="D28" s="128">
         <v>0.2</v>
       </c>
-      <c r="E28" s="130" t="s">
+      <c r="E28" s="129" t="s">
         <v>53</v>
       </c>
-      <c r="F28" s="131" t="s">
-        <v>306</v>
-      </c>
-      <c r="G28" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H28" s="128"/>
-      <c r="I28" s="133"/>
+      <c r="F28" s="130" t="s">
+        <v>299</v>
+      </c>
+      <c r="G28" s="131" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H28" s="127"/>
+      <c r="I28" s="132"/>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B29" s="127" t="s">
+      <c r="B29" s="126" t="s">
         <v>136</v>
       </c>
-      <c r="C29" s="128" t="s">
+      <c r="C29" s="127" t="s">
         <v>138</v>
       </c>
-      <c r="D29" s="129">
+      <c r="D29" s="128">
         <v>2</v>
       </c>
-      <c r="E29" s="130" t="s">
+      <c r="E29" s="129" t="s">
         <v>67</v>
       </c>
-      <c r="F29" s="131" t="s">
-        <v>306</v>
-      </c>
-      <c r="G29" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H29" s="128"/>
-      <c r="I29" s="133"/>
+      <c r="F29" s="130" t="s">
+        <v>299</v>
+      </c>
+      <c r="G29" s="131" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H29" s="127"/>
+      <c r="I29" s="132"/>
     </row>
     <row r="30" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B30" s="134" t="s">
+      <c r="B30" s="133" t="s">
         <v>76</v>
       </c>
-      <c r="C30" s="135" t="s">
+      <c r="C30" s="134" t="s">
         <v>137</v>
       </c>
-      <c r="D30" s="152">
+      <c r="D30" s="151">
         <f>(D27-D28)*(D11+D24+D24)*D29</f>
         <v>32.799999999999997</v>
       </c>
-      <c r="E30" s="130" t="s">
+      <c r="E30" s="129" t="s">
         <v>54</v>
       </c>
-      <c r="F30" s="131" t="s">
-        <v>306</v>
-      </c>
-      <c r="G30" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H30" s="135"/>
-      <c r="I30" s="153"/>
+      <c r="F30" s="130" t="s">
+        <v>299</v>
+      </c>
+      <c r="G30" s="131" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H30" s="134"/>
+      <c r="I30" s="152"/>
     </row>
     <row r="31" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
-      <c r="B31" s="127" t="s">
+      <c r="B31" s="126" t="s">
         <v>139</v>
       </c>
-      <c r="C31" s="128" t="s">
+      <c r="C31" s="127" t="s">
         <v>141</v>
       </c>
-      <c r="D31" s="130">
+      <c r="D31" s="129">
         <f>(D10*D11)-D30</f>
         <v>1262.2</v>
       </c>
-      <c r="E31" s="130" t="s">
+      <c r="E31" s="129" t="s">
         <v>54</v>
       </c>
-      <c r="F31" s="131" t="s">
-        <v>306</v>
-      </c>
-      <c r="G31" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H31" s="128"/>
-      <c r="I31" s="133"/>
+      <c r="F31" s="130" t="s">
+        <v>299</v>
+      </c>
+      <c r="G31" s="131" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H31" s="127"/>
+      <c r="I31" s="132"/>
     </row>
     <row r="32" spans="2:9" ht="45.6" x14ac:dyDescent="0.3">
-      <c r="B32" s="127" t="s">
+      <c r="B32" s="126" t="s">
         <v>140</v>
       </c>
-      <c r="C32" s="128" t="s">
+      <c r="C32" s="127" t="s">
         <v>142</v>
       </c>
-      <c r="D32" s="130">
+      <c r="D32" s="129">
         <f>((D10*D11)+D10*(D24+D24))-D30</f>
         <v>1402.2</v>
       </c>
-      <c r="E32" s="130" t="s">
+      <c r="E32" s="129" t="s">
         <v>54</v>
       </c>
-      <c r="F32" s="131" t="s">
-        <v>306</v>
-      </c>
-      <c r="G32" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H32" s="128"/>
-      <c r="I32" s="133"/>
+      <c r="F32" s="130" t="s">
+        <v>299</v>
+      </c>
+      <c r="G32" s="131" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H32" s="127"/>
+      <c r="I32" s="132"/>
     </row>
     <row r="33" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B33" s="127" t="s">
+      <c r="B33" s="126" t="s">
         <v>77</v>
       </c>
-      <c r="C33" s="128" t="s">
+      <c r="C33" s="127" t="s">
         <v>123</v>
       </c>
-      <c r="D33" s="129">
+      <c r="D33" s="128">
         <v>10</v>
       </c>
-      <c r="E33" s="130" t="s">
+      <c r="E33" s="129" t="s">
         <v>53</v>
       </c>
-      <c r="F33" s="131" t="s">
-        <v>329</v>
-      </c>
-      <c r="G33" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H33" s="128"/>
-      <c r="I33" s="133"/>
+      <c r="F33" s="130" t="s">
+        <v>322</v>
+      </c>
+      <c r="G33" s="131" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H33" s="127"/>
+      <c r="I33" s="132"/>
     </row>
     <row r="34" spans="2:9" ht="45.6" x14ac:dyDescent="0.3">
-      <c r="B34" s="127" t="s">
+      <c r="B34" s="126" t="s">
         <v>78</v>
       </c>
-      <c r="C34" s="128" t="s">
+      <c r="C34" s="127" t="s">
         <v>143</v>
       </c>
-      <c r="D34" s="130">
+      <c r="D34" s="129">
         <f>EVEN(D31/(D33*D33))</f>
         <v>14</v>
       </c>
-      <c r="E34" s="130" t="s">
+      <c r="E34" s="129" t="s">
         <v>115</v>
       </c>
-      <c r="F34" s="131" t="s">
-        <v>329</v>
-      </c>
-      <c r="G34" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H34" s="128"/>
-      <c r="I34" s="133"/>
+      <c r="F34" s="130" t="s">
+        <v>322</v>
+      </c>
+      <c r="G34" s="131" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H34" s="127"/>
+      <c r="I34" s="132"/>
     </row>
     <row r="35" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B35" s="127" t="s">
+      <c r="B35" s="126" t="s">
         <v>79</v>
       </c>
-      <c r="C35" s="128" t="s">
+      <c r="C35" s="127" t="s">
         <v>62</v>
       </c>
-      <c r="D35" s="129">
+      <c r="D35" s="128">
         <v>1200</v>
       </c>
-      <c r="E35" s="130" t="s">
+      <c r="E35" s="129" t="s">
         <v>63</v>
       </c>
-      <c r="F35" s="131" t="s">
-        <v>329</v>
-      </c>
-      <c r="G35" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H35" s="128"/>
-      <c r="I35" s="133"/>
+      <c r="F35" s="130" t="s">
+        <v>322</v>
+      </c>
+      <c r="G35" s="131" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H35" s="127"/>
+      <c r="I35" s="132"/>
     </row>
     <row r="36" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
-      <c r="B36" s="127" t="s">
+      <c r="B36" s="126" t="s">
         <v>80</v>
       </c>
-      <c r="C36" s="128" t="s">
-        <v>337</v>
-      </c>
-      <c r="D36" s="130">
+      <c r="C36" s="127" t="s">
+        <v>330</v>
+      </c>
+      <c r="D36" s="129">
         <f>D35*D35/(1000*1000)</f>
         <v>1.44</v>
       </c>
-      <c r="E36" s="130" t="s">
+      <c r="E36" s="129" t="s">
         <v>54</v>
       </c>
-      <c r="F36" s="131" t="s">
-        <v>329</v>
-      </c>
-      <c r="G36" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H36" s="128"/>
-      <c r="I36" s="133"/>
+      <c r="F36" s="130" t="s">
+        <v>322</v>
+      </c>
+      <c r="G36" s="131" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H36" s="127"/>
+      <c r="I36" s="132"/>
     </row>
     <row r="37" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="B37" s="127" t="s">
+      <c r="B37" s="126" t="s">
         <v>81</v>
       </c>
-      <c r="C37" s="128" t="s">
+      <c r="C37" s="127" t="s">
         <v>144</v>
       </c>
-      <c r="D37" s="130">
+      <c r="D37" s="129">
         <f>D34*D36</f>
         <v>20.16</v>
       </c>
-      <c r="E37" s="130" t="s">
+      <c r="E37" s="129" t="s">
         <v>54</v>
       </c>
-      <c r="F37" s="131" t="s">
-        <v>329</v>
-      </c>
-      <c r="G37" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H37" s="128"/>
-      <c r="I37" s="133"/>
+      <c r="F37" s="130" t="s">
+        <v>322</v>
+      </c>
+      <c r="G37" s="131" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H37" s="127"/>
+      <c r="I37" s="132"/>
     </row>
     <row r="38" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B38" s="136"/>
-      <c r="C38" s="137"/>
-      <c r="D38" s="138"/>
-      <c r="E38" s="138"/>
-      <c r="F38" s="139"/>
-      <c r="G38" s="140" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H38" s="137"/>
-      <c r="I38" s="154"/>
+      <c r="B38" s="135"/>
+      <c r="C38" s="136"/>
+      <c r="D38" s="137"/>
+      <c r="E38" s="137"/>
+      <c r="F38" s="138"/>
+      <c r="G38" s="139" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H38" s="136"/>
+      <c r="I38" s="153"/>
     </row>
     <row r="39" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B39" s="156" t="s">
-        <v>338</v>
-      </c>
-      <c r="C39" s="147"/>
-      <c r="D39" s="148"/>
-      <c r="E39" s="148"/>
-      <c r="F39" s="149"/>
-      <c r="G39" s="148"/>
-      <c r="H39" s="150"/>
-      <c r="I39" s="151"/>
+      <c r="B39" s="155" t="s">
+        <v>331</v>
+      </c>
+      <c r="C39" s="146"/>
+      <c r="D39" s="147"/>
+      <c r="E39" s="147"/>
+      <c r="F39" s="148"/>
+      <c r="G39" s="147"/>
+      <c r="H39" s="149"/>
+      <c r="I39" s="150"/>
     </row>
     <row r="40" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B40" s="127" t="s">
-        <v>339</v>
-      </c>
-      <c r="C40" s="128" t="s">
+      <c r="B40" s="126" t="s">
+        <v>332</v>
+      </c>
+      <c r="C40" s="127" t="s">
         <v>86</v>
       </c>
-      <c r="D40" s="129">
+      <c r="D40" s="128">
         <v>1</v>
       </c>
-      <c r="E40" s="130" t="s">
+      <c r="E40" s="129" t="s">
         <v>53</v>
       </c>
-      <c r="F40" s="131" t="s">
-        <v>306</v>
-      </c>
-      <c r="G40" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H40" s="128"/>
-      <c r="I40" s="133">
+      <c r="F40" s="130" t="s">
+        <v>299</v>
+      </c>
+      <c r="G40" s="131" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H40" s="127"/>
+      <c r="I40" s="132">
         <v>5</v>
       </c>
     </row>
     <row r="41" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B41" s="127" t="s">
+      <c r="B41" s="126" t="s">
         <v>83</v>
       </c>
-      <c r="C41" s="128" t="s">
+      <c r="C41" s="127" t="s">
         <v>87</v>
       </c>
-      <c r="D41" s="129">
+      <c r="D41" s="128">
         <v>15</v>
       </c>
-      <c r="E41" s="130" t="s">
+      <c r="E41" s="129" t="s">
         <v>53</v>
       </c>
-      <c r="F41" s="131" t="s">
-        <v>306</v>
-      </c>
-      <c r="G41" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H41" s="128"/>
-      <c r="I41" s="133"/>
+      <c r="F41" s="130" t="s">
+        <v>299</v>
+      </c>
+      <c r="G41" s="131" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H41" s="127"/>
+      <c r="I41" s="132"/>
     </row>
     <row r="42" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B42" s="127" t="s">
+      <c r="B42" s="126" t="s">
         <v>84</v>
       </c>
-      <c r="C42" s="128" t="s">
-        <v>340</v>
-      </c>
-      <c r="D42" s="130">
+      <c r="C42" s="127" t="s">
+        <v>333</v>
+      </c>
+      <c r="D42" s="129">
         <f>D11+(INT(D11/D41)*D10)</f>
         <v>107</v>
       </c>
-      <c r="E42" s="130" t="s">
+      <c r="E42" s="129" t="s">
         <v>53</v>
       </c>
-      <c r="F42" s="131" t="s">
-        <v>306</v>
-      </c>
-      <c r="G42" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H42" s="128"/>
-      <c r="I42" s="133"/>
+      <c r="F42" s="130" t="s">
+        <v>299</v>
+      </c>
+      <c r="G42" s="131" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H42" s="127"/>
+      <c r="I42" s="132"/>
     </row>
     <row r="43" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B43" s="127" t="s">
+      <c r="B43" s="126" t="s">
         <v>85</v>
       </c>
-      <c r="C43" s="128" t="s">
+      <c r="C43" s="127" t="s">
         <v>88</v>
       </c>
-      <c r="D43" s="130">
+      <c r="D43" s="129">
         <f>D42*D40</f>
         <v>107</v>
       </c>
-      <c r="E43" s="130" t="s">
+      <c r="E43" s="129" t="s">
         <v>54</v>
       </c>
-      <c r="F43" s="131" t="s">
-        <v>306</v>
-      </c>
-      <c r="G43" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H43" s="128"/>
-      <c r="I43" s="133"/>
+      <c r="F43" s="130" t="s">
+        <v>299</v>
+      </c>
+      <c r="G43" s="131" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H43" s="127"/>
+      <c r="I43" s="132"/>
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B44" s="136"/>
-      <c r="C44" s="137"/>
-      <c r="D44" s="138"/>
-      <c r="E44" s="138"/>
-      <c r="F44" s="139"/>
-      <c r="G44" s="140" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H44" s="137"/>
-      <c r="I44" s="154"/>
+      <c r="B44" s="135"/>
+      <c r="C44" s="136"/>
+      <c r="D44" s="137"/>
+      <c r="E44" s="137"/>
+      <c r="F44" s="138"/>
+      <c r="G44" s="139" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H44" s="136"/>
+      <c r="I44" s="153"/>
     </row>
     <row r="45" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B45" s="146" t="s">
-        <v>320</v>
-      </c>
-      <c r="C45" s="147"/>
-      <c r="D45" s="148"/>
-      <c r="E45" s="148"/>
-      <c r="F45" s="149"/>
-      <c r="G45" s="148"/>
-      <c r="H45" s="150"/>
-      <c r="I45" s="151"/>
+      <c r="B45" s="145" t="s">
+        <v>313</v>
+      </c>
+      <c r="C45" s="146"/>
+      <c r="D45" s="147"/>
+      <c r="E45" s="147"/>
+      <c r="F45" s="148"/>
+      <c r="G45" s="147"/>
+      <c r="H45" s="149"/>
+      <c r="I45" s="150"/>
     </row>
     <row r="46" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
-      <c r="B46" s="127" t="s">
+      <c r="B46" s="126" t="s">
         <v>41</v>
       </c>
-      <c r="C46" s="128" t="s">
-        <v>321</v>
-      </c>
-      <c r="D46" s="129">
+      <c r="C46" s="127" t="s">
+        <v>314</v>
+      </c>
+      <c r="D46" s="128">
         <v>60</v>
       </c>
-      <c r="E46" s="130" t="s">
+      <c r="E46" s="129" t="s">
         <v>54</v>
       </c>
-      <c r="F46" s="131" t="s">
-        <v>306</v>
-      </c>
-      <c r="G46" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H46" s="128"/>
-      <c r="I46" s="133">
+      <c r="F46" s="130" t="s">
+        <v>299</v>
+      </c>
+      <c r="G46" s="131" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H46" s="127"/>
+      <c r="I46" s="132">
         <v>5</v>
       </c>
     </row>
     <row r="47" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
-      <c r="B47" s="127" t="s">
+      <c r="B47" s="126" t="s">
         <v>42</v>
       </c>
-      <c r="C47" s="128" t="s">
+      <c r="C47" s="127" t="s">
         <v>43</v>
       </c>
-      <c r="D47" s="129">
+      <c r="D47" s="128">
         <v>24</v>
       </c>
-      <c r="E47" s="130" t="s">
+      <c r="E47" s="129" t="s">
         <v>54</v>
       </c>
-      <c r="F47" s="131" t="s">
-        <v>306</v>
-      </c>
-      <c r="G47" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H47" s="128"/>
-      <c r="I47" s="133"/>
+      <c r="F47" s="130" t="s">
+        <v>299</v>
+      </c>
+      <c r="G47" s="131" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H47" s="127"/>
+      <c r="I47" s="132"/>
     </row>
     <row r="48" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B48" s="127" t="s">
+      <c r="B48" s="126" t="s">
         <v>89</v>
       </c>
-      <c r="C48" s="128" t="s">
+      <c r="C48" s="127" t="s">
         <v>124</v>
       </c>
-      <c r="D48" s="129">
+      <c r="D48" s="128">
         <v>3.9900000000000007</v>
       </c>
-      <c r="E48" s="130" t="s">
+      <c r="E48" s="129" t="s">
         <v>53</v>
       </c>
-      <c r="F48" s="131" t="s">
-        <v>306</v>
-      </c>
-      <c r="G48" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H48" s="128"/>
-      <c r="I48" s="133"/>
+      <c r="F48" s="130" t="s">
+        <v>299</v>
+      </c>
+      <c r="G48" s="131" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H48" s="127"/>
+      <c r="I48" s="132"/>
     </row>
     <row r="49" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B49" s="127" t="s">
+      <c r="B49" s="126" t="s">
         <v>90</v>
       </c>
-      <c r="C49" s="128" t="s">
+      <c r="C49" s="127" t="s">
         <v>145</v>
       </c>
-      <c r="D49" s="130">
+      <c r="D49" s="129">
         <f>D46-D54</f>
         <v>52.943999999999996</v>
       </c>
-      <c r="E49" s="130" t="s">
+      <c r="E49" s="129" t="s">
         <v>54</v>
       </c>
-      <c r="F49" s="131" t="s">
-        <v>306</v>
-      </c>
-      <c r="G49" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H49" s="128"/>
-      <c r="I49" s="133"/>
+      <c r="F49" s="130" t="s">
+        <v>299</v>
+      </c>
+      <c r="G49" s="131" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H49" s="127"/>
+      <c r="I49" s="132"/>
     </row>
     <row r="50" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B50" s="127" t="s">
+      <c r="B50" s="126" t="s">
         <v>57</v>
       </c>
-      <c r="C50" s="128" t="s">
+      <c r="C50" s="127" t="s">
         <v>56</v>
       </c>
-      <c r="D50" s="129">
+      <c r="D50" s="128">
         <v>28</v>
       </c>
-      <c r="E50" s="130" t="s">
+      <c r="E50" s="129" t="s">
         <v>55</v>
       </c>
-      <c r="F50" s="131" t="s">
-        <v>306</v>
-      </c>
-      <c r="G50" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H50" s="128"/>
-      <c r="I50" s="133"/>
+      <c r="F50" s="130" t="s">
+        <v>299</v>
+      </c>
+      <c r="G50" s="131" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H50" s="127"/>
+      <c r="I50" s="132"/>
     </row>
     <row r="51" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B51" s="127" t="s">
+      <c r="B51" s="126" t="s">
         <v>93</v>
       </c>
-      <c r="C51" s="128" t="s">
+      <c r="C51" s="127" t="s">
         <v>58</v>
       </c>
-      <c r="D51" s="129">
+      <c r="D51" s="128">
         <v>19</v>
       </c>
-      <c r="E51" s="130" t="s">
+      <c r="E51" s="129" t="s">
         <v>55</v>
       </c>
-      <c r="F51" s="131" t="s">
-        <v>306</v>
-      </c>
-      <c r="G51" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H51" s="128"/>
-      <c r="I51" s="133"/>
+      <c r="F51" s="130" t="s">
+        <v>299</v>
+      </c>
+      <c r="G51" s="131" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H51" s="127"/>
+      <c r="I51" s="132"/>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B52" s="127" t="s">
+      <c r="B52" s="126" t="s">
         <v>91</v>
       </c>
-      <c r="C52" s="128" t="s">
+      <c r="C52" s="127" t="s">
         <v>92</v>
       </c>
-      <c r="D52" s="130">
+      <c r="D52" s="129">
         <f>D48/(D51/100)</f>
         <v>21.000000000000004</v>
       </c>
-      <c r="E52" s="130" t="s">
+      <c r="E52" s="129" t="s">
         <v>49</v>
       </c>
-      <c r="F52" s="131" t="s">
-        <v>306</v>
-      </c>
-      <c r="G52" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H52" s="128"/>
-      <c r="I52" s="133"/>
+      <c r="F52" s="130" t="s">
+        <v>299</v>
+      </c>
+      <c r="G52" s="131" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H52" s="127"/>
+      <c r="I52" s="132"/>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B53" s="127" t="s">
+      <c r="B53" s="126" t="s">
         <v>94</v>
       </c>
-      <c r="C53" s="128" t="s">
+      <c r="C53" s="127" t="s">
         <v>95</v>
       </c>
-      <c r="D53" s="129">
+      <c r="D53" s="128">
         <v>1.2</v>
       </c>
-      <c r="E53" s="130" t="s">
+      <c r="E53" s="129" t="s">
         <v>53</v>
       </c>
-      <c r="F53" s="131" t="s">
-        <v>306</v>
-      </c>
-      <c r="G53" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H53" s="128"/>
-      <c r="I53" s="133"/>
+      <c r="F53" s="130" t="s">
+        <v>299</v>
+      </c>
+      <c r="G53" s="131" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H53" s="127"/>
+      <c r="I53" s="132"/>
     </row>
     <row r="54" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B54" s="127" t="s">
+      <c r="B54" s="126" t="s">
         <v>96</v>
       </c>
-      <c r="C54" s="128" t="s">
+      <c r="C54" s="127" t="s">
         <v>97</v>
       </c>
-      <c r="D54" s="157">
+      <c r="D54" s="156">
         <f>D53*D52*(D50/100)</f>
         <v>7.0560000000000018</v>
       </c>
-      <c r="E54" s="130" t="s">
+      <c r="E54" s="129" t="s">
         <v>54</v>
       </c>
-      <c r="F54" s="131" t="s">
-        <v>306</v>
-      </c>
-      <c r="G54" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H54" s="128"/>
-      <c r="I54" s="133"/>
+      <c r="F54" s="130" t="s">
+        <v>299</v>
+      </c>
+      <c r="G54" s="131" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H54" s="127"/>
+      <c r="I54" s="132"/>
     </row>
     <row r="55" spans="2:9" ht="68.400000000000006" x14ac:dyDescent="0.3">
-      <c r="B55" s="127" t="s">
+      <c r="B55" s="126" t="s">
         <v>125</v>
       </c>
-      <c r="C55" s="128" t="s">
+      <c r="C55" s="127" t="s">
         <v>184</v>
       </c>
-      <c r="D55" s="129">
+      <c r="D55" s="128">
         <v>6</v>
       </c>
-      <c r="E55" s="130" t="s">
+      <c r="E55" s="129" t="s">
         <v>53</v>
       </c>
-      <c r="F55" s="131" t="s">
-        <v>309</v>
-      </c>
-      <c r="G55" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H55" s="128"/>
-      <c r="I55" s="133"/>
+      <c r="F55" s="130" t="s">
+        <v>302</v>
+      </c>
+      <c r="G55" s="131" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H55" s="127"/>
+      <c r="I55" s="132"/>
     </row>
     <row r="56" spans="2:9" ht="68.400000000000006" x14ac:dyDescent="0.3">
-      <c r="B56" s="127" t="s">
+      <c r="B56" s="126" t="s">
         <v>126</v>
       </c>
-      <c r="C56" s="128" t="s">
+      <c r="C56" s="127" t="s">
         <v>185</v>
       </c>
-      <c r="D56" s="129">
+      <c r="D56" s="128">
         <v>4.5</v>
       </c>
-      <c r="E56" s="130" t="s">
+      <c r="E56" s="129" t="s">
         <v>53</v>
       </c>
-      <c r="F56" s="131" t="s">
-        <v>309</v>
-      </c>
-      <c r="G56" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H56" s="128"/>
-      <c r="I56" s="133"/>
+      <c r="F56" s="130" t="s">
+        <v>302</v>
+      </c>
+      <c r="G56" s="131" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H56" s="127"/>
+      <c r="I56" s="132"/>
     </row>
     <row r="57" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B57" s="127" t="s">
+      <c r="B57" s="126" t="s">
         <v>128</v>
       </c>
-      <c r="C57" s="128" t="s">
+      <c r="C57" s="127" t="s">
         <v>127</v>
       </c>
-      <c r="D57" s="129">
+      <c r="D57" s="128">
         <v>1.2</v>
       </c>
-      <c r="E57" s="130" t="s">
+      <c r="E57" s="129" t="s">
         <v>53</v>
       </c>
-      <c r="F57" s="131" t="s">
-        <v>309</v>
-      </c>
-      <c r="G57" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H57" s="128"/>
-      <c r="I57" s="133"/>
+      <c r="F57" s="130" t="s">
+        <v>302</v>
+      </c>
+      <c r="G57" s="131" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H57" s="127"/>
+      <c r="I57" s="132"/>
     </row>
     <row r="58" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B58" s="127" t="s">
+      <c r="B58" s="126" t="s">
         <v>182</v>
       </c>
-      <c r="C58" s="128" t="s">
+      <c r="C58" s="127" t="s">
         <v>183</v>
       </c>
-      <c r="D58" s="129">
+      <c r="D58" s="128">
         <v>2.2999999999999998</v>
       </c>
-      <c r="E58" s="130" t="s">
+      <c r="E58" s="129" t="s">
         <v>53</v>
       </c>
-      <c r="F58" s="131" t="s">
-        <v>309</v>
-      </c>
-      <c r="G58" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H58" s="128"/>
-      <c r="I58" s="133"/>
+      <c r="F58" s="130" t="s">
+        <v>302</v>
+      </c>
+      <c r="G58" s="131" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H58" s="127"/>
+      <c r="I58" s="132"/>
     </row>
     <row r="59" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B59" s="127" t="s">
+      <c r="B59" s="126" t="s">
         <v>129</v>
       </c>
-      <c r="C59" s="128" t="s">
+      <c r="C59" s="127" t="s">
         <v>186</v>
       </c>
-      <c r="D59" s="129">
+      <c r="D59" s="128">
         <v>3</v>
       </c>
-      <c r="E59" s="130" t="s">
+      <c r="E59" s="129" t="s">
         <v>53</v>
       </c>
-      <c r="F59" s="131" t="s">
-        <v>309</v>
-      </c>
-      <c r="G59" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H59" s="128"/>
-      <c r="I59" s="133"/>
+      <c r="F59" s="130" t="s">
+        <v>302</v>
+      </c>
+      <c r="G59" s="131" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H59" s="127"/>
+      <c r="I59" s="132"/>
     </row>
     <row r="60" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B60" s="127" t="s">
+      <c r="B60" s="126" t="s">
         <v>181</v>
       </c>
-      <c r="C60" s="128" t="s">
+      <c r="C60" s="127" t="s">
         <v>187</v>
       </c>
-      <c r="D60" s="129">
+      <c r="D60" s="128">
         <v>2</v>
       </c>
-      <c r="E60" s="130" t="s">
+      <c r="E60" s="129" t="s">
         <v>53</v>
       </c>
-      <c r="F60" s="131" t="s">
-        <v>309</v>
-      </c>
-      <c r="G60" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H60" s="128"/>
-      <c r="I60" s="133"/>
+      <c r="F60" s="130" t="s">
+        <v>302</v>
+      </c>
+      <c r="G60" s="131" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H60" s="127"/>
+      <c r="I60" s="132"/>
     </row>
     <row r="61" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B61" s="136"/>
-      <c r="C61" s="137"/>
-      <c r="D61" s="138"/>
-      <c r="E61" s="138"/>
-      <c r="F61" s="139"/>
-      <c r="G61" s="140" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H61" s="137"/>
-      <c r="I61" s="154"/>
+      <c r="B61" s="135"/>
+      <c r="C61" s="136"/>
+      <c r="D61" s="137"/>
+      <c r="E61" s="137"/>
+      <c r="F61" s="138"/>
+      <c r="G61" s="139" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H61" s="136"/>
+      <c r="I61" s="153"/>
     </row>
     <row r="62" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B62" s="158" t="s">
+      <c r="B62" s="157" t="s">
+        <v>315</v>
+      </c>
+      <c r="C62" s="158"/>
+      <c r="D62" s="159"/>
+      <c r="E62" s="159"/>
+      <c r="F62" s="160"/>
+      <c r="G62" s="159"/>
+      <c r="H62" s="161"/>
+      <c r="I62" s="162"/>
+    </row>
+    <row r="63" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="B63" s="126" t="s">
+        <v>165</v>
+      </c>
+      <c r="C63" s="127" t="s">
+        <v>103</v>
+      </c>
+      <c r="D63" s="128">
+        <v>40</v>
+      </c>
+      <c r="E63" s="129" t="s">
+        <v>55</v>
+      </c>
+      <c r="F63" s="130" t="s">
         <v>322</v>
       </c>
-      <c r="C62" s="159"/>
-      <c r="D62" s="160"/>
-      <c r="E62" s="160"/>
-      <c r="F62" s="161"/>
-      <c r="G62" s="160"/>
-      <c r="H62" s="162"/>
-      <c r="I62" s="163"/>
-    </row>
-    <row r="63" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B63" s="127" t="s">
-        <v>165</v>
-      </c>
-      <c r="C63" s="128" t="s">
-        <v>103</v>
-      </c>
-      <c r="D63" s="129">
-        <v>40</v>
-      </c>
-      <c r="E63" s="130" t="s">
-        <v>55</v>
-      </c>
-      <c r="F63" s="131" t="s">
-        <v>329</v>
-      </c>
-      <c r="G63" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H63" s="128"/>
-      <c r="I63" s="133">
+      <c r="G63" s="131" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H63" s="127"/>
+      <c r="I63" s="132">
         <v>5</v>
       </c>
     </row>
     <row r="64" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B64" s="127" t="s">
-        <v>345</v>
-      </c>
-      <c r="C64" s="128" t="s">
+      <c r="B64" s="126" t="s">
+        <v>337</v>
+      </c>
+      <c r="C64" s="127" t="s">
         <v>166</v>
       </c>
-      <c r="D64" s="157">
+      <c r="D64" s="156">
         <f>D18</f>
         <v>1435</v>
       </c>
-      <c r="E64" s="130" t="s">
+      <c r="E64" s="129" t="s">
         <v>54</v>
       </c>
-      <c r="F64" s="131" t="s">
-        <v>329</v>
-      </c>
-      <c r="G64" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H64" s="128"/>
-      <c r="I64" s="133"/>
+      <c r="F64" s="130" t="s">
+        <v>322</v>
+      </c>
+      <c r="G64" s="131" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H64" s="127"/>
+      <c r="I64" s="132"/>
     </row>
     <row r="65" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B65" s="127" t="s">
+      <c r="B65" s="126" t="s">
         <v>102</v>
       </c>
-      <c r="C65" s="128" t="s">
+      <c r="C65" s="127" t="s">
         <v>104</v>
       </c>
-      <c r="D65" s="129">
+      <c r="D65" s="128">
         <v>20</v>
       </c>
-      <c r="E65" s="130" t="s">
+      <c r="E65" s="129" t="s">
         <v>55</v>
       </c>
-      <c r="F65" s="131" t="s">
-        <v>329</v>
-      </c>
-      <c r="G65" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H65" s="128"/>
-      <c r="I65" s="133"/>
+      <c r="F65" s="130" t="s">
+        <v>322</v>
+      </c>
+      <c r="G65" s="131" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H65" s="127"/>
+      <c r="I65" s="132"/>
     </row>
     <row r="66" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="B66" s="127" t="s">
+      <c r="B66" s="126" t="s">
         <v>113</v>
       </c>
-      <c r="C66" s="128" t="s">
+      <c r="C66" s="127" t="s">
         <v>106</v>
       </c>
-      <c r="D66" s="129">
+      <c r="D66" s="128">
         <v>6</v>
       </c>
-      <c r="E66" s="130" t="s">
+      <c r="E66" s="129" t="s">
         <v>53</v>
       </c>
-      <c r="F66" s="131" t="s">
-        <v>329</v>
-      </c>
-      <c r="G66" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H66" s="128"/>
-      <c r="I66" s="133"/>
+      <c r="F66" s="130" t="s">
+        <v>322</v>
+      </c>
+      <c r="G66" s="131" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H66" s="127"/>
+      <c r="I66" s="132"/>
     </row>
     <row r="67" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="B67" s="127" t="s">
+      <c r="B67" s="126" t="s">
         <v>114</v>
       </c>
-      <c r="C67" s="128" t="s">
+      <c r="C67" s="127" t="s">
         <v>146</v>
       </c>
-      <c r="D67" s="157">
+      <c r="D67" s="156">
         <f>ROUND(D10/D66,0)</f>
         <v>6</v>
       </c>
-      <c r="E67" s="130" t="s">
+      <c r="E67" s="129" t="s">
         <v>115</v>
       </c>
-      <c r="F67" s="131" t="s">
-        <v>329</v>
-      </c>
-      <c r="G67" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H67" s="128"/>
-      <c r="I67" s="133"/>
+      <c r="F67" s="130" t="s">
+        <v>322</v>
+      </c>
+      <c r="G67" s="131" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H67" s="127"/>
+      <c r="I67" s="132"/>
     </row>
     <row r="68" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="B68" s="127" t="s">
+      <c r="B68" s="126" t="s">
         <v>116</v>
       </c>
-      <c r="C68" s="128" t="s">
+      <c r="C68" s="127" t="s">
         <v>147</v>
       </c>
-      <c r="D68" s="157">
+      <c r="D68" s="156">
         <f>ROUND(D11/D66,0)</f>
         <v>6</v>
       </c>
-      <c r="E68" s="130" t="s">
+      <c r="E68" s="129" t="s">
         <v>115</v>
       </c>
-      <c r="F68" s="131" t="s">
-        <v>329</v>
-      </c>
-      <c r="G68" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H68" s="128"/>
-      <c r="I68" s="133"/>
+      <c r="F68" s="130" t="s">
+        <v>322</v>
+      </c>
+      <c r="G68" s="131" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H68" s="127"/>
+      <c r="I68" s="132"/>
     </row>
     <row r="69" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B69" s="127" t="s">
+      <c r="B69" s="126" t="s">
         <v>117</v>
       </c>
-      <c r="C69" s="128" t="s">
+      <c r="C69" s="127" t="s">
         <v>118</v>
       </c>
-      <c r="D69" s="157">
+      <c r="D69" s="156">
         <f>D68*D67</f>
         <v>36</v>
       </c>
-      <c r="E69" s="130" t="s">
+      <c r="E69" s="129" t="s">
         <v>115</v>
       </c>
-      <c r="F69" s="131" t="s">
+      <c r="F69" s="130" t="s">
+        <v>322</v>
+      </c>
+      <c r="G69" s="131" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H69" s="127"/>
+      <c r="I69" s="132"/>
+    </row>
+    <row r="70" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="B70" s="126" t="s">
+        <v>105</v>
+      </c>
+      <c r="C70" s="127" t="s">
         <v>329</v>
       </c>
-      <c r="G69" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H69" s="128"/>
-      <c r="I69" s="133"/>
-    </row>
-    <row r="70" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
-      <c r="B70" s="127" t="s">
-        <v>105</v>
-      </c>
-      <c r="C70" s="128" t="s">
-        <v>336</v>
-      </c>
-      <c r="D70" s="129">
+      <c r="D70" s="128">
         <v>0.25</v>
       </c>
-      <c r="E70" s="130" t="s">
+      <c r="E70" s="129" t="s">
         <v>53</v>
       </c>
-      <c r="F70" s="131" t="s">
-        <v>329</v>
-      </c>
-      <c r="G70" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H70" s="128"/>
-      <c r="I70" s="133"/>
+      <c r="F70" s="130" t="s">
+        <v>322</v>
+      </c>
+      <c r="G70" s="131" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H70" s="127"/>
+      <c r="I70" s="132"/>
     </row>
     <row r="71" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
-      <c r="B71" s="127" t="s">
+      <c r="B71" s="126" t="s">
         <v>107</v>
       </c>
-      <c r="C71" s="128" t="s">
+      <c r="C71" s="127" t="s">
         <v>148</v>
       </c>
-      <c r="D71" s="129">
+      <c r="D71" s="128">
         <v>0.4</v>
       </c>
-      <c r="E71" s="130" t="s">
+      <c r="E71" s="129" t="s">
         <v>53</v>
       </c>
-      <c r="F71" s="131" t="s">
-        <v>329</v>
-      </c>
-      <c r="G71" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H71" s="128"/>
-      <c r="I71" s="133"/>
+      <c r="F71" s="130" t="s">
+        <v>322</v>
+      </c>
+      <c r="G71" s="131" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H71" s="127"/>
+      <c r="I71" s="132"/>
     </row>
     <row r="72" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
-      <c r="B72" s="127" t="s">
+      <c r="B72" s="126" t="s">
         <v>109</v>
       </c>
-      <c r="C72" s="128" t="s">
+      <c r="C72" s="127" t="s">
         <v>111</v>
       </c>
-      <c r="D72" s="129">
+      <c r="D72" s="128">
         <v>0.15</v>
       </c>
-      <c r="E72" s="130" t="s">
+      <c r="E72" s="129" t="s">
         <v>53</v>
       </c>
-      <c r="F72" s="131" t="s">
-        <v>329</v>
-      </c>
-      <c r="G72" s="132" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H72" s="128"/>
-      <c r="I72" s="133"/>
+      <c r="F72" s="130" t="s">
+        <v>322</v>
+      </c>
+      <c r="G72" s="131" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H72" s="127"/>
+      <c r="I72" s="132"/>
     </row>
     <row r="73" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
-      <c r="B73" s="127" t="s">
+      <c r="B73" s="126" t="s">
         <v>110</v>
       </c>
-      <c r="C73" s="128" t="s">
+      <c r="C73" s="127" t="s">
         <v>112</v>
       </c>
-      <c r="D73" s="129">
+      <c r="D73" s="128">
         <v>0.4</v>
       </c>
-      <c r="E73" s="130" t="s">
+      <c r="E73" s="129" t="s">
         <v>53</v>
       </c>
-      <c r="F73" s="131" t="s">
-        <v>329</v>
-      </c>
-      <c r="G73" s="132" t="str">
+      <c r="F73" s="130" t="s">
+        <v>322</v>
+      </c>
+      <c r="G73" s="131" t="str">
         <f t="shared" ref="G73:G76" si="1">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F73,"/Readme.md"),"Ver")</f>
         <v>Ver</v>
       </c>
-      <c r="H73" s="128"/>
-      <c r="I73" s="133"/>
+      <c r="H73" s="127"/>
+      <c r="I73" s="132"/>
     </row>
     <row r="74" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
-      <c r="B74" s="127" t="s">
+      <c r="B74" s="126" t="s">
         <v>119</v>
       </c>
-      <c r="C74" s="128" t="s">
+      <c r="C74" s="127" t="s">
         <v>121</v>
       </c>
-      <c r="D74" s="157">
+      <c r="D74" s="156">
         <f>(D10-D70)/D67</f>
         <v>5.791666666666667</v>
       </c>
-      <c r="E74" s="130" t="s">
+      <c r="E74" s="129" t="s">
         <v>53</v>
       </c>
-      <c r="F74" s="131" t="s">
-        <v>329</v>
-      </c>
-      <c r="G74" s="132" t="str">
+      <c r="F74" s="130" t="s">
+        <v>322</v>
+      </c>
+      <c r="G74" s="131" t="str">
         <f t="shared" si="1"/>
         <v>Ver</v>
       </c>
-      <c r="H74" s="128"/>
-      <c r="I74" s="133"/>
+      <c r="H74" s="127"/>
+      <c r="I74" s="132"/>
     </row>
     <row r="75" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
-      <c r="B75" s="127" t="s">
+      <c r="B75" s="126" t="s">
         <v>120</v>
       </c>
-      <c r="C75" s="128" t="s">
+      <c r="C75" s="127" t="s">
         <v>122</v>
       </c>
-      <c r="D75" s="157">
+      <c r="D75" s="156">
         <f>(D11-D71)/D68</f>
         <v>6.1000000000000005</v>
       </c>
-      <c r="E75" s="130" t="s">
+      <c r="E75" s="129" t="s">
         <v>53</v>
       </c>
-      <c r="F75" s="131" t="s">
-        <v>329</v>
-      </c>
-      <c r="G75" s="132" t="str">
+      <c r="F75" s="130" t="s">
+        <v>322</v>
+      </c>
+      <c r="G75" s="131" t="str">
         <f t="shared" si="1"/>
         <v>Ver</v>
       </c>
-      <c r="H75" s="128"/>
-      <c r="I75" s="133"/>
+      <c r="H75" s="127"/>
+      <c r="I75" s="132"/>
     </row>
     <row r="76" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B76" s="164"/>
-      <c r="C76" s="165"/>
-      <c r="D76" s="166"/>
-      <c r="E76" s="166"/>
-      <c r="F76" s="167"/>
-      <c r="G76" s="140" t="str">
+      <c r="B76" s="163"/>
+      <c r="C76" s="164"/>
+      <c r="D76" s="165"/>
+      <c r="E76" s="165"/>
+      <c r="F76" s="166"/>
+      <c r="G76" s="139" t="str">
         <f t="shared" si="1"/>
         <v>Ver</v>
       </c>
-      <c r="H76" s="165"/>
-      <c r="I76" s="116"/>
+      <c r="H76" s="164"/>
+      <c r="I76" s="115"/>
     </row>
     <row r="77" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B77" s="182" t="s">
-        <v>323</v>
-      </c>
-      <c r="C77" s="159"/>
-      <c r="D77" s="160"/>
-      <c r="E77" s="160"/>
-      <c r="F77" s="161"/>
-      <c r="G77" s="160"/>
-      <c r="H77" s="162"/>
-      <c r="I77" s="163"/>
+      <c r="B77" s="181" t="s">
+        <v>316</v>
+      </c>
+      <c r="C77" s="158"/>
+      <c r="D77" s="159"/>
+      <c r="E77" s="159"/>
+      <c r="F77" s="160"/>
+      <c r="G77" s="159"/>
+      <c r="H77" s="161"/>
+      <c r="I77" s="162"/>
     </row>
     <row r="78" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B78" s="127" t="s">
+      <c r="B78" s="126" t="s">
         <v>168</v>
       </c>
-      <c r="C78" s="177" t="s">
+      <c r="C78" s="176" t="s">
         <v>167</v>
       </c>
-      <c r="D78" s="178">
+      <c r="D78" s="177">
         <f>D64</f>
         <v>1435</v>
       </c>
-      <c r="E78" s="178" t="s">
+      <c r="E78" s="177" t="s">
         <v>54</v>
       </c>
-      <c r="F78" s="131" t="s">
-        <v>329</v>
-      </c>
-      <c r="G78" s="132" t="str">
+      <c r="F78" s="130" t="s">
+        <v>322</v>
+      </c>
+      <c r="G78" s="131" t="str">
         <f t="shared" ref="G78:G88" si="2">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F78,"/Readme.md"),"Ver")</f>
         <v>Ver</v>
       </c>
-      <c r="H78" s="128"/>
-      <c r="I78" s="133"/>
+      <c r="H78" s="127"/>
+      <c r="I78" s="132"/>
     </row>
     <row r="79" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="B79" s="127" t="s">
+      <c r="B79" s="126" t="s">
         <v>169</v>
       </c>
-      <c r="C79" s="177" t="s">
+      <c r="C79" s="176" t="s">
         <v>170</v>
       </c>
-      <c r="D79" s="178">
+      <c r="D79" s="177">
         <f>D78*D63</f>
         <v>57400</v>
       </c>
-      <c r="E79" s="178" t="s">
+      <c r="E79" s="177" t="s">
         <v>171</v>
       </c>
-      <c r="F79" s="131" t="s">
-        <v>329</v>
-      </c>
-      <c r="G79" s="132" t="str">
+      <c r="F79" s="130" t="s">
+        <v>322</v>
+      </c>
+      <c r="G79" s="131" t="str">
         <f t="shared" si="2"/>
         <v>Ver</v>
       </c>
-      <c r="H79" s="128"/>
-      <c r="I79" s="133"/>
+      <c r="H79" s="127"/>
+      <c r="I79" s="132"/>
     </row>
     <row r="80" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B80" s="127" t="s">
+      <c r="B80" s="126" t="s">
         <v>180</v>
       </c>
-      <c r="C80" s="177" t="s">
+      <c r="C80" s="176" t="s">
         <v>179</v>
       </c>
-      <c r="D80" s="178">
+      <c r="D80" s="177">
         <f>D49</f>
         <v>52.943999999999996</v>
       </c>
-      <c r="E80" s="178" t="s">
+      <c r="E80" s="177" t="s">
         <v>54</v>
       </c>
-      <c r="F80" s="131" t="s">
-        <v>329</v>
-      </c>
-      <c r="G80" s="132" t="str">
+      <c r="F80" s="130" t="s">
+        <v>322</v>
+      </c>
+      <c r="G80" s="131" t="str">
         <f t="shared" si="2"/>
         <v>Ver</v>
       </c>
-      <c r="H80" s="179"/>
-      <c r="I80" s="114"/>
+      <c r="H80" s="178"/>
+      <c r="I80" s="113"/>
     </row>
     <row r="81" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B81" s="127" t="s">
+      <c r="B81" s="126" t="s">
         <v>173</v>
       </c>
-      <c r="C81" s="177" t="s">
+      <c r="C81" s="176" t="s">
         <v>174</v>
       </c>
-      <c r="D81" s="178">
+      <c r="D81" s="177">
         <f>D69</f>
         <v>36</v>
       </c>
-      <c r="E81" s="178" t="s">
+      <c r="E81" s="177" t="s">
         <v>115</v>
       </c>
-      <c r="F81" s="131" t="s">
-        <v>329</v>
-      </c>
-      <c r="G81" s="132" t="str">
+      <c r="F81" s="130" t="s">
+        <v>322</v>
+      </c>
+      <c r="G81" s="131" t="str">
         <f t="shared" si="2"/>
         <v>Ver</v>
       </c>
-      <c r="H81" s="179"/>
-      <c r="I81" s="114"/>
+      <c r="H81" s="178"/>
+      <c r="I81" s="113"/>
     </row>
     <row r="82" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="B82" s="127" t="s">
+      <c r="B82" s="126" t="s">
         <v>175</v>
       </c>
-      <c r="C82" s="177" t="s">
+      <c r="C82" s="176" t="s">
         <v>176</v>
       </c>
-      <c r="D82" s="178">
+      <c r="D82" s="177">
         <f>D81*D12</f>
         <v>432</v>
       </c>
-      <c r="E82" s="178" t="s">
+      <c r="E82" s="177" t="s">
         <v>53</v>
       </c>
-      <c r="F82" s="131" t="s">
-        <v>329</v>
-      </c>
-      <c r="G82" s="132" t="str">
+      <c r="F82" s="130" t="s">
+        <v>322</v>
+      </c>
+      <c r="G82" s="131" t="str">
         <f t="shared" si="2"/>
         <v>Ver</v>
       </c>
-      <c r="H82" s="179"/>
-      <c r="I82" s="114"/>
+      <c r="H82" s="178"/>
+      <c r="I82" s="113"/>
     </row>
     <row r="83" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="B83" s="127" t="s">
+      <c r="B83" s="126" t="s">
         <v>177</v>
       </c>
-      <c r="C83" s="177" t="s">
+      <c r="C83" s="176" t="s">
         <v>178</v>
       </c>
-      <c r="D83" s="178">
+      <c r="D83" s="177">
         <f>((D67*D9)+(D68*D8))*INT(D12/D48)</f>
         <v>324</v>
       </c>
-      <c r="E83" s="178" t="s">
+      <c r="E83" s="177" t="s">
         <v>53</v>
       </c>
-      <c r="F83" s="131" t="s">
-        <v>329</v>
-      </c>
-      <c r="G83" s="132" t="str">
+      <c r="F83" s="130" t="s">
+        <v>322</v>
+      </c>
+      <c r="G83" s="131" t="str">
         <f t="shared" si="2"/>
         <v>Ver</v>
       </c>
-      <c r="H83" s="179"/>
-      <c r="I83" s="114"/>
+      <c r="H83" s="178"/>
+      <c r="I83" s="113"/>
     </row>
     <row r="84" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="B84" s="127" t="s">
+      <c r="B84" s="126" t="s">
         <v>188</v>
       </c>
-      <c r="C84" s="177" t="s">
+      <c r="C84" s="176" t="s">
         <v>191</v>
       </c>
-      <c r="D84" s="180" t="s">
+      <c r="D84" s="179" t="s">
         <v>190</v>
       </c>
-      <c r="E84" s="178" t="s">
+      <c r="E84" s="177" t="s">
         <v>54</v>
       </c>
-      <c r="F84" s="131" t="s">
-        <v>329</v>
-      </c>
-      <c r="G84" s="132" t="str">
+      <c r="F84" s="130" t="s">
+        <v>322</v>
+      </c>
+      <c r="G84" s="131" t="str">
         <f t="shared" si="2"/>
         <v>Ver</v>
       </c>
-      <c r="H84" s="179"/>
-      <c r="I84" s="114">
+      <c r="H84" s="178"/>
+      <c r="I84" s="113">
         <v>5</v>
       </c>
     </row>
     <row r="85" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B85" s="127" t="s">
+      <c r="B85" s="126" t="s">
         <v>189</v>
       </c>
-      <c r="C85" s="177" t="s">
+      <c r="C85" s="176" t="s">
         <v>192</v>
       </c>
-      <c r="D85" s="180">
+      <c r="D85" s="179">
         <v>2</v>
       </c>
-      <c r="E85" s="178" t="s">
+      <c r="E85" s="177" t="s">
         <v>115</v>
       </c>
-      <c r="F85" s="131" t="s">
-        <v>329</v>
-      </c>
-      <c r="G85" s="132" t="str">
+      <c r="F85" s="130" t="s">
+        <v>322</v>
+      </c>
+      <c r="G85" s="131" t="str">
         <f t="shared" si="2"/>
         <v>Ver</v>
       </c>
-      <c r="H85" s="179"/>
-      <c r="I85" s="114"/>
+      <c r="H85" s="178"/>
+      <c r="I85" s="113"/>
     </row>
     <row r="86" spans="2:9" ht="50.4" x14ac:dyDescent="0.3">
-      <c r="B86" s="127" t="s">
+      <c r="B86" s="126" t="s">
         <v>46</v>
       </c>
-      <c r="C86" s="177" t="s">
+      <c r="C86" s="176" t="s">
         <v>193</v>
       </c>
-      <c r="D86" s="180" t="s">
+      <c r="D86" s="179" t="s">
         <v>190</v>
       </c>
-      <c r="E86" s="178" t="s">
+      <c r="E86" s="177" t="s">
         <v>115</v>
       </c>
-      <c r="F86" s="131" t="s">
-        <v>329</v>
-      </c>
-      <c r="G86" s="132" t="str">
+      <c r="F86" s="130" t="s">
+        <v>322</v>
+      </c>
+      <c r="G86" s="131" t="str">
         <f t="shared" si="2"/>
         <v>Ver</v>
       </c>
-      <c r="H86" s="179"/>
-      <c r="I86" s="114"/>
+      <c r="H86" s="178"/>
+      <c r="I86" s="113"/>
     </row>
     <row r="87" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="B87" s="127" t="s">
+      <c r="B87" s="126" t="s">
         <v>47</v>
       </c>
-      <c r="C87" s="177" t="s">
+      <c r="C87" s="176" t="s">
         <v>194</v>
       </c>
-      <c r="D87" s="180" t="s">
+      <c r="D87" s="179" t="s">
         <v>190</v>
       </c>
-      <c r="E87" s="178" t="s">
+      <c r="E87" s="177" t="s">
         <v>115</v>
       </c>
-      <c r="F87" s="131" t="s">
-        <v>329</v>
-      </c>
-      <c r="G87" s="132" t="str">
+      <c r="F87" s="130" t="s">
+        <v>322</v>
+      </c>
+      <c r="G87" s="131" t="str">
         <f t="shared" si="2"/>
         <v>Ver</v>
       </c>
-      <c r="H87" s="179"/>
-      <c r="I87" s="114"/>
+      <c r="H87" s="178"/>
+      <c r="I87" s="113"/>
     </row>
     <row r="88" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B88" s="136"/>
-      <c r="C88" s="181"/>
-      <c r="D88" s="166"/>
-      <c r="E88" s="166"/>
-      <c r="F88" s="167"/>
-      <c r="G88" s="140" t="str">
+      <c r="B88" s="135"/>
+      <c r="C88" s="180"/>
+      <c r="D88" s="165"/>
+      <c r="E88" s="165"/>
+      <c r="F88" s="166"/>
+      <c r="G88" s="139" t="str">
         <f t="shared" si="2"/>
         <v>Ver</v>
       </c>
-      <c r="H88" s="165"/>
-      <c r="I88" s="116"/>
+      <c r="H88" s="164"/>
+      <c r="I88" s="115"/>
     </row>
     <row r="89" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B89" s="168" t="s">
+      <c r="B89" s="167" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="90" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="H90" s="141" t="s">
-        <v>270</v>
-      </c>
-      <c r="I90" s="120">
+      <c r="H90" s="140" t="s">
+        <v>264</v>
+      </c>
+      <c r="I90" s="119">
         <f>AVERAGE(I7:I88)</f>
         <v>5</v>
       </c>
     </row>
     <row r="91" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B91" s="47" t="s">
-        <v>333</v>
+      <c r="B91" s="46" t="s">
+        <v>326</v>
       </c>
     </row>
     <row r="92" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B92" s="146" t="s">
+      <c r="B92" s="145" t="s">
         <v>149</v>
       </c>
-      <c r="C92" s="169" t="s">
+      <c r="C92" s="168" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="93" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B93" s="170" t="s">
+      <c r="B93" s="169" t="s">
         <v>151</v>
       </c>
-      <c r="C93" s="171">
+      <c r="C93" s="170">
         <f>D17</f>
         <v>1925</v>
       </c>
     </row>
     <row r="94" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B94" s="170" t="s">
+      <c r="B94" s="169" t="s">
         <v>154</v>
       </c>
-      <c r="C94" s="171">
+      <c r="C94" s="170">
         <f>D18</f>
         <v>1435</v>
       </c>
     </row>
     <row r="95" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B95" s="170" t="s">
+      <c r="B95" s="169" t="s">
         <v>153</v>
       </c>
-      <c r="C95" s="171">
+      <c r="C95" s="170">
         <f>D46</f>
         <v>60</v>
       </c>
     </row>
     <row r="96" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B96" s="170" t="s">
+      <c r="B96" s="169" t="s">
         <v>45</v>
       </c>
-      <c r="C96" s="171">
+      <c r="C96" s="170">
         <f>D54</f>
         <v>7.0560000000000018</v>
       </c>
     </row>
     <row r="97" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B97" s="170" t="s">
+      <c r="B97" s="169" t="s">
         <v>44</v>
       </c>
-      <c r="C97" s="171">
+      <c r="C97" s="170">
         <f>D49</f>
         <v>52.943999999999996</v>
       </c>
     </row>
     <row r="98" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B98" s="172" t="s">
+      <c r="B98" s="171" t="s">
         <v>152</v>
       </c>
-      <c r="C98" s="173">
+      <c r="C98" s="172">
         <f>D19</f>
         <v>1495</v>
       </c>
     </row>
     <row r="99" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B99" s="174" t="s">
+      <c r="B99" s="173" t="s">
         <v>66</v>
       </c>
-      <c r="C99" s="175">
+      <c r="C99" s="174">
         <f>D20</f>
         <v>0.74545454545454548</v>
       </c>
     </row>
     <row r="100" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B100" s="164" t="s">
+      <c r="B100" s="163" t="s">
         <v>99</v>
       </c>
-      <c r="C100" s="176">
+      <c r="C100" s="175">
         <f>D21</f>
         <v>0.77662337662337666</v>
       </c>
@@ -5806,53 +5894,54 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDC0663E-105D-42EA-893B-DB8B7FE41FC2}">
-  <dimension ref="B2:I28"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="B2:I45"/>
+  <sheetFormatPr defaultRowHeight="16.8" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="2.5546875" customWidth="1"/>
-    <col min="2" max="2" width="30.77734375" customWidth="1"/>
-    <col min="3" max="3" width="50.77734375" customWidth="1"/>
-    <col min="4" max="5" width="10.77734375" customWidth="1"/>
-    <col min="6" max="6" width="7.77734375" style="56" customWidth="1"/>
-    <col min="7" max="7" width="3.77734375" customWidth="1"/>
-    <col min="8" max="8" width="30.77734375" style="56" customWidth="1"/>
-    <col min="9" max="9" width="12.77734375" style="39" customWidth="1"/>
-    <col min="10" max="10" width="2.77734375" customWidth="1"/>
+    <col min="1" max="1" width="2.5546875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="30.77734375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="50.77734375" style="1" customWidth="1"/>
+    <col min="4" max="5" width="10.77734375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="7.77734375" style="11" customWidth="1"/>
+    <col min="7" max="7" width="3.77734375" style="1" customWidth="1"/>
+    <col min="8" max="8" width="30.77734375" style="11" customWidth="1"/>
+    <col min="9" max="9" width="12.77734375" style="55" customWidth="1"/>
+    <col min="10" max="10" width="2.77734375" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="B2" s="2" t="s">
+    <row r="2" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B2" s="36" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="B3" s="9" t="s">
+    <row r="3" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B3" s="58" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="4" spans="2:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="74" t="s">
-        <v>222</v>
-      </c>
-      <c r="C4" s="74"/>
-      <c r="D4" s="74"/>
-      <c r="E4" s="74"/>
-      <c r="F4" s="74"/>
-      <c r="G4" s="74"/>
-      <c r="H4" s="74"/>
-      <c r="I4" s="74"/>
-    </row>
-    <row r="5" spans="2:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="79"/>
-      <c r="C5" s="79"/>
-      <c r="D5" s="79"/>
-      <c r="E5" s="79"/>
-      <c r="F5" s="79"/>
-      <c r="G5" s="79"/>
-      <c r="H5" s="79"/>
-      <c r="I5" s="79"/>
-    </row>
-    <row r="6" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B4" s="73" t="s">
+        <v>217</v>
+      </c>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
+    </row>
+    <row r="5" spans="2:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="B5" s="78"/>
+      <c r="C5" s="78"/>
+      <c r="D5" s="78"/>
+      <c r="E5" s="78"/>
+      <c r="F5" s="78"/>
+      <c r="G5" s="78"/>
+      <c r="H5" s="78"/>
+      <c r="I5" s="78"/>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B6" s="21" t="s">
         <v>36</v>
       </c>
@@ -5865,35 +5954,35 @@
       <c r="E6" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="F6" s="85" t="s">
+      <c r="F6" s="84" t="s">
         <v>38</v>
       </c>
-      <c r="G6" s="86"/>
+      <c r="G6" s="85"/>
       <c r="H6" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="I6" s="41" t="s">
+      <c r="I6" s="40" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="B7" s="5" t="s">
-        <v>351</v>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B7" s="37" t="s">
+        <v>343</v>
       </c>
       <c r="C7" s="17"/>
       <c r="D7" s="18"/>
       <c r="E7" s="18"/>
-      <c r="F7" s="89"/>
+      <c r="F7" s="88"/>
       <c r="G7" s="18"/>
-      <c r="H7" s="54"/>
-      <c r="I7" s="42"/>
-    </row>
-    <row r="8" spans="2:9" ht="57" x14ac:dyDescent="0.3">
+      <c r="H7" s="53"/>
+      <c r="I7" s="41"/>
+    </row>
+    <row r="8" spans="2:9" ht="57" x14ac:dyDescent="0.4">
       <c r="B8" s="16" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="D8" s="15">
         <v>1</v>
@@ -5901,24 +5990,24 @@
       <c r="E8" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="F8" s="87" t="s">
-        <v>329</v>
-      </c>
-      <c r="G8" s="81" t="str">
+      <c r="F8" s="86" t="s">
+        <v>322</v>
+      </c>
+      <c r="G8" s="80" t="str">
         <f t="shared" ref="G8:G21" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F8,"/Readme.md"),"Ver")</f>
         <v>Ver</v>
       </c>
       <c r="H8" s="19"/>
-      <c r="I8" s="43">
+      <c r="I8" s="42">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B9" s="16" t="s">
-        <v>212</v>
+        <v>347</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="D9" s="15">
         <v>1</v>
@@ -5926,22 +6015,22 @@
       <c r="E9" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="F9" s="87" t="s">
-        <v>329</v>
-      </c>
-      <c r="G9" s="81" t="str">
+      <c r="F9" s="86" t="s">
+        <v>322</v>
+      </c>
+      <c r="G9" s="80" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H9" s="19"/>
-      <c r="I9" s="43"/>
-    </row>
-    <row r="10" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="I9" s="42"/>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B10" s="16" t="s">
-        <v>211</v>
+        <v>348</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="D10" s="15">
         <v>1</v>
@@ -5949,22 +6038,22 @@
       <c r="E10" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="F10" s="87" t="s">
-        <v>329</v>
-      </c>
-      <c r="G10" s="81" t="str">
+      <c r="F10" s="86" t="s">
+        <v>322</v>
+      </c>
+      <c r="G10" s="80" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H10" s="19"/>
-      <c r="I10" s="43"/>
-    </row>
-    <row r="11" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="I10" s="42"/>
+    </row>
+    <row r="11" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B11" s="16" t="s">
+        <v>349</v>
+      </c>
+      <c r="C11" s="19" t="s">
         <v>213</v>
-      </c>
-      <c r="C11" s="19" t="s">
-        <v>218</v>
       </c>
       <c r="D11" s="15">
         <v>1</v>
@@ -5972,22 +6061,22 @@
       <c r="E11" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="F11" s="87" t="s">
-        <v>329</v>
-      </c>
-      <c r="G11" s="81" t="str">
+      <c r="F11" s="86" t="s">
+        <v>322</v>
+      </c>
+      <c r="G11" s="80" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H11" s="19"/>
-      <c r="I11" s="43"/>
-    </row>
-    <row r="12" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="I11" s="42"/>
+    </row>
+    <row r="12" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B12" s="27" t="s">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="D12" s="15">
         <v>1</v>
@@ -5995,22 +6084,22 @@
       <c r="E12" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="F12" s="87" t="s">
-        <v>329</v>
-      </c>
-      <c r="G12" s="81" t="str">
+      <c r="F12" s="86" t="s">
+        <v>322</v>
+      </c>
+      <c r="G12" s="80" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H12" s="28"/>
-      <c r="I12" s="44"/>
-    </row>
-    <row r="13" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="I12" s="43"/>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B13" s="27" t="s">
-        <v>214</v>
+        <v>351</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="D13" s="15">
         <v>1</v>
@@ -6018,17 +6107,17 @@
       <c r="E13" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="F13" s="87" t="s">
-        <v>329</v>
-      </c>
-      <c r="G13" s="81" t="str">
+      <c r="F13" s="86" t="s">
+        <v>322</v>
+      </c>
+      <c r="G13" s="80" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H13" s="28"/>
-      <c r="I13" s="44"/>
-    </row>
-    <row r="14" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="I13" s="43"/>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B14" s="16" t="s">
         <v>195</v>
       </c>
@@ -6041,17 +6130,17 @@
       <c r="E14" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="F14" s="87" t="s">
-        <v>309</v>
-      </c>
-      <c r="G14" s="81" t="str">
+      <c r="F14" s="86" t="s">
+        <v>302</v>
+      </c>
+      <c r="G14" s="80" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H14" s="19"/>
-      <c r="I14" s="43"/>
-    </row>
-    <row r="15" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="I14" s="42"/>
+    </row>
+    <row r="15" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B15" s="16" t="s">
         <v>196</v>
       </c>
@@ -6064,17 +6153,17 @@
       <c r="E15" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="F15" s="87" t="s">
-        <v>309</v>
-      </c>
-      <c r="G15" s="81" t="str">
+      <c r="F15" s="86" t="s">
+        <v>302</v>
+      </c>
+      <c r="G15" s="80" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H15" s="19"/>
-      <c r="I15" s="43"/>
-    </row>
-    <row r="16" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="I15" s="42"/>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B16" s="27" t="s">
         <v>197</v>
       </c>
@@ -6087,19 +6176,19 @@
       <c r="E16" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="F16" s="87" t="s">
-        <v>309</v>
-      </c>
-      <c r="G16" s="81" t="str">
+      <c r="F16" s="86" t="s">
+        <v>302</v>
+      </c>
+      <c r="G16" s="80" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H16" s="28"/>
-      <c r="I16" s="44"/>
-    </row>
-    <row r="17" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="I16" s="43"/>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B17" s="27" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="C17" s="19" t="s">
         <v>199</v>
@@ -6110,17 +6199,17 @@
       <c r="E17" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="F17" s="87" t="s">
-        <v>309</v>
-      </c>
-      <c r="G17" s="81" t="str">
+      <c r="F17" s="86" t="s">
+        <v>302</v>
+      </c>
+      <c r="G17" s="80" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H17" s="28"/>
-      <c r="I17" s="44"/>
-    </row>
-    <row r="18" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="I17" s="43"/>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B18" s="27" t="s">
         <v>198</v>
       </c>
@@ -6133,22 +6222,22 @@
       <c r="E18" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="F18" s="87" t="s">
-        <v>309</v>
-      </c>
-      <c r="G18" s="81" t="str">
+      <c r="F18" s="86" t="s">
+        <v>302</v>
+      </c>
+      <c r="G18" s="80" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H18" s="28"/>
-      <c r="I18" s="44"/>
-    </row>
-    <row r="19" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="I18" s="43"/>
+    </row>
+    <row r="19" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.4">
       <c r="B19" s="27" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="D19" s="29">
         <v>1</v>
@@ -6156,19 +6245,19 @@
       <c r="E19" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="F19" s="87" t="s">
-        <v>349</v>
-      </c>
-      <c r="G19" s="81" t="str">
+      <c r="F19" s="86" t="s">
+        <v>341</v>
+      </c>
+      <c r="G19" s="80" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H19" s="28"/>
-      <c r="I19" s="44"/>
-    </row>
-    <row r="20" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="I19" s="43"/>
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B20" s="27" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C20" s="19" t="s">
         <v>199</v>
@@ -6179,47 +6268,47 @@
       <c r="E20" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="F20" s="87" t="s">
-        <v>329</v>
-      </c>
-      <c r="G20" s="81" t="str">
+      <c r="F20" s="86" t="s">
+        <v>322</v>
+      </c>
+      <c r="G20" s="80" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H20" s="28"/>
-      <c r="I20" s="44"/>
-    </row>
-    <row r="21" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="I20" s="43"/>
+    </row>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B21" s="27"/>
       <c r="C21" s="28"/>
       <c r="D21" s="29"/>
       <c r="E21" s="29"/>
-      <c r="F21" s="90"/>
-      <c r="G21" s="82" t="str">
+      <c r="F21" s="89"/>
+      <c r="G21" s="81" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H21" s="28"/>
-      <c r="I21" s="44"/>
-    </row>
-    <row r="22" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="B22" s="5" t="s">
-        <v>324</v>
+      <c r="I21" s="43"/>
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B22" s="37" t="s">
+        <v>317</v>
       </c>
       <c r="C22" s="17"/>
       <c r="D22" s="18"/>
       <c r="E22" s="18"/>
-      <c r="F22" s="89"/>
+      <c r="F22" s="88"/>
       <c r="G22" s="18"/>
-      <c r="H22" s="54"/>
-      <c r="I22" s="42"/>
-    </row>
-    <row r="23" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="H22" s="53"/>
+      <c r="I22" s="41"/>
+    </row>
+    <row r="23" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.4">
       <c r="B23" s="16" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D23" s="30">
         <f>'2.ArquitectonicaEstructural'!D31-'2.ArquitectonicaEstructural'!D37-'2.ArquitectonicaEstructural'!D43</f>
@@ -6228,24 +6317,24 @@
       <c r="E23" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="F23" s="87" t="s">
-        <v>306</v>
-      </c>
-      <c r="G23" s="81" t="str">
+      <c r="F23" s="86" t="s">
+        <v>299</v>
+      </c>
+      <c r="G23" s="80" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F23,"/Readme.md"),"Ver")</f>
         <v>Ver</v>
       </c>
       <c r="H23" s="19"/>
-      <c r="I23" s="43">
+      <c r="I23" s="42">
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B24" s="16" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D24" s="20">
         <v>992</v>
@@ -6253,22 +6342,22 @@
       <c r="E24" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="F24" s="87" t="s">
-        <v>306</v>
-      </c>
-      <c r="G24" s="81" t="str">
+      <c r="F24" s="86" t="s">
+        <v>299</v>
+      </c>
+      <c r="G24" s="80" t="str">
         <f t="shared" ref="G24:G27" si="1">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F24,"/Readme.md"),"Ver")</f>
         <v>Ver</v>
       </c>
       <c r="H24" s="19"/>
-      <c r="I24" s="43"/>
-    </row>
-    <row r="25" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="I24" s="42"/>
+    </row>
+    <row r="25" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B25" s="16" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D25" s="20">
         <v>1950</v>
@@ -6276,22 +6365,22 @@
       <c r="E25" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="F25" s="87" t="s">
-        <v>306</v>
-      </c>
-      <c r="G25" s="81" t="str">
+      <c r="F25" s="86" t="s">
+        <v>299</v>
+      </c>
+      <c r="G25" s="80" t="str">
         <f t="shared" si="1"/>
         <v>Ver</v>
       </c>
       <c r="H25" s="19"/>
-      <c r="I25" s="43"/>
-    </row>
-    <row r="26" spans="2:9" ht="45.6" x14ac:dyDescent="0.3">
+      <c r="I25" s="42"/>
+    </row>
+    <row r="26" spans="2:9" ht="45.6" x14ac:dyDescent="0.4">
       <c r="B26" s="16" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D26" s="15">
         <f>INT(D23/(D24/1000*D25/1000))</f>
@@ -6300,36 +6389,158 @@
       <c r="E26" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="F26" s="87" t="s">
-        <v>306</v>
-      </c>
-      <c r="G26" s="81" t="str">
+      <c r="F26" s="86" t="s">
+        <v>299</v>
+      </c>
+      <c r="G26" s="80" t="str">
         <f t="shared" si="1"/>
         <v>Ver</v>
       </c>
       <c r="H26" s="19"/>
-      <c r="I26" s="43"/>
-    </row>
-    <row r="27" spans="2:9" ht="16.8" x14ac:dyDescent="0.3">
+      <c r="I26" s="42"/>
+    </row>
+    <row r="27" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B27" s="24"/>
       <c r="C27" s="25"/>
       <c r="D27" s="26"/>
       <c r="E27" s="26"/>
-      <c r="F27" s="88"/>
-      <c r="G27" s="82" t="str">
+      <c r="F27" s="87"/>
+      <c r="G27" s="81" t="str">
         <f t="shared" si="1"/>
         <v>Ver</v>
       </c>
       <c r="H27" s="25"/>
-      <c r="I27" s="45"/>
-    </row>
-    <row r="28" spans="2:9" ht="16.8" x14ac:dyDescent="0.4">
-      <c r="H28" s="46" t="s">
-        <v>270</v>
-      </c>
-      <c r="I28" s="57">
+      <c r="I27" s="44"/>
+    </row>
+    <row r="28" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="H28" s="45" t="s">
+        <v>264</v>
+      </c>
+      <c r="I28" s="55">
         <f>AVERAGE(I7:I27)</f>
         <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B29" s="185" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="30" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B30" s="37" t="s">
+        <v>357</v>
+      </c>
+      <c r="C30" s="186" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="31" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B31" s="187" t="s">
+        <v>353</v>
+      </c>
+      <c r="C31" s="188" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="32" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B32" s="187" t="s">
+        <v>354</v>
+      </c>
+      <c r="C32" s="188" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B33" s="187" t="s">
+        <v>355</v>
+      </c>
+      <c r="C33" s="188" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B34" s="189" t="s">
+        <v>356</v>
+      </c>
+      <c r="C34" s="190" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="36" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B36" s="1" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="37" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B37" s="37" t="s">
+        <v>357</v>
+      </c>
+      <c r="C37" s="186" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="38" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B38" s="187" t="s">
+        <v>364</v>
+      </c>
+      <c r="C38" s="188" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="39" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B39" s="187" t="s">
+        <v>368</v>
+      </c>
+      <c r="C39" s="188" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="40" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B40" s="187" t="s">
+        <v>369</v>
+      </c>
+      <c r="C40" s="188" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="41" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B41" s="187" t="s">
+        <v>370</v>
+      </c>
+      <c r="C41" s="188" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="42" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B42" s="187" t="s">
+        <v>372</v>
+      </c>
+      <c r="C42" s="188" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="43" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B43" s="187" t="s">
+        <v>373</v>
+      </c>
+      <c r="C43" s="188" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="44" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B44" s="187" t="s">
+        <v>374</v>
+      </c>
+      <c r="C44" s="188" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="45" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B45" s="189" t="s">
+        <v>365</v>
+      </c>
+      <c r="C45" s="190" t="s">
+        <v>366</v>
       </c>
     </row>
   </sheetData>
@@ -6357,7 +6568,7 @@
     <col min="6" max="6" width="7.77734375" style="11" customWidth="1"/>
     <col min="7" max="7" width="3.77734375" style="1" customWidth="1"/>
     <col min="8" max="8" width="30.77734375" style="11" customWidth="1"/>
-    <col min="9" max="9" width="12.77734375" style="57" customWidth="1"/>
+    <col min="9" max="9" width="12.77734375" style="55" customWidth="1"/>
     <col min="10" max="10" width="2.77734375" style="1" customWidth="1"/>
     <col min="11" max="16384" width="9.109375" style="1"/>
   </cols>
@@ -6369,30 +6580,30 @@
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B3" s="9" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
     </row>
     <row r="4" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="74" t="s">
-        <v>219</v>
-      </c>
-      <c r="C4" s="74"/>
-      <c r="D4" s="74"/>
-      <c r="E4" s="74"/>
-      <c r="F4" s="74"/>
-      <c r="G4" s="74"/>
-      <c r="H4" s="74"/>
-      <c r="I4" s="74"/>
+      <c r="B4" s="73" t="s">
+        <v>214</v>
+      </c>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B5" s="79"/>
-      <c r="C5" s="79"/>
-      <c r="D5" s="79"/>
-      <c r="E5" s="79"/>
-      <c r="F5" s="79"/>
-      <c r="G5" s="79"/>
-      <c r="H5" s="79"/>
-      <c r="I5" s="79"/>
+      <c r="B5" s="78"/>
+      <c r="C5" s="78"/>
+      <c r="D5" s="78"/>
+      <c r="E5" s="78"/>
+      <c r="F5" s="78"/>
+      <c r="G5" s="78"/>
+      <c r="H5" s="78"/>
+      <c r="I5" s="78"/>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B6" s="21" t="s">
@@ -6407,35 +6618,35 @@
       <c r="E6" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="F6" s="85" t="s">
+      <c r="F6" s="84" t="s">
         <v>38</v>
       </c>
-      <c r="G6" s="86"/>
+      <c r="G6" s="85"/>
       <c r="H6" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="I6" s="41" t="s">
+      <c r="I6" s="40" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B7" s="5" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
       <c r="C7" s="17"/>
       <c r="D7" s="18"/>
       <c r="E7" s="18"/>
-      <c r="F7" s="89"/>
+      <c r="F7" s="88"/>
       <c r="G7" s="18"/>
-      <c r="H7" s="54"/>
-      <c r="I7" s="42"/>
+      <c r="H7" s="53"/>
+      <c r="I7" s="41"/>
     </row>
     <row r="8" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B8" s="16" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="D8" s="20">
         <v>3</v>
@@ -6443,24 +6654,24 @@
       <c r="E8" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="F8" s="87" t="s">
-        <v>329</v>
-      </c>
-      <c r="G8" s="81" t="str">
+      <c r="F8" s="86" t="s">
+        <v>322</v>
+      </c>
+      <c r="G8" s="80" t="str">
         <f t="shared" ref="G8:G21" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F8,"/Readme.md"),"Ver")</f>
         <v>Ver</v>
       </c>
       <c r="H8" s="19"/>
-      <c r="I8" s="43">
+      <c r="I8" s="42">
         <v>5</v>
       </c>
     </row>
     <row r="9" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B9" s="16" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="D9" s="20">
         <v>2.5</v>
@@ -6468,45 +6679,45 @@
       <c r="E9" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="F9" s="87" t="s">
-        <v>329</v>
-      </c>
-      <c r="G9" s="81" t="str">
+      <c r="F9" s="86" t="s">
+        <v>322</v>
+      </c>
+      <c r="G9" s="80" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H9" s="19"/>
-      <c r="I9" s="43"/>
+      <c r="I9" s="42"/>
     </row>
     <row r="10" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B10" s="16" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="D10" s="20">
         <v>4</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>226</v>
-      </c>
-      <c r="F10" s="87" t="s">
-        <v>329</v>
-      </c>
-      <c r="G10" s="81" t="str">
+        <v>221</v>
+      </c>
+      <c r="F10" s="86" t="s">
+        <v>322</v>
+      </c>
+      <c r="G10" s="80" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H10" s="19"/>
-      <c r="I10" s="43"/>
+      <c r="I10" s="42"/>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B11" s="16" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="D11" s="20">
         <v>2</v>
@@ -6514,22 +6725,22 @@
       <c r="E11" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="F11" s="87" t="s">
-        <v>329</v>
-      </c>
-      <c r="G11" s="81" t="str">
+      <c r="F11" s="86" t="s">
+        <v>322</v>
+      </c>
+      <c r="G11" s="80" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H11" s="19"/>
-      <c r="I11" s="43"/>
+      <c r="I11" s="42"/>
     </row>
     <row r="12" spans="2:9" ht="33.6" x14ac:dyDescent="0.4">
       <c r="B12" s="16" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="D12" s="15">
         <f>D10*D11</f>
@@ -6538,22 +6749,22 @@
       <c r="E12" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="F12" s="87" t="s">
-        <v>329</v>
-      </c>
-      <c r="G12" s="81" t="str">
+      <c r="F12" s="86" t="s">
+        <v>322</v>
+      </c>
+      <c r="G12" s="80" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H12" s="19"/>
-      <c r="I12" s="43"/>
+      <c r="I12" s="42"/>
     </row>
     <row r="13" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B13" s="16" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="D13" s="20">
         <v>8</v>
@@ -6561,46 +6772,46 @@
       <c r="E13" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="F13" s="87" t="s">
-        <v>329</v>
-      </c>
-      <c r="G13" s="81" t="str">
+      <c r="F13" s="86" t="s">
+        <v>322</v>
+      </c>
+      <c r="G13" s="80" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H13" s="19"/>
-      <c r="I13" s="43"/>
+      <c r="I13" s="42"/>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B14" s="16" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="D14" s="15" t="str">
         <f>IF(D12&lt;=D13, "Cumple","No cumple")</f>
         <v>Cumple</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>239</v>
-      </c>
-      <c r="F14" s="87" t="s">
-        <v>329</v>
-      </c>
-      <c r="G14" s="81" t="str">
+        <v>234</v>
+      </c>
+      <c r="F14" s="86" t="s">
+        <v>322</v>
+      </c>
+      <c r="G14" s="80" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H14" s="19"/>
-      <c r="I14" s="43"/>
+      <c r="I14" s="42"/>
     </row>
     <row r="15" spans="2:9" ht="33.6" x14ac:dyDescent="0.4">
       <c r="B15" s="16" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="D15" s="20">
         <v>60</v>
@@ -6608,22 +6819,22 @@
       <c r="E15" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="F15" s="87" t="s">
-        <v>329</v>
-      </c>
-      <c r="G15" s="81" t="str">
+      <c r="F15" s="86" t="s">
+        <v>322</v>
+      </c>
+      <c r="G15" s="80" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H15" s="19"/>
-      <c r="I15" s="43"/>
+      <c r="I15" s="42"/>
     </row>
     <row r="16" spans="2:9" ht="33.6" x14ac:dyDescent="0.4">
       <c r="B16" s="16" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="D16" s="15">
         <f>D15*D10</f>
@@ -6632,127 +6843,127 @@
       <c r="E16" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="F16" s="87" t="s">
-        <v>329</v>
-      </c>
-      <c r="G16" s="81" t="str">
+      <c r="F16" s="86" t="s">
+        <v>322</v>
+      </c>
+      <c r="G16" s="80" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H16" s="19"/>
-      <c r="I16" s="43"/>
+      <c r="I16" s="42"/>
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B17" s="16"/>
       <c r="C17" s="19"/>
       <c r="D17" s="15"/>
       <c r="E17" s="15"/>
-      <c r="F17" s="87"/>
-      <c r="G17" s="82" t="str">
+      <c r="F17" s="86"/>
+      <c r="G17" s="81" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H17" s="19"/>
-      <c r="I17" s="43"/>
+      <c r="I17" s="42"/>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B18" s="5" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="C18" s="17"/>
       <c r="D18" s="18"/>
       <c r="E18" s="18"/>
-      <c r="F18" s="89"/>
+      <c r="F18" s="88"/>
       <c r="G18" s="18"/>
-      <c r="H18" s="54"/>
-      <c r="I18" s="42"/>
+      <c r="H18" s="53"/>
+      <c r="I18" s="41"/>
     </row>
     <row r="19" spans="2:9" ht="45.6" x14ac:dyDescent="0.4">
       <c r="B19" s="16" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="D19" s="20" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="E19" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="F19" s="87" t="s">
-        <v>329</v>
-      </c>
-      <c r="G19" s="81" t="str">
+      <c r="F19" s="86" t="s">
+        <v>322</v>
+      </c>
+      <c r="G19" s="80" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H19" s="19"/>
-      <c r="I19" s="43">
+      <c r="I19" s="42">
         <v>5</v>
       </c>
     </row>
     <row r="20" spans="2:9" ht="45.6" x14ac:dyDescent="0.4">
       <c r="B20" s="16" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="D20" s="20" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="E20" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="F20" s="87" t="s">
-        <v>329</v>
-      </c>
-      <c r="G20" s="81" t="str">
+      <c r="F20" s="86" t="s">
+        <v>322</v>
+      </c>
+      <c r="G20" s="80" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H20" s="19"/>
-      <c r="I20" s="43"/>
+      <c r="I20" s="42"/>
     </row>
     <row r="21" spans="2:9" ht="45.6" x14ac:dyDescent="0.4">
       <c r="B21" s="16" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="C21" s="19" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="D21" s="20" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="E21" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="F21" s="87" t="s">
-        <v>329</v>
-      </c>
-      <c r="G21" s="81" t="str">
+      <c r="F21" s="86" t="s">
+        <v>322</v>
+      </c>
+      <c r="G21" s="80" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H21" s="19"/>
-      <c r="I21" s="43"/>
+      <c r="I21" s="42"/>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B22" s="24"/>
       <c r="C22" s="25"/>
       <c r="D22" s="26"/>
       <c r="E22" s="26"/>
-      <c r="F22" s="88"/>
+      <c r="F22" s="87"/>
       <c r="G22" s="26"/>
       <c r="H22" s="25"/>
-      <c r="I22" s="45"/>
+      <c r="I22" s="44"/>
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="H23" s="46" t="s">
-        <v>270</v>
-      </c>
-      <c r="I23" s="57">
+      <c r="H23" s="45" t="s">
+        <v>264</v>
+      </c>
+      <c r="I23" s="55">
         <f>AVERAGE(I7:I22)</f>
         <v>5</v>
       </c>
@@ -6779,7 +6990,7 @@
     <col min="6" max="6" width="7.77734375" style="11" customWidth="1"/>
     <col min="7" max="7" width="3.77734375" style="1" customWidth="1"/>
     <col min="8" max="8" width="30.77734375" style="11" customWidth="1"/>
-    <col min="9" max="9" width="12.77734375" style="57" customWidth="1"/>
+    <col min="9" max="9" width="12.77734375" style="55" customWidth="1"/>
     <col min="10" max="10" width="2.77734375" style="1" customWidth="1"/>
     <col min="11" max="16384" width="9.109375" style="1"/>
   </cols>
@@ -6791,30 +7002,30 @@
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B3" s="9" t="s">
-        <v>325</v>
+        <v>318</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B4" s="74" t="s">
-        <v>253</v>
-      </c>
-      <c r="C4" s="74"/>
-      <c r="D4" s="74"/>
-      <c r="E4" s="74"/>
-      <c r="F4" s="74"/>
-      <c r="G4" s="74"/>
-      <c r="H4" s="74"/>
-      <c r="I4" s="74"/>
+      <c r="B4" s="73" t="s">
+        <v>248</v>
+      </c>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B5" s="79"/>
-      <c r="C5" s="79"/>
-      <c r="D5" s="79"/>
-      <c r="E5" s="79"/>
-      <c r="F5" s="79"/>
-      <c r="G5" s="79"/>
-      <c r="H5" s="79"/>
-      <c r="I5" s="79"/>
+      <c r="B5" s="78"/>
+      <c r="C5" s="78"/>
+      <c r="D5" s="78"/>
+      <c r="E5" s="78"/>
+      <c r="F5" s="78"/>
+      <c r="G5" s="78"/>
+      <c r="H5" s="78"/>
+      <c r="I5" s="78"/>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B6" s="21" t="s">
@@ -6829,23 +7040,23 @@
       <c r="E6" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="F6" s="83" t="s">
+      <c r="F6" s="82" t="s">
         <v>38</v>
       </c>
-      <c r="G6" s="84"/>
+      <c r="G6" s="83"/>
       <c r="H6" s="22" t="s">
         <v>26</v>
       </c>
-      <c r="I6" s="41" t="s">
+      <c r="I6" s="40" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B7" s="16" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="D7" s="20">
         <v>1</v>
@@ -6853,24 +7064,24 @@
       <c r="E7" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="F7" s="87" t="s">
-        <v>305</v>
-      </c>
-      <c r="G7" s="81" t="str">
+      <c r="F7" s="86" t="s">
+        <v>298</v>
+      </c>
+      <c r="G7" s="80" t="str">
         <f t="shared" ref="G7:G16" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F7,"/Readme.md"),"Ver")</f>
         <v>Ver</v>
       </c>
       <c r="H7" s="19"/>
-      <c r="I7" s="43">
+      <c r="I7" s="42">
         <v>5</v>
       </c>
     </row>
     <row r="8" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B8" s="16" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="D8" s="20">
         <v>1</v>
@@ -6878,22 +7089,22 @@
       <c r="E8" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="F8" s="87" t="s">
-        <v>305</v>
-      </c>
-      <c r="G8" s="81" t="str">
+      <c r="F8" s="86" t="s">
+        <v>298</v>
+      </c>
+      <c r="G8" s="80" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H8" s="19"/>
-      <c r="I8" s="43"/>
+      <c r="I8" s="42"/>
     </row>
     <row r="9" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B9" s="16" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
       <c r="D9" s="20">
         <v>1</v>
@@ -6901,22 +7112,22 @@
       <c r="E9" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="F9" s="87" t="s">
-        <v>305</v>
-      </c>
-      <c r="G9" s="81" t="str">
+      <c r="F9" s="86" t="s">
+        <v>298</v>
+      </c>
+      <c r="G9" s="80" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H9" s="19"/>
-      <c r="I9" s="43"/>
+      <c r="I9" s="42"/>
     </row>
     <row r="10" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B10" s="16" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="D10" s="20">
         <v>1</v>
@@ -6924,22 +7135,22 @@
       <c r="E10" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="F10" s="87" t="s">
-        <v>305</v>
-      </c>
-      <c r="G10" s="81" t="str">
+      <c r="F10" s="86" t="s">
+        <v>298</v>
+      </c>
+      <c r="G10" s="80" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H10" s="19"/>
-      <c r="I10" s="43"/>
+      <c r="I10" s="42"/>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B11" s="16" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="D11" s="20">
         <v>1</v>
@@ -6947,22 +7158,22 @@
       <c r="E11" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="F11" s="87" t="s">
-        <v>305</v>
-      </c>
-      <c r="G11" s="81" t="str">
+      <c r="F11" s="86" t="s">
+        <v>298</v>
+      </c>
+      <c r="G11" s="80" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H11" s="19"/>
-      <c r="I11" s="43"/>
+      <c r="I11" s="42"/>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B12" s="16" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="D12" s="20">
         <v>1</v>
@@ -6970,22 +7181,22 @@
       <c r="E12" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="F12" s="87" t="s">
-        <v>305</v>
-      </c>
-      <c r="G12" s="81" t="str">
+      <c r="F12" s="86" t="s">
+        <v>298</v>
+      </c>
+      <c r="G12" s="80" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H12" s="19"/>
-      <c r="I12" s="43"/>
+      <c r="I12" s="42"/>
     </row>
     <row r="13" spans="2:9" ht="33.6" x14ac:dyDescent="0.4">
       <c r="B13" s="16" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="D13" s="20">
         <v>1</v>
@@ -6993,22 +7204,22 @@
       <c r="E13" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="F13" s="87" t="s">
-        <v>305</v>
-      </c>
-      <c r="G13" s="81" t="str">
+      <c r="F13" s="86" t="s">
+        <v>298</v>
+      </c>
+      <c r="G13" s="80" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H13" s="19"/>
-      <c r="I13" s="43"/>
+      <c r="I13" s="42"/>
     </row>
     <row r="14" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B14" s="16" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="D14" s="20">
         <v>1</v>
@@ -7016,22 +7227,22 @@
       <c r="E14" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="F14" s="87" t="s">
-        <v>305</v>
-      </c>
-      <c r="G14" s="81" t="str">
+      <c r="F14" s="86" t="s">
+        <v>298</v>
+      </c>
+      <c r="G14" s="80" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H14" s="19"/>
-      <c r="I14" s="43"/>
-    </row>
-    <row r="15" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="I14" s="42"/>
+    </row>
+    <row r="15" spans="2:9" ht="33.6" x14ac:dyDescent="0.4">
       <c r="B15" s="16" t="s">
-        <v>258</v>
+        <v>345</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="D15" s="20">
         <v>1</v>
@@ -7039,34 +7250,34 @@
       <c r="E15" s="15" t="s">
         <v>115</v>
       </c>
-      <c r="F15" s="87" t="s">
-        <v>305</v>
-      </c>
-      <c r="G15" s="81" t="str">
+      <c r="F15" s="86" t="s">
+        <v>298</v>
+      </c>
+      <c r="G15" s="80" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H15" s="19"/>
-      <c r="I15" s="43"/>
+      <c r="I15" s="42"/>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B16" s="24"/>
       <c r="C16" s="25"/>
-      <c r="D16" s="40"/>
+      <c r="D16" s="39"/>
       <c r="E16" s="26"/>
-      <c r="F16" s="88"/>
-      <c r="G16" s="82" t="str">
+      <c r="F16" s="87"/>
+      <c r="G16" s="81" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
       <c r="H16" s="25"/>
-      <c r="I16" s="45"/>
+      <c r="I16" s="44"/>
     </row>
     <row r="17" spans="8:9" x14ac:dyDescent="0.4">
-      <c r="H17" s="46" t="s">
-        <v>270</v>
-      </c>
-      <c r="I17" s="57">
+      <c r="H17" s="45" t="s">
+        <v>264</v>
+      </c>
+      <c r="I17" s="55">
         <f>AVERAGE(I7:I16)</f>
         <v>5</v>
       </c>
@@ -7090,55 +7301,55 @@
     <col min="2" max="2" width="30.77734375" style="2" customWidth="1"/>
     <col min="3" max="3" width="50.77734375" style="2" customWidth="1"/>
     <col min="4" max="4" width="40.77734375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="7.77734375" style="53" customWidth="1"/>
+    <col min="5" max="5" width="7.77734375" style="52" customWidth="1"/>
     <col min="6" max="6" width="3.77734375" style="36" customWidth="1"/>
-    <col min="7" max="7" width="30.77734375" style="53" customWidth="1"/>
+    <col min="7" max="7" width="30.77734375" style="52" customWidth="1"/>
     <col min="8" max="8" width="12.77734375" style="31" customWidth="1"/>
     <col min="9" max="9" width="2.77734375" style="2" customWidth="1"/>
     <col min="10" max="16384" width="9.109375" style="2"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B2" s="72" t="s">
+      <c r="B2" s="71" t="s">
         <v>22</v>
       </c>
-      <c r="C2" s="72"/>
-      <c r="D2" s="72"/>
-      <c r="E2" s="72"/>
-      <c r="F2" s="72"/>
-      <c r="G2" s="72"/>
-      <c r="H2" s="72"/>
+      <c r="C2" s="71"/>
+      <c r="D2" s="71"/>
+      <c r="E2" s="71"/>
+      <c r="F2" s="71"/>
+      <c r="G2" s="71"/>
+      <c r="H2" s="71"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B3" s="80" t="s">
-        <v>326</v>
-      </c>
-      <c r="C3" s="80"/>
-      <c r="D3" s="80"/>
-      <c r="E3" s="80"/>
-      <c r="F3" s="80"/>
-      <c r="G3" s="80"/>
-      <c r="H3" s="80"/>
+      <c r="B3" s="79" t="s">
+        <v>319</v>
+      </c>
+      <c r="C3" s="79"/>
+      <c r="D3" s="79"/>
+      <c r="E3" s="79"/>
+      <c r="F3" s="79"/>
+      <c r="G3" s="79"/>
+      <c r="H3" s="79"/>
     </row>
     <row r="4" spans="2:8" s="36" customFormat="1" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="74" t="s">
-        <v>327</v>
-      </c>
-      <c r="C4" s="74"/>
-      <c r="D4" s="74"/>
-      <c r="E4" s="74"/>
-      <c r="F4" s="74"/>
-      <c r="G4" s="74"/>
-      <c r="H4" s="74"/>
+      <c r="B4" s="73" t="s">
+        <v>320</v>
+      </c>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73"/>
+      <c r="E4" s="73"/>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B5" s="79"/>
-      <c r="C5" s="79"/>
-      <c r="D5" s="79"/>
-      <c r="E5" s="79"/>
-      <c r="F5" s="79"/>
-      <c r="G5" s="79"/>
-      <c r="H5" s="79"/>
+      <c r="B5" s="78"/>
+      <c r="C5" s="78"/>
+      <c r="D5" s="78"/>
+      <c r="E5" s="78"/>
+      <c r="F5" s="78"/>
+      <c r="G5" s="78"/>
+      <c r="H5" s="78"/>
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B6" s="37" t="s">
@@ -7150,10 +7361,10 @@
       <c r="D6" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="83" t="s">
+      <c r="E6" s="82" t="s">
         <v>38</v>
       </c>
-      <c r="F6" s="84"/>
+      <c r="F6" s="83"/>
       <c r="G6" s="38" t="s">
         <v>26</v>
       </c>
@@ -7163,22 +7374,22 @@
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B7" s="16" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
       <c r="C7" s="19" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="D7" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E7" s="131" t="s">
-        <v>304</v>
-      </c>
-      <c r="F7" s="81" t="str">
+      <c r="E7" s="130" t="s">
+        <v>297</v>
+      </c>
+      <c r="F7" s="80" t="str">
         <f t="shared" ref="F7:F17" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",E7,"/Readme.md"),"Ver")</f>
         <v>Ver</v>
       </c>
-      <c r="G7" s="55"/>
+      <c r="G7" s="54"/>
       <c r="H7" s="8">
         <v>5</v>
       </c>
@@ -7188,185 +7399,185 @@
         <v>19</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="131" t="s">
-        <v>304</v>
-      </c>
-      <c r="F8" s="81" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="G8" s="55"/>
+      <c r="E8" s="130" t="s">
+        <v>297</v>
+      </c>
+      <c r="F8" s="80" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="G8" s="54"/>
       <c r="H8" s="8"/>
     </row>
     <row r="9" spans="2:8" ht="91.2" x14ac:dyDescent="0.3">
       <c r="B9" s="16" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="131" t="s">
-        <v>305</v>
-      </c>
-      <c r="F9" s="81" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="G9" s="55"/>
+      <c r="E9" s="130" t="s">
+        <v>298</v>
+      </c>
+      <c r="F9" s="80" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="G9" s="54"/>
       <c r="H9" s="8"/>
     </row>
     <row r="10" spans="2:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B10" s="16" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="E10" s="131" t="s">
-        <v>309</v>
-      </c>
-      <c r="F10" s="81" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="G10" s="55"/>
+      <c r="E10" s="130" t="s">
+        <v>302</v>
+      </c>
+      <c r="F10" s="80" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="G10" s="54"/>
       <c r="H10" s="8"/>
     </row>
     <row r="11" spans="2:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="B11" s="16" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="E11" s="131" t="s">
-        <v>309</v>
-      </c>
-      <c r="F11" s="81" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="G11" s="55"/>
+      <c r="E11" s="130" t="s">
+        <v>302</v>
+      </c>
+      <c r="F11" s="80" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="G11" s="54"/>
       <c r="H11" s="8"/>
     </row>
     <row r="12" spans="2:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B12" s="16" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E12" s="131" t="s">
-        <v>309</v>
-      </c>
-      <c r="F12" s="81" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="G12" s="55"/>
+      <c r="E12" s="130" t="s">
+        <v>302</v>
+      </c>
+      <c r="F12" s="80" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="G12" s="54"/>
       <c r="H12" s="8"/>
     </row>
     <row r="13" spans="2:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B13" s="16" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>313</v>
+        <v>306</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="E13" s="131" t="s">
-        <v>306</v>
-      </c>
-      <c r="F13" s="81" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="G13" s="55"/>
+        <v>287</v>
+      </c>
+      <c r="E13" s="130" t="s">
+        <v>299</v>
+      </c>
+      <c r="F13" s="80" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="G13" s="54"/>
       <c r="H13" s="8"/>
     </row>
     <row r="14" spans="2:8" ht="79.8" x14ac:dyDescent="0.3">
       <c r="B14" s="16" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="E14" s="131" t="s">
-        <v>305</v>
-      </c>
-      <c r="F14" s="81" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="G14" s="55"/>
+        <v>288</v>
+      </c>
+      <c r="E14" s="130" t="s">
+        <v>298</v>
+      </c>
+      <c r="F14" s="80" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="G14" s="54"/>
       <c r="H14" s="8"/>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B15" s="16" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="E15" s="55"/>
-      <c r="F15" s="81" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="G15" s="55"/>
+        <v>294</v>
+      </c>
+      <c r="E15" s="54"/>
+      <c r="F15" s="80" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="G15" s="54"/>
       <c r="H15" s="8"/>
     </row>
     <row r="16" spans="2:8" s="36" customFormat="1" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="B16" s="27" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C16" s="28" t="s">
-        <v>344</v>
-      </c>
-      <c r="D16" s="183" t="s">
-        <v>342</v>
-      </c>
-      <c r="E16" s="131" t="s">
-        <v>307</v>
-      </c>
-      <c r="F16" s="81" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="G16" s="184"/>
-      <c r="H16" s="185"/>
+        <v>336</v>
+      </c>
+      <c r="D16" s="182" t="s">
+        <v>335</v>
+      </c>
+      <c r="E16" s="130" t="s">
+        <v>300</v>
+      </c>
+      <c r="F16" s="80" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="G16" s="183"/>
+      <c r="H16" s="184"/>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B17" s="24"/>
       <c r="C17" s="25"/>
       <c r="D17" s="4"/>
       <c r="E17" s="33"/>
-      <c r="F17" s="82" t="str">
+      <c r="F17" s="81" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
@@ -7374,8 +7585,8 @@
       <c r="H17" s="6"/>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="G18" s="46" t="s">
-        <v>270</v>
+      <c r="G18" s="45" t="s">
+        <v>264</v>
       </c>
       <c r="H18" s="31">
         <f>AVERAGE(H7:H17)</f>

--- a/file/table/DAPC_ProyectoCAD.xlsx
+++ b/file/table/DAPC_ProyectoCAD.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4EB6E26-1BF2-4562-B01D-7EF0F9663201}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54D7A32B-19D4-4E07-83E2-F24C462D0126}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -312,7 +312,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="381">
   <si>
     <t>1. Especificaciones técnicas generales</t>
   </si>
@@ -1565,9 +1565,6 @@
     <t>Descolgada sin cielorraso</t>
   </si>
   <si>
-    <t>* Seguido de la nota descriptva de localización, indique el material, utilice los siguientes códigos:</t>
-  </si>
-  <si>
     <t>PVC</t>
   </si>
   <si>
@@ -1607,13 +1604,19 @@
     <t>Metálica en acero intermedio con resistencia mecánica.</t>
   </si>
   <si>
-    <t>Metálica en acero EMT con baja resistencia mecánica.</t>
-  </si>
-  <si>
     <t>Polímero termoplástico.</t>
   </si>
   <si>
     <t>Hebras de vidrio entrelazadas.</t>
+  </si>
+  <si>
+    <t>* Seguido de la nota descriptiva de localización, indique el material, utilice los siguientes códigos:</t>
+  </si>
+  <si>
+    <t>Material</t>
+  </si>
+  <si>
+    <t>Metálica en acero con baja resistencia mecánica.</t>
   </si>
 </sst>
 </file>
@@ -6468,12 +6471,12 @@
     </row>
     <row r="36" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B36" s="1" t="s">
-        <v>363</v>
+        <v>378</v>
       </c>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B37" s="37" t="s">
-        <v>357</v>
+        <v>379</v>
       </c>
       <c r="C37" s="186" t="s">
         <v>358</v>
@@ -6481,66 +6484,66 @@
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B38" s="187" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C38" s="188" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="39" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B39" s="187" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C39" s="188" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="40" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B40" s="187" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C40" s="188" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B41" s="187" t="s">
+        <v>369</v>
+      </c>
+      <c r="C41" s="188" t="s">
         <v>370</v>
-      </c>
-      <c r="C41" s="188" t="s">
-        <v>371</v>
       </c>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B42" s="187" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C42" s="188" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B43" s="187" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C43" s="188" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="44" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B44" s="187" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C44" s="188" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B45" s="189" t="s">
+        <v>364</v>
+      </c>
+      <c r="C45" s="190" t="s">
         <v>365</v>
-      </c>
-      <c r="C45" s="190" t="s">
-        <v>366</v>
       </c>
     </row>
   </sheetData>

--- a/file/table/DAPC_ProyectoCAD.xlsx
+++ b/file/table/DAPC_ProyectoCAD.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54D7A32B-19D4-4E07-83E2-F24C462D0126}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBBDAC5E-4133-4053-A724-37D205846020}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0.Inicio" sheetId="7" r:id="rId1"/>
@@ -312,7 +312,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="692" uniqueCount="381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="694" uniqueCount="383">
   <si>
     <t>1. Especificaciones técnicas generales</t>
   </si>
@@ -345,9 +345,6 @@
   </si>
   <si>
     <t>#</t>
-  </si>
-  <si>
-    <t>∑:</t>
   </si>
   <si>
     <t>Ingrese el código asignado a su grupo</t>
@@ -1535,36 +1532,9 @@
     <t>* Incluya notas descriptivas de localización del conducto, tubería o canaleta, utilice los siguientes códigos:</t>
   </si>
   <si>
-    <t>tpp</t>
-  </si>
-  <si>
-    <t>tpc</t>
-  </si>
-  <si>
-    <t>tpm</t>
-  </si>
-  <si>
-    <t>td</t>
-  </si>
-  <si>
-    <t>Nota</t>
-  </si>
-  <si>
     <t>Descripción</t>
   </si>
   <si>
-    <t>Por placa o piso</t>
-  </si>
-  <si>
-    <t>Por cielorraso, anclada o descolgada</t>
-  </si>
-  <si>
-    <t>Por muro</t>
-  </si>
-  <si>
-    <t>Descolgada sin cielorraso</t>
-  </si>
-  <si>
     <t>PVC</t>
   </si>
   <si>
@@ -1617,6 +1587,42 @@
   </si>
   <si>
     <t>Metálica en acero con baja resistencia mecánica.</t>
+  </si>
+  <si>
+    <t>Nota de localización</t>
+  </si>
+  <si>
+    <t>Embebida por placa o piso.</t>
+  </si>
+  <si>
+    <t>Por cielorraso, anclada o descolgada.</t>
+  </si>
+  <si>
+    <t>Tpp</t>
+  </si>
+  <si>
+    <t>Tpc</t>
+  </si>
+  <si>
+    <t>Tpm</t>
+  </si>
+  <si>
+    <t>Tam</t>
+  </si>
+  <si>
+    <t>Anclada a muro</t>
+  </si>
+  <si>
+    <t>Embebida en muro.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Descolgada sin cielorraso.  </t>
+  </si>
+  <si>
+    <t>Tdt</t>
+  </si>
+  <si>
+    <t>∑UDig:</t>
   </si>
 </sst>
 </file>
@@ -2380,16 +2386,322 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -2404,6 +2716,15 @@
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
@@ -2416,369 +2737,54 @@
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -3105,138 +3111,138 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="E1" s="99" t="s">
-        <v>328</v>
+      <c r="E1" s="76" t="s">
+        <v>327</v>
       </c>
     </row>
     <row r="2" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B2" s="46" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B3" s="100" t="s">
-        <v>321</v>
+      <c r="B3" s="77" t="s">
+        <v>320</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B4" s="101" t="s">
-        <v>35</v>
-      </c>
-      <c r="C4" s="101"/>
-      <c r="D4" s="101"/>
-      <c r="E4" s="101"/>
+      <c r="B4" s="156" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" s="156"/>
+      <c r="D4" s="156"/>
+      <c r="E4" s="156"/>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B5" s="101"/>
-      <c r="C5" s="101"/>
-      <c r="D5" s="101"/>
-      <c r="E5" s="101"/>
+      <c r="B5" s="156"/>
+      <c r="C5" s="156"/>
+      <c r="D5" s="156"/>
+      <c r="E5" s="156"/>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B6" s="101"/>
-      <c r="C6" s="101"/>
-      <c r="D6" s="101"/>
-      <c r="E6" s="101"/>
+      <c r="B6" s="156"/>
+      <c r="C6" s="156"/>
+      <c r="D6" s="156"/>
+      <c r="E6" s="156"/>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B7" s="102" t="s">
+      <c r="B7" s="163" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="103"/>
-      <c r="D7" s="103"/>
-      <c r="E7" s="104"/>
+      <c r="C7" s="164"/>
+      <c r="D7" s="164"/>
+      <c r="E7" s="165"/>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="65" t="s">
+      <c r="B8" s="166" t="s">
+        <v>11</v>
+      </c>
+      <c r="C8" s="167"/>
+      <c r="D8" s="167"/>
+      <c r="E8" s="168"/>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B9" s="169" t="s">
+        <v>2</v>
+      </c>
+      <c r="C9" s="170"/>
+      <c r="D9" s="170"/>
+      <c r="E9" s="171"/>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="166" t="s">
         <v>12</v>
       </c>
-      <c r="C8" s="66"/>
-      <c r="D8" s="66"/>
-      <c r="E8" s="67"/>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="105" t="s">
-        <v>2</v>
-      </c>
-      <c r="C9" s="106"/>
-      <c r="D9" s="106"/>
-      <c r="E9" s="107"/>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="65" t="s">
+      <c r="C10" s="167"/>
+      <c r="D10" s="167"/>
+      <c r="E10" s="168"/>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B11" s="172"/>
+      <c r="C11" s="173"/>
+      <c r="D11" s="173"/>
+      <c r="E11" s="174"/>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B12" s="169" t="s">
+        <v>19</v>
+      </c>
+      <c r="C12" s="170"/>
+      <c r="D12" s="170"/>
+      <c r="E12" s="171"/>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B13" s="166" t="s">
+        <v>17</v>
+      </c>
+      <c r="C13" s="167"/>
+      <c r="D13" s="167"/>
+      <c r="E13" s="168"/>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B14" s="172"/>
+      <c r="C14" s="173"/>
+      <c r="D14" s="173"/>
+      <c r="E14" s="174"/>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B15" s="78" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="78"/>
+      <c r="D15" s="78"/>
+      <c r="E15" s="78"/>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B16" s="79"/>
+      <c r="C16" s="79"/>
+      <c r="D16" s="79"/>
+      <c r="E16" s="79"/>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
+      <c r="B17" s="177" t="s">
         <v>13</v>
       </c>
-      <c r="C10" s="66"/>
-      <c r="D10" s="66"/>
-      <c r="E10" s="67"/>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B11" s="68"/>
-      <c r="C11" s="69"/>
-      <c r="D11" s="69"/>
-      <c r="E11" s="70"/>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B12" s="105" t="s">
-        <v>20</v>
-      </c>
-      <c r="C12" s="106"/>
-      <c r="D12" s="106"/>
-      <c r="E12" s="107"/>
-    </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="65" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13" s="66"/>
-      <c r="D13" s="66"/>
-      <c r="E13" s="67"/>
-    </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B14" s="68"/>
-      <c r="C14" s="69"/>
-      <c r="D14" s="69"/>
-      <c r="E14" s="70"/>
-    </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B15" s="108" t="s">
-        <v>21</v>
-      </c>
-      <c r="C15" s="108"/>
-      <c r="D15" s="108"/>
-      <c r="E15" s="108"/>
-    </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B16" s="109"/>
-      <c r="C16" s="109"/>
-      <c r="D16" s="109"/>
-      <c r="E16" s="109"/>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B17" s="72" t="s">
-        <v>14</v>
-      </c>
-      <c r="C17" s="72"/>
-      <c r="D17" s="72"/>
-      <c r="E17" s="72"/>
+      <c r="C17" s="177"/>
+      <c r="D17" s="177"/>
+      <c r="E17" s="177"/>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B18" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="110" t="s">
-        <v>29</v>
-      </c>
-      <c r="D18" s="111" t="s">
+      <c r="C18" s="80" t="s">
         <v>28</v>
+      </c>
+      <c r="D18" s="81" t="s">
+        <v>27</v>
       </c>
       <c r="E18" s="48" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B19" s="112">
+      <c r="B19" s="82">
         <v>1</v>
       </c>
       <c r="C19" s="34" t="s">
@@ -3245,13 +3251,13 @@
       <c r="D19" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="E19" s="113">
+      <c r="E19" s="83">
         <f t="shared" ref="E19:E28" si="0">IFERROR(RIGHT(D19,1)*1,0)</f>
         <v>1</v>
       </c>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="112">
+      <c r="B20" s="82">
         <v>2</v>
       </c>
       <c r="C20" s="34" t="s">
@@ -3260,13 +3266,13 @@
       <c r="D20" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="E20" s="113">
+      <c r="E20" s="83">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B21" s="112">
+      <c r="B21" s="82">
         <v>3</v>
       </c>
       <c r="C21" s="34" t="s">
@@ -3275,13 +3281,13 @@
       <c r="D21" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="E21" s="113">
+      <c r="E21" s="83">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="112">
+      <c r="B22" s="82">
         <v>4</v>
       </c>
       <c r="C22" s="34" t="s">
@@ -3290,13 +3296,13 @@
       <c r="D22" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="E22" s="113">
+      <c r="E22" s="83">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B23" s="112">
+      <c r="B23" s="82">
         <v>5</v>
       </c>
       <c r="C23" s="34" t="s">
@@ -3305,79 +3311,79 @@
       <c r="D23" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E23" s="113">
+      <c r="E23" s="83">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B24" s="112">
+      <c r="B24" s="82">
         <v>6</v>
       </c>
       <c r="C24" s="34" t="s">
         <v>8</v>
       </c>
       <c r="D24" s="13"/>
-      <c r="E24" s="113">
+      <c r="E24" s="83">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B25" s="112">
+      <c r="B25" s="82">
         <v>7</v>
       </c>
       <c r="C25" s="34" t="s">
         <v>8</v>
       </c>
       <c r="D25" s="13"/>
-      <c r="E25" s="113">
+      <c r="E25" s="83">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B26" s="112">
+      <c r="B26" s="82">
         <v>8</v>
       </c>
       <c r="C26" s="34" t="s">
         <v>8</v>
       </c>
       <c r="D26" s="13"/>
-      <c r="E26" s="113">
+      <c r="E26" s="83">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B27" s="112">
+      <c r="B27" s="82">
         <v>9</v>
       </c>
       <c r="C27" s="34" t="s">
         <v>8</v>
       </c>
       <c r="D27" s="13"/>
-      <c r="E27" s="113">
+      <c r="E27" s="83">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B28" s="114">
+      <c r="B28" s="84">
         <v>10</v>
       </c>
       <c r="C28" s="35" t="s">
         <v>8</v>
       </c>
       <c r="D28" s="14"/>
-      <c r="E28" s="115">
+      <c r="E28" s="85">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="D29" s="116" t="s">
-        <v>11</v>
+      <c r="D29" s="86" t="s">
+        <v>382</v>
       </c>
       <c r="E29" s="57">
         <f>SUM(E19:E28)</f>
@@ -3385,33 +3391,33 @@
       </c>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B31" s="72" t="s">
-        <v>257</v>
-      </c>
-      <c r="C31" s="72"/>
-      <c r="D31" s="72"/>
-      <c r="E31" s="72"/>
+      <c r="B31" s="177" t="s">
+        <v>256</v>
+      </c>
+      <c r="C31" s="177"/>
+      <c r="D31" s="177"/>
+      <c r="E31" s="177"/>
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B32" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="74" t="s">
-        <v>36</v>
-      </c>
-      <c r="D32" s="75"/>
+      <c r="C32" s="157" t="s">
+        <v>35</v>
+      </c>
+      <c r="D32" s="158"/>
       <c r="E32" s="48" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B33" s="49">
         <v>1</v>
       </c>
-      <c r="C33" s="76" t="s">
-        <v>258</v>
-      </c>
-      <c r="D33" s="77"/>
+      <c r="C33" s="159" t="s">
+        <v>257</v>
+      </c>
+      <c r="D33" s="160"/>
       <c r="E33" s="50">
         <f>'1.Tecnica'!I19</f>
         <v>5</v>
@@ -3421,10 +3427,10 @@
       <c r="B34" s="49">
         <v>2</v>
       </c>
-      <c r="C34" s="61" t="s">
-        <v>296</v>
-      </c>
-      <c r="D34" s="62"/>
+      <c r="C34" s="161" t="s">
+        <v>295</v>
+      </c>
+      <c r="D34" s="162"/>
       <c r="E34" s="50">
         <f>'1.Tecnica'!I19</f>
         <v>5</v>
@@ -3434,10 +3440,10 @@
       <c r="B35" s="49">
         <v>3</v>
       </c>
-      <c r="C35" s="61" t="s">
-        <v>259</v>
-      </c>
-      <c r="D35" s="62"/>
+      <c r="C35" s="161" t="s">
+        <v>258</v>
+      </c>
+      <c r="D35" s="162"/>
       <c r="E35" s="50">
         <f>'3.Electrica'!I28</f>
         <v>5</v>
@@ -3448,7 +3454,7 @@
         <v>4</v>
       </c>
       <c r="C36" s="59" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D36" s="60"/>
       <c r="E36" s="50">
@@ -3460,10 +3466,10 @@
       <c r="B37" s="49">
         <v>4</v>
       </c>
-      <c r="C37" s="61" t="s">
-        <v>260</v>
-      </c>
-      <c r="D37" s="62"/>
+      <c r="C37" s="161" t="s">
+        <v>259</v>
+      </c>
+      <c r="D37" s="162"/>
       <c r="E37" s="50">
         <f>'5.Planos'!I17</f>
         <v>5</v>
@@ -3473,10 +3479,10 @@
       <c r="B38" s="49">
         <v>5</v>
       </c>
-      <c r="C38" s="61" t="s">
-        <v>261</v>
-      </c>
-      <c r="D38" s="62"/>
+      <c r="C38" s="161" t="s">
+        <v>260</v>
+      </c>
+      <c r="D38" s="162"/>
       <c r="E38" s="50">
         <f>'6.Archivos'!H18</f>
         <v>5</v>
@@ -3486,11 +3492,11 @@
       <c r="B39" s="49">
         <v>6</v>
       </c>
-      <c r="C39" s="61" t="s">
-        <v>285</v>
-      </c>
-      <c r="D39" s="62"/>
-      <c r="E39" s="98">
+      <c r="C39" s="161" t="s">
+        <v>284</v>
+      </c>
+      <c r="D39" s="162"/>
+      <c r="E39" s="75">
         <v>5</v>
       </c>
     </row>
@@ -3498,17 +3504,17 @@
       <c r="B40" s="51">
         <v>7</v>
       </c>
-      <c r="C40" s="63" t="s">
-        <v>327</v>
-      </c>
-      <c r="D40" s="64"/>
+      <c r="C40" s="175" t="s">
+        <v>326</v>
+      </c>
+      <c r="D40" s="176"/>
       <c r="E40" s="56">
         <v>5</v>
       </c>
     </row>
     <row r="41" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="D41" s="117" t="s">
-        <v>264</v>
+      <c r="D41" s="87" t="s">
+        <v>263</v>
       </c>
       <c r="E41" s="57">
         <f>AVERAGE(E33:E40)</f>
@@ -3517,6 +3523,13 @@
     </row>
   </sheetData>
   <mergeCells count="18">
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="B13:E14"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="B31:E31"/>
+    <mergeCell ref="C37:D37"/>
     <mergeCell ref="B4:E5"/>
     <mergeCell ref="C32:D32"/>
     <mergeCell ref="C33:D33"/>
@@ -3528,13 +3541,6 @@
     <mergeCell ref="B9:E9"/>
     <mergeCell ref="B10:E11"/>
     <mergeCell ref="B12:E12"/>
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="B13:E14"/>
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="B31:E31"/>
-    <mergeCell ref="C37:D37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -3555,326 +3561,326 @@
     <col min="4" max="5" width="10.77734375" style="46" customWidth="1"/>
     <col min="6" max="6" width="7.77734375" style="46" customWidth="1"/>
     <col min="7" max="7" width="3.77734375" style="46" customWidth="1"/>
-    <col min="8" max="8" width="30.77734375" style="118" customWidth="1"/>
-    <col min="9" max="9" width="12.77734375" style="119" customWidth="1"/>
+    <col min="8" max="8" width="30.77734375" style="88" customWidth="1"/>
+    <col min="9" max="9" width="12.77734375" style="89" customWidth="1"/>
     <col min="10" max="10" width="2.77734375" style="46" customWidth="1"/>
     <col min="11" max="16384" width="9.109375" style="46"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="E1" s="99"/>
+      <c r="E1" s="76"/>
     </row>
     <row r="2" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B2" s="46" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B3" s="100" t="s">
+      <c r="B3" s="77" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B4" s="101" t="s">
+      <c r="B4" s="156" t="s">
+        <v>261</v>
+      </c>
+      <c r="C4" s="156"/>
+      <c r="D4" s="156"/>
+      <c r="E4" s="156"/>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B5" s="156"/>
+      <c r="C5" s="156"/>
+      <c r="D5" s="156"/>
+      <c r="E5" s="156"/>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B6" s="90" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="91" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" s="92" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6" s="92" t="s">
+        <v>48</v>
+      </c>
+      <c r="F6" s="178" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" s="179"/>
+      <c r="H6" s="91" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" s="93" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" ht="68.400000000000006" x14ac:dyDescent="0.3">
+      <c r="B7" s="94" t="s">
         <v>262</v>
       </c>
-      <c r="C4" s="101"/>
-      <c r="D4" s="101"/>
-      <c r="E4" s="101"/>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B5" s="101"/>
-      <c r="C5" s="101"/>
-      <c r="D5" s="101"/>
-      <c r="E5" s="101"/>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B6" s="120" t="s">
-        <v>36</v>
-      </c>
-      <c r="C6" s="121" t="s">
-        <v>37</v>
-      </c>
-      <c r="D6" s="122" t="s">
-        <v>48</v>
-      </c>
-      <c r="E6" s="122" t="s">
-        <v>49</v>
-      </c>
-      <c r="F6" s="123" t="s">
-        <v>38</v>
-      </c>
-      <c r="G6" s="124"/>
-      <c r="H6" s="121" t="s">
-        <v>26</v>
-      </c>
-      <c r="I6" s="125" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" ht="68.400000000000006" x14ac:dyDescent="0.3">
-      <c r="B7" s="126" t="s">
+      <c r="C7" s="95" t="s">
+        <v>339</v>
+      </c>
+      <c r="D7" s="67">
+        <v>1</v>
+      </c>
+      <c r="E7" s="97" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="98" t="s">
+        <v>322</v>
+      </c>
+      <c r="G7" s="99" t="str">
+        <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F7,"/Readme.md"),"Ver")</f>
+        <v>Ver</v>
+      </c>
+      <c r="H7" s="69"/>
+      <c r="I7" s="70">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="B8" s="94" t="s">
+        <v>266</v>
+      </c>
+      <c r="C8" s="95" t="s">
+        <v>306</v>
+      </c>
+      <c r="D8" s="67">
+        <v>1</v>
+      </c>
+      <c r="E8" s="97" t="s">
+        <v>307</v>
+      </c>
+      <c r="F8" s="98" t="s">
+        <v>296</v>
+      </c>
+      <c r="G8" s="99" t="str">
+        <f t="shared" ref="G8:G18" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F8,"/Readme.md"),"Ver")</f>
+        <v>Ver</v>
+      </c>
+      <c r="H8" s="69"/>
+      <c r="I8" s="70"/>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B9" s="94" t="s">
+        <v>264</v>
+      </c>
+      <c r="C9" s="95" t="s">
+        <v>265</v>
+      </c>
+      <c r="D9" s="67" t="s">
+        <v>308</v>
+      </c>
+      <c r="E9" s="97"/>
+      <c r="F9" s="98" t="s">
+        <v>296</v>
+      </c>
+      <c r="G9" s="99" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H9" s="69"/>
+      <c r="I9" s="70"/>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B10" s="94" t="s">
+        <v>268</v>
+      </c>
+      <c r="C10" s="95" t="s">
+        <v>269</v>
+      </c>
+      <c r="D10" s="67">
+        <v>1</v>
+      </c>
+      <c r="E10" s="97" t="s">
+        <v>15</v>
+      </c>
+      <c r="F10" s="98" t="s">
+        <v>297</v>
+      </c>
+      <c r="G10" s="99" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H10" s="69"/>
+      <c r="I10" s="70"/>
+    </row>
+    <row r="11" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="B11" s="94" t="s">
+        <v>267</v>
+      </c>
+      <c r="C11" s="95" t="s">
+        <v>270</v>
+      </c>
+      <c r="D11" s="67" t="s">
+        <v>308</v>
+      </c>
+      <c r="E11" s="97"/>
+      <c r="F11" s="98" t="s">
+        <v>298</v>
+      </c>
+      <c r="G11" s="99" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H11" s="69"/>
+      <c r="I11" s="70"/>
+    </row>
+    <row r="12" spans="2:9" ht="57" x14ac:dyDescent="0.3">
+      <c r="B12" s="94" t="s">
+        <v>276</v>
+      </c>
+      <c r="C12" s="95" t="s">
+        <v>271</v>
+      </c>
+      <c r="D12" s="67" t="s">
+        <v>308</v>
+      </c>
+      <c r="E12" s="97"/>
+      <c r="F12" s="98" t="s">
+        <v>299</v>
+      </c>
+      <c r="G12" s="99" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H12" s="69"/>
+      <c r="I12" s="70"/>
+    </row>
+    <row r="13" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="B13" s="94" t="s">
+        <v>277</v>
+      </c>
+      <c r="C13" s="95" t="s">
+        <v>272</v>
+      </c>
+      <c r="D13" s="67" t="s">
+        <v>308</v>
+      </c>
+      <c r="E13" s="97"/>
+      <c r="F13" s="98" t="s">
+        <v>300</v>
+      </c>
+      <c r="G13" s="99" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H13" s="69"/>
+      <c r="I13" s="70"/>
+    </row>
+    <row r="14" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="B14" s="94" t="s">
+        <v>278</v>
+      </c>
+      <c r="C14" s="95" t="s">
+        <v>343</v>
+      </c>
+      <c r="D14" s="67" t="s">
+        <v>308</v>
+      </c>
+      <c r="E14" s="97"/>
+      <c r="F14" s="98" t="s">
+        <v>297</v>
+      </c>
+      <c r="G14" s="99" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H14" s="69"/>
+      <c r="I14" s="70"/>
+    </row>
+    <row r="15" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="B15" s="94" t="s">
+        <v>273</v>
+      </c>
+      <c r="C15" s="95" t="s">
+        <v>279</v>
+      </c>
+      <c r="D15" s="67">
+        <v>1</v>
+      </c>
+      <c r="E15" s="97" t="s">
+        <v>15</v>
+      </c>
+      <c r="F15" s="98" t="s">
+        <v>301</v>
+      </c>
+      <c r="G15" s="99" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H15" s="69"/>
+      <c r="I15" s="70"/>
+    </row>
+    <row r="16" spans="2:9" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="94" t="s">
+        <v>274</v>
+      </c>
+      <c r="C16" s="95" t="s">
+        <v>280</v>
+      </c>
+      <c r="D16" s="67">
+        <v>1</v>
+      </c>
+      <c r="E16" s="97" t="s">
+        <v>15</v>
+      </c>
+      <c r="F16" s="98" t="s">
+        <v>301</v>
+      </c>
+      <c r="G16" s="99" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H16" s="69"/>
+      <c r="I16" s="70"/>
+    </row>
+    <row r="17" spans="2:9" ht="35.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="101" t="s">
+        <v>275</v>
+      </c>
+      <c r="C17" s="102" t="s">
+        <v>281</v>
+      </c>
+      <c r="D17" s="67">
+        <v>1</v>
+      </c>
+      <c r="E17" s="97" t="s">
+        <v>15</v>
+      </c>
+      <c r="F17" s="98" t="s">
+        <v>301</v>
+      </c>
+      <c r="G17" s="99" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H17" s="71"/>
+      <c r="I17" s="72"/>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B18" s="103"/>
+      <c r="C18" s="104"/>
+      <c r="D18" s="68"/>
+      <c r="E18" s="105"/>
+      <c r="F18" s="106"/>
+      <c r="G18" s="107" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H18" s="73"/>
+      <c r="I18" s="74"/>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="H19" s="108" t="s">
         <v>263</v>
       </c>
-      <c r="C7" s="127" t="s">
-        <v>340</v>
-      </c>
-      <c r="D7" s="90">
-        <v>1</v>
-      </c>
-      <c r="E7" s="129" t="s">
-        <v>16</v>
-      </c>
-      <c r="F7" s="130" t="s">
-        <v>323</v>
-      </c>
-      <c r="G7" s="131" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F7,"/Readme.md"),"Ver")</f>
-        <v>Ver</v>
-      </c>
-      <c r="H7" s="92"/>
-      <c r="I7" s="93">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B8" s="126" t="s">
-        <v>267</v>
-      </c>
-      <c r="C8" s="127" t="s">
-        <v>307</v>
-      </c>
-      <c r="D8" s="90">
-        <v>1</v>
-      </c>
-      <c r="E8" s="129" t="s">
-        <v>308</v>
-      </c>
-      <c r="F8" s="130" t="s">
-        <v>297</v>
-      </c>
-      <c r="G8" s="131" t="str">
-        <f t="shared" ref="G8:G18" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F8,"/Readme.md"),"Ver")</f>
-        <v>Ver</v>
-      </c>
-      <c r="H8" s="92"/>
-      <c r="I8" s="93"/>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B9" s="126" t="s">
-        <v>265</v>
-      </c>
-      <c r="C9" s="127" t="s">
-        <v>266</v>
-      </c>
-      <c r="D9" s="90" t="s">
-        <v>309</v>
-      </c>
-      <c r="E9" s="129"/>
-      <c r="F9" s="130" t="s">
-        <v>297</v>
-      </c>
-      <c r="G9" s="131" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H9" s="92"/>
-      <c r="I9" s="93"/>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B10" s="126" t="s">
-        <v>269</v>
-      </c>
-      <c r="C10" s="127" t="s">
-        <v>270</v>
-      </c>
-      <c r="D10" s="90">
-        <v>1</v>
-      </c>
-      <c r="E10" s="129" t="s">
-        <v>16</v>
-      </c>
-      <c r="F10" s="130" t="s">
-        <v>298</v>
-      </c>
-      <c r="G10" s="131" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H10" s="92"/>
-      <c r="I10" s="93"/>
-    </row>
-    <row r="11" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="B11" s="126" t="s">
-        <v>268</v>
-      </c>
-      <c r="C11" s="127" t="s">
-        <v>271</v>
-      </c>
-      <c r="D11" s="90" t="s">
-        <v>309</v>
-      </c>
-      <c r="E11" s="129"/>
-      <c r="F11" s="130" t="s">
-        <v>299</v>
-      </c>
-      <c r="G11" s="131" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H11" s="92"/>
-      <c r="I11" s="93"/>
-    </row>
-    <row r="12" spans="2:9" ht="57" x14ac:dyDescent="0.3">
-      <c r="B12" s="126" t="s">
-        <v>277</v>
-      </c>
-      <c r="C12" s="127" t="s">
-        <v>272</v>
-      </c>
-      <c r="D12" s="90" t="s">
-        <v>309</v>
-      </c>
-      <c r="E12" s="129"/>
-      <c r="F12" s="130" t="s">
-        <v>300</v>
-      </c>
-      <c r="G12" s="131" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H12" s="92"/>
-      <c r="I12" s="93"/>
-    </row>
-    <row r="13" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B13" s="126" t="s">
-        <v>278</v>
-      </c>
-      <c r="C13" s="127" t="s">
-        <v>273</v>
-      </c>
-      <c r="D13" s="90" t="s">
-        <v>309</v>
-      </c>
-      <c r="E13" s="129"/>
-      <c r="F13" s="130" t="s">
-        <v>301</v>
-      </c>
-      <c r="G13" s="131" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H13" s="92"/>
-      <c r="I13" s="93"/>
-    </row>
-    <row r="14" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="B14" s="126" t="s">
-        <v>279</v>
-      </c>
-      <c r="C14" s="127" t="s">
-        <v>344</v>
-      </c>
-      <c r="D14" s="90" t="s">
-        <v>309</v>
-      </c>
-      <c r="E14" s="129"/>
-      <c r="F14" s="130" t="s">
-        <v>298</v>
-      </c>
-      <c r="G14" s="131" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H14" s="92"/>
-      <c r="I14" s="93"/>
-    </row>
-    <row r="15" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
-      <c r="B15" s="126" t="s">
-        <v>274</v>
-      </c>
-      <c r="C15" s="127" t="s">
-        <v>280</v>
-      </c>
-      <c r="D15" s="90">
-        <v>1</v>
-      </c>
-      <c r="E15" s="129" t="s">
-        <v>16</v>
-      </c>
-      <c r="F15" s="130" t="s">
-        <v>302</v>
-      </c>
-      <c r="G15" s="131" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H15" s="92"/>
-      <c r="I15" s="93"/>
-    </row>
-    <row r="16" spans="2:9" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="126" t="s">
-        <v>275</v>
-      </c>
-      <c r="C16" s="127" t="s">
-        <v>281</v>
-      </c>
-      <c r="D16" s="90">
-        <v>1</v>
-      </c>
-      <c r="E16" s="129" t="s">
-        <v>16</v>
-      </c>
-      <c r="F16" s="130" t="s">
-        <v>302</v>
-      </c>
-      <c r="G16" s="131" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H16" s="92"/>
-      <c r="I16" s="93"/>
-    </row>
-    <row r="17" spans="2:9" ht="35.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="133" t="s">
-        <v>276</v>
-      </c>
-      <c r="C17" s="134" t="s">
-        <v>282</v>
-      </c>
-      <c r="D17" s="90">
-        <v>1</v>
-      </c>
-      <c r="E17" s="129" t="s">
-        <v>16</v>
-      </c>
-      <c r="F17" s="130" t="s">
-        <v>302</v>
-      </c>
-      <c r="G17" s="131" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H17" s="94"/>
-      <c r="I17" s="95"/>
-    </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B18" s="135"/>
-      <c r="C18" s="136"/>
-      <c r="D18" s="91"/>
-      <c r="E18" s="137"/>
-      <c r="F18" s="138"/>
-      <c r="G18" s="139" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H18" s="96"/>
-      <c r="I18" s="97"/>
-    </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="H19" s="140" t="s">
-        <v>264</v>
-      </c>
-      <c r="I19" s="119">
+      <c r="I19" s="89">
         <f>AVERAGE(I7:I18)</f>
         <v>5</v>
       </c>
@@ -3901,1983 +3907,1983 @@
     <col min="1" max="1" width="2.5546875" style="46" customWidth="1"/>
     <col min="2" max="2" width="30.77734375" style="46" customWidth="1"/>
     <col min="3" max="3" width="50.77734375" style="46" customWidth="1"/>
-    <col min="4" max="5" width="10.77734375" style="119" customWidth="1"/>
-    <col min="6" max="6" width="7.77734375" style="141" customWidth="1"/>
-    <col min="7" max="7" width="3.77734375" style="119" customWidth="1"/>
-    <col min="8" max="8" width="30.77734375" style="118" customWidth="1"/>
-    <col min="9" max="9" width="12.77734375" style="119" customWidth="1"/>
+    <col min="4" max="5" width="10.77734375" style="89" customWidth="1"/>
+    <col min="6" max="6" width="7.77734375" style="109" customWidth="1"/>
+    <col min="7" max="7" width="3.77734375" style="89" customWidth="1"/>
+    <col min="8" max="8" width="30.77734375" style="88" customWidth="1"/>
+    <col min="9" max="9" width="12.77734375" style="89" customWidth="1"/>
     <col min="10" max="10" width="2.5546875" style="46" customWidth="1"/>
     <col min="11" max="16384" width="9.109375" style="46"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B2" s="46" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B3" s="100" t="s">
+      <c r="B3" s="77" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B4" s="156" t="s">
+        <v>215</v>
+      </c>
+      <c r="C4" s="156"/>
+      <c r="D4" s="156"/>
+      <c r="E4" s="156"/>
+      <c r="F4" s="156"/>
+      <c r="G4" s="156"/>
+      <c r="H4" s="156"/>
+      <c r="I4" s="156"/>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B5" s="180"/>
+      <c r="C5" s="180"/>
+      <c r="D5" s="180"/>
+      <c r="E5" s="180"/>
+      <c r="F5" s="180"/>
+      <c r="G5" s="180"/>
+      <c r="H5" s="180"/>
+      <c r="I5" s="180"/>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B6" s="90" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="91" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" s="92" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6" s="92" t="s">
+        <v>48</v>
+      </c>
+      <c r="F6" s="181" t="s">
+        <v>37</v>
+      </c>
+      <c r="G6" s="182"/>
+      <c r="H6" s="91" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" s="93" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B7" s="110" t="s">
+        <v>310</v>
+      </c>
+      <c r="C7" s="111"/>
+      <c r="D7" s="112"/>
+      <c r="E7" s="112"/>
+      <c r="F7" s="113"/>
+      <c r="G7" s="112"/>
+      <c r="H7" s="114"/>
+      <c r="I7" s="115"/>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B8" s="94" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B4" s="101" t="s">
-        <v>216</v>
-      </c>
-      <c r="C4" s="101"/>
-      <c r="D4" s="101"/>
-      <c r="E4" s="101"/>
-      <c r="F4" s="101"/>
-      <c r="G4" s="101"/>
-      <c r="H4" s="101"/>
-      <c r="I4" s="101"/>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B5" s="142"/>
-      <c r="C5" s="142"/>
-      <c r="D5" s="142"/>
-      <c r="E5" s="142"/>
-      <c r="F5" s="142"/>
-      <c r="G5" s="142"/>
-      <c r="H5" s="142"/>
-      <c r="I5" s="142"/>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B6" s="120" t="s">
-        <v>36</v>
-      </c>
-      <c r="C6" s="121" t="s">
-        <v>37</v>
-      </c>
-      <c r="D6" s="122" t="s">
-        <v>48</v>
-      </c>
-      <c r="E6" s="122" t="s">
-        <v>49</v>
-      </c>
-      <c r="F6" s="143" t="s">
-        <v>38</v>
-      </c>
-      <c r="G6" s="144"/>
-      <c r="H6" s="121" t="s">
-        <v>26</v>
-      </c>
-      <c r="I6" s="125" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B7" s="145" t="s">
-        <v>311</v>
-      </c>
-      <c r="C7" s="146"/>
-      <c r="D7" s="147"/>
-      <c r="E7" s="147"/>
-      <c r="F7" s="148"/>
-      <c r="G7" s="147"/>
-      <c r="H7" s="149"/>
-      <c r="I7" s="150"/>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B8" s="126" t="s">
+      <c r="C8" s="95" t="s">
+        <v>158</v>
+      </c>
+      <c r="D8" s="96">
+        <v>8</v>
+      </c>
+      <c r="E8" s="97" t="s">
+        <v>52</v>
+      </c>
+      <c r="F8" s="98" t="s">
+        <v>298</v>
+      </c>
+      <c r="G8" s="99" t="str">
+        <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F8,"/Readme.md"),"Ver")</f>
+        <v>Ver</v>
+      </c>
+      <c r="H8" s="95" t="s">
+        <v>283</v>
+      </c>
+      <c r="I8" s="100">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B9" s="94" t="s">
         <v>157</v>
       </c>
-      <c r="C8" s="127" t="s">
+      <c r="C9" s="95" t="s">
         <v>159</v>
       </c>
-      <c r="D8" s="128">
-        <v>8</v>
-      </c>
-      <c r="E8" s="129" t="s">
-        <v>53</v>
-      </c>
-      <c r="F8" s="130" t="s">
-        <v>299</v>
-      </c>
-      <c r="G8" s="131" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F8,"/Readme.md"),"Ver")</f>
-        <v>Ver</v>
-      </c>
-      <c r="H8" s="127" t="s">
-        <v>284</v>
-      </c>
-      <c r="I8" s="132">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B9" s="126" t="s">
-        <v>158</v>
-      </c>
-      <c r="C9" s="127" t="s">
+      <c r="D9" s="96">
+        <v>10</v>
+      </c>
+      <c r="E9" s="97" t="s">
+        <v>52</v>
+      </c>
+      <c r="F9" s="98" t="s">
+        <v>298</v>
+      </c>
+      <c r="G9" s="99" t="str">
+        <f t="shared" ref="G9:G72" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F9,"/Readme.md"),"Ver")</f>
+        <v>Ver</v>
+      </c>
+      <c r="H9" s="95" t="s">
+        <v>283</v>
+      </c>
+      <c r="I9" s="100"/>
+    </row>
+    <row r="10" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="B10" s="94" t="s">
+        <v>162</v>
+      </c>
+      <c r="C10" s="95" t="s">
         <v>160</v>
       </c>
-      <c r="D9" s="128">
-        <v>10</v>
-      </c>
-      <c r="E9" s="129" t="s">
-        <v>53</v>
-      </c>
-      <c r="F9" s="130" t="s">
-        <v>299</v>
-      </c>
-      <c r="G9" s="131" t="str">
-        <f t="shared" ref="G9:G72" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F9,"/Readme.md"),"Ver")</f>
-        <v>Ver</v>
-      </c>
-      <c r="H9" s="127" t="s">
-        <v>284</v>
-      </c>
-      <c r="I9" s="132"/>
-    </row>
-    <row r="10" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B10" s="126" t="s">
-        <v>163</v>
-      </c>
-      <c r="C10" s="127" t="s">
-        <v>161</v>
-      </c>
-      <c r="D10" s="129">
+      <c r="D10" s="97">
         <f>D8+SumUDig</f>
         <v>35</v>
       </c>
-      <c r="E10" s="129" t="s">
-        <v>53</v>
-      </c>
-      <c r="F10" s="130" t="s">
-        <v>299</v>
-      </c>
-      <c r="G10" s="131" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H10" s="127"/>
-      <c r="I10" s="132"/>
+      <c r="E10" s="97" t="s">
+        <v>52</v>
+      </c>
+      <c r="F10" s="98" t="s">
+        <v>298</v>
+      </c>
+      <c r="G10" s="99" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H10" s="95"/>
+      <c r="I10" s="100"/>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B11" s="126" t="s">
-        <v>164</v>
-      </c>
-      <c r="C11" s="127" t="s">
-        <v>162</v>
-      </c>
-      <c r="D11" s="129" cm="1">
+      <c r="B11" s="94" t="s">
+        <v>163</v>
+      </c>
+      <c r="C11" s="95" t="s">
+        <v>161</v>
+      </c>
+      <c r="D11" s="97" cm="1">
         <f t="array" ref="D11">D9+SumUDig</f>
         <v>37</v>
       </c>
-      <c r="E11" s="129" t="s">
-        <v>53</v>
-      </c>
-      <c r="F11" s="130" t="s">
-        <v>299</v>
-      </c>
-      <c r="G11" s="131" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H11" s="127"/>
-      <c r="I11" s="132"/>
+      <c r="E11" s="97" t="s">
+        <v>52</v>
+      </c>
+      <c r="F11" s="98" t="s">
+        <v>298</v>
+      </c>
+      <c r="G11" s="99" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H11" s="95"/>
+      <c r="I11" s="100"/>
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B12" s="126" t="s">
+      <c r="B12" s="94" t="s">
+        <v>38</v>
+      </c>
+      <c r="C12" s="95" t="s">
+        <v>171</v>
+      </c>
+      <c r="D12" s="96">
+        <v>12</v>
+      </c>
+      <c r="E12" s="97" t="s">
+        <v>52</v>
+      </c>
+      <c r="F12" s="98" t="s">
+        <v>298</v>
+      </c>
+      <c r="G12" s="99" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H12" s="95" t="s">
+        <v>283</v>
+      </c>
+      <c r="I12" s="100"/>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B13" s="94" t="s">
+        <v>59</v>
+      </c>
+      <c r="C13" s="95" t="s">
+        <v>64</v>
+      </c>
+      <c r="D13" s="96">
+        <v>6</v>
+      </c>
+      <c r="E13" s="97" t="s">
+        <v>52</v>
+      </c>
+      <c r="F13" s="98" t="s">
+        <v>298</v>
+      </c>
+      <c r="G13" s="99" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H13" s="95" t="s">
+        <v>283</v>
+      </c>
+      <c r="I13" s="100"/>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B14" s="94" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="127" t="s">
-        <v>172</v>
-      </c>
-      <c r="D12" s="128">
+      <c r="C14" s="95" t="s">
+        <v>63</v>
+      </c>
+      <c r="D14" s="96">
         <v>12</v>
       </c>
-      <c r="E12" s="129" t="s">
-        <v>53</v>
-      </c>
-      <c r="F12" s="130" t="s">
-        <v>299</v>
-      </c>
-      <c r="G12" s="131" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H12" s="127" t="s">
-        <v>284</v>
-      </c>
-      <c r="I12" s="132"/>
-    </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B13" s="126" t="s">
+      <c r="E14" s="97" t="s">
+        <v>52</v>
+      </c>
+      <c r="F14" s="98" t="s">
+        <v>298</v>
+      </c>
+      <c r="G14" s="99" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H14" s="95" t="s">
+        <v>283</v>
+      </c>
+      <c r="I14" s="100"/>
+    </row>
+    <row r="15" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="B15" s="94" t="s">
+        <v>51</v>
+      </c>
+      <c r="C15" s="95" t="s">
         <v>60</v>
       </c>
-      <c r="C13" s="127" t="s">
-        <v>65</v>
-      </c>
-      <c r="D13" s="128">
-        <v>6</v>
-      </c>
-      <c r="E13" s="129" t="s">
-        <v>53</v>
-      </c>
-      <c r="F13" s="130" t="s">
-        <v>299</v>
-      </c>
-      <c r="G13" s="131" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H13" s="127" t="s">
-        <v>284</v>
-      </c>
-      <c r="I13" s="132"/>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B14" s="126" t="s">
-        <v>40</v>
-      </c>
-      <c r="C14" s="127" t="s">
-        <v>64</v>
-      </c>
-      <c r="D14" s="128">
-        <v>12</v>
-      </c>
-      <c r="E14" s="129" t="s">
-        <v>53</v>
-      </c>
-      <c r="F14" s="130" t="s">
-        <v>299</v>
-      </c>
-      <c r="G14" s="131" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H14" s="127" t="s">
-        <v>284</v>
-      </c>
-      <c r="I14" s="132"/>
-    </row>
-    <row r="15" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B15" s="126" t="s">
-        <v>52</v>
-      </c>
-      <c r="C15" s="127" t="s">
-        <v>61</v>
-      </c>
-      <c r="D15" s="129">
+      <c r="D15" s="97">
         <f>D10</f>
         <v>35</v>
       </c>
-      <c r="E15" s="129" t="s">
-        <v>53</v>
-      </c>
-      <c r="F15" s="130" t="s">
-        <v>299</v>
-      </c>
-      <c r="G15" s="131" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H15" s="127"/>
-      <c r="I15" s="132"/>
+      <c r="E15" s="97" t="s">
+        <v>52</v>
+      </c>
+      <c r="F15" s="98" t="s">
+        <v>298</v>
+      </c>
+      <c r="G15" s="99" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H15" s="95"/>
+      <c r="I15" s="100"/>
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B16" s="126" t="s">
-        <v>51</v>
-      </c>
-      <c r="C16" s="127" t="s">
-        <v>59</v>
-      </c>
-      <c r="D16" s="129">
+      <c r="B16" s="94" t="s">
+        <v>50</v>
+      </c>
+      <c r="C16" s="95" t="s">
+        <v>58</v>
+      </c>
+      <c r="D16" s="97">
         <f>D11+D14+D13</f>
         <v>55</v>
       </c>
-      <c r="E16" s="129" t="s">
-        <v>53</v>
-      </c>
-      <c r="F16" s="130" t="s">
-        <v>299</v>
-      </c>
-      <c r="G16" s="131" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H16" s="127"/>
-      <c r="I16" s="132"/>
+      <c r="E16" s="97" t="s">
+        <v>52</v>
+      </c>
+      <c r="F16" s="98" t="s">
+        <v>298</v>
+      </c>
+      <c r="G16" s="99" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H16" s="95"/>
+      <c r="I16" s="100"/>
     </row>
     <row r="17" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B17" s="126" t="s">
-        <v>50</v>
-      </c>
-      <c r="C17" s="127" t="s">
-        <v>130</v>
-      </c>
-      <c r="D17" s="129">
+      <c r="B17" s="94" t="s">
+        <v>49</v>
+      </c>
+      <c r="C17" s="95" t="s">
+        <v>129</v>
+      </c>
+      <c r="D17" s="97">
         <f>D16*D15</f>
         <v>1925</v>
       </c>
-      <c r="E17" s="129" t="s">
-        <v>54</v>
-      </c>
-      <c r="F17" s="130" t="s">
-        <v>299</v>
-      </c>
-      <c r="G17" s="131" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H17" s="127"/>
-      <c r="I17" s="132"/>
+      <c r="E17" s="97" t="s">
+        <v>53</v>
+      </c>
+      <c r="F17" s="98" t="s">
+        <v>298</v>
+      </c>
+      <c r="G17" s="99" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H17" s="95"/>
+      <c r="I17" s="100"/>
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B18" s="133" t="s">
+      <c r="B18" s="101" t="s">
+        <v>99</v>
+      </c>
+      <c r="C18" s="102" t="s">
         <v>100</v>
       </c>
-      <c r="C18" s="134" t="s">
-        <v>101</v>
-      </c>
-      <c r="D18" s="151">
+      <c r="D18" s="116">
         <f>D32+D30</f>
         <v>1435</v>
       </c>
-      <c r="E18" s="129" t="s">
-        <v>54</v>
-      </c>
-      <c r="F18" s="130" t="s">
-        <v>299</v>
-      </c>
-      <c r="G18" s="131" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H18" s="134"/>
-      <c r="I18" s="152"/>
+      <c r="E18" s="97" t="s">
+        <v>53</v>
+      </c>
+      <c r="F18" s="98" t="s">
+        <v>298</v>
+      </c>
+      <c r="G18" s="99" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H18" s="102"/>
+      <c r="I18" s="117"/>
     </row>
     <row r="19" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B19" s="133" t="s">
-        <v>98</v>
-      </c>
-      <c r="C19" s="134" t="s">
-        <v>131</v>
-      </c>
-      <c r="D19" s="151">
+      <c r="B19" s="101" t="s">
+        <v>97</v>
+      </c>
+      <c r="C19" s="102" t="s">
+        <v>130</v>
+      </c>
+      <c r="D19" s="116">
         <f>D32+D30+D46</f>
         <v>1495</v>
       </c>
-      <c r="E19" s="129" t="s">
-        <v>54</v>
-      </c>
-      <c r="F19" s="130" t="s">
-        <v>299</v>
-      </c>
-      <c r="G19" s="131" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H19" s="134"/>
-      <c r="I19" s="152"/>
+      <c r="E19" s="97" t="s">
+        <v>53</v>
+      </c>
+      <c r="F19" s="98" t="s">
+        <v>298</v>
+      </c>
+      <c r="G19" s="99" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H19" s="102"/>
+      <c r="I19" s="117"/>
     </row>
     <row r="20" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
-      <c r="B20" s="133" t="s">
-        <v>66</v>
-      </c>
-      <c r="C20" s="134" t="s">
-        <v>132</v>
-      </c>
-      <c r="D20" s="151">
+      <c r="B20" s="101" t="s">
+        <v>65</v>
+      </c>
+      <c r="C20" s="102" t="s">
+        <v>131</v>
+      </c>
+      <c r="D20" s="116">
         <f>D18/D17</f>
         <v>0.74545454545454548</v>
       </c>
-      <c r="E20" s="151" t="s">
-        <v>67</v>
-      </c>
-      <c r="F20" s="130" t="s">
-        <v>299</v>
-      </c>
-      <c r="G20" s="131" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H20" s="134"/>
-      <c r="I20" s="152"/>
+      <c r="E20" s="116" t="s">
+        <v>66</v>
+      </c>
+      <c r="F20" s="98" t="s">
+        <v>298</v>
+      </c>
+      <c r="G20" s="99" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H20" s="102"/>
+      <c r="I20" s="117"/>
     </row>
     <row r="21" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B21" s="133" t="s">
-        <v>99</v>
-      </c>
-      <c r="C21" s="134" t="s">
-        <v>133</v>
-      </c>
-      <c r="D21" s="151">
+      <c r="B21" s="101" t="s">
+        <v>98</v>
+      </c>
+      <c r="C21" s="102" t="s">
+        <v>132</v>
+      </c>
+      <c r="D21" s="116">
         <f>D19/D17</f>
         <v>0.77662337662337666</v>
       </c>
-      <c r="E21" s="151" t="s">
-        <v>67</v>
-      </c>
-      <c r="F21" s="130" t="s">
-        <v>299</v>
-      </c>
-      <c r="G21" s="131" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H21" s="134"/>
-      <c r="I21" s="152"/>
+      <c r="E21" s="116" t="s">
+        <v>66</v>
+      </c>
+      <c r="F21" s="98" t="s">
+        <v>298</v>
+      </c>
+      <c r="G21" s="99" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H21" s="102"/>
+      <c r="I21" s="117"/>
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B22" s="135"/>
-      <c r="C22" s="136"/>
-      <c r="D22" s="137"/>
-      <c r="E22" s="137"/>
-      <c r="F22" s="138"/>
-      <c r="G22" s="139" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H22" s="136"/>
-      <c r="I22" s="153"/>
+      <c r="B22" s="103"/>
+      <c r="C22" s="104"/>
+      <c r="D22" s="105"/>
+      <c r="E22" s="105"/>
+      <c r="F22" s="106"/>
+      <c r="G22" s="107" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H22" s="104"/>
+      <c r="I22" s="118"/>
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B23" s="145" t="s">
-        <v>312</v>
-      </c>
-      <c r="C23" s="146"/>
-      <c r="D23" s="147"/>
-      <c r="E23" s="147"/>
-      <c r="F23" s="148"/>
-      <c r="G23" s="147"/>
-      <c r="H23" s="149"/>
-      <c r="I23" s="150"/>
+      <c r="B23" s="110" t="s">
+        <v>311</v>
+      </c>
+      <c r="C23" s="111"/>
+      <c r="D23" s="112"/>
+      <c r="E23" s="112"/>
+      <c r="F23" s="113"/>
+      <c r="G23" s="112"/>
+      <c r="H23" s="114"/>
+      <c r="I23" s="115"/>
     </row>
     <row r="24" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
-      <c r="B24" s="126" t="s">
+      <c r="B24" s="94" t="s">
+        <v>70</v>
+      </c>
+      <c r="C24" s="95" t="s">
+        <v>133</v>
+      </c>
+      <c r="D24" s="96">
+        <v>2</v>
+      </c>
+      <c r="E24" s="97" t="s">
+        <v>52</v>
+      </c>
+      <c r="F24" s="98" t="s">
+        <v>298</v>
+      </c>
+      <c r="G24" s="99" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H24" s="95" t="s">
+        <v>283</v>
+      </c>
+      <c r="I24" s="100">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="2:9" ht="57" x14ac:dyDescent="0.3">
+      <c r="B25" s="94" t="s">
         <v>71</v>
       </c>
-      <c r="C24" s="127" t="s">
-        <v>134</v>
-      </c>
-      <c r="D24" s="128">
-        <v>2</v>
-      </c>
-      <c r="E24" s="129" t="s">
-        <v>53</v>
-      </c>
-      <c r="F24" s="130" t="s">
-        <v>299</v>
-      </c>
-      <c r="G24" s="131" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H24" s="127" t="s">
-        <v>284</v>
-      </c>
-      <c r="I24" s="132">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="25" spans="2:9" ht="57" x14ac:dyDescent="0.3">
-      <c r="B25" s="126" t="s">
-        <v>72</v>
-      </c>
-      <c r="C25" s="127" t="s">
-        <v>82</v>
+      <c r="C25" s="95" t="s">
+        <v>81</v>
       </c>
       <c r="D25" s="32">
         <v>5</v>
       </c>
-      <c r="E25" s="129" t="s">
-        <v>68</v>
-      </c>
-      <c r="F25" s="130" t="s">
-        <v>299</v>
-      </c>
-      <c r="G25" s="131" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H25" s="127"/>
-      <c r="I25" s="132"/>
+      <c r="E25" s="97" t="s">
+        <v>67</v>
+      </c>
+      <c r="F25" s="98" t="s">
+        <v>298</v>
+      </c>
+      <c r="G25" s="99" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H25" s="95"/>
+      <c r="I25" s="100"/>
     </row>
     <row r="26" spans="2:9" ht="45.6" x14ac:dyDescent="0.3">
-      <c r="B26" s="126" t="s">
-        <v>73</v>
-      </c>
-      <c r="C26" s="127" t="s">
-        <v>70</v>
-      </c>
-      <c r="D26" s="129">
+      <c r="B26" s="94" t="s">
+        <v>72</v>
+      </c>
+      <c r="C26" s="95" t="s">
+        <v>69</v>
+      </c>
+      <c r="D26" s="97">
         <f>ROUND(ATAN(D25/100)*180/PI(),0)</f>
         <v>3</v>
       </c>
-      <c r="E26" s="129" t="s">
-        <v>69</v>
-      </c>
-      <c r="F26" s="130" t="s">
-        <v>299</v>
-      </c>
-      <c r="G26" s="131" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H26" s="127"/>
-      <c r="I26" s="132"/>
+      <c r="E26" s="97" t="s">
+        <v>68</v>
+      </c>
+      <c r="F26" s="98" t="s">
+        <v>298</v>
+      </c>
+      <c r="G26" s="99" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H26" s="95"/>
+      <c r="I26" s="100"/>
     </row>
     <row r="27" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B27" s="133" t="s">
+      <c r="B27" s="101" t="s">
+        <v>74</v>
+      </c>
+      <c r="C27" s="102" t="s">
+        <v>309</v>
+      </c>
+      <c r="D27" s="119">
+        <v>0.6</v>
+      </c>
+      <c r="E27" s="116" t="s">
+        <v>52</v>
+      </c>
+      <c r="F27" s="98" t="s">
+        <v>298</v>
+      </c>
+      <c r="G27" s="99" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H27" s="102"/>
+      <c r="I27" s="117"/>
+    </row>
+    <row r="28" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="B28" s="94" t="s">
+        <v>73</v>
+      </c>
+      <c r="C28" s="95" t="s">
+        <v>134</v>
+      </c>
+      <c r="D28" s="96">
+        <v>0.2</v>
+      </c>
+      <c r="E28" s="97" t="s">
+        <v>52</v>
+      </c>
+      <c r="F28" s="98" t="s">
+        <v>298</v>
+      </c>
+      <c r="G28" s="99" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H28" s="95"/>
+      <c r="I28" s="100"/>
+    </row>
+    <row r="29" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B29" s="94" t="s">
+        <v>135</v>
+      </c>
+      <c r="C29" s="95" t="s">
+        <v>137</v>
+      </c>
+      <c r="D29" s="96">
+        <v>2</v>
+      </c>
+      <c r="E29" s="97" t="s">
+        <v>66</v>
+      </c>
+      <c r="F29" s="98" t="s">
+        <v>298</v>
+      </c>
+      <c r="G29" s="99" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H29" s="95"/>
+      <c r="I29" s="100"/>
+    </row>
+    <row r="30" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="B30" s="101" t="s">
         <v>75</v>
       </c>
-      <c r="C27" s="134" t="s">
-        <v>310</v>
-      </c>
-      <c r="D27" s="154">
-        <v>0.6</v>
-      </c>
-      <c r="E27" s="151" t="s">
-        <v>53</v>
-      </c>
-      <c r="F27" s="130" t="s">
-        <v>299</v>
-      </c>
-      <c r="G27" s="131" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H27" s="134"/>
-      <c r="I27" s="152"/>
-    </row>
-    <row r="28" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="B28" s="126" t="s">
-        <v>74</v>
-      </c>
-      <c r="C28" s="127" t="s">
-        <v>135</v>
-      </c>
-      <c r="D28" s="128">
-        <v>0.2</v>
-      </c>
-      <c r="E28" s="129" t="s">
-        <v>53</v>
-      </c>
-      <c r="F28" s="130" t="s">
-        <v>299</v>
-      </c>
-      <c r="G28" s="131" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H28" s="127"/>
-      <c r="I28" s="132"/>
-    </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B29" s="126" t="s">
+      <c r="C30" s="102" t="s">
         <v>136</v>
       </c>
-      <c r="C29" s="127" t="s">
-        <v>138</v>
-      </c>
-      <c r="D29" s="128">
-        <v>2</v>
-      </c>
-      <c r="E29" s="129" t="s">
-        <v>67</v>
-      </c>
-      <c r="F29" s="130" t="s">
-        <v>299</v>
-      </c>
-      <c r="G29" s="131" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H29" s="127"/>
-      <c r="I29" s="132"/>
-    </row>
-    <row r="30" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B30" s="133" t="s">
-        <v>76</v>
-      </c>
-      <c r="C30" s="134" t="s">
-        <v>137</v>
-      </c>
-      <c r="D30" s="151">
+      <c r="D30" s="116">
         <f>(D27-D28)*(D11+D24+D24)*D29</f>
         <v>32.799999999999997</v>
       </c>
-      <c r="E30" s="129" t="s">
-        <v>54</v>
-      </c>
-      <c r="F30" s="130" t="s">
-        <v>299</v>
-      </c>
-      <c r="G30" s="131" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H30" s="134"/>
-      <c r="I30" s="152"/>
+      <c r="E30" s="97" t="s">
+        <v>53</v>
+      </c>
+      <c r="F30" s="98" t="s">
+        <v>298</v>
+      </c>
+      <c r="G30" s="99" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H30" s="102"/>
+      <c r="I30" s="117"/>
     </row>
     <row r="31" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
-      <c r="B31" s="126" t="s">
-        <v>139</v>
-      </c>
-      <c r="C31" s="127" t="s">
-        <v>141</v>
-      </c>
-      <c r="D31" s="129">
+      <c r="B31" s="94" t="s">
+        <v>138</v>
+      </c>
+      <c r="C31" s="95" t="s">
+        <v>140</v>
+      </c>
+      <c r="D31" s="97">
         <f>(D10*D11)-D30</f>
         <v>1262.2</v>
       </c>
-      <c r="E31" s="129" t="s">
-        <v>54</v>
-      </c>
-      <c r="F31" s="130" t="s">
-        <v>299</v>
-      </c>
-      <c r="G31" s="131" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H31" s="127"/>
-      <c r="I31" s="132"/>
+      <c r="E31" s="97" t="s">
+        <v>53</v>
+      </c>
+      <c r="F31" s="98" t="s">
+        <v>298</v>
+      </c>
+      <c r="G31" s="99" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H31" s="95"/>
+      <c r="I31" s="100"/>
     </row>
     <row r="32" spans="2:9" ht="45.6" x14ac:dyDescent="0.3">
-      <c r="B32" s="126" t="s">
-        <v>140</v>
-      </c>
-      <c r="C32" s="127" t="s">
-        <v>142</v>
-      </c>
-      <c r="D32" s="129">
+      <c r="B32" s="94" t="s">
+        <v>139</v>
+      </c>
+      <c r="C32" s="95" t="s">
+        <v>141</v>
+      </c>
+      <c r="D32" s="97">
         <f>((D10*D11)+D10*(D24+D24))-D30</f>
         <v>1402.2</v>
       </c>
-      <c r="E32" s="129" t="s">
-        <v>54</v>
-      </c>
-      <c r="F32" s="130" t="s">
-        <v>299</v>
-      </c>
-      <c r="G32" s="131" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H32" s="127"/>
-      <c r="I32" s="132"/>
+      <c r="E32" s="97" t="s">
+        <v>53</v>
+      </c>
+      <c r="F32" s="98" t="s">
+        <v>298</v>
+      </c>
+      <c r="G32" s="99" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H32" s="95"/>
+      <c r="I32" s="100"/>
     </row>
     <row r="33" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B33" s="126" t="s">
+      <c r="B33" s="94" t="s">
+        <v>76</v>
+      </c>
+      <c r="C33" s="95" t="s">
+        <v>122</v>
+      </c>
+      <c r="D33" s="96">
+        <v>10</v>
+      </c>
+      <c r="E33" s="97" t="s">
+        <v>52</v>
+      </c>
+      <c r="F33" s="98" t="s">
+        <v>321</v>
+      </c>
+      <c r="G33" s="99" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H33" s="95"/>
+      <c r="I33" s="100"/>
+    </row>
+    <row r="34" spans="2:9" ht="45.6" x14ac:dyDescent="0.3">
+      <c r="B34" s="94" t="s">
         <v>77</v>
       </c>
-      <c r="C33" s="127" t="s">
-        <v>123</v>
-      </c>
-      <c r="D33" s="128">
-        <v>10</v>
-      </c>
-      <c r="E33" s="129" t="s">
-        <v>53</v>
-      </c>
-      <c r="F33" s="130" t="s">
-        <v>322</v>
-      </c>
-      <c r="G33" s="131" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H33" s="127"/>
-      <c r="I33" s="132"/>
-    </row>
-    <row r="34" spans="2:9" ht="45.6" x14ac:dyDescent="0.3">
-      <c r="B34" s="126" t="s">
-        <v>78</v>
-      </c>
-      <c r="C34" s="127" t="s">
-        <v>143</v>
-      </c>
-      <c r="D34" s="129">
+      <c r="C34" s="95" t="s">
+        <v>142</v>
+      </c>
+      <c r="D34" s="97">
         <f>EVEN(D31/(D33*D33))</f>
         <v>14</v>
       </c>
-      <c r="E34" s="129" t="s">
-        <v>115</v>
-      </c>
-      <c r="F34" s="130" t="s">
-        <v>322</v>
-      </c>
-      <c r="G34" s="131" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H34" s="127"/>
-      <c r="I34" s="132"/>
+      <c r="E34" s="97" t="s">
+        <v>114</v>
+      </c>
+      <c r="F34" s="98" t="s">
+        <v>321</v>
+      </c>
+      <c r="G34" s="99" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H34" s="95"/>
+      <c r="I34" s="100"/>
     </row>
     <row r="35" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B35" s="126" t="s">
+      <c r="B35" s="94" t="s">
+        <v>78</v>
+      </c>
+      <c r="C35" s="95" t="s">
+        <v>61</v>
+      </c>
+      <c r="D35" s="96">
+        <v>1200</v>
+      </c>
+      <c r="E35" s="97" t="s">
+        <v>62</v>
+      </c>
+      <c r="F35" s="98" t="s">
+        <v>321</v>
+      </c>
+      <c r="G35" s="99" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H35" s="95"/>
+      <c r="I35" s="100"/>
+    </row>
+    <row r="36" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="B36" s="94" t="s">
         <v>79</v>
       </c>
-      <c r="C35" s="127" t="s">
-        <v>62</v>
-      </c>
-      <c r="D35" s="128">
-        <v>1200</v>
-      </c>
-      <c r="E35" s="129" t="s">
-        <v>63</v>
-      </c>
-      <c r="F35" s="130" t="s">
-        <v>322</v>
-      </c>
-      <c r="G35" s="131" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H35" s="127"/>
-      <c r="I35" s="132"/>
-    </row>
-    <row r="36" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
-      <c r="B36" s="126" t="s">
-        <v>80</v>
-      </c>
-      <c r="C36" s="127" t="s">
-        <v>330</v>
-      </c>
-      <c r="D36" s="129">
+      <c r="C36" s="95" t="s">
+        <v>329</v>
+      </c>
+      <c r="D36" s="97">
         <f>D35*D35/(1000*1000)</f>
         <v>1.44</v>
       </c>
-      <c r="E36" s="129" t="s">
-        <v>54</v>
-      </c>
-      <c r="F36" s="130" t="s">
-        <v>322</v>
-      </c>
-      <c r="G36" s="131" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H36" s="127"/>
-      <c r="I36" s="132"/>
+      <c r="E36" s="97" t="s">
+        <v>53</v>
+      </c>
+      <c r="F36" s="98" t="s">
+        <v>321</v>
+      </c>
+      <c r="G36" s="99" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H36" s="95"/>
+      <c r="I36" s="100"/>
     </row>
     <row r="37" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="B37" s="126" t="s">
-        <v>81</v>
-      </c>
-      <c r="C37" s="127" t="s">
-        <v>144</v>
-      </c>
-      <c r="D37" s="129">
+      <c r="B37" s="94" t="s">
+        <v>80</v>
+      </c>
+      <c r="C37" s="95" t="s">
+        <v>143</v>
+      </c>
+      <c r="D37" s="97">
         <f>D34*D36</f>
         <v>20.16</v>
       </c>
-      <c r="E37" s="129" t="s">
-        <v>54</v>
-      </c>
-      <c r="F37" s="130" t="s">
-        <v>322</v>
-      </c>
-      <c r="G37" s="131" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H37" s="127"/>
-      <c r="I37" s="132"/>
+      <c r="E37" s="97" t="s">
+        <v>53</v>
+      </c>
+      <c r="F37" s="98" t="s">
+        <v>321</v>
+      </c>
+      <c r="G37" s="99" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H37" s="95"/>
+      <c r="I37" s="100"/>
     </row>
     <row r="38" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B38" s="135"/>
-      <c r="C38" s="136"/>
-      <c r="D38" s="137"/>
-      <c r="E38" s="137"/>
-      <c r="F38" s="138"/>
-      <c r="G38" s="139" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H38" s="136"/>
-      <c r="I38" s="153"/>
+      <c r="B38" s="103"/>
+      <c r="C38" s="104"/>
+      <c r="D38" s="105"/>
+      <c r="E38" s="105"/>
+      <c r="F38" s="106"/>
+      <c r="G38" s="107" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H38" s="104"/>
+      <c r="I38" s="118"/>
     </row>
     <row r="39" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B39" s="155" t="s">
+      <c r="B39" s="120" t="s">
+        <v>330</v>
+      </c>
+      <c r="C39" s="111"/>
+      <c r="D39" s="112"/>
+      <c r="E39" s="112"/>
+      <c r="F39" s="113"/>
+      <c r="G39" s="112"/>
+      <c r="H39" s="114"/>
+      <c r="I39" s="115"/>
+    </row>
+    <row r="40" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B40" s="94" t="s">
         <v>331</v>
       </c>
-      <c r="C39" s="146"/>
-      <c r="D39" s="147"/>
-      <c r="E39" s="147"/>
-      <c r="F39" s="148"/>
-      <c r="G39" s="147"/>
-      <c r="H39" s="149"/>
-      <c r="I39" s="150"/>
-    </row>
-    <row r="40" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B40" s="126" t="s">
+      <c r="C40" s="95" t="s">
+        <v>85</v>
+      </c>
+      <c r="D40" s="96">
+        <v>1</v>
+      </c>
+      <c r="E40" s="97" t="s">
+        <v>52</v>
+      </c>
+      <c r="F40" s="98" t="s">
+        <v>298</v>
+      </c>
+      <c r="G40" s="99" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H40" s="95"/>
+      <c r="I40" s="100">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="41" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="B41" s="94" t="s">
+        <v>82</v>
+      </c>
+      <c r="C41" s="95" t="s">
+        <v>86</v>
+      </c>
+      <c r="D41" s="96">
+        <v>15</v>
+      </c>
+      <c r="E41" s="97" t="s">
+        <v>52</v>
+      </c>
+      <c r="F41" s="98" t="s">
+        <v>298</v>
+      </c>
+      <c r="G41" s="99" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H41" s="95"/>
+      <c r="I41" s="100"/>
+    </row>
+    <row r="42" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="B42" s="94" t="s">
+        <v>83</v>
+      </c>
+      <c r="C42" s="95" t="s">
         <v>332</v>
       </c>
-      <c r="C40" s="127" t="s">
-        <v>86</v>
-      </c>
-      <c r="D40" s="128">
-        <v>1</v>
-      </c>
-      <c r="E40" s="129" t="s">
-        <v>53</v>
-      </c>
-      <c r="F40" s="130" t="s">
-        <v>299</v>
-      </c>
-      <c r="G40" s="131" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H40" s="127"/>
-      <c r="I40" s="132">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="41" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B41" s="126" t="s">
-        <v>83</v>
-      </c>
-      <c r="C41" s="127" t="s">
-        <v>87</v>
-      </c>
-      <c r="D41" s="128">
-        <v>15</v>
-      </c>
-      <c r="E41" s="129" t="s">
-        <v>53</v>
-      </c>
-      <c r="F41" s="130" t="s">
-        <v>299</v>
-      </c>
-      <c r="G41" s="131" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H41" s="127"/>
-      <c r="I41" s="132"/>
-    </row>
-    <row r="42" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B42" s="126" t="s">
-        <v>84</v>
-      </c>
-      <c r="C42" s="127" t="s">
-        <v>333</v>
-      </c>
-      <c r="D42" s="129">
+      <c r="D42" s="97">
         <f>D11+(INT(D11/D41)*D10)</f>
         <v>107</v>
       </c>
-      <c r="E42" s="129" t="s">
-        <v>53</v>
-      </c>
-      <c r="F42" s="130" t="s">
-        <v>299</v>
-      </c>
-      <c r="G42" s="131" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H42" s="127"/>
-      <c r="I42" s="132"/>
+      <c r="E42" s="97" t="s">
+        <v>52</v>
+      </c>
+      <c r="F42" s="98" t="s">
+        <v>298</v>
+      </c>
+      <c r="G42" s="99" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H42" s="95"/>
+      <c r="I42" s="100"/>
     </row>
     <row r="43" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B43" s="126" t="s">
-        <v>85</v>
-      </c>
-      <c r="C43" s="127" t="s">
-        <v>88</v>
-      </c>
-      <c r="D43" s="129">
+      <c r="B43" s="94" t="s">
+        <v>84</v>
+      </c>
+      <c r="C43" s="95" t="s">
+        <v>87</v>
+      </c>
+      <c r="D43" s="97">
         <f>D42*D40</f>
         <v>107</v>
       </c>
-      <c r="E43" s="129" t="s">
-        <v>54</v>
-      </c>
-      <c r="F43" s="130" t="s">
-        <v>299</v>
-      </c>
-      <c r="G43" s="131" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H43" s="127"/>
-      <c r="I43" s="132"/>
+      <c r="E43" s="97" t="s">
+        <v>53</v>
+      </c>
+      <c r="F43" s="98" t="s">
+        <v>298</v>
+      </c>
+      <c r="G43" s="99" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H43" s="95"/>
+      <c r="I43" s="100"/>
     </row>
     <row r="44" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B44" s="135"/>
-      <c r="C44" s="136"/>
-      <c r="D44" s="137"/>
-      <c r="E44" s="137"/>
-      <c r="F44" s="138"/>
-      <c r="G44" s="139" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H44" s="136"/>
-      <c r="I44" s="153"/>
+      <c r="B44" s="103"/>
+      <c r="C44" s="104"/>
+      <c r="D44" s="105"/>
+      <c r="E44" s="105"/>
+      <c r="F44" s="106"/>
+      <c r="G44" s="107" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H44" s="104"/>
+      <c r="I44" s="118"/>
     </row>
     <row r="45" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B45" s="145" t="s">
+      <c r="B45" s="110" t="s">
+        <v>312</v>
+      </c>
+      <c r="C45" s="111"/>
+      <c r="D45" s="112"/>
+      <c r="E45" s="112"/>
+      <c r="F45" s="113"/>
+      <c r="G45" s="112"/>
+      <c r="H45" s="114"/>
+      <c r="I45" s="115"/>
+    </row>
+    <row r="46" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="B46" s="94" t="s">
+        <v>40</v>
+      </c>
+      <c r="C46" s="95" t="s">
         <v>313</v>
       </c>
-      <c r="C45" s="146"/>
-      <c r="D45" s="147"/>
-      <c r="E45" s="147"/>
-      <c r="F45" s="148"/>
-      <c r="G45" s="147"/>
-      <c r="H45" s="149"/>
-      <c r="I45" s="150"/>
-    </row>
-    <row r="46" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
-      <c r="B46" s="126" t="s">
+      <c r="D46" s="96">
+        <v>60</v>
+      </c>
+      <c r="E46" s="97" t="s">
+        <v>53</v>
+      </c>
+      <c r="F46" s="98" t="s">
+        <v>298</v>
+      </c>
+      <c r="G46" s="99" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H46" s="95"/>
+      <c r="I46" s="100">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="47" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="B47" s="94" t="s">
         <v>41</v>
       </c>
-      <c r="C46" s="127" t="s">
-        <v>314</v>
-      </c>
-      <c r="D46" s="128">
-        <v>60</v>
-      </c>
-      <c r="E46" s="129" t="s">
-        <v>54</v>
-      </c>
-      <c r="F46" s="130" t="s">
-        <v>299</v>
-      </c>
-      <c r="G46" s="131" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H46" s="127"/>
-      <c r="I46" s="132">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="47" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
-      <c r="B47" s="126" t="s">
+      <c r="C47" s="95" t="s">
         <v>42</v>
       </c>
-      <c r="C47" s="127" t="s">
-        <v>43</v>
-      </c>
-      <c r="D47" s="128">
+      <c r="D47" s="96">
         <v>24</v>
       </c>
-      <c r="E47" s="129" t="s">
-        <v>54</v>
-      </c>
-      <c r="F47" s="130" t="s">
-        <v>299</v>
-      </c>
-      <c r="G47" s="131" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H47" s="127"/>
-      <c r="I47" s="132"/>
+      <c r="E47" s="97" t="s">
+        <v>53</v>
+      </c>
+      <c r="F47" s="98" t="s">
+        <v>298</v>
+      </c>
+      <c r="G47" s="99" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H47" s="95"/>
+      <c r="I47" s="100"/>
     </row>
     <row r="48" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B48" s="126" t="s">
+      <c r="B48" s="94" t="s">
+        <v>88</v>
+      </c>
+      <c r="C48" s="95" t="s">
+        <v>123</v>
+      </c>
+      <c r="D48" s="96">
+        <v>3.9900000000000007</v>
+      </c>
+      <c r="E48" s="97" t="s">
+        <v>52</v>
+      </c>
+      <c r="F48" s="98" t="s">
+        <v>298</v>
+      </c>
+      <c r="G48" s="99" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H48" s="95"/>
+      <c r="I48" s="100"/>
+    </row>
+    <row r="49" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="B49" s="94" t="s">
         <v>89</v>
       </c>
-      <c r="C48" s="127" t="s">
-        <v>124</v>
-      </c>
-      <c r="D48" s="128">
-        <v>3.9900000000000007</v>
-      </c>
-      <c r="E48" s="129" t="s">
-        <v>53</v>
-      </c>
-      <c r="F48" s="130" t="s">
-        <v>299</v>
-      </c>
-      <c r="G48" s="131" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H48" s="127"/>
-      <c r="I48" s="132"/>
-    </row>
-    <row r="49" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B49" s="126" t="s">
-        <v>90</v>
-      </c>
-      <c r="C49" s="127" t="s">
-        <v>145</v>
-      </c>
-      <c r="D49" s="129">
+      <c r="C49" s="95" t="s">
+        <v>144</v>
+      </c>
+      <c r="D49" s="97">
         <f>D46-D54</f>
         <v>52.943999999999996</v>
       </c>
-      <c r="E49" s="129" t="s">
+      <c r="E49" s="97" t="s">
+        <v>53</v>
+      </c>
+      <c r="F49" s="98" t="s">
+        <v>298</v>
+      </c>
+      <c r="G49" s="99" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H49" s="95"/>
+      <c r="I49" s="100"/>
+    </row>
+    <row r="50" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="B50" s="94" t="s">
+        <v>56</v>
+      </c>
+      <c r="C50" s="95" t="s">
+        <v>55</v>
+      </c>
+      <c r="D50" s="96">
+        <v>28</v>
+      </c>
+      <c r="E50" s="97" t="s">
         <v>54</v>
       </c>
-      <c r="F49" s="130" t="s">
-        <v>299</v>
-      </c>
-      <c r="G49" s="131" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H49" s="127"/>
-      <c r="I49" s="132"/>
-    </row>
-    <row r="50" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B50" s="126" t="s">
+      <c r="F50" s="98" t="s">
+        <v>298</v>
+      </c>
+      <c r="G50" s="99" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H50" s="95"/>
+      <c r="I50" s="100"/>
+    </row>
+    <row r="51" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="B51" s="94" t="s">
+        <v>92</v>
+      </c>
+      <c r="C51" s="95" t="s">
         <v>57</v>
       </c>
-      <c r="C50" s="127" t="s">
-        <v>56</v>
-      </c>
-      <c r="D50" s="128">
-        <v>28</v>
-      </c>
-      <c r="E50" s="129" t="s">
-        <v>55</v>
-      </c>
-      <c r="F50" s="130" t="s">
-        <v>299</v>
-      </c>
-      <c r="G50" s="131" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H50" s="127"/>
-      <c r="I50" s="132"/>
-    </row>
-    <row r="51" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B51" s="126" t="s">
-        <v>93</v>
-      </c>
-      <c r="C51" s="127" t="s">
-        <v>58</v>
-      </c>
-      <c r="D51" s="128">
+      <c r="D51" s="96">
         <v>19</v>
       </c>
-      <c r="E51" s="129" t="s">
-        <v>55</v>
-      </c>
-      <c r="F51" s="130" t="s">
-        <v>299</v>
-      </c>
-      <c r="G51" s="131" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H51" s="127"/>
-      <c r="I51" s="132"/>
+      <c r="E51" s="97" t="s">
+        <v>54</v>
+      </c>
+      <c r="F51" s="98" t="s">
+        <v>298</v>
+      </c>
+      <c r="G51" s="99" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H51" s="95"/>
+      <c r="I51" s="100"/>
     </row>
     <row r="52" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B52" s="126" t="s">
+      <c r="B52" s="94" t="s">
+        <v>90</v>
+      </c>
+      <c r="C52" s="95" t="s">
         <v>91</v>
       </c>
-      <c r="C52" s="127" t="s">
-        <v>92</v>
-      </c>
-      <c r="D52" s="129">
+      <c r="D52" s="97">
         <f>D48/(D51/100)</f>
         <v>21.000000000000004</v>
       </c>
-      <c r="E52" s="129" t="s">
-        <v>49</v>
-      </c>
-      <c r="F52" s="130" t="s">
-        <v>299</v>
-      </c>
-      <c r="G52" s="131" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H52" s="127"/>
-      <c r="I52" s="132"/>
+      <c r="E52" s="97" t="s">
+        <v>48</v>
+      </c>
+      <c r="F52" s="98" t="s">
+        <v>298</v>
+      </c>
+      <c r="G52" s="99" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H52" s="95"/>
+      <c r="I52" s="100"/>
     </row>
     <row r="53" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B53" s="126" t="s">
+      <c r="B53" s="94" t="s">
+        <v>93</v>
+      </c>
+      <c r="C53" s="95" t="s">
         <v>94</v>
       </c>
-      <c r="C53" s="127" t="s">
+      <c r="D53" s="96">
+        <v>1.2</v>
+      </c>
+      <c r="E53" s="97" t="s">
+        <v>52</v>
+      </c>
+      <c r="F53" s="98" t="s">
+        <v>298</v>
+      </c>
+      <c r="G53" s="99" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H53" s="95"/>
+      <c r="I53" s="100"/>
+    </row>
+    <row r="54" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="B54" s="94" t="s">
         <v>95</v>
       </c>
-      <c r="D53" s="128">
-        <v>1.2</v>
-      </c>
-      <c r="E53" s="129" t="s">
-        <v>53</v>
-      </c>
-      <c r="F53" s="130" t="s">
-        <v>299</v>
-      </c>
-      <c r="G53" s="131" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H53" s="127"/>
-      <c r="I53" s="132"/>
-    </row>
-    <row r="54" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B54" s="126" t="s">
+      <c r="C54" s="95" t="s">
         <v>96</v>
       </c>
-      <c r="C54" s="127" t="s">
-        <v>97</v>
-      </c>
-      <c r="D54" s="156">
+      <c r="D54" s="121">
         <f>D53*D52*(D50/100)</f>
         <v>7.0560000000000018</v>
       </c>
-      <c r="E54" s="129" t="s">
+      <c r="E54" s="97" t="s">
+        <v>53</v>
+      </c>
+      <c r="F54" s="98" t="s">
+        <v>298</v>
+      </c>
+      <c r="G54" s="99" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H54" s="95"/>
+      <c r="I54" s="100"/>
+    </row>
+    <row r="55" spans="2:9" ht="68.400000000000006" x14ac:dyDescent="0.3">
+      <c r="B55" s="94" t="s">
+        <v>124</v>
+      </c>
+      <c r="C55" s="95" t="s">
+        <v>183</v>
+      </c>
+      <c r="D55" s="96">
+        <v>6</v>
+      </c>
+      <c r="E55" s="97" t="s">
+        <v>52</v>
+      </c>
+      <c r="F55" s="98" t="s">
+        <v>301</v>
+      </c>
+      <c r="G55" s="99" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H55" s="95"/>
+      <c r="I55" s="100"/>
+    </row>
+    <row r="56" spans="2:9" ht="68.400000000000006" x14ac:dyDescent="0.3">
+      <c r="B56" s="94" t="s">
+        <v>125</v>
+      </c>
+      <c r="C56" s="95" t="s">
+        <v>184</v>
+      </c>
+      <c r="D56" s="96">
+        <v>4.5</v>
+      </c>
+      <c r="E56" s="97" t="s">
+        <v>52</v>
+      </c>
+      <c r="F56" s="98" t="s">
+        <v>301</v>
+      </c>
+      <c r="G56" s="99" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H56" s="95"/>
+      <c r="I56" s="100"/>
+    </row>
+    <row r="57" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B57" s="94" t="s">
+        <v>127</v>
+      </c>
+      <c r="C57" s="95" t="s">
+        <v>126</v>
+      </c>
+      <c r="D57" s="96">
+        <v>1.2</v>
+      </c>
+      <c r="E57" s="97" t="s">
+        <v>52</v>
+      </c>
+      <c r="F57" s="98" t="s">
+        <v>301</v>
+      </c>
+      <c r="G57" s="99" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H57" s="95"/>
+      <c r="I57" s="100"/>
+    </row>
+    <row r="58" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B58" s="94" t="s">
+        <v>181</v>
+      </c>
+      <c r="C58" s="95" t="s">
+        <v>182</v>
+      </c>
+      <c r="D58" s="96">
+        <v>2.2999999999999998</v>
+      </c>
+      <c r="E58" s="97" t="s">
+        <v>52</v>
+      </c>
+      <c r="F58" s="98" t="s">
+        <v>301</v>
+      </c>
+      <c r="G58" s="99" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H58" s="95"/>
+      <c r="I58" s="100"/>
+    </row>
+    <row r="59" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="B59" s="94" t="s">
+        <v>128</v>
+      </c>
+      <c r="C59" s="95" t="s">
+        <v>185</v>
+      </c>
+      <c r="D59" s="96">
+        <v>3</v>
+      </c>
+      <c r="E59" s="97" t="s">
+        <v>52</v>
+      </c>
+      <c r="F59" s="98" t="s">
+        <v>301</v>
+      </c>
+      <c r="G59" s="99" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H59" s="95"/>
+      <c r="I59" s="100"/>
+    </row>
+    <row r="60" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="B60" s="94" t="s">
+        <v>180</v>
+      </c>
+      <c r="C60" s="95" t="s">
+        <v>186</v>
+      </c>
+      <c r="D60" s="96">
+        <v>2</v>
+      </c>
+      <c r="E60" s="97" t="s">
+        <v>52</v>
+      </c>
+      <c r="F60" s="98" t="s">
+        <v>301</v>
+      </c>
+      <c r="G60" s="99" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H60" s="95"/>
+      <c r="I60" s="100"/>
+    </row>
+    <row r="61" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B61" s="103"/>
+      <c r="C61" s="104"/>
+      <c r="D61" s="105"/>
+      <c r="E61" s="105"/>
+      <c r="F61" s="106"/>
+      <c r="G61" s="107" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H61" s="104"/>
+      <c r="I61" s="118"/>
+    </row>
+    <row r="62" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B62" s="122" t="s">
+        <v>314</v>
+      </c>
+      <c r="C62" s="123"/>
+      <c r="D62" s="124"/>
+      <c r="E62" s="124"/>
+      <c r="F62" s="125"/>
+      <c r="G62" s="124"/>
+      <c r="H62" s="126"/>
+      <c r="I62" s="127"/>
+    </row>
+    <row r="63" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="B63" s="94" t="s">
+        <v>164</v>
+      </c>
+      <c r="C63" s="95" t="s">
+        <v>102</v>
+      </c>
+      <c r="D63" s="96">
+        <v>40</v>
+      </c>
+      <c r="E63" s="97" t="s">
         <v>54</v>
       </c>
-      <c r="F54" s="130" t="s">
-        <v>299</v>
-      </c>
-      <c r="G54" s="131" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H54" s="127"/>
-      <c r="I54" s="132"/>
-    </row>
-    <row r="55" spans="2:9" ht="68.400000000000006" x14ac:dyDescent="0.3">
-      <c r="B55" s="126" t="s">
-        <v>125</v>
-      </c>
-      <c r="C55" s="127" t="s">
-        <v>184</v>
-      </c>
-      <c r="D55" s="128">
-        <v>6</v>
-      </c>
-      <c r="E55" s="129" t="s">
-        <v>53</v>
-      </c>
-      <c r="F55" s="130" t="s">
-        <v>302</v>
-      </c>
-      <c r="G55" s="131" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H55" s="127"/>
-      <c r="I55" s="132"/>
-    </row>
-    <row r="56" spans="2:9" ht="68.400000000000006" x14ac:dyDescent="0.3">
-      <c r="B56" s="126" t="s">
-        <v>126</v>
-      </c>
-      <c r="C56" s="127" t="s">
-        <v>185</v>
-      </c>
-      <c r="D56" s="128">
-        <v>4.5</v>
-      </c>
-      <c r="E56" s="129" t="s">
-        <v>53</v>
-      </c>
-      <c r="F56" s="130" t="s">
-        <v>302</v>
-      </c>
-      <c r="G56" s="131" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H56" s="127"/>
-      <c r="I56" s="132"/>
-    </row>
-    <row r="57" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B57" s="126" t="s">
-        <v>128</v>
-      </c>
-      <c r="C57" s="127" t="s">
-        <v>127</v>
-      </c>
-      <c r="D57" s="128">
-        <v>1.2</v>
-      </c>
-      <c r="E57" s="129" t="s">
-        <v>53</v>
-      </c>
-      <c r="F57" s="130" t="s">
-        <v>302</v>
-      </c>
-      <c r="G57" s="131" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H57" s="127"/>
-      <c r="I57" s="132"/>
-    </row>
-    <row r="58" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B58" s="126" t="s">
-        <v>182</v>
-      </c>
-      <c r="C58" s="127" t="s">
-        <v>183</v>
-      </c>
-      <c r="D58" s="128">
-        <v>2.2999999999999998</v>
-      </c>
-      <c r="E58" s="129" t="s">
-        <v>53</v>
-      </c>
-      <c r="F58" s="130" t="s">
-        <v>302</v>
-      </c>
-      <c r="G58" s="131" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H58" s="127"/>
-      <c r="I58" s="132"/>
-    </row>
-    <row r="59" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B59" s="126" t="s">
-        <v>129</v>
-      </c>
-      <c r="C59" s="127" t="s">
-        <v>186</v>
-      </c>
-      <c r="D59" s="128">
-        <v>3</v>
-      </c>
-      <c r="E59" s="129" t="s">
-        <v>53</v>
-      </c>
-      <c r="F59" s="130" t="s">
-        <v>302</v>
-      </c>
-      <c r="G59" s="131" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H59" s="127"/>
-      <c r="I59" s="132"/>
-    </row>
-    <row r="60" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B60" s="126" t="s">
-        <v>181</v>
-      </c>
-      <c r="C60" s="127" t="s">
-        <v>187</v>
-      </c>
-      <c r="D60" s="128">
-        <v>2</v>
-      </c>
-      <c r="E60" s="129" t="s">
-        <v>53</v>
-      </c>
-      <c r="F60" s="130" t="s">
-        <v>302</v>
-      </c>
-      <c r="G60" s="131" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H60" s="127"/>
-      <c r="I60" s="132"/>
-    </row>
-    <row r="61" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B61" s="135"/>
-      <c r="C61" s="136"/>
-      <c r="D61" s="137"/>
-      <c r="E61" s="137"/>
-      <c r="F61" s="138"/>
-      <c r="G61" s="139" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H61" s="136"/>
-      <c r="I61" s="153"/>
-    </row>
-    <row r="62" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B62" s="157" t="s">
-        <v>315</v>
-      </c>
-      <c r="C62" s="158"/>
-      <c r="D62" s="159"/>
-      <c r="E62" s="159"/>
-      <c r="F62" s="160"/>
-      <c r="G62" s="159"/>
-      <c r="H62" s="161"/>
-      <c r="I62" s="162"/>
-    </row>
-    <row r="63" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B63" s="126" t="s">
+      <c r="F63" s="98" t="s">
+        <v>321</v>
+      </c>
+      <c r="G63" s="99" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H63" s="95"/>
+      <c r="I63" s="100">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B64" s="94" t="s">
+        <v>336</v>
+      </c>
+      <c r="C64" s="95" t="s">
         <v>165</v>
       </c>
-      <c r="C63" s="127" t="s">
-        <v>103</v>
-      </c>
-      <c r="D63" s="128">
-        <v>40</v>
-      </c>
-      <c r="E63" s="129" t="s">
-        <v>55</v>
-      </c>
-      <c r="F63" s="130" t="s">
-        <v>322</v>
-      </c>
-      <c r="G63" s="131" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H63" s="127"/>
-      <c r="I63" s="132">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="64" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B64" s="126" t="s">
-        <v>337</v>
-      </c>
-      <c r="C64" s="127" t="s">
-        <v>166</v>
-      </c>
-      <c r="D64" s="156">
+      <c r="D64" s="121">
         <f>D18</f>
         <v>1435</v>
       </c>
-      <c r="E64" s="129" t="s">
+      <c r="E64" s="97" t="s">
+        <v>53</v>
+      </c>
+      <c r="F64" s="98" t="s">
+        <v>321</v>
+      </c>
+      <c r="G64" s="99" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H64" s="95"/>
+      <c r="I64" s="100"/>
+    </row>
+    <row r="65" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
+      <c r="B65" s="94" t="s">
+        <v>101</v>
+      </c>
+      <c r="C65" s="95" t="s">
+        <v>103</v>
+      </c>
+      <c r="D65" s="96">
+        <v>20</v>
+      </c>
+      <c r="E65" s="97" t="s">
         <v>54</v>
       </c>
-      <c r="F64" s="130" t="s">
-        <v>322</v>
-      </c>
-      <c r="G64" s="131" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H64" s="127"/>
-      <c r="I64" s="132"/>
-    </row>
-    <row r="65" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B65" s="126" t="s">
-        <v>102</v>
-      </c>
-      <c r="C65" s="127" t="s">
-        <v>104</v>
-      </c>
-      <c r="D65" s="128">
-        <v>20</v>
-      </c>
-      <c r="E65" s="129" t="s">
-        <v>55</v>
-      </c>
-      <c r="F65" s="130" t="s">
-        <v>322</v>
-      </c>
-      <c r="G65" s="131" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H65" s="127"/>
-      <c r="I65" s="132"/>
+      <c r="F65" s="98" t="s">
+        <v>321</v>
+      </c>
+      <c r="G65" s="99" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H65" s="95"/>
+      <c r="I65" s="100"/>
     </row>
     <row r="66" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="B66" s="126" t="s">
+      <c r="B66" s="94" t="s">
+        <v>112</v>
+      </c>
+      <c r="C66" s="95" t="s">
+        <v>105</v>
+      </c>
+      <c r="D66" s="96">
+        <v>6</v>
+      </c>
+      <c r="E66" s="97" t="s">
+        <v>52</v>
+      </c>
+      <c r="F66" s="98" t="s">
+        <v>321</v>
+      </c>
+      <c r="G66" s="99" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H66" s="95"/>
+      <c r="I66" s="100"/>
+    </row>
+    <row r="67" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="B67" s="94" t="s">
         <v>113</v>
       </c>
-      <c r="C66" s="127" t="s">
-        <v>106</v>
-      </c>
-      <c r="D66" s="128">
-        <v>6</v>
-      </c>
-      <c r="E66" s="129" t="s">
-        <v>53</v>
-      </c>
-      <c r="F66" s="130" t="s">
-        <v>322</v>
-      </c>
-      <c r="G66" s="131" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H66" s="127"/>
-      <c r="I66" s="132"/>
-    </row>
-    <row r="67" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="B67" s="126" t="s">
-        <v>114</v>
-      </c>
-      <c r="C67" s="127" t="s">
-        <v>146</v>
-      </c>
-      <c r="D67" s="156">
+      <c r="C67" s="95" t="s">
+        <v>145</v>
+      </c>
+      <c r="D67" s="121">
         <f>ROUND(D10/D66,0)</f>
         <v>6</v>
       </c>
-      <c r="E67" s="129" t="s">
+      <c r="E67" s="97" t="s">
+        <v>114</v>
+      </c>
+      <c r="F67" s="98" t="s">
+        <v>321</v>
+      </c>
+      <c r="G67" s="99" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H67" s="95"/>
+      <c r="I67" s="100"/>
+    </row>
+    <row r="68" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="B68" s="94" t="s">
         <v>115</v>
       </c>
-      <c r="F67" s="130" t="s">
-        <v>322</v>
-      </c>
-      <c r="G67" s="131" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H67" s="127"/>
-      <c r="I67" s="132"/>
-    </row>
-    <row r="68" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="B68" s="126" t="s">
-        <v>116</v>
-      </c>
-      <c r="C68" s="127" t="s">
-        <v>147</v>
-      </c>
-      <c r="D68" s="156">
+      <c r="C68" s="95" t="s">
+        <v>146</v>
+      </c>
+      <c r="D68" s="121">
         <f>ROUND(D11/D66,0)</f>
         <v>6</v>
       </c>
-      <c r="E68" s="129" t="s">
-        <v>115</v>
-      </c>
-      <c r="F68" s="130" t="s">
-        <v>322</v>
-      </c>
-      <c r="G68" s="131" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H68" s="127"/>
-      <c r="I68" s="132"/>
+      <c r="E68" s="97" t="s">
+        <v>114</v>
+      </c>
+      <c r="F68" s="98" t="s">
+        <v>321</v>
+      </c>
+      <c r="G68" s="99" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H68" s="95"/>
+      <c r="I68" s="100"/>
     </row>
     <row r="69" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B69" s="126" t="s">
+      <c r="B69" s="94" t="s">
+        <v>116</v>
+      </c>
+      <c r="C69" s="95" t="s">
         <v>117</v>
       </c>
-      <c r="C69" s="127" t="s">
-        <v>118</v>
-      </c>
-      <c r="D69" s="156">
+      <c r="D69" s="121">
         <f>D68*D67</f>
         <v>36</v>
       </c>
-      <c r="E69" s="129" t="s">
-        <v>115</v>
-      </c>
-      <c r="F69" s="130" t="s">
-        <v>322</v>
-      </c>
-      <c r="G69" s="131" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H69" s="127"/>
-      <c r="I69" s="132"/>
+      <c r="E69" s="97" t="s">
+        <v>114</v>
+      </c>
+      <c r="F69" s="98" t="s">
+        <v>321</v>
+      </c>
+      <c r="G69" s="99" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H69" s="95"/>
+      <c r="I69" s="100"/>
     </row>
     <row r="70" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
-      <c r="B70" s="126" t="s">
-        <v>105</v>
-      </c>
-      <c r="C70" s="127" t="s">
-        <v>329</v>
-      </c>
-      <c r="D70" s="128">
+      <c r="B70" s="94" t="s">
+        <v>104</v>
+      </c>
+      <c r="C70" s="95" t="s">
+        <v>328</v>
+      </c>
+      <c r="D70" s="96">
         <v>0.25</v>
       </c>
-      <c r="E70" s="129" t="s">
-        <v>53</v>
-      </c>
-      <c r="F70" s="130" t="s">
-        <v>322</v>
-      </c>
-      <c r="G70" s="131" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H70" s="127"/>
-      <c r="I70" s="132"/>
+      <c r="E70" s="97" t="s">
+        <v>52</v>
+      </c>
+      <c r="F70" s="98" t="s">
+        <v>321</v>
+      </c>
+      <c r="G70" s="99" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H70" s="95"/>
+      <c r="I70" s="100"/>
     </row>
     <row r="71" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
-      <c r="B71" s="126" t="s">
-        <v>107</v>
-      </c>
-      <c r="C71" s="127" t="s">
-        <v>148</v>
-      </c>
-      <c r="D71" s="128">
+      <c r="B71" s="94" t="s">
+        <v>106</v>
+      </c>
+      <c r="C71" s="95" t="s">
+        <v>147</v>
+      </c>
+      <c r="D71" s="96">
         <v>0.4</v>
       </c>
-      <c r="E71" s="129" t="s">
-        <v>53</v>
-      </c>
-      <c r="F71" s="130" t="s">
-        <v>322</v>
-      </c>
-      <c r="G71" s="131" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H71" s="127"/>
-      <c r="I71" s="132"/>
+      <c r="E71" s="97" t="s">
+        <v>52</v>
+      </c>
+      <c r="F71" s="98" t="s">
+        <v>321</v>
+      </c>
+      <c r="G71" s="99" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H71" s="95"/>
+      <c r="I71" s="100"/>
     </row>
     <row r="72" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
-      <c r="B72" s="126" t="s">
+      <c r="B72" s="94" t="s">
+        <v>108</v>
+      </c>
+      <c r="C72" s="95" t="s">
+        <v>110</v>
+      </c>
+      <c r="D72" s="96">
+        <v>0.15</v>
+      </c>
+      <c r="E72" s="97" t="s">
+        <v>52</v>
+      </c>
+      <c r="F72" s="98" t="s">
+        <v>321</v>
+      </c>
+      <c r="G72" s="99" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H72" s="95"/>
+      <c r="I72" s="100"/>
+    </row>
+    <row r="73" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
+      <c r="B73" s="94" t="s">
         <v>109</v>
       </c>
-      <c r="C72" s="127" t="s">
+      <c r="C73" s="95" t="s">
         <v>111</v>
       </c>
-      <c r="D72" s="128">
-        <v>0.15</v>
-      </c>
-      <c r="E72" s="129" t="s">
-        <v>53</v>
-      </c>
-      <c r="F72" s="130" t="s">
-        <v>322</v>
-      </c>
-      <c r="G72" s="131" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H72" s="127"/>
-      <c r="I72" s="132"/>
-    </row>
-    <row r="73" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
-      <c r="B73" s="126" t="s">
-        <v>110</v>
-      </c>
-      <c r="C73" s="127" t="s">
-        <v>112</v>
-      </c>
-      <c r="D73" s="128">
+      <c r="D73" s="96">
         <v>0.4</v>
       </c>
-      <c r="E73" s="129" t="s">
-        <v>53</v>
-      </c>
-      <c r="F73" s="130" t="s">
-        <v>322</v>
-      </c>
-      <c r="G73" s="131" t="str">
+      <c r="E73" s="97" t="s">
+        <v>52</v>
+      </c>
+      <c r="F73" s="98" t="s">
+        <v>321</v>
+      </c>
+      <c r="G73" s="99" t="str">
         <f t="shared" ref="G73:G76" si="1">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F73,"/Readme.md"),"Ver")</f>
         <v>Ver</v>
       </c>
-      <c r="H73" s="127"/>
-      <c r="I73" s="132"/>
+      <c r="H73" s="95"/>
+      <c r="I73" s="100"/>
     </row>
     <row r="74" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
-      <c r="B74" s="126" t="s">
-        <v>119</v>
-      </c>
-      <c r="C74" s="127" t="s">
-        <v>121</v>
-      </c>
-      <c r="D74" s="156">
+      <c r="B74" s="94" t="s">
+        <v>118</v>
+      </c>
+      <c r="C74" s="95" t="s">
+        <v>120</v>
+      </c>
+      <c r="D74" s="121">
         <f>(D10-D70)/D67</f>
         <v>5.791666666666667</v>
       </c>
-      <c r="E74" s="129" t="s">
-        <v>53</v>
-      </c>
-      <c r="F74" s="130" t="s">
-        <v>322</v>
-      </c>
-      <c r="G74" s="131" t="str">
+      <c r="E74" s="97" t="s">
+        <v>52</v>
+      </c>
+      <c r="F74" s="98" t="s">
+        <v>321</v>
+      </c>
+      <c r="G74" s="99" t="str">
         <f t="shared" si="1"/>
         <v>Ver</v>
       </c>
-      <c r="H74" s="127"/>
-      <c r="I74" s="132"/>
+      <c r="H74" s="95"/>
+      <c r="I74" s="100"/>
     </row>
     <row r="75" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
-      <c r="B75" s="126" t="s">
-        <v>120</v>
-      </c>
-      <c r="C75" s="127" t="s">
-        <v>122</v>
-      </c>
-      <c r="D75" s="156">
+      <c r="B75" s="94" t="s">
+        <v>119</v>
+      </c>
+      <c r="C75" s="95" t="s">
+        <v>121</v>
+      </c>
+      <c r="D75" s="121">
         <f>(D11-D71)/D68</f>
         <v>6.1000000000000005</v>
       </c>
-      <c r="E75" s="129" t="s">
-        <v>53</v>
-      </c>
-      <c r="F75" s="130" t="s">
-        <v>322</v>
-      </c>
-      <c r="G75" s="131" t="str">
+      <c r="E75" s="97" t="s">
+        <v>52</v>
+      </c>
+      <c r="F75" s="98" t="s">
+        <v>321</v>
+      </c>
+      <c r="G75" s="99" t="str">
         <f t="shared" si="1"/>
         <v>Ver</v>
       </c>
-      <c r="H75" s="127"/>
-      <c r="I75" s="132"/>
+      <c r="H75" s="95"/>
+      <c r="I75" s="100"/>
     </row>
     <row r="76" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B76" s="163"/>
-      <c r="C76" s="164"/>
-      <c r="D76" s="165"/>
-      <c r="E76" s="165"/>
-      <c r="F76" s="166"/>
-      <c r="G76" s="139" t="str">
+      <c r="B76" s="128"/>
+      <c r="C76" s="129"/>
+      <c r="D76" s="130"/>
+      <c r="E76" s="130"/>
+      <c r="F76" s="131"/>
+      <c r="G76" s="107" t="str">
         <f t="shared" si="1"/>
         <v>Ver</v>
       </c>
-      <c r="H76" s="164"/>
-      <c r="I76" s="115"/>
+      <c r="H76" s="129"/>
+      <c r="I76" s="85"/>
     </row>
     <row r="77" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B77" s="181" t="s">
-        <v>316</v>
-      </c>
-      <c r="C77" s="158"/>
-      <c r="D77" s="159"/>
-      <c r="E77" s="159"/>
-      <c r="F77" s="160"/>
-      <c r="G77" s="159"/>
-      <c r="H77" s="161"/>
-      <c r="I77" s="162"/>
+      <c r="B77" s="146" t="s">
+        <v>315</v>
+      </c>
+      <c r="C77" s="123"/>
+      <c r="D77" s="124"/>
+      <c r="E77" s="124"/>
+      <c r="F77" s="125"/>
+      <c r="G77" s="124"/>
+      <c r="H77" s="126"/>
+      <c r="I77" s="127"/>
     </row>
     <row r="78" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B78" s="126" t="s">
-        <v>168</v>
-      </c>
-      <c r="C78" s="176" t="s">
+      <c r="B78" s="94" t="s">
         <v>167</v>
       </c>
-      <c r="D78" s="177">
+      <c r="C78" s="141" t="s">
+        <v>166</v>
+      </c>
+      <c r="D78" s="142">
         <f>D64</f>
         <v>1435</v>
       </c>
-      <c r="E78" s="177" t="s">
-        <v>54</v>
-      </c>
-      <c r="F78" s="130" t="s">
-        <v>322</v>
-      </c>
-      <c r="G78" s="131" t="str">
+      <c r="E78" s="142" t="s">
+        <v>53</v>
+      </c>
+      <c r="F78" s="98" t="s">
+        <v>321</v>
+      </c>
+      <c r="G78" s="99" t="str">
         <f t="shared" ref="G78:G88" si="2">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F78,"/Readme.md"),"Ver")</f>
         <v>Ver</v>
       </c>
-      <c r="H78" s="127"/>
-      <c r="I78" s="132"/>
+      <c r="H78" s="95"/>
+      <c r="I78" s="100"/>
     </row>
     <row r="79" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="B79" s="126" t="s">
+      <c r="B79" s="94" t="s">
+        <v>168</v>
+      </c>
+      <c r="C79" s="141" t="s">
         <v>169</v>
       </c>
-      <c r="C79" s="176" t="s">
-        <v>170</v>
-      </c>
-      <c r="D79" s="177">
+      <c r="D79" s="142">
         <f>D78*D63</f>
         <v>57400</v>
       </c>
-      <c r="E79" s="177" t="s">
-        <v>171</v>
-      </c>
-      <c r="F79" s="130" t="s">
-        <v>322</v>
-      </c>
-      <c r="G79" s="131" t="str">
+      <c r="E79" s="142" t="s">
+        <v>170</v>
+      </c>
+      <c r="F79" s="98" t="s">
+        <v>321</v>
+      </c>
+      <c r="G79" s="99" t="str">
         <f t="shared" si="2"/>
         <v>Ver</v>
       </c>
-      <c r="H79" s="127"/>
-      <c r="I79" s="132"/>
+      <c r="H79" s="95"/>
+      <c r="I79" s="100"/>
     </row>
     <row r="80" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B80" s="126" t="s">
-        <v>180</v>
-      </c>
-      <c r="C80" s="176" t="s">
+      <c r="B80" s="94" t="s">
         <v>179</v>
       </c>
-      <c r="D80" s="177">
+      <c r="C80" s="141" t="s">
+        <v>178</v>
+      </c>
+      <c r="D80" s="142">
         <f>D49</f>
         <v>52.943999999999996</v>
       </c>
-      <c r="E80" s="177" t="s">
-        <v>54</v>
-      </c>
-      <c r="F80" s="130" t="s">
-        <v>322</v>
-      </c>
-      <c r="G80" s="131" t="str">
+      <c r="E80" s="142" t="s">
+        <v>53</v>
+      </c>
+      <c r="F80" s="98" t="s">
+        <v>321</v>
+      </c>
+      <c r="G80" s="99" t="str">
         <f t="shared" si="2"/>
         <v>Ver</v>
       </c>
-      <c r="H80" s="178"/>
-      <c r="I80" s="113"/>
+      <c r="H80" s="143"/>
+      <c r="I80" s="83"/>
     </row>
     <row r="81" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B81" s="126" t="s">
+      <c r="B81" s="94" t="s">
+        <v>172</v>
+      </c>
+      <c r="C81" s="141" t="s">
         <v>173</v>
       </c>
-      <c r="C81" s="176" t="s">
-        <v>174</v>
-      </c>
-      <c r="D81" s="177">
+      <c r="D81" s="142">
         <f>D69</f>
         <v>36</v>
       </c>
-      <c r="E81" s="177" t="s">
-        <v>115</v>
-      </c>
-      <c r="F81" s="130" t="s">
-        <v>322</v>
-      </c>
-      <c r="G81" s="131" t="str">
+      <c r="E81" s="142" t="s">
+        <v>114</v>
+      </c>
+      <c r="F81" s="98" t="s">
+        <v>321</v>
+      </c>
+      <c r="G81" s="99" t="str">
         <f t="shared" si="2"/>
         <v>Ver</v>
       </c>
-      <c r="H81" s="178"/>
-      <c r="I81" s="113"/>
+      <c r="H81" s="143"/>
+      <c r="I81" s="83"/>
     </row>
     <row r="82" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="B82" s="126" t="s">
+      <c r="B82" s="94" t="s">
+        <v>174</v>
+      </c>
+      <c r="C82" s="141" t="s">
         <v>175</v>
       </c>
-      <c r="C82" s="176" t="s">
-        <v>176</v>
-      </c>
-      <c r="D82" s="177">
+      <c r="D82" s="142">
         <f>D81*D12</f>
         <v>432</v>
       </c>
-      <c r="E82" s="177" t="s">
-        <v>53</v>
-      </c>
-      <c r="F82" s="130" t="s">
-        <v>322</v>
-      </c>
-      <c r="G82" s="131" t="str">
+      <c r="E82" s="142" t="s">
+        <v>52</v>
+      </c>
+      <c r="F82" s="98" t="s">
+        <v>321</v>
+      </c>
+      <c r="G82" s="99" t="str">
         <f t="shared" si="2"/>
         <v>Ver</v>
       </c>
-      <c r="H82" s="178"/>
-      <c r="I82" s="113"/>
+      <c r="H82" s="143"/>
+      <c r="I82" s="83"/>
     </row>
     <row r="83" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="B83" s="126" t="s">
+      <c r="B83" s="94" t="s">
+        <v>176</v>
+      </c>
+      <c r="C83" s="141" t="s">
         <v>177</v>
       </c>
-      <c r="C83" s="176" t="s">
-        <v>178</v>
-      </c>
-      <c r="D83" s="177">
+      <c r="D83" s="142">
         <f>((D67*D9)+(D68*D8))*INT(D12/D48)</f>
         <v>324</v>
       </c>
-      <c r="E83" s="177" t="s">
+      <c r="E83" s="142" t="s">
+        <v>52</v>
+      </c>
+      <c r="F83" s="98" t="s">
+        <v>321</v>
+      </c>
+      <c r="G83" s="99" t="str">
+        <f t="shared" si="2"/>
+        <v>Ver</v>
+      </c>
+      <c r="H83" s="143"/>
+      <c r="I83" s="83"/>
+    </row>
+    <row r="84" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="B84" s="94" t="s">
+        <v>187</v>
+      </c>
+      <c r="C84" s="141" t="s">
+        <v>190</v>
+      </c>
+      <c r="D84" s="144" t="s">
+        <v>189</v>
+      </c>
+      <c r="E84" s="142" t="s">
         <v>53</v>
       </c>
-      <c r="F83" s="130" t="s">
-        <v>322</v>
-      </c>
-      <c r="G83" s="131" t="str">
+      <c r="F84" s="98" t="s">
+        <v>321</v>
+      </c>
+      <c r="G84" s="99" t="str">
         <f t="shared" si="2"/>
         <v>Ver</v>
       </c>
-      <c r="H83" s="178"/>
-      <c r="I83" s="113"/>
-    </row>
-    <row r="84" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="B84" s="126" t="s">
+      <c r="H84" s="143"/>
+      <c r="I84" s="83">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="85" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B85" s="94" t="s">
         <v>188</v>
       </c>
-      <c r="C84" s="176" t="s">
+      <c r="C85" s="141" t="s">
         <v>191</v>
       </c>
-      <c r="D84" s="179" t="s">
-        <v>190</v>
-      </c>
-      <c r="E84" s="177" t="s">
-        <v>54</v>
-      </c>
-      <c r="F84" s="130" t="s">
-        <v>322</v>
-      </c>
-      <c r="G84" s="131" t="str">
+      <c r="D85" s="144">
+        <v>2</v>
+      </c>
+      <c r="E85" s="142" t="s">
+        <v>114</v>
+      </c>
+      <c r="F85" s="98" t="s">
+        <v>321</v>
+      </c>
+      <c r="G85" s="99" t="str">
         <f t="shared" si="2"/>
         <v>Ver</v>
       </c>
-      <c r="H84" s="178"/>
-      <c r="I84" s="113">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="85" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B85" s="126" t="s">
+      <c r="H85" s="143"/>
+      <c r="I85" s="83"/>
+    </row>
+    <row r="86" spans="2:9" ht="50.4" x14ac:dyDescent="0.3">
+      <c r="B86" s="94" t="s">
+        <v>45</v>
+      </c>
+      <c r="C86" s="141" t="s">
+        <v>192</v>
+      </c>
+      <c r="D86" s="144" t="s">
         <v>189</v>
       </c>
-      <c r="C85" s="176" t="s">
-        <v>192</v>
-      </c>
-      <c r="D85" s="179">
-        <v>2</v>
-      </c>
-      <c r="E85" s="177" t="s">
-        <v>115</v>
-      </c>
-      <c r="F85" s="130" t="s">
-        <v>322</v>
-      </c>
-      <c r="G85" s="131" t="str">
+      <c r="E86" s="142" t="s">
+        <v>114</v>
+      </c>
+      <c r="F86" s="98" t="s">
+        <v>321</v>
+      </c>
+      <c r="G86" s="99" t="str">
         <f t="shared" si="2"/>
         <v>Ver</v>
       </c>
-      <c r="H85" s="178"/>
-      <c r="I85" s="113"/>
-    </row>
-    <row r="86" spans="2:9" ht="50.4" x14ac:dyDescent="0.3">
-      <c r="B86" s="126" t="s">
+      <c r="H86" s="143"/>
+      <c r="I86" s="83"/>
+    </row>
+    <row r="87" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
+      <c r="B87" s="94" t="s">
         <v>46</v>
       </c>
-      <c r="C86" s="176" t="s">
+      <c r="C87" s="141" t="s">
         <v>193</v>
       </c>
-      <c r="D86" s="179" t="s">
-        <v>190</v>
-      </c>
-      <c r="E86" s="177" t="s">
-        <v>115</v>
-      </c>
-      <c r="F86" s="130" t="s">
-        <v>322</v>
-      </c>
-      <c r="G86" s="131" t="str">
+      <c r="D87" s="144" t="s">
+        <v>189</v>
+      </c>
+      <c r="E87" s="142" t="s">
+        <v>114</v>
+      </c>
+      <c r="F87" s="98" t="s">
+        <v>321</v>
+      </c>
+      <c r="G87" s="99" t="str">
         <f t="shared" si="2"/>
         <v>Ver</v>
       </c>
-      <c r="H86" s="178"/>
-      <c r="I86" s="113"/>
-    </row>
-    <row r="87" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="B87" s="126" t="s">
-        <v>47</v>
-      </c>
-      <c r="C87" s="176" t="s">
-        <v>194</v>
-      </c>
-      <c r="D87" s="179" t="s">
-        <v>190</v>
-      </c>
-      <c r="E87" s="177" t="s">
-        <v>115</v>
-      </c>
-      <c r="F87" s="130" t="s">
-        <v>322</v>
-      </c>
-      <c r="G87" s="131" t="str">
+      <c r="H87" s="143"/>
+      <c r="I87" s="83"/>
+    </row>
+    <row r="88" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B88" s="103"/>
+      <c r="C88" s="145"/>
+      <c r="D88" s="130"/>
+      <c r="E88" s="130"/>
+      <c r="F88" s="131"/>
+      <c r="G88" s="107" t="str">
         <f t="shared" si="2"/>
         <v>Ver</v>
       </c>
-      <c r="H87" s="178"/>
-      <c r="I87" s="113"/>
-    </row>
-    <row r="88" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B88" s="135"/>
-      <c r="C88" s="180"/>
-      <c r="D88" s="165"/>
-      <c r="E88" s="165"/>
-      <c r="F88" s="166"/>
-      <c r="G88" s="139" t="str">
-        <f t="shared" si="2"/>
-        <v>Ver</v>
-      </c>
-      <c r="H88" s="164"/>
-      <c r="I88" s="115"/>
+      <c r="H88" s="129"/>
+      <c r="I88" s="85"/>
     </row>
     <row r="89" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B89" s="167" t="s">
-        <v>108</v>
+      <c r="B89" s="132" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="90" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="H90" s="140" t="s">
-        <v>264</v>
-      </c>
-      <c r="I90" s="119">
+      <c r="H90" s="108" t="s">
+        <v>263</v>
+      </c>
+      <c r="I90" s="89">
         <f>AVERAGE(I7:I88)</f>
         <v>5</v>
       </c>
     </row>
     <row r="91" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B91" s="46" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="92" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B92" s="145" t="s">
+      <c r="B92" s="110" t="s">
+        <v>148</v>
+      </c>
+      <c r="C92" s="133" t="s">
         <v>149</v>
       </c>
-      <c r="C92" s="168" t="s">
+    </row>
+    <row r="93" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B93" s="134" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="93" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B93" s="169" t="s">
-        <v>151</v>
-      </c>
-      <c r="C93" s="170">
+      <c r="C93" s="135">
         <f>D17</f>
         <v>1925</v>
       </c>
     </row>
     <row r="94" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B94" s="169" t="s">
-        <v>154</v>
-      </c>
-      <c r="C94" s="170">
+      <c r="B94" s="134" t="s">
+        <v>153</v>
+      </c>
+      <c r="C94" s="135">
         <f>D18</f>
         <v>1435</v>
       </c>
     </row>
     <row r="95" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B95" s="169" t="s">
-        <v>153</v>
-      </c>
-      <c r="C95" s="170">
+      <c r="B95" s="134" t="s">
+        <v>152</v>
+      </c>
+      <c r="C95" s="135">
         <f>D46</f>
         <v>60</v>
       </c>
     </row>
     <row r="96" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B96" s="169" t="s">
-        <v>45</v>
-      </c>
-      <c r="C96" s="170">
+      <c r="B96" s="134" t="s">
+        <v>44</v>
+      </c>
+      <c r="C96" s="135">
         <f>D54</f>
         <v>7.0560000000000018</v>
       </c>
     </row>
     <row r="97" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B97" s="169" t="s">
-        <v>44</v>
-      </c>
-      <c r="C97" s="170">
+      <c r="B97" s="134" t="s">
+        <v>43</v>
+      </c>
+      <c r="C97" s="135">
         <f>D49</f>
         <v>52.943999999999996</v>
       </c>
     </row>
     <row r="98" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B98" s="171" t="s">
-        <v>152</v>
-      </c>
-      <c r="C98" s="172">
+      <c r="B98" s="136" t="s">
+        <v>151</v>
+      </c>
+      <c r="C98" s="137">
         <f>D19</f>
         <v>1495</v>
       </c>
     </row>
     <row r="99" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B99" s="173" t="s">
-        <v>66</v>
-      </c>
-      <c r="C99" s="174">
+      <c r="B99" s="138" t="s">
+        <v>65</v>
+      </c>
+      <c r="C99" s="139">
         <f>D20</f>
         <v>0.74545454545454548</v>
       </c>
     </row>
     <row r="100" spans="2:3" x14ac:dyDescent="0.3">
-      <c r="B100" s="163" t="s">
-        <v>99</v>
-      </c>
-      <c r="C100" s="175">
+      <c r="B100" s="128" t="s">
+        <v>98</v>
+      </c>
+      <c r="C100" s="140">
         <f>D21</f>
         <v>0.77662337662337666</v>
       </c>
@@ -5897,7 +5903,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDC0663E-105D-42EA-893B-DB8B7FE41FC2}">
-  <dimension ref="B2:I45"/>
+  <dimension ref="B2:I46"/>
   <sheetFormatPr defaultRowHeight="16.8" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="2.5546875" style="1" customWidth="1"/>
@@ -5914,89 +5920,89 @@
   <sheetData>
     <row r="2" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B2" s="36" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B3" s="58" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="4" spans="2:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="73" t="s">
-        <v>217</v>
-      </c>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
+      <c r="B4" s="183" t="s">
+        <v>216</v>
+      </c>
+      <c r="C4" s="183"/>
+      <c r="D4" s="183"/>
+      <c r="E4" s="183"/>
+      <c r="F4" s="183"/>
+      <c r="G4" s="183"/>
+      <c r="H4" s="183"/>
+      <c r="I4" s="183"/>
     </row>
     <row r="5" spans="2:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
+      <c r="B5" s="184"/>
+      <c r="C5" s="184"/>
+      <c r="D5" s="184"/>
+      <c r="E5" s="184"/>
+      <c r="F5" s="184"/>
+      <c r="G5" s="184"/>
+      <c r="H5" s="184"/>
+      <c r="I5" s="184"/>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B6" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="D6" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="F6" s="185" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="E6" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="F6" s="84" t="s">
-        <v>38</v>
-      </c>
-      <c r="G6" s="85"/>
+      <c r="G6" s="186"/>
       <c r="H6" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" s="40" t="s">
         <v>26</v>
-      </c>
-      <c r="I6" s="40" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B7" s="37" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="C7" s="17"/>
       <c r="D7" s="18"/>
       <c r="E7" s="18"/>
-      <c r="F7" s="88"/>
+      <c r="F7" s="65"/>
       <c r="G7" s="18"/>
       <c r="H7" s="53"/>
       <c r="I7" s="41"/>
     </row>
     <row r="8" spans="2:9" ht="57" x14ac:dyDescent="0.4">
       <c r="B8" s="16" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D8" s="15">
         <v>1</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="F8" s="86" t="s">
-        <v>322</v>
-      </c>
-      <c r="G8" s="80" t="str">
+        <v>114</v>
+      </c>
+      <c r="F8" s="63" t="s">
+        <v>321</v>
+      </c>
+      <c r="G8" s="61" t="str">
         <f t="shared" ref="G8:G21" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F8,"/Readme.md"),"Ver")</f>
         <v>Ver</v>
       </c>
@@ -6007,21 +6013,21 @@
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B9" s="16" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D9" s="15">
         <v>1</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="F9" s="86" t="s">
-        <v>322</v>
-      </c>
-      <c r="G9" s="80" t="str">
+        <v>114</v>
+      </c>
+      <c r="F9" s="63" t="s">
+        <v>321</v>
+      </c>
+      <c r="G9" s="61" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
@@ -6030,21 +6036,21 @@
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B10" s="16" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D10" s="15">
         <v>1</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="F10" s="86" t="s">
-        <v>322</v>
-      </c>
-      <c r="G10" s="80" t="str">
+        <v>114</v>
+      </c>
+      <c r="F10" s="63" t="s">
+        <v>321</v>
+      </c>
+      <c r="G10" s="61" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
@@ -6053,21 +6059,21 @@
     </row>
     <row r="11" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B11" s="16" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D11" s="15">
         <v>1</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="F11" s="86" t="s">
-        <v>322</v>
-      </c>
-      <c r="G11" s="80" t="str">
+        <v>114</v>
+      </c>
+      <c r="F11" s="63" t="s">
+        <v>321</v>
+      </c>
+      <c r="G11" s="61" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
@@ -6076,21 +6082,21 @@
     </row>
     <row r="12" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B12" s="27" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D12" s="15">
         <v>1</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="F12" s="86" t="s">
-        <v>322</v>
-      </c>
-      <c r="G12" s="80" t="str">
+        <v>114</v>
+      </c>
+      <c r="F12" s="63" t="s">
+        <v>321</v>
+      </c>
+      <c r="G12" s="61" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
@@ -6099,21 +6105,21 @@
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B13" s="27" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D13" s="15">
         <v>1</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="F13" s="86" t="s">
-        <v>322</v>
-      </c>
-      <c r="G13" s="80" t="str">
+        <v>114</v>
+      </c>
+      <c r="F13" s="63" t="s">
+        <v>321</v>
+      </c>
+      <c r="G13" s="61" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
@@ -6122,21 +6128,21 @@
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B14" s="16" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D14" s="15">
         <v>1</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="F14" s="86" t="s">
-        <v>302</v>
-      </c>
-      <c r="G14" s="80" t="str">
+        <v>114</v>
+      </c>
+      <c r="F14" s="63" t="s">
+        <v>301</v>
+      </c>
+      <c r="G14" s="61" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
@@ -6145,21 +6151,21 @@
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B15" s="16" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D15" s="15">
         <v>1</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="F15" s="86" t="s">
-        <v>302</v>
-      </c>
-      <c r="G15" s="80" t="str">
+        <v>114</v>
+      </c>
+      <c r="F15" s="63" t="s">
+        <v>301</v>
+      </c>
+      <c r="G15" s="61" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
@@ -6168,21 +6174,21 @@
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B16" s="27" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C16" s="19" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D16" s="15">
         <v>1</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="F16" s="86" t="s">
-        <v>302</v>
-      </c>
-      <c r="G16" s="80" t="str">
+        <v>114</v>
+      </c>
+      <c r="F16" s="63" t="s">
+        <v>301</v>
+      </c>
+      <c r="G16" s="61" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
@@ -6191,21 +6197,21 @@
     </row>
     <row r="17" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B17" s="27" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="C17" s="19" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D17" s="15">
         <v>1</v>
       </c>
       <c r="E17" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="F17" s="86" t="s">
-        <v>302</v>
-      </c>
-      <c r="G17" s="80" t="str">
+        <v>114</v>
+      </c>
+      <c r="F17" s="63" t="s">
+        <v>301</v>
+      </c>
+      <c r="G17" s="61" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
@@ -6214,21 +6220,21 @@
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B18" s="27" t="s">
+        <v>197</v>
+      </c>
+      <c r="C18" s="19" t="s">
         <v>198</v>
-      </c>
-      <c r="C18" s="19" t="s">
-        <v>199</v>
       </c>
       <c r="D18" s="15">
         <v>1</v>
       </c>
       <c r="E18" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="F18" s="86" t="s">
-        <v>302</v>
-      </c>
-      <c r="G18" s="80" t="str">
+        <v>114</v>
+      </c>
+      <c r="F18" s="63" t="s">
+        <v>301</v>
+      </c>
+      <c r="G18" s="61" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
@@ -6237,21 +6243,21 @@
     </row>
     <row r="19" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.4">
       <c r="B19" s="27" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C19" s="19" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="D19" s="29">
         <v>1</v>
       </c>
       <c r="E19" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="F19" s="86" t="s">
-        <v>341</v>
-      </c>
-      <c r="G19" s="80" t="str">
+        <v>114</v>
+      </c>
+      <c r="F19" s="63" t="s">
+        <v>340</v>
+      </c>
+      <c r="G19" s="61" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
@@ -6260,21 +6266,21 @@
     </row>
     <row r="20" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B20" s="27" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="C20" s="19" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D20" s="29">
         <v>1</v>
       </c>
       <c r="E20" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="F20" s="86" t="s">
-        <v>322</v>
-      </c>
-      <c r="G20" s="80" t="str">
+        <v>114</v>
+      </c>
+      <c r="F20" s="63" t="s">
+        <v>321</v>
+      </c>
+      <c r="G20" s="61" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
@@ -6286,8 +6292,8 @@
       <c r="C21" s="28"/>
       <c r="D21" s="29"/>
       <c r="E21" s="29"/>
-      <c r="F21" s="89"/>
-      <c r="G21" s="81" t="str">
+      <c r="F21" s="66"/>
+      <c r="G21" s="62" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
@@ -6296,34 +6302,34 @@
     </row>
     <row r="22" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B22" s="37" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C22" s="17"/>
       <c r="D22" s="18"/>
       <c r="E22" s="18"/>
-      <c r="F22" s="88"/>
+      <c r="F22" s="65"/>
       <c r="G22" s="18"/>
       <c r="H22" s="53"/>
       <c r="I22" s="41"/>
     </row>
     <row r="23" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.4">
       <c r="B23" s="16" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D23" s="30">
         <f>'2.ArquitectonicaEstructural'!D31-'2.ArquitectonicaEstructural'!D37-'2.ArquitectonicaEstructural'!D43</f>
         <v>1135.04</v>
       </c>
       <c r="E23" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="F23" s="86" t="s">
-        <v>299</v>
-      </c>
-      <c r="G23" s="80" t="str">
+        <v>53</v>
+      </c>
+      <c r="F23" s="63" t="s">
+        <v>298</v>
+      </c>
+      <c r="G23" s="61" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F23,"/Readme.md"),"Ver")</f>
         <v>Ver</v>
       </c>
@@ -6334,21 +6340,21 @@
     </row>
     <row r="24" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B24" s="16" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="C24" s="19" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D24" s="20">
         <v>992</v>
       </c>
       <c r="E24" s="15" t="s">
-        <v>63</v>
-      </c>
-      <c r="F24" s="86" t="s">
-        <v>299</v>
-      </c>
-      <c r="G24" s="80" t="str">
+        <v>62</v>
+      </c>
+      <c r="F24" s="63" t="s">
+        <v>298</v>
+      </c>
+      <c r="G24" s="61" t="str">
         <f t="shared" ref="G24:G27" si="1">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F24,"/Readme.md"),"Ver")</f>
         <v>Ver</v>
       </c>
@@ -6357,21 +6363,21 @@
     </row>
     <row r="25" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B25" s="16" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="C25" s="19" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D25" s="20">
         <v>1950</v>
       </c>
       <c r="E25" s="15" t="s">
-        <v>63</v>
-      </c>
-      <c r="F25" s="86" t="s">
-        <v>299</v>
-      </c>
-      <c r="G25" s="80" t="str">
+        <v>62</v>
+      </c>
+      <c r="F25" s="63" t="s">
+        <v>298</v>
+      </c>
+      <c r="G25" s="61" t="str">
         <f t="shared" si="1"/>
         <v>Ver</v>
       </c>
@@ -6380,22 +6386,22 @@
     </row>
     <row r="26" spans="2:9" ht="45.6" x14ac:dyDescent="0.4">
       <c r="B26" s="16" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C26" s="19" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D26" s="15">
         <f>INT(D23/(D24/1000*D25/1000))</f>
         <v>586</v>
       </c>
       <c r="E26" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="F26" s="86" t="s">
-        <v>299</v>
-      </c>
-      <c r="G26" s="80" t="str">
+        <v>114</v>
+      </c>
+      <c r="F26" s="63" t="s">
+        <v>298</v>
+      </c>
+      <c r="G26" s="61" t="str">
         <f t="shared" si="1"/>
         <v>Ver</v>
       </c>
@@ -6407,8 +6413,8 @@
       <c r="C27" s="25"/>
       <c r="D27" s="26"/>
       <c r="E27" s="26"/>
-      <c r="F27" s="87"/>
-      <c r="G27" s="81" t="str">
+      <c r="F27" s="64"/>
+      <c r="G27" s="62" t="str">
         <f t="shared" si="1"/>
         <v>Ver</v>
       </c>
@@ -6417,7 +6423,7 @@
     </row>
     <row r="28" spans="2:9" x14ac:dyDescent="0.4">
       <c r="H28" s="45" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="I28" s="55">
         <f>AVERAGE(I7:I27)</f>
@@ -6425,125 +6431,133 @@
       </c>
     </row>
     <row r="29" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B29" s="185" t="s">
-        <v>352</v>
+      <c r="B29" s="150" t="s">
+        <v>351</v>
       </c>
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B30" s="37" t="s">
+        <v>371</v>
+      </c>
+      <c r="C30" s="151" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="31" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B31" s="152" t="s">
+        <v>374</v>
+      </c>
+      <c r="C31" s="153" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="32" spans="2:9" x14ac:dyDescent="0.4">
+      <c r="B32" s="152" t="s">
+        <v>375</v>
+      </c>
+      <c r="C32" s="153" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="33" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B33" s="152" t="s">
+        <v>376</v>
+      </c>
+      <c r="C33" s="153" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="34" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B34" s="152" t="s">
+        <v>377</v>
+      </c>
+      <c r="C34" s="153" t="s">
+        <v>378</v>
+      </c>
+    </row>
+    <row r="35" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B35" s="154" t="s">
+        <v>381</v>
+      </c>
+      <c r="C35" s="155" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="37" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B37" s="1" t="s">
+        <v>368</v>
+      </c>
+    </row>
+    <row r="38" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B38" s="37" t="s">
+        <v>369</v>
+      </c>
+      <c r="C38" s="151" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="39" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B39" s="152" t="s">
+        <v>353</v>
+      </c>
+      <c r="C39" s="153" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="40" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B40" s="152" t="s">
         <v>357</v>
       </c>
-      <c r="C30" s="186" t="s">
+      <c r="C40" s="153" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="41" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B41" s="152" t="s">
         <v>358</v>
       </c>
-    </row>
-    <row r="31" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B31" s="187" t="s">
-        <v>353</v>
-      </c>
-      <c r="C31" s="188" t="s">
+      <c r="C41" s="153" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="42" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B42" s="152" t="s">
         <v>359</v>
       </c>
-    </row>
-    <row r="32" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B32" s="187" t="s">
+      <c r="C42" s="153" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="43" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B43" s="152" t="s">
+        <v>361</v>
+      </c>
+      <c r="C43" s="153" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="44" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B44" s="152" t="s">
+        <v>362</v>
+      </c>
+      <c r="C44" s="153" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="45" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B45" s="152" t="s">
+        <v>363</v>
+      </c>
+      <c r="C45" s="153" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="46" spans="2:3" x14ac:dyDescent="0.4">
+      <c r="B46" s="154" t="s">
         <v>354</v>
       </c>
-      <c r="C32" s="188" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="33" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B33" s="187" t="s">
+      <c r="C46" s="155" t="s">
         <v>355</v>
-      </c>
-      <c r="C33" s="188" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="34" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B34" s="189" t="s">
-        <v>356</v>
-      </c>
-      <c r="C34" s="190" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="36" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B36" s="1" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="37" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B37" s="37" t="s">
-        <v>379</v>
-      </c>
-      <c r="C37" s="186" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="38" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B38" s="187" t="s">
-        <v>363</v>
-      </c>
-      <c r="C38" s="188" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="39" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B39" s="187" t="s">
-        <v>367</v>
-      </c>
-      <c r="C39" s="188" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="40" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B40" s="187" t="s">
-        <v>368</v>
-      </c>
-      <c r="C40" s="188" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="41" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B41" s="187" t="s">
-        <v>369</v>
-      </c>
-      <c r="C41" s="188" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="42" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B42" s="187" t="s">
-        <v>371</v>
-      </c>
-      <c r="C42" s="188" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="43" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B43" s="187" t="s">
-        <v>372</v>
-      </c>
-      <c r="C43" s="188" t="s">
-        <v>375</v>
-      </c>
-    </row>
-    <row r="44" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B44" s="187" t="s">
-        <v>373</v>
-      </c>
-      <c r="C44" s="188" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="45" spans="2:3" x14ac:dyDescent="0.4">
-      <c r="B45" s="189" t="s">
-        <v>364</v>
-      </c>
-      <c r="C45" s="190" t="s">
-        <v>365</v>
       </c>
     </row>
   </sheetData>
@@ -6578,89 +6592,89 @@
   <sheetData>
     <row r="2" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B3" s="9" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
     <row r="4" spans="2:9" ht="14.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="B4" s="73" t="s">
-        <v>214</v>
-      </c>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
+      <c r="B4" s="183" t="s">
+        <v>213</v>
+      </c>
+      <c r="C4" s="183"/>
+      <c r="D4" s="183"/>
+      <c r="E4" s="183"/>
+      <c r="F4" s="183"/>
+      <c r="G4" s="183"/>
+      <c r="H4" s="183"/>
+      <c r="I4" s="183"/>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
+      <c r="B5" s="184"/>
+      <c r="C5" s="184"/>
+      <c r="D5" s="184"/>
+      <c r="E5" s="184"/>
+      <c r="F5" s="184"/>
+      <c r="G5" s="184"/>
+      <c r="H5" s="184"/>
+      <c r="I5" s="184"/>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B6" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="D6" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="F6" s="185" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="E6" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="F6" s="84" t="s">
-        <v>38</v>
-      </c>
-      <c r="G6" s="85"/>
+      <c r="G6" s="186"/>
       <c r="H6" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" s="40" t="s">
         <v>26</v>
-      </c>
-      <c r="I6" s="40" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B7" s="5" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="C7" s="17"/>
       <c r="D7" s="18"/>
       <c r="E7" s="18"/>
-      <c r="F7" s="88"/>
+      <c r="F7" s="65"/>
       <c r="G7" s="18"/>
       <c r="H7" s="53"/>
       <c r="I7" s="41"/>
     </row>
     <row r="8" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B8" s="16" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D8" s="20">
         <v>3</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="F8" s="86" t="s">
-        <v>322</v>
-      </c>
-      <c r="G8" s="80" t="str">
+        <v>52</v>
+      </c>
+      <c r="F8" s="63" t="s">
+        <v>321</v>
+      </c>
+      <c r="G8" s="61" t="str">
         <f t="shared" ref="G8:G21" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F8,"/Readme.md"),"Ver")</f>
         <v>Ver</v>
       </c>
@@ -6671,21 +6685,21 @@
     </row>
     <row r="9" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B9" s="16" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D9" s="20">
         <v>2.5</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="F9" s="86" t="s">
-        <v>322</v>
-      </c>
-      <c r="G9" s="80" t="str">
+        <v>52</v>
+      </c>
+      <c r="F9" s="63" t="s">
+        <v>321</v>
+      </c>
+      <c r="G9" s="61" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
@@ -6694,21 +6708,21 @@
     </row>
     <row r="10" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B10" s="16" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D10" s="20">
         <v>4</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>221</v>
-      </c>
-      <c r="F10" s="86" t="s">
-        <v>322</v>
-      </c>
-      <c r="G10" s="80" t="str">
+        <v>220</v>
+      </c>
+      <c r="F10" s="63" t="s">
+        <v>321</v>
+      </c>
+      <c r="G10" s="61" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
@@ -6717,21 +6731,21 @@
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B11" s="16" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D11" s="20">
         <v>2</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="F11" s="86" t="s">
-        <v>322</v>
-      </c>
-      <c r="G11" s="80" t="str">
+        <v>52</v>
+      </c>
+      <c r="F11" s="63" t="s">
+        <v>321</v>
+      </c>
+      <c r="G11" s="61" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
@@ -6740,22 +6754,22 @@
     </row>
     <row r="12" spans="2:9" ht="33.6" x14ac:dyDescent="0.4">
       <c r="B12" s="16" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D12" s="15">
         <f>D10*D11</f>
         <v>8</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="F12" s="86" t="s">
-        <v>322</v>
-      </c>
-      <c r="G12" s="80" t="str">
+        <v>52</v>
+      </c>
+      <c r="F12" s="63" t="s">
+        <v>321</v>
+      </c>
+      <c r="G12" s="61" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
@@ -6764,21 +6778,21 @@
     </row>
     <row r="13" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B13" s="16" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D13" s="20">
         <v>8</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="F13" s="86" t="s">
-        <v>322</v>
-      </c>
-      <c r="G13" s="80" t="str">
+        <v>52</v>
+      </c>
+      <c r="F13" s="63" t="s">
+        <v>321</v>
+      </c>
+      <c r="G13" s="61" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
@@ -6787,22 +6801,22 @@
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B14" s="16" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D14" s="15" t="str">
         <f>IF(D12&lt;=D13, "Cumple","No cumple")</f>
         <v>Cumple</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>234</v>
-      </c>
-      <c r="F14" s="86" t="s">
-        <v>322</v>
-      </c>
-      <c r="G14" s="80" t="str">
+        <v>233</v>
+      </c>
+      <c r="F14" s="63" t="s">
+        <v>321</v>
+      </c>
+      <c r="G14" s="61" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
@@ -6811,21 +6825,21 @@
     </row>
     <row r="15" spans="2:9" ht="33.6" x14ac:dyDescent="0.4">
       <c r="B15" s="16" t="s">
+        <v>235</v>
+      </c>
+      <c r="C15" s="19" t="s">
         <v>236</v>
-      </c>
-      <c r="C15" s="19" t="s">
-        <v>237</v>
       </c>
       <c r="D15" s="20">
         <v>60</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="F15" s="86" t="s">
-        <v>322</v>
-      </c>
-      <c r="G15" s="80" t="str">
+        <v>52</v>
+      </c>
+      <c r="F15" s="63" t="s">
+        <v>321</v>
+      </c>
+      <c r="G15" s="61" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
@@ -6834,22 +6848,22 @@
     </row>
     <row r="16" spans="2:9" ht="33.6" x14ac:dyDescent="0.4">
       <c r="B16" s="16" t="s">
+        <v>237</v>
+      </c>
+      <c r="C16" s="19" t="s">
         <v>238</v>
-      </c>
-      <c r="C16" s="19" t="s">
-        <v>239</v>
       </c>
       <c r="D16" s="15">
         <f>D15*D10</f>
         <v>240</v>
       </c>
       <c r="E16" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="F16" s="86" t="s">
-        <v>322</v>
-      </c>
-      <c r="G16" s="80" t="str">
+        <v>52</v>
+      </c>
+      <c r="F16" s="63" t="s">
+        <v>321</v>
+      </c>
+      <c r="G16" s="61" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
@@ -6861,8 +6875,8 @@
       <c r="C17" s="19"/>
       <c r="D17" s="15"/>
       <c r="E17" s="15"/>
-      <c r="F17" s="86"/>
-      <c r="G17" s="81" t="str">
+      <c r="F17" s="63"/>
+      <c r="G17" s="62" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
@@ -6871,33 +6885,33 @@
     </row>
     <row r="18" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B18" s="5" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C18" s="17"/>
       <c r="D18" s="18"/>
       <c r="E18" s="18"/>
-      <c r="F18" s="88"/>
+      <c r="F18" s="65"/>
       <c r="G18" s="18"/>
       <c r="H18" s="53"/>
       <c r="I18" s="41"/>
     </row>
     <row r="19" spans="2:9" ht="45.6" x14ac:dyDescent="0.4">
       <c r="B19" s="16" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C19" s="19" t="s">
+        <v>228</v>
+      </c>
+      <c r="D19" s="20" t="s">
         <v>229</v>
       </c>
-      <c r="D19" s="20" t="s">
-        <v>230</v>
-      </c>
       <c r="E19" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="F19" s="86" t="s">
-        <v>322</v>
-      </c>
-      <c r="G19" s="80" t="str">
+        <v>114</v>
+      </c>
+      <c r="F19" s="63" t="s">
+        <v>321</v>
+      </c>
+      <c r="G19" s="61" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
@@ -6908,21 +6922,21 @@
     </row>
     <row r="20" spans="2:9" ht="45.6" x14ac:dyDescent="0.4">
       <c r="B20" s="16" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C20" s="19" t="s">
+        <v>228</v>
+      </c>
+      <c r="D20" s="20" t="s">
         <v>229</v>
       </c>
-      <c r="D20" s="20" t="s">
-        <v>230</v>
-      </c>
       <c r="E20" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="F20" s="86" t="s">
-        <v>322</v>
-      </c>
-      <c r="G20" s="80" t="str">
+        <v>114</v>
+      </c>
+      <c r="F20" s="63" t="s">
+        <v>321</v>
+      </c>
+      <c r="G20" s="61" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
@@ -6931,21 +6945,21 @@
     </row>
     <row r="21" spans="2:9" ht="45.6" x14ac:dyDescent="0.4">
       <c r="B21" s="16" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="C21" s="19" t="s">
+        <v>228</v>
+      </c>
+      <c r="D21" s="20" t="s">
         <v>229</v>
       </c>
-      <c r="D21" s="20" t="s">
-        <v>230</v>
-      </c>
       <c r="E21" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="F21" s="86" t="s">
-        <v>322</v>
-      </c>
-      <c r="G21" s="80" t="str">
+        <v>114</v>
+      </c>
+      <c r="F21" s="63" t="s">
+        <v>321</v>
+      </c>
+      <c r="G21" s="61" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
@@ -6957,14 +6971,14 @@
       <c r="C22" s="25"/>
       <c r="D22" s="26"/>
       <c r="E22" s="26"/>
-      <c r="F22" s="87"/>
+      <c r="F22" s="64"/>
       <c r="G22" s="26"/>
       <c r="H22" s="25"/>
       <c r="I22" s="44"/>
     </row>
     <row r="23" spans="2:9" x14ac:dyDescent="0.4">
       <c r="H23" s="45" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="I23" s="55">
         <f>AVERAGE(I7:I22)</f>
@@ -7000,77 +7014,77 @@
   <sheetData>
     <row r="2" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B2" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B3" s="9" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B4" s="73" t="s">
-        <v>248</v>
-      </c>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
+      <c r="B4" s="183" t="s">
+        <v>247</v>
+      </c>
+      <c r="C4" s="183"/>
+      <c r="D4" s="183"/>
+      <c r="E4" s="183"/>
+      <c r="F4" s="183"/>
+      <c r="G4" s="183"/>
+      <c r="H4" s="183"/>
+      <c r="I4" s="183"/>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.4">
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
-      <c r="I5" s="78"/>
+      <c r="B5" s="184"/>
+      <c r="C5" s="184"/>
+      <c r="D5" s="184"/>
+      <c r="E5" s="184"/>
+      <c r="F5" s="184"/>
+      <c r="G5" s="184"/>
+      <c r="H5" s="184"/>
+      <c r="I5" s="184"/>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B6" s="21" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="22" t="s">
+      <c r="D6" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="E6" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="F6" s="187" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="E6" s="23" t="s">
-        <v>49</v>
-      </c>
-      <c r="F6" s="82" t="s">
-        <v>38</v>
-      </c>
-      <c r="G6" s="83"/>
+      <c r="G6" s="188"/>
       <c r="H6" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" s="40" t="s">
         <v>26</v>
-      </c>
-      <c r="I6" s="40" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="7" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B7" s="16" t="s">
+        <v>242</v>
+      </c>
+      <c r="C7" s="19" t="s">
         <v>243</v>
-      </c>
-      <c r="C7" s="19" t="s">
-        <v>244</v>
       </c>
       <c r="D7" s="20">
         <v>1</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="F7" s="86" t="s">
-        <v>298</v>
-      </c>
-      <c r="G7" s="80" t="str">
+        <v>114</v>
+      </c>
+      <c r="F7" s="63" t="s">
+        <v>297</v>
+      </c>
+      <c r="G7" s="61" t="str">
         <f t="shared" ref="G7:G16" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F7,"/Readme.md"),"Ver")</f>
         <v>Ver</v>
       </c>
@@ -7081,21 +7095,21 @@
     </row>
     <row r="8" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B8" s="16" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D8" s="20">
         <v>1</v>
       </c>
       <c r="E8" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="F8" s="86" t="s">
-        <v>298</v>
-      </c>
-      <c r="G8" s="80" t="str">
+        <v>114</v>
+      </c>
+      <c r="F8" s="63" t="s">
+        <v>297</v>
+      </c>
+      <c r="G8" s="61" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
@@ -7104,21 +7118,21 @@
     </row>
     <row r="9" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B9" s="16" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C9" s="19" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D9" s="20">
         <v>1</v>
       </c>
       <c r="E9" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="F9" s="86" t="s">
-        <v>298</v>
-      </c>
-      <c r="G9" s="80" t="str">
+        <v>114</v>
+      </c>
+      <c r="F9" s="63" t="s">
+        <v>297</v>
+      </c>
+      <c r="G9" s="61" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
@@ -7127,21 +7141,21 @@
     </row>
     <row r="10" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B10" s="16" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D10" s="20">
         <v>1</v>
       </c>
       <c r="E10" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="F10" s="86" t="s">
-        <v>298</v>
-      </c>
-      <c r="G10" s="80" t="str">
+        <v>114</v>
+      </c>
+      <c r="F10" s="63" t="s">
+        <v>297</v>
+      </c>
+      <c r="G10" s="61" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
@@ -7150,21 +7164,21 @@
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B11" s="16" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D11" s="20">
         <v>1</v>
       </c>
       <c r="E11" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="F11" s="86" t="s">
-        <v>298</v>
-      </c>
-      <c r="G11" s="80" t="str">
+        <v>114</v>
+      </c>
+      <c r="F11" s="63" t="s">
+        <v>297</v>
+      </c>
+      <c r="G11" s="61" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
@@ -7173,21 +7187,21 @@
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B12" s="16" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D12" s="20">
         <v>1</v>
       </c>
       <c r="E12" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="F12" s="86" t="s">
-        <v>298</v>
-      </c>
-      <c r="G12" s="80" t="str">
+        <v>114</v>
+      </c>
+      <c r="F12" s="63" t="s">
+        <v>297</v>
+      </c>
+      <c r="G12" s="61" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
@@ -7196,21 +7210,21 @@
     </row>
     <row r="13" spans="2:9" ht="33.6" x14ac:dyDescent="0.4">
       <c r="B13" s="16" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D13" s="20">
         <v>1</v>
       </c>
       <c r="E13" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="F13" s="86" t="s">
-        <v>298</v>
-      </c>
-      <c r="G13" s="80" t="str">
+        <v>114</v>
+      </c>
+      <c r="F13" s="63" t="s">
+        <v>297</v>
+      </c>
+      <c r="G13" s="61" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
@@ -7219,21 +7233,21 @@
     </row>
     <row r="14" spans="2:9" ht="22.8" x14ac:dyDescent="0.4">
       <c r="B14" s="16" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C14" s="19" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D14" s="20">
         <v>1</v>
       </c>
       <c r="E14" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="F14" s="86" t="s">
-        <v>298</v>
-      </c>
-      <c r="G14" s="80" t="str">
+        <v>114</v>
+      </c>
+      <c r="F14" s="63" t="s">
+        <v>297</v>
+      </c>
+      <c r="G14" s="61" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
@@ -7242,21 +7256,21 @@
     </row>
     <row r="15" spans="2:9" ht="33.6" x14ac:dyDescent="0.4">
       <c r="B15" s="16" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C15" s="19" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D15" s="20">
         <v>1</v>
       </c>
       <c r="E15" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="F15" s="86" t="s">
-        <v>298</v>
-      </c>
-      <c r="G15" s="80" t="str">
+        <v>114</v>
+      </c>
+      <c r="F15" s="63" t="s">
+        <v>297</v>
+      </c>
+      <c r="G15" s="61" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
@@ -7268,8 +7282,8 @@
       <c r="C16" s="25"/>
       <c r="D16" s="39"/>
       <c r="E16" s="26"/>
-      <c r="F16" s="87"/>
-      <c r="G16" s="81" t="str">
+      <c r="F16" s="64"/>
+      <c r="G16" s="62" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
@@ -7278,7 +7292,7 @@
     </row>
     <row r="17" spans="8:9" x14ac:dyDescent="0.4">
       <c r="H17" s="45" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="I17" s="55">
         <f>AVERAGE(I7:I16)</f>
@@ -7313,82 +7327,82 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B2" s="71" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" s="71"/>
-      <c r="D2" s="71"/>
-      <c r="E2" s="71"/>
-      <c r="F2" s="71"/>
-      <c r="G2" s="71"/>
-      <c r="H2" s="71"/>
+      <c r="B2" s="189" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="189"/>
+      <c r="D2" s="189"/>
+      <c r="E2" s="189"/>
+      <c r="F2" s="189"/>
+      <c r="G2" s="189"/>
+      <c r="H2" s="189"/>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B3" s="79" t="s">
+      <c r="B3" s="190" t="s">
+        <v>318</v>
+      </c>
+      <c r="C3" s="190"/>
+      <c r="D3" s="190"/>
+      <c r="E3" s="190"/>
+      <c r="F3" s="190"/>
+      <c r="G3" s="190"/>
+      <c r="H3" s="190"/>
+    </row>
+    <row r="4" spans="2:8" s="36" customFormat="1" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="183" t="s">
         <v>319</v>
       </c>
-      <c r="C3" s="79"/>
-      <c r="D3" s="79"/>
-      <c r="E3" s="79"/>
-      <c r="F3" s="79"/>
-      <c r="G3" s="79"/>
-      <c r="H3" s="79"/>
-    </row>
-    <row r="4" spans="2:8" s="36" customFormat="1" ht="16.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="73" t="s">
-        <v>320</v>
-      </c>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73"/>
-      <c r="E4" s="73"/>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
+      <c r="C4" s="183"/>
+      <c r="D4" s="183"/>
+      <c r="E4" s="183"/>
+      <c r="F4" s="183"/>
+      <c r="G4" s="183"/>
+      <c r="H4" s="183"/>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.3">
-      <c r="B5" s="78"/>
-      <c r="C5" s="78"/>
-      <c r="D5" s="78"/>
-      <c r="E5" s="78"/>
-      <c r="F5" s="78"/>
-      <c r="G5" s="78"/>
-      <c r="H5" s="78"/>
+      <c r="B5" s="184"/>
+      <c r="C5" s="184"/>
+      <c r="D5" s="184"/>
+      <c r="E5" s="184"/>
+      <c r="F5" s="184"/>
+      <c r="G5" s="184"/>
+      <c r="H5" s="184"/>
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B6" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" s="38" t="s">
+        <v>36</v>
+      </c>
+      <c r="D6" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="38" t="s">
+      <c r="E6" s="187" t="s">
         <v>37</v>
       </c>
-      <c r="D6" s="38" t="s">
-        <v>17</v>
-      </c>
-      <c r="E6" s="82" t="s">
-        <v>38</v>
-      </c>
-      <c r="F6" s="83"/>
+      <c r="F6" s="188"/>
       <c r="G6" s="38" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" s="7" t="s">
         <v>26</v>
-      </c>
-      <c r="H6" s="7" t="s">
-        <v>27</v>
       </c>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B7" s="16" t="s">
+        <v>264</v>
+      </c>
+      <c r="C7" s="19" t="s">
         <v>265</v>
       </c>
-      <c r="C7" s="19" t="s">
-        <v>266</v>
-      </c>
       <c r="D7" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E7" s="130" t="s">
-        <v>297</v>
-      </c>
-      <c r="F7" s="80" t="str">
+        <v>33</v>
+      </c>
+      <c r="E7" s="98" t="s">
+        <v>296</v>
+      </c>
+      <c r="F7" s="61" t="str">
         <f t="shared" ref="F7:F17" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",E7,"/Readme.md"),"Ver")</f>
         <v>Ver</v>
       </c>
@@ -7399,18 +7413,18 @@
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B8" s="16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C8" s="19" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="E8" s="130" t="s">
-        <v>297</v>
-      </c>
-      <c r="F8" s="80" t="str">
+        <v>29</v>
+      </c>
+      <c r="E8" s="98" t="s">
+        <v>296</v>
+      </c>
+      <c r="F8" s="61" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
@@ -7419,18 +7433,18 @@
     </row>
     <row r="9" spans="2:8" ht="91.2" x14ac:dyDescent="0.3">
       <c r="B9" s="16" t="s">
+        <v>289</v>
+      </c>
+      <c r="C9" s="19" t="s">
         <v>290</v>
       </c>
-      <c r="C9" s="19" t="s">
-        <v>291</v>
-      </c>
       <c r="D9" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E9" s="130" t="s">
-        <v>298</v>
-      </c>
-      <c r="F9" s="80" t="str">
+        <v>14</v>
+      </c>
+      <c r="E9" s="98" t="s">
+        <v>297</v>
+      </c>
+      <c r="F9" s="61" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
@@ -7439,18 +7453,18 @@
     </row>
     <row r="10" spans="2:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B10" s="16" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="C10" s="19" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="E10" s="130" t="s">
-        <v>302</v>
-      </c>
-      <c r="F10" s="80" t="str">
+        <v>30</v>
+      </c>
+      <c r="E10" s="98" t="s">
+        <v>301</v>
+      </c>
+      <c r="F10" s="61" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
@@ -7459,18 +7473,18 @@
     </row>
     <row r="11" spans="2:8" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="B11" s="16" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="C11" s="19" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="E11" s="130" t="s">
-        <v>302</v>
-      </c>
-      <c r="F11" s="80" t="str">
+        <v>31</v>
+      </c>
+      <c r="E11" s="98" t="s">
+        <v>301</v>
+      </c>
+      <c r="F11" s="61" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
@@ -7479,18 +7493,18 @@
     </row>
     <row r="12" spans="2:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B12" s="16" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="C12" s="19" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E12" s="130" t="s">
-        <v>302</v>
-      </c>
-      <c r="F12" s="80" t="str">
+        <v>32</v>
+      </c>
+      <c r="E12" s="98" t="s">
+        <v>301</v>
+      </c>
+      <c r="F12" s="61" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
@@ -7499,18 +7513,18 @@
     </row>
     <row r="13" spans="2:8" ht="22.8" x14ac:dyDescent="0.3">
       <c r="B13" s="16" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C13" s="19" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="E13" s="130" t="s">
-        <v>299</v>
-      </c>
-      <c r="F13" s="80" t="str">
+        <v>286</v>
+      </c>
+      <c r="E13" s="98" t="s">
+        <v>298</v>
+      </c>
+      <c r="F13" s="61" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
@@ -7519,18 +7533,18 @@
     </row>
     <row r="14" spans="2:8" ht="79.8" x14ac:dyDescent="0.3">
       <c r="B14" s="16" t="s">
+        <v>323</v>
+      </c>
+      <c r="C14" s="19" t="s">
         <v>324</v>
       </c>
-      <c r="C14" s="19" t="s">
-        <v>325</v>
-      </c>
       <c r="D14" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="E14" s="130" t="s">
-        <v>298</v>
-      </c>
-      <c r="F14" s="80" t="str">
+        <v>287</v>
+      </c>
+      <c r="E14" s="98" t="s">
+        <v>297</v>
+      </c>
+      <c r="F14" s="61" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
@@ -7539,16 +7553,16 @@
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B15" s="16" t="s">
+        <v>291</v>
+      </c>
+      <c r="C15" s="19" t="s">
         <v>292</v>
       </c>
-      <c r="C15" s="19" t="s">
+      <c r="D15" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>294</v>
-      </c>
       <c r="E15" s="54"/>
-      <c r="F15" s="80" t="str">
+      <c r="F15" s="61" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
@@ -7557,30 +7571,30 @@
     </row>
     <row r="16" spans="2:8" s="36" customFormat="1" ht="34.200000000000003" x14ac:dyDescent="0.3">
       <c r="B16" s="27" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C16" s="28" t="s">
-        <v>336</v>
-      </c>
-      <c r="D16" s="182" t="s">
         <v>335</v>
       </c>
-      <c r="E16" s="130" t="s">
-        <v>300</v>
-      </c>
-      <c r="F16" s="80" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="G16" s="183"/>
-      <c r="H16" s="184"/>
+      <c r="D16" s="147" t="s">
+        <v>334</v>
+      </c>
+      <c r="E16" s="98" t="s">
+        <v>299</v>
+      </c>
+      <c r="F16" s="61" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="G16" s="148"/>
+      <c r="H16" s="149"/>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B17" s="24"/>
       <c r="C17" s="25"/>
       <c r="D17" s="4"/>
       <c r="E17" s="33"/>
-      <c r="F17" s="81" t="str">
+      <c r="F17" s="62" t="str">
         <f t="shared" si="0"/>
         <v>Ver</v>
       </c>
@@ -7589,7 +7603,7 @@
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.3">
       <c r="G18" s="45" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H18" s="31">
         <f>AVERAGE(H7:H17)</f>
@@ -7623,17 +7637,17 @@
     </row>
     <row r="2" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B2" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B3" s="10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="2:2" x14ac:dyDescent="0.4">
       <c r="B4" s="11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/file/table/DAPC_ProyectoCAD.xlsx
+++ b/file/table/DAPC_ProyectoCAD.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBBDAC5E-4133-4053-A724-37D205846020}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3ED7595-ABBB-4033-9779-C8984F317693}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/file/table/DAPC_ProyectoCAD.xlsx
+++ b/file/table/DAPC_ProyectoCAD.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3ED7595-ABBB-4033-9779-C8984F317693}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A2EE24F-9202-4BF9-B3EA-7001F5A99AAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0.Inicio" sheetId="7" r:id="rId1"/>
@@ -1550,9 +1550,6 @@
     <t>Polietileno</t>
   </si>
   <si>
-    <t>Fibra de vidrio</t>
-  </si>
-  <si>
     <t>Polipropileno o nylon</t>
   </si>
   <si>
@@ -1577,9 +1574,6 @@
     <t>Polímero termoplástico.</t>
   </si>
   <si>
-    <t>Hebras de vidrio entrelazadas.</t>
-  </si>
-  <si>
     <t>* Seguido de la nota descriptiva de localización, indique el material, utilice los siguientes códigos:</t>
   </si>
   <si>
@@ -1623,6 +1617,12 @@
   </si>
   <si>
     <t>∑UDig:</t>
+  </si>
+  <si>
+    <t>RTRC</t>
+  </si>
+  <si>
+    <t>Fibra de vidrio. Reinforced Thermosetting Resin Conduit.</t>
   </si>
 </sst>
 </file>
@@ -2674,34 +2674,16 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -2716,15 +2698,6 @@
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
@@ -2737,13 +2710,40 @@
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -3126,84 +3126,84 @@
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B4" s="156" t="s">
+      <c r="B4" s="167" t="s">
         <v>34</v>
       </c>
-      <c r="C4" s="156"/>
-      <c r="D4" s="156"/>
-      <c r="E4" s="156"/>
+      <c r="C4" s="167"/>
+      <c r="D4" s="167"/>
+      <c r="E4" s="167"/>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B5" s="156"/>
-      <c r="C5" s="156"/>
-      <c r="D5" s="156"/>
-      <c r="E5" s="156"/>
+      <c r="B5" s="167"/>
+      <c r="C5" s="167"/>
+      <c r="D5" s="167"/>
+      <c r="E5" s="167"/>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B6" s="156"/>
-      <c r="C6" s="156"/>
-      <c r="D6" s="156"/>
-      <c r="E6" s="156"/>
+      <c r="B6" s="167"/>
+      <c r="C6" s="167"/>
+      <c r="D6" s="167"/>
+      <c r="E6" s="167"/>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B7" s="163" t="s">
+      <c r="B7" s="172" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="164"/>
-      <c r="D7" s="164"/>
-      <c r="E7" s="165"/>
+      <c r="C7" s="173"/>
+      <c r="D7" s="173"/>
+      <c r="E7" s="174"/>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="166" t="s">
+      <c r="B8" s="160" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="167"/>
-      <c r="D8" s="167"/>
-      <c r="E8" s="168"/>
+      <c r="C8" s="161"/>
+      <c r="D8" s="161"/>
+      <c r="E8" s="162"/>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="169" t="s">
+      <c r="B9" s="175" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="170"/>
-      <c r="D9" s="170"/>
-      <c r="E9" s="171"/>
+      <c r="C9" s="176"/>
+      <c r="D9" s="176"/>
+      <c r="E9" s="177"/>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="166" t="s">
+      <c r="B10" s="160" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="167"/>
-      <c r="D10" s="167"/>
-      <c r="E10" s="168"/>
+      <c r="C10" s="161"/>
+      <c r="D10" s="161"/>
+      <c r="E10" s="162"/>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B11" s="172"/>
-      <c r="C11" s="173"/>
-      <c r="D11" s="173"/>
-      <c r="E11" s="174"/>
+      <c r="B11" s="163"/>
+      <c r="C11" s="164"/>
+      <c r="D11" s="164"/>
+      <c r="E11" s="165"/>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B12" s="169" t="s">
+      <c r="B12" s="175" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="170"/>
-      <c r="D12" s="170"/>
-      <c r="E12" s="171"/>
+      <c r="C12" s="176"/>
+      <c r="D12" s="176"/>
+      <c r="E12" s="177"/>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="166" t="s">
+      <c r="B13" s="160" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="167"/>
-      <c r="D13" s="167"/>
-      <c r="E13" s="168"/>
+      <c r="C13" s="161"/>
+      <c r="D13" s="161"/>
+      <c r="E13" s="162"/>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B14" s="172"/>
-      <c r="C14" s="173"/>
-      <c r="D14" s="173"/>
-      <c r="E14" s="174"/>
+      <c r="B14" s="163"/>
+      <c r="C14" s="164"/>
+      <c r="D14" s="164"/>
+      <c r="E14" s="165"/>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B15" s="78" t="s">
@@ -3220,12 +3220,12 @@
       <c r="E16" s="79"/>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B17" s="177" t="s">
+      <c r="B17" s="166" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="177"/>
-      <c r="D17" s="177"/>
-      <c r="E17" s="177"/>
+      <c r="C17" s="166"/>
+      <c r="D17" s="166"/>
+      <c r="E17" s="166"/>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B18" s="47" t="s">
@@ -3383,7 +3383,7 @@
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.3">
       <c r="D29" s="86" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="E29" s="57">
         <f>SUM(E19:E28)</f>
@@ -3391,21 +3391,21 @@
       </c>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B31" s="177" t="s">
+      <c r="B31" s="166" t="s">
         <v>256</v>
       </c>
-      <c r="C31" s="177"/>
-      <c r="D31" s="177"/>
-      <c r="E31" s="177"/>
+      <c r="C31" s="166"/>
+      <c r="D31" s="166"/>
+      <c r="E31" s="166"/>
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B32" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="157" t="s">
+      <c r="C32" s="168" t="s">
         <v>35</v>
       </c>
-      <c r="D32" s="158"/>
+      <c r="D32" s="169"/>
       <c r="E32" s="48" t="s">
         <v>26</v>
       </c>
@@ -3414,10 +3414,10 @@
       <c r="B33" s="49">
         <v>1</v>
       </c>
-      <c r="C33" s="159" t="s">
+      <c r="C33" s="170" t="s">
         <v>257</v>
       </c>
-      <c r="D33" s="160"/>
+      <c r="D33" s="171"/>
       <c r="E33" s="50">
         <f>'1.Tecnica'!I19</f>
         <v>5</v>
@@ -3427,10 +3427,10 @@
       <c r="B34" s="49">
         <v>2</v>
       </c>
-      <c r="C34" s="161" t="s">
+      <c r="C34" s="156" t="s">
         <v>295</v>
       </c>
-      <c r="D34" s="162"/>
+      <c r="D34" s="157"/>
       <c r="E34" s="50">
         <f>'1.Tecnica'!I19</f>
         <v>5</v>
@@ -3440,10 +3440,10 @@
       <c r="B35" s="49">
         <v>3</v>
       </c>
-      <c r="C35" s="161" t="s">
+      <c r="C35" s="156" t="s">
         <v>258</v>
       </c>
-      <c r="D35" s="162"/>
+      <c r="D35" s="157"/>
       <c r="E35" s="50">
         <f>'3.Electrica'!I28</f>
         <v>5</v>
@@ -3466,10 +3466,10 @@
       <c r="B37" s="49">
         <v>4</v>
       </c>
-      <c r="C37" s="161" t="s">
+      <c r="C37" s="156" t="s">
         <v>259</v>
       </c>
-      <c r="D37" s="162"/>
+      <c r="D37" s="157"/>
       <c r="E37" s="50">
         <f>'5.Planos'!I17</f>
         <v>5</v>
@@ -3479,10 +3479,10 @@
       <c r="B38" s="49">
         <v>5</v>
       </c>
-      <c r="C38" s="161" t="s">
+      <c r="C38" s="156" t="s">
         <v>260</v>
       </c>
-      <c r="D38" s="162"/>
+      <c r="D38" s="157"/>
       <c r="E38" s="50">
         <f>'6.Archivos'!H18</f>
         <v>5</v>
@@ -3492,10 +3492,10 @@
       <c r="B39" s="49">
         <v>6</v>
       </c>
-      <c r="C39" s="161" t="s">
+      <c r="C39" s="156" t="s">
         <v>284</v>
       </c>
-      <c r="D39" s="162"/>
+      <c r="D39" s="157"/>
       <c r="E39" s="75">
         <v>5</v>
       </c>
@@ -3504,10 +3504,10 @@
       <c r="B40" s="51">
         <v>7</v>
       </c>
-      <c r="C40" s="175" t="s">
+      <c r="C40" s="158" t="s">
         <v>326</v>
       </c>
-      <c r="D40" s="176"/>
+      <c r="D40" s="159"/>
       <c r="E40" s="56">
         <v>5</v>
       </c>
@@ -3523,13 +3523,6 @@
     </row>
   </sheetData>
   <mergeCells count="18">
-    <mergeCell ref="C38:D38"/>
-    <mergeCell ref="C39:D39"/>
-    <mergeCell ref="C40:D40"/>
-    <mergeCell ref="B13:E14"/>
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="B31:E31"/>
-    <mergeCell ref="C37:D37"/>
     <mergeCell ref="B4:E5"/>
     <mergeCell ref="C32:D32"/>
     <mergeCell ref="C33:D33"/>
@@ -3541,6 +3534,13 @@
     <mergeCell ref="B9:E9"/>
     <mergeCell ref="B10:E11"/>
     <mergeCell ref="B12:E12"/>
+    <mergeCell ref="C38:D38"/>
+    <mergeCell ref="C39:D39"/>
+    <mergeCell ref="C40:D40"/>
+    <mergeCell ref="B13:E14"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="B31:E31"/>
+    <mergeCell ref="C37:D37"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -3581,18 +3581,18 @@
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B4" s="156" t="s">
+      <c r="B4" s="167" t="s">
         <v>261</v>
       </c>
-      <c r="C4" s="156"/>
-      <c r="D4" s="156"/>
-      <c r="E4" s="156"/>
+      <c r="C4" s="167"/>
+      <c r="D4" s="167"/>
+      <c r="E4" s="167"/>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B5" s="156"/>
-      <c r="C5" s="156"/>
-      <c r="D5" s="156"/>
-      <c r="E5" s="156"/>
+      <c r="B5" s="167"/>
+      <c r="C5" s="167"/>
+      <c r="D5" s="167"/>
+      <c r="E5" s="167"/>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B6" s="90" t="s">
@@ -3927,16 +3927,16 @@
       </c>
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B4" s="156" t="s">
+      <c r="B4" s="167" t="s">
         <v>215</v>
       </c>
-      <c r="C4" s="156"/>
-      <c r="D4" s="156"/>
-      <c r="E4" s="156"/>
-      <c r="F4" s="156"/>
-      <c r="G4" s="156"/>
-      <c r="H4" s="156"/>
-      <c r="I4" s="156"/>
+      <c r="C4" s="167"/>
+      <c r="D4" s="167"/>
+      <c r="E4" s="167"/>
+      <c r="F4" s="167"/>
+      <c r="G4" s="167"/>
+      <c r="H4" s="167"/>
+      <c r="I4" s="167"/>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.3">
       <c r="B5" s="180"/>
@@ -6437,7 +6437,7 @@
     </row>
     <row r="30" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B30" s="37" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C30" s="151" t="s">
         <v>352</v>
@@ -6445,52 +6445,52 @@
     </row>
     <row r="31" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B31" s="152" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="C31" s="153" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
     </row>
     <row r="32" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B32" s="152" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C32" s="153" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B33" s="152" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="C33" s="153" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
     </row>
     <row r="34" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B34" s="152" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C34" s="153" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B35" s="154" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C35" s="155" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
     </row>
     <row r="37" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B37" s="1" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
     </row>
     <row r="38" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B38" s="37" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C38" s="151" t="s">
         <v>352</v>
@@ -6509,47 +6509,47 @@
         <v>357</v>
       </c>
       <c r="C40" s="153" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="41" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B41" s="152" t="s">
-        <v>358</v>
+        <v>381</v>
       </c>
       <c r="C41" s="153" t="s">
-        <v>367</v>
+        <v>382</v>
       </c>
     </row>
     <row r="42" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B42" s="152" t="s">
+        <v>358</v>
+      </c>
+      <c r="C42" s="153" t="s">
         <v>359</v>
-      </c>
-      <c r="C42" s="153" t="s">
-        <v>360</v>
       </c>
     </row>
     <row r="43" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B43" s="152" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C43" s="153" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="44" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B44" s="152" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C44" s="153" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="45" spans="2:3" x14ac:dyDescent="0.4">
       <c r="B45" s="152" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C45" s="153" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
     </row>
     <row r="46" spans="2:3" x14ac:dyDescent="0.4">

--- a/file/table/DAPC_ProyectoCAD.xlsx
+++ b/file/table/DAPC_ProyectoCAD.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29121"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.DAPC\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A2EE24F-9202-4BF9-B3EA-7001F5A99AAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3B0229A-D5E9-4D1B-BA84-3172A26FBE85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30612" yWindow="-108" windowWidth="30936" windowHeight="16776" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0.Inicio" sheetId="7" r:id="rId1"/>
@@ -2205,7 +2205,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="191">
+  <cellXfs count="140">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2310,12 +2310,6 @@
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -2340,22 +2334,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2370,20 +2358,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2436,221 +2421,113 @@
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2662,28 +2539,37 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -2698,6 +2584,15 @@
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
@@ -2710,59 +2605,20 @@
       <alignment horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -2772,15 +2628,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -3100,149 +2947,149 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{82EDA320-F942-4FCE-8343-60C075021E69}">
   <dimension ref="B1:E41"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="2" width="2.5546875" style="46" customWidth="1"/>
-    <col min="3" max="3" width="50.77734375" style="46" customWidth="1"/>
-    <col min="4" max="4" width="15.77734375" style="46" customWidth="1"/>
-    <col min="5" max="5" width="12.77734375" style="46" customWidth="1"/>
-    <col min="6" max="6" width="2.5546875" style="46" customWidth="1"/>
-    <col min="7" max="16384" width="9.109375" style="46"/>
+    <col min="1" max="2" width="2.53125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="50.796875" style="2" customWidth="1"/>
+    <col min="4" max="4" width="15.796875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="12.796875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="2.53125" style="2" customWidth="1"/>
+    <col min="7" max="16384" width="9.1328125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="E1" s="76" t="s">
+    <row r="1" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="E1" s="12" t="s">
         <v>327</v>
       </c>
     </row>
-    <row r="2" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B2" s="46" t="s">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B2" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B3" s="77" t="s">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B3" s="9" t="s">
         <v>320</v>
       </c>
     </row>
-    <row r="4" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B4" s="167" t="s">
+    <row r="4" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B4" s="112" t="s">
         <v>34</v>
       </c>
-      <c r="C4" s="167"/>
-      <c r="D4" s="167"/>
-      <c r="E4" s="167"/>
-    </row>
-    <row r="5" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B5" s="167"/>
-      <c r="C5" s="167"/>
-      <c r="D5" s="167"/>
-      <c r="E5" s="167"/>
-    </row>
-    <row r="6" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B6" s="167"/>
-      <c r="C6" s="167"/>
-      <c r="D6" s="167"/>
-      <c r="E6" s="167"/>
-    </row>
-    <row r="7" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B7" s="172" t="s">
+      <c r="C4" s="112"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="112"/>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B5" s="112"/>
+      <c r="C5" s="112"/>
+      <c r="D5" s="112"/>
+      <c r="E5" s="112"/>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B6" s="112"/>
+      <c r="C6" s="112"/>
+      <c r="D6" s="112"/>
+      <c r="E6" s="112"/>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B7" s="119" t="s">
         <v>1</v>
       </c>
-      <c r="C7" s="173"/>
-      <c r="D7" s="173"/>
-      <c r="E7" s="174"/>
-    </row>
-    <row r="8" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="160" t="s">
+      <c r="C7" s="120"/>
+      <c r="D7" s="120"/>
+      <c r="E7" s="121"/>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B8" s="122" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="161"/>
-      <c r="D8" s="161"/>
-      <c r="E8" s="162"/>
-    </row>
-    <row r="9" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="175" t="s">
+      <c r="C8" s="123"/>
+      <c r="D8" s="123"/>
+      <c r="E8" s="124"/>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B9" s="125" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="176"/>
-      <c r="D9" s="176"/>
-      <c r="E9" s="177"/>
-    </row>
-    <row r="10" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="160" t="s">
+      <c r="C9" s="126"/>
+      <c r="D9" s="126"/>
+      <c r="E9" s="127"/>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B10" s="122" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="161"/>
-      <c r="D10" s="161"/>
-      <c r="E10" s="162"/>
-    </row>
-    <row r="11" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B11" s="163"/>
-      <c r="C11" s="164"/>
-      <c r="D11" s="164"/>
-      <c r="E11" s="165"/>
-    </row>
-    <row r="12" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B12" s="175" t="s">
+      <c r="C10" s="123"/>
+      <c r="D10" s="123"/>
+      <c r="E10" s="124"/>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B11" s="128"/>
+      <c r="C11" s="129"/>
+      <c r="D11" s="129"/>
+      <c r="E11" s="130"/>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B12" s="125" t="s">
         <v>19</v>
       </c>
-      <c r="C12" s="176"/>
-      <c r="D12" s="176"/>
-      <c r="E12" s="177"/>
-    </row>
-    <row r="13" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B13" s="160" t="s">
+      <c r="C12" s="126"/>
+      <c r="D12" s="126"/>
+      <c r="E12" s="127"/>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B13" s="122" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="161"/>
-      <c r="D13" s="161"/>
-      <c r="E13" s="162"/>
-    </row>
-    <row r="14" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B14" s="163"/>
-      <c r="C14" s="164"/>
-      <c r="D14" s="164"/>
-      <c r="E14" s="165"/>
-    </row>
-    <row r="15" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B15" s="78" t="s">
+      <c r="C13" s="123"/>
+      <c r="D13" s="123"/>
+      <c r="E13" s="124"/>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B14" s="128"/>
+      <c r="C14" s="129"/>
+      <c r="D14" s="129"/>
+      <c r="E14" s="130"/>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B15" s="71" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="78"/>
-      <c r="D15" s="78"/>
-      <c r="E15" s="78"/>
-    </row>
-    <row r="16" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B16" s="79"/>
-      <c r="C16" s="79"/>
-      <c r="D16" s="79"/>
-      <c r="E16" s="79"/>
-    </row>
-    <row r="17" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B17" s="166" t="s">
+      <c r="C15" s="71"/>
+      <c r="D15" s="71"/>
+      <c r="E15" s="71"/>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B16" s="72"/>
+      <c r="C16" s="72"/>
+      <c r="D16" s="72"/>
+      <c r="E16" s="72"/>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B17" s="133" t="s">
         <v>13</v>
       </c>
-      <c r="C17" s="166"/>
-      <c r="D17" s="166"/>
-      <c r="E17" s="166"/>
-    </row>
-    <row r="18" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B18" s="47" t="s">
+      <c r="C17" s="133"/>
+      <c r="D17" s="133"/>
+      <c r="E17" s="133"/>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B18" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="C18" s="80" t="s">
+      <c r="C18" s="36" t="s">
         <v>28</v>
       </c>
-      <c r="D18" s="81" t="s">
+      <c r="D18" s="73" t="s">
         <v>27</v>
       </c>
-      <c r="E18" s="48" t="s">
+      <c r="E18" s="7" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B19" s="82">
+    <row r="19" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B19" s="74">
         <v>1</v>
       </c>
       <c r="C19" s="34" t="s">
@@ -3251,13 +3098,13 @@
       <c r="D19" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="E19" s="83">
+      <c r="E19" s="8">
         <f t="shared" ref="E19:E28" si="0">IFERROR(RIGHT(D19,1)*1,0)</f>
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B20" s="82">
+    <row r="20" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B20" s="74">
         <v>2</v>
       </c>
       <c r="C20" s="34" t="s">
@@ -3266,13 +3113,13 @@
       <c r="D20" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="E20" s="83">
+      <c r="E20" s="8">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B21" s="82">
+    <row r="21" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B21" s="74">
         <v>3</v>
       </c>
       <c r="C21" s="34" t="s">
@@ -3281,13 +3128,13 @@
       <c r="D21" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="E21" s="83">
+      <c r="E21" s="8">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B22" s="82">
+    <row r="22" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B22" s="74">
         <v>4</v>
       </c>
       <c r="C22" s="34" t="s">
@@ -3296,13 +3143,13 @@
       <c r="D22" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="E22" s="83">
+      <c r="E22" s="8">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B23" s="82">
+    <row r="23" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B23" s="74">
         <v>5</v>
       </c>
       <c r="C23" s="34" t="s">
@@ -3311,229 +3158,218 @@
       <c r="D23" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="E23" s="83">
+      <c r="E23" s="8">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B24" s="82">
+    <row r="24" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B24" s="74">
         <v>6</v>
       </c>
       <c r="C24" s="34" t="s">
         <v>8</v>
       </c>
       <c r="D24" s="13"/>
-      <c r="E24" s="83">
+      <c r="E24" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B25" s="82">
+    <row r="25" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B25" s="74">
         <v>7</v>
       </c>
       <c r="C25" s="34" t="s">
         <v>8</v>
       </c>
       <c r="D25" s="13"/>
-      <c r="E25" s="83">
+      <c r="E25" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B26" s="82">
+    <row r="26" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B26" s="74">
         <v>8</v>
       </c>
       <c r="C26" s="34" t="s">
         <v>8</v>
       </c>
       <c r="D26" s="13"/>
-      <c r="E26" s="83">
+      <c r="E26" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B27" s="82">
+    <row r="27" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B27" s="74">
         <v>9</v>
       </c>
       <c r="C27" s="34" t="s">
         <v>8</v>
       </c>
       <c r="D27" s="13"/>
-      <c r="E27" s="83">
+      <c r="E27" s="8">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B28" s="84">
+    <row r="28" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B28" s="75">
         <v>10</v>
       </c>
       <c r="C28" s="35" t="s">
         <v>8</v>
       </c>
       <c r="D28" s="14"/>
-      <c r="E28" s="85">
+      <c r="E28" s="6">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="D29" s="86" t="s">
+    <row r="29" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="D29" s="76" t="s">
         <v>380</v>
       </c>
-      <c r="E29" s="57">
+      <c r="E29" s="53">
         <f>SUM(E19:E28)</f>
         <v>27</v>
       </c>
     </row>
-    <row r="31" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B31" s="166" t="s">
+    <row r="31" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B31" s="133" t="s">
         <v>256</v>
       </c>
-      <c r="C31" s="166"/>
-      <c r="D31" s="166"/>
-      <c r="E31" s="166"/>
-    </row>
-    <row r="32" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B32" s="47" t="s">
+      <c r="C31" s="133"/>
+      <c r="D31" s="133"/>
+      <c r="E31" s="133"/>
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B32" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="C32" s="168" t="s">
+      <c r="C32" s="113" t="s">
         <v>35</v>
       </c>
-      <c r="D32" s="169"/>
-      <c r="E32" s="48" t="s">
+      <c r="D32" s="114"/>
+      <c r="E32" s="7" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="33" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B33" s="49">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B33" s="45">
         <v>1</v>
       </c>
-      <c r="C33" s="170" t="s">
+      <c r="C33" s="115" t="s">
         <v>257</v>
       </c>
-      <c r="D33" s="171"/>
-      <c r="E33" s="50">
+      <c r="D33" s="116"/>
+      <c r="E33" s="46">
         <f>'1.Tecnica'!I19</f>
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B34" s="49">
+    <row r="34" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B34" s="45">
         <v>2</v>
       </c>
-      <c r="C34" s="156" t="s">
+      <c r="C34" s="117" t="s">
         <v>295</v>
       </c>
-      <c r="D34" s="157"/>
-      <c r="E34" s="50">
+      <c r="D34" s="118"/>
+      <c r="E34" s="46">
         <f>'1.Tecnica'!I19</f>
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B35" s="49">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B35" s="45">
         <v>3</v>
       </c>
-      <c r="C35" s="156" t="s">
+      <c r="C35" s="117" t="s">
         <v>258</v>
       </c>
-      <c r="D35" s="157"/>
-      <c r="E35" s="50">
+      <c r="D35" s="118"/>
+      <c r="E35" s="46">
         <f>'3.Electrica'!I28</f>
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B36" s="49">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B36" s="45">
         <v>4</v>
       </c>
-      <c r="C36" s="59" t="s">
+      <c r="C36" s="54" t="s">
         <v>294</v>
       </c>
-      <c r="D36" s="60"/>
-      <c r="E36" s="50">
+      <c r="D36" s="55"/>
+      <c r="E36" s="46">
         <f>'4.Bodegaje'!I23</f>
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B37" s="49">
+    <row r="37" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B37" s="45">
         <v>4</v>
       </c>
-      <c r="C37" s="156" t="s">
+      <c r="C37" s="117" t="s">
         <v>259</v>
       </c>
-      <c r="D37" s="157"/>
-      <c r="E37" s="50">
+      <c r="D37" s="118"/>
+      <c r="E37" s="46">
         <f>'5.Planos'!I17</f>
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B38" s="49">
+    <row r="38" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B38" s="45">
         <v>5</v>
       </c>
-      <c r="C38" s="156" t="s">
+      <c r="C38" s="117" t="s">
         <v>260</v>
       </c>
-      <c r="D38" s="157"/>
-      <c r="E38" s="50">
+      <c r="D38" s="118"/>
+      <c r="E38" s="46">
         <f>'6.Archivos'!H18</f>
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B39" s="49">
+    <row r="39" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B39" s="45">
         <v>6</v>
       </c>
-      <c r="C39" s="156" t="s">
+      <c r="C39" s="117" t="s">
         <v>284</v>
       </c>
-      <c r="D39" s="157"/>
-      <c r="E39" s="75">
+      <c r="D39" s="118"/>
+      <c r="E39" s="70">
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="B40" s="51">
+    <row r="40" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="B40" s="47">
         <v>7</v>
       </c>
-      <c r="C40" s="158" t="s">
+      <c r="C40" s="131" t="s">
         <v>326</v>
       </c>
-      <c r="D40" s="159"/>
-      <c r="E40" s="56">
+      <c r="D40" s="132"/>
+      <c r="E40" s="52">
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="2:5" x14ac:dyDescent="0.3">
-      <c r="D41" s="87" t="s">
+    <row r="41" spans="2:5" x14ac:dyDescent="0.45">
+      <c r="D41" s="77" t="s">
         <v>263</v>
       </c>
-      <c r="E41" s="57">
+      <c r="E41" s="53">
         <f>AVERAGE(E33:E40)</f>
         <v>5</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="B4:E5"/>
-    <mergeCell ref="C32:D32"/>
-    <mergeCell ref="C33:D33"/>
-    <mergeCell ref="C34:D34"/>
-    <mergeCell ref="C35:D35"/>
-    <mergeCell ref="B6:E6"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="B8:E8"/>
-    <mergeCell ref="B9:E9"/>
-    <mergeCell ref="B10:E11"/>
-    <mergeCell ref="B12:E12"/>
+  <mergeCells count="17">
     <mergeCell ref="C38:D38"/>
     <mergeCell ref="C39:D39"/>
     <mergeCell ref="C40:D40"/>
@@ -3541,6 +3377,16 @@
     <mergeCell ref="B17:E17"/>
     <mergeCell ref="B31:E31"/>
     <mergeCell ref="C37:D37"/>
+    <mergeCell ref="B4:E6"/>
+    <mergeCell ref="C32:D32"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="C34:D34"/>
+    <mergeCell ref="C35:D35"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="B8:E8"/>
+    <mergeCell ref="B9:E9"/>
+    <mergeCell ref="B10:E11"/>
+    <mergeCell ref="B12:E12"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -3553,334 +3399,334 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0659C4DD-D653-4634-8C4F-29057F021A54}">
   <dimension ref="B1:I19"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.5546875" style="46" customWidth="1"/>
-    <col min="2" max="2" width="30.77734375" style="46" customWidth="1"/>
-    <col min="3" max="3" width="50.77734375" style="46" customWidth="1"/>
-    <col min="4" max="5" width="10.77734375" style="46" customWidth="1"/>
-    <col min="6" max="6" width="7.77734375" style="46" customWidth="1"/>
-    <col min="7" max="7" width="3.77734375" style="46" customWidth="1"/>
-    <col min="8" max="8" width="30.77734375" style="88" customWidth="1"/>
-    <col min="9" max="9" width="12.77734375" style="89" customWidth="1"/>
-    <col min="10" max="10" width="2.77734375" style="46" customWidth="1"/>
-    <col min="11" max="16384" width="9.109375" style="46"/>
+    <col min="1" max="1" width="2.53125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="30.796875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="50.796875" style="2" customWidth="1"/>
+    <col min="4" max="5" width="10.796875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="7.796875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="3.796875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="30.796875" style="48" customWidth="1"/>
+    <col min="9" max="9" width="12.796875" style="31" customWidth="1"/>
+    <col min="10" max="10" width="2.796875" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="9.1328125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="E1" s="76"/>
-    </row>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B2" s="46" t="s">
+    <row r="1" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="E1" s="12"/>
+    </row>
+    <row r="2" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B2" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B3" s="77" t="s">
+    <row r="3" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B3" s="9" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B4" s="167" t="s">
+    <row r="4" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B4" s="112" t="s">
         <v>261</v>
       </c>
-      <c r="C4" s="167"/>
-      <c r="D4" s="167"/>
-      <c r="E4" s="167"/>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B5" s="167"/>
-      <c r="C5" s="167"/>
-      <c r="D5" s="167"/>
-      <c r="E5" s="167"/>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B6" s="90" t="s">
+      <c r="C4" s="112"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="112"/>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B5" s="112"/>
+      <c r="C5" s="112"/>
+      <c r="D5" s="112"/>
+      <c r="E5" s="112"/>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B6" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="91" t="s">
+      <c r="C6" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="92" t="s">
+      <c r="D6" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="E6" s="92" t="s">
+      <c r="E6" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="F6" s="178" t="s">
+      <c r="F6" s="134" t="s">
         <v>37</v>
       </c>
-      <c r="G6" s="179"/>
-      <c r="H6" s="91" t="s">
+      <c r="G6" s="135"/>
+      <c r="H6" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="93" t="s">
+      <c r="I6" s="38" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="68.400000000000006" x14ac:dyDescent="0.3">
-      <c r="B7" s="94" t="s">
+    <row r="7" spans="2:9" ht="76.5" x14ac:dyDescent="0.45">
+      <c r="B7" s="16" t="s">
         <v>262</v>
       </c>
-      <c r="C7" s="95" t="s">
+      <c r="C7" s="19" t="s">
         <v>339</v>
       </c>
-      <c r="D7" s="67">
+      <c r="D7" s="62">
         <v>1</v>
       </c>
-      <c r="E7" s="97" t="s">
+      <c r="E7" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="98" t="s">
+      <c r="F7" s="58" t="s">
         <v>322</v>
       </c>
-      <c r="G7" s="99" t="str">
+      <c r="G7" s="78" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F7,"/Readme.md"),"Ver")</f>
         <v>Ver</v>
       </c>
-      <c r="H7" s="69"/>
-      <c r="I7" s="70">
+      <c r="H7" s="64"/>
+      <c r="I7" s="65">
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B8" s="94" t="s">
+    <row r="8" spans="2:9" ht="25.5" x14ac:dyDescent="0.45">
+      <c r="B8" s="16" t="s">
         <v>266</v>
       </c>
-      <c r="C8" s="95" t="s">
+      <c r="C8" s="19" t="s">
         <v>306</v>
       </c>
-      <c r="D8" s="67">
+      <c r="D8" s="62">
         <v>1</v>
       </c>
-      <c r="E8" s="97" t="s">
+      <c r="E8" s="15" t="s">
         <v>307</v>
       </c>
-      <c r="F8" s="98" t="s">
+      <c r="F8" s="58" t="s">
         <v>296</v>
       </c>
-      <c r="G8" s="99" t="str">
+      <c r="G8" s="78" t="str">
         <f t="shared" ref="G8:G18" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F8,"/Readme.md"),"Ver")</f>
         <v>Ver</v>
       </c>
-      <c r="H8" s="69"/>
-      <c r="I8" s="70"/>
-    </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B9" s="94" t="s">
+      <c r="H8" s="64"/>
+      <c r="I8" s="65"/>
+    </row>
+    <row r="9" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B9" s="16" t="s">
         <v>264</v>
       </c>
-      <c r="C9" s="95" t="s">
+      <c r="C9" s="19" t="s">
         <v>265</v>
       </c>
-      <c r="D9" s="67" t="s">
+      <c r="D9" s="62" t="s">
         <v>308</v>
       </c>
-      <c r="E9" s="97"/>
-      <c r="F9" s="98" t="s">
+      <c r="E9" s="15"/>
+      <c r="F9" s="58" t="s">
         <v>296</v>
       </c>
-      <c r="G9" s="99" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H9" s="69"/>
-      <c r="I9" s="70"/>
-    </row>
-    <row r="10" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B10" s="94" t="s">
+      <c r="G9" s="78" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H9" s="64"/>
+      <c r="I9" s="65"/>
+    </row>
+    <row r="10" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B10" s="16" t="s">
         <v>268</v>
       </c>
-      <c r="C10" s="95" t="s">
+      <c r="C10" s="19" t="s">
         <v>269</v>
       </c>
-      <c r="D10" s="67">
+      <c r="D10" s="62">
         <v>1</v>
       </c>
-      <c r="E10" s="97" t="s">
+      <c r="E10" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="F10" s="98" t="s">
+      <c r="F10" s="58" t="s">
         <v>297</v>
       </c>
-      <c r="G10" s="99" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H10" s="69"/>
-      <c r="I10" s="70"/>
-    </row>
-    <row r="11" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="B11" s="94" t="s">
+      <c r="G10" s="78" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H10" s="64"/>
+      <c r="I10" s="65"/>
+    </row>
+    <row r="11" spans="2:9" ht="33" x14ac:dyDescent="0.45">
+      <c r="B11" s="16" t="s">
         <v>267</v>
       </c>
-      <c r="C11" s="95" t="s">
+      <c r="C11" s="19" t="s">
         <v>270</v>
       </c>
-      <c r="D11" s="67" t="s">
+      <c r="D11" s="62" t="s">
         <v>308</v>
       </c>
-      <c r="E11" s="97"/>
-      <c r="F11" s="98" t="s">
+      <c r="E11" s="15"/>
+      <c r="F11" s="58" t="s">
         <v>298</v>
       </c>
-      <c r="G11" s="99" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H11" s="69"/>
-      <c r="I11" s="70"/>
-    </row>
-    <row r="12" spans="2:9" ht="57" x14ac:dyDescent="0.3">
-      <c r="B12" s="94" t="s">
+      <c r="G11" s="78" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H11" s="64"/>
+      <c r="I11" s="65"/>
+    </row>
+    <row r="12" spans="2:9" ht="63.75" x14ac:dyDescent="0.45">
+      <c r="B12" s="16" t="s">
         <v>276</v>
       </c>
-      <c r="C12" s="95" t="s">
+      <c r="C12" s="19" t="s">
         <v>271</v>
       </c>
-      <c r="D12" s="67" t="s">
+      <c r="D12" s="62" t="s">
         <v>308</v>
       </c>
-      <c r="E12" s="97"/>
-      <c r="F12" s="98" t="s">
+      <c r="E12" s="15"/>
+      <c r="F12" s="58" t="s">
         <v>299</v>
       </c>
-      <c r="G12" s="99" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H12" s="69"/>
-      <c r="I12" s="70"/>
-    </row>
-    <row r="13" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B13" s="94" t="s">
+      <c r="G12" s="78" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H12" s="64"/>
+      <c r="I12" s="65"/>
+    </row>
+    <row r="13" spans="2:9" ht="25.5" x14ac:dyDescent="0.45">
+      <c r="B13" s="16" t="s">
         <v>277</v>
       </c>
-      <c r="C13" s="95" t="s">
+      <c r="C13" s="19" t="s">
         <v>272</v>
       </c>
-      <c r="D13" s="67" t="s">
+      <c r="D13" s="62" t="s">
         <v>308</v>
       </c>
-      <c r="E13" s="97"/>
-      <c r="F13" s="98" t="s">
+      <c r="E13" s="15"/>
+      <c r="F13" s="58" t="s">
         <v>300</v>
       </c>
-      <c r="G13" s="99" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H13" s="69"/>
-      <c r="I13" s="70"/>
-    </row>
-    <row r="14" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="B14" s="94" t="s">
+      <c r="G13" s="78" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H13" s="64"/>
+      <c r="I13" s="65"/>
+    </row>
+    <row r="14" spans="2:9" ht="33" x14ac:dyDescent="0.45">
+      <c r="B14" s="16" t="s">
         <v>278</v>
       </c>
-      <c r="C14" s="95" t="s">
+      <c r="C14" s="19" t="s">
         <v>343</v>
       </c>
-      <c r="D14" s="67" t="s">
+      <c r="D14" s="62" t="s">
         <v>308</v>
       </c>
-      <c r="E14" s="97"/>
-      <c r="F14" s="98" t="s">
+      <c r="E14" s="15"/>
+      <c r="F14" s="58" t="s">
         <v>297</v>
       </c>
-      <c r="G14" s="99" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H14" s="69"/>
-      <c r="I14" s="70"/>
-    </row>
-    <row r="15" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
-      <c r="B15" s="94" t="s">
+      <c r="G14" s="78" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H14" s="64"/>
+      <c r="I14" s="65"/>
+    </row>
+    <row r="15" spans="2:9" ht="25.5" x14ac:dyDescent="0.45">
+      <c r="B15" s="16" t="s">
         <v>273</v>
       </c>
-      <c r="C15" s="95" t="s">
+      <c r="C15" s="19" t="s">
         <v>279</v>
       </c>
-      <c r="D15" s="67">
+      <c r="D15" s="62">
         <v>1</v>
       </c>
-      <c r="E15" s="97" t="s">
+      <c r="E15" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="F15" s="98" t="s">
+      <c r="F15" s="58" t="s">
         <v>301</v>
       </c>
-      <c r="G15" s="99" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H15" s="69"/>
-      <c r="I15" s="70"/>
-    </row>
-    <row r="16" spans="2:9" ht="52.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="94" t="s">
+      <c r="G15" s="78" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H15" s="64"/>
+      <c r="I15" s="65"/>
+    </row>
+    <row r="16" spans="2:9" ht="52.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B16" s="16" t="s">
         <v>274</v>
       </c>
-      <c r="C16" s="95" t="s">
+      <c r="C16" s="19" t="s">
         <v>280</v>
       </c>
-      <c r="D16" s="67">
+      <c r="D16" s="62">
         <v>1</v>
       </c>
-      <c r="E16" s="97" t="s">
+      <c r="E16" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="F16" s="98" t="s">
+      <c r="F16" s="58" t="s">
         <v>301</v>
       </c>
-      <c r="G16" s="99" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H16" s="69"/>
-      <c r="I16" s="70"/>
-    </row>
-    <row r="17" spans="2:9" ht="35.700000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="101" t="s">
+      <c r="G16" s="78" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H16" s="64"/>
+      <c r="I16" s="65"/>
+    </row>
+    <row r="17" spans="2:9" ht="35.75" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B17" s="27" t="s">
         <v>275</v>
       </c>
-      <c r="C17" s="102" t="s">
+      <c r="C17" s="28" t="s">
         <v>281</v>
       </c>
-      <c r="D17" s="67">
+      <c r="D17" s="62">
         <v>1</v>
       </c>
-      <c r="E17" s="97" t="s">
+      <c r="E17" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="F17" s="98" t="s">
+      <c r="F17" s="58" t="s">
         <v>301</v>
       </c>
-      <c r="G17" s="99" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H17" s="71"/>
-      <c r="I17" s="72"/>
-    </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B18" s="103"/>
-      <c r="C18" s="104"/>
-      <c r="D18" s="68"/>
-      <c r="E18" s="105"/>
-      <c r="F18" s="106"/>
-      <c r="G18" s="107" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H18" s="73"/>
-      <c r="I18" s="74"/>
-    </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="H19" s="108" t="s">
+      <c r="G17" s="78" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H17" s="66"/>
+      <c r="I17" s="67"/>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B18" s="24"/>
+      <c r="C18" s="25"/>
+      <c r="D18" s="63"/>
+      <c r="E18" s="26"/>
+      <c r="F18" s="59"/>
+      <c r="G18" s="79" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H18" s="68"/>
+      <c r="I18" s="69"/>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="H19" s="43" t="s">
         <v>263</v>
       </c>
-      <c r="I19" s="89">
+      <c r="I19" s="31">
         <f>AVERAGE(I7:I18)</f>
         <v>5</v>
       </c>
@@ -3902,1988 +3748,1988 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1EE59D4-4937-4491-BD3F-7DBC007EDF85}">
   <dimension ref="B2:I100"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="16.8" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.1328125" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="2.5546875" style="46" customWidth="1"/>
-    <col min="2" max="2" width="30.77734375" style="46" customWidth="1"/>
-    <col min="3" max="3" width="50.77734375" style="46" customWidth="1"/>
-    <col min="4" max="5" width="10.77734375" style="89" customWidth="1"/>
-    <col min="6" max="6" width="7.77734375" style="109" customWidth="1"/>
-    <col min="7" max="7" width="3.77734375" style="89" customWidth="1"/>
-    <col min="8" max="8" width="30.77734375" style="88" customWidth="1"/>
-    <col min="9" max="9" width="12.77734375" style="89" customWidth="1"/>
-    <col min="10" max="10" width="2.5546875" style="46" customWidth="1"/>
-    <col min="11" max="16384" width="9.109375" style="46"/>
+    <col min="1" max="1" width="2.53125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="30.796875" style="2" customWidth="1"/>
+    <col min="3" max="3" width="50.796875" style="2" customWidth="1"/>
+    <col min="4" max="5" width="10.796875" style="31" customWidth="1"/>
+    <col min="6" max="6" width="7.796875" style="80" customWidth="1"/>
+    <col min="7" max="7" width="3.796875" style="31" customWidth="1"/>
+    <col min="8" max="8" width="30.796875" style="48" customWidth="1"/>
+    <col min="9" max="9" width="12.796875" style="31" customWidth="1"/>
+    <col min="10" max="10" width="2.53125" style="2" customWidth="1"/>
+    <col min="11" max="16384" width="9.1328125" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B2" s="46" t="s">
+    <row r="2" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B2" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="3" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B3" s="77" t="s">
+    <row r="3" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B3" s="9" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="4" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B4" s="167" t="s">
+    <row r="4" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B4" s="112" t="s">
         <v>215</v>
       </c>
-      <c r="C4" s="167"/>
-      <c r="D4" s="167"/>
-      <c r="E4" s="167"/>
-      <c r="F4" s="167"/>
-      <c r="G4" s="167"/>
-      <c r="H4" s="167"/>
-      <c r="I4" s="167"/>
-    </row>
-    <row r="5" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B5" s="180"/>
-      <c r="C5" s="180"/>
-      <c r="D5" s="180"/>
-      <c r="E5" s="180"/>
-      <c r="F5" s="180"/>
-      <c r="G5" s="180"/>
-      <c r="H5" s="180"/>
-      <c r="I5" s="180"/>
-    </row>
-    <row r="6" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B6" s="90" t="s">
+      <c r="C4" s="112"/>
+      <c r="D4" s="112"/>
+      <c r="E4" s="112"/>
+      <c r="F4" s="112"/>
+      <c r="G4" s="112"/>
+      <c r="H4" s="112"/>
+      <c r="I4" s="112"/>
+    </row>
+    <row r="5" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B5" s="136"/>
+      <c r="C5" s="136"/>
+      <c r="D5" s="136"/>
+      <c r="E5" s="136"/>
+      <c r="F5" s="136"/>
+      <c r="G5" s="136"/>
+      <c r="H5" s="136"/>
+      <c r="I5" s="136"/>
+    </row>
+    <row r="6" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B6" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="91" t="s">
+      <c r="C6" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="92" t="s">
+      <c r="D6" s="23" t="s">
         <v>47</v>
       </c>
-      <c r="E6" s="92" t="s">
+      <c r="E6" s="23" t="s">
         <v>48</v>
       </c>
-      <c r="F6" s="181" t="s">
+      <c r="F6" s="137" t="s">
         <v>37</v>
       </c>
-      <c r="G6" s="182"/>
-      <c r="H6" s="91" t="s">
+      <c r="G6" s="138"/>
+      <c r="H6" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="I6" s="93" t="s">
+      <c r="I6" s="38" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B7" s="110" t="s">
+    <row r="7" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B7" s="5" t="s">
         <v>310</v>
       </c>
-      <c r="C7" s="111"/>
-      <c r="D7" s="112"/>
-      <c r="E7" s="112"/>
-      <c r="F7" s="113"/>
-      <c r="G7" s="112"/>
-      <c r="H7" s="114"/>
-      <c r="I7" s="115"/>
-    </row>
-    <row r="8" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B8" s="94" t="s">
+      <c r="C7" s="17"/>
+      <c r="D7" s="18"/>
+      <c r="E7" s="18"/>
+      <c r="F7" s="60"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="49"/>
+      <c r="I7" s="39"/>
+    </row>
+    <row r="8" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B8" s="16" t="s">
         <v>156</v>
       </c>
-      <c r="C8" s="95" t="s">
+      <c r="C8" s="19" t="s">
         <v>158</v>
       </c>
-      <c r="D8" s="96">
+      <c r="D8" s="20">
         <v>8</v>
       </c>
-      <c r="E8" s="97" t="s">
+      <c r="E8" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="F8" s="98" t="s">
+      <c r="F8" s="58" t="s">
         <v>298</v>
       </c>
-      <c r="G8" s="99" t="str">
+      <c r="G8" s="78" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F8,"/Readme.md"),"Ver")</f>
         <v>Ver</v>
       </c>
-      <c r="H8" s="95" t="s">
+      <c r="H8" s="19" t="s">
         <v>283</v>
       </c>
-      <c r="I8" s="100">
+      <c r="I8" s="40">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B9" s="94" t="s">
+    <row r="9" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B9" s="16" t="s">
         <v>157</v>
       </c>
-      <c r="C9" s="95" t="s">
+      <c r="C9" s="19" t="s">
         <v>159</v>
       </c>
-      <c r="D9" s="96">
+      <c r="D9" s="20">
         <v>10</v>
       </c>
-      <c r="E9" s="97" t="s">
+      <c r="E9" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="F9" s="98" t="s">
+      <c r="F9" s="58" t="s">
         <v>298</v>
       </c>
-      <c r="G9" s="99" t="str">
+      <c r="G9" s="78" t="str">
         <f t="shared" ref="G9:G72" si="0">HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.DAPC/blob/main/activity/",F9,"/Readme.md"),"Ver")</f>
         <v>Ver</v>
       </c>
-      <c r="H9" s="95" t="s">
+      <c r="H9" s="19" t="s">
         <v>283</v>
       </c>
-      <c r="I9" s="100"/>
-    </row>
-    <row r="10" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B10" s="94" t="s">
+      <c r="I9" s="40"/>
+    </row>
+    <row r="10" spans="2:9" ht="25.5" x14ac:dyDescent="0.45">
+      <c r="B10" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="C10" s="95" t="s">
+      <c r="C10" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="D10" s="97">
+      <c r="D10" s="15">
         <f>D8+SumUDig</f>
         <v>35</v>
       </c>
-      <c r="E10" s="97" t="s">
+      <c r="E10" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="F10" s="98" t="s">
+      <c r="F10" s="58" t="s">
         <v>298</v>
       </c>
-      <c r="G10" s="99" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H10" s="95"/>
-      <c r="I10" s="100"/>
-    </row>
-    <row r="11" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B11" s="94" t="s">
+      <c r="G10" s="78" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H10" s="19"/>
+      <c r="I10" s="40"/>
+    </row>
+    <row r="11" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B11" s="16" t="s">
         <v>163</v>
       </c>
-      <c r="C11" s="95" t="s">
+      <c r="C11" s="19" t="s">
         <v>161</v>
       </c>
-      <c r="D11" s="97" cm="1">
+      <c r="D11" s="15" cm="1">
         <f t="array" ref="D11">D9+SumUDig</f>
         <v>37</v>
       </c>
-      <c r="E11" s="97" t="s">
+      <c r="E11" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="F11" s="98" t="s">
+      <c r="F11" s="58" t="s">
         <v>298</v>
       </c>
-      <c r="G11" s="99" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H11" s="95"/>
-      <c r="I11" s="100"/>
-    </row>
-    <row r="12" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B12" s="94" t="s">
+      <c r="G11" s="78" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H11" s="19"/>
+      <c r="I11" s="40"/>
+    </row>
+    <row r="12" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B12" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C12" s="95" t="s">
+      <c r="C12" s="19" t="s">
         <v>171</v>
       </c>
-      <c r="D12" s="96">
+      <c r="D12" s="20">
         <v>12</v>
       </c>
-      <c r="E12" s="97" t="s">
+      <c r="E12" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="F12" s="98" t="s">
+      <c r="F12" s="58" t="s">
         <v>298</v>
       </c>
-      <c r="G12" s="99" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H12" s="95" t="s">
+      <c r="G12" s="78" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H12" s="19" t="s">
         <v>283</v>
       </c>
-      <c r="I12" s="100"/>
-    </row>
-    <row r="13" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B13" s="94" t="s">
+      <c r="I12" s="40"/>
+    </row>
+    <row r="13" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B13" s="16" t="s">
         <v>59</v>
       </c>
-      <c r="C13" s="95" t="s">
+      <c r="C13" s="19" t="s">
         <v>64</v>
       </c>
-      <c r="D13" s="96">
+      <c r="D13" s="20">
         <v>6</v>
       </c>
-      <c r="E13" s="97" t="s">
+      <c r="E13" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="F13" s="98" t="s">
+      <c r="F13" s="58" t="s">
         <v>298</v>
       </c>
-      <c r="G13" s="99" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H13" s="95" t="s">
+      <c r="G13" s="78" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H13" s="19" t="s">
         <v>283</v>
       </c>
-      <c r="I13" s="100"/>
-    </row>
-    <row r="14" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B14" s="94" t="s">
+      <c r="I13" s="40"/>
+    </row>
+    <row r="14" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B14" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="C14" s="95" t="s">
+      <c r="C14" s="19" t="s">
         <v>63</v>
       </c>
-      <c r="D14" s="96">
+      <c r="D14" s="20">
         <v>12</v>
       </c>
-      <c r="E14" s="97" t="s">
+      <c r="E14" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="F14" s="98" t="s">
+      <c r="F14" s="58" t="s">
         <v>298</v>
       </c>
-      <c r="G14" s="99" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H14" s="95" t="s">
+      <c r="G14" s="78" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H14" s="19" t="s">
         <v>283</v>
       </c>
-      <c r="I14" s="100"/>
-    </row>
-    <row r="15" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B15" s="94" t="s">
+      <c r="I14" s="40"/>
+    </row>
+    <row r="15" spans="2:9" ht="25.5" x14ac:dyDescent="0.45">
+      <c r="B15" s="16" t="s">
         <v>51</v>
       </c>
-      <c r="C15" s="95" t="s">
+      <c r="C15" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="D15" s="97">
+      <c r="D15" s="15">
         <f>D10</f>
         <v>35</v>
       </c>
-      <c r="E15" s="97" t="s">
+      <c r="E15" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="F15" s="98" t="s">
+      <c r="F15" s="58" t="s">
         <v>298</v>
       </c>
-      <c r="G15" s="99" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H15" s="95"/>
-      <c r="I15" s="100"/>
-    </row>
-    <row r="16" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B16" s="94" t="s">
+      <c r="G15" s="78" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H15" s="19"/>
+      <c r="I15" s="40"/>
+    </row>
+    <row r="16" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B16" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="C16" s="95" t="s">
+      <c r="C16" s="19" t="s">
         <v>58</v>
       </c>
-      <c r="D16" s="97">
+      <c r="D16" s="15">
         <f>D11+D14+D13</f>
         <v>55</v>
       </c>
-      <c r="E16" s="97" t="s">
+      <c r="E16" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="F16" s="98" t="s">
+      <c r="F16" s="58" t="s">
         <v>298</v>
       </c>
-      <c r="G16" s="99" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H16" s="95"/>
-      <c r="I16" s="100"/>
-    </row>
-    <row r="17" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B17" s="94" t="s">
+      <c r="G16" s="78" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H16" s="19"/>
+      <c r="I16" s="40"/>
+    </row>
+    <row r="17" spans="2:9" ht="25.5" x14ac:dyDescent="0.45">
+      <c r="B17" s="16" t="s">
         <v>49</v>
       </c>
-      <c r="C17" s="95" t="s">
+      <c r="C17" s="19" t="s">
         <v>129</v>
       </c>
-      <c r="D17" s="97">
+      <c r="D17" s="15">
         <f>D16*D15</f>
         <v>1925</v>
       </c>
-      <c r="E17" s="97" t="s">
+      <c r="E17" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="F17" s="98" t="s">
+      <c r="F17" s="58" t="s">
         <v>298</v>
       </c>
-      <c r="G17" s="99" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H17" s="95"/>
-      <c r="I17" s="100"/>
-    </row>
-    <row r="18" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B18" s="101" t="s">
+      <c r="G17" s="78" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H17" s="19"/>
+      <c r="I17" s="40"/>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B18" s="27" t="s">
         <v>99</v>
       </c>
-      <c r="C18" s="102" t="s">
+      <c r="C18" s="28" t="s">
         <v>100</v>
       </c>
-      <c r="D18" s="116">
+      <c r="D18" s="29">
         <f>D32+D30</f>
         <v>1435</v>
       </c>
-      <c r="E18" s="97" t="s">
+      <c r="E18" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="F18" s="98" t="s">
+      <c r="F18" s="58" t="s">
         <v>298</v>
       </c>
-      <c r="G18" s="99" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H18" s="102"/>
-      <c r="I18" s="117"/>
-    </row>
-    <row r="19" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B19" s="101" t="s">
+      <c r="G18" s="78" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H18" s="28"/>
+      <c r="I18" s="41"/>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B19" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="C19" s="102" t="s">
+      <c r="C19" s="28" t="s">
         <v>130</v>
       </c>
-      <c r="D19" s="116">
+      <c r="D19" s="29">
         <f>D32+D30+D46</f>
         <v>1495</v>
       </c>
-      <c r="E19" s="97" t="s">
+      <c r="E19" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="F19" s="98" t="s">
+      <c r="F19" s="58" t="s">
         <v>298</v>
       </c>
-      <c r="G19" s="99" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H19" s="102"/>
-      <c r="I19" s="117"/>
-    </row>
-    <row r="20" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
-      <c r="B20" s="101" t="s">
+      <c r="G19" s="78" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H19" s="28"/>
+      <c r="I19" s="41"/>
+    </row>
+    <row r="20" spans="2:9" ht="38.25" x14ac:dyDescent="0.45">
+      <c r="B20" s="27" t="s">
         <v>65</v>
       </c>
-      <c r="C20" s="102" t="s">
+      <c r="C20" s="28" t="s">
         <v>131</v>
       </c>
-      <c r="D20" s="116">
+      <c r="D20" s="29">
         <f>D18/D17</f>
         <v>0.74545454545454548</v>
       </c>
-      <c r="E20" s="116" t="s">
+      <c r="E20" s="29" t="s">
         <v>66</v>
       </c>
-      <c r="F20" s="98" t="s">
+      <c r="F20" s="58" t="s">
         <v>298</v>
       </c>
-      <c r="G20" s="99" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H20" s="102"/>
-      <c r="I20" s="117"/>
-    </row>
-    <row r="21" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B21" s="101" t="s">
+      <c r="G20" s="78" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H20" s="28"/>
+      <c r="I20" s="41"/>
+    </row>
+    <row r="21" spans="2:9" ht="25.5" x14ac:dyDescent="0.45">
+      <c r="B21" s="27" t="s">
         <v>98</v>
       </c>
-      <c r="C21" s="102" t="s">
+      <c r="C21" s="28" t="s">
         <v>132</v>
       </c>
-      <c r="D21" s="116">
+      <c r="D21" s="29">
         <f>D19/D17</f>
         <v>0.77662337662337666</v>
       </c>
-      <c r="E21" s="116" t="s">
+      <c r="E21" s="29" t="s">
         <v>66</v>
       </c>
-      <c r="F21" s="98" t="s">
+      <c r="F21" s="58" t="s">
         <v>298</v>
       </c>
-      <c r="G21" s="99" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H21" s="102"/>
-      <c r="I21" s="117"/>
-    </row>
-    <row r="22" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B22" s="103"/>
-      <c r="C22" s="104"/>
-      <c r="D22" s="105"/>
-      <c r="E22" s="105"/>
-      <c r="F22" s="106"/>
-      <c r="G22" s="107" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H22" s="104"/>
-      <c r="I22" s="118"/>
-    </row>
-    <row r="23" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B23" s="110" t="s">
+      <c r="G21" s="78" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H21" s="28"/>
+      <c r="I21" s="41"/>
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B22" s="24"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="26"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="59"/>
+      <c r="G22" s="79" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H22" s="25"/>
+      <c r="I22" s="42"/>
+    </row>
+    <row r="23" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B23" s="5" t="s">
         <v>311</v>
       </c>
-      <c r="C23" s="111"/>
-      <c r="D23" s="112"/>
-      <c r="E23" s="112"/>
-      <c r="F23" s="113"/>
-      <c r="G23" s="112"/>
-      <c r="H23" s="114"/>
-      <c r="I23" s="115"/>
-    </row>
-    <row r="24" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
-      <c r="B24" s="94" t="s">
+      <c r="C23" s="17"/>
+      <c r="D23" s="18"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="60"/>
+      <c r="G23" s="18"/>
+      <c r="H23" s="49"/>
+      <c r="I23" s="39"/>
+    </row>
+    <row r="24" spans="2:9" ht="38.25" x14ac:dyDescent="0.45">
+      <c r="B24" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="C24" s="95" t="s">
+      <c r="C24" s="19" t="s">
         <v>133</v>
       </c>
-      <c r="D24" s="96">
+      <c r="D24" s="20">
         <v>2</v>
       </c>
-      <c r="E24" s="97" t="s">
+      <c r="E24" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="F24" s="98" t="s">
+      <c r="F24" s="58" t="s">
         <v>298</v>
       </c>
-      <c r="G24" s="99" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H24" s="95" t="s">
+      <c r="G24" s="78" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H24" s="19" t="s">
         <v>283</v>
       </c>
-      <c r="I24" s="100">
+      <c r="I24" s="40">
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="2:9" ht="57" x14ac:dyDescent="0.3">
-      <c r="B25" s="94" t="s">
+    <row r="25" spans="2:9" ht="63.75" x14ac:dyDescent="0.45">
+      <c r="B25" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="C25" s="95" t="s">
+      <c r="C25" s="19" t="s">
         <v>81</v>
       </c>
       <c r="D25" s="32">
         <v>5</v>
       </c>
-      <c r="E25" s="97" t="s">
+      <c r="E25" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="F25" s="98" t="s">
+      <c r="F25" s="58" t="s">
         <v>298</v>
       </c>
-      <c r="G25" s="99" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H25" s="95"/>
-      <c r="I25" s="100"/>
-    </row>
-    <row r="26" spans="2:9" ht="45.6" x14ac:dyDescent="0.3">
-      <c r="B26" s="94" t="s">
+      <c r="G25" s="78" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H25" s="19"/>
+      <c r="I25" s="40"/>
+    </row>
+    <row r="26" spans="2:9" ht="38.25" x14ac:dyDescent="0.45">
+      <c r="B26" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="C26" s="95" t="s">
+      <c r="C26" s="19" t="s">
         <v>69</v>
       </c>
-      <c r="D26" s="97">
+      <c r="D26" s="15">
         <f>ROUND(ATAN(D25/100)*180/PI(),0)</f>
         <v>3</v>
       </c>
-      <c r="E26" s="97" t="s">
+      <c r="E26" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="F26" s="98" t="s">
+      <c r="F26" s="58" t="s">
         <v>298</v>
       </c>
-      <c r="G26" s="99" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H26" s="95"/>
-      <c r="I26" s="100"/>
-    </row>
-    <row r="27" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B27" s="101" t="s">
+      <c r="G26" s="78" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H26" s="19"/>
+      <c r="I26" s="40"/>
+    </row>
+    <row r="27" spans="2:9" ht="25.5" x14ac:dyDescent="0.45">
+      <c r="B27" s="27" t="s">
         <v>74</v>
       </c>
-      <c r="C27" s="102" t="s">
+      <c r="C27" s="28" t="s">
         <v>309</v>
       </c>
-      <c r="D27" s="119">
+      <c r="D27" s="81">
         <v>0.6</v>
       </c>
-      <c r="E27" s="116" t="s">
+      <c r="E27" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="F27" s="98" t="s">
+      <c r="F27" s="58" t="s">
         <v>298</v>
       </c>
-      <c r="G27" s="99" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H27" s="102"/>
-      <c r="I27" s="117"/>
-    </row>
-    <row r="28" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="B28" s="94" t="s">
+      <c r="G27" s="78" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H27" s="28"/>
+      <c r="I27" s="41"/>
+    </row>
+    <row r="28" spans="2:9" ht="33" x14ac:dyDescent="0.45">
+      <c r="B28" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="C28" s="95" t="s">
+      <c r="C28" s="19" t="s">
         <v>134</v>
       </c>
-      <c r="D28" s="96">
+      <c r="D28" s="20">
         <v>0.2</v>
       </c>
-      <c r="E28" s="97" t="s">
+      <c r="E28" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="F28" s="98" t="s">
+      <c r="F28" s="58" t="s">
         <v>298</v>
       </c>
-      <c r="G28" s="99" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H28" s="95"/>
-      <c r="I28" s="100"/>
-    </row>
-    <row r="29" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B29" s="94" t="s">
+      <c r="G28" s="78" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H28" s="19"/>
+      <c r="I28" s="40"/>
+    </row>
+    <row r="29" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B29" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="C29" s="95" t="s">
+      <c r="C29" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="D29" s="96">
+      <c r="D29" s="20">
         <v>2</v>
       </c>
-      <c r="E29" s="97" t="s">
+      <c r="E29" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="F29" s="98" t="s">
+      <c r="F29" s="58" t="s">
         <v>298</v>
       </c>
-      <c r="G29" s="99" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H29" s="95"/>
-      <c r="I29" s="100"/>
-    </row>
-    <row r="30" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B30" s="101" t="s">
+      <c r="G29" s="78" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H29" s="19"/>
+      <c r="I29" s="40"/>
+    </row>
+    <row r="30" spans="2:9" ht="25.5" x14ac:dyDescent="0.45">
+      <c r="B30" s="27" t="s">
         <v>75</v>
       </c>
-      <c r="C30" s="102" t="s">
+      <c r="C30" s="28" t="s">
         <v>136</v>
       </c>
-      <c r="D30" s="116">
+      <c r="D30" s="29">
         <f>(D27-D28)*(D11+D24+D24)*D29</f>
         <v>32.799999999999997</v>
       </c>
-      <c r="E30" s="97" t="s">
+      <c r="E30" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="F30" s="98" t="s">
+      <c r="F30" s="58" t="s">
         <v>298</v>
       </c>
-      <c r="G30" s="99" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H30" s="102"/>
-      <c r="I30" s="117"/>
-    </row>
-    <row r="31" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
-      <c r="B31" s="94" t="s">
+      <c r="G30" s="78" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H30" s="28"/>
+      <c r="I30" s="41"/>
+    </row>
+    <row r="31" spans="2:9" ht="25.5" x14ac:dyDescent="0.45">
+      <c r="B31" s="16" t="s">
         <v>138</v>
       </c>
-      <c r="C31" s="95" t="s">
+      <c r="C31" s="19" t="s">
         <v>140</v>
       </c>
-      <c r="D31" s="97">
+      <c r="D31" s="15">
         <f>(D10*D11)-D30</f>
         <v>1262.2</v>
       </c>
-      <c r="E31" s="97" t="s">
+      <c r="E31" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="F31" s="98" t="s">
+      <c r="F31" s="58" t="s">
         <v>298</v>
       </c>
-      <c r="G31" s="99" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H31" s="95"/>
-      <c r="I31" s="100"/>
-    </row>
-    <row r="32" spans="2:9" ht="45.6" x14ac:dyDescent="0.3">
-      <c r="B32" s="94" t="s">
+      <c r="G31" s="78" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H31" s="19"/>
+      <c r="I31" s="40"/>
+    </row>
+    <row r="32" spans="2:9" ht="38.25" x14ac:dyDescent="0.45">
+      <c r="B32" s="16" t="s">
         <v>139</v>
       </c>
-      <c r="C32" s="95" t="s">
+      <c r="C32" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="D32" s="97">
+      <c r="D32" s="15">
         <f>((D10*D11)+D10*(D24+D24))-D30</f>
         <v>1402.2</v>
       </c>
-      <c r="E32" s="97" t="s">
+      <c r="E32" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="F32" s="98" t="s">
+      <c r="F32" s="58" t="s">
         <v>298</v>
       </c>
-      <c r="G32" s="99" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H32" s="95"/>
-      <c r="I32" s="100"/>
-    </row>
-    <row r="33" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B33" s="94" t="s">
+      <c r="G32" s="78" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H32" s="19"/>
+      <c r="I32" s="40"/>
+    </row>
+    <row r="33" spans="2:9" ht="25.5" x14ac:dyDescent="0.45">
+      <c r="B33" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="C33" s="95" t="s">
+      <c r="C33" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="D33" s="96">
+      <c r="D33" s="20">
         <v>10</v>
       </c>
-      <c r="E33" s="97" t="s">
+      <c r="E33" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="F33" s="98" t="s">
+      <c r="F33" s="58" t="s">
         <v>321</v>
       </c>
-      <c r="G33" s="99" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H33" s="95"/>
-      <c r="I33" s="100"/>
-    </row>
-    <row r="34" spans="2:9" ht="45.6" x14ac:dyDescent="0.3">
-      <c r="B34" s="94" t="s">
+      <c r="G33" s="78" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H33" s="19"/>
+      <c r="I33" s="40"/>
+    </row>
+    <row r="34" spans="2:9" ht="38.25" x14ac:dyDescent="0.45">
+      <c r="B34" s="16" t="s">
         <v>77</v>
       </c>
-      <c r="C34" s="95" t="s">
+      <c r="C34" s="19" t="s">
         <v>142</v>
       </c>
-      <c r="D34" s="97">
+      <c r="D34" s="15">
         <f>EVEN(D31/(D33*D33))</f>
         <v>14</v>
       </c>
-      <c r="E34" s="97" t="s">
+      <c r="E34" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="F34" s="98" t="s">
+      <c r="F34" s="58" t="s">
         <v>321</v>
       </c>
-      <c r="G34" s="99" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H34" s="95"/>
-      <c r="I34" s="100"/>
-    </row>
-    <row r="35" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B35" s="94" t="s">
+      <c r="G34" s="78" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H34" s="19"/>
+      <c r="I34" s="40"/>
+    </row>
+    <row r="35" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B35" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="C35" s="95" t="s">
+      <c r="C35" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="D35" s="96">
+      <c r="D35" s="20">
         <v>1200</v>
       </c>
-      <c r="E35" s="97" t="s">
+      <c r="E35" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="F35" s="98" t="s">
+      <c r="F35" s="58" t="s">
         <v>321</v>
       </c>
-      <c r="G35" s="99" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H35" s="95"/>
-      <c r="I35" s="100"/>
-    </row>
-    <row r="36" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
-      <c r="B36" s="94" t="s">
+      <c r="G35" s="78" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H35" s="19"/>
+      <c r="I35" s="40"/>
+    </row>
+    <row r="36" spans="2:9" ht="38.25" x14ac:dyDescent="0.45">
+      <c r="B36" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="C36" s="95" t="s">
+      <c r="C36" s="19" t="s">
         <v>329</v>
       </c>
-      <c r="D36" s="97">
+      <c r="D36" s="15">
         <f>D35*D35/(1000*1000)</f>
         <v>1.44</v>
       </c>
-      <c r="E36" s="97" t="s">
+      <c r="E36" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="F36" s="98" t="s">
+      <c r="F36" s="58" t="s">
         <v>321</v>
       </c>
-      <c r="G36" s="99" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H36" s="95"/>
-      <c r="I36" s="100"/>
-    </row>
-    <row r="37" spans="2:9" ht="33.6" x14ac:dyDescent="0.3">
-      <c r="B37" s="94" t="s">
+      <c r="G36" s="78" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H36" s="19"/>
+      <c r="I36" s="40"/>
+    </row>
+    <row r="37" spans="2:9" ht="33" x14ac:dyDescent="0.45">
+      <c r="B37" s="16" t="s">
         <v>80</v>
       </c>
-      <c r="C37" s="95" t="s">
+      <c r="C37" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="D37" s="97">
+      <c r="D37" s="15">
         <f>D34*D36</f>
         <v>20.16</v>
       </c>
-      <c r="E37" s="97" t="s">
+      <c r="E37" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="F37" s="98" t="s">
+      <c r="F37" s="58" t="s">
         <v>321</v>
       </c>
-      <c r="G37" s="99" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H37" s="95"/>
-      <c r="I37" s="100"/>
-    </row>
-    <row r="38" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B38" s="103"/>
-      <c r="C38" s="104"/>
-      <c r="D38" s="105"/>
-      <c r="E38" s="105"/>
-      <c r="F38" s="106"/>
-      <c r="G38" s="107" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H38" s="104"/>
-      <c r="I38" s="118"/>
-    </row>
-    <row r="39" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B39" s="120" t="s">
+      <c r="G37" s="78" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H37" s="19"/>
+      <c r="I37" s="40"/>
+    </row>
+    <row r="38" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B38" s="24"/>
+      <c r="C38" s="25"/>
+      <c r="D38" s="26"/>
+      <c r="E38" s="26"/>
+      <c r="F38" s="59"/>
+      <c r="G38" s="79" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H38" s="25"/>
+      <c r="I38" s="42"/>
+    </row>
+    <row r="39" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B39" s="82" t="s">
         <v>330</v>
       </c>
-      <c r="C39" s="111"/>
-      <c r="D39" s="112"/>
-      <c r="E39" s="112"/>
-      <c r="F39" s="113"/>
-      <c r="G39" s="112"/>
-      <c r="H39" s="114"/>
-      <c r="I39" s="115"/>
-    </row>
-    <row r="40" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B40" s="94" t="s">
+      <c r="C39" s="17"/>
+      <c r="D39" s="18"/>
+      <c r="E39" s="18"/>
+      <c r="F39" s="60"/>
+      <c r="G39" s="18"/>
+      <c r="H39" s="49"/>
+      <c r="I39" s="39"/>
+    </row>
+    <row r="40" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B40" s="16" t="s">
         <v>331</v>
       </c>
-      <c r="C40" s="95" t="s">
+      <c r="C40" s="19" t="s">
         <v>85</v>
       </c>
-      <c r="D40" s="96">
+      <c r="D40" s="20">
         <v>1</v>
       </c>
-      <c r="E40" s="97" t="s">
+      <c r="E40" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="F40" s="98" t="s">
+      <c r="F40" s="58" t="s">
         <v>298</v>
       </c>
-      <c r="G40" s="99" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H40" s="95"/>
-      <c r="I40" s="100">
+      <c r="G40" s="78" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H40" s="19"/>
+      <c r="I40" s="40">
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B41" s="94" t="s">
+    <row r="41" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B41" s="16" t="s">
         <v>82</v>
       </c>
-      <c r="C41" s="95" t="s">
+      <c r="C41" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="D41" s="96">
+      <c r="D41" s="20">
         <v>15</v>
       </c>
-      <c r="E41" s="97" t="s">
+      <c r="E41" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="F41" s="98" t="s">
+      <c r="F41" s="58" t="s">
         <v>298</v>
       </c>
-      <c r="G41" s="99" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H41" s="95"/>
-      <c r="I41" s="100"/>
-    </row>
-    <row r="42" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B42" s="94" t="s">
+      <c r="G41" s="78" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H41" s="19"/>
+      <c r="I41" s="40"/>
+    </row>
+    <row r="42" spans="2:9" ht="25.5" x14ac:dyDescent="0.45">
+      <c r="B42" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="C42" s="95" t="s">
+      <c r="C42" s="19" t="s">
         <v>332</v>
       </c>
-      <c r="D42" s="97">
+      <c r="D42" s="15">
         <f>D11+(INT(D11/D41)*D10)</f>
         <v>107</v>
       </c>
-      <c r="E42" s="97" t="s">
+      <c r="E42" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="F42" s="98" t="s">
+      <c r="F42" s="58" t="s">
         <v>298</v>
       </c>
-      <c r="G42" s="99" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H42" s="95"/>
-      <c r="I42" s="100"/>
-    </row>
-    <row r="43" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B43" s="94" t="s">
+      <c r="G42" s="78" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H42" s="19"/>
+      <c r="I42" s="40"/>
+    </row>
+    <row r="43" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B43" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="C43" s="95" t="s">
+      <c r="C43" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="D43" s="97">
+      <c r="D43" s="15">
         <f>D42*D40</f>
         <v>107</v>
       </c>
-      <c r="E43" s="97" t="s">
+      <c r="E43" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="F43" s="98" t="s">
+      <c r="F43" s="58" t="s">
         <v>298</v>
       </c>
-      <c r="G43" s="99" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H43" s="95"/>
-      <c r="I43" s="100"/>
-    </row>
-    <row r="44" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B44" s="103"/>
-      <c r="C44" s="104"/>
-      <c r="D44" s="105"/>
-      <c r="E44" s="105"/>
-      <c r="F44" s="106"/>
-      <c r="G44" s="107" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H44" s="104"/>
-      <c r="I44" s="118"/>
-    </row>
-    <row r="45" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B45" s="110" t="s">
+      <c r="G43" s="78" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H43" s="19"/>
+      <c r="I43" s="40"/>
+    </row>
+    <row r="44" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B44" s="24"/>
+      <c r="C44" s="25"/>
+      <c r="D44" s="26"/>
+      <c r="E44" s="26"/>
+      <c r="F44" s="59"/>
+      <c r="G44" s="79" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H44" s="25"/>
+      <c r="I44" s="42"/>
+    </row>
+    <row r="45" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B45" s="5" t="s">
         <v>312</v>
       </c>
-      <c r="C45" s="111"/>
-      <c r="D45" s="112"/>
-      <c r="E45" s="112"/>
-      <c r="F45" s="113"/>
-      <c r="G45" s="112"/>
-      <c r="H45" s="114"/>
-      <c r="I45" s="115"/>
-    </row>
-    <row r="46" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
-      <c r="B46" s="94" t="s">
+      <c r="C45" s="17"/>
+      <c r="D45" s="18"/>
+      <c r="E45" s="18"/>
+      <c r="F45" s="60"/>
+      <c r="G45" s="18"/>
+      <c r="H45" s="49"/>
+      <c r="I45" s="39"/>
+    </row>
+    <row r="46" spans="2:9" ht="38.25" x14ac:dyDescent="0.45">
+      <c r="B46" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="C46" s="95" t="s">
+      <c r="C46" s="19" t="s">
         <v>313</v>
       </c>
-      <c r="D46" s="96">
+      <c r="D46" s="20">
         <v>60</v>
       </c>
-      <c r="E46" s="97" t="s">
+      <c r="E46" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="F46" s="98" t="s">
+      <c r="F46" s="58" t="s">
         <v>298</v>
       </c>
-      <c r="G46" s="99" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H46" s="95"/>
-      <c r="I46" s="100">
+      <c r="G46" s="78" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H46" s="19"/>
+      <c r="I46" s="40">
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="2:9" ht="34.200000000000003" x14ac:dyDescent="0.3">
-      <c r="B47" s="94" t="s">
+    <row r="47" spans="2:9" ht="38.25" x14ac:dyDescent="0.45">
+      <c r="B47" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="C47" s="95" t="s">
+      <c r="C47" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="D47" s="96">
+      <c r="D47" s="20">
         <v>24</v>
       </c>
-      <c r="E47" s="97" t="s">
+      <c r="E47" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="F47" s="98" t="s">
+      <c r="F47" s="58" t="s">
         <v>298</v>
       </c>
-      <c r="G47" s="99" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H47" s="95"/>
-      <c r="I47" s="100"/>
-    </row>
-    <row r="48" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B48" s="94" t="s">
+      <c r="G47" s="78" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H47" s="19"/>
+      <c r="I47" s="40"/>
+    </row>
+    <row r="48" spans="2:9" ht="25.5" x14ac:dyDescent="0.45">
+      <c r="B48" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="C48" s="95" t="s">
+      <c r="C48" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="D48" s="96">
+      <c r="D48" s="20">
         <v>3.9900000000000007</v>
       </c>
-      <c r="E48" s="97" t="s">
+      <c r="E48" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="F48" s="98" t="s">
+      <c r="F48" s="58" t="s">
         <v>298</v>
       </c>
-      <c r="G48" s="99" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H48" s="95"/>
-      <c r="I48" s="100"/>
-    </row>
-    <row r="49" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B49" s="94" t="s">
+      <c r="G48" s="78" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H48" s="19"/>
+      <c r="I48" s="40"/>
+    </row>
+    <row r="49" spans="2:9" ht="25.5" x14ac:dyDescent="0.45">
+      <c r="B49" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="C49" s="95" t="s">
+      <c r="C49" s="19" t="s">
         <v>144</v>
       </c>
-      <c r="D49" s="97">
+      <c r="D49" s="15">
         <f>D46-D54</f>
         <v>52.943999999999996</v>
       </c>
-      <c r="E49" s="97" t="s">
+      <c r="E49" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="F49" s="98" t="s">
+      <c r="F49" s="58" t="s">
         <v>298</v>
       </c>
-      <c r="G49" s="99" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H49" s="95"/>
-      <c r="I49" s="100"/>
-    </row>
-    <row r="50" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B50" s="94" t="s">
+      <c r="G49" s="78" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H49" s="19"/>
+      <c r="I49" s="40"/>
+    </row>
+    <row r="50" spans="2:9" ht="25.5" x14ac:dyDescent="0.45">
+      <c r="B50" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="C50" s="95" t="s">
+      <c r="C50" s="19" t="s">
         <v>55</v>
       </c>
-      <c r="D50" s="96">
+      <c r="D50" s="20">
         <v>28</v>
       </c>
-      <c r="E50" s="97" t="s">
+      <c r="E50" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="F50" s="98" t="s">
+      <c r="F50" s="58" t="s">
         <v>298</v>
       </c>
-      <c r="G50" s="99" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H50" s="95"/>
-      <c r="I50" s="100"/>
-    </row>
-    <row r="51" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B51" s="94" t="s">
+      <c r="G50" s="78" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H50" s="19"/>
+      <c r="I50" s="40"/>
+    </row>
+    <row r="51" spans="2:9" ht="25.5" x14ac:dyDescent="0.45">
+      <c r="B51" s="16" t="s">
         <v>92</v>
       </c>
-      <c r="C51" s="95" t="s">
+      <c r="C51" s="19" t="s">
         <v>57</v>
       </c>
-      <c r="D51" s="96">
+      <c r="D51" s="20">
         <v>19</v>
       </c>
-      <c r="E51" s="97" t="s">
+      <c r="E51" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="F51" s="98" t="s">
+      <c r="F51" s="58" t="s">
         <v>298</v>
       </c>
-      <c r="G51" s="99" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H51" s="95"/>
-      <c r="I51" s="100"/>
-    </row>
-    <row r="52" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B52" s="94" t="s">
+      <c r="G51" s="78" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H51" s="19"/>
+      <c r="I51" s="40"/>
+    </row>
+    <row r="52" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B52" s="16" t="s">
         <v>90</v>
       </c>
-      <c r="C52" s="95" t="s">
+      <c r="C52" s="19" t="s">
         <v>91</v>
       </c>
-      <c r="D52" s="97">
+      <c r="D52" s="15">
         <f>D48/(D51/100)</f>
         <v>21.000000000000004</v>
       </c>
-      <c r="E52" s="97" t="s">
+      <c r="E52" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="F52" s="98" t="s">
+      <c r="F52" s="58" t="s">
         <v>298</v>
       </c>
-      <c r="G52" s="99" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H52" s="95"/>
-      <c r="I52" s="100"/>
-    </row>
-    <row r="53" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B53" s="94" t="s">
+      <c r="G52" s="78" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H52" s="19"/>
+      <c r="I52" s="40"/>
+    </row>
+    <row r="53" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B53" s="16" t="s">
         <v>93</v>
       </c>
-      <c r="C53" s="95" t="s">
+      <c r="C53" s="19" t="s">
         <v>94</v>
       </c>
-      <c r="D53" s="96">
+      <c r="D53" s="20">
         <v>1.2</v>
       </c>
-      <c r="E53" s="97" t="s">
+      <c r="E53" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="F53" s="98" t="s">
+      <c r="F53" s="58" t="s">
         <v>298</v>
       </c>
-      <c r="G53" s="99" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H53" s="95"/>
-      <c r="I53" s="100"/>
-    </row>
-    <row r="54" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B54" s="94" t="s">
+      <c r="G53" s="78" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H53" s="19"/>
+      <c r="I53" s="40"/>
+    </row>
+    <row r="54" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B54" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="C54" s="95" t="s">
+      <c r="C54" s="19" t="s">
         <v>96</v>
       </c>
-      <c r="D54" s="121">
+      <c r="D54" s="30">
         <f>D53*D52*(D50/100)</f>
         <v>7.0560000000000018</v>
       </c>
-      <c r="E54" s="97" t="s">
+      <c r="E54" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="F54" s="98" t="s">
+      <c r="F54" s="58" t="s">
         <v>298</v>
       </c>
-      <c r="G54" s="99" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H54" s="95"/>
-      <c r="I54" s="100"/>
-    </row>
-    <row r="55" spans="2:9" ht="68.400000000000006" x14ac:dyDescent="0.3">
-      <c r="B55" s="94" t="s">
+      <c r="G54" s="78" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H54" s="19"/>
+      <c r="I54" s="40"/>
+    </row>
+    <row r="55" spans="2:9" ht="76.5" x14ac:dyDescent="0.45">
+      <c r="B55" s="16" t="s">
         <v>124</v>
       </c>
-      <c r="C55" s="95" t="s">
+      <c r="C55" s="19" t="s">
         <v>183</v>
       </c>
-      <c r="D55" s="96">
+      <c r="D55" s="20">
         <v>6</v>
       </c>
-      <c r="E55" s="97" t="s">
+      <c r="E55" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="F55" s="98" t="s">
+      <c r="F55" s="58" t="s">
         <v>301</v>
       </c>
-      <c r="G55" s="99" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H55" s="95"/>
-      <c r="I55" s="100"/>
-    </row>
-    <row r="56" spans="2:9" ht="68.400000000000006" x14ac:dyDescent="0.3">
-      <c r="B56" s="94" t="s">
+      <c r="G55" s="78" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H55" s="19"/>
+      <c r="I55" s="40"/>
+    </row>
+    <row r="56" spans="2:9" ht="76.5" x14ac:dyDescent="0.45">
+      <c r="B56" s="16" t="s">
         <v>125</v>
       </c>
-      <c r="C56" s="95" t="s">
+      <c r="C56" s="19" t="s">
         <v>184</v>
       </c>
-      <c r="D56" s="96">
+      <c r="D56" s="20">
         <v>4.5</v>
       </c>
-      <c r="E56" s="97" t="s">
+      <c r="E56" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="F56" s="98" t="s">
+      <c r="F56" s="58" t="s">
         <v>301</v>
       </c>
-      <c r="G56" s="99" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H56" s="95"/>
-      <c r="I56" s="100"/>
-    </row>
-    <row r="57" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B57" s="94" t="s">
+      <c r="G56" s="78" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H56" s="19"/>
+      <c r="I56" s="40"/>
+    </row>
+    <row r="57" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B57" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="C57" s="95" t="s">
+      <c r="C57" s="19" t="s">
         <v>126</v>
       </c>
-      <c r="D57" s="96">
+      <c r="D57" s="20">
         <v>1.2</v>
       </c>
-      <c r="E57" s="97" t="s">
+      <c r="E57" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="F57" s="98" t="s">
+      <c r="F57" s="58" t="s">
         <v>301</v>
       </c>
-      <c r="G57" s="99" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H57" s="95"/>
-      <c r="I57" s="100"/>
-    </row>
-    <row r="58" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B58" s="94" t="s">
+      <c r="G57" s="78" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H57" s="19"/>
+      <c r="I57" s="40"/>
+    </row>
+    <row r="58" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B58" s="16" t="s">
         <v>181</v>
       </c>
-      <c r="C58" s="95" t="s">
+      <c r="C58" s="19" t="s">
         <v>182</v>
       </c>
-      <c r="D58" s="96">
+      <c r="D58" s="20">
         <v>2.2999999999999998</v>
       </c>
-      <c r="E58" s="97" t="s">
+      <c r="E58" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="F58" s="98" t="s">
+      <c r="F58" s="58" t="s">
         <v>301</v>
       </c>
-      <c r="G58" s="99" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H58" s="95"/>
-      <c r="I58" s="100"/>
-    </row>
-    <row r="59" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B59" s="94" t="s">
+      <c r="G58" s="78" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H58" s="19"/>
+      <c r="I58" s="40"/>
+    </row>
+    <row r="59" spans="2:9" ht="25.5" x14ac:dyDescent="0.45">
+      <c r="B59" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="C59" s="95" t="s">
+      <c r="C59" s="19" t="s">
         <v>185</v>
       </c>
-      <c r="D59" s="96">
+      <c r="D59" s="20">
         <v>3</v>
       </c>
-      <c r="E59" s="97" t="s">
+      <c r="E59" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="F59" s="98" t="s">
+      <c r="F59" s="58" t="s">
         <v>301</v>
       </c>
-      <c r="G59" s="99" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H59" s="95"/>
-      <c r="I59" s="100"/>
-    </row>
-    <row r="60" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B60" s="94" t="s">
+      <c r="G59" s="78" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H59" s="19"/>
+      <c r="I59" s="40"/>
+    </row>
+    <row r="60" spans="2:9" ht="25.5" x14ac:dyDescent="0.45">
+      <c r="B60" s="16" t="s">
         <v>180</v>
       </c>
-      <c r="C60" s="95" t="s">
+      <c r="C60" s="19" t="s">
         <v>186</v>
       </c>
-      <c r="D60" s="96">
+      <c r="D60" s="20">
         <v>2</v>
       </c>
-      <c r="E60" s="97" t="s">
+      <c r="E60" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="F60" s="98" t="s">
+      <c r="F60" s="58" t="s">
         <v>301</v>
       </c>
-      <c r="G60" s="99" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H60" s="95"/>
-      <c r="I60" s="100"/>
-    </row>
-    <row r="61" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B61" s="103"/>
-      <c r="C61" s="104"/>
-      <c r="D61" s="105"/>
-      <c r="E61" s="105"/>
-      <c r="F61" s="106"/>
-      <c r="G61" s="107" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H61" s="104"/>
-      <c r="I61" s="118"/>
-    </row>
-    <row r="62" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B62" s="122" t="s">
+      <c r="G60" s="78" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H60" s="19"/>
+      <c r="I60" s="40"/>
+    </row>
+    <row r="61" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B61" s="24"/>
+      <c r="C61" s="25"/>
+      <c r="D61" s="26"/>
+      <c r="E61" s="26"/>
+      <c r="F61" s="59"/>
+      <c r="G61" s="79" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H61" s="25"/>
+      <c r="I61" s="42"/>
+    </row>
+    <row r="62" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B62" s="83" t="s">
         <v>314</v>
       </c>
-      <c r="C62" s="123"/>
-      <c r="D62" s="124"/>
-      <c r="E62" s="124"/>
-      <c r="F62" s="125"/>
-      <c r="G62" s="124"/>
-      <c r="H62" s="126"/>
-      <c r="I62" s="127"/>
-    </row>
-    <row r="63" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B63" s="94" t="s">
+      <c r="C62" s="84"/>
+      <c r="D62" s="85"/>
+      <c r="E62" s="85"/>
+      <c r="F62" s="86"/>
+      <c r="G62" s="85"/>
+      <c r="H62" s="87"/>
+      <c r="I62" s="88"/>
+    </row>
+    <row r="63" spans="2:9" ht="25.5" x14ac:dyDescent="0.45">
+      <c r="B63" s="16" t="s">
         <v>164</v>
       </c>
-      <c r="C63" s="95" t="s">
+      <c r="C63" s="19" t="s">
         <v>102</v>
       </c>
-      <c r="D63" s="96">
+      <c r="D63" s="20">
         <v>40</v>
       </c>
-      <c r="E63" s="97" t="s">
+      <c r="E63" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="F63" s="98" t="s">
+      <c r="F63" s="58" t="s">
         <v>321</v>
       </c>
-      <c r="G63" s="99" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H63" s="95"/>
-      <c r="I63" s="100">
+      <c r="G63" s="78" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H63" s="19"/>
+      <c r="I63" s="40">
         <v>5</v>
       </c>
     </row>
-    <row r="64" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B64" s="94" t="s">
+    <row r="64" spans="2:9" x14ac:dyDescent="0.45">
+      <c r="B64" s="16" t="s">
         <v>336</v>
       </c>
-      <c r="C64" s="95" t="s">
+      <c r="C64" s="19" t="s">
         <v>165</v>
       </c>
-      <c r="D64" s="121">
+      <c r="D64" s="30">
         <f>D18</f>
         <v>1435</v>
       </c>
-      <c r="E64" s="97" t="s">
+      <c r="E64" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="F64" s="98" t="s">
+      <c r="F64" s="58" t="s">
         <v>321</v>
       </c>
-      <c r="G64" s="99" t="str">
-        <f t="shared" si="0"/>
-        <v>Ver</v>
-      </c>
-      <c r="H64" s="95"/>
-      <c r="I64" s="100"/>
-    </row>
-    <row r="65" spans="2:9" ht="22.8" x14ac:dyDescent="0.3">
-      <c r="B65" s="94" t="s">
+      <c r="G64" s="78" t="str">
+        <f t="shared" si="0"/>
+        <v>Ver</v>
+      </c>
+      <c r="H64" s="19"/>
+      <c r="I64" s="40"/>
+    </row>
+    <row r="65" spans="2:9" ht="25.5" x14ac:dyDescent="0.45">
+      <c r="B65" s="16" t="s">
         <v>101</